--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F64568-FC6F-0643-8871-FB320EDB0AF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02831D26-4027-47C5-924D-AF6DA727E147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1260" windowWidth="28680" windowHeight="17120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="0" windowWidth="30180" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="142">
   <si>
     <t>##var</t>
   </si>
@@ -61,16 +61,6 @@
     <t>itemTips</t>
   </si>
   <si>
-    <t>sourceTips</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>subType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>icon</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -79,105 +69,18 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>quality</t>
-  </si>
-  <si>
-    <t>operate</t>
-  </si>
-  <si>
-    <t>useParam</t>
-  </si>
-  <si>
-    <t>overlying</t>
-  </si>
-  <si>
-    <t>sortId</t>
-  </si>
-  <si>
-    <t>金币</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏内基础货币</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>木头</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>建筑材料</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>伐木场获得</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>%s售出</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1#1001#10</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>石头</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>采石场获得</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1#1001#20</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试不同类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1#1001#999</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>品质（0白色1绿色2蓝色3紫色4橙色5红色）</t>
-  </si>
-  <si>
     <t>道具id</t>
   </si>
   <si>
     <t>道具名称</t>
   </si>
   <si>
-    <t>获取途径</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
-    <t>子类型</t>
-  </si>
-  <si>
-    <t>道具图标</t>
-  </si>
-  <si>
     <t>道具模型</t>
   </si>
   <si>
-    <t>按钮</t>
-  </si>
-  <si>
-    <t>使用效果</t>
-  </si>
-  <si>
-    <t>堆叠数量</t>
-  </si>
-  <si>
-    <t>仓库排序</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
@@ -193,34 +96,472 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>道具获取途径，后面关联多语言表</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1基础资源2建筑材料3测试类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>填工程内文件名称</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>0白色1绿色2蓝色3紫色4橙色5红色</t>
-  </si>
-  <si>
-    <t>按钮文本，后面可能会改成枚举类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1#道具id#数量 获得道具</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>仓库单个位置最大堆叠数，如果为-1不限制</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>仓库中道具排序，ortId字段从小到大质&gt;quality从大到小&gt;id从小到大</t>
+    <t>土豆</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘑菇</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>南瓜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡萝卜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>水甜菜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-红</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-橙</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-黄</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-绿</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-青</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-蓝</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-紫</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>猕猴桃</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>野草</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>洒水壶</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>莲叶</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘑菇-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>南瓜-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡萝卜-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>水甜菜-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-红-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-橙-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-黄-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-绿-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-青-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-蓝-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-紫-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>猕猴桃-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>野草-巨大作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆-种子袋</t>
+  </si>
+  <si>
+    <t>蘑菇-种子袋</t>
+  </si>
+  <si>
+    <t>南瓜-种子袋</t>
+  </si>
+  <si>
+    <t>胡萝卜-种子袋</t>
+  </si>
+  <si>
+    <t>水甜菜-种子袋</t>
+  </si>
+  <si>
+    <t>番茄-红-种子袋</t>
+  </si>
+  <si>
+    <t>番茄-橙-种子袋</t>
+  </si>
+  <si>
+    <t>番茄-黄-种子袋</t>
+  </si>
+  <si>
+    <t>番茄-绿-种子袋</t>
+  </si>
+  <si>
+    <t>番茄-青-种子袋</t>
+  </si>
+  <si>
+    <t>番茄-蓝-种子袋</t>
+  </si>
+  <si>
+    <t>番茄-紫-种子袋</t>
+  </si>
+  <si>
+    <t>土豆-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘑菇-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>南瓜-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡萝卜-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>水甜菜-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-红-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-橙-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-黄-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-绿-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-青-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-蓝-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-紫-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>猕猴桃-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>野草-迷你作物</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1有碰撞 2无碰撞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景内碰撞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景内碰撞效果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里只是备注，具体逻辑还需要程序来实现</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>播放音效</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹飞触碰到的道具，玩家</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景内碰撞音效</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>工程内音效名称</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>不倒翁</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无效果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>染色</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>滚动的更远</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>保龄球音效</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓶子音效</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>台球音效</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除染色</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆-存储</t>
+  </si>
+  <si>
+    <t>蘑菇-存储</t>
+  </si>
+  <si>
+    <t>南瓜-存储</t>
+  </si>
+  <si>
+    <t>胡萝卜-存储</t>
+  </si>
+  <si>
+    <t>水甜菜-存储</t>
+  </si>
+  <si>
+    <t>番茄-红-存储</t>
+  </si>
+  <si>
+    <t>番茄-橙-存储</t>
+  </si>
+  <si>
+    <t>番茄-黄-存储</t>
+  </si>
+  <si>
+    <t>番茄-绿-存储</t>
+  </si>
+  <si>
+    <t>番茄-青-存储</t>
+  </si>
+  <si>
+    <t>番茄-蓝-存储</t>
+  </si>
+  <si>
+    <t>番茄-紫-存储</t>
+  </si>
+  <si>
+    <t>花椰菜-存储</t>
+  </si>
+  <si>
+    <t>猕猴桃-存储</t>
+  </si>
+  <si>
+    <t>野草-存储</t>
+  </si>
+  <si>
+    <t>道具模型大小</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>大小参数 工程内size</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞入碰到的作物/玩家，吞下作物1s吐出（此时不会吞下其他作物/玩家，玩家也无法交互），吞下玩家，玩家模型消失，屏幕显示南瓜头（玩家此时只能按任意方向键从按下的方向键出来）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>作物成熟时效果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>太久没收获，变成5个自动收获</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪烁</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>高度直接5倍</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>有物品碰到，往周围浇一圈水</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>有物品碰到，染色，浇水</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>碰到播放音效，“咩”</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞下时效果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家速度*2，按键反向</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家头闪烁，看到隐藏物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家模型变大，相机抬高，视野变大</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>到处染色喷水</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>变成保龄球，滚动走</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃下后可以和羊npc对话</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具类型 1种子袋 2作物 3巨大作物 4迷你作物 5特殊</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否看染色</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1可以 2不可以</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜-种子袋(一次性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜-种子袋(永久)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜(永久)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>drawing</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>collision</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>sound</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>eat_Effect</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>maturity_Effect</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>collision_Effect</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜汤</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemType</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -232,7 +573,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -240,7 +581,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -248,7 +589,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -257,7 +598,7 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -266,7 +607,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -274,20 +615,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +644,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,7 +756,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -438,9 +785,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -713,17 +1072,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O180"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O192"/>
+  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.1640625" style="1"/>
     <col min="3" max="3" width="22.83203125" style="1" customWidth="1"/>
-    <col min="4" max="11" width="12.1640625" style="1"/>
-    <col min="12" max="12" width="29.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.08203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.75" style="1" customWidth="1"/>
+    <col min="10" max="11" width="12.1640625" style="1"/>
+    <col min="12" max="12" width="14.9140625" style="1" customWidth="1"/>
     <col min="13" max="16384" width="12.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -737,42 +1102,39 @@
         <v>7</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>3</v>
@@ -781,22 +1143,22 @@
         <v>3</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="G2" s="6" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="I2" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="J2" s="6" t="s">
         <v>3</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="K2" s="6" t="s">
         <v>3</v>
@@ -805,1091 +1167,1862 @@
         <v>3</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>47</v>
+        <v>18</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>110</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>49</v>
+        <v>78</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="L4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="9">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="D5" s="9"/>
+      <c r="E5" s="9">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9">
+        <v>1</v>
+      </c>
+      <c r="K5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="9">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="D6" s="9"/>
+      <c r="E6" s="9">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9">
+        <v>1</v>
+      </c>
+      <c r="K6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="9">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1001</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="1">
-        <v>11001</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1">
-        <v>11001</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="1">
-        <v>999</v>
-      </c>
-      <c r="N6" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1">
-        <v>11002</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1">
-        <v>11002</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="1">
-        <v>10</v>
-      </c>
-      <c r="N7" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9">
+        <v>1</v>
+      </c>
+      <c r="K7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="1">
-        <v>21001</v>
+      <c r="B8" s="9">
+        <v>1004</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3</v>
-      </c>
-      <c r="H8" s="1">
-        <v>21001</v>
-      </c>
-      <c r="J8" s="1">
-        <v>4</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="1">
-        <v>999</v>
-      </c>
-      <c r="N8" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1</v>
+      </c>
+      <c r="I8" s="9">
+        <v>1</v>
+      </c>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B9" s="9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="9">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9">
+        <v>1</v>
+      </c>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="9">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9">
+        <v>1</v>
+      </c>
+      <c r="H11" s="9">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9">
+        <v>1</v>
+      </c>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="9">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1</v>
+      </c>
+      <c r="I12" s="9">
+        <v>1</v>
+      </c>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B13" s="9">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9">
+        <v>1</v>
+      </c>
+      <c r="H13" s="9">
+        <v>1</v>
+      </c>
+      <c r="I13" s="9">
+        <v>1</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B14" s="9">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9">
+        <v>1</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B15" s="9">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9">
+        <v>1</v>
+      </c>
+      <c r="I15" s="9">
+        <v>1</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B16" s="9">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9">
+        <v>1</v>
+      </c>
+      <c r="I16" s="9">
+        <v>1</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="B17" s="9">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>130</v>
+      </c>
       <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="3"/>
+      <c r="E17" s="9">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9">
+        <v>1</v>
+      </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>131</v>
+      </c>
       <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="E18" s="9">
+        <v>1</v>
+      </c>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="H18" s="9">
+        <v>1</v>
+      </c>
+      <c r="I18" s="9">
+        <v>1</v>
+      </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="C20" s="9"/>
+    </row>
+    <row r="19" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11">
+        <v>2001</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11">
+        <v>2</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11">
+        <v>1</v>
+      </c>
+      <c r="I19" s="11">
+        <v>1</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9">
+        <v>2002</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>20</v>
+      </c>
       <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="C21" s="9"/>
+      <c r="E20" s="9">
+        <v>2</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9">
+        <v>1</v>
+      </c>
+      <c r="I20" s="9">
+        <v>1</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="N20" s="9"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9">
+        <v>2003</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>21</v>
+      </c>
       <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="E21" s="9">
+        <v>2</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9">
+        <v>1</v>
+      </c>
+      <c r="I21" s="9">
+        <v>1</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="C22" s="9"/>
+      <c r="L21" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="N21" s="9"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9">
+        <v>2004</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>22</v>
+      </c>
       <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="C23" s="9"/>
+      <c r="E22" s="9">
+        <v>2</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9">
+        <v>1</v>
+      </c>
+      <c r="I22" s="9">
+        <v>1</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="N22" s="9"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9">
+        <v>2005</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>23</v>
+      </c>
       <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="E23" s="9">
+        <v>2</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9">
+        <v>1</v>
+      </c>
+      <c r="I23" s="9">
+        <v>1</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>87</v>
+      </c>
       <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L23" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="N23" s="9"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9">
+        <v>2006</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9">
+        <v>2</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9">
+        <v>1</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N24" s="9"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9">
+        <v>2007</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9">
+        <v>2</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9">
+        <v>1</v>
+      </c>
+      <c r="I25" s="9">
+        <v>1</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N25" s="9"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9">
+        <v>2008</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9">
+        <v>2</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9">
+        <v>1</v>
+      </c>
+      <c r="I26" s="9">
+        <v>1</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N26" s="9"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9">
+        <v>2009</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9">
+        <v>2</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9">
+        <v>1</v>
+      </c>
+      <c r="I27" s="9">
+        <v>1</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N27" s="9"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9">
+        <v>2010</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9">
+        <v>2</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9">
+        <v>1</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N28" s="9"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9">
+        <v>2011</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9">
+        <v>2</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9">
+        <v>1</v>
+      </c>
+      <c r="I29" s="9">
+        <v>1</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N29" s="9"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9">
+        <v>2012</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9">
+        <v>2</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9">
+        <v>1</v>
+      </c>
+      <c r="I30" s="9">
+        <v>1</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="N30" s="9"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9">
+        <v>2013</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9">
+        <v>2</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9">
+        <v>1</v>
+      </c>
+      <c r="I31" s="9">
+        <v>1</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9">
+        <v>2014</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9">
+        <v>2</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9">
+        <v>1</v>
+      </c>
+      <c r="I32" s="9">
+        <v>1</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9">
+        <v>2015</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9">
+        <v>2</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9">
+        <v>1</v>
+      </c>
+      <c r="I33" s="9">
+        <v>1</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9">
+        <v>2016</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9">
+        <v>2</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9">
+        <v>1</v>
+      </c>
+      <c r="I34" s="9">
+        <v>2</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="N34" s="9"/>
+    </row>
+    <row r="35" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11">
+        <v>3001</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11">
+        <v>3</v>
+      </c>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11">
+        <v>1</v>
+      </c>
+      <c r="I35" s="11">
+        <v>1</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K35" s="11"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="11"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9">
+        <v>3002</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9">
+        <v>3</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9">
+        <v>1</v>
+      </c>
+      <c r="I36" s="9">
+        <v>1</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9">
+        <v>3003</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9">
+        <v>3</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9">
+        <v>1</v>
+      </c>
+      <c r="I37" s="9">
+        <v>1</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9">
+        <v>3004</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9">
+        <v>3</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9">
+        <v>1</v>
+      </c>
+      <c r="I38" s="9">
+        <v>1</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9">
+        <v>3005</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9">
+        <v>3</v>
+      </c>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9">
+        <v>1</v>
+      </c>
+      <c r="I39" s="9">
+        <v>1</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9">
+        <v>3006</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9">
+        <v>3</v>
+      </c>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9">
+        <v>1</v>
+      </c>
+      <c r="I40" s="9">
+        <v>1</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9">
+        <v>3007</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9">
+        <v>3</v>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9">
+        <v>1</v>
+      </c>
+      <c r="I41" s="9">
+        <v>1</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9">
+        <v>3008</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9">
+        <v>3</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9">
+        <v>1</v>
+      </c>
+      <c r="I42" s="9">
+        <v>1</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9">
+        <v>3009</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9">
+        <v>3</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9">
+        <v>1</v>
+      </c>
+      <c r="I43" s="9">
+        <v>1</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9">
+        <v>3010</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9">
+        <v>3</v>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9">
+        <v>1</v>
+      </c>
+      <c r="I44" s="9">
+        <v>1</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9">
+        <v>3011</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9">
+        <v>3</v>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9">
+        <v>1</v>
+      </c>
+      <c r="I45" s="9">
+        <v>1</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9">
+        <v>3012</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9">
+        <v>3</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9">
+        <v>1</v>
+      </c>
+      <c r="I46" s="9">
+        <v>1</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9">
+        <v>3013</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9">
+        <v>3</v>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9">
+        <v>1</v>
+      </c>
+      <c r="I47" s="9">
+        <v>1</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9">
+        <v>3014</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9">
+        <v>3</v>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9">
+        <v>1</v>
+      </c>
+      <c r="I48" s="9">
+        <v>1</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9">
+        <v>3015</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9">
+        <v>3</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9">
+        <v>1</v>
+      </c>
+      <c r="I49" s="9">
+        <v>2</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+    </row>
+    <row r="50" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11">
+        <v>4001</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11">
+        <v>4</v>
+      </c>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11">
+        <v>1</v>
+      </c>
+      <c r="I50" s="11">
+        <v>1</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A51" s="9"/>
+      <c r="B51" s="9">
+        <v>4002</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9">
+        <v>4</v>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9">
+        <v>1</v>
+      </c>
+      <c r="I51" s="9">
+        <v>1</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9">
+        <v>4003</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9">
+        <v>4</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9">
+        <v>1</v>
+      </c>
+      <c r="I52" s="9">
+        <v>1</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="9"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9">
+        <v>4004</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9">
+        <v>4</v>
+      </c>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9">
+        <v>1</v>
+      </c>
+      <c r="I53" s="9">
+        <v>1</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="9"/>
+      <c r="B54" s="9">
+        <v>4005</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9">
+        <v>4</v>
+      </c>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9">
+        <v>1</v>
+      </c>
+      <c r="I54" s="9">
+        <v>1</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9">
+        <v>4006</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9">
+        <v>4</v>
+      </c>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9">
+        <v>1</v>
+      </c>
+      <c r="I55" s="9">
+        <v>1</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="9"/>
+      <c r="B56" s="9">
+        <v>4007</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9">
+        <v>4</v>
+      </c>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9">
+        <v>1</v>
+      </c>
+      <c r="I56" s="9">
+        <v>1</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+      <c r="M56" s="9"/>
+      <c r="N56" s="9"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9">
+        <v>4008</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9">
+        <v>4</v>
+      </c>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9">
+        <v>1</v>
+      </c>
+      <c r="I57" s="9">
+        <v>1</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9">
+        <v>4009</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9">
+        <v>4</v>
+      </c>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9">
+        <v>1</v>
+      </c>
+      <c r="I58" s="9">
+        <v>1</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+      <c r="M58" s="9"/>
+      <c r="N58" s="9"/>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9">
+        <v>4010</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9">
+        <v>4</v>
+      </c>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9">
+        <v>1</v>
+      </c>
+      <c r="I59" s="9">
+        <v>1</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="9"/>
+      <c r="B60" s="9">
+        <v>4011</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9">
+        <v>4</v>
+      </c>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9">
+        <v>1</v>
+      </c>
+      <c r="I60" s="9">
+        <v>1</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+      <c r="M60" s="9"/>
+      <c r="N60" s="9"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9">
+        <v>4012</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9">
+        <v>4</v>
+      </c>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9">
+        <v>1</v>
+      </c>
+      <c r="I61" s="9">
+        <v>1</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+      <c r="M61" s="9"/>
+      <c r="N61" s="9"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="9"/>
+      <c r="B62" s="9">
+        <v>4013</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9">
+        <v>4</v>
+      </c>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9">
+        <v>1</v>
+      </c>
+      <c r="I62" s="9">
+        <v>1</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
+      <c r="N62" s="9"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="9"/>
+      <c r="B63" s="9">
+        <v>4014</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9">
+        <v>4</v>
+      </c>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9">
+        <v>1</v>
+      </c>
+      <c r="I63" s="9">
+        <v>1</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+      <c r="M63" s="9"/>
+      <c r="N63" s="9"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="9"/>
+      <c r="B64" s="9">
+        <v>4015</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9">
+        <v>4</v>
+      </c>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9">
+        <v>1</v>
+      </c>
+      <c r="I64" s="9">
+        <v>2</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+      <c r="M64" s="9"/>
+      <c r="N64" s="9"/>
+    </row>
+    <row r="65" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11">
+        <v>5001</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="11"/>
+      <c r="E65" s="11">
+        <v>5</v>
+      </c>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11">
+        <v>1</v>
+      </c>
+      <c r="I65" s="11">
+        <v>1</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="N65" s="11"/>
+    </row>
+    <row r="66" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12">
+        <v>5002</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12">
+        <v>5</v>
+      </c>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="12">
+        <v>1</v>
+      </c>
+      <c r="I66" s="12">
+        <v>1</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+    </row>
+    <row r="67" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12">
+        <v>5003</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12">
+        <v>5</v>
+      </c>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12">
+        <v>1</v>
+      </c>
+      <c r="I67" s="12">
+        <v>1</v>
+      </c>
+      <c r="J67" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="7"/>
@@ -1905,7 +3038,7 @@
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="7"/>
@@ -1921,7 +3054,7 @@
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="7"/>
@@ -1937,7 +3070,7 @@
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="7"/>
@@ -1953,7 +3086,7 @@
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="7"/>
@@ -1969,7 +3102,7 @@
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="7"/>
@@ -1985,7 +3118,7 @@
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="7"/>
@@ -2001,7 +3134,7 @@
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="7"/>
@@ -2017,7 +3150,7 @@
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="7"/>
@@ -2033,7 +3166,7 @@
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="7"/>
@@ -2049,7 +3182,7 @@
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="7"/>
@@ -2065,7 +3198,7 @@
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="7"/>
@@ -2081,7 +3214,7 @@
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="7"/>
@@ -2097,7 +3230,7 @@
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="7"/>
@@ -2113,7 +3246,7 @@
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="7"/>
@@ -2129,7 +3262,7 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="7"/>
@@ -2145,7 +3278,7 @@
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="7"/>
@@ -2161,7 +3294,7 @@
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="7"/>
@@ -2177,7 +3310,7 @@
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="7"/>
@@ -2193,7 +3326,7 @@
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="7"/>
@@ -2209,7 +3342,7 @@
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="7"/>
@@ -2225,7 +3358,7 @@
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="7"/>
@@ -2241,7 +3374,7 @@
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="7"/>
@@ -2257,7 +3390,7 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="7"/>
@@ -2273,7 +3406,7 @@
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="7"/>
@@ -2289,7 +3422,7 @@
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="7"/>
@@ -2305,7 +3438,7 @@
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="7"/>
@@ -2321,7 +3454,7 @@
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="7"/>
@@ -2337,7 +3470,7 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="7"/>
@@ -2353,7 +3486,7 @@
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="7"/>
@@ -2369,7 +3502,7 @@
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="7"/>
@@ -2385,7 +3518,7 @@
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="7"/>
@@ -2401,7 +3534,7 @@
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="7"/>
@@ -2417,7 +3550,7 @@
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="7"/>
@@ -2433,7 +3566,7 @@
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="7"/>
@@ -2449,7 +3582,7 @@
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="7"/>
@@ -2465,7 +3598,7 @@
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="7"/>
@@ -2481,7 +3614,7 @@
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="7"/>
@@ -2497,7 +3630,7 @@
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="7"/>
@@ -2513,7 +3646,7 @@
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="7"/>
@@ -2529,7 +3662,7 @@
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="7"/>
@@ -2545,7 +3678,7 @@
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="7"/>
@@ -2561,7 +3694,7 @@
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="7"/>
@@ -2577,7 +3710,7 @@
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="7"/>
@@ -2593,7 +3726,7 @@
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="7"/>
@@ -2609,7 +3742,7 @@
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="7"/>
@@ -2625,7 +3758,7 @@
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="7"/>
@@ -2641,7 +3774,7 @@
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="7"/>
@@ -2657,7 +3790,7 @@
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="7"/>
@@ -2673,7 +3806,7 @@
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="7"/>
@@ -2689,7 +3822,7 @@
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="7"/>
@@ -2705,7 +3838,7 @@
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="7"/>
@@ -2721,7 +3854,7 @@
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="7"/>
@@ -2737,7 +3870,7 @@
       <c r="M120" s="3"/>
       <c r="N120" s="3"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="7"/>
@@ -2753,7 +3886,7 @@
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="7"/>
@@ -2769,7 +3902,7 @@
       <c r="M122" s="3"/>
       <c r="N122" s="3"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="7"/>
@@ -2785,7 +3918,7 @@
       <c r="M123" s="3"/>
       <c r="N123" s="3"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="7"/>
@@ -2801,7 +3934,7 @@
       <c r="M124" s="3"/>
       <c r="N124" s="3"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="7"/>
@@ -2817,7 +3950,7 @@
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="7"/>
@@ -2833,7 +3966,7 @@
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="7"/>
@@ -2849,7 +3982,7 @@
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="7"/>
@@ -2865,7 +3998,7 @@
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="7"/>
@@ -2881,7 +4014,7 @@
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="7"/>
@@ -2897,7 +4030,7 @@
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="7"/>
@@ -2913,7 +4046,7 @@
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="7"/>
@@ -2929,7 +4062,7 @@
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="7"/>
@@ -2945,7 +4078,7 @@
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="7"/>
@@ -2961,7 +4094,7 @@
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="7"/>
@@ -2977,7 +4110,7 @@
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="7"/>
@@ -2993,7 +4126,7 @@
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="7"/>
@@ -3009,7 +4142,7 @@
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="7"/>
@@ -3025,7 +4158,7 @@
       <c r="M138" s="3"/>
       <c r="N138" s="3"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="7"/>
@@ -3041,7 +4174,7 @@
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="7"/>
@@ -3057,7 +4190,7 @@
       <c r="M140" s="3"/>
       <c r="N140" s="3"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="7"/>
@@ -3073,7 +4206,7 @@
       <c r="M141" s="3"/>
       <c r="N141" s="3"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="7"/>
@@ -3089,7 +4222,7 @@
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="7"/>
@@ -3105,7 +4238,7 @@
       <c r="M143" s="3"/>
       <c r="N143" s="3"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="7"/>
@@ -3121,7 +4254,7 @@
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="7"/>
@@ -3137,7 +4270,7 @@
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="7"/>
@@ -3153,7 +4286,7 @@
       <c r="M146" s="3"/>
       <c r="N146" s="3"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="7"/>
@@ -3169,7 +4302,7 @@
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="7"/>
@@ -3185,7 +4318,7 @@
       <c r="M148" s="3"/>
       <c r="N148" s="3"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="7"/>
@@ -3201,7 +4334,7 @@
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="7"/>
@@ -3217,7 +4350,7 @@
       <c r="M150" s="3"/>
       <c r="N150" s="3"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="7"/>
@@ -3233,7 +4366,7 @@
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="7"/>
@@ -3249,7 +4382,7 @@
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="7"/>
@@ -3265,7 +4398,7 @@
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="7"/>
@@ -3281,7 +4414,7 @@
       <c r="M154" s="3"/>
       <c r="N154" s="3"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="7"/>
@@ -3297,7 +4430,7 @@
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="7"/>
@@ -3313,7 +4446,7 @@
       <c r="M156" s="3"/>
       <c r="N156" s="3"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="7"/>
@@ -3329,7 +4462,7 @@
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="7"/>
@@ -3345,7 +4478,7 @@
       <c r="M158" s="3"/>
       <c r="N158" s="3"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="7"/>
@@ -3361,7 +4494,7 @@
       <c r="M159" s="3"/>
       <c r="N159" s="3"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="7"/>
@@ -3377,7 +4510,7 @@
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="7"/>
@@ -3393,7 +4526,7 @@
       <c r="M161" s="3"/>
       <c r="N161" s="3"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="7"/>
@@ -3409,7 +4542,7 @@
       <c r="M162" s="3"/>
       <c r="N162" s="3"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="7"/>
@@ -3425,7 +4558,7 @@
       <c r="M163" s="3"/>
       <c r="N163" s="3"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="7"/>
@@ -3441,7 +4574,7 @@
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="7"/>
@@ -3457,7 +4590,7 @@
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="7"/>
@@ -3473,7 +4606,7 @@
       <c r="M166" s="3"/>
       <c r="N166" s="3"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="7"/>
@@ -3489,7 +4622,7 @@
       <c r="M167" s="3"/>
       <c r="N167" s="3"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="7"/>
@@ -3505,7 +4638,7 @@
       <c r="M168" s="3"/>
       <c r="N168" s="3"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="7"/>
@@ -3521,7 +4654,7 @@
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="7"/>
@@ -3537,7 +4670,7 @@
       <c r="M170" s="3"/>
       <c r="N170" s="3"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="7"/>
@@ -3553,7 +4686,7 @@
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="7"/>
@@ -3569,7 +4702,7 @@
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="7"/>
@@ -3585,7 +4718,7 @@
       <c r="M173" s="3"/>
       <c r="N173" s="3"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="7"/>
@@ -3601,7 +4734,7 @@
       <c r="M174" s="3"/>
       <c r="N174" s="3"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="7"/>
@@ -3617,7 +4750,7 @@
       <c r="M175" s="3"/>
       <c r="N175" s="3"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="7"/>
@@ -3633,7 +4766,7 @@
       <c r="M176" s="3"/>
       <c r="N176" s="3"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="7"/>
@@ -3649,44 +4782,236 @@
       <c r="M177" s="3"/>
       <c r="N177" s="3"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A178" s="8"/>
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="8"/>
-      <c r="H178" s="8"/>
-      <c r="I178" s="8"/>
-      <c r="J178" s="8"/>
-      <c r="K178" s="8"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A179" s="8"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="8"/>
-      <c r="H179" s="8"/>
-      <c r="I179" s="8"/>
-      <c r="J179" s="8"/>
-      <c r="K179" s="8"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A180" s="8"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
-      <c r="F180" s="8"/>
-      <c r="G180" s="8"/>
-      <c r="H180" s="8"/>
-      <c r="I180" s="8"/>
-      <c r="J180" s="8"/>
-      <c r="K180" s="8"/>
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="3"/>
+      <c r="G178" s="3"/>
+      <c r="H178" s="3"/>
+      <c r="I178" s="3"/>
+      <c r="J178" s="3"/>
+      <c r="K178" s="3"/>
+      <c r="L178" s="3"/>
+      <c r="M178" s="3"/>
+      <c r="N178" s="3"/>
+    </row>
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="3"/>
+      <c r="G179" s="3"/>
+      <c r="H179" s="3"/>
+      <c r="I179" s="3"/>
+      <c r="J179" s="3"/>
+      <c r="K179" s="3"/>
+      <c r="L179" s="3"/>
+      <c r="M179" s="3"/>
+      <c r="N179" s="3"/>
+    </row>
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="7"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="3"/>
+      <c r="G180" s="3"/>
+      <c r="H180" s="3"/>
+      <c r="I180" s="3"/>
+      <c r="J180" s="3"/>
+      <c r="K180" s="3"/>
+      <c r="L180" s="3"/>
+      <c r="M180" s="3"/>
+      <c r="N180" s="3"/>
+    </row>
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="7"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3"/>
+      <c r="J181" s="3"/>
+      <c r="K181" s="3"/>
+      <c r="L181" s="3"/>
+      <c r="M181" s="3"/>
+      <c r="N181" s="3"/>
+    </row>
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+      <c r="J182" s="3"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="3"/>
+      <c r="M182" s="3"/>
+      <c r="N182" s="3"/>
+    </row>
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="7"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3"/>
+      <c r="G183" s="3"/>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+      <c r="J183" s="3"/>
+      <c r="K183" s="3"/>
+      <c r="L183" s="3"/>
+      <c r="M183" s="3"/>
+      <c r="N183" s="3"/>
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="J184" s="3"/>
+      <c r="K184" s="3"/>
+      <c r="L184" s="3"/>
+      <c r="M184" s="3"/>
+      <c r="N184" s="3"/>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="7"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="3"/>
+      <c r="G185" s="3"/>
+      <c r="H185" s="3"/>
+      <c r="I185" s="3"/>
+      <c r="J185" s="3"/>
+      <c r="K185" s="3"/>
+      <c r="L185" s="3"/>
+      <c r="M185" s="3"/>
+      <c r="N185" s="3"/>
+    </row>
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="7"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="3"/>
+      <c r="G186" s="3"/>
+      <c r="H186" s="3"/>
+      <c r="I186" s="3"/>
+      <c r="J186" s="3"/>
+      <c r="K186" s="3"/>
+      <c r="L186" s="3"/>
+      <c r="M186" s="3"/>
+      <c r="N186" s="3"/>
+    </row>
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="7"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="3"/>
+      <c r="G187" s="3"/>
+      <c r="H187" s="3"/>
+      <c r="I187" s="3"/>
+      <c r="J187" s="3"/>
+      <c r="K187" s="3"/>
+      <c r="L187" s="3"/>
+      <c r="M187" s="3"/>
+      <c r="N187" s="3"/>
+    </row>
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="7"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="3"/>
+      <c r="G188" s="3"/>
+      <c r="H188" s="3"/>
+      <c r="I188" s="3"/>
+      <c r="J188" s="3"/>
+      <c r="K188" s="3"/>
+      <c r="L188" s="3"/>
+      <c r="M188" s="3"/>
+      <c r="N188" s="3"/>
+    </row>
+    <row r="189" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="7"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="3"/>
+      <c r="F189" s="3"/>
+      <c r="G189" s="3"/>
+      <c r="H189" s="3"/>
+      <c r="I189" s="3"/>
+      <c r="J189" s="3"/>
+      <c r="K189" s="3"/>
+      <c r="L189" s="3"/>
+      <c r="M189" s="3"/>
+      <c r="N189" s="3"/>
+    </row>
+    <row r="190" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="8"/>
+      <c r="B190" s="8"/>
+      <c r="C190" s="8"/>
+      <c r="D190" s="8"/>
+      <c r="E190" s="8"/>
+      <c r="F190" s="8"/>
+      <c r="G190" s="8"/>
+      <c r="H190" s="8"/>
+      <c r="I190" s="8"/>
+      <c r="J190" s="8"/>
+      <c r="K190" s="8"/>
+    </row>
+    <row r="191" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A191" s="8"/>
+      <c r="B191" s="8"/>
+      <c r="C191" s="8"/>
+      <c r="D191" s="8"/>
+      <c r="E191" s="8"/>
+      <c r="F191" s="8"/>
+      <c r="G191" s="8"/>
+      <c r="H191" s="8"/>
+      <c r="I191" s="8"/>
+      <c r="J191" s="8"/>
+      <c r="K191" s="8"/>
+    </row>
+    <row r="192" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A192" s="8"/>
+      <c r="B192" s="8"/>
+      <c r="C192" s="8"/>
+      <c r="D192" s="8"/>
+      <c r="E192" s="8"/>
+      <c r="F192" s="8"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="8"/>
+      <c r="J192" s="8"/>
+      <c r="K192" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02831D26-4027-47C5-924D-AF6DA727E147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7B1798-8D4A-4C3D-AD68-1ABBF158C13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="0" windowWidth="30180" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="170">
   <si>
     <t>##var</t>
   </si>
@@ -324,14 +324,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>1有碰撞 2无碰撞</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景内碰撞</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>场景内碰撞效果</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -513,10 +505,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>1可以 2不可以</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>花椰菜-种子袋(一次性)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -541,10 +529,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>sound</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>eat_Effect</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -562,6 +546,131 @@
   </si>
   <si>
     <t>itemType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/mushroom_002</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Pumpkin</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Carrot</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Beet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Tomato_red</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Tomato_yellow</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Tomato_green</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/sack</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Kiwi</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩小</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以被门吞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以被南瓜吞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否为隐藏物品</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0可以 1不可以</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0是 1不是</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0有碰撞 1无碰撞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品举高时的高度</t>
+  </si>
+  <si>
+    <t>物品举高时的高度</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景内（收获后）碰撞</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffid</t>
+  </si>
+  <si>
+    <t>buffid</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>和地面碰撞音效</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>height</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_door</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_pumpkin</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_hide</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0能举起 1不能被举起</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以举起</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>lift</t>
+  </si>
+  <si>
+    <t>sound_floor</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>sound_collision</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffid#buffid</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -756,7 +865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -795,6 +904,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1072,23 +1184,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O192"/>
+  <dimension ref="A1:Y192"/>
   <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.1640625" style="1"/>
     <col min="3" max="3" width="22.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.08203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.75" style="1" customWidth="1"/>
-    <col min="10" max="11" width="12.1640625" style="1"/>
-    <col min="12" max="12" width="14.9140625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="12.1640625" style="1"/>
+    <col min="9" max="11" width="16.75" style="1" customWidth="1"/>
+    <col min="12" max="16" width="12.1640625" style="1"/>
+    <col min="17" max="18" width="17.9140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.9140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1640625" style="1"/>
+    <col min="26" max="16384" width="12.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1102,7 +1216,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>9</v>
@@ -1111,25 +1225,46 @@
         <v>8</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="T1" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1152,25 +1287,46 @@
         <v>14</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="O2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="S2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1190,28 +1346,49 @@
         <v>13</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1225,35 +1402,55 @@
         <v>17</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>81</v>
+        <v>164</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>85</v>
+        <v>155</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="9">
         <v>1001</v>
@@ -1265,17 +1462,38 @@
       <c r="E5" s="9">
         <v>1</v>
       </c>
+      <c r="F5" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G5" s="9">
+        <v>1</v>
+      </c>
       <c r="H5" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="9">
-        <v>1</v>
-      </c>
-      <c r="K5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>100</v>
+      </c>
+      <c r="L5" s="9">
+        <v>1</v>
+      </c>
+      <c r="M5" s="9">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="T5" s="9"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="9">
         <v>1002</v>
@@ -1287,17 +1505,38 @@
       <c r="E6" s="9">
         <v>1</v>
       </c>
+      <c r="F6" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G6" s="9">
+        <v>1</v>
+      </c>
       <c r="H6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="9">
-        <v>1</v>
-      </c>
-      <c r="K6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>100</v>
+      </c>
+      <c r="L6" s="9">
+        <v>1</v>
+      </c>
+      <c r="M6" s="9">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1</v>
+      </c>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="T6" s="9"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="9">
         <v>1003</v>
@@ -1309,17 +1548,38 @@
       <c r="E7" s="9">
         <v>1</v>
       </c>
+      <c r="F7" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
       <c r="H7" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="9">
-        <v>1</v>
-      </c>
-      <c r="K7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>100</v>
+      </c>
+      <c r="L7" s="9">
+        <v>1</v>
+      </c>
+      <c r="M7" s="9">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="T7" s="9"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="9">
         <v>1004</v>
@@ -1331,18 +1591,39 @@
       <c r="E8" s="9">
         <v>1</v>
       </c>
+      <c r="F8" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1</v>
+      </c>
       <c r="H8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="9">
-        <v>1</v>
-      </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>100</v>
+      </c>
+      <c r="L8" s="9">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1</v>
+      </c>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="9">
         <v>1005</v>
@@ -1354,18 +1635,39 @@
       <c r="E9" s="9">
         <v>1</v>
       </c>
+      <c r="F9" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G9" s="9">
+        <v>1</v>
+      </c>
       <c r="H9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>100</v>
+      </c>
+      <c r="L9" s="9">
+        <v>1</v>
+      </c>
+      <c r="M9" s="9">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="9">
         <v>1006</v>
@@ -1377,18 +1679,39 @@
       <c r="E10" s="9">
         <v>1</v>
       </c>
+      <c r="F10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
       <c r="H10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="9">
-        <v>1</v>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>100</v>
+      </c>
+      <c r="L10" s="9">
+        <v>1</v>
+      </c>
+      <c r="M10" s="9">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="9">
         <v>1007</v>
@@ -1400,18 +1723,39 @@
       <c r="E11" s="9">
         <v>1</v>
       </c>
+      <c r="F11" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1</v>
+      </c>
       <c r="H11" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="9">
-        <v>1</v>
-      </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>100</v>
+      </c>
+      <c r="L11" s="9">
+        <v>1</v>
+      </c>
+      <c r="M11" s="9">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="9">
         <v>1008</v>
@@ -1423,18 +1767,39 @@
       <c r="E12" s="9">
         <v>1</v>
       </c>
+      <c r="F12" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="9">
+        <v>1</v>
+      </c>
       <c r="H12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="9">
-        <v>1</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>100</v>
+      </c>
+      <c r="L12" s="9">
+        <v>1</v>
+      </c>
+      <c r="M12" s="9">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="9">
         <v>1009</v>
@@ -1446,18 +1811,39 @@
       <c r="E13" s="9">
         <v>1</v>
       </c>
+      <c r="F13" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="9">
+        <v>1</v>
+      </c>
       <c r="H13" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9">
-        <v>1</v>
-      </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>100</v>
+      </c>
+      <c r="L13" s="9">
+        <v>1</v>
+      </c>
+      <c r="M13" s="9">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1</v>
+      </c>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="9">
         <v>1010</v>
@@ -1469,18 +1855,39 @@
       <c r="E14" s="9">
         <v>1</v>
       </c>
+      <c r="F14" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" s="9">
+        <v>1</v>
+      </c>
       <c r="H14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9">
-        <v>1</v>
-      </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>100</v>
+      </c>
+      <c r="L14" s="9">
+        <v>1</v>
+      </c>
+      <c r="M14" s="9">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>1</v>
+      </c>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="9">
         <v>1011</v>
@@ -1492,18 +1899,39 @@
       <c r="E15" s="9">
         <v>1</v>
       </c>
+      <c r="F15" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G15" s="9">
+        <v>1</v>
+      </c>
       <c r="H15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9">
-        <v>1</v>
-      </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>100</v>
+      </c>
+      <c r="L15" s="9">
+        <v>1</v>
+      </c>
+      <c r="M15" s="9">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>1</v>
+      </c>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="9">
         <v>1012</v>
@@ -1515,67 +1943,129 @@
       <c r="E16" s="9">
         <v>1</v>
       </c>
+      <c r="F16" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G16" s="9">
+        <v>1</v>
+      </c>
       <c r="H16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9">
-        <v>1</v>
-      </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>100</v>
+      </c>
+      <c r="L16" s="9">
+        <v>1</v>
+      </c>
+      <c r="M16" s="9">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1</v>
+      </c>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="9">
         <v>1013</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
         <v>1</v>
       </c>
+      <c r="F17" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G17" s="9">
+        <v>1</v>
+      </c>
       <c r="H17" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="9">
-        <v>1</v>
-      </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="9">
+        <v>100</v>
+      </c>
+      <c r="L17" s="9">
+        <v>1</v>
+      </c>
+      <c r="M17" s="9">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1</v>
+      </c>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9">
         <v>1014</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9">
         <v>1</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="F18" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="G18" s="9">
+        <v>1</v>
+      </c>
       <c r="H18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9">
-        <v>1</v>
-      </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-    </row>
-    <row r="19" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>100</v>
+      </c>
+      <c r="L18" s="9">
+        <v>1</v>
+      </c>
+      <c r="M18" s="9">
+        <v>1</v>
+      </c>
+      <c r="N18" s="1">
+        <v>1</v>
+      </c>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+    </row>
+    <row r="19" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11">
         <v>2001</v>
@@ -1587,27 +2077,49 @@
       <c r="E19" s="11">
         <v>2</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11">
-        <v>1</v>
-      </c>
-      <c r="I19" s="11">
-        <v>1</v>
-      </c>
-      <c r="J19" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="K19" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="F19" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="9">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>100</v>
+      </c>
+      <c r="L19" s="11">
+        <v>0</v>
+      </c>
+      <c r="M19" s="11">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1</v>
+      </c>
+      <c r="O19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="P19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="R19" s="11"/>
+      <c r="S19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="T19" s="11"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9">
         <v>2002</v>
@@ -1619,27 +2131,47 @@
       <c r="E20" s="9">
         <v>2</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G20" s="9">
+        <v>1</v>
+      </c>
       <c r="H20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9">
-        <v>1</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="M20" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="N20" s="9"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>100</v>
+      </c>
+      <c r="L20" s="11">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>1</v>
+      </c>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9">
         <v>2003</v>
@@ -1651,27 +2183,47 @@
       <c r="E21" s="9">
         <v>2</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="F21" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" s="9">
+        <v>1</v>
+      </c>
       <c r="H21" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9">
-        <v>1</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="M21" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="N21" s="9"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9">
+        <v>100</v>
+      </c>
+      <c r="L21" s="11">
+        <v>0</v>
+      </c>
+      <c r="M21" s="11">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>1</v>
+      </c>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9">
         <v>2004</v>
@@ -1683,29 +2235,51 @@
       <c r="E22" s="9">
         <v>2</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="9">
+        <v>1</v>
+      </c>
       <c r="H22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="9">
-        <v>1</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="N22" s="9"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="9">
+        <v>100</v>
+      </c>
+      <c r="L22" s="11">
+        <v>0</v>
+      </c>
+      <c r="M22" s="11">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="T22" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9">
         <v>2005</v>
@@ -1717,27 +2291,47 @@
       <c r="E23" s="9">
         <v>2</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="F23" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="9">
+        <v>1</v>
+      </c>
       <c r="H23" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9">
-        <v>1</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>100</v>
+      </c>
+      <c r="L23" s="11">
+        <v>0</v>
+      </c>
+      <c r="M23" s="11">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1</v>
+      </c>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="T23" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="M23" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="N23" s="9"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9">
         <v>2006</v>
@@ -1749,27 +2343,47 @@
       <c r="E24" s="9">
         <v>2</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="F24" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="9">
+        <v>1</v>
+      </c>
       <c r="H24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="9">
-        <v>1</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M24" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N24" s="9"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>100</v>
+      </c>
+      <c r="L24" s="11">
+        <v>0</v>
+      </c>
+      <c r="M24" s="11">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1</v>
+      </c>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9">
         <v>2007</v>
@@ -1781,27 +2395,47 @@
       <c r="E25" s="9">
         <v>2</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="F25" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G25" s="9">
+        <v>1</v>
+      </c>
       <c r="H25" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9">
-        <v>1</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N25" s="9"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="9">
+        <v>0</v>
+      </c>
+      <c r="K25" s="9">
+        <v>100</v>
+      </c>
+      <c r="L25" s="11">
+        <v>0</v>
+      </c>
+      <c r="M25" s="11">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>1</v>
+      </c>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9">
         <v>2008</v>
@@ -1813,27 +2447,47 @@
       <c r="E26" s="9">
         <v>2</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="F26" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G26" s="9">
+        <v>1</v>
+      </c>
       <c r="H26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9">
-        <v>1</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M26" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N26" s="9"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="9">
+        <v>0</v>
+      </c>
+      <c r="K26" s="9">
+        <v>100</v>
+      </c>
+      <c r="L26" s="11">
+        <v>0</v>
+      </c>
+      <c r="M26" s="11">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>1</v>
+      </c>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T26" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9">
         <v>2009</v>
@@ -1845,27 +2499,47 @@
       <c r="E27" s="9">
         <v>2</v>
       </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="F27" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G27" s="9">
+        <v>1</v>
+      </c>
       <c r="H27" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="9">
-        <v>1</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N27" s="9"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="9">
+        <v>0</v>
+      </c>
+      <c r="K27" s="9">
+        <v>100</v>
+      </c>
+      <c r="L27" s="11">
+        <v>0</v>
+      </c>
+      <c r="M27" s="11">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>1</v>
+      </c>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T27" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9">
         <v>2010</v>
@@ -1877,27 +2551,47 @@
       <c r="E28" s="9">
         <v>2</v>
       </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G28" s="9">
+        <v>1</v>
+      </c>
       <c r="H28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="9">
-        <v>1</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M28" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N28" s="9"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>100</v>
+      </c>
+      <c r="L28" s="11">
+        <v>0</v>
+      </c>
+      <c r="M28" s="11">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>1</v>
+      </c>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9">
         <v>2011</v>
@@ -1909,27 +2603,47 @@
       <c r="E29" s="9">
         <v>2</v>
       </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
+      <c r="F29" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" s="9">
+        <v>1</v>
+      </c>
       <c r="H29" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="9">
-        <v>1</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N29" s="9"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="9">
+        <v>0</v>
+      </c>
+      <c r="K29" s="9">
+        <v>100</v>
+      </c>
+      <c r="L29" s="11">
+        <v>0</v>
+      </c>
+      <c r="M29" s="11">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>1</v>
+      </c>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9">
         <v>2012</v>
@@ -1941,27 +2655,47 @@
       <c r="E30" s="9">
         <v>2</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
+      <c r="F30" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="9">
+        <v>1</v>
+      </c>
       <c r="H30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="9">
-        <v>1</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M30" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="N30" s="9"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="9">
+        <v>0</v>
+      </c>
+      <c r="K30" s="9">
+        <v>100</v>
+      </c>
+      <c r="L30" s="11">
+        <v>0</v>
+      </c>
+      <c r="M30" s="11">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>1</v>
+      </c>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="T30" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9">
         <v>2013</v>
@@ -1973,61 +2707,99 @@
       <c r="E31" s="9">
         <v>2</v>
       </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="F31" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" s="9">
+        <v>1</v>
+      </c>
       <c r="H31" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9">
-        <v>1</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="M31" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="N31" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="9">
+        <v>0</v>
+      </c>
+      <c r="K31" s="9">
+        <v>100</v>
+      </c>
+      <c r="L31" s="11">
+        <v>0</v>
+      </c>
+      <c r="M31" s="11">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
+        <v>1</v>
+      </c>
       <c r="O31" s="9"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9">
         <v>2014</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9">
         <v>2</v>
       </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" s="9">
+        <v>1</v>
+      </c>
       <c r="H32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="9">
-        <v>1</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="M32" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="N32" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="9">
+        <v>0</v>
+      </c>
+      <c r="K32" s="9">
+        <v>100</v>
+      </c>
+      <c r="L32" s="11">
+        <v>0</v>
+      </c>
+      <c r="M32" s="11">
+        <v>0</v>
+      </c>
+      <c r="N32" s="1">
+        <v>1</v>
+      </c>
       <c r="O32" s="9"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="T32" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9">
         <v>2015</v>
@@ -2039,30 +2811,51 @@
       <c r="E33" s="9">
         <v>2</v>
       </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
+      <c r="F33" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G33" s="9">
+        <v>1</v>
+      </c>
       <c r="H33" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="9">
-        <v>1</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="9">
+        <v>0</v>
+      </c>
+      <c r="K33" s="9">
+        <v>100</v>
+      </c>
+      <c r="L33" s="11">
+        <v>0</v>
+      </c>
+      <c r="M33" s="11">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
+        <v>1</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="T33" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9">
         <v>2016</v>
@@ -2074,27 +2867,47 @@
       <c r="E34" s="9">
         <v>2</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="F34" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="9">
+        <v>1</v>
+      </c>
       <c r="H34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9">
-        <v>2</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="M34" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="N34" s="9"/>
-    </row>
-    <row r="35" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0</v>
+      </c>
+      <c r="K34" s="9">
+        <v>100</v>
+      </c>
+      <c r="L34" s="11">
+        <v>0</v>
+      </c>
+      <c r="M34" s="11">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
+        <v>1</v>
+      </c>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="T34" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
       <c r="B35" s="11">
         <v>3001</v>
@@ -2106,23 +2919,43 @@
       <c r="E35" s="11">
         <v>3</v>
       </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11">
-        <v>1</v>
-      </c>
-      <c r="I35" s="11">
-        <v>1</v>
-      </c>
-      <c r="J35" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="F35" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G35" s="11">
+        <v>4</v>
+      </c>
+      <c r="H35" s="9">
+        <v>0</v>
+      </c>
+      <c r="I35" s="9">
+        <v>0</v>
+      </c>
+      <c r="J35" s="9">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9">
+        <v>100</v>
+      </c>
+      <c r="L35" s="11">
+        <v>0</v>
+      </c>
+      <c r="M35" s="11">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <v>1</v>
+      </c>
+      <c r="O35" s="11"/>
+      <c r="P35" s="11"/>
+      <c r="Q35" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="R35" s="11"/>
+      <c r="S35" s="11"/>
+      <c r="T35" s="11"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9">
         <v>3002</v>
@@ -2134,23 +2967,43 @@
       <c r="E36" s="9">
         <v>3</v>
       </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" s="9">
+        <v>4</v>
+      </c>
       <c r="H36" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="9">
-        <v>1</v>
-      </c>
-      <c r="J36" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="9">
+        <v>0</v>
+      </c>
+      <c r="K36" s="9">
+        <v>100</v>
+      </c>
+      <c r="L36" s="11">
+        <v>0</v>
+      </c>
+      <c r="M36" s="11">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>1</v>
+      </c>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9">
         <v>3003</v>
@@ -2162,23 +3015,43 @@
       <c r="E37" s="9">
         <v>3</v>
       </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="F37" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" s="9">
+        <v>4</v>
+      </c>
       <c r="H37" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9">
-        <v>1</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="9">
+        <v>0</v>
+      </c>
+      <c r="K37" s="9">
+        <v>100</v>
+      </c>
+      <c r="L37" s="11">
+        <v>0</v>
+      </c>
+      <c r="M37" s="11">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
+        <v>1</v>
+      </c>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9">
         <v>3004</v>
@@ -2190,23 +3063,43 @@
       <c r="E38" s="9">
         <v>3</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" s="9">
+        <v>4</v>
+      </c>
       <c r="H38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9">
-        <v>1</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="9">
+        <v>0</v>
+      </c>
+      <c r="K38" s="9">
+        <v>100</v>
+      </c>
+      <c r="L38" s="11">
+        <v>0</v>
+      </c>
+      <c r="M38" s="11">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>1</v>
+      </c>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9">
         <v>3005</v>
@@ -2218,23 +3111,43 @@
       <c r="E39" s="9">
         <v>3</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="F39" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="9">
+        <v>4</v>
+      </c>
       <c r="H39" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="9">
-        <v>1</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="9">
+        <v>0</v>
+      </c>
+      <c r="K39" s="9">
+        <v>100</v>
+      </c>
+      <c r="L39" s="11">
+        <v>0</v>
+      </c>
+      <c r="M39" s="11">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>1</v>
+      </c>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9">
         <v>3006</v>
@@ -2246,23 +3159,43 @@
       <c r="E40" s="9">
         <v>3</v>
       </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="F40" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G40" s="9">
+        <v>4</v>
+      </c>
       <c r="H40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9">
-        <v>1</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="9">
+        <v>0</v>
+      </c>
+      <c r="K40" s="9">
+        <v>100</v>
+      </c>
+      <c r="L40" s="11">
+        <v>0</v>
+      </c>
+      <c r="M40" s="11">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
+        <v>1</v>
+      </c>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9">
         <v>3007</v>
@@ -2274,23 +3207,43 @@
       <c r="E41" s="9">
         <v>3</v>
       </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="F41" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G41" s="9">
+        <v>4</v>
+      </c>
       <c r="H41" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="9">
-        <v>1</v>
-      </c>
-      <c r="J41" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="J41" s="9">
+        <v>0</v>
+      </c>
+      <c r="K41" s="9">
         <v>100</v>
       </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="L41" s="11">
+        <v>0</v>
+      </c>
+      <c r="M41" s="11">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
+        <v>1</v>
+      </c>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9">
         <v>3008</v>
@@ -2302,23 +3255,43 @@
       <c r="E42" s="9">
         <v>3</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
+      <c r="F42" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G42" s="9">
+        <v>4</v>
+      </c>
       <c r="H42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="9">
-        <v>1</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="9">
+        <v>0</v>
+      </c>
+      <c r="K42" s="9">
+        <v>100</v>
+      </c>
+      <c r="L42" s="11">
+        <v>0</v>
+      </c>
+      <c r="M42" s="11">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1">
+        <v>1</v>
+      </c>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9">
         <v>3009</v>
@@ -2330,23 +3303,43 @@
       <c r="E43" s="9">
         <v>3</v>
       </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
+      <c r="F43" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G43" s="9">
+        <v>4</v>
+      </c>
       <c r="H43" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="9">
-        <v>1</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9">
+        <v>0</v>
+      </c>
+      <c r="K43" s="9">
+        <v>100</v>
+      </c>
+      <c r="L43" s="11">
+        <v>0</v>
+      </c>
+      <c r="M43" s="11">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <v>1</v>
+      </c>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9">
         <v>3010</v>
@@ -2358,23 +3351,43 @@
       <c r="E44" s="9">
         <v>3</v>
       </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
+      <c r="F44" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G44" s="9">
+        <v>4</v>
+      </c>
       <c r="H44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="9">
-        <v>1</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="9">
+        <v>0</v>
+      </c>
+      <c r="K44" s="9">
+        <v>100</v>
+      </c>
+      <c r="L44" s="11">
+        <v>0</v>
+      </c>
+      <c r="M44" s="11">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>1</v>
+      </c>
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="R44" s="9"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="9"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9">
         <v>3011</v>
@@ -2386,23 +3399,43 @@
       <c r="E45" s="9">
         <v>3</v>
       </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="9">
+        <v>4</v>
+      </c>
       <c r="H45" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="9">
-        <v>1</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="9">
+        <v>0</v>
+      </c>
+      <c r="K45" s="9">
+        <v>100</v>
+      </c>
+      <c r="L45" s="11">
+        <v>0</v>
+      </c>
+      <c r="M45" s="11">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <v>1</v>
+      </c>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9">
         <v>3012</v>
@@ -2414,23 +3447,43 @@
       <c r="E46" s="9">
         <v>3</v>
       </c>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
+      <c r="F46" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G46" s="9">
+        <v>4</v>
+      </c>
       <c r="H46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="9">
-        <v>1</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="9">
+        <v>0</v>
+      </c>
+      <c r="K46" s="9">
+        <v>100</v>
+      </c>
+      <c r="L46" s="11">
+        <v>0</v>
+      </c>
+      <c r="M46" s="11">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>1</v>
+      </c>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="9">
         <v>3013</v>
@@ -2442,23 +3495,43 @@
       <c r="E47" s="9">
         <v>3</v>
       </c>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
+      <c r="F47" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" s="9">
+        <v>4</v>
+      </c>
       <c r="H47" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" s="9">
-        <v>1</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="9">
+        <v>0</v>
+      </c>
+      <c r="K47" s="9">
+        <v>100</v>
+      </c>
+      <c r="L47" s="11">
+        <v>0</v>
+      </c>
+      <c r="M47" s="11">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1">
+        <v>1</v>
+      </c>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="9">
         <v>3014</v>
@@ -2470,23 +3543,43 @@
       <c r="E48" s="9">
         <v>3</v>
       </c>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
+      <c r="F48" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G48" s="9">
+        <v>4</v>
+      </c>
       <c r="H48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="9">
-        <v>1</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="9">
+        <v>0</v>
+      </c>
+      <c r="K48" s="9">
+        <v>100</v>
+      </c>
+      <c r="L48" s="11">
+        <v>0</v>
+      </c>
+      <c r="M48" s="11">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>1</v>
+      </c>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="R48" s="9"/>
+      <c r="S48" s="9"/>
+      <c r="T48" s="9"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="9">
         <v>3015</v>
@@ -2498,23 +3591,43 @@
       <c r="E49" s="9">
         <v>3</v>
       </c>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
+      <c r="F49" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G49" s="9">
+        <v>4</v>
+      </c>
       <c r="H49" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="9">
-        <v>2</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9"/>
-    </row>
-    <row r="50" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J49" s="9">
+        <v>0</v>
+      </c>
+      <c r="K49" s="9">
+        <v>100</v>
+      </c>
+      <c r="L49" s="11">
+        <v>0</v>
+      </c>
+      <c r="M49" s="11">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
+        <v>1</v>
+      </c>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="R49" s="9"/>
+      <c r="S49" s="9"/>
+      <c r="T49" s="9"/>
+    </row>
+    <row r="50" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11"/>
       <c r="B50" s="11">
         <v>4001</v>
@@ -2526,23 +3639,43 @@
       <c r="E50" s="11">
         <v>4</v>
       </c>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="11">
-        <v>1</v>
-      </c>
-      <c r="I50" s="11">
-        <v>1</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F50" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0</v>
+      </c>
+      <c r="I50" s="9">
+        <v>0</v>
+      </c>
+      <c r="J50" s="9">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9">
+        <v>100</v>
+      </c>
+      <c r="L50" s="11">
+        <v>0</v>
+      </c>
+      <c r="M50" s="11">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>1</v>
+      </c>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="R50" s="11"/>
+      <c r="S50" s="11"/>
+      <c r="T50" s="11"/>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="9">
         <v>4002</v>
@@ -2554,23 +3687,43 @@
       <c r="E51" s="9">
         <v>4</v>
       </c>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
+      <c r="F51" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H51" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="9">
-        <v>1</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="9">
+        <v>0</v>
+      </c>
+      <c r="K51" s="9">
+        <v>100</v>
+      </c>
+      <c r="L51" s="11">
+        <v>0</v>
+      </c>
+      <c r="M51" s="11">
+        <v>0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>1</v>
+      </c>
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9">
         <v>4003</v>
@@ -2582,23 +3735,43 @@
       <c r="E52" s="9">
         <v>4</v>
       </c>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
+      <c r="F52" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="9">
-        <v>1</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="9">
+        <v>0</v>
+      </c>
+      <c r="K52" s="9">
+        <v>100</v>
+      </c>
+      <c r="L52" s="11">
+        <v>0</v>
+      </c>
+      <c r="M52" s="11">
+        <v>0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>1</v>
+      </c>
+      <c r="O52" s="9"/>
+      <c r="P52" s="9"/>
+      <c r="Q52" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="R52" s="9"/>
+      <c r="S52" s="9"/>
+      <c r="T52" s="9"/>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9">
         <v>4004</v>
@@ -2610,23 +3783,43 @@
       <c r="E53" s="9">
         <v>4</v>
       </c>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
+      <c r="F53" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H53" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="9">
-        <v>1</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="9">
+        <v>0</v>
+      </c>
+      <c r="K53" s="9">
+        <v>100</v>
+      </c>
+      <c r="L53" s="11">
+        <v>0</v>
+      </c>
+      <c r="M53" s="11">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>1</v>
+      </c>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9"/>
+      <c r="T53" s="9"/>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="9">
         <v>4005</v>
@@ -2638,23 +3831,43 @@
       <c r="E54" s="9">
         <v>4</v>
       </c>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
+      <c r="F54" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H54" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="9">
-        <v>1</v>
-      </c>
-      <c r="J54" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="9"/>
-      <c r="N54" s="9"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="9">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9">
+        <v>100</v>
+      </c>
+      <c r="L54" s="11">
+        <v>0</v>
+      </c>
+      <c r="M54" s="11">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>1</v>
+      </c>
+      <c r="O54" s="9"/>
+      <c r="P54" s="9"/>
+      <c r="Q54" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R54" s="9"/>
+      <c r="S54" s="9"/>
+      <c r="T54" s="9"/>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="9">
         <v>4006</v>
@@ -2666,23 +3879,43 @@
       <c r="E55" s="9">
         <v>4</v>
       </c>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
+      <c r="F55" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H55" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="9">
-        <v>1</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="9"/>
-      <c r="N55" s="9"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="9">
+        <v>0</v>
+      </c>
+      <c r="K55" s="9">
+        <v>100</v>
+      </c>
+      <c r="L55" s="11">
+        <v>0</v>
+      </c>
+      <c r="M55" s="11">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>1</v>
+      </c>
+      <c r="O55" s="9"/>
+      <c r="P55" s="9"/>
+      <c r="Q55" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R55" s="9"/>
+      <c r="S55" s="9"/>
+      <c r="T55" s="9"/>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="9">
         <v>4007</v>
@@ -2694,23 +3927,43 @@
       <c r="E56" s="9">
         <v>4</v>
       </c>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
+      <c r="F56" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H56" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="9">
-        <v>1</v>
-      </c>
-      <c r="J56" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="9"/>
-      <c r="N56" s="9"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="9">
+        <v>0</v>
+      </c>
+      <c r="K56" s="9">
+        <v>100</v>
+      </c>
+      <c r="L56" s="11">
+        <v>0</v>
+      </c>
+      <c r="M56" s="11">
+        <v>0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>1</v>
+      </c>
+      <c r="O56" s="9"/>
+      <c r="P56" s="9"/>
+      <c r="Q56" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R56" s="9"/>
+      <c r="S56" s="9"/>
+      <c r="T56" s="9"/>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="9">
         <v>4008</v>
@@ -2722,23 +3975,43 @@
       <c r="E57" s="9">
         <v>4</v>
       </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
+      <c r="F57" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H57" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="9">
-        <v>1</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="9"/>
-      <c r="N57" s="9"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="9">
+        <v>0</v>
+      </c>
+      <c r="K57" s="9">
+        <v>100</v>
+      </c>
+      <c r="L57" s="11">
+        <v>0</v>
+      </c>
+      <c r="M57" s="11">
+        <v>0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>1</v>
+      </c>
+      <c r="O57" s="9"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R57" s="9"/>
+      <c r="S57" s="9"/>
+      <c r="T57" s="9"/>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9">
         <v>4009</v>
@@ -2750,23 +4023,43 @@
       <c r="E58" s="9">
         <v>4</v>
       </c>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
+      <c r="F58" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="G58" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H58" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="9">
-        <v>1</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="9"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="9">
+        <v>0</v>
+      </c>
+      <c r="K58" s="9">
+        <v>100</v>
+      </c>
+      <c r="L58" s="11">
+        <v>0</v>
+      </c>
+      <c r="M58" s="11">
+        <v>0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>1</v>
+      </c>
+      <c r="O58" s="9"/>
+      <c r="P58" s="9"/>
+      <c r="Q58" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R58" s="9"/>
+      <c r="S58" s="9"/>
+      <c r="T58" s="9"/>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9">
         <v>4010</v>
@@ -2778,23 +4071,43 @@
       <c r="E59" s="9">
         <v>4</v>
       </c>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
+      <c r="F59" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" s="9">
-        <v>1</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
-      <c r="M59" s="9"/>
-      <c r="N59" s="9"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="9">
+        <v>0</v>
+      </c>
+      <c r="K59" s="9">
+        <v>100</v>
+      </c>
+      <c r="L59" s="11">
+        <v>0</v>
+      </c>
+      <c r="M59" s="11">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>1</v>
+      </c>
+      <c r="O59" s="9"/>
+      <c r="P59" s="9"/>
+      <c r="Q59" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R59" s="9"/>
+      <c r="S59" s="9"/>
+      <c r="T59" s="9"/>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="9">
         <v>4011</v>
@@ -2806,23 +4119,43 @@
       <c r="E60" s="9">
         <v>4</v>
       </c>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
+      <c r="F60" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H60" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="9">
-        <v>1</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K60" s="9"/>
-      <c r="L60" s="9"/>
-      <c r="M60" s="9"/>
-      <c r="N60" s="9"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="9">
+        <v>0</v>
+      </c>
+      <c r="K60" s="9">
+        <v>100</v>
+      </c>
+      <c r="L60" s="11">
+        <v>0</v>
+      </c>
+      <c r="M60" s="11">
+        <v>0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>1</v>
+      </c>
+      <c r="O60" s="9"/>
+      <c r="P60" s="9"/>
+      <c r="Q60" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R60" s="9"/>
+      <c r="S60" s="9"/>
+      <c r="T60" s="9"/>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="9">
         <v>4012</v>
@@ -2834,23 +4167,43 @@
       <c r="E61" s="9">
         <v>4</v>
       </c>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
+      <c r="F61" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H61" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61" s="9">
-        <v>1</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K61" s="9"/>
-      <c r="L61" s="9"/>
-      <c r="M61" s="9"/>
-      <c r="N61" s="9"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="9">
+        <v>0</v>
+      </c>
+      <c r="K61" s="9">
+        <v>100</v>
+      </c>
+      <c r="L61" s="11">
+        <v>0</v>
+      </c>
+      <c r="M61" s="11">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1">
+        <v>1</v>
+      </c>
+      <c r="O61" s="9"/>
+      <c r="P61" s="9"/>
+      <c r="Q61" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="R61" s="9"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="9"/>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9">
         <v>4013</v>
@@ -2862,23 +4215,43 @@
       <c r="E62" s="9">
         <v>4</v>
       </c>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
+      <c r="F62" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H62" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62" s="9">
-        <v>1</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
-      <c r="M62" s="9"/>
-      <c r="N62" s="9"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="9">
+        <v>0</v>
+      </c>
+      <c r="K62" s="9">
+        <v>100</v>
+      </c>
+      <c r="L62" s="11">
+        <v>0</v>
+      </c>
+      <c r="M62" s="11">
+        <v>0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>1</v>
+      </c>
+      <c r="O62" s="9"/>
+      <c r="P62" s="9"/>
+      <c r="Q62" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R62" s="9"/>
+      <c r="S62" s="9"/>
+      <c r="T62" s="9"/>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="9">
         <v>4014</v>
@@ -2890,23 +4263,43 @@
       <c r="E63" s="9">
         <v>4</v>
       </c>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
+      <c r="F63" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H63" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" s="9">
-        <v>1</v>
-      </c>
-      <c r="J63" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
-      <c r="M63" s="9"/>
-      <c r="N63" s="9"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="9">
+        <v>0</v>
+      </c>
+      <c r="K63" s="9">
+        <v>100</v>
+      </c>
+      <c r="L63" s="11">
+        <v>0</v>
+      </c>
+      <c r="M63" s="11">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>1</v>
+      </c>
+      <c r="O63" s="9"/>
+      <c r="P63" s="9"/>
+      <c r="Q63" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="R63" s="9"/>
+      <c r="S63" s="9"/>
+      <c r="T63" s="9"/>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="9">
         <v>4015</v>
@@ -2918,23 +4311,43 @@
       <c r="E64" s="9">
         <v>4</v>
       </c>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
+      <c r="F64" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0.5</v>
+      </c>
       <c r="H64" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9">
-        <v>2</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="K64" s="9"/>
-      <c r="L64" s="9"/>
-      <c r="M64" s="9"/>
-      <c r="N64" s="9"/>
-    </row>
-    <row r="65" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="J64" s="9">
+        <v>0</v>
+      </c>
+      <c r="K64" s="9">
+        <v>100</v>
+      </c>
+      <c r="L64" s="11">
+        <v>0</v>
+      </c>
+      <c r="M64" s="11">
+        <v>0</v>
+      </c>
+      <c r="N64" s="1">
+        <v>1</v>
+      </c>
+      <c r="O64" s="9"/>
+      <c r="P64" s="9"/>
+      <c r="Q64" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="R64" s="9"/>
+      <c r="S64" s="9"/>
+      <c r="T64" s="9"/>
+    </row>
+    <row r="65" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11"/>
       <c r="B65" s="11">
         <v>5001</v>
@@ -2948,25 +4361,41 @@
       </c>
       <c r="F65" s="11"/>
       <c r="G65" s="11"/>
-      <c r="H65" s="11">
-        <v>1</v>
+      <c r="H65" s="9">
+        <v>0</v>
       </c>
       <c r="I65" s="11">
-        <v>1</v>
-      </c>
-      <c r="J65" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="M65" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="N65" s="11"/>
-    </row>
-    <row r="66" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="11">
+        <v>0</v>
+      </c>
+      <c r="K65" s="9">
+        <v>100</v>
+      </c>
+      <c r="L65" s="11">
+        <v>1</v>
+      </c>
+      <c r="M65" s="11">
+        <v>1</v>
+      </c>
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="O65" s="11"/>
+      <c r="P65" s="11"/>
+      <c r="Q65" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="R65" s="11"/>
+      <c r="S65" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="T65" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12"/>
       <c r="B66" s="12">
         <v>5002</v>
@@ -2980,27 +4409,43 @@
       </c>
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
-      <c r="H66" s="12">
-        <v>1</v>
+      <c r="H66" s="9">
+        <v>0</v>
       </c>
       <c r="I66" s="12">
-        <v>1</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K66" s="12"/>
-      <c r="L66" s="12"/>
-      <c r="M66" s="12"/>
-      <c r="N66" s="12"/>
-    </row>
-    <row r="67" spans="1:14" s="13" customFormat="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J66" s="12">
+        <v>1</v>
+      </c>
+      <c r="K66" s="9">
+        <v>100</v>
+      </c>
+      <c r="L66" s="11">
+        <v>1</v>
+      </c>
+      <c r="M66" s="11">
+        <v>1</v>
+      </c>
+      <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="12"/>
+      <c r="P66" s="12"/>
+      <c r="Q66" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R66" s="12"/>
+      <c r="S66" s="12"/>
+      <c r="T66" s="12"/>
+    </row>
+    <row r="67" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12"/>
       <c r="B67" s="12">
         <v>5003</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="12">
@@ -3008,21 +4453,37 @@
       </c>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
-      <c r="H67" s="12">
-        <v>1</v>
+      <c r="H67" s="9">
+        <v>0</v>
       </c>
       <c r="I67" s="12">
-        <v>1</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="12"/>
-      <c r="N67" s="12"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="J67" s="12">
+        <v>0</v>
+      </c>
+      <c r="K67" s="9">
+        <v>100</v>
+      </c>
+      <c r="L67" s="11">
+        <v>0</v>
+      </c>
+      <c r="M67" s="11">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="12"/>
+      <c r="P67" s="12"/>
+      <c r="Q67" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="R67" s="12"/>
+      <c r="S67" s="12"/>
+      <c r="T67" s="12"/>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="7"/>
@@ -3035,10 +4496,14 @@
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="7"/>
@@ -3051,10 +4516,14 @@
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="R69" s="3"/>
+      <c r="S69" s="3"/>
+      <c r="T69" s="3"/>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="7"/>
@@ -3067,10 +4536,14 @@
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="7"/>
@@ -3083,10 +4556,14 @@
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="R71" s="3"/>
+      <c r="S71" s="3"/>
+      <c r="T71" s="3"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="7"/>
@@ -3099,10 +4576,14 @@
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="7"/>
@@ -3115,10 +4596,14 @@
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="R73" s="3"/>
+      <c r="S73" s="3"/>
+      <c r="T73" s="3"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="7"/>
@@ -3131,10 +4616,14 @@
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="7"/>
@@ -3147,10 +4636,14 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="R75" s="3"/>
+      <c r="S75" s="3"/>
+      <c r="T75" s="3"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="7"/>
@@ -3163,10 +4656,14 @@
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="7"/>
@@ -3179,10 +4676,14 @@
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="R77" s="3"/>
+      <c r="S77" s="3"/>
+      <c r="T77" s="3"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="7"/>
@@ -3195,10 +4696,14 @@
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="7"/>
@@ -3211,10 +4716,14 @@
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="R79" s="3"/>
+      <c r="S79" s="3"/>
+      <c r="T79" s="3"/>
+    </row>
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="7"/>
@@ -3227,10 +4736,14 @@
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="3"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+    </row>
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="7"/>
@@ -3243,10 +4756,14 @@
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+      <c r="Q81" s="3"/>
+      <c r="R81" s="3"/>
+      <c r="S81" s="3"/>
+      <c r="T81" s="3"/>
+    </row>
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="7"/>
@@ -3259,10 +4776,14 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-      <c r="M82" s="3"/>
-      <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="7"/>
@@ -3275,10 +4796,14 @@
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
-      <c r="M83" s="3"/>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+      <c r="Q83" s="3"/>
+      <c r="R83" s="3"/>
+      <c r="S83" s="3"/>
+      <c r="T83" s="3"/>
+    </row>
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="7"/>
@@ -3291,10 +4816,14 @@
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+    </row>
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="7"/>
@@ -3307,10 +4836,14 @@
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+      <c r="Q85" s="3"/>
+      <c r="R85" s="3"/>
+      <c r="S85" s="3"/>
+      <c r="T85" s="3"/>
+    </row>
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="7"/>
@@ -3323,10 +4856,14 @@
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
-      <c r="M86" s="3"/>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+    </row>
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="7"/>
@@ -3339,10 +4876,14 @@
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+      <c r="Q87" s="3"/>
+      <c r="R87" s="3"/>
+      <c r="S87" s="3"/>
+      <c r="T87" s="3"/>
+    </row>
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="7"/>
@@ -3355,10 +4896,14 @@
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+    </row>
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="7"/>
@@ -3371,10 +4916,14 @@
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3"/>
-      <c r="M89" s="3"/>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O89" s="3"/>
+      <c r="P89" s="3"/>
+      <c r="Q89" s="3"/>
+      <c r="R89" s="3"/>
+      <c r="S89" s="3"/>
+      <c r="T89" s="3"/>
+    </row>
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="7"/>
@@ -3387,10 +4936,14 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="7"/>
@@ -3403,10 +4956,14 @@
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
       <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
+      <c r="Q91" s="3"/>
+      <c r="R91" s="3"/>
+      <c r="S91" s="3"/>
+      <c r="T91" s="3"/>
+    </row>
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="7"/>
@@ -3419,10 +4976,14 @@
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
       <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3"/>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+    </row>
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="7"/>
@@ -3435,10 +4996,14 @@
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
-      <c r="M93" s="3"/>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+      <c r="Q93" s="3"/>
+      <c r="R93" s="3"/>
+      <c r="S93" s="3"/>
+      <c r="T93" s="3"/>
+    </row>
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="7"/>
@@ -3451,10 +5016,14 @@
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
       <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+    </row>
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="7"/>
@@ -3467,10 +5036,14 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-      <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="7"/>
@@ -3483,10 +5056,14 @@
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
       <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3"/>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+    </row>
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="7"/>
@@ -3499,10 +5076,14 @@
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+      <c r="Q97" s="3"/>
+      <c r="R97" s="3"/>
+      <c r="S97" s="3"/>
+      <c r="T97" s="3"/>
+    </row>
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="7"/>
@@ -3515,10 +5096,14 @@
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
       <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+      <c r="Q98" s="3"/>
+      <c r="R98" s="3"/>
+      <c r="S98" s="3"/>
+      <c r="T98" s="3"/>
+    </row>
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="7"/>
@@ -3531,10 +5116,14 @@
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
-      <c r="M99" s="3"/>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
+      <c r="R99" s="3"/>
+      <c r="S99" s="3"/>
+      <c r="T99" s="3"/>
+    </row>
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="7"/>
@@ -3547,10 +5136,14 @@
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
       <c r="L100" s="3"/>
-      <c r="M100" s="3"/>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+      <c r="Q100" s="3"/>
+      <c r="R100" s="3"/>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3"/>
+    </row>
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="7"/>
@@ -3563,10 +5156,14 @@
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
       <c r="L101" s="3"/>
-      <c r="M101" s="3"/>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
+      <c r="R101" s="3"/>
+      <c r="S101" s="3"/>
+      <c r="T101" s="3"/>
+    </row>
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="7"/>
@@ -3579,10 +5176,14 @@
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
       <c r="L102" s="3"/>
-      <c r="M102" s="3"/>
-      <c r="N102" s="3"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
+      <c r="T102" s="3"/>
+    </row>
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="7"/>
@@ -3595,10 +5196,14 @@
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
-      <c r="M103" s="3"/>
-      <c r="N103" s="3"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O103" s="3"/>
+      <c r="P103" s="3"/>
+      <c r="Q103" s="3"/>
+      <c r="R103" s="3"/>
+      <c r="S103" s="3"/>
+      <c r="T103" s="3"/>
+    </row>
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="7"/>
@@ -3611,10 +5216,14 @@
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
-      <c r="M104" s="3"/>
-      <c r="N104" s="3"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O104" s="3"/>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3"/>
+      <c r="S104" s="3"/>
+      <c r="T104" s="3"/>
+    </row>
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="7"/>
@@ -3627,10 +5236,14 @@
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
-      <c r="M105" s="3"/>
-      <c r="N105" s="3"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O105" s="3"/>
+      <c r="P105" s="3"/>
+      <c r="Q105" s="3"/>
+      <c r="R105" s="3"/>
+      <c r="S105" s="3"/>
+      <c r="T105" s="3"/>
+    </row>
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="7"/>
@@ -3643,10 +5256,14 @@
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
       <c r="L106" s="3"/>
-      <c r="M106" s="3"/>
-      <c r="N106" s="3"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O106" s="3"/>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3"/>
+      <c r="R106" s="3"/>
+      <c r="S106" s="3"/>
+      <c r="T106" s="3"/>
+    </row>
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="7"/>
@@ -3659,10 +5276,14 @@
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
-      <c r="M107" s="3"/>
-      <c r="N107" s="3"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O107" s="3"/>
+      <c r="P107" s="3"/>
+      <c r="Q107" s="3"/>
+      <c r="R107" s="3"/>
+      <c r="S107" s="3"/>
+      <c r="T107" s="3"/>
+    </row>
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="7"/>
@@ -3675,10 +5296,14 @@
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
       <c r="L108" s="3"/>
-      <c r="M108" s="3"/>
-      <c r="N108" s="3"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O108" s="3"/>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3"/>
+      <c r="S108" s="3"/>
+      <c r="T108" s="3"/>
+    </row>
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="7"/>
@@ -3691,10 +5316,14 @@
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
       <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O109" s="3"/>
+      <c r="P109" s="3"/>
+      <c r="Q109" s="3"/>
+      <c r="R109" s="3"/>
+      <c r="S109" s="3"/>
+      <c r="T109" s="3"/>
+    </row>
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="7"/>
@@ -3707,10 +5336,14 @@
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
       <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O110" s="3"/>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="3"/>
+      <c r="R110" s="3"/>
+      <c r="S110" s="3"/>
+      <c r="T110" s="3"/>
+    </row>
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="7"/>
@@ -3723,10 +5356,14 @@
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
-      <c r="M111" s="3"/>
-      <c r="N111" s="3"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O111" s="3"/>
+      <c r="P111" s="3"/>
+      <c r="Q111" s="3"/>
+      <c r="R111" s="3"/>
+      <c r="S111" s="3"/>
+      <c r="T111" s="3"/>
+    </row>
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="7"/>
@@ -3739,10 +5376,14 @@
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
       <c r="L112" s="3"/>
-      <c r="M112" s="3"/>
-      <c r="N112" s="3"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O112" s="3"/>
+      <c r="P112" s="3"/>
+      <c r="Q112" s="3"/>
+      <c r="R112" s="3"/>
+      <c r="S112" s="3"/>
+      <c r="T112" s="3"/>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="7"/>
@@ -3755,10 +5396,14 @@
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
       <c r="L113" s="3"/>
-      <c r="M113" s="3"/>
-      <c r="N113" s="3"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O113" s="3"/>
+      <c r="P113" s="3"/>
+      <c r="Q113" s="3"/>
+      <c r="R113" s="3"/>
+      <c r="S113" s="3"/>
+      <c r="T113" s="3"/>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="7"/>
@@ -3771,10 +5416,14 @@
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
       <c r="L114" s="3"/>
-      <c r="M114" s="3"/>
-      <c r="N114" s="3"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O114" s="3"/>
+      <c r="P114" s="3"/>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="3"/>
+      <c r="S114" s="3"/>
+      <c r="T114" s="3"/>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="7"/>
@@ -3787,10 +5436,14 @@
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
       <c r="L115" s="3"/>
-      <c r="M115" s="3"/>
-      <c r="N115" s="3"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O115" s="3"/>
+      <c r="P115" s="3"/>
+      <c r="Q115" s="3"/>
+      <c r="R115" s="3"/>
+      <c r="S115" s="3"/>
+      <c r="T115" s="3"/>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="7"/>
@@ -3803,10 +5456,14 @@
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
       <c r="L116" s="3"/>
-      <c r="M116" s="3"/>
-      <c r="N116" s="3"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O116" s="3"/>
+      <c r="P116" s="3"/>
+      <c r="Q116" s="3"/>
+      <c r="R116" s="3"/>
+      <c r="S116" s="3"/>
+      <c r="T116" s="3"/>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="7"/>
@@ -3819,10 +5476,14 @@
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
       <c r="L117" s="3"/>
-      <c r="M117" s="3"/>
-      <c r="N117" s="3"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O117" s="3"/>
+      <c r="P117" s="3"/>
+      <c r="Q117" s="3"/>
+      <c r="R117" s="3"/>
+      <c r="S117" s="3"/>
+      <c r="T117" s="3"/>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="7"/>
@@ -3835,10 +5496,14 @@
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
       <c r="L118" s="3"/>
-      <c r="M118" s="3"/>
-      <c r="N118" s="3"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O118" s="3"/>
+      <c r="P118" s="3"/>
+      <c r="Q118" s="3"/>
+      <c r="R118" s="3"/>
+      <c r="S118" s="3"/>
+      <c r="T118" s="3"/>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="7"/>
@@ -3851,10 +5516,14 @@
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
       <c r="L119" s="3"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O119" s="3"/>
+      <c r="P119" s="3"/>
+      <c r="Q119" s="3"/>
+      <c r="R119" s="3"/>
+      <c r="S119" s="3"/>
+      <c r="T119" s="3"/>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="7"/>
@@ -3867,10 +5536,14 @@
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
       <c r="L120" s="3"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="3"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O120" s="3"/>
+      <c r="P120" s="3"/>
+      <c r="Q120" s="3"/>
+      <c r="R120" s="3"/>
+      <c r="S120" s="3"/>
+      <c r="T120" s="3"/>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="7"/>
@@ -3883,10 +5556,14 @@
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
       <c r="L121" s="3"/>
-      <c r="M121" s="3"/>
-      <c r="N121" s="3"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O121" s="3"/>
+      <c r="P121" s="3"/>
+      <c r="Q121" s="3"/>
+      <c r="R121" s="3"/>
+      <c r="S121" s="3"/>
+      <c r="T121" s="3"/>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="7"/>
@@ -3899,10 +5576,14 @@
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
       <c r="L122" s="3"/>
-      <c r="M122" s="3"/>
-      <c r="N122" s="3"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O122" s="3"/>
+      <c r="P122" s="3"/>
+      <c r="Q122" s="3"/>
+      <c r="R122" s="3"/>
+      <c r="S122" s="3"/>
+      <c r="T122" s="3"/>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="7"/>
@@ -3915,10 +5596,14 @@
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
       <c r="L123" s="3"/>
-      <c r="M123" s="3"/>
-      <c r="N123" s="3"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O123" s="3"/>
+      <c r="P123" s="3"/>
+      <c r="Q123" s="3"/>
+      <c r="R123" s="3"/>
+      <c r="S123" s="3"/>
+      <c r="T123" s="3"/>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="7"/>
@@ -3931,10 +5616,14 @@
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
       <c r="L124" s="3"/>
-      <c r="M124" s="3"/>
-      <c r="N124" s="3"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O124" s="3"/>
+      <c r="P124" s="3"/>
+      <c r="Q124" s="3"/>
+      <c r="R124" s="3"/>
+      <c r="S124" s="3"/>
+      <c r="T124" s="3"/>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="7"/>
@@ -3947,10 +5636,14 @@
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
       <c r="L125" s="3"/>
-      <c r="M125" s="3"/>
-      <c r="N125" s="3"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O125" s="3"/>
+      <c r="P125" s="3"/>
+      <c r="Q125" s="3"/>
+      <c r="R125" s="3"/>
+      <c r="S125" s="3"/>
+      <c r="T125" s="3"/>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="7"/>
@@ -3963,10 +5656,14 @@
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
       <c r="L126" s="3"/>
-      <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O126" s="3"/>
+      <c r="P126" s="3"/>
+      <c r="Q126" s="3"/>
+      <c r="R126" s="3"/>
+      <c r="S126" s="3"/>
+      <c r="T126" s="3"/>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="7"/>
@@ -3979,10 +5676,14 @@
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
       <c r="L127" s="3"/>
-      <c r="M127" s="3"/>
-      <c r="N127" s="3"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O127" s="3"/>
+      <c r="P127" s="3"/>
+      <c r="Q127" s="3"/>
+      <c r="R127" s="3"/>
+      <c r="S127" s="3"/>
+      <c r="T127" s="3"/>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="7"/>
@@ -3995,10 +5696,14 @@
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
       <c r="L128" s="3"/>
-      <c r="M128" s="3"/>
-      <c r="N128" s="3"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O128" s="3"/>
+      <c r="P128" s="3"/>
+      <c r="Q128" s="3"/>
+      <c r="R128" s="3"/>
+      <c r="S128" s="3"/>
+      <c r="T128" s="3"/>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="7"/>
@@ -4011,10 +5716,14 @@
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
       <c r="L129" s="3"/>
-      <c r="M129" s="3"/>
-      <c r="N129" s="3"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O129" s="3"/>
+      <c r="P129" s="3"/>
+      <c r="Q129" s="3"/>
+      <c r="R129" s="3"/>
+      <c r="S129" s="3"/>
+      <c r="T129" s="3"/>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="7"/>
@@ -4027,10 +5736,14 @@
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
       <c r="L130" s="3"/>
-      <c r="M130" s="3"/>
-      <c r="N130" s="3"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O130" s="3"/>
+      <c r="P130" s="3"/>
+      <c r="Q130" s="3"/>
+      <c r="R130" s="3"/>
+      <c r="S130" s="3"/>
+      <c r="T130" s="3"/>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="7"/>
@@ -4043,10 +5756,14 @@
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
       <c r="L131" s="3"/>
-      <c r="M131" s="3"/>
-      <c r="N131" s="3"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O131" s="3"/>
+      <c r="P131" s="3"/>
+      <c r="Q131" s="3"/>
+      <c r="R131" s="3"/>
+      <c r="S131" s="3"/>
+      <c r="T131" s="3"/>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="7"/>
@@ -4059,10 +5776,14 @@
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
       <c r="L132" s="3"/>
-      <c r="M132" s="3"/>
-      <c r="N132" s="3"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O132" s="3"/>
+      <c r="P132" s="3"/>
+      <c r="Q132" s="3"/>
+      <c r="R132" s="3"/>
+      <c r="S132" s="3"/>
+      <c r="T132" s="3"/>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="7"/>
@@ -4075,10 +5796,14 @@
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="3"/>
-      <c r="M133" s="3"/>
-      <c r="N133" s="3"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O133" s="3"/>
+      <c r="P133" s="3"/>
+      <c r="Q133" s="3"/>
+      <c r="R133" s="3"/>
+      <c r="S133" s="3"/>
+      <c r="T133" s="3"/>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="7"/>
@@ -4091,10 +5816,14 @@
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
       <c r="L134" s="3"/>
-      <c r="M134" s="3"/>
-      <c r="N134" s="3"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O134" s="3"/>
+      <c r="P134" s="3"/>
+      <c r="Q134" s="3"/>
+      <c r="R134" s="3"/>
+      <c r="S134" s="3"/>
+      <c r="T134" s="3"/>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="7"/>
@@ -4107,10 +5836,14 @@
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="3"/>
-      <c r="M135" s="3"/>
-      <c r="N135" s="3"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O135" s="3"/>
+      <c r="P135" s="3"/>
+      <c r="Q135" s="3"/>
+      <c r="R135" s="3"/>
+      <c r="S135" s="3"/>
+      <c r="T135" s="3"/>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="7"/>
@@ -4123,10 +5856,14 @@
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
       <c r="L136" s="3"/>
-      <c r="M136" s="3"/>
-      <c r="N136" s="3"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O136" s="3"/>
+      <c r="P136" s="3"/>
+      <c r="Q136" s="3"/>
+      <c r="R136" s="3"/>
+      <c r="S136" s="3"/>
+      <c r="T136" s="3"/>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="7"/>
@@ -4139,10 +5876,14 @@
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="3"/>
-      <c r="M137" s="3"/>
-      <c r="N137" s="3"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O137" s="3"/>
+      <c r="P137" s="3"/>
+      <c r="Q137" s="3"/>
+      <c r="R137" s="3"/>
+      <c r="S137" s="3"/>
+      <c r="T137" s="3"/>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="7"/>
@@ -4155,10 +5896,14 @@
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
       <c r="L138" s="3"/>
-      <c r="M138" s="3"/>
-      <c r="N138" s="3"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O138" s="3"/>
+      <c r="P138" s="3"/>
+      <c r="Q138" s="3"/>
+      <c r="R138" s="3"/>
+      <c r="S138" s="3"/>
+      <c r="T138" s="3"/>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="7"/>
@@ -4171,10 +5916,14 @@
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
-      <c r="M139" s="3"/>
-      <c r="N139" s="3"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O139" s="3"/>
+      <c r="P139" s="3"/>
+      <c r="Q139" s="3"/>
+      <c r="R139" s="3"/>
+      <c r="S139" s="3"/>
+      <c r="T139" s="3"/>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="7"/>
@@ -4187,10 +5936,14 @@
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
       <c r="L140" s="3"/>
-      <c r="M140" s="3"/>
-      <c r="N140" s="3"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O140" s="3"/>
+      <c r="P140" s="3"/>
+      <c r="Q140" s="3"/>
+      <c r="R140" s="3"/>
+      <c r="S140" s="3"/>
+      <c r="T140" s="3"/>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="7"/>
@@ -4203,10 +5956,14 @@
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="3"/>
-      <c r="M141" s="3"/>
-      <c r="N141" s="3"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O141" s="3"/>
+      <c r="P141" s="3"/>
+      <c r="Q141" s="3"/>
+      <c r="R141" s="3"/>
+      <c r="S141" s="3"/>
+      <c r="T141" s="3"/>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="7"/>
@@ -4219,10 +5976,14 @@
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
       <c r="L142" s="3"/>
-      <c r="M142" s="3"/>
-      <c r="N142" s="3"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O142" s="3"/>
+      <c r="P142" s="3"/>
+      <c r="Q142" s="3"/>
+      <c r="R142" s="3"/>
+      <c r="S142" s="3"/>
+      <c r="T142" s="3"/>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="7"/>
@@ -4235,10 +5996,14 @@
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="3"/>
-      <c r="M143" s="3"/>
-      <c r="N143" s="3"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O143" s="3"/>
+      <c r="P143" s="3"/>
+      <c r="Q143" s="3"/>
+      <c r="R143" s="3"/>
+      <c r="S143" s="3"/>
+      <c r="T143" s="3"/>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="7"/>
@@ -4251,10 +6016,14 @@
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
       <c r="L144" s="3"/>
-      <c r="M144" s="3"/>
-      <c r="N144" s="3"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O144" s="3"/>
+      <c r="P144" s="3"/>
+      <c r="Q144" s="3"/>
+      <c r="R144" s="3"/>
+      <c r="S144" s="3"/>
+      <c r="T144" s="3"/>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="7"/>
@@ -4267,10 +6036,14 @@
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="3"/>
-      <c r="M145" s="3"/>
-      <c r="N145" s="3"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O145" s="3"/>
+      <c r="P145" s="3"/>
+      <c r="Q145" s="3"/>
+      <c r="R145" s="3"/>
+      <c r="S145" s="3"/>
+      <c r="T145" s="3"/>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="7"/>
@@ -4283,10 +6056,14 @@
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
       <c r="L146" s="3"/>
-      <c r="M146" s="3"/>
-      <c r="N146" s="3"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O146" s="3"/>
+      <c r="P146" s="3"/>
+      <c r="Q146" s="3"/>
+      <c r="R146" s="3"/>
+      <c r="S146" s="3"/>
+      <c r="T146" s="3"/>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="7"/>
@@ -4299,10 +6076,14 @@
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="3"/>
-      <c r="M147" s="3"/>
-      <c r="N147" s="3"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O147" s="3"/>
+      <c r="P147" s="3"/>
+      <c r="Q147" s="3"/>
+      <c r="R147" s="3"/>
+      <c r="S147" s="3"/>
+      <c r="T147" s="3"/>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="7"/>
@@ -4315,10 +6096,14 @@
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
       <c r="L148" s="3"/>
-      <c r="M148" s="3"/>
-      <c r="N148" s="3"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O148" s="3"/>
+      <c r="P148" s="3"/>
+      <c r="Q148" s="3"/>
+      <c r="R148" s="3"/>
+      <c r="S148" s="3"/>
+      <c r="T148" s="3"/>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="7"/>
@@ -4331,10 +6116,14 @@
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="3"/>
-      <c r="M149" s="3"/>
-      <c r="N149" s="3"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O149" s="3"/>
+      <c r="P149" s="3"/>
+      <c r="Q149" s="3"/>
+      <c r="R149" s="3"/>
+      <c r="S149" s="3"/>
+      <c r="T149" s="3"/>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="7"/>
@@ -4347,10 +6136,14 @@
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
       <c r="L150" s="3"/>
-      <c r="M150" s="3"/>
-      <c r="N150" s="3"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O150" s="3"/>
+      <c r="P150" s="3"/>
+      <c r="Q150" s="3"/>
+      <c r="R150" s="3"/>
+      <c r="S150" s="3"/>
+      <c r="T150" s="3"/>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="7"/>
@@ -4363,10 +6156,14 @@
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
       <c r="L151" s="3"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="3"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O151" s="3"/>
+      <c r="P151" s="3"/>
+      <c r="Q151" s="3"/>
+      <c r="R151" s="3"/>
+      <c r="S151" s="3"/>
+      <c r="T151" s="3"/>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="7"/>
@@ -4379,10 +6176,14 @@
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
       <c r="L152" s="3"/>
-      <c r="M152" s="3"/>
-      <c r="N152" s="3"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O152" s="3"/>
+      <c r="P152" s="3"/>
+      <c r="Q152" s="3"/>
+      <c r="R152" s="3"/>
+      <c r="S152" s="3"/>
+      <c r="T152" s="3"/>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="7"/>
@@ -4395,10 +6196,14 @@
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
       <c r="L153" s="3"/>
-      <c r="M153" s="3"/>
-      <c r="N153" s="3"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O153" s="3"/>
+      <c r="P153" s="3"/>
+      <c r="Q153" s="3"/>
+      <c r="R153" s="3"/>
+      <c r="S153" s="3"/>
+      <c r="T153" s="3"/>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="7"/>
@@ -4411,10 +6216,14 @@
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="3"/>
-      <c r="M154" s="3"/>
-      <c r="N154" s="3"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O154" s="3"/>
+      <c r="P154" s="3"/>
+      <c r="Q154" s="3"/>
+      <c r="R154" s="3"/>
+      <c r="S154" s="3"/>
+      <c r="T154" s="3"/>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="7"/>
@@ -4427,10 +6236,14 @@
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
       <c r="L155" s="3"/>
-      <c r="M155" s="3"/>
-      <c r="N155" s="3"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O155" s="3"/>
+      <c r="P155" s="3"/>
+      <c r="Q155" s="3"/>
+      <c r="R155" s="3"/>
+      <c r="S155" s="3"/>
+      <c r="T155" s="3"/>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="7"/>
@@ -4443,10 +6256,14 @@
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="3"/>
-      <c r="M156" s="3"/>
-      <c r="N156" s="3"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O156" s="3"/>
+      <c r="P156" s="3"/>
+      <c r="Q156" s="3"/>
+      <c r="R156" s="3"/>
+      <c r="S156" s="3"/>
+      <c r="T156" s="3"/>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="7"/>
@@ -4459,10 +6276,14 @@
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="3"/>
-      <c r="M157" s="3"/>
-      <c r="N157" s="3"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O157" s="3"/>
+      <c r="P157" s="3"/>
+      <c r="Q157" s="3"/>
+      <c r="R157" s="3"/>
+      <c r="S157" s="3"/>
+      <c r="T157" s="3"/>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="7"/>
@@ -4475,10 +6296,14 @@
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="3"/>
-      <c r="M158" s="3"/>
-      <c r="N158" s="3"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O158" s="3"/>
+      <c r="P158" s="3"/>
+      <c r="Q158" s="3"/>
+      <c r="R158" s="3"/>
+      <c r="S158" s="3"/>
+      <c r="T158" s="3"/>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="7"/>
@@ -4491,10 +6316,14 @@
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
       <c r="L159" s="3"/>
-      <c r="M159" s="3"/>
-      <c r="N159" s="3"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O159" s="3"/>
+      <c r="P159" s="3"/>
+      <c r="Q159" s="3"/>
+      <c r="R159" s="3"/>
+      <c r="S159" s="3"/>
+      <c r="T159" s="3"/>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="7"/>
@@ -4507,10 +6336,14 @@
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
       <c r="L160" s="3"/>
-      <c r="M160" s="3"/>
-      <c r="N160" s="3"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O160" s="3"/>
+      <c r="P160" s="3"/>
+      <c r="Q160" s="3"/>
+      <c r="R160" s="3"/>
+      <c r="S160" s="3"/>
+      <c r="T160" s="3"/>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="7"/>
@@ -4523,10 +6356,14 @@
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
       <c r="L161" s="3"/>
-      <c r="M161" s="3"/>
-      <c r="N161" s="3"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O161" s="3"/>
+      <c r="P161" s="3"/>
+      <c r="Q161" s="3"/>
+      <c r="R161" s="3"/>
+      <c r="S161" s="3"/>
+      <c r="T161" s="3"/>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="7"/>
@@ -4539,10 +6376,14 @@
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
       <c r="L162" s="3"/>
-      <c r="M162" s="3"/>
-      <c r="N162" s="3"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O162" s="3"/>
+      <c r="P162" s="3"/>
+      <c r="Q162" s="3"/>
+      <c r="R162" s="3"/>
+      <c r="S162" s="3"/>
+      <c r="T162" s="3"/>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="7"/>
@@ -4555,10 +6396,14 @@
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
       <c r="L163" s="3"/>
-      <c r="M163" s="3"/>
-      <c r="N163" s="3"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O163" s="3"/>
+      <c r="P163" s="3"/>
+      <c r="Q163" s="3"/>
+      <c r="R163" s="3"/>
+      <c r="S163" s="3"/>
+      <c r="T163" s="3"/>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="7"/>
@@ -4571,10 +6416,14 @@
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
       <c r="L164" s="3"/>
-      <c r="M164" s="3"/>
-      <c r="N164" s="3"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O164" s="3"/>
+      <c r="P164" s="3"/>
+      <c r="Q164" s="3"/>
+      <c r="R164" s="3"/>
+      <c r="S164" s="3"/>
+      <c r="T164" s="3"/>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="7"/>
@@ -4587,10 +6436,14 @@
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
       <c r="L165" s="3"/>
-      <c r="M165" s="3"/>
-      <c r="N165" s="3"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O165" s="3"/>
+      <c r="P165" s="3"/>
+      <c r="Q165" s="3"/>
+      <c r="R165" s="3"/>
+      <c r="S165" s="3"/>
+      <c r="T165" s="3"/>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="7"/>
@@ -4603,10 +6456,14 @@
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
       <c r="L166" s="3"/>
-      <c r="M166" s="3"/>
-      <c r="N166" s="3"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O166" s="3"/>
+      <c r="P166" s="3"/>
+      <c r="Q166" s="3"/>
+      <c r="R166" s="3"/>
+      <c r="S166" s="3"/>
+      <c r="T166" s="3"/>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="7"/>
@@ -4619,10 +6476,14 @@
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
       <c r="L167" s="3"/>
-      <c r="M167" s="3"/>
-      <c r="N167" s="3"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O167" s="3"/>
+      <c r="P167" s="3"/>
+      <c r="Q167" s="3"/>
+      <c r="R167" s="3"/>
+      <c r="S167" s="3"/>
+      <c r="T167" s="3"/>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="7"/>
@@ -4635,10 +6496,14 @@
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
       <c r="L168" s="3"/>
-      <c r="M168" s="3"/>
-      <c r="N168" s="3"/>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O168" s="3"/>
+      <c r="P168" s="3"/>
+      <c r="Q168" s="3"/>
+      <c r="R168" s="3"/>
+      <c r="S168" s="3"/>
+      <c r="T168" s="3"/>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="7"/>
@@ -4651,10 +6516,14 @@
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
       <c r="L169" s="3"/>
-      <c r="M169" s="3"/>
-      <c r="N169" s="3"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O169" s="3"/>
+      <c r="P169" s="3"/>
+      <c r="Q169" s="3"/>
+      <c r="R169" s="3"/>
+      <c r="S169" s="3"/>
+      <c r="T169" s="3"/>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="7"/>
@@ -4667,10 +6536,14 @@
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
       <c r="L170" s="3"/>
-      <c r="M170" s="3"/>
-      <c r="N170" s="3"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O170" s="3"/>
+      <c r="P170" s="3"/>
+      <c r="Q170" s="3"/>
+      <c r="R170" s="3"/>
+      <c r="S170" s="3"/>
+      <c r="T170" s="3"/>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="7"/>
@@ -4683,10 +6556,14 @@
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
       <c r="L171" s="3"/>
-      <c r="M171" s="3"/>
-      <c r="N171" s="3"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O171" s="3"/>
+      <c r="P171" s="3"/>
+      <c r="Q171" s="3"/>
+      <c r="R171" s="3"/>
+      <c r="S171" s="3"/>
+      <c r="T171" s="3"/>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="7"/>
@@ -4699,10 +6576,14 @@
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
       <c r="L172" s="3"/>
-      <c r="M172" s="3"/>
-      <c r="N172" s="3"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O172" s="3"/>
+      <c r="P172" s="3"/>
+      <c r="Q172" s="3"/>
+      <c r="R172" s="3"/>
+      <c r="S172" s="3"/>
+      <c r="T172" s="3"/>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="7"/>
@@ -4715,10 +6596,14 @@
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
       <c r="L173" s="3"/>
-      <c r="M173" s="3"/>
-      <c r="N173" s="3"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O173" s="3"/>
+      <c r="P173" s="3"/>
+      <c r="Q173" s="3"/>
+      <c r="R173" s="3"/>
+      <c r="S173" s="3"/>
+      <c r="T173" s="3"/>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="7"/>
@@ -4731,10 +6616,14 @@
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
       <c r="L174" s="3"/>
-      <c r="M174" s="3"/>
-      <c r="N174" s="3"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O174" s="3"/>
+      <c r="P174" s="3"/>
+      <c r="Q174" s="3"/>
+      <c r="R174" s="3"/>
+      <c r="S174" s="3"/>
+      <c r="T174" s="3"/>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="7"/>
@@ -4747,10 +6636,14 @@
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
       <c r="L175" s="3"/>
-      <c r="M175" s="3"/>
-      <c r="N175" s="3"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O175" s="3"/>
+      <c r="P175" s="3"/>
+      <c r="Q175" s="3"/>
+      <c r="R175" s="3"/>
+      <c r="S175" s="3"/>
+      <c r="T175" s="3"/>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="7"/>
@@ -4763,10 +6656,14 @@
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
       <c r="L176" s="3"/>
-      <c r="M176" s="3"/>
-      <c r="N176" s="3"/>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O176" s="3"/>
+      <c r="P176" s="3"/>
+      <c r="Q176" s="3"/>
+      <c r="R176" s="3"/>
+      <c r="S176" s="3"/>
+      <c r="T176" s="3"/>
+    </row>
+    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="7"/>
@@ -4779,10 +6676,14 @@
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
       <c r="L177" s="3"/>
-      <c r="M177" s="3"/>
-      <c r="N177" s="3"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O177" s="3"/>
+      <c r="P177" s="3"/>
+      <c r="Q177" s="3"/>
+      <c r="R177" s="3"/>
+      <c r="S177" s="3"/>
+      <c r="T177" s="3"/>
+    </row>
+    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="7"/>
@@ -4795,10 +6696,14 @@
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
       <c r="L178" s="3"/>
-      <c r="M178" s="3"/>
-      <c r="N178" s="3"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O178" s="3"/>
+      <c r="P178" s="3"/>
+      <c r="Q178" s="3"/>
+      <c r="R178" s="3"/>
+      <c r="S178" s="3"/>
+      <c r="T178" s="3"/>
+    </row>
+    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="7"/>
@@ -4811,10 +6716,14 @@
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
       <c r="L179" s="3"/>
-      <c r="M179" s="3"/>
-      <c r="N179" s="3"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O179" s="3"/>
+      <c r="P179" s="3"/>
+      <c r="Q179" s="3"/>
+      <c r="R179" s="3"/>
+      <c r="S179" s="3"/>
+      <c r="T179" s="3"/>
+    </row>
+    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="7"/>
@@ -4827,10 +6736,14 @@
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
       <c r="L180" s="3"/>
-      <c r="M180" s="3"/>
-      <c r="N180" s="3"/>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O180" s="3"/>
+      <c r="P180" s="3"/>
+      <c r="Q180" s="3"/>
+      <c r="R180" s="3"/>
+      <c r="S180" s="3"/>
+      <c r="T180" s="3"/>
+    </row>
+    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="7"/>
@@ -4843,10 +6756,14 @@
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
       <c r="L181" s="3"/>
-      <c r="M181" s="3"/>
-      <c r="N181" s="3"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O181" s="3"/>
+      <c r="P181" s="3"/>
+      <c r="Q181" s="3"/>
+      <c r="R181" s="3"/>
+      <c r="S181" s="3"/>
+      <c r="T181" s="3"/>
+    </row>
+    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="7"/>
@@ -4859,10 +6776,14 @@
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
       <c r="L182" s="3"/>
-      <c r="M182" s="3"/>
-      <c r="N182" s="3"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O182" s="3"/>
+      <c r="P182" s="3"/>
+      <c r="Q182" s="3"/>
+      <c r="R182" s="3"/>
+      <c r="S182" s="3"/>
+      <c r="T182" s="3"/>
+    </row>
+    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="7"/>
@@ -4875,10 +6796,14 @@
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
       <c r="L183" s="3"/>
-      <c r="M183" s="3"/>
-      <c r="N183" s="3"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O183" s="3"/>
+      <c r="P183" s="3"/>
+      <c r="Q183" s="3"/>
+      <c r="R183" s="3"/>
+      <c r="S183" s="3"/>
+      <c r="T183" s="3"/>
+    </row>
+    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="7"/>
@@ -4891,10 +6816,14 @@
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
       <c r="L184" s="3"/>
-      <c r="M184" s="3"/>
-      <c r="N184" s="3"/>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O184" s="3"/>
+      <c r="P184" s="3"/>
+      <c r="Q184" s="3"/>
+      <c r="R184" s="3"/>
+      <c r="S184" s="3"/>
+      <c r="T184" s="3"/>
+    </row>
+    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="7"/>
@@ -4907,10 +6836,14 @@
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
       <c r="L185" s="3"/>
-      <c r="M185" s="3"/>
-      <c r="N185" s="3"/>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O185" s="3"/>
+      <c r="P185" s="3"/>
+      <c r="Q185" s="3"/>
+      <c r="R185" s="3"/>
+      <c r="S185" s="3"/>
+      <c r="T185" s="3"/>
+    </row>
+    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="7"/>
@@ -4923,10 +6856,14 @@
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
       <c r="L186" s="3"/>
-      <c r="M186" s="3"/>
-      <c r="N186" s="3"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O186" s="3"/>
+      <c r="P186" s="3"/>
+      <c r="Q186" s="3"/>
+      <c r="R186" s="3"/>
+      <c r="S186" s="3"/>
+      <c r="T186" s="3"/>
+    </row>
+    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="7"/>
@@ -4939,10 +6876,14 @@
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
       <c r="L187" s="3"/>
-      <c r="M187" s="3"/>
-      <c r="N187" s="3"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O187" s="3"/>
+      <c r="P187" s="3"/>
+      <c r="Q187" s="3"/>
+      <c r="R187" s="3"/>
+      <c r="S187" s="3"/>
+      <c r="T187" s="3"/>
+    </row>
+    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="7"/>
@@ -4955,10 +6896,14 @@
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
       <c r="L188" s="3"/>
-      <c r="M188" s="3"/>
-      <c r="N188" s="3"/>
-    </row>
-    <row r="189" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O188" s="3"/>
+      <c r="P188" s="3"/>
+      <c r="Q188" s="3"/>
+      <c r="R188" s="3"/>
+      <c r="S188" s="3"/>
+      <c r="T188" s="3"/>
+    </row>
+    <row r="189" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="7"/>
@@ -4971,10 +6916,14 @@
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
       <c r="L189" s="3"/>
-      <c r="M189" s="3"/>
-      <c r="N189" s="3"/>
-    </row>
-    <row r="190" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O189" s="3"/>
+      <c r="P189" s="3"/>
+      <c r="Q189" s="3"/>
+      <c r="R189" s="3"/>
+      <c r="S189" s="3"/>
+      <c r="T189" s="3"/>
+    </row>
+    <row r="190" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
@@ -4984,10 +6933,14 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
       <c r="I190" s="8"/>
-      <c r="J190" s="8"/>
-      <c r="K190" s="8"/>
-    </row>
-    <row r="191" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J190" s="14"/>
+      <c r="K190" s="14"/>
+      <c r="O190" s="8"/>
+      <c r="P190" s="8"/>
+      <c r="Q190" s="8"/>
+      <c r="R190" s="8"/>
+    </row>
+    <row r="191" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
@@ -4997,10 +6950,14 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
       <c r="I191" s="8"/>
-      <c r="J191" s="8"/>
-      <c r="K191" s="8"/>
-    </row>
-    <row r="192" spans="1:14" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J191" s="14"/>
+      <c r="K191" s="14"/>
+      <c r="O191" s="8"/>
+      <c r="P191" s="8"/>
+      <c r="Q191" s="8"/>
+      <c r="R191" s="8"/>
+    </row>
+    <row r="192" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
@@ -5010,8 +6967,12 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
       <c r="I192" s="8"/>
-      <c r="J192" s="8"/>
-      <c r="K192" s="8"/>
+      <c r="J192" s="14"/>
+      <c r="K192" s="14"/>
+      <c r="O192" s="8"/>
+      <c r="P192" s="8"/>
+      <c r="Q192" s="8"/>
+      <c r="R192" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7B1798-8D4A-4C3D-AD68-1ABBF158C13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAD9A5B-7F49-4884-A445-D8AE447D2FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$Y$106</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="283">
   <si>
     <t>##var</t>
   </si>
@@ -96,10 +100,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>填工程内文件名称</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>土豆</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -497,10 +497,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>道具类型 1种子袋 2作物 3巨大作物 4迷你作物 5特殊</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>是否看染色</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -541,10 +537,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>花椰菜汤</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>itemType</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -671,6 +663,381 @@
   </si>
   <si>
     <t>buffid#buffid</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆-房子</t>
+  </si>
+  <si>
+    <t>蘑菇-房子</t>
+  </si>
+  <si>
+    <t>南瓜-房子</t>
+  </si>
+  <si>
+    <t>胡萝卜-房子</t>
+  </si>
+  <si>
+    <t>水甜菜-房子</t>
+  </si>
+  <si>
+    <t>番茄-红-房子</t>
+  </si>
+  <si>
+    <t>番茄-橙-房子</t>
+  </si>
+  <si>
+    <t>番茄-黄-房子</t>
+  </si>
+  <si>
+    <t>番茄-绿-房子</t>
+  </si>
+  <si>
+    <t>番茄-青-房子</t>
+  </si>
+  <si>
+    <t>番茄-蓝-房子</t>
+  </si>
+  <si>
+    <t>番茄-紫-房子</t>
+  </si>
+  <si>
+    <t>花椰菜-房子</t>
+  </si>
+  <si>
+    <t>猕猴桃-房子</t>
+  </si>
+  <si>
+    <t>野草-房子</t>
+  </si>
+  <si>
+    <t>猕猴桃树</t>
+  </si>
+  <si>
+    <t>灌木丛根</t>
+  </si>
+  <si>
+    <t>传送门</t>
+  </si>
+  <si>
+    <t>隐藏门</t>
+  </si>
+  <si>
+    <t>钥匙</t>
+  </si>
+  <si>
+    <t>爆米花机</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜汤味</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>甜菜女士</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜羊-白</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜羊-绿</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>猴子先生</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>土豆-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘑菇-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>南瓜-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>胡萝卜-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>水甜菜-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-红-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-橙-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-黄-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-绿-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-青-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-蓝-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>番茄-紫-幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜-幼苗(一次性)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>花椰菜-幼苗(永久)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>填工程内文件名称（需要改成预制体路径）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>中文名称</t>
+  </si>
+  <si>
+    <t>分类标识</t>
+  </si>
+  <si>
+    <t>英文名称</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>洒水壶</t>
+  </si>
+  <si>
+    <t>莲叶</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜汤味</t>
+  </si>
+  <si>
+    <t>甜菜女士</t>
+  </si>
+  <si>
+    <t>花椰菜羊-白</t>
+  </si>
+  <si>
+    <t>花椰菜羊-绿</t>
+  </si>
+  <si>
+    <t>猴子先生</t>
+  </si>
+  <si>
+    <t>土豆-幼苗</t>
+  </si>
+  <si>
+    <t>蘑菇-幼苗</t>
+  </si>
+  <si>
+    <t>南瓜-幼苗</t>
+  </si>
+  <si>
+    <t>胡萝卜-幼苗</t>
+  </si>
+  <si>
+    <t>水甜菜-幼苗</t>
+  </si>
+  <si>
+    <t>番茄-红-幼苗</t>
+  </si>
+  <si>
+    <t>番茄-橙-幼苗</t>
+  </si>
+  <si>
+    <t>番茄-黄-幼苗</t>
+  </si>
+  <si>
+    <t>番茄-绿-幼苗</t>
+  </si>
+  <si>
+    <t>番茄-青-幼苗</t>
+  </si>
+  <si>
+    <t>番茄-蓝-幼苗</t>
+  </si>
+  <si>
+    <t>番茄-紫-幼苗</t>
+  </si>
+  <si>
+    <t>花椰菜-幼苗(一次性)</t>
+  </si>
+  <si>
+    <t>花椰菜-幼苗(永久)</t>
+  </si>
+  <si>
+    <t>Watering_Can</t>
+  </si>
+  <si>
+    <t>Item/Watering_Can</t>
+  </si>
+  <si>
+    <t>Lotus_Leaf</t>
+  </si>
+  <si>
+    <t>Kiwi_Tree</t>
+  </si>
+  <si>
+    <t>Bush_Root</t>
+  </si>
+  <si>
+    <t>Hidden_Door</t>
+  </si>
+  <si>
+    <t>Popcorn_Machine</t>
+  </si>
+  <si>
+    <t>Ms._Beet</t>
+  </si>
+  <si>
+    <t>Mr._Monkey</t>
+  </si>
+  <si>
+    <t>Item/</t>
+  </si>
+  <si>
+    <t>Popcorn_Cauliflower_Soup_Flavor</t>
+  </si>
+  <si>
+    <t>Cauliflower_Sheep_White</t>
+  </si>
+  <si>
+    <t>Cauliflower_Sheep_Green</t>
+  </si>
+  <si>
+    <t>Carrot</t>
+  </si>
+  <si>
+    <t>Beet</t>
+  </si>
+  <si>
+    <t>Seedling/</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npc/</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>seedling</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bulit/</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item/Lotus_Leaf</t>
+  </si>
+  <si>
+    <t>Item/Kiwi_Tree</t>
+  </si>
+  <si>
+    <t>Item/Bush_Root</t>
+  </si>
+  <si>
+    <t>Item/Portal</t>
+  </si>
+  <si>
+    <t>Item/Hidden_Door</t>
+  </si>
+  <si>
+    <t>Item/Key</t>
+  </si>
+  <si>
+    <t>Item/Popcorn_Machine</t>
+  </si>
+  <si>
+    <t>Item/Popcorn_Cauliflower_Soup_Flavor</t>
+  </si>
+  <si>
+    <t>Npc/Cauliflower_Sheep_White</t>
+  </si>
+  <si>
+    <t>Npc/Cauliflower_Sheep_Green</t>
+  </si>
+  <si>
+    <t>Seedling/seedling</t>
+  </si>
+  <si>
+    <t>Npc/Mr_Monkey</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npc/Ms_Beet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bulit/mushroom_002</t>
+  </si>
+  <si>
+    <t>mushroom_002</t>
+  </si>
+  <si>
+    <t>Pumpkin</t>
+  </si>
+  <si>
+    <t>Tomato_red</t>
+  </si>
+  <si>
+    <t>Tomato_yellow</t>
+  </si>
+  <si>
+    <t>Tomato_green</t>
+  </si>
+  <si>
+    <t>Kiwi</t>
+  </si>
+  <si>
+    <t>Bulit/Pumpkin</t>
+  </si>
+  <si>
+    <t>Bulit/Carrot</t>
+  </si>
+  <si>
+    <t>Bulit/Beet</t>
+  </si>
+  <si>
+    <t>Bulit/Tomato_red</t>
+  </si>
+  <si>
+    <t>Bulit/Tomato_yellow</t>
+  </si>
+  <si>
+    <t>Bulit/Tomato_green</t>
+  </si>
+  <si>
+    <t>Bulit/Kiwi</t>
+  </si>
+  <si>
+    <t>道具类型 1种子袋 2作物 3巨大作物 4迷你作物 5特殊 6房子 7npc  8幼苗</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -678,7 +1045,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -733,6 +1100,12 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -865,7 +1238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -909,6 +1282,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1184,20 +1562,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y192"/>
+  <dimension ref="A1:Y188"/>
   <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.1640625" style="1"/>
     <col min="3" max="3" width="22.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="16.08203125" style="1" customWidth="1"/>
     <col min="9" max="11" width="16.75" style="1" customWidth="1"/>
     <col min="12" max="16" width="12.1640625" style="1"/>
     <col min="17" max="18" width="17.9140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.9140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="26.33203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="12.1640625" style="1"/>
     <col min="26" max="16384" width="12.1640625" style="1"/>
   </cols>
@@ -1216,7 +1594,7 @@
         <v>7</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>9</v>
@@ -1225,43 +1603,43 @@
         <v>8</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="S1" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="T1" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -1287,25 +1665,25 @@
         <v>14</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>3</v>
@@ -1346,46 +1724,46 @@
         <v>13</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="P3" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="R3" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>157</v>
-      </c>
       <c r="S3" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
@@ -1402,52 +1780,52 @@
         <v>17</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>125</v>
+        <v>282</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
@@ -1456,14 +1834,14 @@
         <v>1001</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9">
         <v>1</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G5" s="9">
         <v>1</v>
@@ -1499,14 +1877,14 @@
         <v>1002</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9">
         <v>1</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G6" s="9">
         <v>1</v>
@@ -1542,14 +1920,14 @@
         <v>1003</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9">
         <v>1</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G7" s="9">
         <v>1</v>
@@ -1585,14 +1963,14 @@
         <v>1004</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9">
         <v>1</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G8" s="9">
         <v>1</v>
@@ -1629,14 +2007,14 @@
         <v>1005</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9">
         <v>1</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G9" s="9">
         <v>1</v>
@@ -1673,14 +2051,14 @@
         <v>1006</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9">
         <v>1</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G10" s="9">
         <v>1</v>
@@ -1717,14 +2095,14 @@
         <v>1007</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9">
         <v>1</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G11" s="9">
         <v>1</v>
@@ -1761,14 +2139,14 @@
         <v>1008</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9">
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G12" s="9">
         <v>1</v>
@@ -1805,14 +2183,14 @@
         <v>1009</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9">
         <v>1</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G13" s="9">
         <v>1</v>
@@ -1849,14 +2227,14 @@
         <v>1010</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9">
         <v>1</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G14" s="9">
         <v>1</v>
@@ -1893,14 +2271,14 @@
         <v>1011</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9">
         <v>1</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G15" s="9">
         <v>1</v>
@@ -1924,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
@@ -1937,14 +2315,14 @@
         <v>1012</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
         <v>1</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G16" s="9">
         <v>1</v>
@@ -1981,14 +2359,14 @@
         <v>1013</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
         <v>1</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G17" s="9">
         <v>1</v>
@@ -2025,14 +2403,14 @@
         <v>1014</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9">
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
@@ -2071,14 +2449,14 @@
         <v>2001</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11">
         <v>2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G19" s="9">
         <v>1</v>
@@ -2105,17 +2483,17 @@
         <v>1</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R19" s="11"/>
       <c r="S19" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T19" s="11"/>
     </row>
@@ -2125,14 +2503,14 @@
         <v>2002</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9">
         <v>2</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G20" s="9">
         <v>1</v>
@@ -2161,14 +2539,14 @@
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R20" s="9"/>
       <c r="S20" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
@@ -2177,14 +2555,14 @@
         <v>2003</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9">
         <v>2</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G21" s="9">
         <v>1</v>
@@ -2213,14 +2591,14 @@
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R21" s="9"/>
       <c r="S21" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
@@ -2229,14 +2607,14 @@
         <v>2004</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9">
         <v>2</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G22" s="9">
         <v>1</v>
@@ -2263,20 +2641,20 @@
         <v>1</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R22" s="9"/>
       <c r="S22" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
@@ -2285,14 +2663,14 @@
         <v>2005</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9">
         <v>2</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G23" s="9">
         <v>1</v>
@@ -2321,14 +2699,14 @@
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R23" s="9"/>
       <c r="S23" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
@@ -2337,14 +2715,14 @@
         <v>2006</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9">
         <v>2</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G24" s="9">
         <v>1</v>
@@ -2373,14 +2751,14 @@
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R24" s="9"/>
       <c r="S24" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
@@ -2389,14 +2767,14 @@
         <v>2007</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9">
         <v>2</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G25" s="9">
         <v>1</v>
@@ -2425,14 +2803,14 @@
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R25" s="9"/>
       <c r="S25" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
@@ -2441,14 +2819,14 @@
         <v>2008</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9">
         <v>2</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G26" s="9">
         <v>1</v>
@@ -2477,14 +2855,14 @@
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R26" s="9"/>
       <c r="S26" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
@@ -2493,14 +2871,14 @@
         <v>2009</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9">
         <v>2</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G27" s="9">
         <v>1</v>
@@ -2529,14 +2907,14 @@
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R27" s="9"/>
       <c r="S27" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
@@ -2545,14 +2923,14 @@
         <v>2010</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9">
         <v>2</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G28" s="9">
         <v>1</v>
@@ -2581,14 +2959,14 @@
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R28" s="9"/>
       <c r="S28" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
@@ -2597,14 +2975,14 @@
         <v>2011</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9">
         <v>2</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G29" s="9">
         <v>1</v>
@@ -2633,14 +3011,14 @@
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R29" s="9"/>
       <c r="S29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
@@ -2649,14 +3027,14 @@
         <v>2012</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9">
         <v>2</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G30" s="9">
         <v>1</v>
@@ -2685,14 +3063,14 @@
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R30" s="9"/>
       <c r="S30" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
@@ -2701,14 +3079,14 @@
         <v>2013</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9">
         <v>2</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G31" s="9">
         <v>1</v>
@@ -2737,14 +3115,14 @@
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
@@ -2753,14 +3131,14 @@
         <v>2014</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9">
         <v>2</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G32" s="9">
         <v>1</v>
@@ -2789,14 +3167,14 @@
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R32" s="9"/>
       <c r="S32" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
@@ -2805,14 +3183,14 @@
         <v>2015</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9">
         <v>2</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G33" s="9">
         <v>1</v>
@@ -2839,20 +3217,20 @@
         <v>1</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R33" s="9"/>
       <c r="S33" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
@@ -2861,14 +3239,14 @@
         <v>2016</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9">
         <v>2</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G34" s="9">
         <v>1</v>
@@ -2897,14 +3275,14 @@
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R34" s="9"/>
       <c r="S34" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
@@ -2913,14 +3291,14 @@
         <v>3001</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11">
         <v>3</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G35" s="11">
         <v>4</v>
@@ -2949,7 +3327,7 @@
       <c r="O35" s="11"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R35" s="11"/>
       <c r="S35" s="11"/>
@@ -2961,14 +3339,14 @@
         <v>3002</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9">
         <v>3</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G36" s="9">
         <v>4</v>
@@ -2997,7 +3375,7 @@
       <c r="O36" s="9"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
@@ -3009,14 +3387,14 @@
         <v>3003</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9">
         <v>3</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G37" s="9">
         <v>4</v>
@@ -3045,7 +3423,7 @@
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
@@ -3057,14 +3435,14 @@
         <v>3004</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9">
         <v>3</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G38" s="9">
         <v>4</v>
@@ -3093,7 +3471,7 @@
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
@@ -3105,14 +3483,14 @@
         <v>3005</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9">
         <v>3</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G39" s="9">
         <v>4</v>
@@ -3141,7 +3519,7 @@
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
@@ -3153,14 +3531,14 @@
         <v>3006</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9">
         <v>3</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G40" s="9">
         <v>4</v>
@@ -3189,7 +3567,7 @@
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
@@ -3201,14 +3579,14 @@
         <v>3007</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9">
         <v>3</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G41" s="9">
         <v>4</v>
@@ -3237,7 +3615,7 @@
       <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
@@ -3249,14 +3627,14 @@
         <v>3008</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9">
         <v>3</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G42" s="9">
         <v>4</v>
@@ -3285,7 +3663,7 @@
       <c r="O42" s="9"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
@@ -3297,14 +3675,14 @@
         <v>3009</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9">
         <v>3</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G43" s="9">
         <v>4</v>
@@ -3333,7 +3711,7 @@
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
@@ -3345,14 +3723,14 @@
         <v>3010</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9">
         <v>3</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G44" s="9">
         <v>4</v>
@@ -3381,7 +3759,7 @@
       <c r="O44" s="9"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
@@ -3393,14 +3771,14 @@
         <v>3011</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9">
         <v>3</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G45" s="9">
         <v>4</v>
@@ -3429,7 +3807,7 @@
       <c r="O45" s="9"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
@@ -3441,14 +3819,14 @@
         <v>3012</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="9">
         <v>3</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G46" s="9">
         <v>4</v>
@@ -3477,7 +3855,7 @@
       <c r="O46" s="9"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
@@ -3489,14 +3867,14 @@
         <v>3013</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9">
         <v>3</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G47" s="9">
         <v>4</v>
@@ -3525,7 +3903,7 @@
       <c r="O47" s="9"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
@@ -3537,14 +3915,14 @@
         <v>3014</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9">
         <v>3</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G48" s="9">
         <v>4</v>
@@ -3573,7 +3951,7 @@
       <c r="O48" s="9"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
@@ -3585,14 +3963,14 @@
         <v>3015</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="9">
         <v>3</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G49" s="9">
         <v>4</v>
@@ -3621,7 +3999,7 @@
       <c r="O49" s="9"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
@@ -3633,14 +4011,14 @@
         <v>4001</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11">
         <v>4</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G50" s="11">
         <v>0.5</v>
@@ -3669,7 +4047,7 @@
       <c r="O50" s="11"/>
       <c r="P50" s="11"/>
       <c r="Q50" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R50" s="11"/>
       <c r="S50" s="11"/>
@@ -3681,14 +4059,14 @@
         <v>4002</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9">
         <v>4</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G51" s="9">
         <v>0.5</v>
@@ -3717,7 +4095,7 @@
       <c r="O51" s="9"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
@@ -3729,14 +4107,14 @@
         <v>4003</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="9">
         <v>4</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G52" s="9">
         <v>0.5</v>
@@ -3765,7 +4143,7 @@
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
@@ -3777,14 +4155,14 @@
         <v>4004</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="9">
         <v>4</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G53" s="9">
         <v>0.5</v>
@@ -3813,7 +4191,7 @@
       <c r="O53" s="9"/>
       <c r="P53" s="9"/>
       <c r="Q53" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
@@ -3825,14 +4203,14 @@
         <v>4005</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9">
         <v>4</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="G54" s="9">
         <v>0.5</v>
@@ -3861,7 +4239,7 @@
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
@@ -3873,14 +4251,14 @@
         <v>4006</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9">
         <v>4</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G55" s="9">
         <v>0.5</v>
@@ -3909,7 +4287,7 @@
       <c r="O55" s="9"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
@@ -3921,14 +4299,14 @@
         <v>4007</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="9">
         <v>4</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G56" s="9">
         <v>0.5</v>
@@ -3957,7 +4335,7 @@
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
@@ -3969,14 +4347,14 @@
         <v>4008</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D57" s="9"/>
       <c r="E57" s="9">
         <v>4</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G57" s="9">
         <v>0.5</v>
@@ -4005,7 +4383,7 @@
       <c r="O57" s="9"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
@@ -4017,14 +4395,14 @@
         <v>4009</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="9">
         <v>4</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G58" s="9">
         <v>0.5</v>
@@ -4053,7 +4431,7 @@
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R58" s="9"/>
       <c r="S58" s="9"/>
@@ -4065,14 +4443,14 @@
         <v>4010</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="9">
         <v>4</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G59" s="9">
         <v>0.5</v>
@@ -4101,7 +4479,7 @@
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
@@ -4113,14 +4491,14 @@
         <v>4011</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="9">
         <v>4</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G60" s="9">
         <v>0.5</v>
@@ -4149,7 +4527,7 @@
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
       <c r="Q60" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R60" s="9"/>
       <c r="S60" s="9"/>
@@ -4161,14 +4539,14 @@
         <v>4012</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="9">
         <v>4</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G61" s="9">
         <v>0.5</v>
@@ -4197,7 +4575,7 @@
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
       <c r="Q61" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R61" s="9"/>
       <c r="S61" s="9"/>
@@ -4209,14 +4587,14 @@
         <v>4013</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="9">
         <v>4</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G62" s="9">
         <v>0.5</v>
@@ -4245,7 +4623,7 @@
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R62" s="9"/>
       <c r="S62" s="9"/>
@@ -4257,14 +4635,14 @@
         <v>4014</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="9">
         <v>4</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G63" s="9">
         <v>0.5</v>
@@ -4293,7 +4671,7 @@
       <c r="O63" s="9"/>
       <c r="P63" s="9"/>
       <c r="Q63" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
@@ -4305,14 +4683,14 @@
         <v>4015</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="9">
         <v>4</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G64" s="9">
         <v>0.5</v>
@@ -4341,7 +4719,7 @@
       <c r="O64" s="9"/>
       <c r="P64" s="9"/>
       <c r="Q64" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
@@ -4353,14 +4731,18 @@
         <v>5001</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="11">
         <v>5</v>
       </c>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
+      <c r="F65" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="G65" s="11">
+        <v>1</v>
+      </c>
       <c r="H65" s="9">
         <v>0</v>
       </c>
@@ -4377,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="M65" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" s="1">
         <v>1</v>
@@ -4385,14 +4767,14 @@
       <c r="O65" s="11"/>
       <c r="P65" s="11"/>
       <c r="Q65" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R65" s="11"/>
       <c r="S65" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T65" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.3">
@@ -4401,14 +4783,18 @@
         <v>5002</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="12">
         <v>5</v>
       </c>
-      <c r="F66" s="12"/>
-      <c r="G66" s="12"/>
+      <c r="F66" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G66" s="12">
+        <v>1</v>
+      </c>
       <c r="H66" s="9">
         <v>0</v>
       </c>
@@ -4428,74 +4814,102 @@
         <v>1</v>
       </c>
       <c r="N66" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" s="12"/>
       <c r="P66" s="12"/>
       <c r="Q66" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R66" s="12"/>
       <c r="S66" s="12"/>
       <c r="T66" s="12"/>
     </row>
-    <row r="67" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A67" s="3"/>
       <c r="B67" s="12">
         <v>5003</v>
       </c>
-      <c r="C67" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="D67" s="12"/>
+      <c r="C67" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D67" s="3"/>
       <c r="E67" s="12">
         <v>5</v>
       </c>
-      <c r="F67" s="12"/>
-      <c r="G67" s="12"/>
+      <c r="F67" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1</v>
+      </c>
       <c r="H67" s="9">
         <v>0</v>
       </c>
       <c r="I67" s="12">
         <v>0</v>
       </c>
-      <c r="J67" s="12">
+      <c r="J67" s="3">
         <v>0</v>
       </c>
       <c r="K67" s="9">
         <v>100</v>
       </c>
       <c r="L67" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" s="1">
         <v>1</v>
       </c>
-      <c r="O67" s="12"/>
-      <c r="P67" s="12"/>
-      <c r="Q67" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="R67" s="12"/>
-      <c r="S67" s="12"/>
-      <c r="T67" s="12"/>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="7"/>
+      <c r="B68" s="12">
+        <v>5004</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>183</v>
+      </c>
       <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
+      <c r="E68" s="12">
+        <v>5</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G68" s="3">
+        <v>1</v>
+      </c>
+      <c r="H68" s="9">
+        <v>0</v>
+      </c>
+      <c r="I68" s="9">
+        <v>1</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+      <c r="K68" s="9">
+        <v>100</v>
+      </c>
+      <c r="L68" s="11">
+        <v>1</v>
+      </c>
+      <c r="M68" s="11">
+        <v>1</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
       <c r="O68" s="3"/>
       <c r="P68" s="3"/>
       <c r="Q68" s="3"/>
@@ -4505,17 +4919,43 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="7"/>
+      <c r="B69" s="12">
+        <v>5005</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>184</v>
+      </c>
       <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
+      <c r="E69" s="12">
+        <v>5</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G69" s="3">
+        <v>1</v>
+      </c>
+      <c r="H69" s="9">
+        <v>0</v>
+      </c>
+      <c r="I69" s="12">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>1</v>
+      </c>
+      <c r="K69" s="9">
+        <v>100</v>
+      </c>
+      <c r="L69" s="11">
+        <v>1</v>
+      </c>
+      <c r="M69" s="11">
+        <v>1</v>
+      </c>
+      <c r="N69" s="1">
+        <v>1</v>
+      </c>
       <c r="O69" s="3"/>
       <c r="P69" s="3"/>
       <c r="Q69" s="3"/>
@@ -4525,17 +4965,43 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="7"/>
+      <c r="B70" s="12">
+        <v>5006</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>185</v>
+      </c>
       <c r="D70" s="3"/>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
+      <c r="E70" s="12">
+        <v>5</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G70" s="3">
+        <v>1</v>
+      </c>
+      <c r="H70" s="9">
+        <v>0</v>
+      </c>
+      <c r="I70" s="12">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1</v>
+      </c>
+      <c r="K70" s="9">
+        <v>100</v>
+      </c>
+      <c r="L70" s="11">
+        <v>1</v>
+      </c>
+      <c r="M70" s="11">
+        <v>1</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
       <c r="O70" s="3"/>
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
@@ -4545,17 +5011,43 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="7"/>
+      <c r="B71" s="12">
+        <v>5007</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>186</v>
+      </c>
       <c r="D71" s="3"/>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
+      <c r="E71" s="12">
+        <v>5</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="G71" s="3">
+        <v>1</v>
+      </c>
+      <c r="H71" s="9">
+        <v>0</v>
+      </c>
+      <c r="I71" s="12">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3">
+        <v>0</v>
+      </c>
+      <c r="K71" s="9">
+        <v>100</v>
+      </c>
+      <c r="L71" s="11">
+        <v>1</v>
+      </c>
+      <c r="M71" s="11">
+        <v>1</v>
+      </c>
+      <c r="N71" s="1">
+        <v>1</v>
+      </c>
       <c r="O71" s="3"/>
       <c r="P71" s="3"/>
       <c r="Q71" s="3"/>
@@ -4565,17 +5057,43 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="7"/>
+      <c r="B72" s="12">
+        <v>5008</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>187</v>
+      </c>
       <c r="D72" s="3"/>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
+      <c r="E72" s="12">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G72" s="3">
+        <v>1</v>
+      </c>
+      <c r="H72" s="9">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="9">
+        <v>100</v>
+      </c>
+      <c r="L72" s="11">
+        <v>1</v>
+      </c>
+      <c r="M72" s="11">
+        <v>0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>1</v>
+      </c>
       <c r="O72" s="3"/>
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
@@ -4583,359 +5101,864 @@
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="7"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="3"/>
-      <c r="S74" s="3"/>
-      <c r="T74" s="3"/>
+    <row r="73" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="12"/>
+      <c r="B73" s="12">
+        <v>5009</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12">
+        <v>5</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="G73" s="3">
+        <v>1</v>
+      </c>
+      <c r="H73" s="9">
+        <v>0</v>
+      </c>
+      <c r="I73" s="12">
+        <v>0</v>
+      </c>
+      <c r="J73" s="12">
+        <v>0</v>
+      </c>
+      <c r="K73" s="9">
+        <v>100</v>
+      </c>
+      <c r="L73" s="11">
+        <v>0</v>
+      </c>
+      <c r="M73" s="11">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>1</v>
+      </c>
+      <c r="O73" s="12"/>
+      <c r="P73" s="12"/>
+      <c r="Q73" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="R73" s="12"/>
+      <c r="S73" s="12"/>
+      <c r="T73" s="12"/>
+    </row>
+    <row r="74" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11">
+        <v>6001</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11">
+        <v>6</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="G74" s="16">
+        <v>1</v>
+      </c>
+      <c r="H74" s="11">
+        <v>0</v>
+      </c>
+      <c r="I74" s="11">
+        <v>0</v>
+      </c>
+      <c r="J74" s="11">
+        <v>0</v>
+      </c>
+      <c r="K74" s="9">
+        <v>100</v>
+      </c>
+      <c r="L74" s="11">
+        <v>0</v>
+      </c>
+      <c r="M74" s="11">
+        <v>0</v>
+      </c>
+      <c r="N74" s="10">
+        <v>1</v>
+      </c>
+      <c r="O74" s="11"/>
+      <c r="P74" s="11"/>
+      <c r="Q74" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="R74" s="11"/>
+      <c r="S74" s="11"/>
+      <c r="T74" s="11"/>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="3"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
+      <c r="A75" s="9"/>
+      <c r="B75" s="9">
+        <v>6002</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9">
+        <v>6</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="G75" s="3">
+        <v>1</v>
+      </c>
+      <c r="H75" s="9">
+        <v>0</v>
+      </c>
+      <c r="I75" s="9">
+        <v>0</v>
+      </c>
+      <c r="J75" s="9">
+        <v>0</v>
+      </c>
+      <c r="K75" s="9">
+        <v>100</v>
+      </c>
+      <c r="L75" s="11">
+        <v>0</v>
+      </c>
+      <c r="M75" s="11">
+        <v>0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>1</v>
+      </c>
+      <c r="O75" s="9"/>
+      <c r="P75" s="9"/>
+      <c r="Q75" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="R75" s="9"/>
+      <c r="S75" s="9"/>
+      <c r="T75" s="9"/>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="7"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
-      <c r="R76" s="3"/>
-      <c r="S76" s="3"/>
-      <c r="T76" s="3"/>
+      <c r="A76" s="9"/>
+      <c r="B76" s="9">
+        <v>6003</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9">
+        <v>6</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="G76" s="3">
+        <v>1</v>
+      </c>
+      <c r="H76" s="9">
+        <v>0</v>
+      </c>
+      <c r="I76" s="9">
+        <v>0</v>
+      </c>
+      <c r="J76" s="9">
+        <v>0</v>
+      </c>
+      <c r="K76" s="9">
+        <v>100</v>
+      </c>
+      <c r="L76" s="11">
+        <v>0</v>
+      </c>
+      <c r="M76" s="11">
+        <v>0</v>
+      </c>
+      <c r="N76" s="1">
+        <v>1</v>
+      </c>
+      <c r="O76" s="9"/>
+      <c r="P76" s="9"/>
+      <c r="Q76" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="R76" s="9"/>
+      <c r="S76" s="9"/>
+      <c r="T76" s="9"/>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="7"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="3"/>
-      <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
+      <c r="A77" s="9"/>
+      <c r="B77" s="9">
+        <v>6004</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9">
+        <v>6</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G77" s="3">
+        <v>1</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0</v>
+      </c>
+      <c r="I77" s="9">
+        <v>0</v>
+      </c>
+      <c r="J77" s="9">
+        <v>0</v>
+      </c>
+      <c r="K77" s="9">
+        <v>100</v>
+      </c>
+      <c r="L77" s="11">
+        <v>0</v>
+      </c>
+      <c r="M77" s="11">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1">
+        <v>1</v>
+      </c>
+      <c r="O77" s="9"/>
+      <c r="P77" s="9"/>
+      <c r="Q77" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="R77" s="9"/>
+      <c r="S77" s="9"/>
+      <c r="T77" s="9"/>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="7"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3"/>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
-      <c r="Q78" s="3"/>
-      <c r="R78" s="3"/>
-      <c r="S78" s="3"/>
-      <c r="T78" s="3"/>
+      <c r="A78" s="9"/>
+      <c r="B78" s="9">
+        <v>6005</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9">
+        <v>6</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="G78" s="3">
+        <v>1</v>
+      </c>
+      <c r="H78" s="9">
+        <v>0</v>
+      </c>
+      <c r="I78" s="9">
+        <v>0</v>
+      </c>
+      <c r="J78" s="9">
+        <v>0</v>
+      </c>
+      <c r="K78" s="9">
+        <v>100</v>
+      </c>
+      <c r="L78" s="11">
+        <v>0</v>
+      </c>
+      <c r="M78" s="11">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>1</v>
+      </c>
+      <c r="O78" s="9"/>
+      <c r="P78" s="9"/>
+      <c r="Q78" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R78" s="9"/>
+      <c r="S78" s="9"/>
+      <c r="T78" s="9"/>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3"/>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-      <c r="Q79" s="3"/>
-      <c r="R79" s="3"/>
-      <c r="S79" s="3"/>
-      <c r="T79" s="3"/>
+      <c r="A79" s="9"/>
+      <c r="B79" s="9">
+        <v>6006</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9">
+        <v>6</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G79" s="3">
+        <v>1</v>
+      </c>
+      <c r="H79" s="9">
+        <v>0</v>
+      </c>
+      <c r="I79" s="9">
+        <v>0</v>
+      </c>
+      <c r="J79" s="9">
+        <v>0</v>
+      </c>
+      <c r="K79" s="9">
+        <v>100</v>
+      </c>
+      <c r="L79" s="11">
+        <v>0</v>
+      </c>
+      <c r="M79" s="11">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>1</v>
+      </c>
+      <c r="O79" s="9"/>
+      <c r="P79" s="9"/>
+      <c r="Q79" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="R79" s="9"/>
+      <c r="S79" s="9"/>
+      <c r="T79" s="9"/>
     </row>
     <row r="80" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
-      <c r="O80" s="3"/>
-      <c r="P80" s="3"/>
-      <c r="Q80" s="3"/>
-      <c r="R80" s="3"/>
-      <c r="S80" s="3"/>
-      <c r="T80" s="3"/>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="7"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3"/>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-      <c r="Q81" s="3"/>
-      <c r="R81" s="3"/>
-      <c r="S81" s="3"/>
-      <c r="T81" s="3"/>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="7"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-      <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3"/>
-      <c r="O82" s="3"/>
-      <c r="P82" s="3"/>
-      <c r="Q82" s="3"/>
-      <c r="R82" s="3"/>
-      <c r="S82" s="3"/>
-      <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-      <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="O83" s="3"/>
-      <c r="P83" s="3"/>
-      <c r="Q83" s="3"/>
-      <c r="R83" s="3"/>
-      <c r="S83" s="3"/>
-      <c r="T83" s="3"/>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="O84" s="3"/>
-      <c r="P84" s="3"/>
-      <c r="Q84" s="3"/>
-      <c r="R84" s="3"/>
-      <c r="S84" s="3"/>
-      <c r="T84" s="3"/>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="7"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3"/>
-      <c r="F85" s="3"/>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="O85" s="3"/>
-      <c r="P85" s="3"/>
-      <c r="Q85" s="3"/>
-      <c r="R85" s="3"/>
-      <c r="S85" s="3"/>
-      <c r="T85" s="3"/>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="O86" s="3"/>
-      <c r="P86" s="3"/>
-      <c r="Q86" s="3"/>
-      <c r="R86" s="3"/>
-      <c r="S86" s="3"/>
-      <c r="T86" s="3"/>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="O87" s="3"/>
-      <c r="P87" s="3"/>
-      <c r="Q87" s="3"/>
-      <c r="R87" s="3"/>
-      <c r="S87" s="3"/>
-      <c r="T87" s="3"/>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="O88" s="3"/>
-      <c r="P88" s="3"/>
-      <c r="Q88" s="3"/>
-      <c r="R88" s="3"/>
-      <c r="S88" s="3"/>
-      <c r="T88" s="3"/>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-      <c r="O89" s="3"/>
-      <c r="P89" s="3"/>
-      <c r="Q89" s="3"/>
-      <c r="R89" s="3"/>
-      <c r="S89" s="3"/>
-      <c r="T89" s="3"/>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A80" s="9"/>
+      <c r="B80" s="9">
+        <v>6007</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9">
+        <v>6</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G80" s="3">
+        <v>1</v>
+      </c>
+      <c r="H80" s="9">
+        <v>0</v>
+      </c>
+      <c r="I80" s="9">
+        <v>0</v>
+      </c>
+      <c r="J80" s="9">
+        <v>0</v>
+      </c>
+      <c r="K80" s="9">
+        <v>100</v>
+      </c>
+      <c r="L80" s="11">
+        <v>0</v>
+      </c>
+      <c r="M80" s="11">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>1</v>
+      </c>
+      <c r="O80" s="9"/>
+      <c r="P80" s="9"/>
+      <c r="Q80" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="R80" s="9"/>
+      <c r="S80" s="9"/>
+      <c r="T80" s="9"/>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" s="9"/>
+      <c r="B81" s="9">
+        <v>6008</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9">
+        <v>6</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="G81" s="3">
+        <v>1</v>
+      </c>
+      <c r="H81" s="9">
+        <v>0</v>
+      </c>
+      <c r="I81" s="9">
+        <v>0</v>
+      </c>
+      <c r="J81" s="9">
+        <v>0</v>
+      </c>
+      <c r="K81" s="9">
+        <v>100</v>
+      </c>
+      <c r="L81" s="11">
+        <v>0</v>
+      </c>
+      <c r="M81" s="11">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>1</v>
+      </c>
+      <c r="O81" s="9"/>
+      <c r="P81" s="9"/>
+      <c r="Q81" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="R81" s="9"/>
+      <c r="S81" s="9"/>
+      <c r="T81" s="9"/>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" s="9"/>
+      <c r="B82" s="9">
+        <v>6009</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9">
+        <v>6</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="G82" s="3">
+        <v>1</v>
+      </c>
+      <c r="H82" s="9">
+        <v>0</v>
+      </c>
+      <c r="I82" s="9">
+        <v>0</v>
+      </c>
+      <c r="J82" s="9">
+        <v>0</v>
+      </c>
+      <c r="K82" s="9">
+        <v>100</v>
+      </c>
+      <c r="L82" s="11">
+        <v>0</v>
+      </c>
+      <c r="M82" s="11">
+        <v>0</v>
+      </c>
+      <c r="N82" s="1">
+        <v>1</v>
+      </c>
+      <c r="O82" s="9"/>
+      <c r="P82" s="9"/>
+      <c r="Q82" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="R82" s="9"/>
+      <c r="S82" s="9"/>
+      <c r="T82" s="9"/>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" s="9"/>
+      <c r="B83" s="9">
+        <v>6010</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9">
+        <v>6</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G83" s="3">
+        <v>1</v>
+      </c>
+      <c r="H83" s="9">
+        <v>0</v>
+      </c>
+      <c r="I83" s="9">
+        <v>0</v>
+      </c>
+      <c r="J83" s="9">
+        <v>0</v>
+      </c>
+      <c r="K83" s="9">
+        <v>100</v>
+      </c>
+      <c r="L83" s="11">
+        <v>0</v>
+      </c>
+      <c r="M83" s="11">
+        <v>0</v>
+      </c>
+      <c r="N83" s="1">
+        <v>1</v>
+      </c>
+      <c r="O83" s="9"/>
+      <c r="P83" s="9"/>
+      <c r="Q83" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="R83" s="9"/>
+      <c r="S83" s="9"/>
+      <c r="T83" s="9"/>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" s="9"/>
+      <c r="B84" s="9">
+        <v>6011</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9">
+        <v>6</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G84" s="3">
+        <v>1</v>
+      </c>
+      <c r="H84" s="9">
+        <v>0</v>
+      </c>
+      <c r="I84" s="9">
+        <v>0</v>
+      </c>
+      <c r="J84" s="9">
+        <v>0</v>
+      </c>
+      <c r="K84" s="9">
+        <v>100</v>
+      </c>
+      <c r="L84" s="11">
+        <v>0</v>
+      </c>
+      <c r="M84" s="11">
+        <v>0</v>
+      </c>
+      <c r="N84" s="1">
+        <v>1</v>
+      </c>
+      <c r="O84" s="9"/>
+      <c r="P84" s="9"/>
+      <c r="Q84" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="R84" s="9"/>
+      <c r="S84" s="9"/>
+      <c r="T84" s="9"/>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" s="9"/>
+      <c r="B85" s="9">
+        <v>6012</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9">
+        <v>6</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" s="3">
+        <v>1</v>
+      </c>
+      <c r="H85" s="9">
+        <v>0</v>
+      </c>
+      <c r="I85" s="9">
+        <v>0</v>
+      </c>
+      <c r="J85" s="9">
+        <v>0</v>
+      </c>
+      <c r="K85" s="9">
+        <v>100</v>
+      </c>
+      <c r="L85" s="11">
+        <v>0</v>
+      </c>
+      <c r="M85" s="11">
+        <v>0</v>
+      </c>
+      <c r="N85" s="1">
+        <v>1</v>
+      </c>
+      <c r="O85" s="9"/>
+      <c r="P85" s="9"/>
+      <c r="Q85" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="R85" s="9"/>
+      <c r="S85" s="9"/>
+      <c r="T85" s="9"/>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" s="9"/>
+      <c r="B86" s="9">
+        <v>6013</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9">
+        <v>6</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="G86" s="3">
+        <v>1</v>
+      </c>
+      <c r="H86" s="9">
+        <v>0</v>
+      </c>
+      <c r="I86" s="9">
+        <v>0</v>
+      </c>
+      <c r="J86" s="9">
+        <v>0</v>
+      </c>
+      <c r="K86" s="9">
+        <v>100</v>
+      </c>
+      <c r="L86" s="11">
+        <v>0</v>
+      </c>
+      <c r="M86" s="11">
+        <v>0</v>
+      </c>
+      <c r="N86" s="1">
+        <v>1</v>
+      </c>
+      <c r="O86" s="9"/>
+      <c r="P86" s="9"/>
+      <c r="Q86" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="R86" s="9"/>
+      <c r="S86" s="9"/>
+      <c r="T86" s="9"/>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" s="9"/>
+      <c r="B87" s="9">
+        <v>6014</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9">
+        <v>6</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="G87" s="3">
+        <v>1</v>
+      </c>
+      <c r="H87" s="9">
+        <v>0</v>
+      </c>
+      <c r="I87" s="9">
+        <v>0</v>
+      </c>
+      <c r="J87" s="9">
+        <v>0</v>
+      </c>
+      <c r="K87" s="9">
+        <v>100</v>
+      </c>
+      <c r="L87" s="11">
+        <v>0</v>
+      </c>
+      <c r="M87" s="11">
+        <v>0</v>
+      </c>
+      <c r="N87" s="1">
+        <v>1</v>
+      </c>
+      <c r="O87" s="9"/>
+      <c r="P87" s="9"/>
+      <c r="Q87" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="R87" s="9"/>
+      <c r="S87" s="9"/>
+      <c r="T87" s="9"/>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" s="9"/>
+      <c r="B88" s="9">
+        <v>6015</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9">
+        <v>6</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="G88" s="3">
+        <v>1</v>
+      </c>
+      <c r="H88" s="9">
+        <v>0</v>
+      </c>
+      <c r="I88" s="9">
+        <v>1</v>
+      </c>
+      <c r="J88" s="9">
+        <v>0</v>
+      </c>
+      <c r="K88" s="9">
+        <v>100</v>
+      </c>
+      <c r="L88" s="11">
+        <v>0</v>
+      </c>
+      <c r="M88" s="11">
+        <v>0</v>
+      </c>
+      <c r="N88" s="1">
+        <v>1</v>
+      </c>
+      <c r="O88" s="9"/>
+      <c r="P88" s="9"/>
+      <c r="Q88" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="R88" s="9"/>
+      <c r="S88" s="9"/>
+      <c r="T88" s="9"/>
+    </row>
+    <row r="89" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="16"/>
+      <c r="B89" s="16">
+        <v>7001</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D89" s="16"/>
+      <c r="E89" s="16">
+        <v>7</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G89" s="16">
+        <v>1</v>
+      </c>
+      <c r="H89" s="9">
+        <v>0</v>
+      </c>
+      <c r="I89" s="9">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="9">
+        <v>100</v>
+      </c>
+      <c r="L89" s="11">
+        <v>1</v>
+      </c>
+      <c r="M89" s="11">
+        <v>0</v>
+      </c>
+      <c r="N89" s="1">
+        <v>1</v>
+      </c>
+      <c r="O89" s="16"/>
+      <c r="P89" s="16"/>
+      <c r="Q89" s="16"/>
+      <c r="R89" s="16"/>
+      <c r="S89" s="16"/>
+      <c r="T89" s="16"/>
+      <c r="U89" s="17"/>
+      <c r="V89" s="17"/>
+      <c r="W89" s="17"/>
+      <c r="X89" s="17"/>
+      <c r="Y89" s="17"/>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="7"/>
+      <c r="B90" s="3">
+        <v>7002</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>190</v>
+      </c>
       <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
+      <c r="E90" s="3">
+        <v>7</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G90" s="3">
+        <v>1</v>
+      </c>
+      <c r="H90" s="9">
+        <v>0</v>
+      </c>
+      <c r="I90" s="9">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <v>0</v>
+      </c>
+      <c r="K90" s="9">
+        <v>100</v>
+      </c>
+      <c r="L90" s="11">
+        <v>1</v>
+      </c>
+      <c r="M90" s="11">
+        <v>0</v>
+      </c>
+      <c r="N90" s="1">
+        <v>1</v>
+      </c>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
@@ -4943,19 +5966,45 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="7"/>
+      <c r="B91" s="3">
+        <v>7003</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>191</v>
+      </c>
       <c r="D91" s="3"/>
-      <c r="E91" s="3"/>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
+      <c r="E91" s="3">
+        <v>7</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G91" s="3">
+        <v>1</v>
+      </c>
+      <c r="H91" s="9">
+        <v>0</v>
+      </c>
+      <c r="I91" s="9">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="9">
+        <v>100</v>
+      </c>
+      <c r="L91" s="11">
+        <v>1</v>
+      </c>
+      <c r="M91" s="11">
+        <v>0</v>
+      </c>
+      <c r="N91" s="1">
+        <v>0</v>
+      </c>
       <c r="O91" s="3"/>
       <c r="P91" s="3"/>
       <c r="Q91" s="3"/>
@@ -4963,19 +6012,45 @@
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="7"/>
+      <c r="B92" s="3">
+        <v>7004</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>192</v>
+      </c>
       <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
+      <c r="E92" s="3">
+        <v>7</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="G92" s="3">
+        <v>1</v>
+      </c>
+      <c r="H92" s="9">
+        <v>0</v>
+      </c>
+      <c r="I92" s="9">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+      <c r="K92" s="9">
+        <v>100</v>
+      </c>
+      <c r="L92" s="11">
+        <v>1</v>
+      </c>
+      <c r="M92" s="11">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1">
+        <v>1</v>
+      </c>
       <c r="O92" s="3"/>
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
@@ -4983,39 +6058,96 @@
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="7"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3"/>
-      <c r="F93" s="3"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
-      <c r="O93" s="3"/>
-      <c r="P93" s="3"/>
-      <c r="Q93" s="3"/>
-      <c r="R93" s="3"/>
-      <c r="S93" s="3"/>
-      <c r="T93" s="3"/>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="16"/>
+      <c r="B93" s="16">
+        <v>8001</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="D93" s="16"/>
+      <c r="E93" s="16">
+        <v>8</v>
+      </c>
+      <c r="F93" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="G93" s="3">
+        <v>1</v>
+      </c>
+      <c r="H93" s="9">
+        <v>0</v>
+      </c>
+      <c r="I93" s="9">
+        <v>1</v>
+      </c>
+      <c r="J93" s="3">
+        <v>1</v>
+      </c>
+      <c r="K93" s="9">
+        <v>100</v>
+      </c>
+      <c r="L93" s="9">
+        <v>1</v>
+      </c>
+      <c r="M93" s="9">
+        <v>1</v>
+      </c>
+      <c r="N93" s="1">
+        <v>1</v>
+      </c>
+      <c r="O93" s="16"/>
+      <c r="P93" s="16"/>
+      <c r="Q93" s="16"/>
+      <c r="R93" s="16"/>
+      <c r="S93" s="16"/>
+      <c r="T93" s="16"/>
+      <c r="U93" s="17"/>
+      <c r="V93" s="17"/>
+      <c r="W93" s="17"/>
+      <c r="X93" s="17"/>
+      <c r="Y93" s="17"/>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="7"/>
+      <c r="B94" s="3">
+        <v>8002</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>194</v>
+      </c>
       <c r="D94" s="3"/>
-      <c r="E94" s="3"/>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
+      <c r="E94" s="3">
+        <v>8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G94" s="3">
+        <v>1</v>
+      </c>
+      <c r="H94" s="9">
+        <v>0</v>
+      </c>
+      <c r="I94" s="9">
+        <v>1</v>
+      </c>
+      <c r="J94" s="3">
+        <v>1</v>
+      </c>
+      <c r="K94" s="9">
+        <v>100</v>
+      </c>
+      <c r="L94" s="9">
+        <v>1</v>
+      </c>
+      <c r="M94" s="9">
+        <v>1</v>
+      </c>
+      <c r="N94" s="1">
+        <v>1</v>
+      </c>
       <c r="O94" s="3"/>
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
@@ -5023,19 +6155,45 @@
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="7"/>
+      <c r="B95" s="3">
+        <v>8003</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>195</v>
+      </c>
       <c r="D95" s="3"/>
-      <c r="E95" s="3"/>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
+      <c r="E95" s="3">
+        <v>8</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G95" s="3">
+        <v>1</v>
+      </c>
+      <c r="H95" s="9">
+        <v>0</v>
+      </c>
+      <c r="I95" s="9">
+        <v>1</v>
+      </c>
+      <c r="J95" s="3">
+        <v>1</v>
+      </c>
+      <c r="K95" s="9">
+        <v>100</v>
+      </c>
+      <c r="L95" s="9">
+        <v>1</v>
+      </c>
+      <c r="M95" s="9">
+        <v>1</v>
+      </c>
+      <c r="N95" s="1">
+        <v>1</v>
+      </c>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
@@ -5043,19 +6201,45 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="7"/>
+      <c r="B96" s="3">
+        <v>8004</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>196</v>
+      </c>
       <c r="D96" s="3"/>
-      <c r="E96" s="3"/>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
+      <c r="E96" s="3">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G96" s="3">
+        <v>1</v>
+      </c>
+      <c r="H96" s="9">
+        <v>0</v>
+      </c>
+      <c r="I96" s="9">
+        <v>1</v>
+      </c>
+      <c r="J96" s="3">
+        <v>1</v>
+      </c>
+      <c r="K96" s="9">
+        <v>100</v>
+      </c>
+      <c r="L96" s="9">
+        <v>1</v>
+      </c>
+      <c r="M96" s="9">
+        <v>1</v>
+      </c>
+      <c r="N96" s="1">
+        <v>1</v>
+      </c>
       <c r="O96" s="3"/>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
@@ -5065,17 +6249,43 @@
     </row>
     <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
-      <c r="C97" s="7"/>
+      <c r="B97" s="3">
+        <v>8005</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>197</v>
+      </c>
       <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
+      <c r="E97" s="3">
+        <v>8</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G97" s="3">
+        <v>1</v>
+      </c>
+      <c r="H97" s="9">
+        <v>0</v>
+      </c>
+      <c r="I97" s="9">
+        <v>1</v>
+      </c>
+      <c r="J97" s="3">
+        <v>1</v>
+      </c>
+      <c r="K97" s="9">
+        <v>100</v>
+      </c>
+      <c r="L97" s="9">
+        <v>1</v>
+      </c>
+      <c r="M97" s="9">
+        <v>1</v>
+      </c>
+      <c r="N97" s="1">
+        <v>1</v>
+      </c>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
       <c r="Q97" s="3"/>
@@ -5085,17 +6295,43 @@
     </row>
     <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="7"/>
+      <c r="B98" s="3">
+        <v>8006</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
+      <c r="E98" s="3">
+        <v>8</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G98" s="3">
+        <v>1</v>
+      </c>
+      <c r="H98" s="9">
+        <v>0</v>
+      </c>
+      <c r="I98" s="9">
+        <v>1</v>
+      </c>
+      <c r="J98" s="3">
+        <v>1</v>
+      </c>
+      <c r="K98" s="9">
+        <v>100</v>
+      </c>
+      <c r="L98" s="9">
+        <v>1</v>
+      </c>
+      <c r="M98" s="9">
+        <v>1</v>
+      </c>
+      <c r="N98" s="1">
+        <v>1</v>
+      </c>
       <c r="O98" s="3"/>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
@@ -5105,17 +6341,43 @@
     </row>
     <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="7"/>
+      <c r="B99" s="3">
+        <v>8007</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>199</v>
+      </c>
       <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
+      <c r="E99" s="3">
+        <v>8</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G99" s="3">
+        <v>1</v>
+      </c>
+      <c r="H99" s="9">
+        <v>0</v>
+      </c>
+      <c r="I99" s="9">
+        <v>1</v>
+      </c>
+      <c r="J99" s="3">
+        <v>1</v>
+      </c>
+      <c r="K99" s="9">
+        <v>100</v>
+      </c>
+      <c r="L99" s="9">
+        <v>1</v>
+      </c>
+      <c r="M99" s="9">
+        <v>1</v>
+      </c>
+      <c r="N99" s="1">
+        <v>1</v>
+      </c>
       <c r="O99" s="3"/>
       <c r="P99" s="3"/>
       <c r="Q99" s="3"/>
@@ -5125,17 +6387,43 @@
     </row>
     <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="7"/>
+      <c r="B100" s="3">
+        <v>8008</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>200</v>
+      </c>
       <c r="D100" s="3"/>
-      <c r="E100" s="3"/>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3"/>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
+      <c r="E100" s="3">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G100" s="3">
+        <v>1</v>
+      </c>
+      <c r="H100" s="9">
+        <v>0</v>
+      </c>
+      <c r="I100" s="9">
+        <v>1</v>
+      </c>
+      <c r="J100" s="3">
+        <v>1</v>
+      </c>
+      <c r="K100" s="9">
+        <v>100</v>
+      </c>
+      <c r="L100" s="9">
+        <v>1</v>
+      </c>
+      <c r="M100" s="9">
+        <v>1</v>
+      </c>
+      <c r="N100" s="1">
+        <v>1</v>
+      </c>
       <c r="O100" s="3"/>
       <c r="P100" s="3"/>
       <c r="Q100" s="3"/>
@@ -5145,17 +6433,43 @@
     </row>
     <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="7"/>
+      <c r="B101" s="3">
+        <v>8009</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>201</v>
+      </c>
       <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
+      <c r="E101" s="3">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G101" s="3">
+        <v>1</v>
+      </c>
+      <c r="H101" s="9">
+        <v>0</v>
+      </c>
+      <c r="I101" s="9">
+        <v>1</v>
+      </c>
+      <c r="J101" s="3">
+        <v>1</v>
+      </c>
+      <c r="K101" s="9">
+        <v>100</v>
+      </c>
+      <c r="L101" s="9">
+        <v>1</v>
+      </c>
+      <c r="M101" s="9">
+        <v>1</v>
+      </c>
+      <c r="N101" s="1">
+        <v>1</v>
+      </c>
       <c r="O101" s="3"/>
       <c r="P101" s="3"/>
       <c r="Q101" s="3"/>
@@ -5165,17 +6479,43 @@
     </row>
     <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="7"/>
+      <c r="B102" s="3">
+        <v>8010</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>202</v>
+      </c>
       <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
+      <c r="E102" s="3">
+        <v>8</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G102" s="3">
+        <v>1</v>
+      </c>
+      <c r="H102" s="9">
+        <v>0</v>
+      </c>
+      <c r="I102" s="9">
+        <v>1</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1</v>
+      </c>
+      <c r="K102" s="9">
+        <v>100</v>
+      </c>
+      <c r="L102" s="9">
+        <v>1</v>
+      </c>
+      <c r="M102" s="9">
+        <v>1</v>
+      </c>
+      <c r="N102" s="1">
+        <v>1</v>
+      </c>
       <c r="O102" s="3"/>
       <c r="P102" s="3"/>
       <c r="Q102" s="3"/>
@@ -5185,17 +6525,43 @@
     </row>
     <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="7"/>
+      <c r="B103" s="3">
+        <v>8011</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>203</v>
+      </c>
       <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-      <c r="J103" s="3"/>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
+      <c r="E103" s="3">
+        <v>8</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G103" s="3">
+        <v>1</v>
+      </c>
+      <c r="H103" s="9">
+        <v>0</v>
+      </c>
+      <c r="I103" s="9">
+        <v>1</v>
+      </c>
+      <c r="J103" s="3">
+        <v>1</v>
+      </c>
+      <c r="K103" s="9">
+        <v>100</v>
+      </c>
+      <c r="L103" s="9">
+        <v>1</v>
+      </c>
+      <c r="M103" s="9">
+        <v>1</v>
+      </c>
+      <c r="N103" s="1">
+        <v>1</v>
+      </c>
       <c r="O103" s="3"/>
       <c r="P103" s="3"/>
       <c r="Q103" s="3"/>
@@ -5205,17 +6571,43 @@
     </row>
     <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="7"/>
+      <c r="B104" s="3">
+        <v>8012</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>204</v>
+      </c>
       <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3"/>
-      <c r="J104" s="3"/>
-      <c r="K104" s="3"/>
-      <c r="L104" s="3"/>
+      <c r="E104" s="3">
+        <v>8</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G104" s="3">
+        <v>1</v>
+      </c>
+      <c r="H104" s="9">
+        <v>0</v>
+      </c>
+      <c r="I104" s="9">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3">
+        <v>1</v>
+      </c>
+      <c r="K104" s="9">
+        <v>100</v>
+      </c>
+      <c r="L104" s="9">
+        <v>1</v>
+      </c>
+      <c r="M104" s="9">
+        <v>1</v>
+      </c>
+      <c r="N104" s="1">
+        <v>1</v>
+      </c>
       <c r="O104" s="3"/>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
@@ -5225,17 +6617,43 @@
     </row>
     <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="7"/>
+      <c r="B105" s="3">
+        <v>8013</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>205</v>
+      </c>
       <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3"/>
-      <c r="J105" s="3"/>
-      <c r="K105" s="3"/>
-      <c r="L105" s="3"/>
+      <c r="E105" s="3">
+        <v>8</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G105" s="3">
+        <v>1</v>
+      </c>
+      <c r="H105" s="9">
+        <v>0</v>
+      </c>
+      <c r="I105" s="9">
+        <v>1</v>
+      </c>
+      <c r="J105" s="3">
+        <v>1</v>
+      </c>
+      <c r="K105" s="9">
+        <v>100</v>
+      </c>
+      <c r="L105" s="9">
+        <v>1</v>
+      </c>
+      <c r="M105" s="9">
+        <v>1</v>
+      </c>
+      <c r="N105" s="1">
+        <v>1</v>
+      </c>
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
       <c r="Q105" s="3"/>
@@ -5245,17 +6663,43 @@
     </row>
     <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="7"/>
+      <c r="B106" s="3">
+        <v>8014</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>206</v>
+      </c>
       <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3"/>
-      <c r="J106" s="3"/>
-      <c r="K106" s="3"/>
-      <c r="L106" s="3"/>
+      <c r="E106" s="3">
+        <v>8</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G106" s="3">
+        <v>1</v>
+      </c>
+      <c r="H106" s="9">
+        <v>0</v>
+      </c>
+      <c r="I106" s="9">
+        <v>1</v>
+      </c>
+      <c r="J106" s="3">
+        <v>1</v>
+      </c>
+      <c r="K106" s="9">
+        <v>100</v>
+      </c>
+      <c r="L106" s="9">
+        <v>1</v>
+      </c>
+      <c r="M106" s="9">
+        <v>1</v>
+      </c>
+      <c r="N106" s="1">
+        <v>1</v>
+      </c>
       <c r="O106" s="3"/>
       <c r="P106" s="3"/>
       <c r="Q106" s="3"/>
@@ -6823,7 +8267,7 @@
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="7"/>
@@ -6843,139 +8287,1057 @@
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A186" s="3"/>
-      <c r="B186" s="3"/>
-      <c r="C186" s="7"/>
-      <c r="D186" s="3"/>
-      <c r="E186" s="3"/>
-      <c r="F186" s="3"/>
-      <c r="G186" s="3"/>
-      <c r="H186" s="3"/>
-      <c r="I186" s="3"/>
-      <c r="J186" s="3"/>
-      <c r="K186" s="3"/>
-      <c r="L186" s="3"/>
-      <c r="O186" s="3"/>
-      <c r="P186" s="3"/>
-      <c r="Q186" s="3"/>
-      <c r="R186" s="3"/>
-      <c r="S186" s="3"/>
-      <c r="T186" s="3"/>
-    </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A187" s="3"/>
-      <c r="B187" s="3"/>
-      <c r="C187" s="7"/>
-      <c r="D187" s="3"/>
-      <c r="E187" s="3"/>
-      <c r="F187" s="3"/>
-      <c r="G187" s="3"/>
-      <c r="H187" s="3"/>
-      <c r="I187" s="3"/>
-      <c r="J187" s="3"/>
-      <c r="K187" s="3"/>
-      <c r="L187" s="3"/>
-      <c r="O187" s="3"/>
-      <c r="P187" s="3"/>
-      <c r="Q187" s="3"/>
-      <c r="R187" s="3"/>
-      <c r="S187" s="3"/>
-      <c r="T187" s="3"/>
-    </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A188" s="3"/>
-      <c r="B188" s="3"/>
-      <c r="C188" s="7"/>
-      <c r="D188" s="3"/>
-      <c r="E188" s="3"/>
-      <c r="F188" s="3"/>
-      <c r="G188" s="3"/>
-      <c r="H188" s="3"/>
-      <c r="I188" s="3"/>
-      <c r="J188" s="3"/>
-      <c r="K188" s="3"/>
-      <c r="L188" s="3"/>
-      <c r="O188" s="3"/>
-      <c r="P188" s="3"/>
-      <c r="Q188" s="3"/>
-      <c r="R188" s="3"/>
-      <c r="S188" s="3"/>
-      <c r="T188" s="3"/>
-    </row>
-    <row r="189" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
-      <c r="C189" s="7"/>
-      <c r="D189" s="3"/>
-      <c r="E189" s="3"/>
-      <c r="F189" s="3"/>
-      <c r="G189" s="3"/>
-      <c r="H189" s="3"/>
-      <c r="I189" s="3"/>
-      <c r="J189" s="3"/>
-      <c r="K189" s="3"/>
-      <c r="L189" s="3"/>
-      <c r="O189" s="3"/>
-      <c r="P189" s="3"/>
-      <c r="Q189" s="3"/>
-      <c r="R189" s="3"/>
-      <c r="S189" s="3"/>
-      <c r="T189" s="3"/>
-    </row>
-    <row r="190" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="8"/>
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-      <c r="F190" s="8"/>
-      <c r="G190" s="8"/>
-      <c r="H190" s="8"/>
-      <c r="I190" s="8"/>
-      <c r="J190" s="14"/>
-      <c r="K190" s="14"/>
-      <c r="O190" s="8"/>
-      <c r="P190" s="8"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-    </row>
-    <row r="191" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A191" s="8"/>
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-      <c r="F191" s="8"/>
-      <c r="G191" s="8"/>
-      <c r="H191" s="8"/>
-      <c r="I191" s="8"/>
-      <c r="J191" s="14"/>
-      <c r="K191" s="14"/>
-      <c r="O191" s="8"/>
-      <c r="P191" s="8"/>
-      <c r="Q191" s="8"/>
-      <c r="R191" s="8"/>
-    </row>
-    <row r="192" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A192" s="8"/>
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
-      <c r="F192" s="8"/>
-      <c r="G192" s="8"/>
-      <c r="H192" s="8"/>
-      <c r="I192" s="8"/>
-      <c r="J192" s="14"/>
-      <c r="K192" s="14"/>
-      <c r="O192" s="8"/>
-      <c r="P192" s="8"/>
-      <c r="Q192" s="8"/>
-      <c r="R192" s="8"/>
+    <row r="186" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="8"/>
+      <c r="B186" s="8"/>
+      <c r="C186" s="8"/>
+      <c r="D186" s="8"/>
+      <c r="E186" s="8"/>
+      <c r="F186" s="8"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="8"/>
+      <c r="I186" s="8"/>
+      <c r="J186" s="14"/>
+      <c r="K186" s="14"/>
+      <c r="O186" s="8"/>
+      <c r="P186" s="8"/>
+      <c r="Q186" s="8"/>
+      <c r="R186" s="8"/>
+    </row>
+    <row r="187" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A187" s="8"/>
+      <c r="B187" s="8"/>
+      <c r="C187" s="8"/>
+      <c r="D187" s="8"/>
+      <c r="E187" s="8"/>
+      <c r="F187" s="8"/>
+      <c r="G187" s="8"/>
+      <c r="H187" s="8"/>
+      <c r="I187" s="8"/>
+      <c r="J187" s="14"/>
+      <c r="K187" s="14"/>
+      <c r="O187" s="8"/>
+      <c r="P187" s="8"/>
+      <c r="Q187" s="8"/>
+      <c r="R187" s="8"/>
+    </row>
+    <row r="188" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A188" s="8"/>
+      <c r="B188" s="8"/>
+      <c r="C188" s="8"/>
+      <c r="D188" s="8"/>
+      <c r="E188" s="8"/>
+      <c r="F188" s="8"/>
+      <c r="G188" s="8"/>
+      <c r="H188" s="8"/>
+      <c r="I188" s="8"/>
+      <c r="J188" s="14"/>
+      <c r="K188" s="14"/>
+      <c r="O188" s="8"/>
+      <c r="P188" s="8"/>
+      <c r="Q188" s="8"/>
+      <c r="R188" s="8"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:Y106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8A5C4E9-D329-4E3E-B26B-2A90B7C353D7}">
+  <dimension ref="L19:R61"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="20.5" customWidth="1"/>
+    <col min="16" max="17" width="30.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L19" t="s">
+        <v>208</v>
+      </c>
+      <c r="M19" t="s">
+        <v>209</v>
+      </c>
+      <c r="N19" t="s">
+        <v>210</v>
+      </c>
+      <c r="P19" t="s">
+        <v>211</v>
+      </c>
+      <c r="R19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>5001</v>
+      </c>
+      <c r="M20" t="s">
+        <v>213</v>
+      </c>
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20" t="s">
+        <v>245</v>
+      </c>
+      <c r="P20" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q20" t="str">
+        <f>O20&amp;P20</f>
+        <v>Item/Watering_Can</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>5002</v>
+      </c>
+      <c r="M21" t="s">
+        <v>214</v>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21" t="s">
+        <v>245</v>
+      </c>
+      <c r="P21" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q21" t="str">
+        <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
+        <v>Item/Lotus_Leaf</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>5003</v>
+      </c>
+      <c r="M22" t="s">
+        <v>182</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22" t="s">
+        <v>245</v>
+      </c>
+      <c r="P22" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q22" t="str">
+        <f t="shared" si="0"/>
+        <v>Item/Kiwi_Tree</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L23">
+        <v>5004</v>
+      </c>
+      <c r="M23" t="s">
+        <v>183</v>
+      </c>
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23" t="s">
+        <v>245</v>
+      </c>
+      <c r="P23" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q23" t="str">
+        <f t="shared" si="0"/>
+        <v>Item/Bush_Root</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L24">
+        <v>5005</v>
+      </c>
+      <c r="M24" t="s">
+        <v>184</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24" t="s">
+        <v>245</v>
+      </c>
+      <c r="P24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q24" t="str">
+        <f t="shared" si="0"/>
+        <v>Item/Portal</v>
+      </c>
+      <c r="R24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L25">
+        <v>5006</v>
+      </c>
+      <c r="M25" t="s">
+        <v>185</v>
+      </c>
+      <c r="N25">
+        <v>5</v>
+      </c>
+      <c r="O25" t="s">
+        <v>245</v>
+      </c>
+      <c r="P25" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q25" t="str">
+        <f t="shared" si="0"/>
+        <v>Item/Hidden_Door</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L26">
+        <v>5007</v>
+      </c>
+      <c r="M26" t="s">
+        <v>186</v>
+      </c>
+      <c r="N26">
+        <v>5</v>
+      </c>
+      <c r="O26" t="s">
+        <v>245</v>
+      </c>
+      <c r="P26" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q26" t="str">
+        <f t="shared" si="0"/>
+        <v>Item/Key</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L27">
+        <v>5008</v>
+      </c>
+      <c r="M27" t="s">
+        <v>187</v>
+      </c>
+      <c r="N27">
+        <v>5</v>
+      </c>
+      <c r="O27" t="s">
+        <v>245</v>
+      </c>
+      <c r="P27" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q27" t="str">
+        <f t="shared" si="0"/>
+        <v>Item/Popcorn_Machine</v>
+      </c>
+      <c r="R27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L28">
+        <v>5009</v>
+      </c>
+      <c r="M28" t="s">
+        <v>217</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28" t="s">
+        <v>245</v>
+      </c>
+      <c r="P28" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q28" t="str">
+        <f t="shared" si="0"/>
+        <v>Item/Popcorn_Cauliflower_Soup_Flavor</v>
+      </c>
+      <c r="R28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L29">
+        <v>6001</v>
+      </c>
+      <c r="M29" t="s">
+        <v>167</v>
+      </c>
+      <c r="O29" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P29" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q29" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/mushroom_002</v>
+      </c>
+      <c r="R29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L30">
+        <v>6002</v>
+      </c>
+      <c r="M30" t="s">
+        <v>168</v>
+      </c>
+      <c r="O30" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P30" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q30" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/mushroom_002</v>
+      </c>
+      <c r="R30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L31">
+        <v>6003</v>
+      </c>
+      <c r="M31" t="s">
+        <v>169</v>
+      </c>
+      <c r="O31" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P31" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q31" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Pumpkin</v>
+      </c>
+      <c r="R31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L32">
+        <v>6004</v>
+      </c>
+      <c r="M32" t="s">
+        <v>170</v>
+      </c>
+      <c r="O32" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P32" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q32" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Carrot</v>
+      </c>
+      <c r="R32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L33">
+        <v>6005</v>
+      </c>
+      <c r="M33" t="s">
+        <v>171</v>
+      </c>
+      <c r="O33" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P33" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q33" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Beet</v>
+      </c>
+      <c r="R33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L34">
+        <v>6006</v>
+      </c>
+      <c r="M34" t="s">
+        <v>172</v>
+      </c>
+      <c r="O34" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P34" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q34" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Tomato_red</v>
+      </c>
+      <c r="R34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L35">
+        <v>6007</v>
+      </c>
+      <c r="M35" t="s">
+        <v>173</v>
+      </c>
+      <c r="O35" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P35" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q35" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Tomato_red</v>
+      </c>
+      <c r="R35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L36">
+        <v>6008</v>
+      </c>
+      <c r="M36" t="s">
+        <v>174</v>
+      </c>
+      <c r="O36" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P36" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q36" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Tomato_yellow</v>
+      </c>
+      <c r="R36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L37">
+        <v>6009</v>
+      </c>
+      <c r="M37" t="s">
+        <v>175</v>
+      </c>
+      <c r="O37" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P37" t="s">
+        <v>273</v>
+      </c>
+      <c r="Q37" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Tomato_green</v>
+      </c>
+      <c r="R37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L38">
+        <v>6010</v>
+      </c>
+      <c r="M38" t="s">
+        <v>176</v>
+      </c>
+      <c r="O38" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P38" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q38" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Tomato_red</v>
+      </c>
+      <c r="R38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L39">
+        <v>6011</v>
+      </c>
+      <c r="M39" t="s">
+        <v>177</v>
+      </c>
+      <c r="O39" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P39" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q39" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Tomato_red</v>
+      </c>
+      <c r="R39">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L40">
+        <v>6012</v>
+      </c>
+      <c r="M40" t="s">
+        <v>178</v>
+      </c>
+      <c r="O40" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P40" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q40" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Tomato_red</v>
+      </c>
+      <c r="R40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L41">
+        <v>6013</v>
+      </c>
+      <c r="M41" t="s">
+        <v>179</v>
+      </c>
+      <c r="O41" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P41" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q41" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/mushroom_002</v>
+      </c>
+      <c r="R41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L42">
+        <v>6014</v>
+      </c>
+      <c r="M42" t="s">
+        <v>180</v>
+      </c>
+      <c r="O42" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P42" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q42" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/Kiwi</v>
+      </c>
+      <c r="R42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L43">
+        <v>6015</v>
+      </c>
+      <c r="M43" t="s">
+        <v>181</v>
+      </c>
+      <c r="O43" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="P43" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q43" t="str">
+        <f t="shared" si="0"/>
+        <v>Bulit/mushroom_002</v>
+      </c>
+      <c r="R43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L44">
+        <v>7001</v>
+      </c>
+      <c r="M44" t="s">
+        <v>218</v>
+      </c>
+      <c r="N44">
+        <v>7</v>
+      </c>
+      <c r="O44" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="P44" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q44" t="str">
+        <f t="shared" si="0"/>
+        <v>Npc/Ms._Beet</v>
+      </c>
+      <c r="R44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L45">
+        <v>7002</v>
+      </c>
+      <c r="M45" t="s">
+        <v>219</v>
+      </c>
+      <c r="N45">
+        <v>7</v>
+      </c>
+      <c r="O45" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="P45" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q45" t="str">
+        <f t="shared" si="0"/>
+        <v>Npc/Cauliflower_Sheep_White</v>
+      </c>
+      <c r="R45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L46">
+        <v>7003</v>
+      </c>
+      <c r="M46" t="s">
+        <v>220</v>
+      </c>
+      <c r="N46">
+        <v>7</v>
+      </c>
+      <c r="O46" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="P46" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q46" t="str">
+        <f t="shared" si="0"/>
+        <v>Npc/Cauliflower_Sheep_Green</v>
+      </c>
+      <c r="R46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L47">
+        <v>7004</v>
+      </c>
+      <c r="M47" t="s">
+        <v>221</v>
+      </c>
+      <c r="N47">
+        <v>7</v>
+      </c>
+      <c r="O47" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="P47" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q47" t="str">
+        <f t="shared" si="0"/>
+        <v>Npc/Mr._Monkey</v>
+      </c>
+      <c r="R47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L48">
+        <v>8001</v>
+      </c>
+      <c r="M48" t="s">
+        <v>222</v>
+      </c>
+      <c r="N48">
+        <v>8</v>
+      </c>
+      <c r="O48" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P48" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q48" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L49">
+        <v>8002</v>
+      </c>
+      <c r="M49" t="s">
+        <v>223</v>
+      </c>
+      <c r="N49">
+        <v>8</v>
+      </c>
+      <c r="O49" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P49" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q49" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L50">
+        <v>8003</v>
+      </c>
+      <c r="M50" t="s">
+        <v>224</v>
+      </c>
+      <c r="N50">
+        <v>8</v>
+      </c>
+      <c r="O50" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P50" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q50" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L51">
+        <v>8004</v>
+      </c>
+      <c r="M51" t="s">
+        <v>225</v>
+      </c>
+      <c r="N51">
+        <v>8</v>
+      </c>
+      <c r="O51" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P51" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q51" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L52">
+        <v>8005</v>
+      </c>
+      <c r="M52" t="s">
+        <v>226</v>
+      </c>
+      <c r="N52">
+        <v>8</v>
+      </c>
+      <c r="O52" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P52" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q52" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L53">
+        <v>8006</v>
+      </c>
+      <c r="M53" t="s">
+        <v>227</v>
+      </c>
+      <c r="N53">
+        <v>8</v>
+      </c>
+      <c r="O53" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P53" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q53" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L54">
+        <v>8007</v>
+      </c>
+      <c r="M54" t="s">
+        <v>228</v>
+      </c>
+      <c r="N54">
+        <v>8</v>
+      </c>
+      <c r="O54" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P54" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q54" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L55">
+        <v>8008</v>
+      </c>
+      <c r="M55" t="s">
+        <v>229</v>
+      </c>
+      <c r="N55">
+        <v>8</v>
+      </c>
+      <c r="O55" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P55" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q55" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L56">
+        <v>8009</v>
+      </c>
+      <c r="M56" t="s">
+        <v>230</v>
+      </c>
+      <c r="N56">
+        <v>8</v>
+      </c>
+      <c r="O56" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P56" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q56" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L57">
+        <v>8010</v>
+      </c>
+      <c r="M57" t="s">
+        <v>231</v>
+      </c>
+      <c r="N57">
+        <v>8</v>
+      </c>
+      <c r="O57" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P57" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q57" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L58">
+        <v>8011</v>
+      </c>
+      <c r="M58" t="s">
+        <v>232</v>
+      </c>
+      <c r="N58">
+        <v>8</v>
+      </c>
+      <c r="O58" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P58" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q58" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L59">
+        <v>8012</v>
+      </c>
+      <c r="M59" t="s">
+        <v>233</v>
+      </c>
+      <c r="N59">
+        <v>8</v>
+      </c>
+      <c r="O59" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P59" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q59" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L60">
+        <v>8013</v>
+      </c>
+      <c r="M60" t="s">
+        <v>234</v>
+      </c>
+      <c r="N60">
+        <v>8</v>
+      </c>
+      <c r="O60" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P60" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q60" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="12:18" x14ac:dyDescent="0.3">
+      <c r="L61">
+        <v>8014</v>
+      </c>
+      <c r="M61" t="s">
+        <v>235</v>
+      </c>
+      <c r="N61">
+        <v>8</v>
+      </c>
+      <c r="O61" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="P61" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q61" t="str">
+        <f t="shared" si="0"/>
+        <v>Seedling/seedling</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BAD9A5B-7F49-4884-A445-D8AE447D2FB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A1F8E7-5300-4D89-B8D9-F883090C4C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38290" yWindow="4430" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$Y$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$Z$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="288">
   <si>
     <t>##var</t>
   </si>
@@ -63,10 +63,6 @@
   </si>
   <si>
     <t>itemTips</t>
-  </si>
-  <si>
-    <t>icon</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>model</t>
@@ -1038,6 +1034,30 @@
   </si>
   <si>
     <t>道具类型 1种子袋 2作物 3巨大作物 4迷你作物 5特殊 6房子 7npc  8幼苗</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞下是否有效果</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_eat</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>model_size</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0吞下无效果 1吞下有效果</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1106,6 +1126,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1562,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y188"/>
+  <dimension ref="A1:Z188"/>
   <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.1640625" style="1"/>
@@ -1575,12 +1596,12 @@
     <col min="9" max="11" width="16.75" style="1" customWidth="1"/>
     <col min="12" max="16" width="12.1640625" style="1"/>
     <col min="17" max="18" width="17.9140625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="26.33203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1640625" style="1"/>
-    <col min="26" max="16384" width="12.1640625" style="1"/>
+    <col min="19" max="20" width="26.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="12.1640625" style="1"/>
+    <col min="27" max="16384" width="12.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1594,60 +1615,63 @@
         <v>7</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>8</v>
+        <v>286</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="U1" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="P1" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>3</v>
@@ -1656,34 +1680,34 @@
         <v>3</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>14</v>
+        <v>285</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>3</v>
@@ -1701,147 +1725,156 @@
         <v>3</v>
       </c>
       <c r="T2" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="U2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>11</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="G3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="K3" s="6" t="s">
+      <c r="H4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="N3" s="6" t="s">
+      <c r="L4" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="M4" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="O4" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="6" t="s">
+      <c r="P4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q4" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="R4" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="9">
         <v>1001</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9">
         <v>1</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G5" s="9">
         <v>1</v>
@@ -1869,22 +1902,25 @@
       </c>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
-      <c r="T5" s="9"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T5" s="1">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="9">
         <v>1002</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9">
         <v>1</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G6" s="9">
         <v>1</v>
@@ -1912,22 +1948,25 @@
       </c>
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
-      <c r="T6" s="9"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="9"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="9">
         <v>1003</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9">
         <v>1</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G7" s="9">
         <v>1</v>
@@ -1955,22 +1994,25 @@
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="9"/>
-      <c r="T7" s="9"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="9"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="9">
         <v>1004</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9">
         <v>1</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G8" s="9">
         <v>1</v>
@@ -1999,22 +2041,25 @@
       <c r="O8" s="9"/>
       <c r="P8" s="9"/>
       <c r="S8" s="9"/>
-      <c r="T8" s="9"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="9">
         <v>1005</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9">
         <v>1</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G9" s="9">
         <v>1</v>
@@ -2043,22 +2088,25 @@
       <c r="O9" s="9"/>
       <c r="P9" s="9"/>
       <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="9">
         <v>1006</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9">
         <v>1</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G10" s="9">
         <v>1</v>
@@ -2087,22 +2135,25 @@
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="S10" s="9"/>
-      <c r="T10" s="9"/>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="9">
         <v>1007</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9">
         <v>1</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G11" s="9">
         <v>1</v>
@@ -2131,22 +2182,25 @@
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T11" s="1">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="9">
         <v>1008</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9">
         <v>1</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G12" s="9">
         <v>1</v>
@@ -2175,22 +2229,25 @@
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="9">
         <v>1009</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9">
         <v>1</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G13" s="9">
         <v>1</v>
@@ -2219,22 +2276,25 @@
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T13" s="1">
+        <v>0</v>
+      </c>
+      <c r="U13" s="9"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="9">
         <v>1010</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9">
         <v>1</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G14" s="9">
         <v>1</v>
@@ -2263,22 +2323,25 @@
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="9">
         <v>1011</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9">
         <v>1</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G15" s="9">
         <v>1</v>
@@ -2307,22 +2370,25 @@
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="S15" s="9"/>
-      <c r="T15" s="9"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="9"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="9">
         <v>1012</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
         <v>1</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G16" s="9">
         <v>1</v>
@@ -2351,22 +2417,25 @@
       <c r="O16" s="9"/>
       <c r="P16" s="9"/>
       <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="9"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="9">
         <v>1013</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
         <v>1</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G17" s="9">
         <v>1</v>
@@ -2395,22 +2464,25 @@
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="9"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9">
         <v>1014</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9">
         <v>1</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
@@ -2441,22 +2513,25 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
-      <c r="T18" s="9"/>
-    </row>
-    <row r="19" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T18" s="1">
+        <v>0</v>
+      </c>
+      <c r="U18" s="9"/>
+    </row>
+    <row r="19" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11">
         <v>2001</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11">
         <v>2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G19" s="9">
         <v>1</v>
@@ -2483,34 +2558,37 @@
         <v>1</v>
       </c>
       <c r="O19" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P19" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R19" s="11"/>
       <c r="S19" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="T19" s="11"/>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="T19" s="11">
+        <v>1</v>
+      </c>
+      <c r="U19" s="11"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9">
         <v>2002</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9">
         <v>2</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G20" s="9">
         <v>1</v>
@@ -2539,30 +2617,33 @@
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R20" s="9"/>
       <c r="S20" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="T20" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="T20" s="9">
+        <v>1</v>
+      </c>
+      <c r="U20" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9">
         <v>2003</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9">
         <v>2</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G21" s="9">
         <v>1</v>
@@ -2591,30 +2672,33 @@
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R21" s="9"/>
       <c r="S21" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="T21" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+      <c r="T21" s="9">
+        <v>1</v>
+      </c>
+      <c r="U21" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9">
         <v>2004</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9">
         <v>2</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G22" s="9">
         <v>1</v>
@@ -2641,36 +2725,39 @@
         <v>1</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R22" s="9"/>
       <c r="S22" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="T22" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+      <c r="T22" s="9">
+        <v>1</v>
+      </c>
+      <c r="U22" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9">
         <v>2005</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9">
         <v>2</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G23" s="9">
         <v>1</v>
@@ -2699,30 +2786,33 @@
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R23" s="9"/>
       <c r="S23" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="T23" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="T23" s="9">
+        <v>1</v>
+      </c>
+      <c r="U23" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9">
         <v>2006</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9">
         <v>2</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G24" s="9">
         <v>1</v>
@@ -2751,30 +2841,33 @@
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R24" s="9"/>
       <c r="S24" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="T24" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="T24" s="9">
+        <v>1</v>
+      </c>
+      <c r="U24" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9">
         <v>2007</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9">
         <v>2</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G25" s="9">
         <v>1</v>
@@ -2803,30 +2896,33 @@
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R25" s="9"/>
       <c r="S25" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="T25" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="T25" s="9">
+        <v>1</v>
+      </c>
+      <c r="U25" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9">
         <v>2008</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9">
         <v>2</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G26" s="9">
         <v>1</v>
@@ -2855,30 +2951,33 @@
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R26" s="9"/>
       <c r="S26" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="T26" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="T26" s="9">
+        <v>1</v>
+      </c>
+      <c r="U26" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9">
         <v>2009</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9">
         <v>2</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G27" s="9">
         <v>1</v>
@@ -2907,30 +3006,33 @@
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R27" s="9"/>
       <c r="S27" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="T27" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="T27" s="9">
+        <v>1</v>
+      </c>
+      <c r="U27" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9">
         <v>2010</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9">
         <v>2</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G28" s="9">
         <v>1</v>
@@ -2959,30 +3061,33 @@
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R28" s="9"/>
       <c r="S28" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="T28" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="T28" s="9">
+        <v>1</v>
+      </c>
+      <c r="U28" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9">
         <v>2011</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9">
         <v>2</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G29" s="9">
         <v>1</v>
@@ -3011,30 +3116,33 @@
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R29" s="9"/>
       <c r="S29" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="T29" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="T29" s="9">
+        <v>1</v>
+      </c>
+      <c r="U29" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9">
         <v>2012</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9">
         <v>2</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G30" s="9">
         <v>1</v>
@@ -3063,30 +3171,33 @@
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R30" s="9"/>
       <c r="S30" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="T30" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="T30" s="9">
+        <v>1</v>
+      </c>
+      <c r="U30" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9">
         <v>2013</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9">
         <v>2</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G31" s="9">
         <v>1</v>
@@ -3115,30 +3226,33 @@
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="T31" s="9" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T31" s="9">
+        <v>1</v>
+      </c>
+      <c r="U31" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9">
         <v>2014</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9">
         <v>2</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G32" s="9">
         <v>1</v>
@@ -3167,30 +3281,33 @@
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R32" s="9"/>
       <c r="S32" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="T32" s="9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+      <c r="T32" s="9">
+        <v>1</v>
+      </c>
+      <c r="U32" s="9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9">
         <v>2015</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9">
         <v>2</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G33" s="9">
         <v>1</v>
@@ -3217,36 +3334,39 @@
         <v>1</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R33" s="9"/>
       <c r="S33" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="T33" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="T33" s="9">
+        <v>1</v>
+      </c>
+      <c r="U33" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9">
         <v>2016</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9">
         <v>2</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G34" s="9">
         <v>1</v>
@@ -3275,30 +3395,33 @@
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R34" s="9"/>
       <c r="S34" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="T34" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="T34" s="9">
+        <v>1</v>
+      </c>
+      <c r="U34" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
       <c r="B35" s="11">
         <v>3001</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11">
         <v>3</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G35" s="11">
         <v>4</v>
@@ -3327,26 +3450,29 @@
       <c r="O35" s="11"/>
       <c r="P35" s="11"/>
       <c r="Q35" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R35" s="11"/>
       <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T35" s="9">
+        <v>1</v>
+      </c>
+      <c r="U35" s="11"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9">
         <v>3002</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9">
         <v>3</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G36" s="9">
         <v>4</v>
@@ -3375,26 +3501,29 @@
       <c r="O36" s="9"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T36" s="9">
+        <v>1</v>
+      </c>
+      <c r="U36" s="9"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9">
         <v>3003</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9">
         <v>3</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G37" s="9">
         <v>4</v>
@@ -3423,26 +3552,29 @@
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
-      <c r="T37" s="9"/>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T37" s="9">
+        <v>1</v>
+      </c>
+      <c r="U37" s="9"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9">
         <v>3004</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9">
         <v>3</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G38" s="9">
         <v>4</v>
@@ -3471,26 +3603,29 @@
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
-      <c r="T38" s="9"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T38" s="9">
+        <v>1</v>
+      </c>
+      <c r="U38" s="9"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9">
         <v>3005</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9">
         <v>3</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G39" s="9">
         <v>4</v>
@@ -3519,26 +3654,29 @@
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
-      <c r="T39" s="9"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T39" s="9">
+        <v>1</v>
+      </c>
+      <c r="U39" s="9"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9">
         <v>3006</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9">
         <v>3</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G40" s="9">
         <v>4</v>
@@ -3567,26 +3705,29 @@
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
-      <c r="T40" s="9"/>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T40" s="9">
+        <v>1</v>
+      </c>
+      <c r="U40" s="9"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9">
         <v>3007</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9">
         <v>3</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G41" s="9">
         <v>4</v>
@@ -3615,26 +3756,29 @@
       <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
-      <c r="T41" s="9"/>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T41" s="9">
+        <v>1</v>
+      </c>
+      <c r="U41" s="9"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9">
         <v>3008</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9">
         <v>3</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G42" s="9">
         <v>4</v>
@@ -3663,26 +3807,29 @@
       <c r="O42" s="9"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
-      <c r="T42" s="9"/>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T42" s="9">
+        <v>1</v>
+      </c>
+      <c r="U42" s="9"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9">
         <v>3009</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9">
         <v>3</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G43" s="9">
         <v>4</v>
@@ -3711,26 +3858,29 @@
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R43" s="9"/>
       <c r="S43" s="9"/>
-      <c r="T43" s="9"/>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T43" s="9">
+        <v>1</v>
+      </c>
+      <c r="U43" s="9"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9">
         <v>3010</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9">
         <v>3</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G44" s="9">
         <v>4</v>
@@ -3759,26 +3909,29 @@
       <c r="O44" s="9"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R44" s="9"/>
       <c r="S44" s="9"/>
-      <c r="T44" s="9"/>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T44" s="9">
+        <v>1</v>
+      </c>
+      <c r="U44" s="9"/>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9">
         <v>3011</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9">
         <v>3</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G45" s="9">
         <v>4</v>
@@ -3807,26 +3960,29 @@
       <c r="O45" s="9"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T45" s="9">
+        <v>1</v>
+      </c>
+      <c r="U45" s="9"/>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9">
         <v>3012</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="9">
         <v>3</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G46" s="9">
         <v>4</v>
@@ -3855,26 +4011,29 @@
       <c r="O46" s="9"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
-      <c r="T46" s="9"/>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T46" s="9">
+        <v>1</v>
+      </c>
+      <c r="U46" s="9"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="9">
         <v>3013</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9">
         <v>3</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G47" s="9">
         <v>4</v>
@@ -3903,26 +4062,29 @@
       <c r="O47" s="9"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
-      <c r="T47" s="9"/>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T47" s="9">
+        <v>1</v>
+      </c>
+      <c r="U47" s="9"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="9">
         <v>3014</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9">
         <v>3</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G48" s="9">
         <v>4</v>
@@ -3951,26 +4113,29 @@
       <c r="O48" s="9"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R48" s="9"/>
       <c r="S48" s="9"/>
-      <c r="T48" s="9"/>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T48" s="9">
+        <v>1</v>
+      </c>
+      <c r="U48" s="9"/>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="9">
         <v>3015</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="9">
         <v>3</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G49" s="9">
         <v>4</v>
@@ -3999,26 +4164,29 @@
       <c r="O49" s="9"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R49" s="9"/>
       <c r="S49" s="9"/>
-      <c r="T49" s="9"/>
-    </row>
-    <row r="50" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T49" s="9">
+        <v>1</v>
+      </c>
+      <c r="U49" s="9"/>
+    </row>
+    <row r="50" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11"/>
       <c r="B50" s="11">
         <v>4001</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11">
         <v>4</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G50" s="11">
         <v>0.5</v>
@@ -4047,26 +4215,29 @@
       <c r="O50" s="11"/>
       <c r="P50" s="11"/>
       <c r="Q50" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R50" s="11"/>
       <c r="S50" s="11"/>
-      <c r="T50" s="11"/>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T50" s="9">
+        <v>1</v>
+      </c>
+      <c r="U50" s="11"/>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="9">
         <v>4002</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9">
         <v>4</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G51" s="9">
         <v>0.5</v>
@@ -4095,26 +4266,29 @@
       <c r="O51" s="9"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
-      <c r="T51" s="9"/>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T51" s="9">
+        <v>1</v>
+      </c>
+      <c r="U51" s="9"/>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9">
         <v>4003</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="9">
         <v>4</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G52" s="9">
         <v>0.5</v>
@@ -4143,26 +4317,29 @@
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
-      <c r="T52" s="9"/>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T52" s="9">
+        <v>1</v>
+      </c>
+      <c r="U52" s="9"/>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9">
         <v>4004</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="9">
         <v>4</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G53" s="9">
         <v>0.5</v>
@@ -4191,26 +4368,29 @@
       <c r="O53" s="9"/>
       <c r="P53" s="9"/>
       <c r="Q53" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
-      <c r="T53" s="9"/>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T53" s="9">
+        <v>1</v>
+      </c>
+      <c r="U53" s="9"/>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="9">
         <v>4005</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9">
         <v>4</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G54" s="9">
         <v>0.5</v>
@@ -4239,26 +4419,29 @@
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="9"/>
-      <c r="T54" s="9"/>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T54" s="9">
+        <v>1</v>
+      </c>
+      <c r="U54" s="9"/>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="9">
         <v>4006</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9">
         <v>4</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G55" s="9">
         <v>0.5</v>
@@ -4287,26 +4470,29 @@
       <c r="O55" s="9"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R55" s="9"/>
       <c r="S55" s="9"/>
-      <c r="T55" s="9"/>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T55" s="9">
+        <v>1</v>
+      </c>
+      <c r="U55" s="9"/>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="9">
         <v>4007</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="9">
         <v>4</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G56" s="9">
         <v>0.5</v>
@@ -4335,26 +4521,29 @@
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
-      <c r="T56" s="9"/>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T56" s="9">
+        <v>1</v>
+      </c>
+      <c r="U56" s="9"/>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="9">
         <v>4008</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D57" s="9"/>
       <c r="E57" s="9">
         <v>4</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G57" s="9">
         <v>0.5</v>
@@ -4383,26 +4572,29 @@
       <c r="O57" s="9"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R57" s="9"/>
       <c r="S57" s="9"/>
-      <c r="T57" s="9"/>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T57" s="9">
+        <v>1</v>
+      </c>
+      <c r="U57" s="9"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9">
         <v>4009</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="9">
         <v>4</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G58" s="9">
         <v>0.5</v>
@@ -4431,26 +4623,29 @@
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R58" s="9"/>
       <c r="S58" s="9"/>
-      <c r="T58" s="9"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T58" s="9">
+        <v>1</v>
+      </c>
+      <c r="U58" s="9"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9">
         <v>4010</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="9">
         <v>4</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G59" s="9">
         <v>0.5</v>
@@ -4479,26 +4674,29 @@
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
-      <c r="T59" s="9"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T59" s="9">
+        <v>1</v>
+      </c>
+      <c r="U59" s="9"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="9">
         <v>4011</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="9">
         <v>4</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G60" s="9">
         <v>0.5</v>
@@ -4527,26 +4725,29 @@
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
       <c r="Q60" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R60" s="9"/>
       <c r="S60" s="9"/>
-      <c r="T60" s="9"/>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T60" s="9">
+        <v>1</v>
+      </c>
+      <c r="U60" s="9"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="9">
         <v>4012</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="9">
         <v>4</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G61" s="9">
         <v>0.5</v>
@@ -4575,26 +4776,29 @@
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
       <c r="Q61" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R61" s="9"/>
       <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T61" s="9">
+        <v>1</v>
+      </c>
+      <c r="U61" s="9"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9">
         <v>4013</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="9">
         <v>4</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G62" s="9">
         <v>0.5</v>
@@ -4623,26 +4827,29 @@
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R62" s="9"/>
       <c r="S62" s="9"/>
-      <c r="T62" s="9"/>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T62" s="9">
+        <v>1</v>
+      </c>
+      <c r="U62" s="9"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="9">
         <v>4014</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="9">
         <v>4</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G63" s="9">
         <v>0.5</v>
@@ -4671,26 +4878,29 @@
       <c r="O63" s="9"/>
       <c r="P63" s="9"/>
       <c r="Q63" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R63" s="9"/>
       <c r="S63" s="9"/>
-      <c r="T63" s="9"/>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T63" s="9">
+        <v>1</v>
+      </c>
+      <c r="U63" s="9"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="9">
         <v>4015</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="9">
         <v>4</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G64" s="9">
         <v>0.5</v>
@@ -4719,26 +4929,29 @@
       <c r="O64" s="9"/>
       <c r="P64" s="9"/>
       <c r="Q64" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
-      <c r="T64" s="9"/>
-    </row>
-    <row r="65" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T64" s="9">
+        <v>1</v>
+      </c>
+      <c r="U64" s="9"/>
+    </row>
+    <row r="65" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11"/>
       <c r="B65" s="11">
         <v>5001</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="11">
         <v>5</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G65" s="11">
         <v>1</v>
@@ -4767,30 +4980,33 @@
       <c r="O65" s="11"/>
       <c r="P65" s="11"/>
       <c r="Q65" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R65" s="11"/>
       <c r="S65" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="T65" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="T65" s="9">
+        <v>1</v>
+      </c>
+      <c r="U65" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12"/>
       <c r="B66" s="12">
         <v>5002</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="12">
         <v>5</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -4819,26 +5035,29 @@
       <c r="O66" s="12"/>
       <c r="P66" s="12"/>
       <c r="Q66" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R66" s="12"/>
       <c r="S66" s="12"/>
-      <c r="T66" s="12"/>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T66" s="12">
+        <v>0</v>
+      </c>
+      <c r="U66" s="12"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="12">
         <v>5003</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="12">
         <v>5</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G67" s="3">
         <v>1</v>
@@ -4869,22 +5088,25 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T67" s="12">
+        <v>0</v>
+      </c>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="12">
         <v>5004</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D68" s="3"/>
       <c r="E68" s="12">
         <v>5</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G68" s="3">
         <v>1</v>
@@ -4915,22 +5137,25 @@
       <c r="Q68" s="3"/>
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
-      <c r="T68" s="3"/>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T68" s="12">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="12">
         <v>5005</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="12">
         <v>5</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G69" s="3">
         <v>1</v>
@@ -4961,22 +5186,25 @@
       <c r="Q69" s="3"/>
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T69" s="12">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="12">
         <v>5006</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="12">
         <v>5</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G70" s="3">
         <v>1</v>
@@ -5007,22 +5235,25 @@
       <c r="Q70" s="3"/>
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T70" s="12">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="12">
         <v>5007</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="12">
         <v>5</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G71" s="3">
         <v>1</v>
@@ -5053,22 +5284,25 @@
       <c r="Q71" s="3"/>
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
-      <c r="T71" s="3"/>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T71" s="12">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="12">
         <v>5008</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="12">
         <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G72" s="3">
         <v>1</v>
@@ -5099,22 +5333,25 @@
       <c r="Q72" s="3"/>
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
-    </row>
-    <row r="73" spans="1:20" s="13" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T72" s="12">
+        <v>0</v>
+      </c>
+      <c r="U72" s="3"/>
+    </row>
+    <row r="73" spans="1:21" s="13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12"/>
       <c r="B73" s="12">
         <v>5009</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="12">
         <v>5</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G73" s="3">
         <v>1</v>
@@ -5143,26 +5380,29 @@
       <c r="O73" s="12"/>
       <c r="P73" s="12"/>
       <c r="Q73" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R73" s="12"/>
       <c r="S73" s="12"/>
-      <c r="T73" s="12"/>
-    </row>
-    <row r="74" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T73" s="12">
+        <v>1</v>
+      </c>
+      <c r="U73" s="12"/>
+    </row>
+    <row r="74" spans="1:21" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11"/>
       <c r="B74" s="11">
         <v>6001</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11">
         <v>6</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G74" s="16">
         <v>1</v>
@@ -5191,26 +5431,29 @@
       <c r="O74" s="11"/>
       <c r="P74" s="11"/>
       <c r="Q74" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R74" s="11"/>
       <c r="S74" s="11"/>
-      <c r="T74" s="11"/>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T74" s="11">
+        <v>0</v>
+      </c>
+      <c r="U74" s="11"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9">
         <v>6002</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="9">
         <v>6</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G75" s="3">
         <v>1</v>
@@ -5239,26 +5482,29 @@
       <c r="O75" s="9"/>
       <c r="P75" s="9"/>
       <c r="Q75" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="R75" s="9"/>
       <c r="S75" s="9"/>
-      <c r="T75" s="9"/>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T75" s="12">
+        <v>0</v>
+      </c>
+      <c r="U75" s="9"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="9">
         <v>6003</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="9">
         <v>6</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G76" s="3">
         <v>1</v>
@@ -5287,26 +5533,29 @@
       <c r="O76" s="9"/>
       <c r="P76" s="9"/>
       <c r="Q76" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R76" s="9"/>
       <c r="S76" s="9"/>
-      <c r="T76" s="9"/>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T76" s="12">
+        <v>0</v>
+      </c>
+      <c r="U76" s="9"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
       <c r="B77" s="9">
         <v>6004</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="9">
         <v>6</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G77" s="3">
         <v>1</v>
@@ -5335,26 +5584,29 @@
       <c r="O77" s="9"/>
       <c r="P77" s="9"/>
       <c r="Q77" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R77" s="9"/>
       <c r="S77" s="9"/>
-      <c r="T77" s="9"/>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T77" s="12">
+        <v>0</v>
+      </c>
+      <c r="U77" s="9"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
       <c r="B78" s="9">
         <v>6005</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="9">
         <v>6</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G78" s="3">
         <v>1</v>
@@ -5383,26 +5635,29 @@
       <c r="O78" s="9"/>
       <c r="P78" s="9"/>
       <c r="Q78" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R78" s="9"/>
       <c r="S78" s="9"/>
-      <c r="T78" s="9"/>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T78" s="12">
+        <v>0</v>
+      </c>
+      <c r="U78" s="9"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9">
         <v>6006</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="9">
         <v>6</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -5431,26 +5686,29 @@
       <c r="O79" s="9"/>
       <c r="P79" s="9"/>
       <c r="Q79" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R79" s="9"/>
       <c r="S79" s="9"/>
-      <c r="T79" s="9"/>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T79" s="12">
+        <v>0</v>
+      </c>
+      <c r="U79" s="9"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
       <c r="B80" s="9">
         <v>6007</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="9">
         <v>6</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G80" s="3">
         <v>1</v>
@@ -5479,26 +5737,29 @@
       <c r="O80" s="9"/>
       <c r="P80" s="9"/>
       <c r="Q80" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R80" s="9"/>
       <c r="S80" s="9"/>
-      <c r="T80" s="9"/>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T80" s="12">
+        <v>0</v>
+      </c>
+      <c r="U80" s="9"/>
+    </row>
+    <row r="81" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
       <c r="B81" s="9">
         <v>6008</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="9">
         <v>6</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G81" s="3">
         <v>1</v>
@@ -5527,26 +5788,29 @@
       <c r="O81" s="9"/>
       <c r="P81" s="9"/>
       <c r="Q81" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="R81" s="9"/>
       <c r="S81" s="9"/>
-      <c r="T81" s="9"/>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T81" s="12">
+        <v>0</v>
+      </c>
+      <c r="U81" s="9"/>
+    </row>
+    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
       <c r="B82" s="9">
         <v>6009</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="9">
         <v>6</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G82" s="3">
         <v>1</v>
@@ -5575,26 +5839,29 @@
       <c r="O82" s="9"/>
       <c r="P82" s="9"/>
       <c r="Q82" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R82" s="9"/>
       <c r="S82" s="9"/>
-      <c r="T82" s="9"/>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T82" s="12">
+        <v>0</v>
+      </c>
+      <c r="U82" s="9"/>
+    </row>
+    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="9">
         <v>6010</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="9">
         <v>6</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G83" s="3">
         <v>1</v>
@@ -5623,26 +5890,29 @@
       <c r="O83" s="9"/>
       <c r="P83" s="9"/>
       <c r="Q83" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R83" s="9"/>
       <c r="S83" s="9"/>
-      <c r="T83" s="9"/>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T83" s="12">
+        <v>0</v>
+      </c>
+      <c r="U83" s="9"/>
+    </row>
+    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A84" s="9"/>
       <c r="B84" s="9">
         <v>6011</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9">
         <v>6</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G84" s="3">
         <v>1</v>
@@ -5671,26 +5941,29 @@
       <c r="O84" s="9"/>
       <c r="P84" s="9"/>
       <c r="Q84" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R84" s="9"/>
       <c r="S84" s="9"/>
-      <c r="T84" s="9"/>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T84" s="12">
+        <v>0</v>
+      </c>
+      <c r="U84" s="9"/>
+    </row>
+    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
       <c r="B85" s="9">
         <v>6012</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="9">
         <v>6</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G85" s="3">
         <v>1</v>
@@ -5719,26 +5992,29 @@
       <c r="O85" s="9"/>
       <c r="P85" s="9"/>
       <c r="Q85" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R85" s="9"/>
       <c r="S85" s="9"/>
-      <c r="T85" s="9"/>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T85" s="12">
+        <v>0</v>
+      </c>
+      <c r="U85" s="9"/>
+    </row>
+    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A86" s="9"/>
       <c r="B86" s="9">
         <v>6013</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="9">
         <v>6</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G86" s="3">
         <v>1</v>
@@ -5767,26 +6043,29 @@
       <c r="O86" s="9"/>
       <c r="P86" s="9"/>
       <c r="Q86" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R86" s="9"/>
       <c r="S86" s="9"/>
-      <c r="T86" s="9"/>
-    </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T86" s="12">
+        <v>0</v>
+      </c>
+      <c r="U86" s="9"/>
+    </row>
+    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
       <c r="B87" s="9">
         <v>6014</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="9">
         <v>6</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G87" s="3">
         <v>1</v>
@@ -5815,26 +6094,29 @@
       <c r="O87" s="9"/>
       <c r="P87" s="9"/>
       <c r="Q87" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="R87" s="9"/>
       <c r="S87" s="9"/>
-      <c r="T87" s="9"/>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T87" s="12">
+        <v>0</v>
+      </c>
+      <c r="U87" s="9"/>
+    </row>
+    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A88" s="9"/>
       <c r="B88" s="9">
         <v>6015</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="9">
         <v>6</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G88" s="3">
         <v>1</v>
@@ -5863,26 +6145,29 @@
       <c r="O88" s="9"/>
       <c r="P88" s="9"/>
       <c r="Q88" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R88" s="9"/>
       <c r="S88" s="9"/>
-      <c r="T88" s="9"/>
-    </row>
-    <row r="89" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T88" s="12">
+        <v>0</v>
+      </c>
+      <c r="U88" s="9"/>
+    </row>
+    <row r="89" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="16"/>
       <c r="B89" s="16">
         <v>7001</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D89" s="16"/>
       <c r="E89" s="16">
         <v>7</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G89" s="16">
         <v>1</v>
@@ -5913,27 +6198,30 @@
       <c r="Q89" s="16"/>
       <c r="R89" s="16"/>
       <c r="S89" s="16"/>
-      <c r="T89" s="16"/>
-      <c r="U89" s="17"/>
+      <c r="T89" s="12">
+        <v>0</v>
+      </c>
+      <c r="U89" s="16"/>
       <c r="V89" s="17"/>
       <c r="W89" s="17"/>
       <c r="X89" s="17"/>
       <c r="Y89" s="17"/>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z89" s="17"/>
+    </row>
+    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3">
         <v>7002</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="3">
         <v>7</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G90" s="3">
         <v>1</v>
@@ -5964,22 +6252,25 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-      <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T90" s="12">
+        <v>0</v>
+      </c>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3">
         <v>7003</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="3">
         <v>7</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G91" s="3">
         <v>1</v>
@@ -6010,22 +6301,25 @@
       <c r="Q91" s="3"/>
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
-      <c r="T91" s="3"/>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T91" s="12">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3"/>
+    </row>
+    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3">
         <v>7004</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3">
         <v>7</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G92" s="3">
         <v>1</v>
@@ -6056,22 +6350,25 @@
       <c r="Q92" s="3"/>
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
-      <c r="T92" s="3"/>
-    </row>
-    <row r="93" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="T92" s="12">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3"/>
+    </row>
+    <row r="93" spans="1:26" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="16"/>
       <c r="B93" s="16">
         <v>8001</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D93" s="16"/>
       <c r="E93" s="16">
         <v>8</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G93" s="3">
         <v>1</v>
@@ -6102,27 +6399,30 @@
       <c r="Q93" s="16"/>
       <c r="R93" s="16"/>
       <c r="S93" s="16"/>
-      <c r="T93" s="16"/>
-      <c r="U93" s="17"/>
+      <c r="T93" s="12">
+        <v>0</v>
+      </c>
+      <c r="U93" s="16"/>
       <c r="V93" s="17"/>
       <c r="W93" s="17"/>
       <c r="X93" s="17"/>
       <c r="Y93" s="17"/>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="Z93" s="17"/>
+    </row>
+    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3">
         <v>8002</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3">
         <v>8</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G94" s="3">
         <v>1</v>
@@ -6153,22 +6453,25 @@
       <c r="Q94" s="3"/>
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
-      <c r="T94" s="3"/>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T94" s="12">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3"/>
+    </row>
+    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3">
         <v>8003</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3">
         <v>8</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G95" s="3">
         <v>1</v>
@@ -6199,22 +6502,25 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-      <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="T95" s="12">
+        <v>0</v>
+      </c>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3">
         <v>8004</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3">
         <v>8</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G96" s="3">
         <v>1</v>
@@ -6245,22 +6551,25 @@
       <c r="Q96" s="3"/>
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
-      <c r="T96" s="3"/>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T96" s="12">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3"/>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3">
         <v>8005</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3">
         <v>8</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G97" s="3">
         <v>1</v>
@@ -6291,22 +6600,25 @@
       <c r="Q97" s="3"/>
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
-      <c r="T97" s="3"/>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T97" s="12">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3">
         <v>8006</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3">
         <v>8</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G98" s="3">
         <v>1</v>
@@ -6337,22 +6649,25 @@
       <c r="Q98" s="3"/>
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
-      <c r="T98" s="3"/>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T98" s="12">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3">
         <v>8007</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3">
         <v>8</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G99" s="3">
         <v>1</v>
@@ -6383,22 +6698,25 @@
       <c r="Q99" s="3"/>
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
-      <c r="T99" s="3"/>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T99" s="12">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3">
         <v>8008</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3">
         <v>8</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G100" s="3">
         <v>1</v>
@@ -6429,22 +6747,25 @@
       <c r="Q100" s="3"/>
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
-      <c r="T100" s="3"/>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T100" s="12">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3">
         <v>8009</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3">
         <v>8</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G101" s="3">
         <v>1</v>
@@ -6475,22 +6796,25 @@
       <c r="Q101" s="3"/>
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
-      <c r="T101" s="3"/>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T101" s="12">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3">
         <v>8010</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="3">
         <v>8</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G102" s="3">
         <v>1</v>
@@ -6521,22 +6845,25 @@
       <c r="Q102" s="3"/>
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
-      <c r="T102" s="3"/>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T102" s="12">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3">
         <v>8011</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="3">
         <v>8</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G103" s="3">
         <v>1</v>
@@ -6567,22 +6894,25 @@
       <c r="Q103" s="3"/>
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
-      <c r="T103" s="3"/>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T103" s="12">
+        <v>0</v>
+      </c>
+      <c r="U103" s="3"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3">
         <v>8012</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3">
         <v>8</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G104" s="3">
         <v>1</v>
@@ -6613,22 +6943,25 @@
       <c r="Q104" s="3"/>
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
-      <c r="T104" s="3"/>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T104" s="12">
+        <v>0</v>
+      </c>
+      <c r="U104" s="3"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3">
         <v>8013</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="3">
         <v>8</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G105" s="3">
         <v>1</v>
@@ -6659,22 +6992,25 @@
       <c r="Q105" s="3"/>
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
-      <c r="T105" s="3"/>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T105" s="12">
+        <v>0</v>
+      </c>
+      <c r="U105" s="3"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3">
         <v>8014</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3">
         <v>8</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G106" s="3">
         <v>1</v>
@@ -6705,9 +7041,12 @@
       <c r="Q106" s="3"/>
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
-      <c r="T106" s="3"/>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="T106" s="12">
+        <v>0</v>
+      </c>
+      <c r="U106" s="3"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="7"/>
@@ -6726,8 +7065,9 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U107" s="3"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="7"/>
@@ -6746,8 +7086,9 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U108" s="3"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="7"/>
@@ -6766,8 +7107,9 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U109" s="3"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="7"/>
@@ -6786,8 +7128,9 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U110" s="3"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="7"/>
@@ -6806,8 +7149,9 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U111" s="3"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="7"/>
@@ -6826,8 +7170,9 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U112" s="3"/>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="7"/>
@@ -6846,8 +7191,9 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U113" s="3"/>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="7"/>
@@ -6866,8 +7212,9 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U114" s="3"/>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="7"/>
@@ -6886,8 +7233,9 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U115" s="3"/>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="7"/>
@@ -6906,8 +7254,9 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U116" s="3"/>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="7"/>
@@ -6926,8 +7275,9 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U117" s="3"/>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="7"/>
@@ -6946,8 +7296,9 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U118" s="3"/>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="7"/>
@@ -6966,8 +7317,9 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U119" s="3"/>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="7"/>
@@ -6986,8 +7338,9 @@
       <c r="R120" s="3"/>
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U120" s="3"/>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="7"/>
@@ -7006,8 +7359,9 @@
       <c r="R121" s="3"/>
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U121" s="3"/>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="7"/>
@@ -7026,8 +7380,9 @@
       <c r="R122" s="3"/>
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U122" s="3"/>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="7"/>
@@ -7046,8 +7401,9 @@
       <c r="R123" s="3"/>
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U123" s="3"/>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="7"/>
@@ -7066,8 +7422,9 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U124" s="3"/>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="7"/>
@@ -7086,8 +7443,9 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U125" s="3"/>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="7"/>
@@ -7106,8 +7464,9 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U126" s="3"/>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="7"/>
@@ -7126,8 +7485,9 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U127" s="3"/>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="7"/>
@@ -7146,8 +7506,9 @@
       <c r="R128" s="3"/>
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U128" s="3"/>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="7"/>
@@ -7166,8 +7527,9 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U129" s="3"/>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="7"/>
@@ -7186,8 +7548,9 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U130" s="3"/>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="7"/>
@@ -7206,8 +7569,9 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U131" s="3"/>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="7"/>
@@ -7226,8 +7590,9 @@
       <c r="R132" s="3"/>
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U132" s="3"/>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="7"/>
@@ -7246,8 +7611,9 @@
       <c r="R133" s="3"/>
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U133" s="3"/>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="7"/>
@@ -7266,8 +7632,9 @@
       <c r="R134" s="3"/>
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U134" s="3"/>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="7"/>
@@ -7286,8 +7653,9 @@
       <c r="R135" s="3"/>
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U135" s="3"/>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="7"/>
@@ -7306,8 +7674,9 @@
       <c r="R136" s="3"/>
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U136" s="3"/>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="7"/>
@@ -7326,8 +7695,9 @@
       <c r="R137" s="3"/>
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U137" s="3"/>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="7"/>
@@ -7346,8 +7716,9 @@
       <c r="R138" s="3"/>
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U138" s="3"/>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="7"/>
@@ -7366,8 +7737,9 @@
       <c r="R139" s="3"/>
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U139" s="3"/>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="7"/>
@@ -7386,8 +7758,9 @@
       <c r="R140" s="3"/>
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U140" s="3"/>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="7"/>
@@ -7406,8 +7779,9 @@
       <c r="R141" s="3"/>
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U141" s="3"/>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="7"/>
@@ -7426,8 +7800,9 @@
       <c r="R142" s="3"/>
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
-    </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U142" s="3"/>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="7"/>
@@ -7446,8 +7821,9 @@
       <c r="R143" s="3"/>
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
-    </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U143" s="3"/>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="7"/>
@@ -7466,8 +7842,9 @@
       <c r="R144" s="3"/>
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
-    </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U144" s="3"/>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="7"/>
@@ -7486,8 +7863,9 @@
       <c r="R145" s="3"/>
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
-    </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U145" s="3"/>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="7"/>
@@ -7506,8 +7884,9 @@
       <c r="R146" s="3"/>
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
-    </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U146" s="3"/>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="7"/>
@@ -7526,8 +7905,9 @@
       <c r="R147" s="3"/>
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
-    </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U147" s="3"/>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="7"/>
@@ -7546,8 +7926,9 @@
       <c r="R148" s="3"/>
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
-    </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U148" s="3"/>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="7"/>
@@ -7566,8 +7947,9 @@
       <c r="R149" s="3"/>
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
-    </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U149" s="3"/>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="7"/>
@@ -7586,8 +7968,9 @@
       <c r="R150" s="3"/>
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
-    </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U150" s="3"/>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="7"/>
@@ -7606,8 +7989,9 @@
       <c r="R151" s="3"/>
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
-    </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U151" s="3"/>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="7"/>
@@ -7626,8 +8010,9 @@
       <c r="R152" s="3"/>
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
-    </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U152" s="3"/>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="7"/>
@@ -7646,8 +8031,9 @@
       <c r="R153" s="3"/>
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
-    </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U153" s="3"/>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="7"/>
@@ -7666,8 +8052,9 @@
       <c r="R154" s="3"/>
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
-    </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U154" s="3"/>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="7"/>
@@ -7686,8 +8073,9 @@
       <c r="R155" s="3"/>
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
-    </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U155" s="3"/>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="7"/>
@@ -7706,8 +8094,9 @@
       <c r="R156" s="3"/>
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
-    </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U156" s="3"/>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="7"/>
@@ -7726,8 +8115,9 @@
       <c r="R157" s="3"/>
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
-    </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U157" s="3"/>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="7"/>
@@ -7746,8 +8136,9 @@
       <c r="R158" s="3"/>
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
-    </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U158" s="3"/>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="7"/>
@@ -7766,8 +8157,9 @@
       <c r="R159" s="3"/>
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
-    </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U159" s="3"/>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="7"/>
@@ -7786,8 +8178,9 @@
       <c r="R160" s="3"/>
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
-    </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U160" s="3"/>
+    </row>
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="7"/>
@@ -7806,8 +8199,9 @@
       <c r="R161" s="3"/>
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
-    </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U161" s="3"/>
+    </row>
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="7"/>
@@ -7826,8 +8220,9 @@
       <c r="R162" s="3"/>
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
-    </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U162" s="3"/>
+    </row>
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="7"/>
@@ -7846,8 +8241,9 @@
       <c r="R163" s="3"/>
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
-    </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U163" s="3"/>
+    </row>
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="7"/>
@@ -7866,8 +8262,9 @@
       <c r="R164" s="3"/>
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
-    </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U164" s="3"/>
+    </row>
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="7"/>
@@ -7886,8 +8283,9 @@
       <c r="R165" s="3"/>
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
-    </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U165" s="3"/>
+    </row>
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="7"/>
@@ -7906,8 +8304,9 @@
       <c r="R166" s="3"/>
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
-    </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U166" s="3"/>
+    </row>
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="7"/>
@@ -7926,8 +8325,9 @@
       <c r="R167" s="3"/>
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
-    </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U167" s="3"/>
+    </row>
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="7"/>
@@ -7946,8 +8346,9 @@
       <c r="R168" s="3"/>
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
-    </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U168" s="3"/>
+    </row>
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="7"/>
@@ -7966,8 +8367,9 @@
       <c r="R169" s="3"/>
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
-    </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U169" s="3"/>
+    </row>
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="7"/>
@@ -7986,8 +8388,9 @@
       <c r="R170" s="3"/>
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
-    </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U170" s="3"/>
+    </row>
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="7"/>
@@ -8006,8 +8409,9 @@
       <c r="R171" s="3"/>
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
-    </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U171" s="3"/>
+    </row>
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="7"/>
@@ -8026,8 +8430,9 @@
       <c r="R172" s="3"/>
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
-    </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U172" s="3"/>
+    </row>
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="7"/>
@@ -8046,8 +8451,9 @@
       <c r="R173" s="3"/>
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
-    </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U173" s="3"/>
+    </row>
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="7"/>
@@ -8066,8 +8472,9 @@
       <c r="R174" s="3"/>
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
-    </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U174" s="3"/>
+    </row>
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="7"/>
@@ -8086,8 +8493,9 @@
       <c r="R175" s="3"/>
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
-    </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U175" s="3"/>
+    </row>
+    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="7"/>
@@ -8106,8 +8514,9 @@
       <c r="R176" s="3"/>
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
-    </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U176" s="3"/>
+    </row>
+    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="7"/>
@@ -8126,8 +8535,9 @@
       <c r="R177" s="3"/>
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
-    </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U177" s="3"/>
+    </row>
+    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="7"/>
@@ -8146,8 +8556,9 @@
       <c r="R178" s="3"/>
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
-    </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U178" s="3"/>
+    </row>
+    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="7"/>
@@ -8166,8 +8577,9 @@
       <c r="R179" s="3"/>
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
-    </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U179" s="3"/>
+    </row>
+    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="7"/>
@@ -8186,8 +8598,9 @@
       <c r="R180" s="3"/>
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
-    </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U180" s="3"/>
+    </row>
+    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="7"/>
@@ -8206,8 +8619,9 @@
       <c r="R181" s="3"/>
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
-    </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U181" s="3"/>
+    </row>
+    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="7"/>
@@ -8226,8 +8640,9 @@
       <c r="R182" s="3"/>
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
-    </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U182" s="3"/>
+    </row>
+    <row r="183" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="7"/>
@@ -8246,8 +8661,9 @@
       <c r="R183" s="3"/>
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
-    </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U183" s="3"/>
+    </row>
+    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="7"/>
@@ -8266,8 +8682,9 @@
       <c r="R184" s="3"/>
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
-    </row>
-    <row r="185" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U184" s="3"/>
+    </row>
+    <row r="185" spans="1:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="7"/>
@@ -8286,8 +8703,9 @@
       <c r="R185" s="3"/>
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
-    </row>
-    <row r="186" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="U185" s="3"/>
+    </row>
+    <row r="186" spans="1:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
@@ -8304,7 +8722,7 @@
       <c r="Q186" s="8"/>
       <c r="R186" s="8"/>
     </row>
-    <row r="187" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
@@ -8321,7 +8739,7 @@
       <c r="Q187" s="8"/>
       <c r="R187" s="8"/>
     </row>
-    <row r="188" spans="1:20" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="8"/>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
@@ -8339,7 +8757,6 @@
       <c r="R188" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8358,19 +8775,19 @@
   <sheetData>
     <row r="19" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
+        <v>207</v>
+      </c>
+      <c r="M19" t="s">
         <v>208</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>209</v>
       </c>
-      <c r="N19" t="s">
+      <c r="P19" t="s">
         <v>210</v>
       </c>
-      <c r="P19" t="s">
+      <c r="R19" t="s">
         <v>211</v>
-      </c>
-      <c r="R19" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="20" spans="12:18" x14ac:dyDescent="0.3">
@@ -8378,16 +8795,16 @@
         <v>5001</v>
       </c>
       <c r="M20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -8402,16 +8819,16 @@
         <v>5002</v>
       </c>
       <c r="M21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P21" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -8426,16 +8843,16 @@
         <v>5003</v>
       </c>
       <c r="M22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P22" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -8450,16 +8867,16 @@
         <v>5004</v>
       </c>
       <c r="M23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -8474,16 +8891,16 @@
         <v>5005</v>
       </c>
       <c r="M24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -8498,16 +8915,16 @@
         <v>5006</v>
       </c>
       <c r="M25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P25" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -8522,16 +8939,16 @@
         <v>5007</v>
       </c>
       <c r="M26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -8546,16 +8963,16 @@
         <v>5008</v>
       </c>
       <c r="M27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P27" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -8570,16 +8987,16 @@
         <v>5009</v>
       </c>
       <c r="M28" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28" t="s">
+        <v>244</v>
+      </c>
+      <c r="P28" t="s">
         <v>245</v>
-      </c>
-      <c r="P28" t="s">
-        <v>246</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -8594,13 +9011,13 @@
         <v>6001</v>
       </c>
       <c r="M29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O29" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P29" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -8615,13 +9032,13 @@
         <v>6002</v>
       </c>
       <c r="M30" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O30" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P30" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -8636,13 +9053,13 @@
         <v>6003</v>
       </c>
       <c r="M31" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O31" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -8657,13 +9074,13 @@
         <v>6004</v>
       </c>
       <c r="M32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O32" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P32" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -8678,13 +9095,13 @@
         <v>6005</v>
       </c>
       <c r="M33" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="O33" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -8699,13 +9116,13 @@
         <v>6006</v>
       </c>
       <c r="M34" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O34" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -8720,13 +9137,13 @@
         <v>6007</v>
       </c>
       <c r="M35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O35" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -8741,13 +9158,13 @@
         <v>6008</v>
       </c>
       <c r="M36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O36" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -8762,13 +9179,13 @@
         <v>6009</v>
       </c>
       <c r="M37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O37" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -8783,13 +9200,13 @@
         <v>6010</v>
       </c>
       <c r="M38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O38" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -8804,13 +9221,13 @@
         <v>6011</v>
       </c>
       <c r="M39" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O39" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -8825,13 +9242,13 @@
         <v>6012</v>
       </c>
       <c r="M40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O40" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -8846,13 +9263,13 @@
         <v>6013</v>
       </c>
       <c r="M41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="O41" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -8867,13 +9284,13 @@
         <v>6014</v>
       </c>
       <c r="M42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="O42" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -8888,13 +9305,13 @@
         <v>6015</v>
       </c>
       <c r="M43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O43" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P43" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -8909,16 +9326,16 @@
         <v>7001</v>
       </c>
       <c r="M44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N44">
         <v>7</v>
       </c>
       <c r="O44" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P44" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -8933,16 +9350,16 @@
         <v>7002</v>
       </c>
       <c r="M45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
       <c r="O45" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -8957,16 +9374,16 @@
         <v>7003</v>
       </c>
       <c r="M46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P46" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -8981,16 +9398,16 @@
         <v>7004</v>
       </c>
       <c r="M47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -9005,16 +9422,16 @@
         <v>8001</v>
       </c>
       <c r="M48" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
       <c r="O48" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P48" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -9029,16 +9446,16 @@
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P49" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -9053,16 +9470,16 @@
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P50" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -9077,16 +9494,16 @@
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P51" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -9101,16 +9518,16 @@
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P52" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -9125,16 +9542,16 @@
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P53" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -9149,16 +9566,16 @@
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P54" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -9173,16 +9590,16 @@
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P55" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -9197,16 +9614,16 @@
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P56" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -9221,16 +9638,16 @@
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P57" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -9245,16 +9662,16 @@
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P58" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -9269,16 +9686,16 @@
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P59" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -9293,16 +9710,16 @@
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P60" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -9317,16 +9734,16 @@
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="P61" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E0DEAA-CFA0-415B-A92C-E3A11F4FA272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="279">
   <si>
     <t>##var</t>
   </si>
@@ -222,9 +228,6 @@
     <t>土豆-种子袋</t>
   </si>
   <si>
-    <t>plant/sack</t>
-  </si>
-  <si>
     <t>蘑菇-种子袋</t>
   </si>
   <si>
@@ -696,9 +699,6 @@
     <t>土豆-幼苗</t>
   </si>
   <si>
-    <t>Seedling/seedling</t>
-  </si>
-  <si>
     <t>蘑菇-幼苗</t>
   </si>
   <si>
@@ -829,19 +829,72 @@
   </si>
   <si>
     <t>seedling</t>
+  </si>
+  <si>
+    <t>是否会被爆米花机吃</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否会被隐藏门吃</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否会被湖神吃</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0可以被吞下 1不可以被吞下</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0可以被隐藏门吃 1不可以被隐藏门吃</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0可以被湖神吃 1不可以被湖神吃</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_popcorn</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_hidden_door</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>if_lake</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/mihoutao</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/mushroom_002</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/PotatoModel</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/seedbag</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Seedling</t>
+  </si>
+  <si>
+    <t>plant/Seedling</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -888,151 +941,45 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1057,194 +1004,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1344,251 +1105,20 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FFDEE0E3"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1643,62 +1173,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1956,31 +1454,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA188"/>
-  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.1666666666667" style="4"/>
-    <col min="3" max="3" width="22.8333333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.1666666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.8333333333333" style="4" customWidth="1"/>
+    <col min="1" max="2" width="12.1640625" style="4"/>
+    <col min="3" max="3" width="22.83203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="4" customWidth="1"/>
     <col min="6" max="6" width="26.5" style="4" customWidth="1"/>
     <col min="7" max="8" width="16.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.0833333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.08203125" style="4" customWidth="1"/>
     <col min="10" max="12" width="16.75" style="4" customWidth="1"/>
-    <col min="13" max="17" width="12.1666666666667" style="4"/>
-    <col min="18" max="19" width="17.9166666666667" style="4" customWidth="1"/>
-    <col min="20" max="21" width="26.3333333333333" style="4" customWidth="1"/>
-    <col min="22" max="22" width="12.1666666666667" style="4"/>
-    <col min="28" max="16384" width="12.1666666666667" style="4"/>
+    <col min="13" max="17" width="12.1640625" style="4"/>
+    <col min="18" max="19" width="17.9140625" style="4" customWidth="1"/>
+    <col min="20" max="21" width="26.33203125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="12.1640625" style="4"/>
+    <col min="28" max="16384" width="12.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2047,8 +1545,17 @@
       <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="X1" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y1" s="21" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
@@ -2083,7 +1590,7 @@
         <v>23</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>23</v>
@@ -2115,8 +1622,17 @@
       <c r="V2" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="W2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>26</v>
       </c>
@@ -2183,8 +1699,17 @@
       <c r="V3" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="W3" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="Y3" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>26</v>
       </c>
@@ -2251,8 +1776,17 @@
       <c r="V4" s="9" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="W4" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="X4" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="Y4" s="20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="9">
         <v>1001</v>
@@ -2264,8 +1798,8 @@
       <c r="E5" s="9">
         <v>1</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>63</v>
+      <c r="F5" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G5" s="9">
         <v>1</v>
@@ -2299,20 +1833,20 @@
       </c>
       <c r="V5" s="9"/>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
       <c r="B6" s="9">
         <v>1002</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>63</v>
+      <c r="F6" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G6" s="9">
         <v>1</v>
@@ -2346,20 +1880,20 @@
       </c>
       <c r="V6" s="9"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="9">
         <v>1003</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7" s="9" t="s">
-        <v>63</v>
+      <c r="F7" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G7" s="9">
         <v>1</v>
@@ -2393,20 +1927,20 @@
       </c>
       <c r="V7" s="9"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="9">
         <v>1004</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9">
         <v>1</v>
       </c>
-      <c r="F8" s="9" t="s">
-        <v>63</v>
+      <c r="F8" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G8" s="9">
         <v>1</v>
@@ -2441,20 +1975,20 @@
       </c>
       <c r="V8" s="9"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="9">
         <v>1005</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9">
         <v>1</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>63</v>
+      <c r="F9" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G9" s="9">
         <v>1</v>
@@ -2489,20 +2023,20 @@
       </c>
       <c r="V9" s="9"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="9">
         <v>1006</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9">
         <v>1</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>63</v>
+      <c r="F10" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G10" s="9">
         <v>1</v>
@@ -2537,20 +2071,20 @@
       </c>
       <c r="V10" s="9"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="9">
         <v>1007</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9">
         <v>1</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>63</v>
+      <c r="F11" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G11" s="9">
         <v>1</v>
@@ -2585,20 +2119,20 @@
       </c>
       <c r="V11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="9">
         <v>1008</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9">
         <v>1</v>
       </c>
-      <c r="F12" s="9" t="s">
-        <v>63</v>
+      <c r="F12" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G12" s="9">
         <v>1</v>
@@ -2633,20 +2167,20 @@
       </c>
       <c r="V12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="9">
         <v>1009</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9">
         <v>1</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>63</v>
+      <c r="F13" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G13" s="9">
         <v>1</v>
@@ -2681,20 +2215,20 @@
       </c>
       <c r="V13" s="9"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="9">
         <v>1010</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9">
         <v>1</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>63</v>
+      <c r="F14" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G14" s="9">
         <v>1</v>
@@ -2729,20 +2263,20 @@
       </c>
       <c r="V14" s="9"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="9">
         <v>1011</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9">
         <v>1</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>63</v>
+      <c r="F15" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G15" s="9">
         <v>1</v>
@@ -2777,20 +2311,20 @@
       </c>
       <c r="V15" s="9"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="9">
         <v>1012</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
         <v>1</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>63</v>
+      <c r="F16" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G16" s="9">
         <v>1</v>
@@ -2825,20 +2359,20 @@
       </c>
       <c r="V16" s="9"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="9">
         <v>1013</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
         <v>1</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>63</v>
+      <c r="F17" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G17" s="9">
         <v>1</v>
@@ -2873,20 +2407,20 @@
       </c>
       <c r="V17" s="9"/>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9">
         <v>1014</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9">
         <v>1</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>63</v>
+      <c r="F18" s="20" t="s">
+        <v>276</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
@@ -2923,20 +2457,20 @@
       </c>
       <c r="V18" s="9"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:22">
+    <row r="19" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11"/>
       <c r="B19" s="11">
         <v>2001</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11">
         <v>2</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>78</v>
+      <c r="F19" s="22" t="s">
+        <v>275</v>
       </c>
       <c r="G19" s="9">
         <v>1</v>
@@ -2966,37 +2500,37 @@
         <v>1</v>
       </c>
       <c r="P19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="R19" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="R19" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="S19" s="11"/>
       <c r="T19" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U19" s="11">
         <v>1</v>
       </c>
       <c r="V19" s="11"/>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9">
         <v>2002</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9">
         <v>2</v>
       </c>
-      <c r="F20" s="9" t="s">
-        <v>78</v>
+      <c r="F20" s="20" t="s">
+        <v>274</v>
       </c>
       <c r="G20" s="9">
         <v>1</v>
@@ -3014,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M20" s="11">
         <v>0</v>
@@ -3028,33 +2562,33 @@
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S20" s="9"/>
       <c r="T20" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="U20" s="9">
+        <v>1</v>
+      </c>
+      <c r="V20" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="U20" s="9">
-        <v>1</v>
-      </c>
-      <c r="V20" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9">
         <v>2003</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9">
         <v>2</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="9">
         <v>1</v>
@@ -3072,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="9">
-        <v>100</v>
+        <v>0.35</v>
       </c>
       <c r="M21" s="11">
         <v>0</v>
@@ -3086,33 +2620,33 @@
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S21" s="9"/>
       <c r="T21" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="U21" s="9">
+        <v>1</v>
+      </c>
+      <c r="V21" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="U21" s="9">
-        <v>1</v>
-      </c>
-      <c r="V21" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9">
         <v>2004</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9">
         <v>2</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G22" s="9">
         <v>1</v>
@@ -3142,39 +2676,39 @@
         <v>1</v>
       </c>
       <c r="P22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="R22" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="Q22" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="R22" s="9" t="s">
-        <v>93</v>
       </c>
       <c r="S22" s="9"/>
       <c r="T22" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="U22" s="9">
+        <v>1</v>
+      </c>
+      <c r="V22" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="U22" s="9">
-        <v>1</v>
-      </c>
-      <c r="V22" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9">
         <v>2005</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9">
         <v>2</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G23" s="9">
         <v>1</v>
@@ -3206,33 +2740,33 @@
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S23" s="9"/>
       <c r="T23" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="U23" s="9">
+        <v>1</v>
+      </c>
+      <c r="V23" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="U23" s="9">
-        <v>1</v>
-      </c>
-      <c r="V23" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9">
         <v>2006</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9">
         <v>2</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G24" s="9">
         <v>1</v>
@@ -3264,33 +2798,33 @@
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S24" s="9"/>
       <c r="T24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U24" s="9">
+        <v>1</v>
+      </c>
+      <c r="V24" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="U24" s="9">
-        <v>1</v>
-      </c>
-      <c r="V24" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9">
         <v>2007</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9">
         <v>2</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G25" s="9">
         <v>1</v>
@@ -3322,33 +2856,33 @@
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S25" s="9"/>
       <c r="T25" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U25" s="9">
+        <v>1</v>
+      </c>
+      <c r="V25" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="U25" s="9">
-        <v>1</v>
-      </c>
-      <c r="V25" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9">
         <v>2008</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9">
         <v>2</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G26" s="9">
         <v>1</v>
@@ -3380,33 +2914,33 @@
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S26" s="9"/>
       <c r="T26" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U26" s="9">
+        <v>1</v>
+      </c>
+      <c r="V26" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="U26" s="9">
-        <v>1</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9">
         <v>2009</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9">
         <v>2</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G27" s="9">
         <v>1</v>
@@ -3438,33 +2972,33 @@
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S27" s="9"/>
       <c r="T27" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U27" s="9">
+        <v>1</v>
+      </c>
+      <c r="V27" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="U27" s="9">
-        <v>1</v>
-      </c>
-      <c r="V27" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9">
         <v>2010</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9">
         <v>2</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G28" s="9">
         <v>1</v>
@@ -3496,33 +3030,33 @@
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S28" s="9"/>
       <c r="T28" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U28" s="9">
+        <v>1</v>
+      </c>
+      <c r="V28" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="U28" s="9">
-        <v>1</v>
-      </c>
-      <c r="V28" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9">
         <v>2011</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9">
         <v>2</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G29" s="9">
         <v>1</v>
@@ -3554,33 +3088,33 @@
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S29" s="9"/>
       <c r="T29" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U29" s="9">
+        <v>1</v>
+      </c>
+      <c r="V29" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="U29" s="9">
-        <v>1</v>
-      </c>
-      <c r="V29" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9">
         <v>2012</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9">
         <v>2</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G30" s="9">
         <v>1</v>
@@ -3612,33 +3146,33 @@
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S30" s="9"/>
       <c r="T30" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="U30" s="9">
+        <v>1</v>
+      </c>
+      <c r="V30" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="U30" s="9">
-        <v>1</v>
-      </c>
-      <c r="V30" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22">
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9">
         <v>2013</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9">
         <v>2</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="9">
         <v>1</v>
@@ -3670,33 +3204,33 @@
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S31" s="9"/>
       <c r="T31" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="U31" s="9">
         <v>1</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9">
         <v>2014</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9">
         <v>2</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G32" s="9">
         <v>1</v>
@@ -3728,33 +3262,33 @@
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S32" s="9"/>
       <c r="T32" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U32" s="9">
         <v>1</v>
       </c>
       <c r="V32" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9">
         <v>2015</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9">
         <v>2</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>119</v>
+      <c r="F33" s="20" t="s">
+        <v>273</v>
       </c>
       <c r="G33" s="9">
         <v>1</v>
@@ -3784,39 +3318,39 @@
         <v>1</v>
       </c>
       <c r="P33" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="R33" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="Q33" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="R33" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="S33" s="9"/>
       <c r="T33" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U33" s="9">
         <v>1</v>
       </c>
       <c r="V33" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9">
         <v>2016</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9">
         <v>2</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G34" s="9">
         <v>1</v>
@@ -3848,33 +3382,33 @@
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S34" s="9"/>
       <c r="T34" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U34" s="9">
         <v>1</v>
       </c>
       <c r="V34" s="9" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" spans="1:22">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
       <c r="B35" s="11">
         <v>3001</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" s="11"/>
       <c r="E35" s="11">
         <v>3</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G35" s="11">
         <v>4</v>
@@ -3904,7 +3438,7 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
       <c r="R35" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S35" s="11"/>
       <c r="T35" s="11"/>
@@ -3913,20 +3447,20 @@
       </c>
       <c r="V35" s="11"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9">
         <v>3002</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9">
         <v>3</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G36" s="9">
         <v>4</v>
@@ -3956,7 +3490,7 @@
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S36" s="9"/>
       <c r="T36" s="9"/>
@@ -3965,20 +3499,20 @@
       </c>
       <c r="V36" s="9"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9">
         <v>3003</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9">
         <v>3</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G37" s="9">
         <v>4</v>
@@ -4008,7 +3542,7 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
@@ -4017,20 +3551,20 @@
       </c>
       <c r="V37" s="9"/>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9">
         <v>3004</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9">
         <v>3</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G38" s="9">
         <v>4</v>
@@ -4060,7 +3594,7 @@
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S38" s="9"/>
       <c r="T38" s="9"/>
@@ -4069,20 +3603,20 @@
       </c>
       <c r="V38" s="9"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9">
         <v>3005</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9">
         <v>3</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G39" s="9">
         <v>4</v>
@@ -4112,7 +3646,7 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
@@ -4121,20 +3655,20 @@
       </c>
       <c r="V39" s="9"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9">
         <v>3006</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9">
         <v>3</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G40" s="9">
         <v>4</v>
@@ -4164,7 +3698,7 @@
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S40" s="9"/>
       <c r="T40" s="9"/>
@@ -4173,20 +3707,20 @@
       </c>
       <c r="V40" s="9"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9">
         <v>3007</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9">
         <v>3</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G41" s="9">
         <v>4</v>
@@ -4216,7 +3750,7 @@
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S41" s="9"/>
       <c r="T41" s="9"/>
@@ -4225,20 +3759,20 @@
       </c>
       <c r="V41" s="9"/>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9">
         <v>3008</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9">
         <v>3</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G42" s="9">
         <v>4</v>
@@ -4268,7 +3802,7 @@
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="R42" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S42" s="9"/>
       <c r="T42" s="9"/>
@@ -4277,20 +3811,20 @@
       </c>
       <c r="V42" s="9"/>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9">
         <v>3009</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9">
         <v>3</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G43" s="9">
         <v>4</v>
@@ -4320,7 +3854,7 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S43" s="9"/>
       <c r="T43" s="9"/>
@@ -4329,20 +3863,20 @@
       </c>
       <c r="V43" s="9"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9">
         <v>3010</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9">
         <v>3</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G44" s="9">
         <v>4</v>
@@ -4372,7 +3906,7 @@
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
       <c r="R44" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S44" s="9"/>
       <c r="T44" s="9"/>
@@ -4381,20 +3915,20 @@
       </c>
       <c r="V44" s="9"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9">
         <v>3011</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9">
         <v>3</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G45" s="9">
         <v>4</v>
@@ -4424,7 +3958,7 @@
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
       <c r="R45" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S45" s="9"/>
       <c r="T45" s="9"/>
@@ -4433,20 +3967,20 @@
       </c>
       <c r="V45" s="9"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9">
         <v>3012</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="9">
         <v>3</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G46" s="9">
         <v>4</v>
@@ -4476,7 +4010,7 @@
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
       <c r="R46" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S46" s="9"/>
       <c r="T46" s="9"/>
@@ -4485,20 +4019,20 @@
       </c>
       <c r="V46" s="9"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="9">
         <v>3013</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9">
         <v>3</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G47" s="9">
         <v>4</v>
@@ -4528,7 +4062,7 @@
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
       <c r="R47" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S47" s="9"/>
       <c r="T47" s="9"/>
@@ -4537,20 +4071,20 @@
       </c>
       <c r="V47" s="9"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="9">
         <v>3014</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9">
         <v>3</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G48" s="9">
         <v>4</v>
@@ -4580,7 +4114,7 @@
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
       <c r="R48" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S48" s="9"/>
       <c r="T48" s="9"/>
@@ -4589,20 +4123,20 @@
       </c>
       <c r="V48" s="9"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="9">
         <v>3015</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="9">
         <v>3</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G49" s="9">
         <v>4</v>
@@ -4632,7 +4166,7 @@
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
       <c r="R49" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S49" s="9"/>
       <c r="T49" s="9"/>
@@ -4641,20 +4175,20 @@
       </c>
       <c r="V49" s="9"/>
     </row>
-    <row r="50" s="2" customFormat="1" spans="1:22">
+    <row r="50" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="11"/>
       <c r="B50" s="11">
         <v>4001</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D50" s="11"/>
       <c r="E50" s="11">
         <v>4</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G50" s="11">
         <v>0.5</v>
@@ -4684,7 +4218,7 @@
       <c r="P50" s="11"/>
       <c r="Q50" s="11"/>
       <c r="R50" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S50" s="11"/>
       <c r="T50" s="11"/>
@@ -4693,20 +4227,20 @@
       </c>
       <c r="V50" s="11"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="9">
         <v>4002</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9">
         <v>4</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G51" s="9">
         <v>0.5</v>
@@ -4736,7 +4270,7 @@
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S51" s="9"/>
       <c r="T51" s="9"/>
@@ -4745,20 +4279,20 @@
       </c>
       <c r="V51" s="9"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9">
         <v>4003</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="9">
         <v>4</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G52" s="9">
         <v>0.5</v>
@@ -4788,7 +4322,7 @@
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
       <c r="R52" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S52" s="9"/>
       <c r="T52" s="9"/>
@@ -4797,20 +4331,20 @@
       </c>
       <c r="V52" s="9"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9">
         <v>4004</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="9">
         <v>4</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G53" s="9">
         <v>0.5</v>
@@ -4840,7 +4374,7 @@
       <c r="P53" s="9"/>
       <c r="Q53" s="9"/>
       <c r="R53" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S53" s="9"/>
       <c r="T53" s="9"/>
@@ -4849,20 +4383,20 @@
       </c>
       <c r="V53" s="9"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="9">
         <v>4005</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9">
         <v>4</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G54" s="9">
         <v>0.5</v>
@@ -4892,7 +4426,7 @@
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
       <c r="R54" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S54" s="9"/>
       <c r="T54" s="9"/>
@@ -4901,20 +4435,20 @@
       </c>
       <c r="V54" s="9"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="9">
         <v>4006</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9">
         <v>4</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G55" s="9">
         <v>0.5</v>
@@ -4944,7 +4478,7 @@
       <c r="P55" s="9"/>
       <c r="Q55" s="9"/>
       <c r="R55" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S55" s="9"/>
       <c r="T55" s="9"/>
@@ -4953,20 +4487,20 @@
       </c>
       <c r="V55" s="9"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="9">
         <v>4007</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="9">
         <v>4</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G56" s="9">
         <v>0.5</v>
@@ -4996,7 +4530,7 @@
       <c r="P56" s="9"/>
       <c r="Q56" s="9"/>
       <c r="R56" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S56" s="9"/>
       <c r="T56" s="9"/>
@@ -5005,20 +4539,20 @@
       </c>
       <c r="V56" s="9"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="9">
         <v>4008</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D57" s="9"/>
       <c r="E57" s="9">
         <v>4</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G57" s="9">
         <v>0.5</v>
@@ -5048,7 +4582,7 @@
       <c r="P57" s="9"/>
       <c r="Q57" s="9"/>
       <c r="R57" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S57" s="9"/>
       <c r="T57" s="9"/>
@@ -5057,20 +4591,20 @@
       </c>
       <c r="V57" s="9"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9">
         <v>4009</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="9">
         <v>4</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G58" s="9">
         <v>0.5</v>
@@ -5100,7 +4634,7 @@
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
       <c r="R58" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S58" s="9"/>
       <c r="T58" s="9"/>
@@ -5109,20 +4643,20 @@
       </c>
       <c r="V58" s="9"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9">
         <v>4010</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="9">
         <v>4</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G59" s="9">
         <v>0.5</v>
@@ -5152,7 +4686,7 @@
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
       <c r="R59" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
@@ -5161,20 +4695,20 @@
       </c>
       <c r="V59" s="9"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="9">
         <v>4011</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="9">
         <v>4</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G60" s="9">
         <v>0.5</v>
@@ -5204,7 +4738,7 @@
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
       <c r="R60" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S60" s="9"/>
       <c r="T60" s="9"/>
@@ -5213,20 +4747,20 @@
       </c>
       <c r="V60" s="9"/>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="9">
         <v>4012</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="9">
         <v>4</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G61" s="9">
         <v>0.5</v>
@@ -5256,7 +4790,7 @@
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
       <c r="R61" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S61" s="9"/>
       <c r="T61" s="9"/>
@@ -5265,20 +4799,20 @@
       </c>
       <c r="V61" s="9"/>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9">
         <v>4013</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="9">
         <v>4</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G62" s="9">
         <v>0.5</v>
@@ -5308,7 +4842,7 @@
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S62" s="9"/>
       <c r="T62" s="9"/>
@@ -5317,20 +4851,20 @@
       </c>
       <c r="V62" s="9"/>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="9">
         <v>4014</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="9">
         <v>4</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G63" s="9">
         <v>0.5</v>
@@ -5360,7 +4894,7 @@
       <c r="P63" s="9"/>
       <c r="Q63" s="9"/>
       <c r="R63" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
@@ -5369,20 +4903,20 @@
       </c>
       <c r="V63" s="9"/>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="9">
         <v>4015</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="9">
         <v>4</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G64" s="9">
         <v>0.5</v>
@@ -5412,7 +4946,7 @@
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
       <c r="R64" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S64" s="9"/>
       <c r="T64" s="9"/>
@@ -5421,20 +4955,20 @@
       </c>
       <c r="V64" s="9"/>
     </row>
-    <row r="65" s="2" customFormat="1" spans="1:22">
+    <row r="65" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11"/>
       <c r="B65" s="11">
         <v>5001</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D65" s="11"/>
       <c r="E65" s="11">
         <v>5</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G65" s="11">
         <v>1</v>
@@ -5464,33 +4998,33 @@
       <c r="P65" s="11"/>
       <c r="Q65" s="11"/>
       <c r="R65" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S65" s="11"/>
       <c r="T65" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U65" s="9">
         <v>1</v>
       </c>
       <c r="V65" s="11" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="66" s="3" customFormat="1" spans="1:22">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12"/>
       <c r="B66" s="12">
         <v>5002</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="12">
         <v>5</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5520,7 +5054,7 @@
       <c r="P66" s="12"/>
       <c r="Q66" s="12"/>
       <c r="R66" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S66" s="12"/>
       <c r="T66" s="12"/>
@@ -5529,20 +5063,20 @@
       </c>
       <c r="V66" s="12"/>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="12">
         <v>5003</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D67" s="10"/>
       <c r="E67" s="12">
         <v>5</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G67" s="10">
         <v>1</v>
@@ -5579,20 +5113,20 @@
       </c>
       <c r="V67" s="10"/>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="12">
         <v>5004</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D68" s="10"/>
       <c r="E68" s="12">
         <v>5</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G68" s="10">
         <v>1</v>
@@ -5629,20 +5163,20 @@
       </c>
       <c r="V68" s="10"/>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="12">
         <v>5005</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D69" s="10"/>
       <c r="E69" s="12">
         <v>5</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G69" s="10">
         <v>1</v>
@@ -5679,20 +5213,20 @@
       </c>
       <c r="V69" s="10"/>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="12">
         <v>5006</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D70" s="10"/>
       <c r="E70" s="12">
         <v>5</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G70" s="10">
         <v>1</v>
@@ -5729,20 +5263,20 @@
       </c>
       <c r="V70" s="10"/>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="12">
         <v>5007</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="12">
         <v>5</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G71" s="10">
         <v>1</v>
@@ -5779,20 +5313,20 @@
       </c>
       <c r="V71" s="10"/>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="12">
         <v>5008</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D72" s="10"/>
       <c r="E72" s="12">
         <v>5</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G72" s="10">
         <v>1</v>
@@ -5829,20 +5363,20 @@
       </c>
       <c r="V72" s="10"/>
     </row>
-    <row r="73" s="3" customFormat="1" spans="1:22">
+    <row r="73" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="12"/>
       <c r="B73" s="12">
         <v>5009</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="12">
         <v>5</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G73" s="10">
         <v>1</v>
@@ -5872,7 +5406,7 @@
       <c r="P73" s="12"/>
       <c r="Q73" s="12"/>
       <c r="R73" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S73" s="12"/>
       <c r="T73" s="12"/>
@@ -5881,20 +5415,20 @@
       </c>
       <c r="V73" s="12"/>
     </row>
-    <row r="74" s="2" customFormat="1" spans="1:22">
+    <row r="74" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11"/>
       <c r="B74" s="11">
         <v>6001</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11">
         <v>6</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G74" s="14">
         <v>1</v>
@@ -5924,7 +5458,7 @@
       <c r="P74" s="11"/>
       <c r="Q74" s="11"/>
       <c r="R74" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S74" s="11"/>
       <c r="T74" s="11"/>
@@ -5933,20 +5467,20 @@
       </c>
       <c r="V74" s="11"/>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9">
         <v>6002</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="9">
         <v>6</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G75" s="10">
         <v>1</v>
@@ -5976,7 +5510,7 @@
       <c r="P75" s="9"/>
       <c r="Q75" s="9"/>
       <c r="R75" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S75" s="9"/>
       <c r="T75" s="9"/>
@@ -5985,20 +5519,20 @@
       </c>
       <c r="V75" s="9"/>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="9">
         <v>6003</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="9">
         <v>6</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G76" s="10">
         <v>1</v>
@@ -6028,7 +5562,7 @@
       <c r="P76" s="9"/>
       <c r="Q76" s="9"/>
       <c r="R76" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S76" s="9"/>
       <c r="T76" s="9"/>
@@ -6037,20 +5571,20 @@
       </c>
       <c r="V76" s="9"/>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
       <c r="B77" s="9">
         <v>6004</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="9">
         <v>6</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -6080,7 +5614,7 @@
       <c r="P77" s="9"/>
       <c r="Q77" s="9"/>
       <c r="R77" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="S77" s="9"/>
       <c r="T77" s="9"/>
@@ -6089,20 +5623,20 @@
       </c>
       <c r="V77" s="9"/>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
       <c r="B78" s="9">
         <v>6005</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="9">
         <v>6</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G78" s="10">
         <v>1</v>
@@ -6132,7 +5666,7 @@
       <c r="P78" s="9"/>
       <c r="Q78" s="9"/>
       <c r="R78" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="S78" s="9"/>
       <c r="T78" s="9"/>
@@ -6141,20 +5675,20 @@
       </c>
       <c r="V78" s="9"/>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9">
         <v>6006</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="9">
         <v>6</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G79" s="10">
         <v>1</v>
@@ -6184,7 +5718,7 @@
       <c r="P79" s="9"/>
       <c r="Q79" s="9"/>
       <c r="R79" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="S79" s="9"/>
       <c r="T79" s="9"/>
@@ -6193,20 +5727,20 @@
       </c>
       <c r="V79" s="9"/>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
       <c r="B80" s="9">
         <v>6007</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="9">
         <v>6</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G80" s="10">
         <v>1</v>
@@ -6236,7 +5770,7 @@
       <c r="P80" s="9"/>
       <c r="Q80" s="9"/>
       <c r="R80" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S80" s="9"/>
       <c r="T80" s="9"/>
@@ -6245,20 +5779,20 @@
       </c>
       <c r="V80" s="9"/>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
       <c r="B81" s="9">
         <v>6008</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="9">
         <v>6</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G81" s="10">
         <v>1</v>
@@ -6288,7 +5822,7 @@
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
       <c r="R81" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="S81" s="9"/>
       <c r="T81" s="9"/>
@@ -6297,20 +5831,20 @@
       </c>
       <c r="V81" s="9"/>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
       <c r="B82" s="9">
         <v>6009</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="9">
         <v>6</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G82" s="10">
         <v>1</v>
@@ -6340,7 +5874,7 @@
       <c r="P82" s="9"/>
       <c r="Q82" s="9"/>
       <c r="R82" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S82" s="9"/>
       <c r="T82" s="9"/>
@@ -6349,20 +5883,20 @@
       </c>
       <c r="V82" s="9"/>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="9">
         <v>6010</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="9">
         <v>6</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G83" s="10">
         <v>1</v>
@@ -6392,7 +5926,7 @@
       <c r="P83" s="9"/>
       <c r="Q83" s="9"/>
       <c r="R83" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S83" s="9"/>
       <c r="T83" s="9"/>
@@ -6401,20 +5935,20 @@
       </c>
       <c r="V83" s="9"/>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" s="9"/>
       <c r="B84" s="9">
         <v>6011</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9">
         <v>6</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G84" s="10">
         <v>1</v>
@@ -6444,7 +5978,7 @@
       <c r="P84" s="9"/>
       <c r="Q84" s="9"/>
       <c r="R84" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S84" s="9"/>
       <c r="T84" s="9"/>
@@ -6453,20 +5987,20 @@
       </c>
       <c r="V84" s="9"/>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
       <c r="B85" s="9">
         <v>6012</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="9">
         <v>6</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G85" s="10">
         <v>1</v>
@@ -6496,7 +6030,7 @@
       <c r="P85" s="9"/>
       <c r="Q85" s="9"/>
       <c r="R85" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="S85" s="9"/>
       <c r="T85" s="9"/>
@@ -6505,20 +6039,20 @@
       </c>
       <c r="V85" s="9"/>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" s="9"/>
       <c r="B86" s="9">
         <v>6013</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="9">
         <v>6</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G86" s="10">
         <v>1</v>
@@ -6548,7 +6082,7 @@
       <c r="P86" s="9"/>
       <c r="Q86" s="9"/>
       <c r="R86" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="S86" s="9"/>
       <c r="T86" s="9"/>
@@ -6557,20 +6091,20 @@
       </c>
       <c r="V86" s="9"/>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
       <c r="B87" s="9">
         <v>6014</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="9">
         <v>6</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G87" s="10">
         <v>1</v>
@@ -6600,7 +6134,7 @@
       <c r="P87" s="9"/>
       <c r="Q87" s="9"/>
       <c r="R87" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
@@ -6609,20 +6143,20 @@
       </c>
       <c r="V87" s="9"/>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A88" s="9"/>
       <c r="B88" s="9">
         <v>6015</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="9">
         <v>6</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G88" s="10">
         <v>1</v>
@@ -6652,7 +6186,7 @@
       <c r="P88" s="9"/>
       <c r="Q88" s="9"/>
       <c r="R88" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S88" s="9"/>
       <c r="T88" s="9"/>
@@ -6661,20 +6195,20 @@
       </c>
       <c r="V88" s="9"/>
     </row>
-    <row r="89" s="2" customFormat="1" spans="1:27">
+    <row r="89" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="14"/>
       <c r="B89" s="14">
         <v>7001</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14">
         <v>7</v>
       </c>
       <c r="F89" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G89" s="14">
         <v>1</v>
@@ -6716,20 +6250,20 @@
       <c r="Z89" s="17"/>
       <c r="AA89" s="17"/>
     </row>
-    <row r="90" spans="1:22">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="10">
         <v>7002</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D90" s="10"/>
       <c r="E90" s="10">
         <v>7</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G90" s="10">
         <v>1</v>
@@ -6766,20 +6300,20 @@
       </c>
       <c r="V90" s="10"/>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="10">
         <v>7003</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10">
         <v>7</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G91" s="10">
         <v>1</v>
@@ -6816,20 +6350,20 @@
       </c>
       <c r="V91" s="10"/>
     </row>
-    <row r="92" spans="1:22">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="10">
         <v>7004</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D92" s="10"/>
       <c r="E92" s="10">
         <v>7</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G92" s="10">
         <v>1</v>
@@ -6866,20 +6400,20 @@
       </c>
       <c r="V92" s="10"/>
     </row>
-    <row r="93" s="2" customFormat="1" spans="1:27">
+    <row r="93" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="14"/>
       <c r="B93" s="14">
         <v>8001</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D93" s="14"/>
       <c r="E93" s="14">
         <v>8</v>
       </c>
-      <c r="F93" s="14" t="s">
-        <v>221</v>
+      <c r="F93" s="23" t="s">
+        <v>278</v>
       </c>
       <c r="G93" s="10">
         <v>1</v>
@@ -6921,20 +6455,20 @@
       <c r="Z93" s="17"/>
       <c r="AA93" s="17"/>
     </row>
-    <row r="94" spans="1:22">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="10">
         <v>8002</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D94" s="10"/>
       <c r="E94" s="10">
         <v>8</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G94" s="10">
         <v>1</v>
@@ -6971,20 +6505,20 @@
       </c>
       <c r="V94" s="10"/>
     </row>
-    <row r="95" spans="1:22">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="10">
         <v>8003</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="10">
         <v>8</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G95" s="10">
         <v>1</v>
@@ -7021,20 +6555,20 @@
       </c>
       <c r="V95" s="10"/>
     </row>
-    <row r="96" spans="1:22">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="10">
         <v>8004</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D96" s="10"/>
       <c r="E96" s="10">
         <v>8</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G96" s="10">
         <v>1</v>
@@ -7071,20 +6605,20 @@
       </c>
       <c r="V96" s="10"/>
     </row>
-    <row r="97" spans="1:22">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="10">
         <v>8005</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D97" s="10"/>
       <c r="E97" s="10">
         <v>8</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G97" s="10">
         <v>1</v>
@@ -7121,20 +6655,20 @@
       </c>
       <c r="V97" s="10"/>
     </row>
-    <row r="98" spans="1:22">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="10">
         <v>8006</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D98" s="10"/>
       <c r="E98" s="10">
         <v>8</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G98" s="10">
         <v>1</v>
@@ -7171,20 +6705,20 @@
       </c>
       <c r="V98" s="10"/>
     </row>
-    <row r="99" spans="1:22">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="10">
         <v>8007</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D99" s="10"/>
       <c r="E99" s="10">
         <v>8</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G99" s="10">
         <v>1</v>
@@ -7221,20 +6755,20 @@
       </c>
       <c r="V99" s="10"/>
     </row>
-    <row r="100" spans="1:22">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="10">
         <v>8008</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D100" s="10"/>
       <c r="E100" s="10">
         <v>8</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G100" s="10">
         <v>1</v>
@@ -7271,20 +6805,20 @@
       </c>
       <c r="V100" s="10"/>
     </row>
-    <row r="101" spans="1:22">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="10">
         <v>8009</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D101" s="10"/>
       <c r="E101" s="10">
         <v>8</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G101" s="10">
         <v>1</v>
@@ -7321,20 +6855,20 @@
       </c>
       <c r="V101" s="10"/>
     </row>
-    <row r="102" spans="1:22">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="10">
         <v>8010</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D102" s="10"/>
       <c r="E102" s="10">
         <v>8</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G102" s="10">
         <v>1</v>
@@ -7371,20 +6905,20 @@
       </c>
       <c r="V102" s="10"/>
     </row>
-    <row r="103" spans="1:22">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="10">
         <v>8011</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D103" s="10"/>
       <c r="E103" s="10">
         <v>8</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G103" s="10">
         <v>1</v>
@@ -7421,20 +6955,20 @@
       </c>
       <c r="V103" s="10"/>
     </row>
-    <row r="104" spans="1:22">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="10">
         <v>8012</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D104" s="10"/>
       <c r="E104" s="10">
         <v>8</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G104" s="10">
         <v>1</v>
@@ -7471,20 +7005,20 @@
       </c>
       <c r="V104" s="10"/>
     </row>
-    <row r="105" spans="1:22">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="10">
         <v>8013</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D105" s="10"/>
       <c r="E105" s="10">
         <v>8</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G105" s="10">
         <v>1</v>
@@ -7521,20 +7055,20 @@
       </c>
       <c r="V105" s="10"/>
     </row>
-    <row r="106" spans="1:22">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="10">
         <v>8014</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D106" s="10"/>
       <c r="E106" s="10">
         <v>8</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>221</v>
+        <v>277</v>
       </c>
       <c r="G106" s="10">
         <v>1</v>
@@ -7571,7 +7105,7 @@
       </c>
       <c r="V106" s="10"/>
     </row>
-    <row r="107" spans="1:22">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="10"/>
       <c r="C107" s="16"/>
@@ -7593,7 +7127,7 @@
       <c r="U107" s="10"/>
       <c r="V107" s="10"/>
     </row>
-    <row r="108" spans="1:22">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="16"/>
@@ -7615,7 +7149,7 @@
       <c r="U108" s="10"/>
       <c r="V108" s="10"/>
     </row>
-    <row r="109" spans="1:22">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A109" s="10"/>
       <c r="B109" s="10"/>
       <c r="C109" s="16"/>
@@ -7637,7 +7171,7 @@
       <c r="U109" s="10"/>
       <c r="V109" s="10"/>
     </row>
-    <row r="110" spans="1:22">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" s="10"/>
       <c r="B110" s="10"/>
       <c r="C110" s="16"/>
@@ -7659,7 +7193,7 @@
       <c r="U110" s="10"/>
       <c r="V110" s="10"/>
     </row>
-    <row r="111" spans="1:22">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" s="10"/>
       <c r="B111" s="10"/>
       <c r="C111" s="16"/>
@@ -7681,7 +7215,7 @@
       <c r="U111" s="10"/>
       <c r="V111" s="10"/>
     </row>
-    <row r="112" spans="1:22">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
       <c r="B112" s="10"/>
       <c r="C112" s="16"/>
@@ -7703,7 +7237,7 @@
       <c r="U112" s="10"/>
       <c r="V112" s="10"/>
     </row>
-    <row r="113" spans="1:22">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
       <c r="C113" s="16"/>
@@ -7725,7 +7259,7 @@
       <c r="U113" s="10"/>
       <c r="V113" s="10"/>
     </row>
-    <row r="114" spans="1:22">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A114" s="10"/>
       <c r="B114" s="10"/>
       <c r="C114" s="16"/>
@@ -7747,7 +7281,7 @@
       <c r="U114" s="10"/>
       <c r="V114" s="10"/>
     </row>
-    <row r="115" spans="1:22">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
       <c r="C115" s="16"/>
@@ -7769,7 +7303,7 @@
       <c r="U115" s="10"/>
       <c r="V115" s="10"/>
     </row>
-    <row r="116" spans="1:22">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="16"/>
@@ -7791,7 +7325,7 @@
       <c r="U116" s="10"/>
       <c r="V116" s="10"/>
     </row>
-    <row r="117" spans="1:22">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="16"/>
@@ -7813,7 +7347,7 @@
       <c r="U117" s="10"/>
       <c r="V117" s="10"/>
     </row>
-    <row r="118" spans="1:22">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A118" s="10"/>
       <c r="B118" s="10"/>
       <c r="C118" s="16"/>
@@ -7835,7 +7369,7 @@
       <c r="U118" s="10"/>
       <c r="V118" s="10"/>
     </row>
-    <row r="119" spans="1:22">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
       <c r="C119" s="16"/>
@@ -7857,7 +7391,7 @@
       <c r="U119" s="10"/>
       <c r="V119" s="10"/>
     </row>
-    <row r="120" spans="1:22">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
       <c r="C120" s="16"/>
@@ -7879,7 +7413,7 @@
       <c r="U120" s="10"/>
       <c r="V120" s="10"/>
     </row>
-    <row r="121" spans="1:22">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
       <c r="C121" s="16"/>
@@ -7901,7 +7435,7 @@
       <c r="U121" s="10"/>
       <c r="V121" s="10"/>
     </row>
-    <row r="122" spans="1:22">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A122" s="10"/>
       <c r="B122" s="10"/>
       <c r="C122" s="16"/>
@@ -7923,7 +7457,7 @@
       <c r="U122" s="10"/>
       <c r="V122" s="10"/>
     </row>
-    <row r="123" spans="1:22">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A123" s="10"/>
       <c r="B123" s="10"/>
       <c r="C123" s="16"/>
@@ -7945,7 +7479,7 @@
       <c r="U123" s="10"/>
       <c r="V123" s="10"/>
     </row>
-    <row r="124" spans="1:22">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
       <c r="B124" s="10"/>
       <c r="C124" s="16"/>
@@ -7967,7 +7501,7 @@
       <c r="U124" s="10"/>
       <c r="V124" s="10"/>
     </row>
-    <row r="125" spans="1:22">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A125" s="10"/>
       <c r="B125" s="10"/>
       <c r="C125" s="16"/>
@@ -7989,7 +7523,7 @@
       <c r="U125" s="10"/>
       <c r="V125" s="10"/>
     </row>
-    <row r="126" spans="1:22">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A126" s="10"/>
       <c r="B126" s="10"/>
       <c r="C126" s="16"/>
@@ -8011,7 +7545,7 @@
       <c r="U126" s="10"/>
       <c r="V126" s="10"/>
     </row>
-    <row r="127" spans="1:22">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
       <c r="C127" s="16"/>
@@ -8033,7 +7567,7 @@
       <c r="U127" s="10"/>
       <c r="V127" s="10"/>
     </row>
-    <row r="128" spans="1:22">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A128" s="10"/>
       <c r="B128" s="10"/>
       <c r="C128" s="16"/>
@@ -8055,7 +7589,7 @@
       <c r="U128" s="10"/>
       <c r="V128" s="10"/>
     </row>
-    <row r="129" spans="1:22">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="16"/>
@@ -8077,7 +7611,7 @@
       <c r="U129" s="10"/>
       <c r="V129" s="10"/>
     </row>
-    <row r="130" spans="1:22">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
       <c r="B130" s="10"/>
       <c r="C130" s="16"/>
@@ -8099,7 +7633,7 @@
       <c r="U130" s="10"/>
       <c r="V130" s="10"/>
     </row>
-    <row r="131" spans="1:22">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A131" s="10"/>
       <c r="B131" s="10"/>
       <c r="C131" s="16"/>
@@ -8121,7 +7655,7 @@
       <c r="U131" s="10"/>
       <c r="V131" s="10"/>
     </row>
-    <row r="132" spans="1:22">
+    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A132" s="10"/>
       <c r="B132" s="10"/>
       <c r="C132" s="16"/>
@@ -8143,7 +7677,7 @@
       <c r="U132" s="10"/>
       <c r="V132" s="10"/>
     </row>
-    <row r="133" spans="1:22">
+    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A133" s="10"/>
       <c r="B133" s="10"/>
       <c r="C133" s="16"/>
@@ -8165,7 +7699,7 @@
       <c r="U133" s="10"/>
       <c r="V133" s="10"/>
     </row>
-    <row r="134" spans="1:22">
+    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A134" s="10"/>
       <c r="B134" s="10"/>
       <c r="C134" s="16"/>
@@ -8187,7 +7721,7 @@
       <c r="U134" s="10"/>
       <c r="V134" s="10"/>
     </row>
-    <row r="135" spans="1:22">
+    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A135" s="10"/>
       <c r="B135" s="10"/>
       <c r="C135" s="16"/>
@@ -8209,7 +7743,7 @@
       <c r="U135" s="10"/>
       <c r="V135" s="10"/>
     </row>
-    <row r="136" spans="1:22">
+    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
       <c r="B136" s="10"/>
       <c r="C136" s="16"/>
@@ -8231,7 +7765,7 @@
       <c r="U136" s="10"/>
       <c r="V136" s="10"/>
     </row>
-    <row r="137" spans="1:22">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A137" s="10"/>
       <c r="B137" s="10"/>
       <c r="C137" s="16"/>
@@ -8253,7 +7787,7 @@
       <c r="U137" s="10"/>
       <c r="V137" s="10"/>
     </row>
-    <row r="138" spans="1:22">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A138" s="10"/>
       <c r="B138" s="10"/>
       <c r="C138" s="16"/>
@@ -8275,7 +7809,7 @@
       <c r="U138" s="10"/>
       <c r="V138" s="10"/>
     </row>
-    <row r="139" spans="1:22">
+    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
       <c r="C139" s="16"/>
@@ -8297,7 +7831,7 @@
       <c r="U139" s="10"/>
       <c r="V139" s="10"/>
     </row>
-    <row r="140" spans="1:22">
+    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="16"/>
@@ -8319,7 +7853,7 @@
       <c r="U140" s="10"/>
       <c r="V140" s="10"/>
     </row>
-    <row r="141" spans="1:22">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
       <c r="C141" s="16"/>
@@ -8341,7 +7875,7 @@
       <c r="U141" s="10"/>
       <c r="V141" s="10"/>
     </row>
-    <row r="142" spans="1:22">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
       <c r="C142" s="16"/>
@@ -8363,7 +7897,7 @@
       <c r="U142" s="10"/>
       <c r="V142" s="10"/>
     </row>
-    <row r="143" spans="1:22">
+    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
       <c r="C143" s="16"/>
@@ -8385,7 +7919,7 @@
       <c r="U143" s="10"/>
       <c r="V143" s="10"/>
     </row>
-    <row r="144" spans="1:22">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
       <c r="C144" s="16"/>
@@ -8407,7 +7941,7 @@
       <c r="U144" s="10"/>
       <c r="V144" s="10"/>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="16"/>
@@ -8429,7 +7963,7 @@
       <c r="U145" s="10"/>
       <c r="V145" s="10"/>
     </row>
-    <row r="146" spans="1:22">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="16"/>
@@ -8451,7 +7985,7 @@
       <c r="U146" s="10"/>
       <c r="V146" s="10"/>
     </row>
-    <row r="147" spans="1:22">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="16"/>
@@ -8473,7 +8007,7 @@
       <c r="U147" s="10"/>
       <c r="V147" s="10"/>
     </row>
-    <row r="148" spans="1:22">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="16"/>
@@ -8495,7 +8029,7 @@
       <c r="U148" s="10"/>
       <c r="V148" s="10"/>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
       <c r="C149" s="16"/>
@@ -8517,7 +8051,7 @@
       <c r="U149" s="10"/>
       <c r="V149" s="10"/>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="16"/>
@@ -8539,7 +8073,7 @@
       <c r="U150" s="10"/>
       <c r="V150" s="10"/>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
       <c r="C151" s="16"/>
@@ -8561,7 +8095,7 @@
       <c r="U151" s="10"/>
       <c r="V151" s="10"/>
     </row>
-    <row r="152" spans="1:22">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="16"/>
@@ -8583,7 +8117,7 @@
       <c r="U152" s="10"/>
       <c r="V152" s="10"/>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="16"/>
@@ -8605,7 +8139,7 @@
       <c r="U153" s="10"/>
       <c r="V153" s="10"/>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="16"/>
@@ -8627,7 +8161,7 @@
       <c r="U154" s="10"/>
       <c r="V154" s="10"/>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="16"/>
@@ -8649,7 +8183,7 @@
       <c r="U155" s="10"/>
       <c r="V155" s="10"/>
     </row>
-    <row r="156" spans="1:22">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="16"/>
@@ -8671,7 +8205,7 @@
       <c r="U156" s="10"/>
       <c r="V156" s="10"/>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="16"/>
@@ -8693,7 +8227,7 @@
       <c r="U157" s="10"/>
       <c r="V157" s="10"/>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="16"/>
@@ -8715,7 +8249,7 @@
       <c r="U158" s="10"/>
       <c r="V158" s="10"/>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="16"/>
@@ -8737,7 +8271,7 @@
       <c r="U159" s="10"/>
       <c r="V159" s="10"/>
     </row>
-    <row r="160" spans="1:22">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="16"/>
@@ -8759,7 +8293,7 @@
       <c r="U160" s="10"/>
       <c r="V160" s="10"/>
     </row>
-    <row r="161" spans="1:22">
+    <row r="161" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="16"/>
@@ -8781,7 +8315,7 @@
       <c r="U161" s="10"/>
       <c r="V161" s="10"/>
     </row>
-    <row r="162" spans="1:22">
+    <row r="162" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="16"/>
@@ -8803,7 +8337,7 @@
       <c r="U162" s="10"/>
       <c r="V162" s="10"/>
     </row>
-    <row r="163" spans="1:22">
+    <row r="163" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
       <c r="C163" s="16"/>
@@ -8825,7 +8359,7 @@
       <c r="U163" s="10"/>
       <c r="V163" s="10"/>
     </row>
-    <row r="164" spans="1:22">
+    <row r="164" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
       <c r="C164" s="16"/>
@@ -8847,7 +8381,7 @@
       <c r="U164" s="10"/>
       <c r="V164" s="10"/>
     </row>
-    <row r="165" spans="1:22">
+    <row r="165" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
       <c r="C165" s="16"/>
@@ -8869,7 +8403,7 @@
       <c r="U165" s="10"/>
       <c r="V165" s="10"/>
     </row>
-    <row r="166" spans="1:22">
+    <row r="166" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
       <c r="C166" s="16"/>
@@ -8891,7 +8425,7 @@
       <c r="U166" s="10"/>
       <c r="V166" s="10"/>
     </row>
-    <row r="167" spans="1:22">
+    <row r="167" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
       <c r="C167" s="16"/>
@@ -8913,7 +8447,7 @@
       <c r="U167" s="10"/>
       <c r="V167" s="10"/>
     </row>
-    <row r="168" spans="1:22">
+    <row r="168" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
       <c r="C168" s="16"/>
@@ -8935,7 +8469,7 @@
       <c r="U168" s="10"/>
       <c r="V168" s="10"/>
     </row>
-    <row r="169" spans="1:22">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="16"/>
@@ -8957,7 +8491,7 @@
       <c r="U169" s="10"/>
       <c r="V169" s="10"/>
     </row>
-    <row r="170" spans="1:22">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
       <c r="C170" s="16"/>
@@ -8979,7 +8513,7 @@
       <c r="U170" s="10"/>
       <c r="V170" s="10"/>
     </row>
-    <row r="171" spans="1:22">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
       <c r="C171" s="16"/>
@@ -9001,7 +8535,7 @@
       <c r="U171" s="10"/>
       <c r="V171" s="10"/>
     </row>
-    <row r="172" spans="1:22">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
       <c r="C172" s="16"/>
@@ -9023,7 +8557,7 @@
       <c r="U172" s="10"/>
       <c r="V172" s="10"/>
     </row>
-    <row r="173" spans="1:22">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
       <c r="C173" s="16"/>
@@ -9045,7 +8579,7 @@
       <c r="U173" s="10"/>
       <c r="V173" s="10"/>
     </row>
-    <row r="174" spans="1:22">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
       <c r="C174" s="16"/>
@@ -9067,7 +8601,7 @@
       <c r="U174" s="10"/>
       <c r="V174" s="10"/>
     </row>
-    <row r="175" spans="1:22">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
       <c r="C175" s="16"/>
@@ -9089,7 +8623,7 @@
       <c r="U175" s="10"/>
       <c r="V175" s="10"/>
     </row>
-    <row r="176" spans="1:22">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A176" s="10"/>
       <c r="B176" s="10"/>
       <c r="C176" s="16"/>
@@ -9111,7 +8645,7 @@
       <c r="U176" s="10"/>
       <c r="V176" s="10"/>
     </row>
-    <row r="177" spans="1:22">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A177" s="10"/>
       <c r="B177" s="10"/>
       <c r="C177" s="16"/>
@@ -9133,7 +8667,7 @@
       <c r="U177" s="10"/>
       <c r="V177" s="10"/>
     </row>
-    <row r="178" spans="1:22">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
       <c r="B178" s="10"/>
       <c r="C178" s="16"/>
@@ -9155,7 +8689,7 @@
       <c r="U178" s="10"/>
       <c r="V178" s="10"/>
     </row>
-    <row r="179" spans="1:22">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A179" s="10"/>
       <c r="B179" s="10"/>
       <c r="C179" s="16"/>
@@ -9177,7 +8711,7 @@
       <c r="U179" s="10"/>
       <c r="V179" s="10"/>
     </row>
-    <row r="180" spans="1:22">
+    <row r="180" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
       <c r="C180" s="16"/>
@@ -9199,7 +8733,7 @@
       <c r="U180" s="10"/>
       <c r="V180" s="10"/>
     </row>
-    <row r="181" spans="1:22">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="16"/>
@@ -9221,7 +8755,7 @@
       <c r="U181" s="10"/>
       <c r="V181" s="10"/>
     </row>
-    <row r="182" spans="1:22">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A182" s="10"/>
       <c r="B182" s="10"/>
       <c r="C182" s="16"/>
@@ -9243,7 +8777,7 @@
       <c r="U182" s="10"/>
       <c r="V182" s="10"/>
     </row>
-    <row r="183" spans="1:22">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A183" s="10"/>
       <c r="B183" s="10"/>
       <c r="C183" s="16"/>
@@ -9265,7 +8799,7 @@
       <c r="U183" s="10"/>
       <c r="V183" s="10"/>
     </row>
-    <row r="184" spans="1:22">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A184" s="10"/>
       <c r="B184" s="10"/>
       <c r="C184" s="16"/>
@@ -9287,7 +8821,7 @@
       <c r="U184" s="10"/>
       <c r="V184" s="10"/>
     </row>
-    <row r="185" spans="1:22">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A185" s="10"/>
       <c r="B185" s="10"/>
       <c r="C185" s="16"/>
@@ -9309,7 +8843,7 @@
       <c r="U185" s="10"/>
       <c r="V185" s="10"/>
     </row>
-    <row r="186" spans="1:19">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A186" s="18"/>
       <c r="B186" s="18"/>
       <c r="C186" s="18"/>
@@ -9327,7 +8861,7 @@
       <c r="R186" s="18"/>
       <c r="S186" s="18"/>
     </row>
-    <row r="187" spans="1:19">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A187" s="18"/>
       <c r="B187" s="18"/>
       <c r="C187" s="18"/>
@@ -9345,7 +8879,7 @@
       <c r="R187" s="18"/>
       <c r="S187" s="18"/>
     </row>
-    <row r="188" spans="1:19">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A188" s="18"/>
       <c r="B188" s="18"/>
       <c r="C188" s="18"/>
@@ -9364,55 +8898,54 @@
       <c r="S188" s="18"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="L19:R61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="12" max="12" width="5.16666666666667" customWidth="1"/>
-    <col min="13" max="13" width="18.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
     <col min="14" max="15" width="20.5" customWidth="1"/>
-    <col min="16" max="17" width="30.0833333333333" customWidth="1"/>
+    <col min="16" max="17" width="30.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="12:18">
+    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
+        <v>233</v>
+      </c>
+      <c r="M19" t="s">
+        <v>234</v>
+      </c>
+      <c r="N19" t="s">
         <v>235</v>
       </c>
-      <c r="M19" t="s">
+      <c r="P19" t="s">
         <v>236</v>
       </c>
-      <c r="N19" t="s">
+      <c r="R19" t="s">
         <v>237</v>
       </c>
-      <c r="P19" t="s">
-        <v>238</v>
-      </c>
-      <c r="R19" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="12:18">
+    </row>
+    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L20">
         <v>5001</v>
       </c>
       <c r="M20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -9422,21 +8955,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="12:18">
+    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L21">
         <v>5002</v>
       </c>
       <c r="M21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21" t="s">
+        <v>238</v>
+      </c>
+      <c r="P21" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -9446,21 +8979,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="12:18">
+    <row r="22" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L22">
         <v>5003</v>
       </c>
       <c r="M22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P22" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -9470,21 +9003,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="12:18">
+    <row r="23" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>5004</v>
       </c>
       <c r="M23" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P23" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -9494,21 +9027,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="12:18">
+    <row r="24" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L24">
         <v>5005</v>
       </c>
       <c r="M24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -9518,21 +9051,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="12:18">
+    <row r="25" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L25">
         <v>5006</v>
       </c>
       <c r="M25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -9542,21 +9075,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="12:18">
+    <row r="26" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L26">
         <v>5007</v>
       </c>
       <c r="M26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -9566,21 +9099,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="12:18">
+    <row r="27" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L27">
         <v>5008</v>
       </c>
       <c r="M27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -9590,21 +9123,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="12:18">
+    <row r="28" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L28">
         <v>5009</v>
       </c>
       <c r="M28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -9614,18 +9147,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="12:18">
+    <row r="29" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L29">
         <v>6001</v>
       </c>
       <c r="M29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -9635,18 +9168,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="12:18">
+    <row r="30" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L30">
         <v>6002</v>
       </c>
       <c r="M30" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -9656,18 +9189,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="12:18">
+    <row r="31" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L31">
         <v>6003</v>
       </c>
       <c r="M31" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O31" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="P31" t="s">
         <v>250</v>
-      </c>
-      <c r="P31" t="s">
-        <v>252</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -9677,18 +9210,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="12:18">
+    <row r="32" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L32">
         <v>6004</v>
       </c>
       <c r="M32" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P32" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -9698,18 +9231,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="12:18">
+    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L33">
         <v>6005</v>
       </c>
       <c r="M33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P33" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -9719,18 +9252,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="12:18">
+    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L34">
         <v>6006</v>
       </c>
       <c r="M34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P34" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -9740,18 +9273,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="12:18">
+    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L35">
         <v>6007</v>
       </c>
       <c r="M35" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P35" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -9761,18 +9294,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="12:18">
+    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L36">
         <v>6008</v>
       </c>
       <c r="M36" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -9782,18 +9315,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="12:18">
+    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L37">
         <v>6009</v>
       </c>
       <c r="M37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P37" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -9803,18 +9336,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="12:18">
+    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L38">
         <v>6010</v>
       </c>
       <c r="M38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P38" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -9824,18 +9357,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="12:18">
+    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L39">
         <v>6011</v>
       </c>
       <c r="M39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -9845,18 +9378,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="12:18">
+    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L40">
         <v>6012</v>
       </c>
       <c r="M40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P40" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -9866,18 +9399,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="12:18">
+    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L41">
         <v>6013</v>
       </c>
       <c r="M41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P41" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -9887,18 +9420,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="12:18">
+    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L42">
         <v>6014</v>
       </c>
       <c r="M42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -9908,18 +9441,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="12:18">
+    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L43">
         <v>6015</v>
       </c>
       <c r="M43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="P43" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -9929,21 +9462,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="12:18">
+    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L44">
         <v>7001</v>
       </c>
       <c r="M44" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N44">
         <v>7</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P44" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -9953,21 +9486,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="12:18">
+    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L45">
         <v>7002</v>
       </c>
       <c r="M45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
       <c r="O45" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="P45" t="s">
         <v>259</v>
-      </c>
-      <c r="P45" t="s">
-        <v>261</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -9977,21 +9510,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="12:18">
+    <row r="46" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L46">
         <v>7003</v>
       </c>
       <c r="M46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -10001,21 +9534,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="12:18">
+    <row r="47" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L47">
         <v>7004</v>
       </c>
       <c r="M47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P47" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -10025,21 +9558,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="12:18">
+    <row r="48" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L48">
         <v>8001</v>
       </c>
       <c r="M48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -10049,21 +9582,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="12:18">
+    <row r="49" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L49">
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -10073,21 +9606,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="12:18">
+    <row r="50" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L50">
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -10097,21 +9630,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="12:18">
+    <row r="51" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L51">
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -10121,21 +9654,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="12:18">
+    <row r="52" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L52">
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -10145,21 +9678,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="12:18">
+    <row r="53" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L53">
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -10169,21 +9702,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="12:18">
+    <row r="54" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L54">
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -10193,21 +9726,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="12:18">
+    <row r="55" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L55">
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -10217,21 +9750,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="12:18">
+    <row r="56" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L56">
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -10241,21 +9774,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="12:18">
+    <row r="57" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L57">
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -10265,21 +9798,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="12:18">
+    <row r="58" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L58">
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -10289,21 +9822,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="12:18">
+    <row r="59" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L59">
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -10313,21 +9846,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="12:18">
+    <row r="60" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L60">
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -10337,21 +9870,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="12:18">
+    <row r="61" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L61">
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>
@@ -10362,7 +9895,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E0DEAA-CFA0-415B-A92C-E3A11F4FA272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED207A91-E7D3-410F-81E6-089896C25602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="280">
   <si>
     <t>##var</t>
   </si>
@@ -549,9 +549,6 @@
     <t>洒水壶</t>
   </si>
   <si>
-    <t>Item/Watering_Can</t>
-  </si>
-  <si>
     <t>删除染色</t>
   </si>
   <si>
@@ -675,25 +672,13 @@
     <t>甜菜女士</t>
   </si>
   <si>
-    <t>Npc/Ms_Beet</t>
-  </si>
-  <si>
     <t>花椰菜羊-白</t>
   </si>
   <si>
-    <t>Npc/Cauliflower_Sheep_White</t>
-  </si>
-  <si>
     <t>花椰菜羊-绿</t>
   </si>
   <si>
-    <t>Npc/Cauliflower_Sheep_Green</t>
-  </si>
-  <si>
     <t>猴子先生</t>
-  </si>
-  <si>
-    <t>Npc/Mr_Monkey</t>
   </si>
   <si>
     <t>土豆-幼苗</t>
@@ -887,6 +872,30 @@
   </si>
   <si>
     <t>plant/Seedling</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>plant/Cauliflower</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npc/Character_beet</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npc/sheep_White</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npc/sheep_Green</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Npc/Character_monkey</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item/Wateringpot</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1118,7 +1127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1185,6 +1194,10 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1546,13 +1559,13 @@
         <v>21</v>
       </c>
       <c r="W1" s="21" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="X1" s="21" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -1700,13 +1713,13 @@
         <v>46</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
@@ -1777,13 +1790,13 @@
         <v>59</v>
       </c>
       <c r="W4" s="20" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="X4" s="20" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="Y4" s="20" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
@@ -1799,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G5" s="9">
         <v>1</v>
@@ -1846,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G6" s="9">
         <v>1</v>
@@ -1893,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G7" s="9">
         <v>1</v>
@@ -1940,7 +1953,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G8" s="9">
         <v>1</v>
@@ -1988,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G9" s="9">
         <v>1</v>
@@ -2036,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G10" s="9">
         <v>1</v>
@@ -2084,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G11" s="9">
         <v>1</v>
@@ -2132,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G12" s="9">
         <v>1</v>
@@ -2180,7 +2193,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G13" s="9">
         <v>1</v>
@@ -2228,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G14" s="9">
         <v>1</v>
@@ -2276,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G15" s="9">
         <v>1</v>
@@ -2324,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G16" s="9">
         <v>1</v>
@@ -2372,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G17" s="9">
         <v>1</v>
@@ -2420,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
@@ -2470,7 +2483,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="G19" s="9">
         <v>1</v>
@@ -2530,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G20" s="9">
         <v>1</v>
@@ -3171,8 +3184,8 @@
       <c r="E31" s="9">
         <v>2</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>77</v>
+      <c r="F31" s="20" t="s">
+        <v>274</v>
       </c>
       <c r="G31" s="9">
         <v>1</v>
@@ -3229,8 +3242,8 @@
       <c r="E32" s="9">
         <v>2</v>
       </c>
-      <c r="F32" s="9" t="s">
-        <v>77</v>
+      <c r="F32" s="20" t="s">
+        <v>274</v>
       </c>
       <c r="G32" s="9">
         <v>1</v>
@@ -3288,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G33" s="9">
         <v>1</v>
@@ -4967,8 +4980,8 @@
       <c r="E65" s="11">
         <v>5</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>170</v>
+      <c r="F65" s="25" t="s">
+        <v>279</v>
       </c>
       <c r="G65" s="11">
         <v>1</v>
@@ -4998,7 +5011,7 @@
       <c r="P65" s="11"/>
       <c r="Q65" s="11"/>
       <c r="R65" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="S65" s="11"/>
       <c r="T65" s="11" t="s">
@@ -5008,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="V65" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -5017,14 +5030,14 @@
         <v>5002</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="12">
         <v>5</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5069,14 +5082,14 @@
         <v>5003</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D67" s="10"/>
       <c r="E67" s="12">
         <v>5</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G67" s="10">
         <v>1</v>
@@ -5119,14 +5132,14 @@
         <v>5004</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D68" s="10"/>
       <c r="E68" s="12">
         <v>5</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G68" s="10">
         <v>1</v>
@@ -5169,14 +5182,14 @@
         <v>5005</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D69" s="10"/>
       <c r="E69" s="12">
         <v>5</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G69" s="10">
         <v>1</v>
@@ -5219,14 +5232,14 @@
         <v>5006</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D70" s="10"/>
       <c r="E70" s="12">
         <v>5</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G70" s="10">
         <v>1</v>
@@ -5269,14 +5282,14 @@
         <v>5007</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="12">
         <v>5</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G71" s="10">
         <v>1</v>
@@ -5319,14 +5332,14 @@
         <v>5008</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D72" s="10"/>
       <c r="E72" s="12">
         <v>5</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G72" s="10">
         <v>1</v>
@@ -5369,14 +5382,14 @@
         <v>5009</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="12">
         <v>5</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G73" s="10">
         <v>1</v>
@@ -5421,14 +5434,14 @@
         <v>6001</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D74" s="11"/>
       <c r="E74" s="11">
         <v>6</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G74" s="14">
         <v>1</v>
@@ -5473,14 +5486,14 @@
         <v>6002</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="9">
         <v>6</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G75" s="10">
         <v>1</v>
@@ -5525,14 +5538,14 @@
         <v>6003</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="9">
         <v>6</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G76" s="10">
         <v>1</v>
@@ -5577,14 +5590,14 @@
         <v>6004</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="9">
         <v>6</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -5629,14 +5642,14 @@
         <v>6005</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="9">
         <v>6</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G78" s="10">
         <v>1</v>
@@ -5681,14 +5694,14 @@
         <v>6006</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="9">
         <v>6</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G79" s="10">
         <v>1</v>
@@ -5733,14 +5746,14 @@
         <v>6007</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="9">
         <v>6</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G80" s="10">
         <v>1</v>
@@ -5785,14 +5798,14 @@
         <v>6008</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="9">
         <v>6</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G81" s="10">
         <v>1</v>
@@ -5837,14 +5850,14 @@
         <v>6009</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="9">
         <v>6</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G82" s="10">
         <v>1</v>
@@ -5889,14 +5902,14 @@
         <v>6010</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="9">
         <v>6</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G83" s="10">
         <v>1</v>
@@ -5941,14 +5954,14 @@
         <v>6011</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9">
         <v>6</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G84" s="10">
         <v>1</v>
@@ -5993,14 +6006,14 @@
         <v>6012</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="9">
         <v>6</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G85" s="10">
         <v>1</v>
@@ -6045,14 +6058,14 @@
         <v>6013</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="9">
         <v>6</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G86" s="10">
         <v>1</v>
@@ -6097,14 +6110,14 @@
         <v>6014</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="9">
         <v>6</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G87" s="10">
         <v>1</v>
@@ -6149,14 +6162,14 @@
         <v>6015</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="9">
         <v>6</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G88" s="10">
         <v>1</v>
@@ -6201,14 +6214,14 @@
         <v>7001</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D89" s="14"/>
       <c r="E89" s="14">
         <v>7</v>
       </c>
-      <c r="F89" s="14" t="s">
-        <v>212</v>
+      <c r="F89" s="23" t="s">
+        <v>275</v>
       </c>
       <c r="G89" s="14">
         <v>1</v>
@@ -6256,14 +6269,14 @@
         <v>7002</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D90" s="10"/>
       <c r="E90" s="10">
         <v>7</v>
       </c>
-      <c r="F90" s="10" t="s">
-        <v>214</v>
+      <c r="F90" s="24" t="s">
+        <v>276</v>
       </c>
       <c r="G90" s="10">
         <v>1</v>
@@ -6306,14 +6319,14 @@
         <v>7003</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10">
         <v>7</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>216</v>
+      <c r="F91" s="24" t="s">
+        <v>277</v>
       </c>
       <c r="G91" s="10">
         <v>1</v>
@@ -6356,14 +6369,14 @@
         <v>7004</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D92" s="10"/>
       <c r="E92" s="10">
         <v>7</v>
       </c>
-      <c r="F92" s="10" t="s">
-        <v>218</v>
+      <c r="F92" s="24" t="s">
+        <v>278</v>
       </c>
       <c r="G92" s="10">
         <v>1</v>
@@ -6406,14 +6419,14 @@
         <v>8001</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D93" s="14"/>
       <c r="E93" s="14">
         <v>8</v>
       </c>
       <c r="F93" s="23" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G93" s="10">
         <v>1</v>
@@ -6461,14 +6474,14 @@
         <v>8002</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D94" s="10"/>
       <c r="E94" s="10">
         <v>8</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G94" s="10">
         <v>1</v>
@@ -6511,14 +6524,14 @@
         <v>8003</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="10">
         <v>8</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G95" s="10">
         <v>1</v>
@@ -6561,14 +6574,14 @@
         <v>8004</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D96" s="10"/>
       <c r="E96" s="10">
         <v>8</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G96" s="10">
         <v>1</v>
@@ -6611,14 +6624,14 @@
         <v>8005</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D97" s="10"/>
       <c r="E97" s="10">
         <v>8</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G97" s="10">
         <v>1</v>
@@ -6661,14 +6674,14 @@
         <v>8006</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D98" s="10"/>
       <c r="E98" s="10">
         <v>8</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G98" s="10">
         <v>1</v>
@@ -6711,14 +6724,14 @@
         <v>8007</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D99" s="10"/>
       <c r="E99" s="10">
         <v>8</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G99" s="10">
         <v>1</v>
@@ -6761,14 +6774,14 @@
         <v>8008</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D100" s="10"/>
       <c r="E100" s="10">
         <v>8</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G100" s="10">
         <v>1</v>
@@ -6811,14 +6824,14 @@
         <v>8009</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D101" s="10"/>
       <c r="E101" s="10">
         <v>8</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G101" s="10">
         <v>1</v>
@@ -6861,14 +6874,14 @@
         <v>8010</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D102" s="10"/>
       <c r="E102" s="10">
         <v>8</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G102" s="10">
         <v>1</v>
@@ -6911,14 +6924,14 @@
         <v>8011</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D103" s="10"/>
       <c r="E103" s="10">
         <v>8</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G103" s="10">
         <v>1</v>
@@ -6961,14 +6974,14 @@
         <v>8012</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D104" s="10"/>
       <c r="E104" s="10">
         <v>8</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G104" s="10">
         <v>1</v>
@@ -7011,14 +7024,14 @@
         <v>8013</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D105" s="10"/>
       <c r="E105" s="10">
         <v>8</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G105" s="10">
         <v>1</v>
@@ -7061,14 +7074,14 @@
         <v>8014</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D106" s="10"/>
       <c r="E106" s="10">
         <v>8</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G106" s="10">
         <v>1</v>
@@ -8916,19 +8929,19 @@
   <sheetData>
     <row r="19" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="M19" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N19" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="P19" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="R19" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="12:18" x14ac:dyDescent="0.3">
@@ -8942,10 +8955,10 @@
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -8960,16 +8973,16 @@
         <v>5002</v>
       </c>
       <c r="M21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -8984,16 +8997,16 @@
         <v>5003</v>
       </c>
       <c r="M22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -9008,16 +9021,16 @@
         <v>5004</v>
       </c>
       <c r="M23" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -9032,16 +9045,16 @@
         <v>5005</v>
       </c>
       <c r="M24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24" t="s">
+        <v>233</v>
+      </c>
+      <c r="P24" t="s">
         <v>238</v>
-      </c>
-      <c r="P24" t="s">
-        <v>243</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -9056,16 +9069,16 @@
         <v>5006</v>
       </c>
       <c r="M25" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P25" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -9080,16 +9093,16 @@
         <v>5007</v>
       </c>
       <c r="M26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P26" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -9104,16 +9117,16 @@
         <v>5008</v>
       </c>
       <c r="M27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P27" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -9128,16 +9141,16 @@
         <v>5009</v>
       </c>
       <c r="M28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P28" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -9152,13 +9165,13 @@
         <v>6001</v>
       </c>
       <c r="M29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -9173,13 +9186,13 @@
         <v>6002</v>
       </c>
       <c r="M30" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P30" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -9194,13 +9207,13 @@
         <v>6003</v>
       </c>
       <c r="M31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P31" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -9215,13 +9228,13 @@
         <v>6004</v>
       </c>
       <c r="M32" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P32" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -9236,13 +9249,13 @@
         <v>6005</v>
       </c>
       <c r="M33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P33" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -9257,13 +9270,13 @@
         <v>6006</v>
       </c>
       <c r="M34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O34" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P34" t="s">
         <v>248</v>
-      </c>
-      <c r="P34" t="s">
-        <v>253</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -9278,13 +9291,13 @@
         <v>6007</v>
       </c>
       <c r="M35" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O35" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P35" t="s">
         <v>248</v>
-      </c>
-      <c r="P35" t="s">
-        <v>253</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -9299,13 +9312,13 @@
         <v>6008</v>
       </c>
       <c r="M36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P36" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -9320,13 +9333,13 @@
         <v>6009</v>
       </c>
       <c r="M37" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P37" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -9341,13 +9354,13 @@
         <v>6010</v>
       </c>
       <c r="M38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O38" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P38" t="s">
         <v>248</v>
-      </c>
-      <c r="P38" t="s">
-        <v>253</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -9362,13 +9375,13 @@
         <v>6011</v>
       </c>
       <c r="M39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O39" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P39" t="s">
         <v>248</v>
-      </c>
-      <c r="P39" t="s">
-        <v>253</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -9383,13 +9396,13 @@
         <v>6012</v>
       </c>
       <c r="M40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O40" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P40" t="s">
         <v>248</v>
-      </c>
-      <c r="P40" t="s">
-        <v>253</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -9404,13 +9417,13 @@
         <v>6013</v>
       </c>
       <c r="M41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -9425,13 +9438,13 @@
         <v>6014</v>
       </c>
       <c r="M42" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -9446,13 +9459,13 @@
         <v>6015</v>
       </c>
       <c r="M43" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="P43" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -9467,16 +9480,16 @@
         <v>7001</v>
       </c>
       <c r="M44" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N44">
         <v>7</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P44" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -9491,16 +9504,16 @@
         <v>7002</v>
       </c>
       <c r="M45" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P45" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -9515,16 +9528,16 @@
         <v>7003</v>
       </c>
       <c r="M46" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P46" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -9539,16 +9552,16 @@
         <v>7004</v>
       </c>
       <c r="M47" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P47" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -9563,16 +9576,16 @@
         <v>8001</v>
       </c>
       <c r="M48" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -9587,16 +9600,16 @@
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -9611,16 +9624,16 @@
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -9635,16 +9648,16 @@
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -9659,16 +9672,16 @@
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -9683,16 +9696,16 @@
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -9707,16 +9720,16 @@
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -9731,16 +9744,16 @@
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -9755,16 +9768,16 @@
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -9779,16 +9792,16 @@
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -9803,16 +9816,16 @@
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -9827,16 +9840,16 @@
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -9851,16 +9864,16 @@
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -9875,16 +9888,16 @@
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED207A91-E7D3-410F-81E6-089896C25602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="289">
   <si>
     <t>##var</t>
   </si>
@@ -105,6 +99,15 @@
     <t>eat_Effect</t>
   </si>
   <si>
+    <t>if_popcorn</t>
+  </si>
+  <si>
+    <t>if_hidden_door</t>
+  </si>
+  <si>
+    <t>if_lake</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -180,6 +183,15 @@
     <t>吞下时效果</t>
   </si>
   <si>
+    <t>是否会被爆米花机吃</t>
+  </si>
+  <si>
+    <t>是否会被隐藏门吃</t>
+  </si>
+  <si>
+    <t>是否会被湖神吃</t>
+  </si>
+  <si>
     <t>唯一id</t>
   </si>
   <si>
@@ -225,52 +237,100 @@
     <t>0吞下无效果 1吞下有效果</t>
   </si>
   <si>
+    <t>0可以被吞下 1不可以被吞下</t>
+  </si>
+  <si>
+    <t>0可以被隐藏门吃 1不可以被隐藏门吃</t>
+  </si>
+  <si>
+    <t>0可以被湖神吃 1不可以被湖神吃</t>
+  </si>
+  <si>
     <t>土豆-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag Potato</t>
+  </si>
+  <si>
     <t>蘑菇-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/seedbag</t>
+  </si>
+  <si>
     <t>南瓜-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag Pumkin</t>
+  </si>
+  <si>
     <t>胡萝卜-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag Carrot</t>
+  </si>
+  <si>
     <t>水甜菜-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag Beet</t>
+  </si>
+  <si>
     <t>番茄-红-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag TomatoRed</t>
+  </si>
+  <si>
     <t>番茄-橙-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag TomatoOrange</t>
+  </si>
+  <si>
     <t>番茄-黄-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag TomatoYellow</t>
+  </si>
+  <si>
     <t>番茄-绿-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag TomatoGreen</t>
+  </si>
+  <si>
     <t>番茄-青-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag TomatoCyan</t>
+  </si>
+  <si>
     <t>番茄-蓝-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag TomatoBlue</t>
+  </si>
+  <si>
     <t>番茄-紫-种子袋</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag TomatoPurple</t>
+  </si>
+  <si>
     <t>花椰菜-种子袋(一次性)</t>
   </si>
   <si>
+    <t>prefab/plant/SeedBag CauliFlower</t>
+  </si>
+  <si>
     <t>花椰菜-种子袋(永久)</t>
   </si>
   <si>
     <t>土豆</t>
   </si>
   <si>
-    <t>plant/mushroom_002</t>
+    <t>prefab/plant/PotatoModel</t>
   </si>
   <si>
     <t>台球音效</t>
@@ -285,6 +345,9 @@
     <t>蘑菇</t>
   </si>
   <si>
+    <t>prefab/plant/mushroom_002</t>
+  </si>
+  <si>
     <t>弹飞触碰到的道具，玩家</t>
   </si>
   <si>
@@ -294,7 +357,7 @@
     <t>南瓜</t>
   </si>
   <si>
-    <t>plant/Pumpkin</t>
+    <t>prefab/plant/Pumpkin</t>
   </si>
   <si>
     <t>吞入碰到的作物/玩家，吞下作物1s吐出（此时不会吞下其他作物/玩家，玩家也无法交互），吞下玩家，玩家模型消失，屏幕显示南瓜头（玩家此时只能按任意方向键从按下的方向键出来）</t>
@@ -309,7 +372,7 @@
     <t>胡萝卜</t>
   </si>
   <si>
-    <t>plant/Carrot</t>
+    <t>prefab/plant/Carrot</t>
   </si>
   <si>
     <t>瓶子音效</t>
@@ -327,7 +390,7 @@
     <t>水甜菜</t>
   </si>
   <si>
-    <t>plant/Beet</t>
+    <t>prefab/plant/Beet</t>
   </si>
   <si>
     <t>无效果</t>
@@ -342,7 +405,7 @@
     <t>番茄-红</t>
   </si>
   <si>
-    <t>plant/Tomato_red</t>
+    <t>prefab/plant/Tomato_red</t>
   </si>
   <si>
     <t>染色</t>
@@ -360,13 +423,13 @@
     <t>番茄-黄</t>
   </si>
   <si>
-    <t>plant/Tomato_yellow</t>
+    <t>prefab/plant/Tomato_yellow</t>
   </si>
   <si>
     <t>番茄-绿</t>
   </si>
   <si>
-    <t>plant/Tomato_green</t>
+    <t>prefab/plant/Tomato_green</t>
   </si>
   <si>
     <t>番茄-青</t>
@@ -381,6 +444,9 @@
     <t>花椰菜</t>
   </si>
   <si>
+    <t>prefab/plant/Cauliflower</t>
+  </si>
+  <si>
     <t>碰到播放音效，“咩”</t>
   </si>
   <si>
@@ -393,7 +459,7 @@
     <t>猕猴桃</t>
   </si>
   <si>
-    <t>plant/Kiwi</t>
+    <t>prefab/plant/mihoutao</t>
   </si>
   <si>
     <t>保龄球音效</t>
@@ -549,61 +615,64 @@
     <t>洒水壶</t>
   </si>
   <si>
+    <t>prefab/Item/Wateringpot</t>
+  </si>
+  <si>
     <t>删除染色</t>
   </si>
   <si>
     <t>莲叶</t>
   </si>
   <si>
-    <t>Item/Lotus_Leaf</t>
+    <t>prefab/Item/Lotus_Leaf</t>
   </si>
   <si>
     <t>猕猴桃树</t>
   </si>
   <si>
-    <t>Item/Kiwi_Tree</t>
+    <t>prefab/Item/Kiwi_Tree</t>
   </si>
   <si>
     <t>灌木丛根</t>
   </si>
   <si>
-    <t>Item/Bush_Root</t>
+    <t>prefab/Item/Bush_Root</t>
   </si>
   <si>
     <t>传送门</t>
   </si>
   <si>
-    <t>Item/Portal</t>
+    <t>prefab/Item/Portal</t>
   </si>
   <si>
     <t>隐藏门</t>
   </si>
   <si>
-    <t>Item/Hidden_Door</t>
+    <t>prefab/Item/Hidden_Door</t>
   </si>
   <si>
     <t>钥匙</t>
   </si>
   <si>
-    <t>Item/Key</t>
+    <t>prefab/Item/Key</t>
   </si>
   <si>
     <t>爆米花机</t>
   </si>
   <si>
-    <t>Item/Popcorn_Machine</t>
+    <t>prefab/Item/Popcorn_Machine</t>
   </si>
   <si>
     <t>爆米花-花椰菜汤味</t>
   </si>
   <si>
-    <t>Item/Popcorn_Cauliflower_Soup_Flavor</t>
+    <t>prefab/Item/Popcorn_Cauliflower_Soup_Flavor</t>
   </si>
   <si>
     <t>土豆-房子</t>
   </si>
   <si>
-    <t>Bulit/mushroom_002</t>
+    <t>prefab/Bulit/mushroom_002</t>
   </si>
   <si>
     <t>蘑菇-房子</t>
@@ -612,25 +681,25 @@
     <t>南瓜-房子</t>
   </si>
   <si>
-    <t>Bulit/Pumpkin</t>
+    <t>prefab/Bulit/Pumpkin</t>
   </si>
   <si>
     <t>胡萝卜-房子</t>
   </si>
   <si>
-    <t>Bulit/Carrot</t>
+    <t>prefab/Bulit/Carrot</t>
   </si>
   <si>
     <t>水甜菜-房子</t>
   </si>
   <si>
-    <t>Bulit/Beet</t>
+    <t>prefab/Bulit/Beet</t>
   </si>
   <si>
     <t>番茄-红-房子</t>
   </si>
   <si>
-    <t>Bulit/Tomato_red</t>
+    <t>prefab/Bulit/Tomato_red</t>
   </si>
   <si>
     <t>番茄-橙-房子</t>
@@ -639,13 +708,13 @@
     <t>番茄-黄-房子</t>
   </si>
   <si>
-    <t>Bulit/Tomato_yellow</t>
+    <t>prefab/Bulit/Tomato_yellow</t>
   </si>
   <si>
     <t>番茄-绿-房子</t>
   </si>
   <si>
-    <t>Bulit/Tomato_green</t>
+    <t>prefab/Bulit/Tomato_green</t>
   </si>
   <si>
     <t>番茄-青-房子</t>
@@ -663,7 +732,7 @@
     <t>猕猴桃-房子</t>
   </si>
   <si>
-    <t>Bulit/Kiwi</t>
+    <t>prefab/Bulit/Kiwi</t>
   </si>
   <si>
     <t>野草-房子</t>
@@ -672,18 +741,33 @@
     <t>甜菜女士</t>
   </si>
   <si>
+    <t>prefab/Npc/Character_beet</t>
+  </si>
+  <si>
     <t>花椰菜羊-白</t>
   </si>
   <si>
+    <t>prefab/Npc/sheep_White</t>
+  </si>
+  <si>
     <t>花椰菜羊-绿</t>
   </si>
   <si>
+    <t>prefab/Npc/sheep_Green</t>
+  </si>
+  <si>
     <t>猴子先生</t>
   </si>
   <si>
+    <t>prefab/Npc/Character_monkey</t>
+  </si>
+  <si>
     <t>土豆-幼苗</t>
   </si>
   <si>
+    <t>prefab/plant/Seedling</t>
+  </si>
+  <si>
     <t>蘑菇-幼苗</t>
   </si>
   <si>
@@ -814,103 +898,19 @@
   </si>
   <si>
     <t>seedling</t>
-  </si>
-  <si>
-    <t>是否会被爆米花机吃</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否会被隐藏门吃</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否会被湖神吃</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>0可以被吞下 1不可以被吞下</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>0可以被隐藏门吃 1不可以被隐藏门吃</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>0可以被湖神吃 1不可以被湖神吃</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>if_popcorn</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>if_hidden_door</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>if_lake</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>plant/mihoutao</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>plant/mushroom_002</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>plant/PotatoModel</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>plant/seedbag</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>plant/Seedling</t>
-  </si>
-  <si>
-    <t>plant/Seedling</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>plant/Cauliflower</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Npc/Character_beet</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Npc/sheep_White</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Npc/sheep_Green</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Npc/Character_monkey</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item/Wateringpot</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -950,23 +950,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -975,7 +961,6 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -983,12 +968,155 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1013,8 +1141,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1098,6 +1412,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FFDEE0E3"/>
       </left>
@@ -1114,22 +1439,253 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFDEE0E3"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1139,77 +1695,121 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1467,31 +2067,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AA188"/>
-  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="12.1640625" style="4"/>
-    <col min="3" max="3" width="22.83203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.1640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="26.5" style="4" customWidth="1"/>
+    <col min="1" max="2" width="12.1666666666667" style="4"/>
+    <col min="3" max="3" width="22.8333333333333" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.1666666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.8333333333333" style="4" customWidth="1"/>
+    <col min="6" max="6" width="36.75" style="4" customWidth="1"/>
     <col min="7" max="8" width="16.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.08203125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.0833333333333" style="4" customWidth="1"/>
     <col min="10" max="12" width="16.75" style="4" customWidth="1"/>
-    <col min="13" max="17" width="12.1640625" style="4"/>
-    <col min="18" max="19" width="17.9140625" style="4" customWidth="1"/>
-    <col min="20" max="21" width="26.33203125" style="4" customWidth="1"/>
-    <col min="22" max="22" width="12.1640625" style="4"/>
-    <col min="28" max="16384" width="12.1640625" style="4"/>
+    <col min="13" max="17" width="12.1666666666667" style="4"/>
+    <col min="18" max="19" width="17.9166666666667" style="4" customWidth="1"/>
+    <col min="20" max="21" width="26.3333333333333" style="4" customWidth="1"/>
+    <col min="22" max="22" width="12.1666666666667" style="4"/>
+    <col min="28" max="16384" width="12.1666666666667" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1558,261 +2158,261 @@
       <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="X1" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="Y1" s="21" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="V2" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S3" s="6" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>259</v>
+        <v>50</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>260</v>
+        <v>51</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="W4" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="X4" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="Y4" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y4" s="11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="10"/>
       <c r="B5" s="9">
         <v>1001</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9">
         <v>1</v>
       </c>
-      <c r="F5" s="20" t="s">
-        <v>271</v>
+      <c r="F5" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="G5" s="9">
         <v>1</v>
@@ -1828,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M5" s="9">
         <v>1</v>
@@ -1846,20 +2446,20 @@
       </c>
       <c r="V5" s="9"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22">
       <c r="A6" s="10"/>
       <c r="B6" s="9">
         <v>1002</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>271</v>
+      <c r="F6" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="G6" s="9">
         <v>1</v>
@@ -1875,7 +2475,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M6" s="9">
         <v>1</v>
@@ -1893,20 +2493,20 @@
       </c>
       <c r="V6" s="9"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22">
       <c r="A7" s="10"/>
       <c r="B7" s="9">
         <v>1003</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>271</v>
+      <c r="F7" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="G7" s="9">
         <v>1</v>
@@ -1922,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M7" s="9">
         <v>1</v>
@@ -1940,20 +2540,20 @@
       </c>
       <c r="V7" s="9"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22">
       <c r="A8" s="10"/>
       <c r="B8" s="9">
         <v>1004</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9">
         <v>1</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>271</v>
+      <c r="F8" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="G8" s="9">
         <v>1</v>
@@ -1969,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M8" s="9">
         <v>1</v>
@@ -1988,20 +2588,20 @@
       </c>
       <c r="V8" s="9"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22">
       <c r="A9" s="10"/>
       <c r="B9" s="9">
         <v>1005</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9">
         <v>1</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>271</v>
+      <c r="F9" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="G9" s="9">
         <v>1</v>
@@ -2017,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M9" s="9">
         <v>1</v>
@@ -2036,20 +2636,20 @@
       </c>
       <c r="V9" s="9"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22">
       <c r="A10" s="10"/>
       <c r="B10" s="9">
         <v>1006</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9">
         <v>1</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>271</v>
+      <c r="F10" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="G10" s="9">
         <v>1</v>
@@ -2065,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M10" s="9">
         <v>1</v>
@@ -2084,20 +2684,20 @@
       </c>
       <c r="V10" s="9"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22">
       <c r="A11" s="10"/>
       <c r="B11" s="9">
         <v>1007</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9">
         <v>1</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>271</v>
+      <c r="F11" s="11" t="s">
+        <v>84</v>
       </c>
       <c r="G11" s="9">
         <v>1</v>
@@ -2113,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M11" s="9">
         <v>1</v>
@@ -2132,20 +2732,20 @@
       </c>
       <c r="V11" s="9"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22">
       <c r="A12" s="10"/>
       <c r="B12" s="9">
         <v>1008</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9">
         <v>1</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>271</v>
+      <c r="F12" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="G12" s="9">
         <v>1</v>
@@ -2161,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M12" s="9">
         <v>1</v>
@@ -2180,20 +2780,20 @@
       </c>
       <c r="V12" s="9"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22">
       <c r="A13" s="10"/>
       <c r="B13" s="9">
         <v>1009</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9">
         <v>1</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>271</v>
+      <c r="F13" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="G13" s="9">
         <v>1</v>
@@ -2209,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M13" s="9">
         <v>1</v>
@@ -2228,20 +2828,20 @@
       </c>
       <c r="V13" s="9"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22">
       <c r="A14" s="10"/>
       <c r="B14" s="9">
         <v>1010</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9">
         <v>1</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>271</v>
+      <c r="F14" s="11" t="s">
+        <v>90</v>
       </c>
       <c r="G14" s="9">
         <v>1</v>
@@ -2257,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M14" s="9">
         <v>1</v>
@@ -2276,20 +2876,20 @@
       </c>
       <c r="V14" s="9"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22">
       <c r="A15" s="10"/>
       <c r="B15" s="9">
         <v>1011</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9">
         <v>1</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>271</v>
+      <c r="F15" s="11" t="s">
+        <v>92</v>
       </c>
       <c r="G15" s="9">
         <v>1</v>
@@ -2305,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M15" s="9">
         <v>1</v>
@@ -2324,20 +2924,20 @@
       </c>
       <c r="V15" s="9"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22">
       <c r="A16" s="10"/>
       <c r="B16" s="9">
         <v>1012</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9">
         <v>1</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>271</v>
+      <c r="F16" s="11" t="s">
+        <v>94</v>
       </c>
       <c r="G16" s="9">
         <v>1</v>
@@ -2353,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M16" s="9">
         <v>1</v>
@@ -2372,20 +2972,20 @@
       </c>
       <c r="V16" s="9"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22">
       <c r="A17" s="10"/>
       <c r="B17" s="9">
         <v>1013</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9">
         <v>1</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>271</v>
+      <c r="F17" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="G17" s="9">
         <v>1</v>
@@ -2401,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M17" s="9">
         <v>1</v>
@@ -2420,20 +3020,20 @@
       </c>
       <c r="V17" s="9"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22">
       <c r="A18" s="9"/>
       <c r="B18" s="9">
         <v>1014</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9">
         <v>1</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>271</v>
+      <c r="F18" s="11" t="s">
+        <v>96</v>
       </c>
       <c r="G18" s="9">
         <v>1</v>
@@ -2449,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M18" s="9">
         <v>1</v>
@@ -2470,25 +3070,25 @@
       </c>
       <c r="V18" s="9"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11">
+    <row r="19" s="2" customFormat="1" spans="1:22">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12">
         <v>2001</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11">
+      <c r="C19" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12">
         <v>2</v>
       </c>
-      <c r="F19" s="22" t="s">
-        <v>270</v>
+      <c r="F19" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="G19" s="9">
         <v>1</v>
       </c>
-      <c r="H19" s="11">
+      <c r="H19" s="12">
         <v>3001</v>
       </c>
       <c r="I19" s="9">
@@ -2501,49 +3101,49 @@
         <v>0</v>
       </c>
       <c r="L19" s="9">
+        <v>0.3</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0</v>
+      </c>
+      <c r="N19" s="12">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4">
+        <v>1</v>
+      </c>
+      <c r="P19" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="M19" s="11">
-        <v>0</v>
-      </c>
-      <c r="N19" s="11">
-        <v>0</v>
-      </c>
-      <c r="O19" s="4">
-        <v>1</v>
-      </c>
-      <c r="P19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="R19" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="U19" s="11">
-        <v>1</v>
-      </c>
-      <c r="V19" s="11"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="Q19" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="R19" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="U19" s="12">
+        <v>1</v>
+      </c>
+      <c r="V19" s="12"/>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="9"/>
       <c r="B20" s="9">
         <v>2002</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9">
         <v>2</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>269</v>
+      <c r="F20" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="G20" s="9">
         <v>1</v>
@@ -2563,10 +3163,10 @@
       <c r="L20" s="9">
         <v>0.3</v>
       </c>
-      <c r="M20" s="11">
-        <v>0</v>
-      </c>
-      <c r="N20" s="11">
+      <c r="M20" s="12">
+        <v>0</v>
+      </c>
+      <c r="N20" s="12">
         <v>0</v>
       </c>
       <c r="O20" s="4">
@@ -2575,33 +3175,33 @@
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="9" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="S20" s="9"/>
       <c r="T20" s="9" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="U20" s="9">
         <v>1</v>
       </c>
       <c r="V20" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="9"/>
       <c r="B21" s="9">
         <v>2003</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9">
         <v>2</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="G21" s="9">
         <v>1</v>
@@ -2621,10 +3221,10 @@
       <c r="L21" s="9">
         <v>0.35</v>
       </c>
-      <c r="M21" s="11">
-        <v>0</v>
-      </c>
-      <c r="N21" s="11">
+      <c r="M21" s="12">
+        <v>0</v>
+      </c>
+      <c r="N21" s="12">
         <v>0</v>
       </c>
       <c r="O21" s="4">
@@ -2633,33 +3233,33 @@
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="9" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="S21" s="9"/>
       <c r="T21" s="9" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="U21" s="9">
         <v>1</v>
       </c>
       <c r="V21" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="9"/>
       <c r="B22" s="9">
         <v>2004</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9">
         <v>2</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="G22" s="9">
         <v>1</v>
@@ -2677,51 +3277,51 @@
         <v>0</v>
       </c>
       <c r="L22" s="9">
-        <v>100</v>
-      </c>
-      <c r="M22" s="11">
-        <v>0</v>
-      </c>
-      <c r="N22" s="11">
+        <v>0.45</v>
+      </c>
+      <c r="M22" s="12">
+        <v>0</v>
+      </c>
+      <c r="N22" s="12">
         <v>0</v>
       </c>
       <c r="O22" s="4">
         <v>1</v>
       </c>
       <c r="P22" s="9" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="R22" s="9" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="S22" s="9"/>
       <c r="T22" s="9" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="U22" s="9">
         <v>1</v>
       </c>
       <c r="V22" s="9" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="9"/>
       <c r="B23" s="9">
         <v>2005</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9">
         <v>2</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="G23" s="9">
         <v>1</v>
@@ -2739,12 +3339,12 @@
         <v>0</v>
       </c>
       <c r="L23" s="9">
-        <v>100</v>
-      </c>
-      <c r="M23" s="11">
-        <v>0</v>
-      </c>
-      <c r="N23" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M23" s="12">
+        <v>0</v>
+      </c>
+      <c r="N23" s="12">
         <v>0</v>
       </c>
       <c r="O23" s="4">
@@ -2753,33 +3353,33 @@
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="9" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="S23" s="9"/>
       <c r="T23" s="9" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="U23" s="9">
         <v>1</v>
       </c>
       <c r="V23" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="9"/>
       <c r="B24" s="9">
         <v>2006</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9">
         <v>2</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G24" s="9">
         <v>1</v>
@@ -2797,12 +3397,12 @@
         <v>0</v>
       </c>
       <c r="L24" s="9">
-        <v>100</v>
-      </c>
-      <c r="M24" s="11">
-        <v>0</v>
-      </c>
-      <c r="N24" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M24" s="12">
+        <v>0</v>
+      </c>
+      <c r="N24" s="12">
         <v>0</v>
       </c>
       <c r="O24" s="4">
@@ -2811,33 +3411,33 @@
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S24" s="9"/>
       <c r="T24" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="U24" s="9">
         <v>1</v>
       </c>
       <c r="V24" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="9"/>
       <c r="B25" s="9">
         <v>2007</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9">
         <v>2</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G25" s="9">
         <v>1</v>
@@ -2855,12 +3455,12 @@
         <v>0</v>
       </c>
       <c r="L25" s="9">
-        <v>100</v>
-      </c>
-      <c r="M25" s="11">
-        <v>0</v>
-      </c>
-      <c r="N25" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M25" s="12">
+        <v>0</v>
+      </c>
+      <c r="N25" s="12">
         <v>0</v>
       </c>
       <c r="O25" s="4">
@@ -2869,33 +3469,33 @@
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S25" s="9"/>
       <c r="T25" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="U25" s="9">
         <v>1</v>
       </c>
       <c r="V25" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="9"/>
       <c r="B26" s="9">
         <v>2008</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9">
         <v>2</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="G26" s="9">
         <v>1</v>
@@ -2913,12 +3513,12 @@
         <v>0</v>
       </c>
       <c r="L26" s="9">
-        <v>100</v>
-      </c>
-      <c r="M26" s="11">
-        <v>0</v>
-      </c>
-      <c r="N26" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M26" s="12">
+        <v>0</v>
+      </c>
+      <c r="N26" s="12">
         <v>0</v>
       </c>
       <c r="O26" s="4">
@@ -2927,33 +3527,33 @@
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S26" s="9"/>
       <c r="T26" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="U26" s="9">
         <v>1</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="9"/>
       <c r="B27" s="9">
         <v>2009</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9">
         <v>2</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="G27" s="9">
         <v>1</v>
@@ -2971,12 +3571,12 @@
         <v>0</v>
       </c>
       <c r="L27" s="9">
-        <v>100</v>
-      </c>
-      <c r="M27" s="11">
-        <v>0</v>
-      </c>
-      <c r="N27" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M27" s="12">
+        <v>0</v>
+      </c>
+      <c r="N27" s="12">
         <v>0</v>
       </c>
       <c r="O27" s="4">
@@ -2985,33 +3585,33 @@
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S27" s="9"/>
       <c r="T27" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="U27" s="9">
         <v>1</v>
       </c>
       <c r="V27" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="9"/>
       <c r="B28" s="9">
         <v>2010</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9">
         <v>2</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G28" s="9">
         <v>1</v>
@@ -3029,12 +3629,12 @@
         <v>0</v>
       </c>
       <c r="L28" s="9">
-        <v>100</v>
-      </c>
-      <c r="M28" s="11">
-        <v>0</v>
-      </c>
-      <c r="N28" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M28" s="12">
+        <v>0</v>
+      </c>
+      <c r="N28" s="12">
         <v>0</v>
       </c>
       <c r="O28" s="4">
@@ -3043,33 +3643,33 @@
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S28" s="9"/>
       <c r="T28" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="U28" s="9">
         <v>1</v>
       </c>
       <c r="V28" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="9"/>
       <c r="B29" s="9">
         <v>2011</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9">
         <v>2</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G29" s="9">
         <v>1</v>
@@ -3087,12 +3687,12 @@
         <v>0</v>
       </c>
       <c r="L29" s="9">
-        <v>100</v>
-      </c>
-      <c r="M29" s="11">
-        <v>0</v>
-      </c>
-      <c r="N29" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M29" s="12">
+        <v>0</v>
+      </c>
+      <c r="N29" s="12">
         <v>0</v>
       </c>
       <c r="O29" s="4">
@@ -3101,33 +3701,33 @@
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S29" s="9"/>
       <c r="T29" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="U29" s="9">
         <v>1</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="9"/>
       <c r="B30" s="9">
         <v>2012</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9">
         <v>2</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G30" s="9">
         <v>1</v>
@@ -3145,12 +3745,12 @@
         <v>0</v>
       </c>
       <c r="L30" s="9">
-        <v>100</v>
-      </c>
-      <c r="M30" s="11">
-        <v>0</v>
-      </c>
-      <c r="N30" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M30" s="12">
+        <v>0</v>
+      </c>
+      <c r="N30" s="12">
         <v>0</v>
       </c>
       <c r="O30" s="4">
@@ -3159,33 +3759,33 @@
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S30" s="9"/>
       <c r="T30" s="9" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="U30" s="9">
         <v>1</v>
       </c>
       <c r="V30" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="9"/>
       <c r="B31" s="9">
         <v>2013</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9">
         <v>2</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>274</v>
+      <c r="F31" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="G31" s="9">
         <v>1</v>
@@ -3203,12 +3803,12 @@
         <v>0</v>
       </c>
       <c r="L31" s="9">
-        <v>100</v>
-      </c>
-      <c r="M31" s="11">
-        <v>0</v>
-      </c>
-      <c r="N31" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M31" s="12">
+        <v>0</v>
+      </c>
+      <c r="N31" s="12">
         <v>0</v>
       </c>
       <c r="O31" s="4">
@@ -3217,33 +3817,33 @@
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="9" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="S31" s="9"/>
       <c r="T31" s="9" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="U31" s="9">
         <v>1</v>
       </c>
       <c r="V31" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="9"/>
       <c r="B32" s="9">
         <v>2014</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9">
         <v>2</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>274</v>
+      <c r="F32" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="G32" s="9">
         <v>1</v>
@@ -3261,12 +3861,12 @@
         <v>0</v>
       </c>
       <c r="L32" s="9">
-        <v>100</v>
-      </c>
-      <c r="M32" s="11">
-        <v>0</v>
-      </c>
-      <c r="N32" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M32" s="12">
+        <v>0</v>
+      </c>
+      <c r="N32" s="12">
         <v>0</v>
       </c>
       <c r="O32" s="4">
@@ -3275,33 +3875,33 @@
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="9" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="S32" s="9"/>
       <c r="T32" s="9" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="U32" s="9">
         <v>1</v>
       </c>
       <c r="V32" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="9"/>
       <c r="B33" s="9">
         <v>2015</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9">
         <v>2</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>268</v>
+      <c r="F33" s="11" t="s">
+        <v>142</v>
       </c>
       <c r="G33" s="9">
         <v>1</v>
@@ -3319,51 +3919,51 @@
         <v>0</v>
       </c>
       <c r="L33" s="9">
-        <v>100</v>
-      </c>
-      <c r="M33" s="11">
-        <v>0</v>
-      </c>
-      <c r="N33" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M33" s="12">
+        <v>0</v>
+      </c>
+      <c r="N33" s="12">
         <v>0</v>
       </c>
       <c r="O33" s="4">
         <v>1</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="R33" s="9" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="S33" s="9"/>
       <c r="T33" s="9" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="U33" s="9">
         <v>1</v>
       </c>
       <c r="V33" s="9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" s="9"/>
       <c r="B34" s="9">
         <v>2016</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9">
         <v>2</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="G34" s="9">
         <v>1</v>
@@ -3381,12 +3981,12 @@
         <v>0</v>
       </c>
       <c r="L34" s="9">
-        <v>100</v>
-      </c>
-      <c r="M34" s="11">
-        <v>0</v>
-      </c>
-      <c r="N34" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M34" s="12">
+        <v>0</v>
+      </c>
+      <c r="N34" s="12">
         <v>0</v>
       </c>
       <c r="O34" s="4">
@@ -3395,38 +3995,38 @@
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="9" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="S34" s="9"/>
       <c r="T34" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="U34" s="9">
+        <v>1</v>
+      </c>
+      <c r="V34" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" spans="1:22">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12">
+        <v>3001</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12">
+        <v>3</v>
+      </c>
+      <c r="F35" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="U34" s="9">
-        <v>1</v>
-      </c>
-      <c r="V34" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11">
-        <v>3001</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11">
-        <v>3</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G35" s="11">
+      <c r="G35" s="12">
         <v>4</v>
       </c>
-      <c r="H35" s="11"/>
+      <c r="H35" s="12"/>
       <c r="I35" s="9">
         <v>0</v>
       </c>
@@ -3437,43 +4037,43 @@
         <v>0</v>
       </c>
       <c r="L35" s="9">
-        <v>100</v>
-      </c>
-      <c r="M35" s="11">
-        <v>0</v>
-      </c>
-      <c r="N35" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M35" s="12">
+        <v>0</v>
+      </c>
+      <c r="N35" s="12">
         <v>0</v>
       </c>
       <c r="O35" s="4">
         <v>1</v>
       </c>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12"/>
       <c r="U35" s="9">
         <v>1</v>
       </c>
-      <c r="V35" s="11"/>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V35" s="12"/>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="9"/>
       <c r="B36" s="9">
         <v>3002</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9">
         <v>3</v>
       </c>
-      <c r="F36" s="9" t="s">
-        <v>77</v>
+      <c r="F36" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="G36" s="9">
         <v>4</v>
@@ -3489,12 +4089,12 @@
         <v>0</v>
       </c>
       <c r="L36" s="9">
-        <v>100</v>
-      </c>
-      <c r="M36" s="11">
-        <v>0</v>
-      </c>
-      <c r="N36" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M36" s="12">
+        <v>0</v>
+      </c>
+      <c r="N36" s="12">
         <v>0</v>
       </c>
       <c r="O36" s="4">
@@ -3503,7 +4103,7 @@
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="9" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="S36" s="9"/>
       <c r="T36" s="9"/>
@@ -3512,20 +4112,20 @@
       </c>
       <c r="V36" s="9"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:22">
       <c r="A37" s="9"/>
       <c r="B37" s="9">
         <v>3003</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9">
         <v>3</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="G37" s="9">
         <v>4</v>
@@ -3541,12 +4141,12 @@
         <v>0</v>
       </c>
       <c r="L37" s="9">
-        <v>100</v>
-      </c>
-      <c r="M37" s="11">
-        <v>0</v>
-      </c>
-      <c r="N37" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M37" s="12">
+        <v>0</v>
+      </c>
+      <c r="N37" s="12">
         <v>0</v>
       </c>
       <c r="O37" s="4">
@@ -3555,7 +4155,7 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="9" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
@@ -3564,20 +4164,20 @@
       </c>
       <c r="V37" s="9"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22">
       <c r="A38" s="9"/>
       <c r="B38" s="9">
         <v>3004</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9">
         <v>3</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="G38" s="9">
         <v>4</v>
@@ -3593,12 +4193,12 @@
         <v>0</v>
       </c>
       <c r="L38" s="9">
-        <v>100</v>
-      </c>
-      <c r="M38" s="11">
-        <v>0</v>
-      </c>
-      <c r="N38" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M38" s="12">
+        <v>0</v>
+      </c>
+      <c r="N38" s="12">
         <v>0</v>
       </c>
       <c r="O38" s="4">
@@ -3607,7 +4207,7 @@
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="9" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="S38" s="9"/>
       <c r="T38" s="9"/>
@@ -3616,20 +4216,20 @@
       </c>
       <c r="V38" s="9"/>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22">
       <c r="A39" s="9"/>
       <c r="B39" s="9">
         <v>3005</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="D39" s="9"/>
       <c r="E39" s="9">
         <v>3</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="G39" s="9">
         <v>4</v>
@@ -3645,12 +4245,12 @@
         <v>0</v>
       </c>
       <c r="L39" s="9">
-        <v>100</v>
-      </c>
-      <c r="M39" s="11">
-        <v>0</v>
-      </c>
-      <c r="N39" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M39" s="12">
+        <v>0</v>
+      </c>
+      <c r="N39" s="12">
         <v>0</v>
       </c>
       <c r="O39" s="4">
@@ -3659,7 +4259,7 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="9" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
@@ -3668,20 +4268,20 @@
       </c>
       <c r="V39" s="9"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22">
       <c r="A40" s="9"/>
       <c r="B40" s="9">
         <v>3006</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D40" s="9"/>
       <c r="E40" s="9">
         <v>3</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G40" s="9">
         <v>4</v>
@@ -3697,12 +4297,12 @@
         <v>0</v>
       </c>
       <c r="L40" s="9">
-        <v>100</v>
-      </c>
-      <c r="M40" s="11">
-        <v>0</v>
-      </c>
-      <c r="N40" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M40" s="12">
+        <v>0</v>
+      </c>
+      <c r="N40" s="12">
         <v>0</v>
       </c>
       <c r="O40" s="4">
@@ -3711,7 +4311,7 @@
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="9" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="S40" s="9"/>
       <c r="T40" s="9"/>
@@ -3720,20 +4320,20 @@
       </c>
       <c r="V40" s="9"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22">
       <c r="A41" s="9"/>
       <c r="B41" s="9">
         <v>3007</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="D41" s="9"/>
       <c r="E41" s="9">
         <v>3</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G41" s="9">
         <v>4</v>
@@ -3749,12 +4349,12 @@
         <v>0</v>
       </c>
       <c r="L41" s="9">
-        <v>100</v>
-      </c>
-      <c r="M41" s="11">
-        <v>0</v>
-      </c>
-      <c r="N41" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M41" s="12">
+        <v>0</v>
+      </c>
+      <c r="N41" s="12">
         <v>0</v>
       </c>
       <c r="O41" s="4">
@@ -3763,7 +4363,7 @@
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="9" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="S41" s="9"/>
       <c r="T41" s="9"/>
@@ -3772,20 +4372,20 @@
       </c>
       <c r="V41" s="9"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22">
       <c r="A42" s="9"/>
       <c r="B42" s="9">
         <v>3008</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="D42" s="9"/>
       <c r="E42" s="9">
         <v>3</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="G42" s="9">
         <v>4</v>
@@ -3801,12 +4401,12 @@
         <v>0</v>
       </c>
       <c r="L42" s="9">
-        <v>100</v>
-      </c>
-      <c r="M42" s="11">
-        <v>0</v>
-      </c>
-      <c r="N42" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M42" s="12">
+        <v>0</v>
+      </c>
+      <c r="N42" s="12">
         <v>0</v>
       </c>
       <c r="O42" s="4">
@@ -3815,7 +4415,7 @@
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="R42" s="9" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="S42" s="9"/>
       <c r="T42" s="9"/>
@@ -3824,20 +4424,20 @@
       </c>
       <c r="V42" s="9"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22">
       <c r="A43" s="9"/>
       <c r="B43" s="9">
         <v>3009</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D43" s="9"/>
       <c r="E43" s="9">
         <v>3</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="G43" s="9">
         <v>4</v>
@@ -3853,12 +4453,12 @@
         <v>0</v>
       </c>
       <c r="L43" s="9">
-        <v>100</v>
-      </c>
-      <c r="M43" s="11">
-        <v>0</v>
-      </c>
-      <c r="N43" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M43" s="12">
+        <v>0</v>
+      </c>
+      <c r="N43" s="12">
         <v>0</v>
       </c>
       <c r="O43" s="4">
@@ -3867,7 +4467,7 @@
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="9" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="S43" s="9"/>
       <c r="T43" s="9"/>
@@ -3876,20 +4476,20 @@
       </c>
       <c r="V43" s="9"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22">
       <c r="A44" s="9"/>
       <c r="B44" s="9">
         <v>3010</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="D44" s="9"/>
       <c r="E44" s="9">
         <v>3</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G44" s="9">
         <v>4</v>
@@ -3905,12 +4505,12 @@
         <v>0</v>
       </c>
       <c r="L44" s="9">
-        <v>100</v>
-      </c>
-      <c r="M44" s="11">
-        <v>0</v>
-      </c>
-      <c r="N44" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M44" s="12">
+        <v>0</v>
+      </c>
+      <c r="N44" s="12">
         <v>0</v>
       </c>
       <c r="O44" s="4">
@@ -3919,7 +4519,7 @@
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
       <c r="R44" s="9" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="S44" s="9"/>
       <c r="T44" s="9"/>
@@ -3928,20 +4528,20 @@
       </c>
       <c r="V44" s="9"/>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22">
       <c r="A45" s="9"/>
       <c r="B45" s="9">
         <v>3011</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="D45" s="9"/>
       <c r="E45" s="9">
         <v>3</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G45" s="9">
         <v>4</v>
@@ -3957,12 +4557,12 @@
         <v>0</v>
       </c>
       <c r="L45" s="9">
-        <v>100</v>
-      </c>
-      <c r="M45" s="11">
-        <v>0</v>
-      </c>
-      <c r="N45" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M45" s="12">
+        <v>0</v>
+      </c>
+      <c r="N45" s="12">
         <v>0</v>
       </c>
       <c r="O45" s="4">
@@ -3971,7 +4571,7 @@
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
       <c r="R45" s="9" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S45" s="9"/>
       <c r="T45" s="9"/>
@@ -3980,20 +4580,20 @@
       </c>
       <c r="V45" s="9"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22">
       <c r="A46" s="9"/>
       <c r="B46" s="9">
         <v>3012</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="D46" s="9"/>
       <c r="E46" s="9">
         <v>3</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G46" s="9">
         <v>4</v>
@@ -4009,12 +4609,12 @@
         <v>0</v>
       </c>
       <c r="L46" s="9">
-        <v>100</v>
-      </c>
-      <c r="M46" s="11">
-        <v>0</v>
-      </c>
-      <c r="N46" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M46" s="12">
+        <v>0</v>
+      </c>
+      <c r="N46" s="12">
         <v>0</v>
       </c>
       <c r="O46" s="4">
@@ -4023,7 +4623,7 @@
       <c r="P46" s="9"/>
       <c r="Q46" s="9"/>
       <c r="R46" s="9" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="S46" s="9"/>
       <c r="T46" s="9"/>
@@ -4032,20 +4632,20 @@
       </c>
       <c r="V46" s="9"/>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22">
       <c r="A47" s="9"/>
       <c r="B47" s="9">
         <v>3013</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>148</v>
+        <v>172</v>
       </c>
       <c r="D47" s="9"/>
       <c r="E47" s="9">
         <v>3</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>77</v>
+      <c r="F47" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="G47" s="9">
         <v>4</v>
@@ -4061,12 +4661,12 @@
         <v>0</v>
       </c>
       <c r="L47" s="9">
-        <v>100</v>
-      </c>
-      <c r="M47" s="11">
-        <v>0</v>
-      </c>
-      <c r="N47" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M47" s="12">
+        <v>0</v>
+      </c>
+      <c r="N47" s="12">
         <v>0</v>
       </c>
       <c r="O47" s="4">
@@ -4075,7 +4675,7 @@
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
       <c r="R47" s="9" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="S47" s="9"/>
       <c r="T47" s="9"/>
@@ -4084,20 +4684,20 @@
       </c>
       <c r="V47" s="9"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22">
       <c r="A48" s="9"/>
       <c r="B48" s="9">
         <v>3014</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="D48" s="9"/>
       <c r="E48" s="9">
         <v>3</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>118</v>
+      <c r="F48" s="11" t="s">
+        <v>142</v>
       </c>
       <c r="G48" s="9">
         <v>4</v>
@@ -4113,12 +4713,12 @@
         <v>0</v>
       </c>
       <c r="L48" s="9">
-        <v>100</v>
-      </c>
-      <c r="M48" s="11">
-        <v>0</v>
-      </c>
-      <c r="N48" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M48" s="12">
+        <v>0</v>
+      </c>
+      <c r="N48" s="12">
         <v>0</v>
       </c>
       <c r="O48" s="4">
@@ -4127,7 +4727,7 @@
       <c r="P48" s="9"/>
       <c r="Q48" s="9"/>
       <c r="R48" s="9" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="S48" s="9"/>
       <c r="T48" s="9"/>
@@ -4136,20 +4736,20 @@
       </c>
       <c r="V48" s="9"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:22">
       <c r="A49" s="9"/>
       <c r="B49" s="9">
         <v>3015</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="D49" s="9"/>
       <c r="E49" s="9">
         <v>3</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="G49" s="9">
         <v>4</v>
@@ -4165,12 +4765,12 @@
         <v>0</v>
       </c>
       <c r="L49" s="9">
-        <v>100</v>
-      </c>
-      <c r="M49" s="11">
-        <v>0</v>
-      </c>
-      <c r="N49" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M49" s="12">
+        <v>0</v>
+      </c>
+      <c r="N49" s="12">
         <v>0</v>
       </c>
       <c r="O49" s="4">
@@ -4179,7 +4779,7 @@
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
       <c r="R49" s="9" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="S49" s="9"/>
       <c r="T49" s="9"/>
@@ -4188,25 +4788,25 @@
       </c>
       <c r="V49" s="9"/>
     </row>
-    <row r="50" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11">
+    <row r="50" s="2" customFormat="1" spans="1:22">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12">
         <v>4001</v>
       </c>
-      <c r="C50" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11">
+      <c r="C50" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12">
         <v>4</v>
       </c>
-      <c r="F50" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G50" s="11">
+      <c r="F50" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" s="12">
         <v>0.5</v>
       </c>
-      <c r="H50" s="11"/>
+      <c r="H50" s="12"/>
       <c r="I50" s="9">
         <v>0</v>
       </c>
@@ -4217,43 +4817,43 @@
         <v>0</v>
       </c>
       <c r="L50" s="9">
-        <v>100</v>
-      </c>
-      <c r="M50" s="11">
-        <v>0</v>
-      </c>
-      <c r="N50" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M50" s="12">
+        <v>0</v>
+      </c>
+      <c r="N50" s="12">
         <v>0</v>
       </c>
       <c r="O50" s="4">
         <v>1</v>
       </c>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11"/>
-      <c r="R50" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="S50" s="11"/>
-      <c r="T50" s="11"/>
+      <c r="P50" s="12"/>
+      <c r="Q50" s="12"/>
+      <c r="R50" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="S50" s="12"/>
+      <c r="T50" s="12"/>
       <c r="U50" s="9">
         <v>1</v>
       </c>
-      <c r="V50" s="11"/>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V50" s="12"/>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" s="9"/>
       <c r="B51" s="9">
         <v>4002</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D51" s="9"/>
       <c r="E51" s="9">
         <v>4</v>
       </c>
-      <c r="F51" s="9" t="s">
-        <v>77</v>
+      <c r="F51" s="11" t="s">
+        <v>104</v>
       </c>
       <c r="G51" s="9">
         <v>0.5</v>
@@ -4269,12 +4869,12 @@
         <v>0</v>
       </c>
       <c r="L51" s="9">
-        <v>100</v>
-      </c>
-      <c r="M51" s="11">
-        <v>0</v>
-      </c>
-      <c r="N51" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M51" s="12">
+        <v>0</v>
+      </c>
+      <c r="N51" s="12">
         <v>0</v>
       </c>
       <c r="O51" s="4">
@@ -4283,7 +4883,7 @@
       <c r="P51" s="9"/>
       <c r="Q51" s="9"/>
       <c r="R51" s="9" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="S51" s="9"/>
       <c r="T51" s="9"/>
@@ -4292,20 +4892,20 @@
       </c>
       <c r="V51" s="9"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:22">
       <c r="A52" s="9"/>
       <c r="B52" s="9">
         <v>4003</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D52" s="9"/>
       <c r="E52" s="9">
         <v>4</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="G52" s="9">
         <v>0.5</v>
@@ -4321,12 +4921,12 @@
         <v>0</v>
       </c>
       <c r="L52" s="9">
-        <v>100</v>
-      </c>
-      <c r="M52" s="11">
-        <v>0</v>
-      </c>
-      <c r="N52" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M52" s="12">
+        <v>0</v>
+      </c>
+      <c r="N52" s="12">
         <v>0</v>
       </c>
       <c r="O52" s="4">
@@ -4335,7 +4935,7 @@
       <c r="P52" s="9"/>
       <c r="Q52" s="9"/>
       <c r="R52" s="9" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="S52" s="9"/>
       <c r="T52" s="9"/>
@@ -4344,20 +4944,20 @@
       </c>
       <c r="V52" s="9"/>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:22">
       <c r="A53" s="9"/>
       <c r="B53" s="9">
         <v>4004</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="D53" s="9"/>
       <c r="E53" s="9">
         <v>4</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="G53" s="9">
         <v>0.5</v>
@@ -4373,12 +4973,12 @@
         <v>0</v>
       </c>
       <c r="L53" s="9">
-        <v>100</v>
-      </c>
-      <c r="M53" s="11">
-        <v>0</v>
-      </c>
-      <c r="N53" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M53" s="12">
+        <v>0</v>
+      </c>
+      <c r="N53" s="12">
         <v>0</v>
       </c>
       <c r="O53" s="4">
@@ -4387,7 +4987,7 @@
       <c r="P53" s="9"/>
       <c r="Q53" s="9"/>
       <c r="R53" s="9" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="S53" s="9"/>
       <c r="T53" s="9"/>
@@ -4396,20 +4996,20 @@
       </c>
       <c r="V53" s="9"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:22">
       <c r="A54" s="9"/>
       <c r="B54" s="9">
         <v>4005</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9">
         <v>4</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="G54" s="9">
         <v>0.5</v>
@@ -4425,12 +5025,12 @@
         <v>0</v>
       </c>
       <c r="L54" s="9">
-        <v>100</v>
-      </c>
-      <c r="M54" s="11">
-        <v>0</v>
-      </c>
-      <c r="N54" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M54" s="12">
+        <v>0</v>
+      </c>
+      <c r="N54" s="12">
         <v>0</v>
       </c>
       <c r="O54" s="4">
@@ -4439,7 +5039,7 @@
       <c r="P54" s="9"/>
       <c r="Q54" s="9"/>
       <c r="R54" s="9" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="S54" s="9"/>
       <c r="T54" s="9"/>
@@ -4448,20 +5048,20 @@
       </c>
       <c r="V54" s="9"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:22">
       <c r="A55" s="9"/>
       <c r="B55" s="9">
         <v>4006</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9">
         <v>4</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G55" s="9">
         <v>0.5</v>
@@ -4477,12 +5077,12 @@
         <v>0</v>
       </c>
       <c r="L55" s="9">
-        <v>100</v>
-      </c>
-      <c r="M55" s="11">
-        <v>0</v>
-      </c>
-      <c r="N55" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M55" s="12">
+        <v>0</v>
+      </c>
+      <c r="N55" s="12">
         <v>0</v>
       </c>
       <c r="O55" s="4">
@@ -4491,7 +5091,7 @@
       <c r="P55" s="9"/>
       <c r="Q55" s="9"/>
       <c r="R55" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S55" s="9"/>
       <c r="T55" s="9"/>
@@ -4500,20 +5100,20 @@
       </c>
       <c r="V55" s="9"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:22">
       <c r="A56" s="9"/>
       <c r="B56" s="9">
         <v>4007</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>160</v>
+        <v>184</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="9">
         <v>4</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G56" s="9">
         <v>0.5</v>
@@ -4529,12 +5129,12 @@
         <v>0</v>
       </c>
       <c r="L56" s="9">
-        <v>100</v>
-      </c>
-      <c r="M56" s="11">
-        <v>0</v>
-      </c>
-      <c r="N56" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M56" s="12">
+        <v>0</v>
+      </c>
+      <c r="N56" s="12">
         <v>0</v>
       </c>
       <c r="O56" s="4">
@@ -4543,7 +5143,7 @@
       <c r="P56" s="9"/>
       <c r="Q56" s="9"/>
       <c r="R56" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S56" s="9"/>
       <c r="T56" s="9"/>
@@ -4552,20 +5152,20 @@
       </c>
       <c r="V56" s="9"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:22">
       <c r="A57" s="9"/>
       <c r="B57" s="9">
         <v>4008</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="D57" s="9"/>
       <c r="E57" s="9">
         <v>4</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="G57" s="9">
         <v>0.5</v>
@@ -4581,12 +5181,12 @@
         <v>0</v>
       </c>
       <c r="L57" s="9">
-        <v>100</v>
-      </c>
-      <c r="M57" s="11">
-        <v>0</v>
-      </c>
-      <c r="N57" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M57" s="12">
+        <v>0</v>
+      </c>
+      <c r="N57" s="12">
         <v>0</v>
       </c>
       <c r="O57" s="4">
@@ -4595,7 +5195,7 @@
       <c r="P57" s="9"/>
       <c r="Q57" s="9"/>
       <c r="R57" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S57" s="9"/>
       <c r="T57" s="9"/>
@@ -4604,20 +5204,20 @@
       </c>
       <c r="V57" s="9"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:22">
       <c r="A58" s="9"/>
       <c r="B58" s="9">
         <v>4009</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="D58" s="9"/>
       <c r="E58" s="9">
         <v>4</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="G58" s="9">
         <v>0.5</v>
@@ -4633,12 +5233,12 @@
         <v>0</v>
       </c>
       <c r="L58" s="9">
-        <v>100</v>
-      </c>
-      <c r="M58" s="11">
-        <v>0</v>
-      </c>
-      <c r="N58" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M58" s="12">
+        <v>0</v>
+      </c>
+      <c r="N58" s="12">
         <v>0</v>
       </c>
       <c r="O58" s="4">
@@ -4647,7 +5247,7 @@
       <c r="P58" s="9"/>
       <c r="Q58" s="9"/>
       <c r="R58" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S58" s="9"/>
       <c r="T58" s="9"/>
@@ -4656,20 +5256,20 @@
       </c>
       <c r="V58" s="9"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:22">
       <c r="A59" s="9"/>
       <c r="B59" s="9">
         <v>4010</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="D59" s="9"/>
       <c r="E59" s="9">
         <v>4</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G59" s="9">
         <v>0.5</v>
@@ -4685,12 +5285,12 @@
         <v>0</v>
       </c>
       <c r="L59" s="9">
-        <v>100</v>
-      </c>
-      <c r="M59" s="11">
-        <v>0</v>
-      </c>
-      <c r="N59" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M59" s="12">
+        <v>0</v>
+      </c>
+      <c r="N59" s="12">
         <v>0</v>
       </c>
       <c r="O59" s="4">
@@ -4699,7 +5299,7 @@
       <c r="P59" s="9"/>
       <c r="Q59" s="9"/>
       <c r="R59" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
@@ -4708,20 +5308,20 @@
       </c>
       <c r="V59" s="9"/>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:22">
       <c r="A60" s="9"/>
       <c r="B60" s="9">
         <v>4011</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="D60" s="9"/>
       <c r="E60" s="9">
         <v>4</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G60" s="9">
         <v>0.5</v>
@@ -4737,12 +5337,12 @@
         <v>0</v>
       </c>
       <c r="L60" s="9">
-        <v>100</v>
-      </c>
-      <c r="M60" s="11">
-        <v>0</v>
-      </c>
-      <c r="N60" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M60" s="12">
+        <v>0</v>
+      </c>
+      <c r="N60" s="12">
         <v>0</v>
       </c>
       <c r="O60" s="4">
@@ -4751,7 +5351,7 @@
       <c r="P60" s="9"/>
       <c r="Q60" s="9"/>
       <c r="R60" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S60" s="9"/>
       <c r="T60" s="9"/>
@@ -4760,20 +5360,20 @@
       </c>
       <c r="V60" s="9"/>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:22">
       <c r="A61" s="9"/>
       <c r="B61" s="9">
         <v>4012</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="D61" s="9"/>
       <c r="E61" s="9">
         <v>4</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="G61" s="9">
         <v>0.5</v>
@@ -4789,12 +5389,12 @@
         <v>0</v>
       </c>
       <c r="L61" s="9">
-        <v>100</v>
-      </c>
-      <c r="M61" s="11">
-        <v>0</v>
-      </c>
-      <c r="N61" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M61" s="12">
+        <v>0</v>
+      </c>
+      <c r="N61" s="12">
         <v>0</v>
       </c>
       <c r="O61" s="4">
@@ -4803,7 +5403,7 @@
       <c r="P61" s="9"/>
       <c r="Q61" s="9"/>
       <c r="R61" s="9" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="S61" s="9"/>
       <c r="T61" s="9"/>
@@ -4812,20 +5412,20 @@
       </c>
       <c r="V61" s="9"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:22">
       <c r="A62" s="9"/>
       <c r="B62" s="9">
         <v>4013</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="D62" s="9"/>
       <c r="E62" s="9">
         <v>4</v>
       </c>
-      <c r="F62" s="9" t="s">
-        <v>77</v>
+      <c r="F62" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="G62" s="9">
         <v>0.5</v>
@@ -4841,12 +5441,12 @@
         <v>0</v>
       </c>
       <c r="L62" s="9">
-        <v>100</v>
-      </c>
-      <c r="M62" s="11">
-        <v>0</v>
-      </c>
-      <c r="N62" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M62" s="12">
+        <v>0</v>
+      </c>
+      <c r="N62" s="12">
         <v>0</v>
       </c>
       <c r="O62" s="4">
@@ -4855,7 +5455,7 @@
       <c r="P62" s="9"/>
       <c r="Q62" s="9"/>
       <c r="R62" s="9" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="S62" s="9"/>
       <c r="T62" s="9"/>
@@ -4864,20 +5464,20 @@
       </c>
       <c r="V62" s="9"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:22">
       <c r="A63" s="9"/>
       <c r="B63" s="9">
         <v>4014</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="D63" s="9"/>
       <c r="E63" s="9">
         <v>4</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>118</v>
+      <c r="F63" s="11" t="s">
+        <v>142</v>
       </c>
       <c r="G63" s="9">
         <v>0.5</v>
@@ -4893,12 +5493,12 @@
         <v>0</v>
       </c>
       <c r="L63" s="9">
-        <v>100</v>
-      </c>
-      <c r="M63" s="11">
-        <v>0</v>
-      </c>
-      <c r="N63" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M63" s="12">
+        <v>0</v>
+      </c>
+      <c r="N63" s="12">
         <v>0</v>
       </c>
       <c r="O63" s="4">
@@ -4907,7 +5507,7 @@
       <c r="P63" s="9"/>
       <c r="Q63" s="9"/>
       <c r="R63" s="9" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="S63" s="9"/>
       <c r="T63" s="9"/>
@@ -4916,20 +5516,20 @@
       </c>
       <c r="V63" s="9"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:22">
       <c r="A64" s="9"/>
       <c r="B64" s="9">
         <v>4015</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="D64" s="9"/>
       <c r="E64" s="9">
         <v>4</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="G64" s="9">
         <v>0.5</v>
@@ -4945,12 +5545,12 @@
         <v>0</v>
       </c>
       <c r="L64" s="9">
-        <v>100</v>
-      </c>
-      <c r="M64" s="11">
-        <v>0</v>
-      </c>
-      <c r="N64" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M64" s="12">
+        <v>0</v>
+      </c>
+      <c r="N64" s="12">
         <v>0</v>
       </c>
       <c r="O64" s="4">
@@ -4959,7 +5559,7 @@
       <c r="P64" s="9"/>
       <c r="Q64" s="9"/>
       <c r="R64" s="9" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="S64" s="9"/>
       <c r="T64" s="9"/>
@@ -4968,149 +5568,149 @@
       </c>
       <c r="V64" s="9"/>
     </row>
-    <row r="65" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11">
+    <row r="65" s="2" customFormat="1" spans="1:22">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12">
         <v>5001</v>
       </c>
-      <c r="C65" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11">
+      <c r="C65" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12">
         <v>5</v>
       </c>
-      <c r="F65" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="G65" s="11">
-        <v>1</v>
-      </c>
-      <c r="H65" s="11"/>
+      <c r="F65" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="G65" s="12">
+        <v>1</v>
+      </c>
+      <c r="H65" s="12"/>
       <c r="I65" s="9">
         <v>0</v>
       </c>
-      <c r="J65" s="11">
-        <v>0</v>
-      </c>
-      <c r="K65" s="11">
+      <c r="J65" s="12">
+        <v>0</v>
+      </c>
+      <c r="K65" s="12">
         <v>0</v>
       </c>
       <c r="L65" s="9">
-        <v>100</v>
-      </c>
-      <c r="M65" s="11">
-        <v>1</v>
-      </c>
-      <c r="N65" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M65" s="12">
+        <v>1</v>
+      </c>
+      <c r="N65" s="12">
         <v>0</v>
       </c>
       <c r="O65" s="4">
         <v>1</v>
       </c>
-      <c r="P65" s="11"/>
-      <c r="Q65" s="11"/>
-      <c r="R65" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="S65" s="11"/>
-      <c r="T65" s="11" t="s">
-        <v>99</v>
+      <c r="P65" s="12"/>
+      <c r="Q65" s="12"/>
+      <c r="R65" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="S65" s="12"/>
+      <c r="T65" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="U65" s="9">
         <v>1</v>
       </c>
-      <c r="V65" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12">
+      <c r="V65" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="66" s="3" customFormat="1" spans="1:22">
+      <c r="A66" s="16"/>
+      <c r="B66" s="16">
         <v>5002</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12">
+      <c r="C66" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16">
         <v>5</v>
       </c>
-      <c r="F66" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="G66" s="12">
-        <v>1</v>
-      </c>
-      <c r="H66" s="12"/>
+      <c r="F66" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="G66" s="16">
+        <v>1</v>
+      </c>
+      <c r="H66" s="16"/>
       <c r="I66" s="9">
         <v>0</v>
       </c>
-      <c r="J66" s="12">
-        <v>0</v>
-      </c>
-      <c r="K66" s="12">
+      <c r="J66" s="16">
+        <v>0</v>
+      </c>
+      <c r="K66" s="16">
         <v>1</v>
       </c>
       <c r="L66" s="9">
-        <v>100</v>
-      </c>
-      <c r="M66" s="11">
-        <v>1</v>
-      </c>
-      <c r="N66" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M66" s="12">
+        <v>1</v>
+      </c>
+      <c r="N66" s="12">
         <v>1</v>
       </c>
       <c r="O66" s="4">
         <v>0</v>
       </c>
-      <c r="P66" s="12"/>
-      <c r="Q66" s="12"/>
-      <c r="R66" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="S66" s="12"/>
-      <c r="T66" s="12"/>
-      <c r="U66" s="12">
-        <v>0</v>
-      </c>
-      <c r="V66" s="12"/>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="P66" s="16"/>
+      <c r="Q66" s="16"/>
+      <c r="R66" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="S66" s="16"/>
+      <c r="T66" s="16"/>
+      <c r="U66" s="16">
+        <v>0</v>
+      </c>
+      <c r="V66" s="16"/>
+    </row>
+    <row r="67" spans="1:22">
       <c r="A67" s="10"/>
-      <c r="B67" s="12">
+      <c r="B67" s="16">
         <v>5003</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="D67" s="10"/>
-      <c r="E67" s="12">
+      <c r="E67" s="16">
         <v>5</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="G67" s="10">
         <v>1</v>
       </c>
-      <c r="H67" s="13"/>
+      <c r="H67" s="17"/>
       <c r="I67" s="9">
         <v>0</v>
       </c>
-      <c r="J67" s="12">
+      <c r="J67" s="16">
         <v>0</v>
       </c>
       <c r="K67" s="10">
         <v>0</v>
       </c>
       <c r="L67" s="9">
-        <v>100</v>
-      </c>
-      <c r="M67" s="11">
-        <v>1</v>
-      </c>
-      <c r="N67" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M67" s="12">
+        <v>1</v>
+      </c>
+      <c r="N67" s="12">
         <v>1</v>
       </c>
       <c r="O67" s="4">
@@ -5121,30 +5721,30 @@
       <c r="R67" s="10"/>
       <c r="S67" s="10"/>
       <c r="T67" s="10"/>
-      <c r="U67" s="12">
+      <c r="U67" s="16">
         <v>0</v>
       </c>
       <c r="V67" s="10"/>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:22">
       <c r="A68" s="10"/>
-      <c r="B68" s="12">
+      <c r="B68" s="16">
         <v>5004</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="D68" s="10"/>
-      <c r="E68" s="12">
+      <c r="E68" s="16">
         <v>5</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="G68" s="10">
         <v>1</v>
       </c>
-      <c r="H68" s="13"/>
+      <c r="H68" s="17"/>
       <c r="I68" s="9">
         <v>0</v>
       </c>
@@ -5155,12 +5755,12 @@
         <v>0</v>
       </c>
       <c r="L68" s="9">
-        <v>100</v>
-      </c>
-      <c r="M68" s="11">
-        <v>1</v>
-      </c>
-      <c r="N68" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M68" s="12">
+        <v>1</v>
+      </c>
+      <c r="N68" s="12">
         <v>1</v>
       </c>
       <c r="O68" s="4">
@@ -5171,46 +5771,46 @@
       <c r="R68" s="10"/>
       <c r="S68" s="10"/>
       <c r="T68" s="10"/>
-      <c r="U68" s="12">
+      <c r="U68" s="16">
         <v>0</v>
       </c>
       <c r="V68" s="10"/>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:22">
       <c r="A69" s="10"/>
-      <c r="B69" s="12">
+      <c r="B69" s="16">
         <v>5005</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="D69" s="10"/>
-      <c r="E69" s="12">
+      <c r="E69" s="16">
         <v>5</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="G69" s="10">
         <v>1</v>
       </c>
-      <c r="H69" s="13"/>
+      <c r="H69" s="17"/>
       <c r="I69" s="9">
         <v>0</v>
       </c>
-      <c r="J69" s="12">
+      <c r="J69" s="16">
         <v>0</v>
       </c>
       <c r="K69" s="10">
         <v>1</v>
       </c>
       <c r="L69" s="9">
-        <v>100</v>
-      </c>
-      <c r="M69" s="11">
-        <v>1</v>
-      </c>
-      <c r="N69" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M69" s="12">
+        <v>1</v>
+      </c>
+      <c r="N69" s="12">
         <v>1</v>
       </c>
       <c r="O69" s="4">
@@ -5221,46 +5821,46 @@
       <c r="R69" s="10"/>
       <c r="S69" s="10"/>
       <c r="T69" s="10"/>
-      <c r="U69" s="12">
+      <c r="U69" s="16">
         <v>0</v>
       </c>
       <c r="V69" s="10"/>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:22">
       <c r="A70" s="10"/>
-      <c r="B70" s="12">
+      <c r="B70" s="16">
         <v>5006</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="D70" s="10"/>
-      <c r="E70" s="12">
+      <c r="E70" s="16">
         <v>5</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="G70" s="10">
         <v>1</v>
       </c>
-      <c r="H70" s="13"/>
+      <c r="H70" s="17"/>
       <c r="I70" s="9">
         <v>0</v>
       </c>
-      <c r="J70" s="12">
+      <c r="J70" s="16">
         <v>0</v>
       </c>
       <c r="K70" s="10">
         <v>1</v>
       </c>
       <c r="L70" s="9">
-        <v>100</v>
-      </c>
-      <c r="M70" s="11">
-        <v>1</v>
-      </c>
-      <c r="N70" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M70" s="12">
+        <v>1</v>
+      </c>
+      <c r="N70" s="12">
         <v>1</v>
       </c>
       <c r="O70" s="4">
@@ -5271,46 +5871,46 @@
       <c r="R70" s="10"/>
       <c r="S70" s="10"/>
       <c r="T70" s="10"/>
-      <c r="U70" s="12">
+      <c r="U70" s="16">
         <v>0</v>
       </c>
       <c r="V70" s="10"/>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:22">
       <c r="A71" s="10"/>
-      <c r="B71" s="12">
+      <c r="B71" s="16">
         <v>5007</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="D71" s="10"/>
-      <c r="E71" s="12">
+      <c r="E71" s="16">
         <v>5</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="G71" s="10">
         <v>1</v>
       </c>
-      <c r="H71" s="13"/>
+      <c r="H71" s="17"/>
       <c r="I71" s="9">
         <v>0</v>
       </c>
-      <c r="J71" s="12">
+      <c r="J71" s="16">
         <v>0</v>
       </c>
       <c r="K71" s="10">
         <v>0</v>
       </c>
       <c r="L71" s="9">
-        <v>100</v>
-      </c>
-      <c r="M71" s="11">
-        <v>1</v>
-      </c>
-      <c r="N71" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M71" s="12">
+        <v>1</v>
+      </c>
+      <c r="N71" s="12">
         <v>1</v>
       </c>
       <c r="O71" s="4">
@@ -5321,46 +5921,46 @@
       <c r="R71" s="10"/>
       <c r="S71" s="10"/>
       <c r="T71" s="10"/>
-      <c r="U71" s="12">
+      <c r="U71" s="16">
         <v>0</v>
       </c>
       <c r="V71" s="10"/>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:22">
       <c r="A72" s="10"/>
-      <c r="B72" s="12">
+      <c r="B72" s="16">
         <v>5008</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="D72" s="10"/>
-      <c r="E72" s="12">
+      <c r="E72" s="16">
         <v>5</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="G72" s="10">
         <v>1</v>
       </c>
-      <c r="H72" s="13"/>
+      <c r="H72" s="17"/>
       <c r="I72" s="9">
         <v>0</v>
       </c>
-      <c r="J72" s="12">
+      <c r="J72" s="16">
         <v>0</v>
       </c>
       <c r="K72" s="10">
         <v>0</v>
       </c>
       <c r="L72" s="9">
-        <v>100</v>
-      </c>
-      <c r="M72" s="11">
-        <v>1</v>
-      </c>
-      <c r="N72" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M72" s="12">
+        <v>1</v>
+      </c>
+      <c r="N72" s="12">
         <v>0</v>
       </c>
       <c r="O72" s="4">
@@ -5371,134 +5971,134 @@
       <c r="R72" s="10"/>
       <c r="S72" s="10"/>
       <c r="T72" s="10"/>
-      <c r="U72" s="12">
+      <c r="U72" s="16">
         <v>0</v>
       </c>
       <c r="V72" s="10"/>
     </row>
-    <row r="73" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12">
+    <row r="73" s="3" customFormat="1" spans="1:22">
+      <c r="A73" s="16"/>
+      <c r="B73" s="16">
         <v>5009</v>
       </c>
-      <c r="C73" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12">
+      <c r="C73" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D73" s="16"/>
+      <c r="E73" s="16">
         <v>5</v>
       </c>
-      <c r="F73" s="12" t="s">
-        <v>186</v>
+      <c r="F73" s="16" t="s">
+        <v>211</v>
       </c>
       <c r="G73" s="10">
         <v>1</v>
       </c>
-      <c r="H73" s="13"/>
+      <c r="H73" s="17"/>
       <c r="I73" s="9">
         <v>0</v>
       </c>
-      <c r="J73" s="12">
-        <v>0</v>
-      </c>
-      <c r="K73" s="12">
+      <c r="J73" s="16">
+        <v>0</v>
+      </c>
+      <c r="K73" s="16">
         <v>0</v>
       </c>
       <c r="L73" s="9">
-        <v>100</v>
-      </c>
-      <c r="M73" s="11">
-        <v>0</v>
-      </c>
-      <c r="N73" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M73" s="12">
+        <v>0</v>
+      </c>
+      <c r="N73" s="12">
         <v>0</v>
       </c>
       <c r="O73" s="4">
         <v>1</v>
       </c>
-      <c r="P73" s="12"/>
-      <c r="Q73" s="12"/>
-      <c r="R73" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="S73" s="12"/>
-      <c r="T73" s="12"/>
-      <c r="U73" s="12">
-        <v>1</v>
-      </c>
-      <c r="V73" s="12"/>
-    </row>
-    <row r="74" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11">
+      <c r="P73" s="16"/>
+      <c r="Q73" s="16"/>
+      <c r="R73" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="S73" s="16"/>
+      <c r="T73" s="16"/>
+      <c r="U73" s="16">
+        <v>1</v>
+      </c>
+      <c r="V73" s="16"/>
+    </row>
+    <row r="74" s="2" customFormat="1" spans="1:22">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12">
         <v>6001</v>
       </c>
-      <c r="C74" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11">
+      <c r="C74" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12">
         <v>6</v>
       </c>
-      <c r="F74" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G74" s="14">
-        <v>1</v>
-      </c>
-      <c r="H74" s="15"/>
-      <c r="I74" s="11">
-        <v>0</v>
-      </c>
-      <c r="J74" s="11">
-        <v>0</v>
-      </c>
-      <c r="K74" s="11">
+      <c r="F74" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G74" s="18">
+        <v>1</v>
+      </c>
+      <c r="H74" s="19"/>
+      <c r="I74" s="12">
+        <v>0</v>
+      </c>
+      <c r="J74" s="12">
+        <v>0</v>
+      </c>
+      <c r="K74" s="12">
         <v>0</v>
       </c>
       <c r="L74" s="9">
-        <v>100</v>
-      </c>
-      <c r="M74" s="11">
-        <v>0</v>
-      </c>
-      <c r="N74" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M74" s="12">
+        <v>0</v>
+      </c>
+      <c r="N74" s="12">
         <v>0</v>
       </c>
       <c r="O74" s="2">
         <v>1</v>
       </c>
-      <c r="P74" s="11"/>
-      <c r="Q74" s="11"/>
-      <c r="R74" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="S74" s="11"/>
-      <c r="T74" s="11"/>
-      <c r="U74" s="11">
-        <v>0</v>
-      </c>
-      <c r="V74" s="11"/>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="P74" s="12"/>
+      <c r="Q74" s="12"/>
+      <c r="R74" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="S74" s="12"/>
+      <c r="T74" s="12"/>
+      <c r="U74" s="12">
+        <v>0</v>
+      </c>
+      <c r="V74" s="12"/>
+    </row>
+    <row r="75" spans="1:22">
       <c r="A75" s="9"/>
       <c r="B75" s="9">
         <v>6002</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="D75" s="9"/>
       <c r="E75" s="9">
         <v>6</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="G75" s="10">
         <v>1</v>
       </c>
-      <c r="H75" s="13"/>
+      <c r="H75" s="17"/>
       <c r="I75" s="9">
         <v>0</v>
       </c>
@@ -5509,12 +6109,12 @@
         <v>0</v>
       </c>
       <c r="L75" s="9">
-        <v>100</v>
-      </c>
-      <c r="M75" s="11">
-        <v>0</v>
-      </c>
-      <c r="N75" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M75" s="12">
+        <v>0</v>
+      </c>
+      <c r="N75" s="12">
         <v>0</v>
       </c>
       <c r="O75" s="4">
@@ -5523,34 +6123,34 @@
       <c r="P75" s="9"/>
       <c r="Q75" s="9"/>
       <c r="R75" s="9" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="S75" s="9"/>
       <c r="T75" s="9"/>
-      <c r="U75" s="12">
+      <c r="U75" s="16">
         <v>0</v>
       </c>
       <c r="V75" s="9"/>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:22">
       <c r="A76" s="9"/>
       <c r="B76" s="9">
         <v>6003</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="D76" s="9"/>
       <c r="E76" s="9">
         <v>6</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="G76" s="10">
         <v>1</v>
       </c>
-      <c r="H76" s="13"/>
+      <c r="H76" s="17"/>
       <c r="I76" s="9">
         <v>0</v>
       </c>
@@ -5561,12 +6161,12 @@
         <v>0</v>
       </c>
       <c r="L76" s="9">
-        <v>100</v>
-      </c>
-      <c r="M76" s="11">
-        <v>0</v>
-      </c>
-      <c r="N76" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M76" s="12">
+        <v>0</v>
+      </c>
+      <c r="N76" s="12">
         <v>0</v>
       </c>
       <c r="O76" s="4">
@@ -5575,34 +6175,34 @@
       <c r="P76" s="9"/>
       <c r="Q76" s="9"/>
       <c r="R76" s="9" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="S76" s="9"/>
       <c r="T76" s="9"/>
-      <c r="U76" s="12">
+      <c r="U76" s="16">
         <v>0</v>
       </c>
       <c r="V76" s="9"/>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:22">
       <c r="A77" s="9"/>
       <c r="B77" s="9">
         <v>6004</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="9">
         <v>6</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
       </c>
-      <c r="H77" s="13"/>
+      <c r="H77" s="17"/>
       <c r="I77" s="9">
         <v>0</v>
       </c>
@@ -5613,12 +6213,12 @@
         <v>0</v>
       </c>
       <c r="L77" s="9">
-        <v>100</v>
-      </c>
-      <c r="M77" s="11">
-        <v>0</v>
-      </c>
-      <c r="N77" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M77" s="12">
+        <v>0</v>
+      </c>
+      <c r="N77" s="12">
         <v>0</v>
       </c>
       <c r="O77" s="4">
@@ -5627,34 +6227,34 @@
       <c r="P77" s="9"/>
       <c r="Q77" s="9"/>
       <c r="R77" s="9" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="S77" s="9"/>
       <c r="T77" s="9"/>
-      <c r="U77" s="12">
+      <c r="U77" s="16">
         <v>0</v>
       </c>
       <c r="V77" s="9"/>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:22">
       <c r="A78" s="9"/>
       <c r="B78" s="9">
         <v>6005</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="D78" s="9"/>
       <c r="E78" s="9">
         <v>6</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="G78" s="10">
         <v>1</v>
       </c>
-      <c r="H78" s="13"/>
+      <c r="H78" s="17"/>
       <c r="I78" s="9">
         <v>0</v>
       </c>
@@ -5665,12 +6265,12 @@
         <v>0</v>
       </c>
       <c r="L78" s="9">
-        <v>100</v>
-      </c>
-      <c r="M78" s="11">
-        <v>0</v>
-      </c>
-      <c r="N78" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M78" s="12">
+        <v>0</v>
+      </c>
+      <c r="N78" s="12">
         <v>0</v>
       </c>
       <c r="O78" s="4">
@@ -5679,34 +6279,34 @@
       <c r="P78" s="9"/>
       <c r="Q78" s="9"/>
       <c r="R78" s="9" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="S78" s="9"/>
       <c r="T78" s="9"/>
-      <c r="U78" s="12">
+      <c r="U78" s="16">
         <v>0</v>
       </c>
       <c r="V78" s="9"/>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:22">
       <c r="A79" s="9"/>
       <c r="B79" s="9">
         <v>6006</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="9">
         <v>6</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="G79" s="10">
         <v>1</v>
       </c>
-      <c r="H79" s="13"/>
+      <c r="H79" s="17"/>
       <c r="I79" s="9">
         <v>0</v>
       </c>
@@ -5717,12 +6317,12 @@
         <v>0</v>
       </c>
       <c r="L79" s="9">
-        <v>100</v>
-      </c>
-      <c r="M79" s="11">
-        <v>0</v>
-      </c>
-      <c r="N79" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M79" s="12">
+        <v>0</v>
+      </c>
+      <c r="N79" s="12">
         <v>0</v>
       </c>
       <c r="O79" s="4">
@@ -5731,34 +6331,34 @@
       <c r="P79" s="9"/>
       <c r="Q79" s="9"/>
       <c r="R79" s="9" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="S79" s="9"/>
       <c r="T79" s="9"/>
-      <c r="U79" s="12">
+      <c r="U79" s="16">
         <v>0</v>
       </c>
       <c r="V79" s="9"/>
     </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:22">
       <c r="A80" s="9"/>
       <c r="B80" s="9">
         <v>6007</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="D80" s="9"/>
       <c r="E80" s="9">
         <v>6</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="G80" s="10">
         <v>1</v>
       </c>
-      <c r="H80" s="13"/>
+      <c r="H80" s="17"/>
       <c r="I80" s="9">
         <v>0</v>
       </c>
@@ -5769,12 +6369,12 @@
         <v>0</v>
       </c>
       <c r="L80" s="9">
-        <v>100</v>
-      </c>
-      <c r="M80" s="11">
-        <v>0</v>
-      </c>
-      <c r="N80" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M80" s="12">
+        <v>0</v>
+      </c>
+      <c r="N80" s="12">
         <v>0</v>
       </c>
       <c r="O80" s="4">
@@ -5783,34 +6383,34 @@
       <c r="P80" s="9"/>
       <c r="Q80" s="9"/>
       <c r="R80" s="9" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="S80" s="9"/>
       <c r="T80" s="9"/>
-      <c r="U80" s="12">
+      <c r="U80" s="16">
         <v>0</v>
       </c>
       <c r="V80" s="9"/>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:22">
       <c r="A81" s="9"/>
       <c r="B81" s="9">
         <v>6008</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="D81" s="9"/>
       <c r="E81" s="9">
         <v>6</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="G81" s="10">
         <v>1</v>
       </c>
-      <c r="H81" s="13"/>
+      <c r="H81" s="17"/>
       <c r="I81" s="9">
         <v>0</v>
       </c>
@@ -5821,12 +6421,12 @@
         <v>0</v>
       </c>
       <c r="L81" s="9">
-        <v>100</v>
-      </c>
-      <c r="M81" s="11">
-        <v>0</v>
-      </c>
-      <c r="N81" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M81" s="12">
+        <v>0</v>
+      </c>
+      <c r="N81" s="12">
         <v>0</v>
       </c>
       <c r="O81" s="4">
@@ -5835,34 +6435,34 @@
       <c r="P81" s="9"/>
       <c r="Q81" s="9"/>
       <c r="R81" s="9" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="S81" s="9"/>
       <c r="T81" s="9"/>
-      <c r="U81" s="12">
+      <c r="U81" s="16">
         <v>0</v>
       </c>
       <c r="V81" s="9"/>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:22">
       <c r="A82" s="9"/>
       <c r="B82" s="9">
         <v>6009</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="D82" s="9"/>
       <c r="E82" s="9">
         <v>6</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="G82" s="10">
         <v>1</v>
       </c>
-      <c r="H82" s="13"/>
+      <c r="H82" s="17"/>
       <c r="I82" s="9">
         <v>0</v>
       </c>
@@ -5873,12 +6473,12 @@
         <v>0</v>
       </c>
       <c r="L82" s="9">
-        <v>100</v>
-      </c>
-      <c r="M82" s="11">
-        <v>0</v>
-      </c>
-      <c r="N82" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M82" s="12">
+        <v>0</v>
+      </c>
+      <c r="N82" s="12">
         <v>0</v>
       </c>
       <c r="O82" s="4">
@@ -5887,34 +6487,34 @@
       <c r="P82" s="9"/>
       <c r="Q82" s="9"/>
       <c r="R82" s="9" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="S82" s="9"/>
       <c r="T82" s="9"/>
-      <c r="U82" s="12">
+      <c r="U82" s="16">
         <v>0</v>
       </c>
       <c r="V82" s="9"/>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:22">
       <c r="A83" s="9"/>
       <c r="B83" s="9">
         <v>6010</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="D83" s="9"/>
       <c r="E83" s="9">
         <v>6</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="G83" s="10">
         <v>1</v>
       </c>
-      <c r="H83" s="13"/>
+      <c r="H83" s="17"/>
       <c r="I83" s="9">
         <v>0</v>
       </c>
@@ -5925,12 +6525,12 @@
         <v>0</v>
       </c>
       <c r="L83" s="9">
-        <v>100</v>
-      </c>
-      <c r="M83" s="11">
-        <v>0</v>
-      </c>
-      <c r="N83" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M83" s="12">
+        <v>0</v>
+      </c>
+      <c r="N83" s="12">
         <v>0</v>
       </c>
       <c r="O83" s="4">
@@ -5939,34 +6539,34 @@
       <c r="P83" s="9"/>
       <c r="Q83" s="9"/>
       <c r="R83" s="9" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="S83" s="9"/>
       <c r="T83" s="9"/>
-      <c r="U83" s="12">
+      <c r="U83" s="16">
         <v>0</v>
       </c>
       <c r="V83" s="9"/>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:22">
       <c r="A84" s="9"/>
       <c r="B84" s="9">
         <v>6011</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="D84" s="9"/>
       <c r="E84" s="9">
         <v>6</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="G84" s="10">
         <v>1</v>
       </c>
-      <c r="H84" s="13"/>
+      <c r="H84" s="17"/>
       <c r="I84" s="9">
         <v>0</v>
       </c>
@@ -5977,12 +6577,12 @@
         <v>0</v>
       </c>
       <c r="L84" s="9">
-        <v>100</v>
-      </c>
-      <c r="M84" s="11">
-        <v>0</v>
-      </c>
-      <c r="N84" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M84" s="12">
+        <v>0</v>
+      </c>
+      <c r="N84" s="12">
         <v>0</v>
       </c>
       <c r="O84" s="4">
@@ -5991,34 +6591,34 @@
       <c r="P84" s="9"/>
       <c r="Q84" s="9"/>
       <c r="R84" s="9" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="S84" s="9"/>
       <c r="T84" s="9"/>
-      <c r="U84" s="12">
+      <c r="U84" s="16">
         <v>0</v>
       </c>
       <c r="V84" s="9"/>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:22">
       <c r="A85" s="9"/>
       <c r="B85" s="9">
         <v>6012</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="D85" s="9"/>
       <c r="E85" s="9">
         <v>6</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="G85" s="10">
         <v>1</v>
       </c>
-      <c r="H85" s="13"/>
+      <c r="H85" s="17"/>
       <c r="I85" s="9">
         <v>0</v>
       </c>
@@ -6029,12 +6629,12 @@
         <v>0</v>
       </c>
       <c r="L85" s="9">
-        <v>100</v>
-      </c>
-      <c r="M85" s="11">
-        <v>0</v>
-      </c>
-      <c r="N85" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M85" s="12">
+        <v>0</v>
+      </c>
+      <c r="N85" s="12">
         <v>0</v>
       </c>
       <c r="O85" s="4">
@@ -6043,34 +6643,34 @@
       <c r="P85" s="9"/>
       <c r="Q85" s="9"/>
       <c r="R85" s="9" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="S85" s="9"/>
       <c r="T85" s="9"/>
-      <c r="U85" s="12">
+      <c r="U85" s="16">
         <v>0</v>
       </c>
       <c r="V85" s="9"/>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:22">
       <c r="A86" s="9"/>
       <c r="B86" s="9">
         <v>6013</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="D86" s="9"/>
       <c r="E86" s="9">
         <v>6</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="G86" s="10">
         <v>1</v>
       </c>
-      <c r="H86" s="13"/>
+      <c r="H86" s="17"/>
       <c r="I86" s="9">
         <v>0</v>
       </c>
@@ -6081,12 +6681,12 @@
         <v>0</v>
       </c>
       <c r="L86" s="9">
-        <v>100</v>
-      </c>
-      <c r="M86" s="11">
-        <v>0</v>
-      </c>
-      <c r="N86" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M86" s="12">
+        <v>0</v>
+      </c>
+      <c r="N86" s="12">
         <v>0</v>
       </c>
       <c r="O86" s="4">
@@ -6095,34 +6695,34 @@
       <c r="P86" s="9"/>
       <c r="Q86" s="9"/>
       <c r="R86" s="9" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="S86" s="9"/>
       <c r="T86" s="9"/>
-      <c r="U86" s="12">
+      <c r="U86" s="16">
         <v>0</v>
       </c>
       <c r="V86" s="9"/>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:22">
       <c r="A87" s="9"/>
       <c r="B87" s="9">
         <v>6014</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="D87" s="9"/>
       <c r="E87" s="9">
         <v>6</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="G87" s="10">
         <v>1</v>
       </c>
-      <c r="H87" s="13"/>
+      <c r="H87" s="17"/>
       <c r="I87" s="9">
         <v>0</v>
       </c>
@@ -6133,12 +6733,12 @@
         <v>0</v>
       </c>
       <c r="L87" s="9">
-        <v>100</v>
-      </c>
-      <c r="M87" s="11">
-        <v>0</v>
-      </c>
-      <c r="N87" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M87" s="12">
+        <v>0</v>
+      </c>
+      <c r="N87" s="12">
         <v>0</v>
       </c>
       <c r="O87" s="4">
@@ -6147,34 +6747,34 @@
       <c r="P87" s="9"/>
       <c r="Q87" s="9"/>
       <c r="R87" s="9" t="s">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="S87" s="9"/>
       <c r="T87" s="9"/>
-      <c r="U87" s="12">
+      <c r="U87" s="16">
         <v>0</v>
       </c>
       <c r="V87" s="9"/>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:22">
       <c r="A88" s="9"/>
       <c r="B88" s="9">
         <v>6015</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="D88" s="9"/>
       <c r="E88" s="9">
         <v>6</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="G88" s="10">
         <v>1</v>
       </c>
-      <c r="H88" s="13"/>
+      <c r="H88" s="17"/>
       <c r="I88" s="9">
         <v>0</v>
       </c>
@@ -6185,12 +6785,12 @@
         <v>0</v>
       </c>
       <c r="L88" s="9">
-        <v>100</v>
-      </c>
-      <c r="M88" s="11">
-        <v>0</v>
-      </c>
-      <c r="N88" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M88" s="12">
+        <v>0</v>
+      </c>
+      <c r="N88" s="12">
         <v>0</v>
       </c>
       <c r="O88" s="4">
@@ -6199,34 +6799,34 @@
       <c r="P88" s="9"/>
       <c r="Q88" s="9"/>
       <c r="R88" s="9" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="S88" s="9"/>
       <c r="T88" s="9"/>
-      <c r="U88" s="12">
+      <c r="U88" s="16">
         <v>0</v>
       </c>
       <c r="V88" s="9"/>
     </row>
-    <row r="89" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="14"/>
-      <c r="B89" s="14">
+    <row r="89" s="2" customFormat="1" spans="1:27">
+      <c r="A89" s="18"/>
+      <c r="B89" s="18">
         <v>7001</v>
       </c>
-      <c r="C89" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D89" s="14"/>
-      <c r="E89" s="14">
+      <c r="C89" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18">
         <v>7</v>
       </c>
-      <c r="F89" s="23" t="s">
-        <v>275</v>
-      </c>
-      <c r="G89" s="14">
-        <v>1</v>
-      </c>
-      <c r="H89" s="15"/>
+      <c r="F89" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="G89" s="18">
+        <v>1</v>
+      </c>
+      <c r="H89" s="19"/>
       <c r="I89" s="9">
         <v>0</v>
       </c>
@@ -6237,51 +6837,51 @@
         <v>0</v>
       </c>
       <c r="L89" s="9">
-        <v>100</v>
-      </c>
-      <c r="M89" s="11">
-        <v>1</v>
-      </c>
-      <c r="N89" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M89" s="12">
+        <v>1</v>
+      </c>
+      <c r="N89" s="12">
         <v>0</v>
       </c>
       <c r="O89" s="4">
         <v>1</v>
       </c>
-      <c r="P89" s="14"/>
-      <c r="Q89" s="14"/>
-      <c r="R89" s="14"/>
-      <c r="S89" s="14"/>
-      <c r="T89" s="14"/>
-      <c r="U89" s="12">
-        <v>0</v>
-      </c>
-      <c r="V89" s="14"/>
-      <c r="W89" s="17"/>
-      <c r="X89" s="17"/>
-      <c r="Y89" s="17"/>
-      <c r="Z89" s="17"/>
-      <c r="AA89" s="17"/>
-    </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="P89" s="18"/>
+      <c r="Q89" s="18"/>
+      <c r="R89" s="18"/>
+      <c r="S89" s="18"/>
+      <c r="T89" s="18"/>
+      <c r="U89" s="16">
+        <v>0</v>
+      </c>
+      <c r="V89" s="18"/>
+      <c r="W89" s="23"/>
+      <c r="X89" s="23"/>
+      <c r="Y89" s="23"/>
+      <c r="Z89" s="23"/>
+      <c r="AA89" s="23"/>
+    </row>
+    <row r="90" spans="1:22">
       <c r="A90" s="10"/>
       <c r="B90" s="10">
         <v>7002</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="D90" s="10"/>
       <c r="E90" s="10">
         <v>7</v>
       </c>
-      <c r="F90" s="24" t="s">
-        <v>276</v>
+      <c r="F90" s="21" t="s">
+        <v>238</v>
       </c>
       <c r="G90" s="10">
         <v>1</v>
       </c>
-      <c r="H90" s="13"/>
+      <c r="H90" s="17"/>
       <c r="I90" s="9">
         <v>0</v>
       </c>
@@ -6292,12 +6892,12 @@
         <v>0</v>
       </c>
       <c r="L90" s="9">
-        <v>100</v>
-      </c>
-      <c r="M90" s="11">
-        <v>1</v>
-      </c>
-      <c r="N90" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M90" s="12">
+        <v>1</v>
+      </c>
+      <c r="N90" s="12">
         <v>0</v>
       </c>
       <c r="O90" s="4">
@@ -6308,30 +6908,30 @@
       <c r="R90" s="10"/>
       <c r="S90" s="10"/>
       <c r="T90" s="10"/>
-      <c r="U90" s="12">
+      <c r="U90" s="16">
         <v>0</v>
       </c>
       <c r="V90" s="10"/>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:22">
       <c r="A91" s="10"/>
       <c r="B91" s="10">
         <v>7003</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="D91" s="10"/>
       <c r="E91" s="10">
         <v>7</v>
       </c>
-      <c r="F91" s="24" t="s">
-        <v>277</v>
+      <c r="F91" s="21" t="s">
+        <v>240</v>
       </c>
       <c r="G91" s="10">
         <v>1</v>
       </c>
-      <c r="H91" s="13"/>
+      <c r="H91" s="17"/>
       <c r="I91" s="9">
         <v>0</v>
       </c>
@@ -6342,12 +6942,12 @@
         <v>0</v>
       </c>
       <c r="L91" s="9">
-        <v>100</v>
-      </c>
-      <c r="M91" s="11">
-        <v>1</v>
-      </c>
-      <c r="N91" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M91" s="12">
+        <v>1</v>
+      </c>
+      <c r="N91" s="12">
         <v>0</v>
       </c>
       <c r="O91" s="4">
@@ -6358,30 +6958,30 @@
       <c r="R91" s="10"/>
       <c r="S91" s="10"/>
       <c r="T91" s="10"/>
-      <c r="U91" s="12">
+      <c r="U91" s="16">
         <v>0</v>
       </c>
       <c r="V91" s="10"/>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:22">
       <c r="A92" s="10"/>
       <c r="B92" s="10">
         <v>7004</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D92" s="10"/>
       <c r="E92" s="10">
         <v>7</v>
       </c>
-      <c r="F92" s="24" t="s">
-        <v>278</v>
+      <c r="F92" s="21" t="s">
+        <v>242</v>
       </c>
       <c r="G92" s="10">
         <v>1</v>
       </c>
-      <c r="H92" s="13"/>
+      <c r="H92" s="17"/>
       <c r="I92" s="9">
         <v>0</v>
       </c>
@@ -6392,12 +6992,12 @@
         <v>0</v>
       </c>
       <c r="L92" s="9">
-        <v>100</v>
-      </c>
-      <c r="M92" s="11">
-        <v>1</v>
-      </c>
-      <c r="N92" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="M92" s="12">
+        <v>1</v>
+      </c>
+      <c r="N92" s="12">
         <v>0</v>
       </c>
       <c r="O92" s="4">
@@ -6408,30 +7008,30 @@
       <c r="R92" s="10"/>
       <c r="S92" s="10"/>
       <c r="T92" s="10"/>
-      <c r="U92" s="12">
+      <c r="U92" s="16">
         <v>0</v>
       </c>
       <c r="V92" s="10"/>
     </row>
-    <row r="93" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="14"/>
-      <c r="B93" s="14">
+    <row r="93" s="2" customFormat="1" spans="1:27">
+      <c r="A93" s="18"/>
+      <c r="B93" s="18">
         <v>8001</v>
       </c>
-      <c r="C93" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D93" s="14"/>
-      <c r="E93" s="14">
+      <c r="C93" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="D93" s="18"/>
+      <c r="E93" s="18">
         <v>8</v>
       </c>
-      <c r="F93" s="23" t="s">
-        <v>273</v>
+      <c r="F93" s="20" t="s">
+        <v>244</v>
       </c>
       <c r="G93" s="10">
         <v>1</v>
       </c>
-      <c r="H93" s="13"/>
+      <c r="H93" s="17"/>
       <c r="I93" s="9">
         <v>0</v>
       </c>
@@ -6442,7 +7042,7 @@
         <v>1</v>
       </c>
       <c r="L93" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M93" s="9">
         <v>1</v>
@@ -6453,40 +7053,40 @@
       <c r="O93" s="4">
         <v>1</v>
       </c>
-      <c r="P93" s="14"/>
-      <c r="Q93" s="14"/>
-      <c r="R93" s="14"/>
-      <c r="S93" s="14"/>
-      <c r="T93" s="14"/>
-      <c r="U93" s="12">
-        <v>0</v>
-      </c>
-      <c r="V93" s="14"/>
-      <c r="W93" s="17"/>
-      <c r="X93" s="17"/>
-      <c r="Y93" s="17"/>
-      <c r="Z93" s="17"/>
-      <c r="AA93" s="17"/>
-    </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="P93" s="18"/>
+      <c r="Q93" s="18"/>
+      <c r="R93" s="18"/>
+      <c r="S93" s="18"/>
+      <c r="T93" s="18"/>
+      <c r="U93" s="16">
+        <v>0</v>
+      </c>
+      <c r="V93" s="18"/>
+      <c r="W93" s="23"/>
+      <c r="X93" s="23"/>
+      <c r="Y93" s="23"/>
+      <c r="Z93" s="23"/>
+      <c r="AA93" s="23"/>
+    </row>
+    <row r="94" spans="1:22">
       <c r="A94" s="10"/>
       <c r="B94" s="10">
         <v>8002</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="D94" s="10"/>
       <c r="E94" s="10">
         <v>8</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G94" s="10">
         <v>1</v>
       </c>
-      <c r="H94" s="13"/>
+      <c r="H94" s="17"/>
       <c r="I94" s="9">
         <v>0</v>
       </c>
@@ -6497,7 +7097,7 @@
         <v>1</v>
       </c>
       <c r="L94" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M94" s="9">
         <v>1</v>
@@ -6513,30 +7113,30 @@
       <c r="R94" s="10"/>
       <c r="S94" s="10"/>
       <c r="T94" s="10"/>
-      <c r="U94" s="12">
+      <c r="U94" s="16">
         <v>0</v>
       </c>
       <c r="V94" s="10"/>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:22">
       <c r="A95" s="10"/>
       <c r="B95" s="10">
         <v>8003</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="10">
         <v>8</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G95" s="10">
         <v>1</v>
       </c>
-      <c r="H95" s="13"/>
+      <c r="H95" s="17"/>
       <c r="I95" s="9">
         <v>0</v>
       </c>
@@ -6547,7 +7147,7 @@
         <v>1</v>
       </c>
       <c r="L95" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M95" s="9">
         <v>1</v>
@@ -6563,30 +7163,30 @@
       <c r="R95" s="10"/>
       <c r="S95" s="10"/>
       <c r="T95" s="10"/>
-      <c r="U95" s="12">
+      <c r="U95" s="16">
         <v>0</v>
       </c>
       <c r="V95" s="10"/>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:22">
       <c r="A96" s="10"/>
       <c r="B96" s="10">
         <v>8004</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="D96" s="10"/>
       <c r="E96" s="10">
         <v>8</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G96" s="10">
         <v>1</v>
       </c>
-      <c r="H96" s="13"/>
+      <c r="H96" s="17"/>
       <c r="I96" s="9">
         <v>0</v>
       </c>
@@ -6597,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="L96" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M96" s="9">
         <v>1</v>
@@ -6613,30 +7213,30 @@
       <c r="R96" s="10"/>
       <c r="S96" s="10"/>
       <c r="T96" s="10"/>
-      <c r="U96" s="12">
+      <c r="U96" s="16">
         <v>0</v>
       </c>
       <c r="V96" s="10"/>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:22">
       <c r="A97" s="10"/>
       <c r="B97" s="10">
         <v>8005</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="D97" s="10"/>
       <c r="E97" s="10">
         <v>8</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G97" s="10">
         <v>1</v>
       </c>
-      <c r="H97" s="13"/>
+      <c r="H97" s="17"/>
       <c r="I97" s="9">
         <v>0</v>
       </c>
@@ -6647,7 +7247,7 @@
         <v>1</v>
       </c>
       <c r="L97" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M97" s="9">
         <v>1</v>
@@ -6663,30 +7263,30 @@
       <c r="R97" s="10"/>
       <c r="S97" s="10"/>
       <c r="T97" s="10"/>
-      <c r="U97" s="12">
+      <c r="U97" s="16">
         <v>0</v>
       </c>
       <c r="V97" s="10"/>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:22">
       <c r="A98" s="10"/>
       <c r="B98" s="10">
         <v>8006</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="D98" s="10"/>
       <c r="E98" s="10">
         <v>8</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G98" s="10">
         <v>1</v>
       </c>
-      <c r="H98" s="13"/>
+      <c r="H98" s="17"/>
       <c r="I98" s="9">
         <v>0</v>
       </c>
@@ -6697,7 +7297,7 @@
         <v>1</v>
       </c>
       <c r="L98" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M98" s="9">
         <v>1</v>
@@ -6713,30 +7313,30 @@
       <c r="R98" s="10"/>
       <c r="S98" s="10"/>
       <c r="T98" s="10"/>
-      <c r="U98" s="12">
+      <c r="U98" s="16">
         <v>0</v>
       </c>
       <c r="V98" s="10"/>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:22">
       <c r="A99" s="10"/>
       <c r="B99" s="10">
         <v>8007</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D99" s="10"/>
       <c r="E99" s="10">
         <v>8</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G99" s="10">
         <v>1</v>
       </c>
-      <c r="H99" s="13"/>
+      <c r="H99" s="17"/>
       <c r="I99" s="9">
         <v>0</v>
       </c>
@@ -6747,7 +7347,7 @@
         <v>1</v>
       </c>
       <c r="L99" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M99" s="9">
         <v>1</v>
@@ -6763,30 +7363,30 @@
       <c r="R99" s="10"/>
       <c r="S99" s="10"/>
       <c r="T99" s="10"/>
-      <c r="U99" s="12">
+      <c r="U99" s="16">
         <v>0</v>
       </c>
       <c r="V99" s="10"/>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:22">
       <c r="A100" s="10"/>
       <c r="B100" s="10">
         <v>8008</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="D100" s="10"/>
       <c r="E100" s="10">
         <v>8</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G100" s="10">
         <v>1</v>
       </c>
-      <c r="H100" s="13"/>
+      <c r="H100" s="17"/>
       <c r="I100" s="9">
         <v>0</v>
       </c>
@@ -6797,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="L100" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M100" s="9">
         <v>1</v>
@@ -6813,30 +7413,30 @@
       <c r="R100" s="10"/>
       <c r="S100" s="10"/>
       <c r="T100" s="10"/>
-      <c r="U100" s="12">
+      <c r="U100" s="16">
         <v>0</v>
       </c>
       <c r="V100" s="10"/>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:22">
       <c r="A101" s="10"/>
       <c r="B101" s="10">
         <v>8009</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="D101" s="10"/>
       <c r="E101" s="10">
         <v>8</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G101" s="10">
         <v>1</v>
       </c>
-      <c r="H101" s="13"/>
+      <c r="H101" s="17"/>
       <c r="I101" s="9">
         <v>0</v>
       </c>
@@ -6847,7 +7447,7 @@
         <v>1</v>
       </c>
       <c r="L101" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M101" s="9">
         <v>1</v>
@@ -6863,30 +7463,30 @@
       <c r="R101" s="10"/>
       <c r="S101" s="10"/>
       <c r="T101" s="10"/>
-      <c r="U101" s="12">
+      <c r="U101" s="16">
         <v>0</v>
       </c>
       <c r="V101" s="10"/>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:22">
       <c r="A102" s="10"/>
       <c r="B102" s="10">
         <v>8010</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="D102" s="10"/>
       <c r="E102" s="10">
         <v>8</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G102" s="10">
         <v>1</v>
       </c>
-      <c r="H102" s="13"/>
+      <c r="H102" s="17"/>
       <c r="I102" s="9">
         <v>0</v>
       </c>
@@ -6897,7 +7497,7 @@
         <v>1</v>
       </c>
       <c r="L102" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M102" s="9">
         <v>1</v>
@@ -6913,30 +7513,30 @@
       <c r="R102" s="10"/>
       <c r="S102" s="10"/>
       <c r="T102" s="10"/>
-      <c r="U102" s="12">
+      <c r="U102" s="16">
         <v>0</v>
       </c>
       <c r="V102" s="10"/>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:22">
       <c r="A103" s="10"/>
       <c r="B103" s="10">
         <v>8011</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D103" s="10"/>
       <c r="E103" s="10">
         <v>8</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G103" s="10">
         <v>1</v>
       </c>
-      <c r="H103" s="13"/>
+      <c r="H103" s="17"/>
       <c r="I103" s="9">
         <v>0</v>
       </c>
@@ -6947,7 +7547,7 @@
         <v>1</v>
       </c>
       <c r="L103" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M103" s="9">
         <v>1</v>
@@ -6963,30 +7563,30 @@
       <c r="R103" s="10"/>
       <c r="S103" s="10"/>
       <c r="T103" s="10"/>
-      <c r="U103" s="12">
+      <c r="U103" s="16">
         <v>0</v>
       </c>
       <c r="V103" s="10"/>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:22">
       <c r="A104" s="10"/>
       <c r="B104" s="10">
         <v>8012</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="D104" s="10"/>
       <c r="E104" s="10">
         <v>8</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G104" s="10">
         <v>1</v>
       </c>
-      <c r="H104" s="13"/>
+      <c r="H104" s="17"/>
       <c r="I104" s="9">
         <v>0</v>
       </c>
@@ -6997,7 +7597,7 @@
         <v>1</v>
       </c>
       <c r="L104" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M104" s="9">
         <v>1</v>
@@ -7013,30 +7613,30 @@
       <c r="R104" s="10"/>
       <c r="S104" s="10"/>
       <c r="T104" s="10"/>
-      <c r="U104" s="12">
+      <c r="U104" s="16">
         <v>0</v>
       </c>
       <c r="V104" s="10"/>
     </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:22">
       <c r="A105" s="10"/>
       <c r="B105" s="10">
         <v>8013</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="D105" s="10"/>
       <c r="E105" s="10">
         <v>8</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G105" s="10">
         <v>1</v>
       </c>
-      <c r="H105" s="13"/>
+      <c r="H105" s="17"/>
       <c r="I105" s="9">
         <v>0</v>
       </c>
@@ -7047,7 +7647,7 @@
         <v>1</v>
       </c>
       <c r="L105" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M105" s="9">
         <v>1</v>
@@ -7063,30 +7663,30 @@
       <c r="R105" s="10"/>
       <c r="S105" s="10"/>
       <c r="T105" s="10"/>
-      <c r="U105" s="12">
+      <c r="U105" s="16">
         <v>0</v>
       </c>
       <c r="V105" s="10"/>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:22">
       <c r="A106" s="10"/>
       <c r="B106" s="10">
         <v>8014</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="D106" s="10"/>
       <c r="E106" s="10">
         <v>8</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="G106" s="10">
         <v>1</v>
       </c>
-      <c r="H106" s="13"/>
+      <c r="H106" s="17"/>
       <c r="I106" s="9">
         <v>0</v>
       </c>
@@ -7097,7 +7697,7 @@
         <v>1</v>
       </c>
       <c r="L106" s="9">
-        <v>100</v>
+        <v>0.3</v>
       </c>
       <c r="M106" s="9">
         <v>1</v>
@@ -7113,15 +7713,15 @@
       <c r="R106" s="10"/>
       <c r="S106" s="10"/>
       <c r="T106" s="10"/>
-      <c r="U106" s="12">
+      <c r="U106" s="16">
         <v>0</v>
       </c>
       <c r="V106" s="10"/>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:22">
       <c r="A107" s="10"/>
       <c r="B107" s="10"/>
-      <c r="C107" s="16"/>
+      <c r="C107" s="22"/>
       <c r="D107" s="10"/>
       <c r="E107" s="10"/>
       <c r="F107" s="10"/>
@@ -7140,10 +7740,10 @@
       <c r="U107" s="10"/>
       <c r="V107" s="10"/>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:22">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
-      <c r="C108" s="16"/>
+      <c r="C108" s="22"/>
       <c r="D108" s="10"/>
       <c r="E108" s="10"/>
       <c r="F108" s="10"/>
@@ -7162,10 +7762,10 @@
       <c r="U108" s="10"/>
       <c r="V108" s="10"/>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:22">
       <c r="A109" s="10"/>
       <c r="B109" s="10"/>
-      <c r="C109" s="16"/>
+      <c r="C109" s="22"/>
       <c r="D109" s="10"/>
       <c r="E109" s="10"/>
       <c r="F109" s="10"/>
@@ -7184,10 +7784,10 @@
       <c r="U109" s="10"/>
       <c r="V109" s="10"/>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:22">
       <c r="A110" s="10"/>
       <c r="B110" s="10"/>
-      <c r="C110" s="16"/>
+      <c r="C110" s="22"/>
       <c r="D110" s="10"/>
       <c r="E110" s="10"/>
       <c r="F110" s="10"/>
@@ -7206,10 +7806,10 @@
       <c r="U110" s="10"/>
       <c r="V110" s="10"/>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:22">
       <c r="A111" s="10"/>
       <c r="B111" s="10"/>
-      <c r="C111" s="16"/>
+      <c r="C111" s="22"/>
       <c r="D111" s="10"/>
       <c r="E111" s="10"/>
       <c r="F111" s="10"/>
@@ -7228,10 +7828,10 @@
       <c r="U111" s="10"/>
       <c r="V111" s="10"/>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:22">
       <c r="A112" s="10"/>
       <c r="B112" s="10"/>
-      <c r="C112" s="16"/>
+      <c r="C112" s="22"/>
       <c r="D112" s="10"/>
       <c r="E112" s="10"/>
       <c r="F112" s="10"/>
@@ -7250,10 +7850,10 @@
       <c r="U112" s="10"/>
       <c r="V112" s="10"/>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:22">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
-      <c r="C113" s="16"/>
+      <c r="C113" s="22"/>
       <c r="D113" s="10"/>
       <c r="E113" s="10"/>
       <c r="F113" s="10"/>
@@ -7272,10 +7872,10 @@
       <c r="U113" s="10"/>
       <c r="V113" s="10"/>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:22">
       <c r="A114" s="10"/>
       <c r="B114" s="10"/>
-      <c r="C114" s="16"/>
+      <c r="C114" s="22"/>
       <c r="D114" s="10"/>
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
@@ -7294,10 +7894,10 @@
       <c r="U114" s="10"/>
       <c r="V114" s="10"/>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:22">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
-      <c r="C115" s="16"/>
+      <c r="C115" s="22"/>
       <c r="D115" s="10"/>
       <c r="E115" s="10"/>
       <c r="F115" s="10"/>
@@ -7316,10 +7916,10 @@
       <c r="U115" s="10"/>
       <c r="V115" s="10"/>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:22">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
-      <c r="C116" s="16"/>
+      <c r="C116" s="22"/>
       <c r="D116" s="10"/>
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
@@ -7338,10 +7938,10 @@
       <c r="U116" s="10"/>
       <c r="V116" s="10"/>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:22">
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
-      <c r="C117" s="16"/>
+      <c r="C117" s="22"/>
       <c r="D117" s="10"/>
       <c r="E117" s="10"/>
       <c r="F117" s="10"/>
@@ -7360,10 +7960,10 @@
       <c r="U117" s="10"/>
       <c r="V117" s="10"/>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:22">
       <c r="A118" s="10"/>
       <c r="B118" s="10"/>
-      <c r="C118" s="16"/>
+      <c r="C118" s="22"/>
       <c r="D118" s="10"/>
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
@@ -7382,10 +7982,10 @@
       <c r="U118" s="10"/>
       <c r="V118" s="10"/>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:22">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
-      <c r="C119" s="16"/>
+      <c r="C119" s="22"/>
       <c r="D119" s="10"/>
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
@@ -7404,10 +8004,10 @@
       <c r="U119" s="10"/>
       <c r="V119" s="10"/>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:22">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
-      <c r="C120" s="16"/>
+      <c r="C120" s="22"/>
       <c r="D120" s="10"/>
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
@@ -7426,10 +8026,10 @@
       <c r="U120" s="10"/>
       <c r="V120" s="10"/>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:22">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
-      <c r="C121" s="16"/>
+      <c r="C121" s="22"/>
       <c r="D121" s="10"/>
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
@@ -7448,10 +8048,10 @@
       <c r="U121" s="10"/>
       <c r="V121" s="10"/>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:22">
       <c r="A122" s="10"/>
       <c r="B122" s="10"/>
-      <c r="C122" s="16"/>
+      <c r="C122" s="22"/>
       <c r="D122" s="10"/>
       <c r="E122" s="10"/>
       <c r="F122" s="10"/>
@@ -7470,10 +8070,10 @@
       <c r="U122" s="10"/>
       <c r="V122" s="10"/>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:22">
       <c r="A123" s="10"/>
       <c r="B123" s="10"/>
-      <c r="C123" s="16"/>
+      <c r="C123" s="22"/>
       <c r="D123" s="10"/>
       <c r="E123" s="10"/>
       <c r="F123" s="10"/>
@@ -7492,10 +8092,10 @@
       <c r="U123" s="10"/>
       <c r="V123" s="10"/>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:22">
       <c r="A124" s="10"/>
       <c r="B124" s="10"/>
-      <c r="C124" s="16"/>
+      <c r="C124" s="22"/>
       <c r="D124" s="10"/>
       <c r="E124" s="10"/>
       <c r="F124" s="10"/>
@@ -7514,10 +8114,10 @@
       <c r="U124" s="10"/>
       <c r="V124" s="10"/>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:22">
       <c r="A125" s="10"/>
       <c r="B125" s="10"/>
-      <c r="C125" s="16"/>
+      <c r="C125" s="22"/>
       <c r="D125" s="10"/>
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
@@ -7536,10 +8136,10 @@
       <c r="U125" s="10"/>
       <c r="V125" s="10"/>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:22">
       <c r="A126" s="10"/>
       <c r="B126" s="10"/>
-      <c r="C126" s="16"/>
+      <c r="C126" s="22"/>
       <c r="D126" s="10"/>
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
@@ -7558,10 +8158,10 @@
       <c r="U126" s="10"/>
       <c r="V126" s="10"/>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:22">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
-      <c r="C127" s="16"/>
+      <c r="C127" s="22"/>
       <c r="D127" s="10"/>
       <c r="E127" s="10"/>
       <c r="F127" s="10"/>
@@ -7580,10 +8180,10 @@
       <c r="U127" s="10"/>
       <c r="V127" s="10"/>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:22">
       <c r="A128" s="10"/>
       <c r="B128" s="10"/>
-      <c r="C128" s="16"/>
+      <c r="C128" s="22"/>
       <c r="D128" s="10"/>
       <c r="E128" s="10"/>
       <c r="F128" s="10"/>
@@ -7602,10 +8202,10 @@
       <c r="U128" s="10"/>
       <c r="V128" s="10"/>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:22">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
-      <c r="C129" s="16"/>
+      <c r="C129" s="22"/>
       <c r="D129" s="10"/>
       <c r="E129" s="10"/>
       <c r="F129" s="10"/>
@@ -7624,10 +8224,10 @@
       <c r="U129" s="10"/>
       <c r="V129" s="10"/>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:22">
       <c r="A130" s="10"/>
       <c r="B130" s="10"/>
-      <c r="C130" s="16"/>
+      <c r="C130" s="22"/>
       <c r="D130" s="10"/>
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
@@ -7646,10 +8246,10 @@
       <c r="U130" s="10"/>
       <c r="V130" s="10"/>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:22">
       <c r="A131" s="10"/>
       <c r="B131" s="10"/>
-      <c r="C131" s="16"/>
+      <c r="C131" s="22"/>
       <c r="D131" s="10"/>
       <c r="E131" s="10"/>
       <c r="F131" s="10"/>
@@ -7668,10 +8268,10 @@
       <c r="U131" s="10"/>
       <c r="V131" s="10"/>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:22">
       <c r="A132" s="10"/>
       <c r="B132" s="10"/>
-      <c r="C132" s="16"/>
+      <c r="C132" s="22"/>
       <c r="D132" s="10"/>
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
@@ -7690,10 +8290,10 @@
       <c r="U132" s="10"/>
       <c r="V132" s="10"/>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:22">
       <c r="A133" s="10"/>
       <c r="B133" s="10"/>
-      <c r="C133" s="16"/>
+      <c r="C133" s="22"/>
       <c r="D133" s="10"/>
       <c r="E133" s="10"/>
       <c r="F133" s="10"/>
@@ -7712,10 +8312,10 @@
       <c r="U133" s="10"/>
       <c r="V133" s="10"/>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:22">
       <c r="A134" s="10"/>
       <c r="B134" s="10"/>
-      <c r="C134" s="16"/>
+      <c r="C134" s="22"/>
       <c r="D134" s="10"/>
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
@@ -7734,10 +8334,10 @@
       <c r="U134" s="10"/>
       <c r="V134" s="10"/>
     </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:22">
       <c r="A135" s="10"/>
       <c r="B135" s="10"/>
-      <c r="C135" s="16"/>
+      <c r="C135" s="22"/>
       <c r="D135" s="10"/>
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
@@ -7756,10 +8356,10 @@
       <c r="U135" s="10"/>
       <c r="V135" s="10"/>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:22">
       <c r="A136" s="10"/>
       <c r="B136" s="10"/>
-      <c r="C136" s="16"/>
+      <c r="C136" s="22"/>
       <c r="D136" s="10"/>
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
@@ -7778,10 +8378,10 @@
       <c r="U136" s="10"/>
       <c r="V136" s="10"/>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:22">
       <c r="A137" s="10"/>
       <c r="B137" s="10"/>
-      <c r="C137" s="16"/>
+      <c r="C137" s="22"/>
       <c r="D137" s="10"/>
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
@@ -7800,10 +8400,10 @@
       <c r="U137" s="10"/>
       <c r="V137" s="10"/>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:22">
       <c r="A138" s="10"/>
       <c r="B138" s="10"/>
-      <c r="C138" s="16"/>
+      <c r="C138" s="22"/>
       <c r="D138" s="10"/>
       <c r="E138" s="10"/>
       <c r="F138" s="10"/>
@@ -7822,10 +8422,10 @@
       <c r="U138" s="10"/>
       <c r="V138" s="10"/>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:22">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
-      <c r="C139" s="16"/>
+      <c r="C139" s="22"/>
       <c r="D139" s="10"/>
       <c r="E139" s="10"/>
       <c r="F139" s="10"/>
@@ -7844,10 +8444,10 @@
       <c r="U139" s="10"/>
       <c r="V139" s="10"/>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:22">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
-      <c r="C140" s="16"/>
+      <c r="C140" s="22"/>
       <c r="D140" s="10"/>
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
@@ -7866,10 +8466,10 @@
       <c r="U140" s="10"/>
       <c r="V140" s="10"/>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:22">
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
-      <c r="C141" s="16"/>
+      <c r="C141" s="22"/>
       <c r="D141" s="10"/>
       <c r="E141" s="10"/>
       <c r="F141" s="10"/>
@@ -7888,10 +8488,10 @@
       <c r="U141" s="10"/>
       <c r="V141" s="10"/>
     </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:22">
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
-      <c r="C142" s="16"/>
+      <c r="C142" s="22"/>
       <c r="D142" s="10"/>
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
@@ -7910,10 +8510,10 @@
       <c r="U142" s="10"/>
       <c r="V142" s="10"/>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:22">
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
-      <c r="C143" s="16"/>
+      <c r="C143" s="22"/>
       <c r="D143" s="10"/>
       <c r="E143" s="10"/>
       <c r="F143" s="10"/>
@@ -7932,10 +8532,10 @@
       <c r="U143" s="10"/>
       <c r="V143" s="10"/>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:22">
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
-      <c r="C144" s="16"/>
+      <c r="C144" s="22"/>
       <c r="D144" s="10"/>
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
@@ -7954,10 +8554,10 @@
       <c r="U144" s="10"/>
       <c r="V144" s="10"/>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:22">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
-      <c r="C145" s="16"/>
+      <c r="C145" s="22"/>
       <c r="D145" s="10"/>
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
@@ -7976,10 +8576,10 @@
       <c r="U145" s="10"/>
       <c r="V145" s="10"/>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:22">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
-      <c r="C146" s="16"/>
+      <c r="C146" s="22"/>
       <c r="D146" s="10"/>
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
@@ -7998,10 +8598,10 @@
       <c r="U146" s="10"/>
       <c r="V146" s="10"/>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:22">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
-      <c r="C147" s="16"/>
+      <c r="C147" s="22"/>
       <c r="D147" s="10"/>
       <c r="E147" s="10"/>
       <c r="F147" s="10"/>
@@ -8020,10 +8620,10 @@
       <c r="U147" s="10"/>
       <c r="V147" s="10"/>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:22">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
-      <c r="C148" s="16"/>
+      <c r="C148" s="22"/>
       <c r="D148" s="10"/>
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
@@ -8042,10 +8642,10 @@
       <c r="U148" s="10"/>
       <c r="V148" s="10"/>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:22">
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
-      <c r="C149" s="16"/>
+      <c r="C149" s="22"/>
       <c r="D149" s="10"/>
       <c r="E149" s="10"/>
       <c r="F149" s="10"/>
@@ -8064,10 +8664,10 @@
       <c r="U149" s="10"/>
       <c r="V149" s="10"/>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:22">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
-      <c r="C150" s="16"/>
+      <c r="C150" s="22"/>
       <c r="D150" s="10"/>
       <c r="E150" s="10"/>
       <c r="F150" s="10"/>
@@ -8086,10 +8686,10 @@
       <c r="U150" s="10"/>
       <c r="V150" s="10"/>
     </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:22">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
-      <c r="C151" s="16"/>
+      <c r="C151" s="22"/>
       <c r="D151" s="10"/>
       <c r="E151" s="10"/>
       <c r="F151" s="10"/>
@@ -8108,10 +8708,10 @@
       <c r="U151" s="10"/>
       <c r="V151" s="10"/>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:22">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
-      <c r="C152" s="16"/>
+      <c r="C152" s="22"/>
       <c r="D152" s="10"/>
       <c r="E152" s="10"/>
       <c r="F152" s="10"/>
@@ -8130,10 +8730,10 @@
       <c r="U152" s="10"/>
       <c r="V152" s="10"/>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:22">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
-      <c r="C153" s="16"/>
+      <c r="C153" s="22"/>
       <c r="D153" s="10"/>
       <c r="E153" s="10"/>
       <c r="F153" s="10"/>
@@ -8152,10 +8752,10 @@
       <c r="U153" s="10"/>
       <c r="V153" s="10"/>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:22">
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
-      <c r="C154" s="16"/>
+      <c r="C154" s="22"/>
       <c r="D154" s="10"/>
       <c r="E154" s="10"/>
       <c r="F154" s="10"/>
@@ -8174,10 +8774,10 @@
       <c r="U154" s="10"/>
       <c r="V154" s="10"/>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:22">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
-      <c r="C155" s="16"/>
+      <c r="C155" s="22"/>
       <c r="D155" s="10"/>
       <c r="E155" s="10"/>
       <c r="F155" s="10"/>
@@ -8196,10 +8796,10 @@
       <c r="U155" s="10"/>
       <c r="V155" s="10"/>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:22">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
-      <c r="C156" s="16"/>
+      <c r="C156" s="22"/>
       <c r="D156" s="10"/>
       <c r="E156" s="10"/>
       <c r="F156" s="10"/>
@@ -8218,10 +8818,10 @@
       <c r="U156" s="10"/>
       <c r="V156" s="10"/>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:22">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
-      <c r="C157" s="16"/>
+      <c r="C157" s="22"/>
       <c r="D157" s="10"/>
       <c r="E157" s="10"/>
       <c r="F157" s="10"/>
@@ -8240,10 +8840,10 @@
       <c r="U157" s="10"/>
       <c r="V157" s="10"/>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:22">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
-      <c r="C158" s="16"/>
+      <c r="C158" s="22"/>
       <c r="D158" s="10"/>
       <c r="E158" s="10"/>
       <c r="F158" s="10"/>
@@ -8262,10 +8862,10 @@
       <c r="U158" s="10"/>
       <c r="V158" s="10"/>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:22">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
-      <c r="C159" s="16"/>
+      <c r="C159" s="22"/>
       <c r="D159" s="10"/>
       <c r="E159" s="10"/>
       <c r="F159" s="10"/>
@@ -8284,10 +8884,10 @@
       <c r="U159" s="10"/>
       <c r="V159" s="10"/>
     </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:22">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
-      <c r="C160" s="16"/>
+      <c r="C160" s="22"/>
       <c r="D160" s="10"/>
       <c r="E160" s="10"/>
       <c r="F160" s="10"/>
@@ -8306,10 +8906,10 @@
       <c r="U160" s="10"/>
       <c r="V160" s="10"/>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:22">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
-      <c r="C161" s="16"/>
+      <c r="C161" s="22"/>
       <c r="D161" s="10"/>
       <c r="E161" s="10"/>
       <c r="F161" s="10"/>
@@ -8328,10 +8928,10 @@
       <c r="U161" s="10"/>
       <c r="V161" s="10"/>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:22">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
-      <c r="C162" s="16"/>
+      <c r="C162" s="22"/>
       <c r="D162" s="10"/>
       <c r="E162" s="10"/>
       <c r="F162" s="10"/>
@@ -8350,10 +8950,10 @@
       <c r="U162" s="10"/>
       <c r="V162" s="10"/>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:22">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
-      <c r="C163" s="16"/>
+      <c r="C163" s="22"/>
       <c r="D163" s="10"/>
       <c r="E163" s="10"/>
       <c r="F163" s="10"/>
@@ -8372,10 +8972,10 @@
       <c r="U163" s="10"/>
       <c r="V163" s="10"/>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:22">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
-      <c r="C164" s="16"/>
+      <c r="C164" s="22"/>
       <c r="D164" s="10"/>
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
@@ -8394,10 +8994,10 @@
       <c r="U164" s="10"/>
       <c r="V164" s="10"/>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:22">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
-      <c r="C165" s="16"/>
+      <c r="C165" s="22"/>
       <c r="D165" s="10"/>
       <c r="E165" s="10"/>
       <c r="F165" s="10"/>
@@ -8416,10 +9016,10 @@
       <c r="U165" s="10"/>
       <c r="V165" s="10"/>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:22">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
-      <c r="C166" s="16"/>
+      <c r="C166" s="22"/>
       <c r="D166" s="10"/>
       <c r="E166" s="10"/>
       <c r="F166" s="10"/>
@@ -8438,10 +9038,10 @@
       <c r="U166" s="10"/>
       <c r="V166" s="10"/>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:22">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
-      <c r="C167" s="16"/>
+      <c r="C167" s="22"/>
       <c r="D167" s="10"/>
       <c r="E167" s="10"/>
       <c r="F167" s="10"/>
@@ -8460,10 +9060,10 @@
       <c r="U167" s="10"/>
       <c r="V167" s="10"/>
     </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:22">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
-      <c r="C168" s="16"/>
+      <c r="C168" s="22"/>
       <c r="D168" s="10"/>
       <c r="E168" s="10"/>
       <c r="F168" s="10"/>
@@ -8482,10 +9082,10 @@
       <c r="U168" s="10"/>
       <c r="V168" s="10"/>
     </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:22">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
-      <c r="C169" s="16"/>
+      <c r="C169" s="22"/>
       <c r="D169" s="10"/>
       <c r="E169" s="10"/>
       <c r="F169" s="10"/>
@@ -8504,10 +9104,10 @@
       <c r="U169" s="10"/>
       <c r="V169" s="10"/>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:22">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
-      <c r="C170" s="16"/>
+      <c r="C170" s="22"/>
       <c r="D170" s="10"/>
       <c r="E170" s="10"/>
       <c r="F170" s="10"/>
@@ -8526,10 +9126,10 @@
       <c r="U170" s="10"/>
       <c r="V170" s="10"/>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:22">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
-      <c r="C171" s="16"/>
+      <c r="C171" s="22"/>
       <c r="D171" s="10"/>
       <c r="E171" s="10"/>
       <c r="F171" s="10"/>
@@ -8548,10 +9148,10 @@
       <c r="U171" s="10"/>
       <c r="V171" s="10"/>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:22">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
-      <c r="C172" s="16"/>
+      <c r="C172" s="22"/>
       <c r="D172" s="10"/>
       <c r="E172" s="10"/>
       <c r="F172" s="10"/>
@@ -8570,10 +9170,10 @@
       <c r="U172" s="10"/>
       <c r="V172" s="10"/>
     </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:22">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
-      <c r="C173" s="16"/>
+      <c r="C173" s="22"/>
       <c r="D173" s="10"/>
       <c r="E173" s="10"/>
       <c r="F173" s="10"/>
@@ -8592,10 +9192,10 @@
       <c r="U173" s="10"/>
       <c r="V173" s="10"/>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:22">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
-      <c r="C174" s="16"/>
+      <c r="C174" s="22"/>
       <c r="D174" s="10"/>
       <c r="E174" s="10"/>
       <c r="F174" s="10"/>
@@ -8614,10 +9214,10 @@
       <c r="U174" s="10"/>
       <c r="V174" s="10"/>
     </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:22">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
-      <c r="C175" s="16"/>
+      <c r="C175" s="22"/>
       <c r="D175" s="10"/>
       <c r="E175" s="10"/>
       <c r="F175" s="10"/>
@@ -8636,10 +9236,10 @@
       <c r="U175" s="10"/>
       <c r="V175" s="10"/>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:22">
       <c r="A176" s="10"/>
       <c r="B176" s="10"/>
-      <c r="C176" s="16"/>
+      <c r="C176" s="22"/>
       <c r="D176" s="10"/>
       <c r="E176" s="10"/>
       <c r="F176" s="10"/>
@@ -8658,10 +9258,10 @@
       <c r="U176" s="10"/>
       <c r="V176" s="10"/>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:22">
       <c r="A177" s="10"/>
       <c r="B177" s="10"/>
-      <c r="C177" s="16"/>
+      <c r="C177" s="22"/>
       <c r="D177" s="10"/>
       <c r="E177" s="10"/>
       <c r="F177" s="10"/>
@@ -8680,10 +9280,10 @@
       <c r="U177" s="10"/>
       <c r="V177" s="10"/>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:22">
       <c r="A178" s="10"/>
       <c r="B178" s="10"/>
-      <c r="C178" s="16"/>
+      <c r="C178" s="22"/>
       <c r="D178" s="10"/>
       <c r="E178" s="10"/>
       <c r="F178" s="10"/>
@@ -8702,10 +9302,10 @@
       <c r="U178" s="10"/>
       <c r="V178" s="10"/>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:22">
       <c r="A179" s="10"/>
       <c r="B179" s="10"/>
-      <c r="C179" s="16"/>
+      <c r="C179" s="22"/>
       <c r="D179" s="10"/>
       <c r="E179" s="10"/>
       <c r="F179" s="10"/>
@@ -8724,10 +9324,10 @@
       <c r="U179" s="10"/>
       <c r="V179" s="10"/>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:22">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
-      <c r="C180" s="16"/>
+      <c r="C180" s="22"/>
       <c r="D180" s="10"/>
       <c r="E180" s="10"/>
       <c r="F180" s="10"/>
@@ -8746,10 +9346,10 @@
       <c r="U180" s="10"/>
       <c r="V180" s="10"/>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:22">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
-      <c r="C181" s="16"/>
+      <c r="C181" s="22"/>
       <c r="D181" s="10"/>
       <c r="E181" s="10"/>
       <c r="F181" s="10"/>
@@ -8768,10 +9368,10 @@
       <c r="U181" s="10"/>
       <c r="V181" s="10"/>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:22">
       <c r="A182" s="10"/>
       <c r="B182" s="10"/>
-      <c r="C182" s="16"/>
+      <c r="C182" s="22"/>
       <c r="D182" s="10"/>
       <c r="E182" s="10"/>
       <c r="F182" s="10"/>
@@ -8790,10 +9390,10 @@
       <c r="U182" s="10"/>
       <c r="V182" s="10"/>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:22">
       <c r="A183" s="10"/>
       <c r="B183" s="10"/>
-      <c r="C183" s="16"/>
+      <c r="C183" s="22"/>
       <c r="D183" s="10"/>
       <c r="E183" s="10"/>
       <c r="F183" s="10"/>
@@ -8812,10 +9412,10 @@
       <c r="U183" s="10"/>
       <c r="V183" s="10"/>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:22">
       <c r="A184" s="10"/>
       <c r="B184" s="10"/>
-      <c r="C184" s="16"/>
+      <c r="C184" s="22"/>
       <c r="D184" s="10"/>
       <c r="E184" s="10"/>
       <c r="F184" s="10"/>
@@ -8834,10 +9434,10 @@
       <c r="U184" s="10"/>
       <c r="V184" s="10"/>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="185" ht="14.75" spans="1:22">
       <c r="A185" s="10"/>
       <c r="B185" s="10"/>
-      <c r="C185" s="16"/>
+      <c r="C185" s="22"/>
       <c r="D185" s="10"/>
       <c r="E185" s="10"/>
       <c r="F185" s="10"/>
@@ -8856,109 +9456,110 @@
       <c r="U185" s="10"/>
       <c r="V185" s="10"/>
     </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A186" s="18"/>
-      <c r="B186" s="18"/>
-      <c r="C186" s="18"/>
-      <c r="D186" s="18"/>
-      <c r="E186" s="18"/>
-      <c r="F186" s="18"/>
-      <c r="G186" s="18"/>
-      <c r="H186" s="18"/>
-      <c r="I186" s="18"/>
-      <c r="J186" s="18"/>
-      <c r="K186" s="19"/>
-      <c r="L186" s="19"/>
-      <c r="P186" s="18"/>
-      <c r="Q186" s="18"/>
-      <c r="R186" s="18"/>
-      <c r="S186" s="18"/>
-    </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A187" s="18"/>
-      <c r="B187" s="18"/>
-      <c r="C187" s="18"/>
-      <c r="D187" s="18"/>
-      <c r="E187" s="18"/>
-      <c r="F187" s="18"/>
-      <c r="G187" s="18"/>
-      <c r="H187" s="18"/>
-      <c r="I187" s="18"/>
-      <c r="J187" s="18"/>
-      <c r="K187" s="19"/>
-      <c r="L187" s="19"/>
-      <c r="P187" s="18"/>
-      <c r="Q187" s="18"/>
-      <c r="R187" s="18"/>
-      <c r="S187" s="18"/>
-    </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A188" s="18"/>
-      <c r="B188" s="18"/>
-      <c r="C188" s="18"/>
-      <c r="D188" s="18"/>
-      <c r="E188" s="18"/>
-      <c r="F188" s="18"/>
-      <c r="G188" s="18"/>
-      <c r="H188" s="18"/>
-      <c r="I188" s="18"/>
-      <c r="J188" s="18"/>
-      <c r="K188" s="19"/>
-      <c r="L188" s="19"/>
-      <c r="P188" s="18"/>
-      <c r="Q188" s="18"/>
-      <c r="R188" s="18"/>
-      <c r="S188" s="18"/>
+    <row r="186" ht="14.75" spans="1:19">
+      <c r="A186" s="24"/>
+      <c r="B186" s="24"/>
+      <c r="C186" s="24"/>
+      <c r="D186" s="24"/>
+      <c r="E186" s="24"/>
+      <c r="F186" s="24"/>
+      <c r="G186" s="24"/>
+      <c r="H186" s="24"/>
+      <c r="I186" s="24"/>
+      <c r="J186" s="24"/>
+      <c r="K186" s="25"/>
+      <c r="L186" s="25"/>
+      <c r="P186" s="24"/>
+      <c r="Q186" s="24"/>
+      <c r="R186" s="24"/>
+      <c r="S186" s="24"/>
+    </row>
+    <row r="187" ht="14.75" spans="1:19">
+      <c r="A187" s="24"/>
+      <c r="B187" s="24"/>
+      <c r="C187" s="24"/>
+      <c r="D187" s="24"/>
+      <c r="E187" s="24"/>
+      <c r="F187" s="24"/>
+      <c r="G187" s="24"/>
+      <c r="H187" s="24"/>
+      <c r="I187" s="24"/>
+      <c r="J187" s="24"/>
+      <c r="K187" s="25"/>
+      <c r="L187" s="25"/>
+      <c r="P187" s="24"/>
+      <c r="Q187" s="24"/>
+      <c r="R187" s="24"/>
+      <c r="S187" s="24"/>
+    </row>
+    <row r="188" ht="14.75" spans="1:19">
+      <c r="A188" s="24"/>
+      <c r="B188" s="24"/>
+      <c r="C188" s="24"/>
+      <c r="D188" s="24"/>
+      <c r="E188" s="24"/>
+      <c r="F188" s="24"/>
+      <c r="G188" s="24"/>
+      <c r="H188" s="24"/>
+      <c r="I188" s="24"/>
+      <c r="J188" s="24"/>
+      <c r="K188" s="25"/>
+      <c r="L188" s="25"/>
+      <c r="P188" s="24"/>
+      <c r="Q188" s="24"/>
+      <c r="R188" s="24"/>
+      <c r="S188" s="24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="L19:R61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="12" max="12" width="5.1640625" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="5.16666666666667" customWidth="1"/>
+    <col min="13" max="13" width="18.3333333333333" customWidth="1"/>
     <col min="14" max="15" width="20.5" customWidth="1"/>
-    <col min="16" max="17" width="30.08203125" customWidth="1"/>
+    <col min="16" max="17" width="30.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="12:18">
       <c r="L19" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="M19" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="N19" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="P19" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="R19" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="12:18">
       <c r="L20">
         <v>5001</v>
       </c>
       <c r="M20" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -8968,21 +9569,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="12:18">
       <c r="L21">
         <v>5002</v>
       </c>
       <c r="M21" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -8992,21 +9593,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="12:18">
       <c r="L22">
         <v>5003</v>
       </c>
       <c r="M22" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P22" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -9016,21 +9617,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="12:18">
       <c r="L23">
         <v>5004</v>
       </c>
       <c r="M23" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P23" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -9040,21 +9641,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="12:18">
       <c r="L24">
         <v>5005</v>
       </c>
       <c r="M24" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P24" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -9064,21 +9665,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="12:18">
       <c r="L25">
         <v>5006</v>
       </c>
       <c r="M25" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -9088,21 +9689,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="12:18">
       <c r="L26">
         <v>5007</v>
       </c>
       <c r="M26" t="s">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -9112,21 +9713,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="12:18">
       <c r="L27">
         <v>5008</v>
       </c>
       <c r="M27" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P27" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -9136,21 +9737,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="12:18">
       <c r="L28">
         <v>5009</v>
       </c>
       <c r="M28" t="s">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="P28" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -9160,18 +9761,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="12:18">
       <c r="L29">
         <v>6001</v>
       </c>
       <c r="M29" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -9181,18 +9782,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="12:18">
       <c r="L30">
         <v>6002</v>
       </c>
       <c r="M30" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -9202,18 +9803,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="12:18">
       <c r="L31">
         <v>6003</v>
       </c>
       <c r="M31" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P31" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -9223,18 +9824,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="12:18">
       <c r="L32">
         <v>6004</v>
       </c>
       <c r="M32" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P32" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -9244,18 +9845,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:18">
       <c r="L33">
         <v>6005</v>
       </c>
       <c r="M33" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P33" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -9265,18 +9866,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:18">
       <c r="L34">
         <v>6006</v>
       </c>
       <c r="M34" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P34" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -9286,18 +9887,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:18">
       <c r="L35">
         <v>6007</v>
       </c>
       <c r="M35" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P35" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -9307,18 +9908,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:18">
       <c r="L36">
         <v>6008</v>
       </c>
       <c r="M36" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P36" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -9328,18 +9929,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:18">
       <c r="L37">
         <v>6009</v>
       </c>
       <c r="M37" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P37" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -9349,18 +9950,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:18">
       <c r="L38">
         <v>6010</v>
       </c>
       <c r="M38" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P38" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -9370,18 +9971,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:18">
       <c r="L39">
         <v>6011</v>
       </c>
       <c r="M39" t="s">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P39" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -9391,18 +9992,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:18">
       <c r="L40">
         <v>6012</v>
       </c>
       <c r="M40" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P40" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -9412,18 +10013,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:18">
       <c r="L41">
         <v>6013</v>
       </c>
       <c r="M41" t="s">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P41" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -9433,18 +10034,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="12:18">
       <c r="L42">
         <v>6014</v>
       </c>
       <c r="M42" t="s">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -9454,18 +10055,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="12:18">
       <c r="L43">
         <v>6015</v>
       </c>
       <c r="M43" t="s">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="P43" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -9475,21 +10076,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="12:18">
       <c r="L44">
         <v>7001</v>
       </c>
       <c r="M44" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="N44">
         <v>7</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="P44" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -9499,21 +10100,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="12:18">
       <c r="L45">
         <v>7002</v>
       </c>
       <c r="M45" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="P45" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -9523,21 +10124,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="12:18">
       <c r="L46">
         <v>7003</v>
       </c>
       <c r="M46" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="P46" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -9547,21 +10148,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="12:18">
       <c r="L47">
         <v>7004</v>
       </c>
       <c r="M47" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="P47" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -9571,21 +10172,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="12:18">
       <c r="L48">
         <v>8001</v>
       </c>
       <c r="M48" t="s">
-        <v>214</v>
+        <v>243</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -9595,21 +10196,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:18">
       <c r="L49">
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -9619,21 +10220,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="12:18">
       <c r="L50">
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -9643,21 +10244,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="12:18">
       <c r="L51">
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -9667,21 +10268,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:18">
       <c r="L52">
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -9691,21 +10292,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:18">
       <c r="L53">
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -9715,21 +10316,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:18">
       <c r="L54">
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -9739,21 +10340,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="12:18">
       <c r="L55">
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -9763,21 +10364,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="12:18">
       <c r="L56">
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -9787,21 +10388,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="12:18">
       <c r="L57">
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -9811,21 +10412,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="12:18">
       <c r="L58">
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -9835,21 +10436,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:18">
       <c r="L59">
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -9859,21 +10460,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:18">
       <c r="L60">
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -9883,21 +10484,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="12:18">
       <c r="L61">
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>
@@ -9908,7 +10509,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2005DD5-0678-49EB-B5A5-5AEABB46D97B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -903,14 +909,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -972,151 +972,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1141,194 +1003,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1437,251 +1113,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1755,61 +1189,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2067,31 +1457,31 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA188"/>
-  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="12.1666666666667" style="4"/>
-    <col min="3" max="3" width="22.8333333333333" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.1666666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="13.8333333333333" style="4" customWidth="1"/>
+    <col min="1" max="2" width="12.1640625" style="4"/>
+    <col min="3" max="3" width="22.83203125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="4" customWidth="1"/>
     <col min="6" max="6" width="36.75" style="4" customWidth="1"/>
     <col min="7" max="8" width="16.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.0833333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.08203125" style="4" customWidth="1"/>
     <col min="10" max="12" width="16.75" style="4" customWidth="1"/>
-    <col min="13" max="17" width="12.1666666666667" style="4"/>
-    <col min="18" max="19" width="17.9166666666667" style="4" customWidth="1"/>
-    <col min="20" max="21" width="26.3333333333333" style="4" customWidth="1"/>
-    <col min="22" max="22" width="12.1666666666667" style="4"/>
-    <col min="28" max="16384" width="12.1666666666667" style="4"/>
+    <col min="13" max="17" width="12.1640625" style="4"/>
+    <col min="18" max="19" width="17.9140625" style="4" customWidth="1"/>
+    <col min="20" max="21" width="26.33203125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="12.1640625" style="4"/>
+    <col min="28" max="16384" width="12.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2168,7 +1558,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
@@ -2245,7 +1635,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>29</v>
       </c>
@@ -2322,7 +1712,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>29</v>
       </c>
@@ -2399,7 +1789,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="10"/>
       <c r="B5" s="9">
         <v>1001</v>
@@ -2446,7 +1836,7 @@
       </c>
       <c r="V5" s="9"/>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="10"/>
       <c r="B6" s="9">
         <v>1002</v>
@@ -2493,7 +1883,7 @@
       </c>
       <c r="V6" s="9"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="10"/>
       <c r="B7" s="9">
         <v>1003</v>
@@ -2540,7 +1930,7 @@
       </c>
       <c r="V7" s="9"/>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="9">
         <v>1004</v>
@@ -2588,7 +1978,7 @@
       </c>
       <c r="V8" s="9"/>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="9">
         <v>1005</v>
@@ -2636,7 +2026,7 @@
       </c>
       <c r="V9" s="9"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="9">
         <v>1006</v>
@@ -2684,7 +2074,7 @@
       </c>
       <c r="V10" s="9"/>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
       <c r="B11" s="9">
         <v>1007</v>
@@ -2732,7 +2122,7 @@
       </c>
       <c r="V11" s="9"/>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
       <c r="B12" s="9">
         <v>1008</v>
@@ -2780,7 +2170,7 @@
       </c>
       <c r="V12" s="9"/>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
       <c r="B13" s="9">
         <v>1009</v>
@@ -2828,7 +2218,7 @@
       </c>
       <c r="V13" s="9"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="9">
         <v>1010</v>
@@ -2876,7 +2266,7 @@
       </c>
       <c r="V14" s="9"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
       <c r="B15" s="9">
         <v>1011</v>
@@ -2924,7 +2314,7 @@
       </c>
       <c r="V15" s="9"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
       <c r="B16" s="9">
         <v>1012</v>
@@ -2972,7 +2362,7 @@
       </c>
       <c r="V16" s="9"/>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="9">
         <v>1013</v>
@@ -3020,7 +2410,7 @@
       </c>
       <c r="V17" s="9"/>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9">
         <v>1014</v>
@@ -3070,7 +2460,7 @@
       </c>
       <c r="V18" s="9"/>
     </row>
-    <row r="19" s="2" customFormat="1" spans="1:22">
+    <row r="19" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12"/>
       <c r="B19" s="12">
         <v>2001</v>
@@ -3130,7 +2520,7 @@
       </c>
       <c r="V19" s="12"/>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9">
         <v>2002</v>
@@ -3188,7 +2578,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9">
         <v>2003</v>
@@ -3246,7 +2636,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9">
         <v>2004</v>
@@ -3308,7 +2698,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9">
         <v>2005</v>
@@ -3366,7 +2756,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9">
         <v>2006</v>
@@ -3424,7 +2814,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9">
         <v>2007</v>
@@ -3482,7 +2872,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9">
         <v>2008</v>
@@ -3540,7 +2930,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9">
         <v>2009</v>
@@ -3598,7 +2988,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9">
         <v>2010</v>
@@ -3656,7 +3046,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9">
         <v>2011</v>
@@ -3714,7 +3104,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9">
         <v>2012</v>
@@ -3772,7 +3162,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9">
         <v>2013</v>
@@ -3830,7 +3220,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9">
         <v>2014</v>
@@ -3888,7 +3278,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9">
         <v>2015</v>
@@ -3950,7 +3340,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9">
         <v>2016</v>
@@ -4008,7 +3398,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" spans="1:22">
+    <row r="35" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12"/>
       <c r="B35" s="12">
         <v>3001</v>
@@ -4060,7 +3450,7 @@
       </c>
       <c r="V35" s="12"/>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9">
         <v>3002</v>
@@ -4112,7 +3502,7 @@
       </c>
       <c r="V36" s="9"/>
     </row>
-    <row r="37" spans="1:22">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9">
         <v>3003</v>
@@ -4164,7 +3554,7 @@
       </c>
       <c r="V37" s="9"/>
     </row>
-    <row r="38" spans="1:22">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9">
         <v>3004</v>
@@ -4216,7 +3606,7 @@
       </c>
       <c r="V38" s="9"/>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9">
         <v>3005</v>
@@ -4268,7 +3658,7 @@
       </c>
       <c r="V39" s="9"/>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9">
         <v>3006</v>
@@ -4320,7 +3710,7 @@
       </c>
       <c r="V40" s="9"/>
     </row>
-    <row r="41" spans="1:22">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9">
         <v>3007</v>
@@ -4372,7 +3762,7 @@
       </c>
       <c r="V41" s="9"/>
     </row>
-    <row r="42" spans="1:22">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="9"/>
       <c r="B42" s="9">
         <v>3008</v>
@@ -4424,7 +3814,7 @@
       </c>
       <c r="V42" s="9"/>
     </row>
-    <row r="43" spans="1:22">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="9"/>
       <c r="B43" s="9">
         <v>3009</v>
@@ -4476,7 +3866,7 @@
       </c>
       <c r="V43" s="9"/>
     </row>
-    <row r="44" spans="1:22">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="9">
         <v>3010</v>
@@ -4528,7 +3918,7 @@
       </c>
       <c r="V44" s="9"/>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="9">
         <v>3011</v>
@@ -4580,7 +3970,7 @@
       </c>
       <c r="V45" s="9"/>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="9">
         <v>3012</v>
@@ -4632,7 +4022,7 @@
       </c>
       <c r="V46" s="9"/>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="9">
         <v>3013</v>
@@ -4684,7 +4074,7 @@
       </c>
       <c r="V47" s="9"/>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="9">
         <v>3014</v>
@@ -4736,7 +4126,7 @@
       </c>
       <c r="V48" s="9"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="9">
         <v>3015</v>
@@ -4788,7 +4178,7 @@
       </c>
       <c r="V49" s="9"/>
     </row>
-    <row r="50" s="2" customFormat="1" spans="1:22">
+    <row r="50" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="12">
         <v>4001</v>
@@ -4840,7 +4230,7 @@
       </c>
       <c r="V50" s="12"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="9">
         <v>4002</v>
@@ -4892,7 +4282,7 @@
       </c>
       <c r="V51" s="9"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="9">
         <v>4003</v>
@@ -4944,7 +4334,7 @@
       </c>
       <c r="V52" s="9"/>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="9">
         <v>4004</v>
@@ -4996,7 +4386,7 @@
       </c>
       <c r="V53" s="9"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="9">
         <v>4005</v>
@@ -5048,7 +4438,7 @@
       </c>
       <c r="V54" s="9"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="9">
         <v>4006</v>
@@ -5100,7 +4490,7 @@
       </c>
       <c r="V55" s="9"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="9">
         <v>4007</v>
@@ -5152,7 +4542,7 @@
       </c>
       <c r="V56" s="9"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="9">
         <v>4008</v>
@@ -5204,7 +4594,7 @@
       </c>
       <c r="V57" s="9"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="9">
         <v>4009</v>
@@ -5256,7 +4646,7 @@
       </c>
       <c r="V58" s="9"/>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="9">
         <v>4010</v>
@@ -5308,7 +4698,7 @@
       </c>
       <c r="V59" s="9"/>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="9">
         <v>4011</v>
@@ -5360,7 +4750,7 @@
       </c>
       <c r="V60" s="9"/>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="9">
         <v>4012</v>
@@ -5412,7 +4802,7 @@
       </c>
       <c r="V61" s="9"/>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="9">
         <v>4013</v>
@@ -5464,7 +4854,7 @@
       </c>
       <c r="V62" s="9"/>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="9">
         <v>4014</v>
@@ -5516,7 +4906,7 @@
       </c>
       <c r="V63" s="9"/>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="9">
         <v>4015</v>
@@ -5568,7 +4958,7 @@
       </c>
       <c r="V64" s="9"/>
     </row>
-    <row r="65" s="2" customFormat="1" spans="1:22">
+    <row r="65" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12"/>
       <c r="B65" s="12">
         <v>5001</v>
@@ -5624,7 +5014,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="66" s="3" customFormat="1" spans="1:22">
+    <row r="66" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="16"/>
       <c r="B66" s="16">
         <v>5002</v>
@@ -5676,7 +5066,7 @@
       </c>
       <c r="V66" s="16"/>
     </row>
-    <row r="67" spans="1:22">
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="16">
         <v>5003</v>
@@ -5726,7 +5116,7 @@
       </c>
       <c r="V67" s="10"/>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="16">
         <v>5004</v>
@@ -5776,7 +5166,7 @@
       </c>
       <c r="V68" s="10"/>
     </row>
-    <row r="69" spans="1:22">
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="16">
         <v>5005</v>
@@ -5826,7 +5216,7 @@
       </c>
       <c r="V69" s="10"/>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="16">
         <v>5006</v>
@@ -5876,7 +5266,7 @@
       </c>
       <c r="V70" s="10"/>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="16">
         <v>5007</v>
@@ -5926,7 +5316,7 @@
       </c>
       <c r="V71" s="10"/>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="16">
         <v>5008</v>
@@ -5976,7 +5366,7 @@
       </c>
       <c r="V72" s="10"/>
     </row>
-    <row r="73" s="3" customFormat="1" spans="1:22">
+    <row r="73" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="16"/>
       <c r="B73" s="16">
         <v>5009</v>
@@ -6028,7 +5418,7 @@
       </c>
       <c r="V73" s="16"/>
     </row>
-    <row r="74" s="2" customFormat="1" spans="1:22">
+    <row r="74" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="12"/>
       <c r="B74" s="12">
         <v>6001</v>
@@ -6080,7 +5470,7 @@
       </c>
       <c r="V74" s="12"/>
     </row>
-    <row r="75" spans="1:22">
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A75" s="9"/>
       <c r="B75" s="9">
         <v>6002</v>
@@ -6132,7 +5522,7 @@
       </c>
       <c r="V75" s="9"/>
     </row>
-    <row r="76" spans="1:22">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A76" s="9"/>
       <c r="B76" s="9">
         <v>6003</v>
@@ -6184,7 +5574,7 @@
       </c>
       <c r="V76" s="9"/>
     </row>
-    <row r="77" spans="1:22">
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A77" s="9"/>
       <c r="B77" s="9">
         <v>6004</v>
@@ -6236,7 +5626,7 @@
       </c>
       <c r="V77" s="9"/>
     </row>
-    <row r="78" spans="1:22">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A78" s="9"/>
       <c r="B78" s="9">
         <v>6005</v>
@@ -6288,7 +5678,7 @@
       </c>
       <c r="V78" s="9"/>
     </row>
-    <row r="79" spans="1:22">
+    <row r="79" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A79" s="9"/>
       <c r="B79" s="9">
         <v>6006</v>
@@ -6340,7 +5730,7 @@
       </c>
       <c r="V79" s="9"/>
     </row>
-    <row r="80" spans="1:22">
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A80" s="9"/>
       <c r="B80" s="9">
         <v>6007</v>
@@ -6392,7 +5782,7 @@
       </c>
       <c r="V80" s="9"/>
     </row>
-    <row r="81" spans="1:22">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="9"/>
       <c r="B81" s="9">
         <v>6008</v>
@@ -6444,7 +5834,7 @@
       </c>
       <c r="V81" s="9"/>
     </row>
-    <row r="82" spans="1:22">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" s="9"/>
       <c r="B82" s="9">
         <v>6009</v>
@@ -6496,7 +5886,7 @@
       </c>
       <c r="V82" s="9"/>
     </row>
-    <row r="83" spans="1:22">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" s="9"/>
       <c r="B83" s="9">
         <v>6010</v>
@@ -6548,7 +5938,7 @@
       </c>
       <c r="V83" s="9"/>
     </row>
-    <row r="84" spans="1:22">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" s="9"/>
       <c r="B84" s="9">
         <v>6011</v>
@@ -6600,7 +5990,7 @@
       </c>
       <c r="V84" s="9"/>
     </row>
-    <row r="85" spans="1:22">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" s="9"/>
       <c r="B85" s="9">
         <v>6012</v>
@@ -6652,7 +6042,7 @@
       </c>
       <c r="V85" s="9"/>
     </row>
-    <row r="86" spans="1:22">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" s="9"/>
       <c r="B86" s="9">
         <v>6013</v>
@@ -6704,7 +6094,7 @@
       </c>
       <c r="V86" s="9"/>
     </row>
-    <row r="87" spans="1:22">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87" s="9"/>
       <c r="B87" s="9">
         <v>6014</v>
@@ -6756,7 +6146,7 @@
       </c>
       <c r="V87" s="9"/>
     </row>
-    <row r="88" spans="1:22">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A88" s="9"/>
       <c r="B88" s="9">
         <v>6015</v>
@@ -6808,7 +6198,7 @@
       </c>
       <c r="V88" s="9"/>
     </row>
-    <row r="89" s="2" customFormat="1" spans="1:27">
+    <row r="89" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="18"/>
       <c r="B89" s="18">
         <v>7001</v>
@@ -6863,7 +6253,7 @@
       <c r="Z89" s="23"/>
       <c r="AA89" s="23"/>
     </row>
-    <row r="90" spans="1:22">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="10">
         <v>7002</v>
@@ -6913,7 +6303,7 @@
       </c>
       <c r="V90" s="10"/>
     </row>
-    <row r="91" spans="1:22">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="10">
         <v>7003</v>
@@ -6963,7 +6353,7 @@
       </c>
       <c r="V91" s="10"/>
     </row>
-    <row r="92" spans="1:22">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="10">
         <v>7004</v>
@@ -7013,7 +6403,7 @@
       </c>
       <c r="V92" s="10"/>
     </row>
-    <row r="93" s="2" customFormat="1" spans="1:27">
+    <row r="93" spans="1:27" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="18"/>
       <c r="B93" s="18">
         <v>8001</v>
@@ -7068,7 +6458,7 @@
       <c r="Z93" s="23"/>
       <c r="AA93" s="23"/>
     </row>
-    <row r="94" spans="1:22">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="10">
         <v>8002</v>
@@ -7118,7 +6508,7 @@
       </c>
       <c r="V94" s="10"/>
     </row>
-    <row r="95" spans="1:22">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="10">
         <v>8003</v>
@@ -7168,7 +6558,7 @@
       </c>
       <c r="V95" s="10"/>
     </row>
-    <row r="96" spans="1:22">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="10">
         <v>8004</v>
@@ -7218,7 +6608,7 @@
       </c>
       <c r="V96" s="10"/>
     </row>
-    <row r="97" spans="1:22">
+    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="10">
         <v>8005</v>
@@ -7268,7 +6658,7 @@
       </c>
       <c r="V97" s="10"/>
     </row>
-    <row r="98" spans="1:22">
+    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="10">
         <v>8006</v>
@@ -7318,7 +6708,7 @@
       </c>
       <c r="V98" s="10"/>
     </row>
-    <row r="99" spans="1:22">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="10">
         <v>8007</v>
@@ -7368,7 +6758,7 @@
       </c>
       <c r="V99" s="10"/>
     </row>
-    <row r="100" spans="1:22">
+    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="10">
         <v>8008</v>
@@ -7418,7 +6808,7 @@
       </c>
       <c r="V100" s="10"/>
     </row>
-    <row r="101" spans="1:22">
+    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="10">
         <v>8009</v>
@@ -7468,7 +6858,7 @@
       </c>
       <c r="V101" s="10"/>
     </row>
-    <row r="102" spans="1:22">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="10">
         <v>8010</v>
@@ -7518,7 +6908,7 @@
       </c>
       <c r="V102" s="10"/>
     </row>
-    <row r="103" spans="1:22">
+    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="10">
         <v>8011</v>
@@ -7568,7 +6958,7 @@
       </c>
       <c r="V103" s="10"/>
     </row>
-    <row r="104" spans="1:22">
+    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="10">
         <v>8012</v>
@@ -7618,7 +7008,7 @@
       </c>
       <c r="V104" s="10"/>
     </row>
-    <row r="105" spans="1:22">
+    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="10">
         <v>8013</v>
@@ -7668,7 +7058,7 @@
       </c>
       <c r="V105" s="10"/>
     </row>
-    <row r="106" spans="1:22">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="10">
         <v>8014</v>
@@ -7718,7 +7108,7 @@
       </c>
       <c r="V106" s="10"/>
     </row>
-    <row r="107" spans="1:22">
+    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="10"/>
       <c r="C107" s="22"/>
@@ -7740,7 +7130,7 @@
       <c r="U107" s="10"/>
       <c r="V107" s="10"/>
     </row>
-    <row r="108" spans="1:22">
+    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="10"/>
       <c r="C108" s="22"/>
@@ -7762,7 +7152,7 @@
       <c r="U108" s="10"/>
       <c r="V108" s="10"/>
     </row>
-    <row r="109" spans="1:22">
+    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A109" s="10"/>
       <c r="B109" s="10"/>
       <c r="C109" s="22"/>
@@ -7784,7 +7174,7 @@
       <c r="U109" s="10"/>
       <c r="V109" s="10"/>
     </row>
-    <row r="110" spans="1:22">
+    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A110" s="10"/>
       <c r="B110" s="10"/>
       <c r="C110" s="22"/>
@@ -7806,7 +7196,7 @@
       <c r="U110" s="10"/>
       <c r="V110" s="10"/>
     </row>
-    <row r="111" spans="1:22">
+    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A111" s="10"/>
       <c r="B111" s="10"/>
       <c r="C111" s="22"/>
@@ -7828,7 +7218,7 @@
       <c r="U111" s="10"/>
       <c r="V111" s="10"/>
     </row>
-    <row r="112" spans="1:22">
+    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
       <c r="B112" s="10"/>
       <c r="C112" s="22"/>
@@ -7850,7 +7240,7 @@
       <c r="U112" s="10"/>
       <c r="V112" s="10"/>
     </row>
-    <row r="113" spans="1:22">
+    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
       <c r="C113" s="22"/>
@@ -7872,7 +7262,7 @@
       <c r="U113" s="10"/>
       <c r="V113" s="10"/>
     </row>
-    <row r="114" spans="1:22">
+    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A114" s="10"/>
       <c r="B114" s="10"/>
       <c r="C114" s="22"/>
@@ -7894,7 +7284,7 @@
       <c r="U114" s="10"/>
       <c r="V114" s="10"/>
     </row>
-    <row r="115" spans="1:22">
+    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
       <c r="C115" s="22"/>
@@ -7916,7 +7306,7 @@
       <c r="U115" s="10"/>
       <c r="V115" s="10"/>
     </row>
-    <row r="116" spans="1:22">
+    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="22"/>
@@ -7938,7 +7328,7 @@
       <c r="U116" s="10"/>
       <c r="V116" s="10"/>
     </row>
-    <row r="117" spans="1:22">
+    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="22"/>
@@ -7960,7 +7350,7 @@
       <c r="U117" s="10"/>
       <c r="V117" s="10"/>
     </row>
-    <row r="118" spans="1:22">
+    <row r="118" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A118" s="10"/>
       <c r="B118" s="10"/>
       <c r="C118" s="22"/>
@@ -7982,7 +7372,7 @@
       <c r="U118" s="10"/>
       <c r="V118" s="10"/>
     </row>
-    <row r="119" spans="1:22">
+    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A119" s="10"/>
       <c r="B119" s="10"/>
       <c r="C119" s="22"/>
@@ -8004,7 +7394,7 @@
       <c r="U119" s="10"/>
       <c r="V119" s="10"/>
     </row>
-    <row r="120" spans="1:22">
+    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A120" s="10"/>
       <c r="B120" s="10"/>
       <c r="C120" s="22"/>
@@ -8026,7 +7416,7 @@
       <c r="U120" s="10"/>
       <c r="V120" s="10"/>
     </row>
-    <row r="121" spans="1:22">
+    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A121" s="10"/>
       <c r="B121" s="10"/>
       <c r="C121" s="22"/>
@@ -8048,7 +7438,7 @@
       <c r="U121" s="10"/>
       <c r="V121" s="10"/>
     </row>
-    <row r="122" spans="1:22">
+    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A122" s="10"/>
       <c r="B122" s="10"/>
       <c r="C122" s="22"/>
@@ -8070,7 +7460,7 @@
       <c r="U122" s="10"/>
       <c r="V122" s="10"/>
     </row>
-    <row r="123" spans="1:22">
+    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A123" s="10"/>
       <c r="B123" s="10"/>
       <c r="C123" s="22"/>
@@ -8092,7 +7482,7 @@
       <c r="U123" s="10"/>
       <c r="V123" s="10"/>
     </row>
-    <row r="124" spans="1:22">
+    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
       <c r="B124" s="10"/>
       <c r="C124" s="22"/>
@@ -8114,7 +7504,7 @@
       <c r="U124" s="10"/>
       <c r="V124" s="10"/>
     </row>
-    <row r="125" spans="1:22">
+    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A125" s="10"/>
       <c r="B125" s="10"/>
       <c r="C125" s="22"/>
@@ -8136,7 +7526,7 @@
       <c r="U125" s="10"/>
       <c r="V125" s="10"/>
     </row>
-    <row r="126" spans="1:22">
+    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A126" s="10"/>
       <c r="B126" s="10"/>
       <c r="C126" s="22"/>
@@ -8158,7 +7548,7 @@
       <c r="U126" s="10"/>
       <c r="V126" s="10"/>
     </row>
-    <row r="127" spans="1:22">
+    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A127" s="10"/>
       <c r="B127" s="10"/>
       <c r="C127" s="22"/>
@@ -8180,7 +7570,7 @@
       <c r="U127" s="10"/>
       <c r="V127" s="10"/>
     </row>
-    <row r="128" spans="1:22">
+    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A128" s="10"/>
       <c r="B128" s="10"/>
       <c r="C128" s="22"/>
@@ -8202,7 +7592,7 @@
       <c r="U128" s="10"/>
       <c r="V128" s="10"/>
     </row>
-    <row r="129" spans="1:22">
+    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A129" s="10"/>
       <c r="B129" s="10"/>
       <c r="C129" s="22"/>
@@ -8224,7 +7614,7 @@
       <c r="U129" s="10"/>
       <c r="V129" s="10"/>
     </row>
-    <row r="130" spans="1:22">
+    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
       <c r="B130" s="10"/>
       <c r="C130" s="22"/>
@@ -8246,7 +7636,7 @@
       <c r="U130" s="10"/>
       <c r="V130" s="10"/>
     </row>
-    <row r="131" spans="1:22">
+    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A131" s="10"/>
       <c r="B131" s="10"/>
       <c r="C131" s="22"/>
@@ -8268,7 +7658,7 @@
       <c r="U131" s="10"/>
       <c r="V131" s="10"/>
     </row>
-    <row r="132" spans="1:22">
+    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A132" s="10"/>
       <c r="B132" s="10"/>
       <c r="C132" s="22"/>
@@ -8290,7 +7680,7 @@
       <c r="U132" s="10"/>
       <c r="V132" s="10"/>
     </row>
-    <row r="133" spans="1:22">
+    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A133" s="10"/>
       <c r="B133" s="10"/>
       <c r="C133" s="22"/>
@@ -8312,7 +7702,7 @@
       <c r="U133" s="10"/>
       <c r="V133" s="10"/>
     </row>
-    <row r="134" spans="1:22">
+    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A134" s="10"/>
       <c r="B134" s="10"/>
       <c r="C134" s="22"/>
@@ -8334,7 +7724,7 @@
       <c r="U134" s="10"/>
       <c r="V134" s="10"/>
     </row>
-    <row r="135" spans="1:22">
+    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A135" s="10"/>
       <c r="B135" s="10"/>
       <c r="C135" s="22"/>
@@ -8356,7 +7746,7 @@
       <c r="U135" s="10"/>
       <c r="V135" s="10"/>
     </row>
-    <row r="136" spans="1:22">
+    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
       <c r="B136" s="10"/>
       <c r="C136" s="22"/>
@@ -8378,7 +7768,7 @@
       <c r="U136" s="10"/>
       <c r="V136" s="10"/>
     </row>
-    <row r="137" spans="1:22">
+    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A137" s="10"/>
       <c r="B137" s="10"/>
       <c r="C137" s="22"/>
@@ -8400,7 +7790,7 @@
       <c r="U137" s="10"/>
       <c r="V137" s="10"/>
     </row>
-    <row r="138" spans="1:22">
+    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A138" s="10"/>
       <c r="B138" s="10"/>
       <c r="C138" s="22"/>
@@ -8422,7 +7812,7 @@
       <c r="U138" s="10"/>
       <c r="V138" s="10"/>
     </row>
-    <row r="139" spans="1:22">
+    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A139" s="10"/>
       <c r="B139" s="10"/>
       <c r="C139" s="22"/>
@@ -8444,7 +7834,7 @@
       <c r="U139" s="10"/>
       <c r="V139" s="10"/>
     </row>
-    <row r="140" spans="1:22">
+    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="10"/>
       <c r="C140" s="22"/>
@@ -8466,7 +7856,7 @@
       <c r="U140" s="10"/>
       <c r="V140" s="10"/>
     </row>
-    <row r="141" spans="1:22">
+    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A141" s="10"/>
       <c r="B141" s="10"/>
       <c r="C141" s="22"/>
@@ -8488,7 +7878,7 @@
       <c r="U141" s="10"/>
       <c r="V141" s="10"/>
     </row>
-    <row r="142" spans="1:22">
+    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A142" s="10"/>
       <c r="B142" s="10"/>
       <c r="C142" s="22"/>
@@ -8510,7 +7900,7 @@
       <c r="U142" s="10"/>
       <c r="V142" s="10"/>
     </row>
-    <row r="143" spans="1:22">
+    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A143" s="10"/>
       <c r="B143" s="10"/>
       <c r="C143" s="22"/>
@@ -8532,7 +7922,7 @@
       <c r="U143" s="10"/>
       <c r="V143" s="10"/>
     </row>
-    <row r="144" spans="1:22">
+    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A144" s="10"/>
       <c r="B144" s="10"/>
       <c r="C144" s="22"/>
@@ -8554,7 +7944,7 @@
       <c r="U144" s="10"/>
       <c r="V144" s="10"/>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="10"/>
       <c r="C145" s="22"/>
@@ -8576,7 +7966,7 @@
       <c r="U145" s="10"/>
       <c r="V145" s="10"/>
     </row>
-    <row r="146" spans="1:22">
+    <row r="146" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="10"/>
       <c r="C146" s="22"/>
@@ -8598,7 +7988,7 @@
       <c r="U146" s="10"/>
       <c r="V146" s="10"/>
     </row>
-    <row r="147" spans="1:22">
+    <row r="147" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="10"/>
       <c r="C147" s="22"/>
@@ -8620,7 +8010,7 @@
       <c r="U147" s="10"/>
       <c r="V147" s="10"/>
     </row>
-    <row r="148" spans="1:22">
+    <row r="148" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="10"/>
       <c r="C148" s="22"/>
@@ -8642,7 +8032,7 @@
       <c r="U148" s="10"/>
       <c r="V148" s="10"/>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="10"/>
       <c r="C149" s="22"/>
@@ -8664,7 +8054,7 @@
       <c r="U149" s="10"/>
       <c r="V149" s="10"/>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="10"/>
       <c r="C150" s="22"/>
@@ -8686,7 +8076,7 @@
       <c r="U150" s="10"/>
       <c r="V150" s="10"/>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="10"/>
       <c r="C151" s="22"/>
@@ -8708,7 +8098,7 @@
       <c r="U151" s="10"/>
       <c r="V151" s="10"/>
     </row>
-    <row r="152" spans="1:22">
+    <row r="152" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="10"/>
       <c r="C152" s="22"/>
@@ -8730,7 +8120,7 @@
       <c r="U152" s="10"/>
       <c r="V152" s="10"/>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="10"/>
       <c r="C153" s="22"/>
@@ -8752,7 +8142,7 @@
       <c r="U153" s="10"/>
       <c r="V153" s="10"/>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
       <c r="B154" s="10"/>
       <c r="C154" s="22"/>
@@ -8774,7 +8164,7 @@
       <c r="U154" s="10"/>
       <c r="V154" s="10"/>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A155" s="10"/>
       <c r="B155" s="10"/>
       <c r="C155" s="22"/>
@@ -8796,7 +8186,7 @@
       <c r="U155" s="10"/>
       <c r="V155" s="10"/>
     </row>
-    <row r="156" spans="1:22">
+    <row r="156" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A156" s="10"/>
       <c r="B156" s="10"/>
       <c r="C156" s="22"/>
@@ -8818,7 +8208,7 @@
       <c r="U156" s="10"/>
       <c r="V156" s="10"/>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A157" s="10"/>
       <c r="B157" s="10"/>
       <c r="C157" s="22"/>
@@ -8840,7 +8230,7 @@
       <c r="U157" s="10"/>
       <c r="V157" s="10"/>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A158" s="10"/>
       <c r="B158" s="10"/>
       <c r="C158" s="22"/>
@@ -8862,7 +8252,7 @@
       <c r="U158" s="10"/>
       <c r="V158" s="10"/>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A159" s="10"/>
       <c r="B159" s="10"/>
       <c r="C159" s="22"/>
@@ -8884,7 +8274,7 @@
       <c r="U159" s="10"/>
       <c r="V159" s="10"/>
     </row>
-    <row r="160" spans="1:22">
+    <row r="160" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
       <c r="B160" s="10"/>
       <c r="C160" s="22"/>
@@ -8906,7 +8296,7 @@
       <c r="U160" s="10"/>
       <c r="V160" s="10"/>
     </row>
-    <row r="161" spans="1:22">
+    <row r="161" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A161" s="10"/>
       <c r="B161" s="10"/>
       <c r="C161" s="22"/>
@@ -8928,7 +8318,7 @@
       <c r="U161" s="10"/>
       <c r="V161" s="10"/>
     </row>
-    <row r="162" spans="1:22">
+    <row r="162" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A162" s="10"/>
       <c r="B162" s="10"/>
       <c r="C162" s="22"/>
@@ -8950,7 +8340,7 @@
       <c r="U162" s="10"/>
       <c r="V162" s="10"/>
     </row>
-    <row r="163" spans="1:22">
+    <row r="163" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A163" s="10"/>
       <c r="B163" s="10"/>
       <c r="C163" s="22"/>
@@ -8972,7 +8362,7 @@
       <c r="U163" s="10"/>
       <c r="V163" s="10"/>
     </row>
-    <row r="164" spans="1:22">
+    <row r="164" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A164" s="10"/>
       <c r="B164" s="10"/>
       <c r="C164" s="22"/>
@@ -8994,7 +8384,7 @@
       <c r="U164" s="10"/>
       <c r="V164" s="10"/>
     </row>
-    <row r="165" spans="1:22">
+    <row r="165" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A165" s="10"/>
       <c r="B165" s="10"/>
       <c r="C165" s="22"/>
@@ -9016,7 +8406,7 @@
       <c r="U165" s="10"/>
       <c r="V165" s="10"/>
     </row>
-    <row r="166" spans="1:22">
+    <row r="166" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A166" s="10"/>
       <c r="B166" s="10"/>
       <c r="C166" s="22"/>
@@ -9038,7 +8428,7 @@
       <c r="U166" s="10"/>
       <c r="V166" s="10"/>
     </row>
-    <row r="167" spans="1:22">
+    <row r="167" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A167" s="10"/>
       <c r="B167" s="10"/>
       <c r="C167" s="22"/>
@@ -9060,7 +8450,7 @@
       <c r="U167" s="10"/>
       <c r="V167" s="10"/>
     </row>
-    <row r="168" spans="1:22">
+    <row r="168" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A168" s="10"/>
       <c r="B168" s="10"/>
       <c r="C168" s="22"/>
@@ -9082,7 +8472,7 @@
       <c r="U168" s="10"/>
       <c r="V168" s="10"/>
     </row>
-    <row r="169" spans="1:22">
+    <row r="169" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="22"/>
@@ -9104,7 +8494,7 @@
       <c r="U169" s="10"/>
       <c r="V169" s="10"/>
     </row>
-    <row r="170" spans="1:22">
+    <row r="170" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A170" s="10"/>
       <c r="B170" s="10"/>
       <c r="C170" s="22"/>
@@ -9126,7 +8516,7 @@
       <c r="U170" s="10"/>
       <c r="V170" s="10"/>
     </row>
-    <row r="171" spans="1:22">
+    <row r="171" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A171" s="10"/>
       <c r="B171" s="10"/>
       <c r="C171" s="22"/>
@@ -9148,7 +8538,7 @@
       <c r="U171" s="10"/>
       <c r="V171" s="10"/>
     </row>
-    <row r="172" spans="1:22">
+    <row r="172" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
       <c r="B172" s="10"/>
       <c r="C172" s="22"/>
@@ -9170,7 +8560,7 @@
       <c r="U172" s="10"/>
       <c r="V172" s="10"/>
     </row>
-    <row r="173" spans="1:22">
+    <row r="173" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A173" s="10"/>
       <c r="B173" s="10"/>
       <c r="C173" s="22"/>
@@ -9192,7 +8582,7 @@
       <c r="U173" s="10"/>
       <c r="V173" s="10"/>
     </row>
-    <row r="174" spans="1:22">
+    <row r="174" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A174" s="10"/>
       <c r="B174" s="10"/>
       <c r="C174" s="22"/>
@@ -9214,7 +8604,7 @@
       <c r="U174" s="10"/>
       <c r="V174" s="10"/>
     </row>
-    <row r="175" spans="1:22">
+    <row r="175" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A175" s="10"/>
       <c r="B175" s="10"/>
       <c r="C175" s="22"/>
@@ -9236,7 +8626,7 @@
       <c r="U175" s="10"/>
       <c r="V175" s="10"/>
     </row>
-    <row r="176" spans="1:22">
+    <row r="176" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A176" s="10"/>
       <c r="B176" s="10"/>
       <c r="C176" s="22"/>
@@ -9258,7 +8648,7 @@
       <c r="U176" s="10"/>
       <c r="V176" s="10"/>
     </row>
-    <row r="177" spans="1:22">
+    <row r="177" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A177" s="10"/>
       <c r="B177" s="10"/>
       <c r="C177" s="22"/>
@@ -9280,7 +8670,7 @@
       <c r="U177" s="10"/>
       <c r="V177" s="10"/>
     </row>
-    <row r="178" spans="1:22">
+    <row r="178" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
       <c r="B178" s="10"/>
       <c r="C178" s="22"/>
@@ -9302,7 +8692,7 @@
       <c r="U178" s="10"/>
       <c r="V178" s="10"/>
     </row>
-    <row r="179" spans="1:22">
+    <row r="179" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A179" s="10"/>
       <c r="B179" s="10"/>
       <c r="C179" s="22"/>
@@ -9324,7 +8714,7 @@
       <c r="U179" s="10"/>
       <c r="V179" s="10"/>
     </row>
-    <row r="180" spans="1:22">
+    <row r="180" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A180" s="10"/>
       <c r="B180" s="10"/>
       <c r="C180" s="22"/>
@@ -9346,7 +8736,7 @@
       <c r="U180" s="10"/>
       <c r="V180" s="10"/>
     </row>
-    <row r="181" spans="1:22">
+    <row r="181" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A181" s="10"/>
       <c r="B181" s="10"/>
       <c r="C181" s="22"/>
@@ -9368,7 +8758,7 @@
       <c r="U181" s="10"/>
       <c r="V181" s="10"/>
     </row>
-    <row r="182" spans="1:22">
+    <row r="182" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A182" s="10"/>
       <c r="B182" s="10"/>
       <c r="C182" s="22"/>
@@ -9390,7 +8780,7 @@
       <c r="U182" s="10"/>
       <c r="V182" s="10"/>
     </row>
-    <row r="183" spans="1:22">
+    <row r="183" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A183" s="10"/>
       <c r="B183" s="10"/>
       <c r="C183" s="22"/>
@@ -9412,7 +8802,7 @@
       <c r="U183" s="10"/>
       <c r="V183" s="10"/>
     </row>
-    <row r="184" spans="1:22">
+    <row r="184" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A184" s="10"/>
       <c r="B184" s="10"/>
       <c r="C184" s="22"/>
@@ -9434,7 +8824,7 @@
       <c r="U184" s="10"/>
       <c r="V184" s="10"/>
     </row>
-    <row r="185" ht="14.75" spans="1:22">
+    <row r="185" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A185" s="10"/>
       <c r="B185" s="10"/>
       <c r="C185" s="22"/>
@@ -9456,7 +8846,7 @@
       <c r="U185" s="10"/>
       <c r="V185" s="10"/>
     </row>
-    <row r="186" ht="14.75" spans="1:19">
+    <row r="186" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A186" s="24"/>
       <c r="B186" s="24"/>
       <c r="C186" s="24"/>
@@ -9474,7 +8864,7 @@
       <c r="R186" s="24"/>
       <c r="S186" s="24"/>
     </row>
-    <row r="187" ht="14.75" spans="1:19">
+    <row r="187" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A187" s="24"/>
       <c r="B187" s="24"/>
       <c r="C187" s="24"/>
@@ -9492,7 +8882,7 @@
       <c r="R187" s="24"/>
       <c r="S187" s="24"/>
     </row>
-    <row r="188" ht="14.75" spans="1:19">
+    <row r="188" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A188" s="24"/>
       <c r="B188" s="24"/>
       <c r="C188" s="24"/>
@@ -9511,24 +8901,23 @@
       <c r="S188" s="24"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="L19:R61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="12" max="12" width="5.16666666666667" customWidth="1"/>
-    <col min="13" max="13" width="18.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
     <col min="14" max="15" width="20.5" customWidth="1"/>
-    <col min="16" max="17" width="30.0833333333333" customWidth="1"/>
+    <col min="16" max="17" width="30.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="12:18">
+    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
         <v>258</v>
       </c>
@@ -9545,7 +8934,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="20" spans="12:18">
+    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L20">
         <v>5001</v>
       </c>
@@ -9569,7 +8958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="12:18">
+    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L21">
         <v>5002</v>
       </c>
@@ -9593,7 +8982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="12:18">
+    <row r="22" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L22">
         <v>5003</v>
       </c>
@@ -9617,7 +9006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="12:18">
+    <row r="23" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>5004</v>
       </c>
@@ -9641,7 +9030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="12:18">
+    <row r="24" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L24">
         <v>5005</v>
       </c>
@@ -9665,7 +9054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="12:18">
+    <row r="25" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L25">
         <v>5006</v>
       </c>
@@ -9689,7 +9078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="12:18">
+    <row r="26" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L26">
         <v>5007</v>
       </c>
@@ -9713,7 +9102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="12:18">
+    <row r="27" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L27">
         <v>5008</v>
       </c>
@@ -9737,7 +9126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="12:18">
+    <row r="28" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L28">
         <v>5009</v>
       </c>
@@ -9761,7 +9150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="12:18">
+    <row r="29" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L29">
         <v>6001</v>
       </c>
@@ -9782,7 +9171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="12:18">
+    <row r="30" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L30">
         <v>6002</v>
       </c>
@@ -9803,7 +9192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="12:18">
+    <row r="31" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L31">
         <v>6003</v>
       </c>
@@ -9824,7 +9213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="12:18">
+    <row r="32" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L32">
         <v>6004</v>
       </c>
@@ -9845,7 +9234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="12:18">
+    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L33">
         <v>6005</v>
       </c>
@@ -9866,7 +9255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="12:18">
+    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L34">
         <v>6006</v>
       </c>
@@ -9887,7 +9276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="12:18">
+    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L35">
         <v>6007</v>
       </c>
@@ -9908,7 +9297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="12:18">
+    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L36">
         <v>6008</v>
       </c>
@@ -9929,7 +9318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="12:18">
+    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L37">
         <v>6009</v>
       </c>
@@ -9950,7 +9339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="12:18">
+    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L38">
         <v>6010</v>
       </c>
@@ -9971,7 +9360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="12:18">
+    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L39">
         <v>6011</v>
       </c>
@@ -9992,7 +9381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="12:18">
+    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L40">
         <v>6012</v>
       </c>
@@ -10013,7 +9402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="12:18">
+    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L41">
         <v>6013</v>
       </c>
@@ -10034,7 +9423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="12:18">
+    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L42">
         <v>6014</v>
       </c>
@@ -10055,7 +9444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="12:18">
+    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L43">
         <v>6015</v>
       </c>
@@ -10076,7 +9465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="12:18">
+    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L44">
         <v>7001</v>
       </c>
@@ -10100,7 +9489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="12:18">
+    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L45">
         <v>7002</v>
       </c>
@@ -10124,7 +9513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="12:18">
+    <row r="46" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L46">
         <v>7003</v>
       </c>
@@ -10148,7 +9537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="12:18">
+    <row r="47" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L47">
         <v>7004</v>
       </c>
@@ -10172,7 +9561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="12:18">
+    <row r="48" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L48">
         <v>8001</v>
       </c>
@@ -10196,7 +9585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="12:18">
+    <row r="49" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L49">
         <v>8002</v>
       </c>
@@ -10220,7 +9609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="12:18">
+    <row r="50" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L50">
         <v>8003</v>
       </c>
@@ -10244,7 +9633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="12:18">
+    <row r="51" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L51">
         <v>8004</v>
       </c>
@@ -10268,7 +9657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="12:18">
+    <row r="52" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L52">
         <v>8005</v>
       </c>
@@ -10292,7 +9681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="12:18">
+    <row r="53" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L53">
         <v>8006</v>
       </c>
@@ -10316,7 +9705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="12:18">
+    <row r="54" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L54">
         <v>8007</v>
       </c>
@@ -10340,7 +9729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="12:18">
+    <row r="55" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L55">
         <v>8008</v>
       </c>
@@ -10364,7 +9753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="12:18">
+    <row r="56" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L56">
         <v>8009</v>
       </c>
@@ -10388,7 +9777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="12:18">
+    <row r="57" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L57">
         <v>8010</v>
       </c>
@@ -10412,7 +9801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="12:18">
+    <row r="58" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L58">
         <v>8011</v>
       </c>
@@ -10436,7 +9825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="12:18">
+    <row r="59" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L59">
         <v>8012</v>
       </c>
@@ -10460,7 +9849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="12:18">
+    <row r="60" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L60">
         <v>8013</v>
       </c>
@@ -10484,7 +9873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="12:18">
+    <row r="61" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L61">
         <v>8014</v>
       </c>
@@ -10509,7 +9898,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C207EB40-B504-40C7-AFD2-CAAF08F275CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42B100D-7009-E547-98EA-70E9ACCB7EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="2540" windowWidth="23600" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="299">
   <si>
     <t>##var</t>
   </si>
@@ -252,9 +252,6 @@
     <t>土豆-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag Potato</t>
-  </si>
-  <si>
     <t>蘑菇-种子袋</t>
   </si>
   <si>
@@ -276,9 +273,6 @@
     <t>水甜菜-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag Beet</t>
-  </si>
-  <si>
     <t>番茄-红-种子袋</t>
   </si>
   <si>
@@ -616,9 +610,6 @@
   </si>
   <si>
     <t>洒水壶</t>
-  </si>
-  <si>
-    <t>prefab/Item/Wateringpot</t>
   </si>
   <si>
     <t>删除染色</t>
@@ -948,6 +939,12 @@
   <si>
     <t>buffid，buffid 只有合成道具配置</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab/Plants/Potato</t>
+  </si>
+  <si>
+    <t>Prefab/Plants/WaterBeet</t>
   </si>
 </sst>
 </file>
@@ -958,7 +955,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -966,7 +963,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -975,7 +972,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -984,7 +981,7 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -992,7 +989,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1000,7 +997,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1009,7 +1006,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1017,14 +1014,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1032,21 +1029,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1055,7 +1052,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1272,7 +1269,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1546,7 +1543,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB189"/>
-  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="12.1640625" style="2"/>
     <col min="3" max="3" width="22.83203125" style="2" customWidth="1"/>
@@ -1564,7 +1561,7 @@
     <col min="29" max="16384" width="12.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1575,7 +1572,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
@@ -1584,7 +1581,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>5</v>
@@ -1644,10 +1641,10 @@
         <v>23</v>
       </c>
       <c r="AA1" s="23" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -1727,10 +1724,10 @@
         <v>25</v>
       </c>
       <c r="AA2" s="24" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
@@ -1750,7 +1747,7 @@
         <v>33</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>34</v>
@@ -1810,10 +1807,10 @@
         <v>51</v>
       </c>
       <c r="AA3" s="23" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
@@ -1893,10 +1890,10 @@
         <v>69</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="2">
         <v>1001</v>
@@ -1908,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>71</v>
+        <v>297</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="2">
@@ -1942,19 +1939,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="2">
@@ -1988,19 +1985,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="2">
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="2">
@@ -2034,19 +2031,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="2">
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>77</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="2">
@@ -2080,19 +2077,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="2">
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="2">
@@ -2126,19 +2123,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="2">
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="2">
@@ -2172,19 +2169,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="2">
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="2">
@@ -2218,19 +2215,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="2">
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="2">
@@ -2264,19 +2261,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="2">
         <v>1009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="2">
@@ -2310,19 +2307,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="2">
         <v>1010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="2">
@@ -2356,19 +2353,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="2">
         <v>1011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="2">
@@ -2402,19 +2399,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
       <c r="B16" s="2">
         <v>1012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="2">
@@ -2448,19 +2445,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
       <c r="B17" s="2">
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="2">
@@ -2494,18 +2491,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B18" s="2">
         <v>1014</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="2">
@@ -2539,24 +2536,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1">
         <v>2001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -2586,39 +2583,39 @@
         <v>1</v>
       </c>
       <c r="Q19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="U19" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="V19" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B20" s="2">
         <v>2002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2648,36 +2645,36 @@
         <v>1</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V20" s="2">
         <v>1</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B21" s="2">
         <v>2003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2707,36 +2704,36 @@
         <v>1</v>
       </c>
       <c r="S21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V21" s="2">
+        <v>1</v>
+      </c>
+      <c r="W21" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="U21" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="V21" s="2">
-        <v>1</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B22" s="2">
         <v>2004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E22" s="2">
         <v>2</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2766,42 +2763,42 @@
         <v>1</v>
       </c>
       <c r="Q22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="U22" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="S22" s="2" t="s">
+      <c r="V22" s="2">
+        <v>1</v>
+      </c>
+      <c r="W22" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="V22" s="2">
-        <v>1</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B23" s="2">
         <v>2005</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E23" s="2">
         <v>2</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2831,36 +2828,36 @@
         <v>1</v>
       </c>
       <c r="S23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="V23" s="2">
+        <v>1</v>
+      </c>
+      <c r="W23" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="U23" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="V23" s="2">
-        <v>1</v>
-      </c>
-      <c r="W23" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B24" s="2">
         <v>2006</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E24" s="2">
         <v>2</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -2890,36 +2887,36 @@
         <v>1</v>
       </c>
       <c r="S24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V24" s="2">
+        <v>1</v>
+      </c>
+      <c r="W24" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U24" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V24" s="2">
-        <v>1</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B25" s="2">
         <v>2007</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E25" s="2">
         <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -2949,36 +2946,36 @@
         <v>1</v>
       </c>
       <c r="S25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V25" s="2">
+        <v>1</v>
+      </c>
+      <c r="W25" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U25" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V25" s="2">
-        <v>1</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B26" s="2">
         <v>2008</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E26" s="2">
         <v>2</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3008,36 +3005,36 @@
         <v>1</v>
       </c>
       <c r="S26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V26" s="2">
+        <v>1</v>
+      </c>
+      <c r="W26" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U26" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V26" s="2">
-        <v>1</v>
-      </c>
-      <c r="W26" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B27" s="2">
         <v>2009</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E27" s="2">
         <v>2</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3067,36 +3064,36 @@
         <v>1</v>
       </c>
       <c r="S27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V27" s="2">
+        <v>1</v>
+      </c>
+      <c r="W27" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U27" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V27" s="2">
-        <v>1</v>
-      </c>
-      <c r="W27" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B28" s="2">
         <v>2010</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E28" s="2">
         <v>2</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3126,36 +3123,36 @@
         <v>1</v>
       </c>
       <c r="S28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V28" s="2">
+        <v>1</v>
+      </c>
+      <c r="W28" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U28" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V28" s="2">
-        <v>1</v>
-      </c>
-      <c r="W28" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B29" s="2">
         <v>2011</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2">
         <v>2</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3185,36 +3182,36 @@
         <v>1</v>
       </c>
       <c r="S29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V29" s="2">
+        <v>1</v>
+      </c>
+      <c r="W29" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U29" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V29" s="2">
-        <v>1</v>
-      </c>
-      <c r="W29" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B30" s="2">
         <v>2012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E30" s="2">
         <v>2</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3244,36 +3241,36 @@
         <v>1</v>
       </c>
       <c r="S30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="V30" s="2">
+        <v>1</v>
+      </c>
+      <c r="W30" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="U30" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="V30" s="2">
-        <v>1</v>
-      </c>
-      <c r="W30" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B31" s="2">
         <v>2013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E31" s="2">
         <v>2</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3303,36 +3300,36 @@
         <v>1</v>
       </c>
       <c r="S31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="V31" s="2">
+        <v>1</v>
+      </c>
+      <c r="W31" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="U31" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="V31" s="2">
-        <v>1</v>
-      </c>
-      <c r="W31" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B32" s="2">
         <v>2014</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E32" s="2">
         <v>2</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -3362,36 +3359,36 @@
         <v>1</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="V32" s="2">
         <v>1</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B33" s="2">
         <v>2015</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E33" s="2">
         <v>2</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -3421,42 +3418,42 @@
         <v>1</v>
       </c>
       <c r="Q33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="V33" s="2">
+        <v>1</v>
+      </c>
+      <c r="W33" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="R33" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="U33" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="V33" s="2">
-        <v>1</v>
-      </c>
-      <c r="W33" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B34" s="2">
         <v>2016</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E34" s="2">
         <v>2</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -3486,30 +3483,30 @@
         <v>1</v>
       </c>
       <c r="S34" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="U34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="U34" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="V34" s="2">
         <v>1</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="35" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="1">
         <v>3001</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="1">
@@ -3537,24 +3534,24 @@
         <v>1</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="V35" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B36" s="2">
         <v>3002</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E36" s="2">
         <v>3</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="2">
@@ -3582,24 +3579,24 @@
         <v>1</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="V36" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="2">
         <v>3003</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E37" s="2">
         <v>3</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H37" s="2">
         <v>4</v>
@@ -3626,24 +3623,24 @@
         <v>1</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="V37" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B38" s="2">
         <v>3004</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E38" s="2">
         <v>3</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H38" s="2">
         <v>4</v>
@@ -3670,24 +3667,24 @@
         <v>1</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="V38" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B39" s="2">
         <v>3005</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E39" s="2">
         <v>3</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H39" s="2">
         <v>4</v>
@@ -3714,24 +3711,24 @@
         <v>1</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="V39" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B40" s="2">
         <v>3006</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E40" s="2">
         <v>3</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H40" s="2">
         <v>4</v>
@@ -3758,24 +3755,24 @@
         <v>1</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="V40" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B41" s="2">
         <v>3007</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E41" s="2">
         <v>3</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H41" s="2">
         <v>4</v>
@@ -3802,24 +3799,24 @@
         <v>1</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V41" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B42" s="2">
         <v>3008</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H42" s="2">
         <v>4</v>
@@ -3846,24 +3843,24 @@
         <v>1</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V42" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B43" s="2">
         <v>3009</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E43" s="2">
         <v>3</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H43" s="2">
         <v>4</v>
@@ -3890,24 +3887,24 @@
         <v>1</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="V43" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B44" s="2">
         <v>3010</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E44" s="2">
         <v>3</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H44" s="2">
         <v>4</v>
@@ -3934,24 +3931,24 @@
         <v>1</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="V44" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B45" s="2">
         <v>3011</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E45" s="2">
         <v>3</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H45" s="2">
         <v>4</v>
@@ -3978,24 +3975,24 @@
         <v>1</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V45" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B46" s="2">
         <v>3012</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E46" s="2">
         <v>3</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H46" s="2">
         <v>4</v>
@@ -4022,24 +4019,24 @@
         <v>1</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V46" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B47" s="2">
         <v>3013</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E47" s="2">
         <v>3</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="2">
@@ -4067,24 +4064,24 @@
         <v>1</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="V47" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B48" s="2">
         <v>3014</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E48" s="2">
         <v>3</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G48" s="8"/>
       <c r="H48" s="2">
@@ -4112,24 +4109,24 @@
         <v>1</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V48" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B49" s="2">
         <v>3015</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E49" s="2">
         <v>3</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H49" s="2">
         <v>4</v>
@@ -4156,24 +4153,24 @@
         <v>1</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="V49" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="1">
         <v>4001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E50" s="1">
         <v>4</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G50" s="9"/>
       <c r="H50" s="1">
@@ -4201,24 +4198,24 @@
         <v>1</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="V50" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B51" s="2">
         <v>4002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E51" s="2">
         <v>4</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="2">
@@ -4246,24 +4243,24 @@
         <v>1</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="V51" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B52" s="2">
         <v>4003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E52" s="2">
         <v>4</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H52" s="2">
         <v>0.5</v>
@@ -4290,24 +4287,24 @@
         <v>1</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V52" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B53" s="2">
         <v>4004</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E53" s="2">
         <v>4</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H53" s="2">
         <v>0.5</v>
@@ -4334,24 +4331,24 @@
         <v>1</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="V53" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B54" s="2">
         <v>4005</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E54" s="2">
         <v>4</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H54" s="2">
         <v>0.5</v>
@@ -4378,24 +4375,24 @@
         <v>1</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V54" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B55" s="2">
         <v>4006</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E55" s="2">
         <v>4</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H55" s="2">
         <v>0.5</v>
@@ -4422,24 +4419,24 @@
         <v>1</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V55" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B56" s="2">
         <v>4007</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E56" s="2">
         <v>4</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H56" s="2">
         <v>0.5</v>
@@ -4466,24 +4463,24 @@
         <v>1</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V56" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B57" s="2">
         <v>4008</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E57" s="2">
         <v>4</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H57" s="2">
         <v>0.5</v>
@@ -4510,24 +4507,24 @@
         <v>1</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V57" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B58" s="2">
         <v>4009</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E58" s="2">
         <v>4</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H58" s="2">
         <v>0.5</v>
@@ -4554,24 +4551,24 @@
         <v>1</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V58" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B59" s="2">
         <v>4010</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E59" s="2">
         <v>4</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H59" s="2">
         <v>0.5</v>
@@ -4598,24 +4595,24 @@
         <v>1</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V59" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B60" s="2">
         <v>4011</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E60" s="2">
         <v>4</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H60" s="2">
         <v>0.5</v>
@@ -4642,24 +4639,24 @@
         <v>1</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V60" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B61" s="2">
         <v>4012</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E61" s="2">
         <v>4</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H61" s="2">
         <v>0.5</v>
@@ -4686,24 +4683,24 @@
         <v>1</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V61" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B62" s="2">
         <v>4013</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E62" s="2">
         <v>4</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="2">
@@ -4731,24 +4728,24 @@
         <v>1</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V62" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B63" s="2">
         <v>4014</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E63" s="2">
         <v>4</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="2">
@@ -4776,24 +4773,24 @@
         <v>1</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="V63" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B64" s="2">
         <v>4015</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E64" s="2">
         <v>4</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H64" s="2">
         <v>0.5</v>
@@ -4820,24 +4817,24 @@
         <v>1</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V64" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B65" s="1">
         <v>5001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E65" s="1">
         <v>5</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="1">
@@ -4865,30 +4862,30 @@
         <v>1</v>
       </c>
       <c r="S65" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="V65" s="2">
         <v>1</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B66" s="2">
         <v>5002</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H66" s="2">
         <v>1</v>
@@ -4915,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V66" s="2">
         <v>0</v>
@@ -4926,20 +4923,20 @@
       <c r="AA66" s="2"/>
       <c r="AB66" s="2"/>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A67" s="7"/>
       <c r="B67" s="2">
         <v>5003</v>
       </c>
       <c r="C67" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D67" s="7"/>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7">
@@ -4977,20 +4974,20 @@
       </c>
       <c r="W67" s="7"/>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A68" s="7"/>
       <c r="B68" s="2">
         <v>5004</v>
       </c>
       <c r="C68" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7">
@@ -5028,20 +5025,20 @@
       </c>
       <c r="W68" s="7"/>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A69" s="7"/>
       <c r="B69" s="2">
         <v>5005</v>
       </c>
       <c r="C69" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D69" s="7"/>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7">
@@ -5079,20 +5076,20 @@
       </c>
       <c r="W69" s="7"/>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="2">
         <v>5006</v>
       </c>
       <c r="C70" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D70" s="7"/>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7">
@@ -5130,20 +5127,20 @@
       </c>
       <c r="W70" s="7"/>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A71" s="7"/>
       <c r="B71" s="2">
         <v>5007</v>
       </c>
       <c r="C71" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7">
@@ -5181,20 +5178,20 @@
       </c>
       <c r="W71" s="7"/>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A72" s="7"/>
       <c r="B72" s="2">
         <v>5008</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D72" s="7"/>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7">
@@ -5232,18 +5229,18 @@
       </c>
       <c r="W72" s="7"/>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B73" s="2">
         <v>5009</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E73" s="2">
         <v>5</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G73" s="20"/>
       <c r="H73" s="7">
@@ -5272,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V73" s="2">
         <v>1</v>
@@ -5283,18 +5280,18 @@
       <c r="AA73" s="2"/>
       <c r="AB73" s="2"/>
     </row>
-    <row r="74" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B74" s="1">
         <v>6001</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E74" s="1">
         <v>6</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H74" s="13">
         <v>1</v>
@@ -5322,24 +5319,24 @@
         <v>1</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="V74" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B75" s="2">
         <v>6002</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E75" s="2">
         <v>6</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H75" s="7">
         <v>1</v>
@@ -5367,24 +5364,24 @@
         <v>1</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="V75" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B76" s="2">
         <v>6003</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E76" s="2">
         <v>6</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H76" s="7">
         <v>1</v>
@@ -5412,24 +5409,24 @@
         <v>1</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="V76" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B77" s="2">
         <v>6004</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E77" s="2">
         <v>6</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H77" s="7">
         <v>1</v>
@@ -5457,24 +5454,24 @@
         <v>1</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="V77" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B78" s="2">
         <v>6005</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E78" s="2">
         <v>6</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H78" s="7">
         <v>1</v>
@@ -5502,24 +5499,24 @@
         <v>1</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="V78" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B79" s="2">
         <v>6006</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E79" s="2">
         <v>6</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H79" s="7">
         <v>1</v>
@@ -5547,24 +5544,24 @@
         <v>1</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="V79" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B80" s="2">
         <v>6007</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E80" s="2">
         <v>6</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H80" s="7">
         <v>1</v>
@@ -5592,24 +5589,24 @@
         <v>1</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V80" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B81" s="2">
         <v>6008</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E81" s="2">
         <v>6</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H81" s="7">
         <v>1</v>
@@ -5637,24 +5634,24 @@
         <v>1</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V81" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B82" s="2">
         <v>6009</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E82" s="2">
         <v>6</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H82" s="7">
         <v>1</v>
@@ -5682,24 +5679,24 @@
         <v>1</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="V82" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B83" s="2">
         <v>6010</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E83" s="2">
         <v>6</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H83" s="7">
         <v>1</v>
@@ -5727,24 +5724,24 @@
         <v>1</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="V83" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B84" s="2">
         <v>6011</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E84" s="2">
         <v>6</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H84" s="7">
         <v>1</v>
@@ -5772,24 +5769,24 @@
         <v>1</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="V84" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B85" s="2">
         <v>6012</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E85" s="2">
         <v>6</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H85" s="7">
         <v>1</v>
@@ -5817,24 +5814,24 @@
         <v>1</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="V85" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B86" s="2">
         <v>6013</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E86" s="2">
         <v>6</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H86" s="7">
         <v>1</v>
@@ -5862,24 +5859,24 @@
         <v>1</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="V86" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B87" s="2">
         <v>6014</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E87" s="2">
         <v>6</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H87" s="7">
         <v>1</v>
@@ -5907,24 +5904,24 @@
         <v>1</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="V87" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B88" s="2">
         <v>6015</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E88" s="2">
         <v>6</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="H88" s="7">
         <v>1</v>
@@ -5952,31 +5949,31 @@
         <v>1</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="V88" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="13"/>
       <c r="B89" s="13">
         <v>7001</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E89" s="13">
         <v>7</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G89" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H89" s="13">
         <v>1</v>
@@ -6018,25 +6015,25 @@
       <c r="AA89" s="18"/>
       <c r="AB89" s="18"/>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7">
         <v>7002</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E90" s="7">
         <v>7</v>
       </c>
       <c r="F90" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G90" s="22" t="s">
         <v>291</v>
-      </c>
-      <c r="G90" s="22" t="s">
-        <v>294</v>
       </c>
       <c r="H90" s="7">
         <v>1</v>
@@ -6073,25 +6070,25 @@
       </c>
       <c r="W90" s="7"/>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A91" s="7"/>
       <c r="B91" s="7">
         <v>7003</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E91" s="7">
         <v>7</v>
       </c>
       <c r="F91" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="G91" s="22" t="s">
         <v>291</v>
-      </c>
-      <c r="G91" s="22" t="s">
-        <v>294</v>
       </c>
       <c r="H91" s="7">
         <v>1</v>
@@ -6128,25 +6125,25 @@
       </c>
       <c r="W91" s="7"/>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A92" s="7"/>
       <c r="B92" s="7">
         <v>7004</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E92" s="7">
         <v>7</v>
       </c>
       <c r="F92" s="16" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H92" s="7">
         <v>1</v>
@@ -6183,25 +6180,25 @@
       </c>
       <c r="W92" s="7"/>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A93" s="7"/>
       <c r="B93" s="7">
         <v>7005</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E93" s="7">
         <v>7</v>
       </c>
       <c r="F93" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H93" s="7">
         <v>1</v>
@@ -6238,20 +6235,20 @@
       </c>
       <c r="W93" s="7"/>
     </row>
-    <row r="94" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="13"/>
       <c r="B94" s="13">
         <v>8001</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D94" s="13"/>
       <c r="E94" s="13">
         <v>8</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G94" s="15"/>
       <c r="H94" s="7">
@@ -6294,20 +6291,20 @@
       <c r="AA94" s="18"/>
       <c r="AB94" s="18"/>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A95" s="7"/>
       <c r="B95" s="7">
         <v>8002</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D95" s="7"/>
       <c r="E95" s="7">
         <v>8</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7">
@@ -6345,20 +6342,20 @@
       </c>
       <c r="W95" s="7"/>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <v>8003</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7">
         <v>8</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7">
@@ -6396,20 +6393,20 @@
       </c>
       <c r="W96" s="7"/>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A97" s="7"/>
       <c r="B97" s="7">
         <v>8004</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="7">
         <v>8</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7">
@@ -6447,20 +6444,20 @@
       </c>
       <c r="W97" s="7"/>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A98" s="7"/>
       <c r="B98" s="7">
         <v>8005</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="7">
         <v>8</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7">
@@ -6498,20 +6495,20 @@
       </c>
       <c r="W98" s="7"/>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A99" s="7"/>
       <c r="B99" s="7">
         <v>8006</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="7">
         <v>8</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7">
@@ -6549,20 +6546,20 @@
       </c>
       <c r="W99" s="7"/>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A100" s="7"/>
       <c r="B100" s="7">
         <v>8007</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="7">
         <v>8</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7">
@@ -6600,20 +6597,20 @@
       </c>
       <c r="W100" s="7"/>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A101" s="7"/>
       <c r="B101" s="7">
         <v>8008</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="7">
         <v>8</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7">
@@ -6651,20 +6648,20 @@
       </c>
       <c r="W101" s="7"/>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A102" s="7"/>
       <c r="B102" s="7">
         <v>8009</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="7">
         <v>8</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7">
@@ -6702,20 +6699,20 @@
       </c>
       <c r="W102" s="7"/>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A103" s="7"/>
       <c r="B103" s="7">
         <v>8010</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="7">
         <v>8</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="7">
@@ -6753,20 +6750,20 @@
       </c>
       <c r="W103" s="7"/>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A104" s="7"/>
       <c r="B104" s="7">
         <v>8011</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="7">
         <v>8</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7">
@@ -6804,20 +6801,20 @@
       </c>
       <c r="W104" s="7"/>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A105" s="7"/>
       <c r="B105" s="7">
         <v>8012</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="7">
         <v>8</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7">
@@ -6855,20 +6852,20 @@
       </c>
       <c r="W105" s="7"/>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A106" s="7"/>
       <c r="B106" s="7">
         <v>8013</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="7">
         <v>8</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7">
@@ -6906,20 +6903,20 @@
       </c>
       <c r="W106" s="7"/>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A107" s="7"/>
       <c r="B107" s="7">
         <v>8014</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="7">
         <v>8</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7">
@@ -6957,7 +6954,7 @@
       </c>
       <c r="W107" s="7"/>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="17"/>
@@ -6980,7 +6977,7 @@
       <c r="V108" s="7"/>
       <c r="W108" s="7"/>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="17"/>
@@ -7003,7 +7000,7 @@
       <c r="V109" s="7"/>
       <c r="W109" s="7"/>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="17"/>
@@ -7026,7 +7023,7 @@
       <c r="V110" s="7"/>
       <c r="W110" s="7"/>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="17"/>
@@ -7049,7 +7046,7 @@
       <c r="V111" s="7"/>
       <c r="W111" s="7"/>
     </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="17"/>
@@ -7072,7 +7069,7 @@
       <c r="V112" s="7"/>
       <c r="W112" s="7"/>
     </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="17"/>
@@ -7095,7 +7092,7 @@
       <c r="V113" s="7"/>
       <c r="W113" s="7"/>
     </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="17"/>
@@ -7118,7 +7115,7 @@
       <c r="V114" s="7"/>
       <c r="W114" s="7"/>
     </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="17"/>
@@ -7141,7 +7138,7 @@
       <c r="V115" s="7"/>
       <c r="W115" s="7"/>
     </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="17"/>
@@ -7164,7 +7161,7 @@
       <c r="V116" s="7"/>
       <c r="W116" s="7"/>
     </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="17"/>
@@ -7187,7 +7184,7 @@
       <c r="V117" s="7"/>
       <c r="W117" s="7"/>
     </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="17"/>
@@ -7210,7 +7207,7 @@
       <c r="V118" s="7"/>
       <c r="W118" s="7"/>
     </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="17"/>
@@ -7233,7 +7230,7 @@
       <c r="V119" s="7"/>
       <c r="W119" s="7"/>
     </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="17"/>
@@ -7256,7 +7253,7 @@
       <c r="V120" s="7"/>
       <c r="W120" s="7"/>
     </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="17"/>
@@ -7279,7 +7276,7 @@
       <c r="V121" s="7"/>
       <c r="W121" s="7"/>
     </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="17"/>
@@ -7302,7 +7299,7 @@
       <c r="V122" s="7"/>
       <c r="W122" s="7"/>
     </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="17"/>
@@ -7325,7 +7322,7 @@
       <c r="V123" s="7"/>
       <c r="W123" s="7"/>
     </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="17"/>
@@ -7348,7 +7345,7 @@
       <c r="V124" s="7"/>
       <c r="W124" s="7"/>
     </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="17"/>
@@ -7371,7 +7368,7 @@
       <c r="V125" s="7"/>
       <c r="W125" s="7"/>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="17"/>
@@ -7394,7 +7391,7 @@
       <c r="V126" s="7"/>
       <c r="W126" s="7"/>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="17"/>
@@ -7417,7 +7414,7 @@
       <c r="V127" s="7"/>
       <c r="W127" s="7"/>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="17"/>
@@ -7440,7 +7437,7 @@
       <c r="V128" s="7"/>
       <c r="W128" s="7"/>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="17"/>
@@ -7463,7 +7460,7 @@
       <c r="V129" s="7"/>
       <c r="W129" s="7"/>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="17"/>
@@ -7486,7 +7483,7 @@
       <c r="V130" s="7"/>
       <c r="W130" s="7"/>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="17"/>
@@ -7509,7 +7506,7 @@
       <c r="V131" s="7"/>
       <c r="W131" s="7"/>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="17"/>
@@ -7532,7 +7529,7 @@
       <c r="V132" s="7"/>
       <c r="W132" s="7"/>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="17"/>
@@ -7555,7 +7552,7 @@
       <c r="V133" s="7"/>
       <c r="W133" s="7"/>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="17"/>
@@ -7578,7 +7575,7 @@
       <c r="V134" s="7"/>
       <c r="W134" s="7"/>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="17"/>
@@ -7601,7 +7598,7 @@
       <c r="V135" s="7"/>
       <c r="W135" s="7"/>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="17"/>
@@ -7624,7 +7621,7 @@
       <c r="V136" s="7"/>
       <c r="W136" s="7"/>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="17"/>
@@ -7647,7 +7644,7 @@
       <c r="V137" s="7"/>
       <c r="W137" s="7"/>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="17"/>
@@ -7670,7 +7667,7 @@
       <c r="V138" s="7"/>
       <c r="W138" s="7"/>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="17"/>
@@ -7693,7 +7690,7 @@
       <c r="V139" s="7"/>
       <c r="W139" s="7"/>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="17"/>
@@ -7716,7 +7713,7 @@
       <c r="V140" s="7"/>
       <c r="W140" s="7"/>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
       <c r="C141" s="17"/>
@@ -7739,7 +7736,7 @@
       <c r="V141" s="7"/>
       <c r="W141" s="7"/>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
       <c r="C142" s="17"/>
@@ -7762,7 +7759,7 @@
       <c r="V142" s="7"/>
       <c r="W142" s="7"/>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
       <c r="C143" s="17"/>
@@ -7785,7 +7782,7 @@
       <c r="V143" s="7"/>
       <c r="W143" s="7"/>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
       <c r="C144" s="17"/>
@@ -7808,7 +7805,7 @@
       <c r="V144" s="7"/>
       <c r="W144" s="7"/>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
       <c r="C145" s="17"/>
@@ -7831,7 +7828,7 @@
       <c r="V145" s="7"/>
       <c r="W145" s="7"/>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
       <c r="C146" s="17"/>
@@ -7854,7 +7851,7 @@
       <c r="V146" s="7"/>
       <c r="W146" s="7"/>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
       <c r="C147" s="17"/>
@@ -7877,7 +7874,7 @@
       <c r="V147" s="7"/>
       <c r="W147" s="7"/>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
       <c r="C148" s="17"/>
@@ -7900,7 +7897,7 @@
       <c r="V148" s="7"/>
       <c r="W148" s="7"/>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
       <c r="C149" s="17"/>
@@ -7923,7 +7920,7 @@
       <c r="V149" s="7"/>
       <c r="W149" s="7"/>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
       <c r="C150" s="17"/>
@@ -7946,7 +7943,7 @@
       <c r="V150" s="7"/>
       <c r="W150" s="7"/>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
       <c r="C151" s="17"/>
@@ -7969,7 +7966,7 @@
       <c r="V151" s="7"/>
       <c r="W151" s="7"/>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
       <c r="C152" s="17"/>
@@ -7992,7 +7989,7 @@
       <c r="V152" s="7"/>
       <c r="W152" s="7"/>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
       <c r="C153" s="17"/>
@@ -8015,7 +8012,7 @@
       <c r="V153" s="7"/>
       <c r="W153" s="7"/>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
       <c r="C154" s="17"/>
@@ -8038,7 +8035,7 @@
       <c r="V154" s="7"/>
       <c r="W154" s="7"/>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="17"/>
@@ -8061,7 +8058,7 @@
       <c r="V155" s="7"/>
       <c r="W155" s="7"/>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
       <c r="C156" s="17"/>
@@ -8084,7 +8081,7 @@
       <c r="V156" s="7"/>
       <c r="W156" s="7"/>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
       <c r="C157" s="17"/>
@@ -8107,7 +8104,7 @@
       <c r="V157" s="7"/>
       <c r="W157" s="7"/>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="17"/>
@@ -8130,7 +8127,7 @@
       <c r="V158" s="7"/>
       <c r="W158" s="7"/>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
       <c r="C159" s="17"/>
@@ -8153,7 +8150,7 @@
       <c r="V159" s="7"/>
       <c r="W159" s="7"/>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
       <c r="C160" s="17"/>
@@ -8176,7 +8173,7 @@
       <c r="V160" s="7"/>
       <c r="W160" s="7"/>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
       <c r="C161" s="17"/>
@@ -8199,7 +8196,7 @@
       <c r="V161" s="7"/>
       <c r="W161" s="7"/>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
       <c r="C162" s="17"/>
@@ -8222,7 +8219,7 @@
       <c r="V162" s="7"/>
       <c r="W162" s="7"/>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
       <c r="C163" s="17"/>
@@ -8245,7 +8242,7 @@
       <c r="V163" s="7"/>
       <c r="W163" s="7"/>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
       <c r="C164" s="17"/>
@@ -8268,7 +8265,7 @@
       <c r="V164" s="7"/>
       <c r="W164" s="7"/>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
       <c r="C165" s="17"/>
@@ -8291,7 +8288,7 @@
       <c r="V165" s="7"/>
       <c r="W165" s="7"/>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
       <c r="C166" s="17"/>
@@ -8314,7 +8311,7 @@
       <c r="V166" s="7"/>
       <c r="W166" s="7"/>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
       <c r="C167" s="17"/>
@@ -8337,7 +8334,7 @@
       <c r="V167" s="7"/>
       <c r="W167" s="7"/>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
       <c r="C168" s="17"/>
@@ -8360,7 +8357,7 @@
       <c r="V168" s="7"/>
       <c r="W168" s="7"/>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
       <c r="C169" s="17"/>
@@ -8383,7 +8380,7 @@
       <c r="V169" s="7"/>
       <c r="W169" s="7"/>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
       <c r="C170" s="17"/>
@@ -8406,7 +8403,7 @@
       <c r="V170" s="7"/>
       <c r="W170" s="7"/>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
       <c r="C171" s="17"/>
@@ -8429,7 +8426,7 @@
       <c r="V171" s="7"/>
       <c r="W171" s="7"/>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
       <c r="C172" s="17"/>
@@ -8452,7 +8449,7 @@
       <c r="V172" s="7"/>
       <c r="W172" s="7"/>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
       <c r="C173" s="17"/>
@@ -8475,7 +8472,7 @@
       <c r="V173" s="7"/>
       <c r="W173" s="7"/>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
       <c r="C174" s="17"/>
@@ -8498,7 +8495,7 @@
       <c r="V174" s="7"/>
       <c r="W174" s="7"/>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
       <c r="C175" s="17"/>
@@ -8521,7 +8518,7 @@
       <c r="V175" s="7"/>
       <c r="W175" s="7"/>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
       <c r="C176" s="17"/>
@@ -8544,7 +8541,7 @@
       <c r="V176" s="7"/>
       <c r="W176" s="7"/>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
       <c r="C177" s="17"/>
@@ -8567,7 +8564,7 @@
       <c r="V177" s="7"/>
       <c r="W177" s="7"/>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
       <c r="C178" s="17"/>
@@ -8590,7 +8587,7 @@
       <c r="V178" s="7"/>
       <c r="W178" s="7"/>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
       <c r="C179" s="17"/>
@@ -8613,7 +8610,7 @@
       <c r="V179" s="7"/>
       <c r="W179" s="7"/>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
       <c r="C180" s="17"/>
@@ -8636,7 +8633,7 @@
       <c r="V180" s="7"/>
       <c r="W180" s="7"/>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
       <c r="C181" s="17"/>
@@ -8659,7 +8656,7 @@
       <c r="V181" s="7"/>
       <c r="W181" s="7"/>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
       <c r="C182" s="17"/>
@@ -8682,7 +8679,7 @@
       <c r="V182" s="7"/>
       <c r="W182" s="7"/>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
       <c r="C183" s="17"/>
@@ -8705,7 +8702,7 @@
       <c r="V183" s="7"/>
       <c r="W183" s="7"/>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
       <c r="C184" s="17"/>
@@ -8728,7 +8725,7 @@
       <c r="V184" s="7"/>
       <c r="W184" s="7"/>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
       <c r="C185" s="17"/>
@@ -8751,7 +8748,7 @@
       <c r="V185" s="7"/>
       <c r="W185" s="7"/>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
       <c r="C186" s="17"/>
@@ -8774,7 +8771,7 @@
       <c r="V186" s="7"/>
       <c r="W186" s="7"/>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A187" s="19"/>
       <c r="B187" s="19"/>
       <c r="C187" s="19"/>
@@ -8793,7 +8790,7 @@
       <c r="S187" s="19"/>
       <c r="T187" s="19"/>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A188" s="19"/>
       <c r="B188" s="19"/>
       <c r="C188" s="19"/>
@@ -8812,7 +8809,7 @@
       <c r="S188" s="19"/>
       <c r="T188" s="19"/>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A189" s="19"/>
       <c r="B189" s="19"/>
       <c r="C189" s="19"/>
@@ -8840,7 +8837,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="L19:R61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="12" max="12" width="5.1640625" customWidth="1"/>
     <col min="13" max="13" width="18.33203125" customWidth="1"/>
@@ -8848,38 +8845,38 @@
     <col min="16" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L19" t="s">
+        <v>251</v>
+      </c>
+      <c r="M19" t="s">
+        <v>252</v>
+      </c>
+      <c r="N19" t="s">
+        <v>253</v>
+      </c>
+      <c r="P19" t="s">
         <v>254</v>
       </c>
-      <c r="M19" t="s">
+      <c r="R19" t="s">
         <v>255</v>
       </c>
-      <c r="N19" t="s">
-        <v>256</v>
-      </c>
-      <c r="P19" t="s">
-        <v>257</v>
-      </c>
-      <c r="R19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L20">
         <v>5001</v>
       </c>
       <c r="M20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -8889,21 +8886,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L21">
         <v>5002</v>
       </c>
       <c r="M21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P21" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -8913,21 +8910,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L22">
         <v>5003</v>
       </c>
       <c r="M22" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22" t="s">
+        <v>256</v>
+      </c>
+      <c r="P22" t="s">
         <v>259</v>
-      </c>
-      <c r="P22" t="s">
-        <v>262</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -8937,21 +8934,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L23">
         <v>5004</v>
       </c>
       <c r="M23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P23" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -8961,21 +8958,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L24">
         <v>5005</v>
       </c>
       <c r="M24" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -8985,21 +8982,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L25">
         <v>5006</v>
       </c>
       <c r="M25" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -9009,21 +9006,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L26">
         <v>5007</v>
       </c>
       <c r="M26" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P26" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -9033,21 +9030,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L27">
         <v>5008</v>
       </c>
       <c r="M27" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P27" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -9057,21 +9054,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L28">
         <v>5009</v>
       </c>
       <c r="M28" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P28" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -9081,18 +9078,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L29">
         <v>6001</v>
       </c>
       <c r="M29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="O29" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P29" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -9102,18 +9099,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L30">
         <v>6002</v>
       </c>
       <c r="M30" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O30" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -9123,18 +9120,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L31">
         <v>6003</v>
       </c>
       <c r="M31" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O31" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P31" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -9144,18 +9141,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L32">
         <v>6004</v>
       </c>
       <c r="M32" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O32" t="s">
+        <v>266</v>
+      </c>
+      <c r="P32" t="s">
         <v>269</v>
-      </c>
-      <c r="P32" t="s">
-        <v>272</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -9165,18 +9162,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L33">
         <v>6005</v>
       </c>
       <c r="M33" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O33" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P33" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -9186,18 +9183,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L34">
         <v>6006</v>
       </c>
       <c r="M34" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="O34" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P34" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -9207,18 +9204,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L35">
         <v>6007</v>
       </c>
       <c r="M35" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="O35" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P35" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -9228,18 +9225,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L36">
         <v>6008</v>
       </c>
       <c r="M36" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O36" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P36" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -9249,18 +9246,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L37">
         <v>6009</v>
       </c>
       <c r="M37" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O37" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P37" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -9270,18 +9267,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L38">
         <v>6010</v>
       </c>
       <c r="M38" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="O38" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P38" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -9291,18 +9288,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L39">
         <v>6011</v>
       </c>
       <c r="M39" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O39" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P39" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -9312,18 +9309,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L40">
         <v>6012</v>
       </c>
       <c r="M40" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="O40" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P40" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -9333,18 +9330,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L41">
         <v>6013</v>
       </c>
       <c r="M41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O41" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P41" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -9354,18 +9351,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L42">
         <v>6014</v>
       </c>
       <c r="M42" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="O42" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -9375,18 +9372,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L43">
         <v>6015</v>
       </c>
       <c r="M43" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O43" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="P43" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -9396,21 +9393,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L44">
         <v>7001</v>
       </c>
       <c r="M44" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N44">
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P44" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -9420,21 +9417,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L45">
         <v>7002</v>
       </c>
       <c r="M45" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P45" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -9444,21 +9441,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L46">
         <v>7003</v>
       </c>
       <c r="M46" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46" t="s">
+        <v>275</v>
+      </c>
+      <c r="P46" t="s">
         <v>278</v>
-      </c>
-      <c r="P46" t="s">
-        <v>281</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -9468,21 +9465,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L47">
         <v>7004</v>
       </c>
       <c r="M47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -9492,21 +9489,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L48">
         <v>8001</v>
       </c>
       <c r="M48" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
       <c r="O48" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P48" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -9516,21 +9513,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L49">
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P49" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -9540,21 +9537,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L50">
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P50" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -9564,21 +9561,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L51">
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P51" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -9588,21 +9585,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L52">
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P52" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -9612,21 +9609,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L53">
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P53" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -9636,21 +9633,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L54">
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P54" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -9660,21 +9657,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L55">
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P55" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -9684,21 +9681,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L56">
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P56" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -9708,21 +9705,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L57">
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P57" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -9732,21 +9729,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L58">
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P58" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -9756,21 +9753,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L59">
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -9780,21 +9777,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L60">
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P60" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -9804,21 +9801,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="12:18" x14ac:dyDescent="0.2">
       <c r="L61">
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="P61" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42B100D-7009-E547-98EA-70E9ACCB7EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A927ED-08EB-46E2-AC58-0C92C90A547C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="2540" windowWidth="23600" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$AB$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$AB$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="334">
   <si>
     <t>##var</t>
   </si>
@@ -748,9 +748,6 @@
   </si>
   <si>
     <t>土豆-幼苗</t>
-  </si>
-  <si>
-    <t>prefab/plant/Seedling</t>
   </si>
   <si>
     <t>蘑菇-幼苗</t>
@@ -945,17 +942,125 @@
   </si>
   <si>
     <t>Prefab/Plants/WaterBeet</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;蘑菇味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;南瓜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;南瓜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-猕猴桃&amp;野草味</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -963,7 +1068,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -972,7 +1077,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -981,7 +1086,7 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -989,7 +1094,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -997,7 +1102,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1006,7 +1111,7 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1014,14 +1119,14 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1029,21 +1134,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1052,7 +1157,15 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1197,7 +1310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1239,9 +1352,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1267,9 +1377,15 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1542,18 +1658,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB189"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AB210"/>
+  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="12.1640625" style="2"/>
     <col min="3" max="3" width="22.83203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="36.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.58203125" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.33203125" style="2" customWidth="1"/>
-    <col min="8" max="9" width="16.1640625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="16" style="2" customWidth="1"/>
-    <col min="11" max="13" width="16.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.9140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.4140625" style="2" customWidth="1"/>
+    <col min="10" max="12" width="7.08203125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" style="2" customWidth="1"/>
     <col min="14" max="18" width="12.1640625" style="2"/>
     <col min="19" max="20" width="17.83203125" style="2" customWidth="1"/>
     <col min="21" max="22" width="26.33203125" style="2" customWidth="1"/>
@@ -1561,7 +1678,7 @@
     <col min="29" max="16384" width="12.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1572,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
@@ -1581,7 +1698,7 @@
         <v>4</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>5</v>
@@ -1640,11 +1757,11 @@
       <c r="Z1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="23" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA1" s="22" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>24</v>
       </c>
@@ -1723,11 +1840,11 @@
       <c r="Z2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="24" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA2" s="23" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
@@ -1747,7 +1864,7 @@
         <v>33</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>34</v>
@@ -1806,11 +1923,11 @@
       <c r="Z3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AA3" s="23" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AA3" s="22" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>28</v>
       </c>
@@ -1890,10 +2007,10 @@
         <v>69</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="2">
         <v>1001</v>
@@ -1905,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="2">
@@ -1924,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N5" s="2">
         <v>1</v>
@@ -1939,7 +2056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="2">
         <v>1002</v>
@@ -1970,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N6" s="2">
         <v>1</v>
@@ -1985,7 +2102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="2">
         <v>1003</v>
@@ -2016,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N7" s="2">
         <v>1</v>
@@ -2031,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="2">
         <v>1004</v>
@@ -2062,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="M8" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N8" s="2">
         <v>1</v>
@@ -2077,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="2">
         <v>1005</v>
@@ -2089,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="2">
@@ -2108,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N9" s="2">
         <v>1</v>
@@ -2123,7 +2240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="2">
         <v>1006</v>
@@ -2154,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N10" s="2">
         <v>1</v>
@@ -2169,7 +2286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
       <c r="B11" s="2">
         <v>1007</v>
@@ -2200,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N11" s="2">
         <v>1</v>
@@ -2215,7 +2332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
       <c r="B12" s="2">
         <v>1008</v>
@@ -2246,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N12" s="2">
         <v>1</v>
@@ -2261,7 +2378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
       <c r="B13" s="2">
         <v>1009</v>
@@ -2292,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N13" s="2">
         <v>1</v>
@@ -2307,7 +2424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
       <c r="B14" s="2">
         <v>1010</v>
@@ -2338,7 +2455,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N14" s="2">
         <v>1</v>
@@ -2353,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
       <c r="B15" s="2">
         <v>1011</v>
@@ -2384,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N15" s="2">
         <v>1</v>
@@ -2399,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
       <c r="B16" s="2">
         <v>1012</v>
@@ -2430,7 +2547,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N16" s="2">
         <v>1</v>
@@ -2445,7 +2562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
       <c r="B17" s="2">
         <v>1013</v>
@@ -2476,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N17" s="2">
         <v>1</v>
@@ -2491,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>1014</v>
       </c>
@@ -2521,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N18" s="2">
         <v>1</v>
@@ -2536,15 +2653,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>2001</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>285</v>
+      <c r="D19" s="20" t="s">
+        <v>284</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -2552,8 +2669,8 @@
       <c r="F19" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G19" s="22" t="s">
-        <v>291</v>
+      <c r="G19" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -2598,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>2002</v>
       </c>
@@ -2606,7 +2723,7 @@
         <v>100</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
@@ -2614,8 +2731,8 @@
       <c r="F20" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="22" t="s">
-        <v>291</v>
+      <c r="G20" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2633,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N20" s="1">
         <v>0</v>
@@ -2657,7 +2774,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>2003</v>
       </c>
@@ -2665,7 +2782,7 @@
         <v>104</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
@@ -2673,8 +2790,8 @@
       <c r="F21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G21" s="22" t="s">
-        <v>291</v>
+      <c r="G21" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2692,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N21" s="1">
         <v>0</v>
@@ -2716,7 +2833,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>2004</v>
       </c>
@@ -2724,7 +2841,7 @@
         <v>109</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E22" s="2">
         <v>2</v>
@@ -2732,8 +2849,8 @@
       <c r="F22" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="22" t="s">
-        <v>291</v>
+      <c r="G22" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2781,7 +2898,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>2005</v>
       </c>
@@ -2789,7 +2906,7 @@
         <v>115</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E23" s="2">
         <v>2</v>
@@ -2797,8 +2914,8 @@
       <c r="F23" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="22" t="s">
-        <v>291</v>
+      <c r="G23" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2816,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N23" s="1">
         <v>0</v>
@@ -2840,7 +2957,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>2006</v>
       </c>
@@ -2848,7 +2965,7 @@
         <v>120</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E24" s="2">
         <v>2</v>
@@ -2856,8 +2973,8 @@
       <c r="F24" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G24" s="22" t="s">
-        <v>291</v>
+      <c r="G24" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -2899,7 +3016,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>2007</v>
       </c>
@@ -2907,7 +3024,7 @@
         <v>125</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E25" s="2">
         <v>2</v>
@@ -2915,8 +3032,8 @@
       <c r="F25" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G25" s="22" t="s">
-        <v>291</v>
+      <c r="G25" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -2958,7 +3075,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>2008</v>
       </c>
@@ -2966,7 +3083,7 @@
         <v>126</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E26" s="2">
         <v>2</v>
@@ -2974,8 +3091,8 @@
       <c r="F26" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G26" s="22" t="s">
-        <v>291</v>
+      <c r="G26" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3017,7 +3134,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>2009</v>
       </c>
@@ -3025,7 +3142,7 @@
         <v>128</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E27" s="2">
         <v>2</v>
@@ -3033,8 +3150,8 @@
       <c r="F27" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G27" s="22" t="s">
-        <v>291</v>
+      <c r="G27" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3076,7 +3193,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>2010</v>
       </c>
@@ -3084,7 +3201,7 @@
         <v>130</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E28" s="2">
         <v>2</v>
@@ -3092,8 +3209,8 @@
       <c r="F28" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G28" s="22" t="s">
-        <v>291</v>
+      <c r="G28" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3135,7 +3252,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>2011</v>
       </c>
@@ -3143,7 +3260,7 @@
         <v>131</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E29" s="2">
         <v>2</v>
@@ -3151,8 +3268,8 @@
       <c r="F29" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G29" s="22" t="s">
-        <v>291</v>
+      <c r="G29" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3194,7 +3311,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>2012</v>
       </c>
@@ -3202,7 +3319,7 @@
         <v>132</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E30" s="2">
         <v>2</v>
@@ -3210,8 +3327,8 @@
       <c r="F30" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G30" s="22" t="s">
-        <v>291</v>
+      <c r="G30" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3253,7 +3370,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>2013</v>
       </c>
@@ -3261,7 +3378,7 @@
         <v>133</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E31" s="2">
         <v>2</v>
@@ -3269,8 +3386,8 @@
       <c r="F31" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G31" s="22" t="s">
-        <v>291</v>
+      <c r="G31" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3288,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N31" s="1">
         <v>0</v>
@@ -3312,7 +3429,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>2014</v>
       </c>
@@ -3320,7 +3437,7 @@
         <v>136</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E32" s="2">
         <v>2</v>
@@ -3328,8 +3445,8 @@
       <c r="F32" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G32" s="22" t="s">
-        <v>291</v>
+      <c r="G32" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -3347,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N32" s="1">
         <v>0</v>
@@ -3371,7 +3488,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>2015</v>
       </c>
@@ -3379,7 +3496,7 @@
         <v>138</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E33" s="2">
         <v>2</v>
@@ -3387,8 +3504,8 @@
       <c r="F33" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="G33" s="22" t="s">
-        <v>291</v>
+      <c r="G33" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -3406,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="2">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N33" s="1">
         <v>0</v>
@@ -3436,7 +3553,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <v>2016</v>
       </c>
@@ -3444,7 +3561,7 @@
         <v>143</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E34" s="2">
         <v>2</v>
@@ -3452,8 +3569,8 @@
       <c r="F34" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="G34" s="22" t="s">
-        <v>291</v>
+      <c r="G34" s="21" t="s">
+        <v>290</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -3495,7 +3612,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="35" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B35" s="1">
         <v>3001</v>
       </c>
@@ -3521,7 +3638,7 @@
       <c r="L35" s="2">
         <v>0</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35" s="1">
         <v>0.3</v>
       </c>
       <c r="N35" s="1">
@@ -3540,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <v>3002</v>
       </c>
@@ -3567,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N36" s="1">
         <v>0</v>
@@ -3585,11 +3702,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>3003</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>149</v>
       </c>
       <c r="E37" s="2">
@@ -3629,11 +3746,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <v>3004</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>151</v>
       </c>
       <c r="E38" s="2">
@@ -3655,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="2">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="N38" s="1">
         <v>0</v>
@@ -3673,11 +3790,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <v>3005</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E39" s="2">
@@ -3699,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="2">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N39" s="1">
         <v>0</v>
@@ -3717,11 +3834,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <v>3006</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="24" t="s">
         <v>155</v>
       </c>
       <c r="E40" s="2">
@@ -3761,7 +3878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <v>3007</v>
       </c>
@@ -3805,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <v>3008</v>
       </c>
@@ -3849,7 +3966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>3009</v>
       </c>
@@ -3893,7 +4010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>3010</v>
       </c>
@@ -3937,7 +4054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>3011</v>
       </c>
@@ -3981,7 +4098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>3012</v>
       </c>
@@ -4025,7 +4142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>3013</v>
       </c>
@@ -4052,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N47" s="1">
         <v>0</v>
@@ -4070,11 +4187,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>3014</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E48" s="2">
@@ -4097,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="2">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="N48" s="1">
         <v>0</v>
@@ -4115,11 +4232,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>3015</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="1" t="s">
         <v>173</v>
       </c>
       <c r="E49" s="2">
@@ -4159,7 +4276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1">
         <v>4001</v>
       </c>
@@ -4204,7 +4321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <v>4002</v>
       </c>
@@ -4249,7 +4366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <v>4003</v>
       </c>
@@ -4293,7 +4410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <v>4004</v>
       </c>
@@ -4337,7 +4454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <v>4005</v>
       </c>
@@ -4381,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <v>4006</v>
       </c>
@@ -4425,7 +4542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <v>4007</v>
       </c>
@@ -4469,7 +4586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <v>4008</v>
       </c>
@@ -4513,7 +4630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <v>4009</v>
       </c>
@@ -4557,7 +4674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <v>4010</v>
       </c>
@@ -4601,7 +4718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
         <v>4011</v>
       </c>
@@ -4645,7 +4762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B61" s="2">
         <v>4012</v>
       </c>
@@ -4689,7 +4806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B62" s="2">
         <v>4013</v>
       </c>
@@ -4734,7 +4851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
         <v>4014</v>
       </c>
@@ -4779,7 +4896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <v>4015</v>
       </c>
@@ -4823,7 +4940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B65" s="1">
         <v>5001</v>
       </c>
@@ -4834,7 +4951,7 @@
         <v>5</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G65" s="11"/>
       <c r="H65" s="1">
@@ -4850,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="2">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N65" s="1">
         <v>1</v>
@@ -4874,7 +4991,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
         <v>5002</v>
       </c>
@@ -4923,7 +5040,7 @@
       <c r="AA66" s="2"/>
       <c r="AB66" s="2"/>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A67" s="7"/>
       <c r="B67" s="2">
         <v>5003</v>
@@ -4974,7 +5091,7 @@
       </c>
       <c r="W67" s="7"/>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A68" s="7"/>
       <c r="B68" s="2">
         <v>5004</v>
@@ -5025,7 +5142,7 @@
       </c>
       <c r="W68" s="7"/>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A69" s="7"/>
       <c r="B69" s="2">
         <v>5005</v>
@@ -5076,7 +5193,7 @@
       </c>
       <c r="W69" s="7"/>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A70" s="7"/>
       <c r="B70" s="2">
         <v>5006</v>
@@ -5127,7 +5244,7 @@
       </c>
       <c r="W70" s="7"/>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A71" s="7"/>
       <c r="B71" s="2">
         <v>5007</v>
@@ -5178,7 +5295,7 @@
       </c>
       <c r="W71" s="7"/>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A72" s="7"/>
       <c r="B72" s="2">
         <v>5008</v>
@@ -5229,34 +5346,34 @@
       </c>
       <c r="W72" s="7"/>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B73" s="2">
+    <row r="73" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="20">
         <v>5009</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E73" s="2">
+      <c r="C73" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E73" s="1">
         <v>5</v>
       </c>
-      <c r="F73" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G73" s="20"/>
-      <c r="H73" s="7">
-        <v>1</v>
-      </c>
-      <c r="I73" s="12"/>
-      <c r="J73" s="2">
-        <v>0</v>
-      </c>
-      <c r="K73" s="2">
-        <v>0</v>
-      </c>
-      <c r="L73" s="2">
-        <v>0</v>
-      </c>
-      <c r="M73" s="2">
+      <c r="F73" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="G73" s="25"/>
+      <c r="H73" s="13">
+        <v>1</v>
+      </c>
+      <c r="I73" s="14"/>
+      <c r="J73" s="1">
+        <v>0</v>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1">
         <v>0.3</v>
       </c>
       <c r="N73" s="1">
@@ -5265,45 +5382,41 @@
       <c r="O73" s="1">
         <v>0</v>
       </c>
-      <c r="P73" s="2">
-        <v>1</v>
-      </c>
-      <c r="S73" s="2" t="s">
+      <c r="P73" s="1">
+        <v>1</v>
+      </c>
+      <c r="S73" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="V73" s="2">
-        <v>1</v>
-      </c>
-      <c r="X73" s="2"/>
-      <c r="Y73" s="2"/>
-      <c r="Z73" s="2"/>
-      <c r="AA73" s="2"/>
-      <c r="AB73" s="2"/>
-    </row>
-    <row r="74" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B74" s="1">
-        <v>6001</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E74" s="1">
-        <v>6</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="H74" s="13">
-        <v>1</v>
-      </c>
-      <c r="I74" s="14"/>
-      <c r="J74" s="1">
-        <v>0</v>
-      </c>
-      <c r="K74" s="1">
-        <v>0</v>
-      </c>
-      <c r="L74" s="1">
+      <c r="V73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B74" s="21">
+        <v>5010</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E74" s="2">
+        <v>5</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G74" s="19"/>
+      <c r="H74" s="7">
+        <v>1</v>
+      </c>
+      <c r="I74" s="12"/>
+      <c r="J74" s="2">
+        <v>0</v>
+      </c>
+      <c r="K74" s="2">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2">
         <v>0</v>
       </c>
       <c r="M74" s="2">
@@ -5315,29 +5428,35 @@
       <c r="O74" s="1">
         <v>0</v>
       </c>
-      <c r="P74" s="1">
-        <v>1</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="V74" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B75" s="2">
-        <v>6002</v>
+      <c r="P74" s="2">
+        <v>1</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="V74" s="2">
+        <v>1</v>
+      </c>
+      <c r="X74" s="2"/>
+      <c r="Y74" s="2"/>
+      <c r="Z74" s="2"/>
+      <c r="AA74" s="2"/>
+      <c r="AB74" s="2"/>
+    </row>
+    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B75" s="21">
+        <v>5011</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="E75" s="2">
-        <v>6</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>208</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G75" s="19"/>
       <c r="H75" s="7">
         <v>1</v>
       </c>
@@ -5364,25 +5483,31 @@
         <v>1</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="V75" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B76" s="2">
-        <v>6003</v>
+        <v>1</v>
+      </c>
+      <c r="X75" s="2"/>
+      <c r="Y75" s="2"/>
+      <c r="Z75" s="2"/>
+      <c r="AA75" s="2"/>
+      <c r="AB75" s="2"/>
+    </row>
+    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B76" s="21">
+        <v>5012</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>210</v>
+        <v>301</v>
       </c>
       <c r="E76" s="2">
-        <v>6</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>211</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G76" s="19"/>
       <c r="H76" s="7">
         <v>1</v>
       </c>
@@ -5409,25 +5534,31 @@
         <v>1</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>150</v>
+        <v>117</v>
       </c>
       <c r="V76" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B77" s="2">
-        <v>6004</v>
+        <v>1</v>
+      </c>
+      <c r="X76" s="2"/>
+      <c r="Y76" s="2"/>
+      <c r="Z76" s="2"/>
+      <c r="AA76" s="2"/>
+      <c r="AB76" s="2"/>
+    </row>
+    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B77" s="21">
+        <v>5013</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>212</v>
+        <v>302</v>
       </c>
       <c r="E77" s="2">
-        <v>6</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>213</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G77" s="19"/>
       <c r="H77" s="7">
         <v>1</v>
       </c>
@@ -5454,25 +5585,31 @@
         <v>1</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="V77" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B78" s="2">
-        <v>6005</v>
+        <v>1</v>
+      </c>
+      <c r="X77" s="2"/>
+      <c r="Y77" s="2"/>
+      <c r="Z77" s="2"/>
+      <c r="AA77" s="2"/>
+      <c r="AB77" s="2"/>
+    </row>
+    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B78" s="21">
+        <v>5014</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>214</v>
+        <v>303</v>
       </c>
       <c r="E78" s="2">
-        <v>6</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>215</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G78" s="19"/>
       <c r="H78" s="7">
         <v>1</v>
       </c>
@@ -5499,25 +5636,31 @@
         <v>1</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>154</v>
+        <v>117</v>
       </c>
       <c r="V78" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B79" s="2">
-        <v>6006</v>
+        <v>1</v>
+      </c>
+      <c r="X78" s="2"/>
+      <c r="Y78" s="2"/>
+      <c r="Z78" s="2"/>
+      <c r="AA78" s="2"/>
+      <c r="AB78" s="2"/>
+    </row>
+    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B79" s="21">
+        <v>5015</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>216</v>
+        <v>304</v>
       </c>
       <c r="E79" s="2">
-        <v>6</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G79" s="19"/>
       <c r="H79" s="7">
         <v>1</v>
       </c>
@@ -5544,25 +5687,31 @@
         <v>1</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="V79" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B80" s="2">
-        <v>6007</v>
+        <v>1</v>
+      </c>
+      <c r="X79" s="2"/>
+      <c r="Y79" s="2"/>
+      <c r="Z79" s="2"/>
+      <c r="AA79" s="2"/>
+      <c r="AB79" s="2"/>
+    </row>
+    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B80" s="21">
+        <v>5016</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>218</v>
+        <v>305</v>
       </c>
       <c r="E80" s="2">
-        <v>6</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G80" s="19"/>
       <c r="H80" s="7">
         <v>1</v>
       </c>
@@ -5589,25 +5738,31 @@
         <v>1</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="V80" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B81" s="2">
-        <v>6008</v>
+        <v>1</v>
+      </c>
+      <c r="X80" s="2"/>
+      <c r="Y80" s="2"/>
+      <c r="Z80" s="2"/>
+      <c r="AA80" s="2"/>
+      <c r="AB80" s="2"/>
+    </row>
+    <row r="81" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B81" s="21">
+        <v>5017</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>219</v>
+        <v>306</v>
       </c>
       <c r="E81" s="2">
-        <v>6</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>220</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G81" s="19"/>
       <c r="H81" s="7">
         <v>1</v>
       </c>
@@ -5634,25 +5789,31 @@
         <v>1</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="V81" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B82" s="2">
-        <v>6009</v>
+        <v>1</v>
+      </c>
+      <c r="X81" s="2"/>
+      <c r="Y81" s="2"/>
+      <c r="Z81" s="2"/>
+      <c r="AA81" s="2"/>
+      <c r="AB81" s="2"/>
+    </row>
+    <row r="82" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B82" s="21">
+        <v>5018</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>221</v>
+        <v>307</v>
       </c>
       <c r="E82" s="2">
-        <v>6</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>222</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G82" s="19"/>
       <c r="H82" s="7">
         <v>1</v>
       </c>
@@ -5679,25 +5840,31 @@
         <v>1</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="V82" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B83" s="2">
-        <v>6010</v>
+        <v>1</v>
+      </c>
+      <c r="X82" s="2"/>
+      <c r="Y82" s="2"/>
+      <c r="Z82" s="2"/>
+      <c r="AA82" s="2"/>
+      <c r="AB82" s="2"/>
+    </row>
+    <row r="83" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B83" s="21">
+        <v>5019</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>223</v>
+        <v>308</v>
       </c>
       <c r="E83" s="2">
-        <v>6</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G83" s="19"/>
       <c r="H83" s="7">
         <v>1</v>
       </c>
@@ -5724,25 +5891,31 @@
         <v>1</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>164</v>
+        <v>117</v>
       </c>
       <c r="V83" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B84" s="2">
-        <v>6011</v>
+        <v>1</v>
+      </c>
+      <c r="X83" s="2"/>
+      <c r="Y83" s="2"/>
+      <c r="Z83" s="2"/>
+      <c r="AA83" s="2"/>
+      <c r="AB83" s="2"/>
+    </row>
+    <row r="84" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B84" s="21">
+        <v>5020</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>224</v>
+        <v>309</v>
       </c>
       <c r="E84" s="2">
-        <v>6</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G84" s="19"/>
       <c r="H84" s="7">
         <v>1</v>
       </c>
@@ -5769,25 +5942,31 @@
         <v>1</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="V84" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B85" s="2">
-        <v>6012</v>
+        <v>1</v>
+      </c>
+      <c r="X84" s="2"/>
+      <c r="Y84" s="2"/>
+      <c r="Z84" s="2"/>
+      <c r="AA84" s="2"/>
+      <c r="AB84" s="2"/>
+    </row>
+    <row r="85" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B85" s="21">
+        <v>5021</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>225</v>
+        <v>310</v>
       </c>
       <c r="E85" s="2">
-        <v>6</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>217</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G85" s="19"/>
       <c r="H85" s="7">
         <v>1</v>
       </c>
@@ -5814,25 +5993,31 @@
         <v>1</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="V85" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B86" s="2">
-        <v>6013</v>
+        <v>1</v>
+      </c>
+      <c r="X85" s="2"/>
+      <c r="Y85" s="2"/>
+      <c r="Z85" s="2"/>
+      <c r="AA85" s="2"/>
+      <c r="AB85" s="2"/>
+    </row>
+    <row r="86" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B86" s="21">
+        <v>5022</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="E86" s="2">
-        <v>6</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>208</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G86" s="19"/>
       <c r="H86" s="7">
         <v>1</v>
       </c>
@@ -5859,25 +6044,31 @@
         <v>1</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="V86" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B87" s="2">
-        <v>6014</v>
+        <v>1</v>
+      </c>
+      <c r="X86" s="2"/>
+      <c r="Y86" s="2"/>
+      <c r="Z86" s="2"/>
+      <c r="AA86" s="2"/>
+      <c r="AB86" s="2"/>
+    </row>
+    <row r="87" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B87" s="21">
+        <v>5023</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="E87" s="2">
-        <v>6</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G87" s="19"/>
       <c r="H87" s="7">
         <v>1</v>
       </c>
@@ -5904,25 +6095,31 @@
         <v>1</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="V87" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B88" s="2">
-        <v>6015</v>
+        <v>1</v>
+      </c>
+      <c r="X87" s="2"/>
+      <c r="Y87" s="2"/>
+      <c r="Z87" s="2"/>
+      <c r="AA87" s="2"/>
+      <c r="AB87" s="2"/>
+    </row>
+    <row r="88" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B88" s="21">
+        <v>5024</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>229</v>
+        <v>313</v>
       </c>
       <c r="E88" s="2">
-        <v>6</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>208</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G88" s="19"/>
       <c r="H88" s="7">
         <v>1</v>
       </c>
@@ -5931,7 +6128,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2">
         <v>0</v>
@@ -5949,50 +6146,49 @@
         <v>1</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="V88" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="13"/>
-      <c r="B89" s="13">
-        <v>7001</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E89" s="13">
-        <v>7</v>
-      </c>
-      <c r="F89" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="G89" s="22" t="s">
-        <v>291</v>
-      </c>
-      <c r="H89" s="13">
-        <v>1</v>
-      </c>
-      <c r="I89" s="14"/>
+        <v>1</v>
+      </c>
+      <c r="X88" s="2"/>
+      <c r="Y88" s="2"/>
+      <c r="Z88" s="2"/>
+      <c r="AA88" s="2"/>
+      <c r="AB88" s="2"/>
+    </row>
+    <row r="89" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B89" s="21">
+        <v>5025</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E89" s="2">
+        <v>5</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G89" s="19"/>
+      <c r="H89" s="7">
+        <v>1</v>
+      </c>
+      <c r="I89" s="12"/>
       <c r="J89" s="2">
         <v>0</v>
       </c>
       <c r="K89" s="2">
         <v>0</v>
       </c>
-      <c r="L89" s="7">
+      <c r="L89" s="2">
         <v>0</v>
       </c>
       <c r="M89" s="2">
         <v>0.3</v>
       </c>
       <c r="N89" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" s="1">
         <v>0</v>
@@ -6000,41 +6196,32 @@
       <c r="P89" s="2">
         <v>1</v>
       </c>
-      <c r="Q89" s="13"/>
-      <c r="R89" s="13"/>
-      <c r="S89" s="13"/>
-      <c r="T89" s="13"/>
-      <c r="U89" s="13"/>
+      <c r="S89" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V89" s="2">
-        <v>0</v>
-      </c>
-      <c r="W89" s="13"/>
-      <c r="X89" s="18"/>
-      <c r="Y89" s="18"/>
-      <c r="Z89" s="18"/>
-      <c r="AA89" s="18"/>
-      <c r="AB89" s="18"/>
-    </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A90" s="7"/>
-      <c r="B90" s="7">
-        <v>7002</v>
-      </c>
-      <c r="C90" s="22" t="s">
-        <v>292</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E90" s="7">
-        <v>7</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G90" s="22" t="s">
-        <v>291</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X89" s="2"/>
+      <c r="Y89" s="2"/>
+      <c r="Z89" s="2"/>
+      <c r="AA89" s="2"/>
+      <c r="AB89" s="2"/>
+    </row>
+    <row r="90" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B90" s="21">
+        <v>5026</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E90" s="2">
+        <v>5</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G90" s="19"/>
       <c r="H90" s="7">
         <v>1</v>
       </c>
@@ -6045,14 +6232,14 @@
       <c r="K90" s="2">
         <v>0</v>
       </c>
-      <c r="L90" s="7">
+      <c r="L90" s="2">
         <v>0</v>
       </c>
       <c r="M90" s="2">
         <v>0.3</v>
       </c>
       <c r="N90" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" s="1">
         <v>0</v>
@@ -6060,36 +6247,32 @@
       <c r="P90" s="2">
         <v>1</v>
       </c>
-      <c r="Q90" s="7"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="7"/>
-      <c r="T90" s="7"/>
-      <c r="U90" s="7"/>
+      <c r="S90" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V90" s="2">
-        <v>0</v>
-      </c>
-      <c r="W90" s="7"/>
-    </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A91" s="7"/>
-      <c r="B91" s="7">
-        <v>7003</v>
+        <v>1</v>
+      </c>
+      <c r="X90" s="2"/>
+      <c r="Y90" s="2"/>
+      <c r="Z90" s="2"/>
+      <c r="AA90" s="2"/>
+      <c r="AB90" s="2"/>
+    </row>
+    <row r="91" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B91" s="21">
+        <v>5027</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E91" s="7">
-        <v>7</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="G91" s="22" t="s">
-        <v>291</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="E91" s="2">
+        <v>5</v>
+      </c>
+      <c r="F91" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G91" s="19"/>
       <c r="H91" s="7">
         <v>1</v>
       </c>
@@ -6100,14 +6283,14 @@
       <c r="K91" s="2">
         <v>0</v>
       </c>
-      <c r="L91" s="7">
+      <c r="L91" s="2">
         <v>0</v>
       </c>
       <c r="M91" s="2">
         <v>0.3</v>
       </c>
       <c r="N91" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" s="1">
         <v>0</v>
@@ -6115,36 +6298,32 @@
       <c r="P91" s="2">
         <v>1</v>
       </c>
-      <c r="Q91" s="7"/>
-      <c r="R91" s="7"/>
-      <c r="S91" s="7"/>
-      <c r="T91" s="7"/>
-      <c r="U91" s="7"/>
+      <c r="S91" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V91" s="2">
-        <v>0</v>
-      </c>
-      <c r="W91" s="7"/>
-    </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A92" s="7"/>
-      <c r="B92" s="7">
-        <v>7004</v>
+        <v>1</v>
+      </c>
+      <c r="X91" s="2"/>
+      <c r="Y91" s="2"/>
+      <c r="Z91" s="2"/>
+      <c r="AA91" s="2"/>
+      <c r="AB91" s="2"/>
+    </row>
+    <row r="92" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B92" s="21">
+        <v>5028</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E92" s="7">
-        <v>7</v>
-      </c>
-      <c r="F92" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="G92" s="22" t="s">
-        <v>291</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="E92" s="2">
+        <v>5</v>
+      </c>
+      <c r="F92" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G92" s="19"/>
       <c r="H92" s="7">
         <v>1</v>
       </c>
@@ -6155,51 +6334,47 @@
       <c r="K92" s="2">
         <v>0</v>
       </c>
-      <c r="L92" s="7">
+      <c r="L92" s="2">
         <v>0</v>
       </c>
       <c r="M92" s="2">
         <v>0.3</v>
       </c>
       <c r="N92" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" s="1">
         <v>0</v>
       </c>
       <c r="P92" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="7"/>
-      <c r="S92" s="7"/>
-      <c r="T92" s="7"/>
-      <c r="U92" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V92" s="2">
-        <v>0</v>
-      </c>
-      <c r="W92" s="7"/>
-    </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A93" s="7"/>
-      <c r="B93" s="7">
-        <v>7005</v>
+        <v>1</v>
+      </c>
+      <c r="X92" s="2"/>
+      <c r="Y92" s="2"/>
+      <c r="Z92" s="2"/>
+      <c r="AA92" s="2"/>
+      <c r="AB92" s="2"/>
+    </row>
+    <row r="93" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B93" s="21">
+        <v>5029</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E93" s="7">
-        <v>7</v>
-      </c>
-      <c r="F93" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="G93" s="22" t="s">
-        <v>291</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="E93" s="2">
+        <v>5</v>
+      </c>
+      <c r="F93" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G93" s="19"/>
       <c r="H93" s="7">
         <v>1</v>
       </c>
@@ -6210,14 +6385,14 @@
       <c r="K93" s="2">
         <v>0</v>
       </c>
-      <c r="L93" s="7">
+      <c r="L93" s="2">
         <v>0</v>
       </c>
       <c r="M93" s="2">
         <v>0.3</v>
       </c>
       <c r="N93" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" s="1">
         <v>0</v>
@@ -6225,32 +6400,32 @@
       <c r="P93" s="2">
         <v>1</v>
       </c>
-      <c r="Q93" s="7"/>
-      <c r="R93" s="7"/>
-      <c r="S93" s="7"/>
-      <c r="T93" s="7"/>
-      <c r="U93" s="7"/>
+      <c r="S93" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V93" s="2">
-        <v>0</v>
-      </c>
-      <c r="W93" s="7"/>
-    </row>
-    <row r="94" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="13"/>
-      <c r="B94" s="13">
-        <v>8001</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13">
-        <v>8</v>
-      </c>
-      <c r="F94" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="G94" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="X93" s="2"/>
+      <c r="Y93" s="2"/>
+      <c r="Z93" s="2"/>
+      <c r="AA93" s="2"/>
+      <c r="AB93" s="2"/>
+    </row>
+    <row r="94" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B94" s="21">
+        <v>5030</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E94" s="2">
+        <v>5</v>
+      </c>
+      <c r="F94" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G94" s="19"/>
       <c r="H94" s="7">
         <v>1</v>
       </c>
@@ -6259,54 +6434,49 @@
         <v>0</v>
       </c>
       <c r="K94" s="2">
-        <v>1</v>
-      </c>
-      <c r="L94" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L94" s="2">
+        <v>0</v>
       </c>
       <c r="M94" s="2">
         <v>0.3</v>
       </c>
-      <c r="N94" s="2">
-        <v>1</v>
-      </c>
-      <c r="O94" s="2">
-        <v>1</v>
+      <c r="N94" s="1">
+        <v>0</v>
+      </c>
+      <c r="O94" s="1">
+        <v>0</v>
       </c>
       <c r="P94" s="2">
         <v>1</v>
       </c>
-      <c r="Q94" s="13"/>
-      <c r="R94" s="13"/>
-      <c r="S94" s="13"/>
-      <c r="T94" s="13"/>
-      <c r="U94" s="13"/>
+      <c r="S94" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V94" s="2">
-        <v>0</v>
-      </c>
-      <c r="W94" s="13"/>
-      <c r="X94" s="18"/>
-      <c r="Y94" s="18"/>
-      <c r="Z94" s="18"/>
-      <c r="AA94" s="18"/>
-      <c r="AB94" s="18"/>
-    </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A95" s="7"/>
-      <c r="B95" s="7">
-        <v>8002</v>
+        <v>1</v>
+      </c>
+      <c r="X94" s="2"/>
+      <c r="Y94" s="2"/>
+      <c r="Z94" s="2"/>
+      <c r="AA94" s="2"/>
+      <c r="AB94" s="2"/>
+    </row>
+    <row r="95" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B95" s="21">
+        <v>5031</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7">
-        <v>8</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G95" s="7"/>
+        <v>320</v>
+      </c>
+      <c r="E95" s="2">
+        <v>5</v>
+      </c>
+      <c r="F95" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G95" s="19"/>
       <c r="H95" s="7">
         <v>1</v>
       </c>
@@ -6315,49 +6485,49 @@
         <v>0</v>
       </c>
       <c r="K95" s="2">
-        <v>1</v>
-      </c>
-      <c r="L95" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L95" s="2">
+        <v>0</v>
       </c>
       <c r="M95" s="2">
         <v>0.3</v>
       </c>
-      <c r="N95" s="2">
-        <v>1</v>
-      </c>
-      <c r="O95" s="2">
-        <v>1</v>
+      <c r="N95" s="1">
+        <v>0</v>
+      </c>
+      <c r="O95" s="1">
+        <v>0</v>
       </c>
       <c r="P95" s="2">
         <v>1</v>
       </c>
-      <c r="Q95" s="7"/>
-      <c r="R95" s="7"/>
-      <c r="S95" s="7"/>
-      <c r="T95" s="7"/>
-      <c r="U95" s="7"/>
+      <c r="S95" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V95" s="2">
-        <v>0</v>
-      </c>
-      <c r="W95" s="7"/>
-    </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A96" s="7"/>
-      <c r="B96" s="7">
-        <v>8003</v>
+        <v>1</v>
+      </c>
+      <c r="X95" s="2"/>
+      <c r="Y95" s="2"/>
+      <c r="Z95" s="2"/>
+      <c r="AA95" s="2"/>
+      <c r="AB95" s="2"/>
+    </row>
+    <row r="96" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B96" s="21">
+        <v>5032</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7">
-        <v>8</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G96" s="7"/>
+        <v>321</v>
+      </c>
+      <c r="E96" s="2">
+        <v>5</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G96" s="19"/>
       <c r="H96" s="7">
         <v>1</v>
       </c>
@@ -6366,49 +6536,49 @@
         <v>0</v>
       </c>
       <c r="K96" s="2">
-        <v>1</v>
-      </c>
-      <c r="L96" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L96" s="2">
+        <v>0</v>
       </c>
       <c r="M96" s="2">
         <v>0.3</v>
       </c>
-      <c r="N96" s="2">
-        <v>1</v>
-      </c>
-      <c r="O96" s="2">
-        <v>1</v>
+      <c r="N96" s="1">
+        <v>0</v>
+      </c>
+      <c r="O96" s="1">
+        <v>0</v>
       </c>
       <c r="P96" s="2">
         <v>1</v>
       </c>
-      <c r="Q96" s="7"/>
-      <c r="R96" s="7"/>
-      <c r="S96" s="7"/>
-      <c r="T96" s="7"/>
-      <c r="U96" s="7"/>
+      <c r="S96" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V96" s="2">
-        <v>0</v>
-      </c>
-      <c r="W96" s="7"/>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A97" s="7"/>
-      <c r="B97" s="7">
-        <v>8004</v>
+        <v>1</v>
+      </c>
+      <c r="X96" s="2"/>
+      <c r="Y96" s="2"/>
+      <c r="Z96" s="2"/>
+      <c r="AA96" s="2"/>
+      <c r="AB96" s="2"/>
+    </row>
+    <row r="97" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B97" s="21">
+        <v>5033</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7">
-        <v>8</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G97" s="7"/>
+        <v>322</v>
+      </c>
+      <c r="E97" s="2">
+        <v>5</v>
+      </c>
+      <c r="F97" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G97" s="19"/>
       <c r="H97" s="7">
         <v>1</v>
       </c>
@@ -6417,49 +6587,49 @@
         <v>0</v>
       </c>
       <c r="K97" s="2">
-        <v>1</v>
-      </c>
-      <c r="L97" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L97" s="2">
+        <v>0</v>
       </c>
       <c r="M97" s="2">
         <v>0.3</v>
       </c>
-      <c r="N97" s="2">
-        <v>1</v>
-      </c>
-      <c r="O97" s="2">
-        <v>1</v>
+      <c r="N97" s="1">
+        <v>0</v>
+      </c>
+      <c r="O97" s="1">
+        <v>0</v>
       </c>
       <c r="P97" s="2">
         <v>1</v>
       </c>
-      <c r="Q97" s="7"/>
-      <c r="R97" s="7"/>
-      <c r="S97" s="7"/>
-      <c r="T97" s="7"/>
-      <c r="U97" s="7"/>
+      <c r="S97" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V97" s="2">
-        <v>0</v>
-      </c>
-      <c r="W97" s="7"/>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A98" s="7"/>
-      <c r="B98" s="7">
-        <v>8005</v>
+        <v>1</v>
+      </c>
+      <c r="X97" s="2"/>
+      <c r="Y97" s="2"/>
+      <c r="Z97" s="2"/>
+      <c r="AA97" s="2"/>
+      <c r="AB97" s="2"/>
+    </row>
+    <row r="98" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B98" s="21">
+        <v>5034</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7">
-        <v>8</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G98" s="7"/>
+        <v>323</v>
+      </c>
+      <c r="E98" s="2">
+        <v>5</v>
+      </c>
+      <c r="F98" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G98" s="19"/>
       <c r="H98" s="7">
         <v>1</v>
       </c>
@@ -6468,49 +6638,49 @@
         <v>0</v>
       </c>
       <c r="K98" s="2">
-        <v>1</v>
-      </c>
-      <c r="L98" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L98" s="2">
+        <v>0</v>
       </c>
       <c r="M98" s="2">
         <v>0.3</v>
       </c>
-      <c r="N98" s="2">
-        <v>1</v>
-      </c>
-      <c r="O98" s="2">
-        <v>1</v>
+      <c r="N98" s="1">
+        <v>0</v>
+      </c>
+      <c r="O98" s="1">
+        <v>0</v>
       </c>
       <c r="P98" s="2">
         <v>1</v>
       </c>
-      <c r="Q98" s="7"/>
-      <c r="R98" s="7"/>
-      <c r="S98" s="7"/>
-      <c r="T98" s="7"/>
-      <c r="U98" s="7"/>
+      <c r="S98" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V98" s="2">
-        <v>0</v>
-      </c>
-      <c r="W98" s="7"/>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A99" s="7"/>
-      <c r="B99" s="7">
-        <v>8006</v>
+        <v>1</v>
+      </c>
+      <c r="X98" s="2"/>
+      <c r="Y98" s="2"/>
+      <c r="Z98" s="2"/>
+      <c r="AA98" s="2"/>
+      <c r="AB98" s="2"/>
+    </row>
+    <row r="99" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B99" s="21">
+        <v>5035</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7">
-        <v>8</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G99" s="7"/>
+        <v>324</v>
+      </c>
+      <c r="E99" s="2">
+        <v>5</v>
+      </c>
+      <c r="F99" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G99" s="19"/>
       <c r="H99" s="7">
         <v>1</v>
       </c>
@@ -6519,49 +6689,49 @@
         <v>0</v>
       </c>
       <c r="K99" s="2">
-        <v>1</v>
-      </c>
-      <c r="L99" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L99" s="2">
+        <v>0</v>
       </c>
       <c r="M99" s="2">
         <v>0.3</v>
       </c>
-      <c r="N99" s="2">
-        <v>1</v>
-      </c>
-      <c r="O99" s="2">
-        <v>1</v>
+      <c r="N99" s="1">
+        <v>0</v>
+      </c>
+      <c r="O99" s="1">
+        <v>0</v>
       </c>
       <c r="P99" s="2">
         <v>1</v>
       </c>
-      <c r="Q99" s="7"/>
-      <c r="R99" s="7"/>
-      <c r="S99" s="7"/>
-      <c r="T99" s="7"/>
-      <c r="U99" s="7"/>
+      <c r="S99" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V99" s="2">
-        <v>0</v>
-      </c>
-      <c r="W99" s="7"/>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A100" s="7"/>
-      <c r="B100" s="7">
-        <v>8007</v>
+        <v>1</v>
+      </c>
+      <c r="X99" s="2"/>
+      <c r="Y99" s="2"/>
+      <c r="Z99" s="2"/>
+      <c r="AA99" s="2"/>
+      <c r="AB99" s="2"/>
+    </row>
+    <row r="100" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B100" s="21">
+        <v>5036</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7">
-        <v>8</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G100" s="7"/>
+        <v>325</v>
+      </c>
+      <c r="E100" s="2">
+        <v>5</v>
+      </c>
+      <c r="F100" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G100" s="19"/>
       <c r="H100" s="7">
         <v>1</v>
       </c>
@@ -6570,49 +6740,49 @@
         <v>0</v>
       </c>
       <c r="K100" s="2">
-        <v>1</v>
-      </c>
-      <c r="L100" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L100" s="2">
+        <v>0</v>
       </c>
       <c r="M100" s="2">
         <v>0.3</v>
       </c>
-      <c r="N100" s="2">
-        <v>1</v>
-      </c>
-      <c r="O100" s="2">
-        <v>1</v>
+      <c r="N100" s="1">
+        <v>0</v>
+      </c>
+      <c r="O100" s="1">
+        <v>0</v>
       </c>
       <c r="P100" s="2">
         <v>1</v>
       </c>
-      <c r="Q100" s="7"/>
-      <c r="R100" s="7"/>
-      <c r="S100" s="7"/>
-      <c r="T100" s="7"/>
-      <c r="U100" s="7"/>
+      <c r="S100" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V100" s="2">
-        <v>0</v>
-      </c>
-      <c r="W100" s="7"/>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A101" s="7"/>
-      <c r="B101" s="7">
-        <v>8008</v>
+        <v>1</v>
+      </c>
+      <c r="X100" s="2"/>
+      <c r="Y100" s="2"/>
+      <c r="Z100" s="2"/>
+      <c r="AA100" s="2"/>
+      <c r="AB100" s="2"/>
+    </row>
+    <row r="101" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B101" s="21">
+        <v>5037</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7">
-        <v>8</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G101" s="7"/>
+        <v>326</v>
+      </c>
+      <c r="E101" s="2">
+        <v>5</v>
+      </c>
+      <c r="F101" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G101" s="19"/>
       <c r="H101" s="7">
         <v>1</v>
       </c>
@@ -6621,49 +6791,49 @@
         <v>0</v>
       </c>
       <c r="K101" s="2">
-        <v>1</v>
-      </c>
-      <c r="L101" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L101" s="2">
+        <v>0</v>
       </c>
       <c r="M101" s="2">
         <v>0.3</v>
       </c>
-      <c r="N101" s="2">
-        <v>1</v>
-      </c>
-      <c r="O101" s="2">
-        <v>1</v>
+      <c r="N101" s="1">
+        <v>0</v>
+      </c>
+      <c r="O101" s="1">
+        <v>0</v>
       </c>
       <c r="P101" s="2">
         <v>1</v>
       </c>
-      <c r="Q101" s="7"/>
-      <c r="R101" s="7"/>
-      <c r="S101" s="7"/>
-      <c r="T101" s="7"/>
-      <c r="U101" s="7"/>
+      <c r="S101" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V101" s="2">
-        <v>0</v>
-      </c>
-      <c r="W101" s="7"/>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A102" s="7"/>
-      <c r="B102" s="7">
-        <v>8009</v>
+        <v>1</v>
+      </c>
+      <c r="X101" s="2"/>
+      <c r="Y101" s="2"/>
+      <c r="Z101" s="2"/>
+      <c r="AA101" s="2"/>
+      <c r="AB101" s="2"/>
+    </row>
+    <row r="102" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B102" s="21">
+        <v>5038</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7">
-        <v>8</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G102" s="7"/>
+        <v>327</v>
+      </c>
+      <c r="E102" s="2">
+        <v>5</v>
+      </c>
+      <c r="F102" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G102" s="19"/>
       <c r="H102" s="7">
         <v>1</v>
       </c>
@@ -6672,49 +6842,49 @@
         <v>0</v>
       </c>
       <c r="K102" s="2">
-        <v>1</v>
-      </c>
-      <c r="L102" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L102" s="2">
+        <v>0</v>
       </c>
       <c r="M102" s="2">
         <v>0.3</v>
       </c>
-      <c r="N102" s="2">
-        <v>1</v>
-      </c>
-      <c r="O102" s="2">
-        <v>1</v>
+      <c r="N102" s="1">
+        <v>0</v>
+      </c>
+      <c r="O102" s="1">
+        <v>0</v>
       </c>
       <c r="P102" s="2">
         <v>1</v>
       </c>
-      <c r="Q102" s="7"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="7"/>
-      <c r="T102" s="7"/>
-      <c r="U102" s="7"/>
+      <c r="S102" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V102" s="2">
-        <v>0</v>
-      </c>
-      <c r="W102" s="7"/>
-    </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A103" s="7"/>
-      <c r="B103" s="7">
-        <v>8010</v>
+        <v>1</v>
+      </c>
+      <c r="X102" s="2"/>
+      <c r="Y102" s="2"/>
+      <c r="Z102" s="2"/>
+      <c r="AA102" s="2"/>
+      <c r="AB102" s="2"/>
+    </row>
+    <row r="103" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B103" s="21">
+        <v>5039</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7">
-        <v>8</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G103" s="7"/>
+        <v>328</v>
+      </c>
+      <c r="E103" s="2">
+        <v>5</v>
+      </c>
+      <c r="F103" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G103" s="19"/>
       <c r="H103" s="7">
         <v>1</v>
       </c>
@@ -6723,49 +6893,49 @@
         <v>0</v>
       </c>
       <c r="K103" s="2">
-        <v>1</v>
-      </c>
-      <c r="L103" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L103" s="2">
+        <v>0</v>
       </c>
       <c r="M103" s="2">
         <v>0.3</v>
       </c>
-      <c r="N103" s="2">
-        <v>1</v>
-      </c>
-      <c r="O103" s="2">
-        <v>1</v>
+      <c r="N103" s="1">
+        <v>0</v>
+      </c>
+      <c r="O103" s="1">
+        <v>0</v>
       </c>
       <c r="P103" s="2">
         <v>1</v>
       </c>
-      <c r="Q103" s="7"/>
-      <c r="R103" s="7"/>
-      <c r="S103" s="7"/>
-      <c r="T103" s="7"/>
-      <c r="U103" s="7"/>
+      <c r="S103" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V103" s="2">
-        <v>0</v>
-      </c>
-      <c r="W103" s="7"/>
-    </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A104" s="7"/>
-      <c r="B104" s="7">
-        <v>8011</v>
+        <v>1</v>
+      </c>
+      <c r="X103" s="2"/>
+      <c r="Y103" s="2"/>
+      <c r="Z103" s="2"/>
+      <c r="AA103" s="2"/>
+      <c r="AB103" s="2"/>
+    </row>
+    <row r="104" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B104" s="21">
+        <v>5040</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7">
-        <v>8</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G104" s="7"/>
+        <v>329</v>
+      </c>
+      <c r="E104" s="2">
+        <v>5</v>
+      </c>
+      <c r="F104" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G104" s="19"/>
       <c r="H104" s="7">
         <v>1</v>
       </c>
@@ -6774,49 +6944,49 @@
         <v>0</v>
       </c>
       <c r="K104" s="2">
-        <v>1</v>
-      </c>
-      <c r="L104" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L104" s="2">
+        <v>0</v>
       </c>
       <c r="M104" s="2">
         <v>0.3</v>
       </c>
-      <c r="N104" s="2">
-        <v>1</v>
-      </c>
-      <c r="O104" s="2">
-        <v>1</v>
+      <c r="N104" s="1">
+        <v>0</v>
+      </c>
+      <c r="O104" s="1">
+        <v>0</v>
       </c>
       <c r="P104" s="2">
         <v>1</v>
       </c>
-      <c r="Q104" s="7"/>
-      <c r="R104" s="7"/>
-      <c r="S104" s="7"/>
-      <c r="T104" s="7"/>
-      <c r="U104" s="7"/>
+      <c r="S104" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V104" s="2">
-        <v>0</v>
-      </c>
-      <c r="W104" s="7"/>
-    </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A105" s="7"/>
-      <c r="B105" s="7">
-        <v>8012</v>
+        <v>1</v>
+      </c>
+      <c r="X104" s="2"/>
+      <c r="Y104" s="2"/>
+      <c r="Z104" s="2"/>
+      <c r="AA104" s="2"/>
+      <c r="AB104" s="2"/>
+    </row>
+    <row r="105" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B105" s="21">
+        <v>5041</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7">
-        <v>8</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G105" s="7"/>
+        <v>330</v>
+      </c>
+      <c r="E105" s="2">
+        <v>5</v>
+      </c>
+      <c r="F105" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G105" s="19"/>
       <c r="H105" s="7">
         <v>1</v>
       </c>
@@ -6825,49 +6995,49 @@
         <v>0</v>
       </c>
       <c r="K105" s="2">
-        <v>1</v>
-      </c>
-      <c r="L105" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L105" s="2">
+        <v>0</v>
       </c>
       <c r="M105" s="2">
         <v>0.3</v>
       </c>
-      <c r="N105" s="2">
-        <v>1</v>
-      </c>
-      <c r="O105" s="2">
-        <v>1</v>
+      <c r="N105" s="1">
+        <v>0</v>
+      </c>
+      <c r="O105" s="1">
+        <v>0</v>
       </c>
       <c r="P105" s="2">
         <v>1</v>
       </c>
-      <c r="Q105" s="7"/>
-      <c r="R105" s="7"/>
-      <c r="S105" s="7"/>
-      <c r="T105" s="7"/>
-      <c r="U105" s="7"/>
+      <c r="S105" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V105" s="2">
-        <v>0</v>
-      </c>
-      <c r="W105" s="7"/>
-    </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A106" s="7"/>
-      <c r="B106" s="7">
-        <v>8013</v>
+        <v>1</v>
+      </c>
+      <c r="X105" s="2"/>
+      <c r="Y105" s="2"/>
+      <c r="Z105" s="2"/>
+      <c r="AA105" s="2"/>
+      <c r="AB105" s="2"/>
+    </row>
+    <row r="106" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B106" s="21">
+        <v>5042</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7">
-        <v>8</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G106" s="7"/>
+        <v>331</v>
+      </c>
+      <c r="E106" s="2">
+        <v>5</v>
+      </c>
+      <c r="F106" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G106" s="19"/>
       <c r="H106" s="7">
         <v>1</v>
       </c>
@@ -6876,49 +7046,49 @@
         <v>0</v>
       </c>
       <c r="K106" s="2">
-        <v>1</v>
-      </c>
-      <c r="L106" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L106" s="2">
+        <v>0</v>
       </c>
       <c r="M106" s="2">
         <v>0.3</v>
       </c>
-      <c r="N106" s="2">
-        <v>1</v>
-      </c>
-      <c r="O106" s="2">
-        <v>1</v>
+      <c r="N106" s="1">
+        <v>0</v>
+      </c>
+      <c r="O106" s="1">
+        <v>0</v>
       </c>
       <c r="P106" s="2">
         <v>1</v>
       </c>
-      <c r="Q106" s="7"/>
-      <c r="R106" s="7"/>
-      <c r="S106" s="7"/>
-      <c r="T106" s="7"/>
-      <c r="U106" s="7"/>
+      <c r="S106" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V106" s="2">
-        <v>0</v>
-      </c>
-      <c r="W106" s="7"/>
-    </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A107" s="7"/>
-      <c r="B107" s="7">
-        <v>8014</v>
+        <v>1</v>
+      </c>
+      <c r="X106" s="2"/>
+      <c r="Y106" s="2"/>
+      <c r="Z106" s="2"/>
+      <c r="AA106" s="2"/>
+      <c r="AB106" s="2"/>
+    </row>
+    <row r="107" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B107" s="21">
+        <v>5043</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7">
-        <v>8</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G107" s="7"/>
+        <v>332</v>
+      </c>
+      <c r="E107" s="2">
+        <v>5</v>
+      </c>
+      <c r="F107" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G107" s="19"/>
       <c r="H107" s="7">
         <v>1</v>
       </c>
@@ -6927,520 +7097,1045 @@
         <v>0</v>
       </c>
       <c r="K107" s="2">
-        <v>1</v>
-      </c>
-      <c r="L107" s="7">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="L107" s="2">
+        <v>0</v>
       </c>
       <c r="M107" s="2">
         <v>0.3</v>
       </c>
-      <c r="N107" s="2">
-        <v>1</v>
-      </c>
-      <c r="O107" s="2">
-        <v>1</v>
+      <c r="N107" s="1">
+        <v>0</v>
+      </c>
+      <c r="O107" s="1">
+        <v>0</v>
       </c>
       <c r="P107" s="2">
         <v>1</v>
       </c>
-      <c r="Q107" s="7"/>
-      <c r="R107" s="7"/>
-      <c r="S107" s="7"/>
-      <c r="T107" s="7"/>
-      <c r="U107" s="7"/>
+      <c r="S107" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="V107" s="2">
-        <v>0</v>
-      </c>
-      <c r="W107" s="7"/>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A108" s="7"/>
-      <c r="B108" s="7"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="7"/>
-      <c r="G108" s="7"/>
-      <c r="H108" s="7"/>
-      <c r="I108" s="7"/>
-      <c r="J108" s="7"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
-      <c r="Q108" s="7"/>
-      <c r="R108" s="7"/>
-      <c r="S108" s="7"/>
-      <c r="T108" s="7"/>
-      <c r="U108" s="7"/>
-      <c r="V108" s="7"/>
-      <c r="W108" s="7"/>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A109" s="7"/>
-      <c r="B109" s="7"/>
-      <c r="C109" s="17"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="7"/>
-      <c r="G109" s="7"/>
-      <c r="H109" s="7"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="7"/>
-      <c r="K109" s="7"/>
-      <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
-      <c r="N109" s="7"/>
-      <c r="Q109" s="7"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="7"/>
-      <c r="T109" s="7"/>
-      <c r="U109" s="7"/>
-      <c r="V109" s="7"/>
-      <c r="W109" s="7"/>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A110" s="7"/>
-      <c r="B110" s="7"/>
-      <c r="C110" s="17"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
-      <c r="Q110" s="7"/>
-      <c r="R110" s="7"/>
-      <c r="S110" s="7"/>
-      <c r="T110" s="7"/>
-      <c r="U110" s="7"/>
-      <c r="V110" s="7"/>
-      <c r="W110" s="7"/>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A111" s="7"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="17"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="7"/>
-      <c r="G111" s="7"/>
-      <c r="H111" s="7"/>
-      <c r="I111" s="7"/>
-      <c r="J111" s="7"/>
-      <c r="K111" s="7"/>
-      <c r="L111" s="7"/>
-      <c r="M111" s="7"/>
-      <c r="N111" s="7"/>
-      <c r="Q111" s="7"/>
-      <c r="R111" s="7"/>
-      <c r="S111" s="7"/>
-      <c r="T111" s="7"/>
-      <c r="U111" s="7"/>
-      <c r="V111" s="7"/>
-      <c r="W111" s="7"/>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A112" s="7"/>
-      <c r="B112" s="7"/>
-      <c r="C112" s="17"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
-      <c r="H112" s="7"/>
-      <c r="I112" s="7"/>
-      <c r="J112" s="7"/>
-      <c r="K112" s="7"/>
-      <c r="L112" s="7"/>
-      <c r="M112" s="7"/>
-      <c r="N112" s="7"/>
-      <c r="Q112" s="7"/>
-      <c r="R112" s="7"/>
-      <c r="S112" s="7"/>
-      <c r="T112" s="7"/>
-      <c r="U112" s="7"/>
-      <c r="V112" s="7"/>
-      <c r="W112" s="7"/>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A113" s="7"/>
-      <c r="B113" s="7"/>
-      <c r="C113" s="17"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="7"/>
-      <c r="G113" s="7"/>
-      <c r="H113" s="7"/>
-      <c r="I113" s="7"/>
-      <c r="J113" s="7"/>
-      <c r="K113" s="7"/>
-      <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
-      <c r="N113" s="7"/>
-      <c r="Q113" s="7"/>
-      <c r="R113" s="7"/>
-      <c r="S113" s="7"/>
-      <c r="T113" s="7"/>
-      <c r="U113" s="7"/>
-      <c r="V113" s="7"/>
-      <c r="W113" s="7"/>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A114" s="7"/>
-      <c r="B114" s="7"/>
-      <c r="C114" s="17"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="7"/>
-      <c r="G114" s="7"/>
-      <c r="H114" s="7"/>
-      <c r="I114" s="7"/>
-      <c r="J114" s="7"/>
-      <c r="K114" s="7"/>
-      <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
-      <c r="N114" s="7"/>
-      <c r="Q114" s="7"/>
-      <c r="R114" s="7"/>
-      <c r="S114" s="7"/>
-      <c r="T114" s="7"/>
-      <c r="U114" s="7"/>
-      <c r="V114" s="7"/>
-      <c r="W114" s="7"/>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A115" s="7"/>
-      <c r="B115" s="7"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="7"/>
-      <c r="G115" s="7"/>
-      <c r="H115" s="7"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="7"/>
-      <c r="K115" s="7"/>
-      <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
-      <c r="N115" s="7"/>
-      <c r="Q115" s="7"/>
-      <c r="R115" s="7"/>
-      <c r="S115" s="7"/>
-      <c r="T115" s="7"/>
-      <c r="U115" s="7"/>
-      <c r="V115" s="7"/>
-      <c r="W115" s="7"/>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A116" s="7"/>
-      <c r="B116" s="7"/>
-      <c r="C116" s="17"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="7"/>
-      <c r="G116" s="7"/>
-      <c r="H116" s="7"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="7"/>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
-      <c r="N116" s="7"/>
-      <c r="Q116" s="7"/>
-      <c r="R116" s="7"/>
-      <c r="S116" s="7"/>
-      <c r="T116" s="7"/>
-      <c r="U116" s="7"/>
-      <c r="V116" s="7"/>
-      <c r="W116" s="7"/>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A117" s="7"/>
-      <c r="B117" s="7"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="7"/>
-      <c r="G117" s="7"/>
-      <c r="H117" s="7"/>
-      <c r="I117" s="7"/>
-      <c r="J117" s="7"/>
-      <c r="K117" s="7"/>
-      <c r="L117" s="7"/>
-      <c r="M117" s="7"/>
-      <c r="N117" s="7"/>
-      <c r="Q117" s="7"/>
-      <c r="R117" s="7"/>
-      <c r="S117" s="7"/>
-      <c r="T117" s="7"/>
-      <c r="U117" s="7"/>
-      <c r="V117" s="7"/>
-      <c r="W117" s="7"/>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A118" s="7"/>
-      <c r="B118" s="7"/>
-      <c r="C118" s="17"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7"/>
-      <c r="G118" s="7"/>
-      <c r="H118" s="7"/>
-      <c r="I118" s="7"/>
-      <c r="J118" s="7"/>
-      <c r="K118" s="7"/>
-      <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
-      <c r="N118" s="7"/>
-      <c r="Q118" s="7"/>
-      <c r="R118" s="7"/>
-      <c r="S118" s="7"/>
-      <c r="T118" s="7"/>
-      <c r="U118" s="7"/>
-      <c r="V118" s="7"/>
-      <c r="W118" s="7"/>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A119" s="7"/>
-      <c r="B119" s="7"/>
-      <c r="C119" s="17"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="7"/>
-      <c r="G119" s="7"/>
-      <c r="H119" s="7"/>
-      <c r="I119" s="7"/>
-      <c r="J119" s="7"/>
-      <c r="K119" s="7"/>
-      <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-      <c r="Q119" s="7"/>
-      <c r="R119" s="7"/>
-      <c r="S119" s="7"/>
-      <c r="T119" s="7"/>
-      <c r="U119" s="7"/>
-      <c r="V119" s="7"/>
-      <c r="W119" s="7"/>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A120" s="7"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="17"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="7"/>
-      <c r="H120" s="7"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="7"/>
-      <c r="S120" s="7"/>
-      <c r="T120" s="7"/>
-      <c r="U120" s="7"/>
-      <c r="V120" s="7"/>
-      <c r="W120" s="7"/>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A121" s="7"/>
-      <c r="B121" s="7"/>
-      <c r="C121" s="17"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="7"/>
-      <c r="G121" s="7"/>
-      <c r="H121" s="7"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="7"/>
-      <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
-      <c r="N121" s="7"/>
-      <c r="Q121" s="7"/>
-      <c r="R121" s="7"/>
-      <c r="S121" s="7"/>
-      <c r="T121" s="7"/>
-      <c r="U121" s="7"/>
-      <c r="V121" s="7"/>
-      <c r="W121" s="7"/>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A122" s="7"/>
-      <c r="B122" s="7"/>
-      <c r="C122" s="17"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7"/>
-      <c r="G122" s="7"/>
-      <c r="H122" s="7"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="7"/>
-      <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
-      <c r="N122" s="7"/>
-      <c r="Q122" s="7"/>
-      <c r="R122" s="7"/>
-      <c r="S122" s="7"/>
-      <c r="T122" s="7"/>
-      <c r="U122" s="7"/>
-      <c r="V122" s="7"/>
-      <c r="W122" s="7"/>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A123" s="7"/>
-      <c r="B123" s="7"/>
-      <c r="C123" s="17"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7"/>
-      <c r="G123" s="7"/>
-      <c r="H123" s="7"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="7"/>
-      <c r="K123" s="7"/>
-      <c r="L123" s="7"/>
-      <c r="M123" s="7"/>
-      <c r="N123" s="7"/>
-      <c r="Q123" s="7"/>
-      <c r="R123" s="7"/>
-      <c r="S123" s="7"/>
-      <c r="T123" s="7"/>
-      <c r="U123" s="7"/>
-      <c r="V123" s="7"/>
-      <c r="W123" s="7"/>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A124" s="7"/>
-      <c r="B124" s="7"/>
-      <c r="C124" s="17"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-      <c r="G124" s="7"/>
-      <c r="H124" s="7"/>
-      <c r="I124" s="7"/>
-      <c r="J124" s="7"/>
-      <c r="K124" s="7"/>
-      <c r="L124" s="7"/>
-      <c r="M124" s="7"/>
-      <c r="N124" s="7"/>
-      <c r="Q124" s="7"/>
-      <c r="R124" s="7"/>
-      <c r="S124" s="7"/>
-      <c r="T124" s="7"/>
-      <c r="U124" s="7"/>
-      <c r="V124" s="7"/>
-      <c r="W124" s="7"/>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="X107" s="2"/>
+      <c r="Y107" s="2"/>
+      <c r="Z107" s="2"/>
+      <c r="AA107" s="2"/>
+      <c r="AB107" s="2"/>
+    </row>
+    <row r="108" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B108" s="21">
+        <v>5044</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E108" s="2">
+        <v>5</v>
+      </c>
+      <c r="F108" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G108" s="19"/>
+      <c r="H108" s="7">
+        <v>1</v>
+      </c>
+      <c r="I108" s="12"/>
+      <c r="J108" s="2">
+        <v>0</v>
+      </c>
+      <c r="K108" s="2">
+        <v>0</v>
+      </c>
+      <c r="L108" s="2">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N108" s="1">
+        <v>0</v>
+      </c>
+      <c r="O108" s="1">
+        <v>0</v>
+      </c>
+      <c r="P108" s="2">
+        <v>1</v>
+      </c>
+      <c r="S108" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="V108" s="2">
+        <v>1</v>
+      </c>
+      <c r="X108" s="2"/>
+      <c r="Y108" s="2"/>
+      <c r="Z108" s="2"/>
+      <c r="AA108" s="2"/>
+      <c r="AB108" s="2"/>
+    </row>
+    <row r="109" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B109" s="1">
+        <v>6001</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E109" s="1">
+        <v>6</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H109" s="13">
+        <v>1</v>
+      </c>
+      <c r="I109" s="14"/>
+      <c r="J109" s="1">
+        <v>0</v>
+      </c>
+      <c r="K109" s="1">
+        <v>0</v>
+      </c>
+      <c r="L109" s="1">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N109" s="1">
+        <v>0</v>
+      </c>
+      <c r="O109" s="1">
+        <v>0</v>
+      </c>
+      <c r="P109" s="1">
+        <v>1</v>
+      </c>
+      <c r="S109" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="V109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B110" s="2">
+        <v>6002</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E110" s="2">
+        <v>6</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H110" s="7">
+        <v>1</v>
+      </c>
+      <c r="I110" s="12"/>
+      <c r="J110" s="2">
+        <v>0</v>
+      </c>
+      <c r="K110" s="2">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N110" s="1">
+        <v>0</v>
+      </c>
+      <c r="O110" s="1">
+        <v>0</v>
+      </c>
+      <c r="P110" s="2">
+        <v>1</v>
+      </c>
+      <c r="S110" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="V110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B111" s="2">
+        <v>6003</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E111" s="2">
+        <v>6</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H111" s="7">
+        <v>1</v>
+      </c>
+      <c r="I111" s="12"/>
+      <c r="J111" s="2">
+        <v>0</v>
+      </c>
+      <c r="K111" s="2">
+        <v>0</v>
+      </c>
+      <c r="L111" s="2">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N111" s="1">
+        <v>0</v>
+      </c>
+      <c r="O111" s="1">
+        <v>0</v>
+      </c>
+      <c r="P111" s="2">
+        <v>1</v>
+      </c>
+      <c r="S111" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="V111" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:28" x14ac:dyDescent="0.3">
+      <c r="B112" s="2">
+        <v>6004</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E112" s="2">
+        <v>6</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H112" s="7">
+        <v>1</v>
+      </c>
+      <c r="I112" s="12"/>
+      <c r="J112" s="2">
+        <v>0</v>
+      </c>
+      <c r="K112" s="2">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N112" s="1">
+        <v>0</v>
+      </c>
+      <c r="O112" s="1">
+        <v>0</v>
+      </c>
+      <c r="P112" s="2">
+        <v>1</v>
+      </c>
+      <c r="S112" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="V112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B113" s="2">
+        <v>6005</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E113" s="2">
+        <v>6</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H113" s="7">
+        <v>1</v>
+      </c>
+      <c r="I113" s="12"/>
+      <c r="J113" s="2">
+        <v>0</v>
+      </c>
+      <c r="K113" s="2">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N113" s="1">
+        <v>0</v>
+      </c>
+      <c r="O113" s="1">
+        <v>0</v>
+      </c>
+      <c r="P113" s="2">
+        <v>1</v>
+      </c>
+      <c r="S113" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="V113" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B114" s="2">
+        <v>6006</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E114" s="2">
+        <v>6</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H114" s="7">
+        <v>1</v>
+      </c>
+      <c r="I114" s="12"/>
+      <c r="J114" s="2">
+        <v>0</v>
+      </c>
+      <c r="K114" s="2">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N114" s="1">
+        <v>0</v>
+      </c>
+      <c r="O114" s="1">
+        <v>0</v>
+      </c>
+      <c r="P114" s="2">
+        <v>1</v>
+      </c>
+      <c r="S114" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="V114" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B115" s="2">
+        <v>6007</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E115" s="2">
+        <v>6</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H115" s="7">
+        <v>1</v>
+      </c>
+      <c r="I115" s="12"/>
+      <c r="J115" s="2">
+        <v>0</v>
+      </c>
+      <c r="K115" s="2">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N115" s="1">
+        <v>0</v>
+      </c>
+      <c r="O115" s="1">
+        <v>0</v>
+      </c>
+      <c r="P115" s="2">
+        <v>1</v>
+      </c>
+      <c r="S115" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="V115" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B116" s="2">
+        <v>6008</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E116" s="2">
+        <v>6</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H116" s="7">
+        <v>1</v>
+      </c>
+      <c r="I116" s="12"/>
+      <c r="J116" s="2">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N116" s="1">
+        <v>0</v>
+      </c>
+      <c r="O116" s="1">
+        <v>0</v>
+      </c>
+      <c r="P116" s="2">
+        <v>1</v>
+      </c>
+      <c r="S116" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="V116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B117" s="2">
+        <v>6009</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E117" s="2">
+        <v>6</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H117" s="7">
+        <v>1</v>
+      </c>
+      <c r="I117" s="12"/>
+      <c r="J117" s="2">
+        <v>0</v>
+      </c>
+      <c r="K117" s="2">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N117" s="1">
+        <v>0</v>
+      </c>
+      <c r="O117" s="1">
+        <v>0</v>
+      </c>
+      <c r="P117" s="2">
+        <v>1</v>
+      </c>
+      <c r="S117" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="V117" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B118" s="2">
+        <v>6010</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E118" s="2">
+        <v>6</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H118" s="7">
+        <v>1</v>
+      </c>
+      <c r="I118" s="12"/>
+      <c r="J118" s="2">
+        <v>0</v>
+      </c>
+      <c r="K118" s="2">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N118" s="1">
+        <v>0</v>
+      </c>
+      <c r="O118" s="1">
+        <v>0</v>
+      </c>
+      <c r="P118" s="2">
+        <v>1</v>
+      </c>
+      <c r="S118" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="V118" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B119" s="2">
+        <v>6011</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E119" s="2">
+        <v>6</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H119" s="7">
+        <v>1</v>
+      </c>
+      <c r="I119" s="12"/>
+      <c r="J119" s="2">
+        <v>0</v>
+      </c>
+      <c r="K119" s="2">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N119" s="1">
+        <v>0</v>
+      </c>
+      <c r="O119" s="1">
+        <v>0</v>
+      </c>
+      <c r="P119" s="2">
+        <v>1</v>
+      </c>
+      <c r="S119" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="V119" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B120" s="2">
+        <v>6012</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E120" s="2">
+        <v>6</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H120" s="7">
+        <v>1</v>
+      </c>
+      <c r="I120" s="12"/>
+      <c r="J120" s="2">
+        <v>0</v>
+      </c>
+      <c r="K120" s="2">
+        <v>0</v>
+      </c>
+      <c r="L120" s="2">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N120" s="1">
+        <v>0</v>
+      </c>
+      <c r="O120" s="1">
+        <v>0</v>
+      </c>
+      <c r="P120" s="2">
+        <v>1</v>
+      </c>
+      <c r="S120" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="V120" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B121" s="2">
+        <v>6013</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E121" s="2">
+        <v>6</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H121" s="7">
+        <v>1</v>
+      </c>
+      <c r="I121" s="12"/>
+      <c r="J121" s="2">
+        <v>0</v>
+      </c>
+      <c r="K121" s="2">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N121" s="1">
+        <v>0</v>
+      </c>
+      <c r="O121" s="1">
+        <v>0</v>
+      </c>
+      <c r="P121" s="2">
+        <v>1</v>
+      </c>
+      <c r="S121" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="V121" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B122" s="2">
+        <v>6014</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E122" s="2">
+        <v>6</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H122" s="7">
+        <v>1</v>
+      </c>
+      <c r="I122" s="12"/>
+      <c r="J122" s="2">
+        <v>0</v>
+      </c>
+      <c r="K122" s="2">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N122" s="1">
+        <v>0</v>
+      </c>
+      <c r="O122" s="1">
+        <v>0</v>
+      </c>
+      <c r="P122" s="2">
+        <v>1</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="V122" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="B123" s="2">
+        <v>6015</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E123" s="2">
+        <v>6</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H123" s="7">
+        <v>1</v>
+      </c>
+      <c r="I123" s="12"/>
+      <c r="J123" s="2">
+        <v>0</v>
+      </c>
+      <c r="K123" s="2">
+        <v>1</v>
+      </c>
+      <c r="L123" s="2">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N123" s="1">
+        <v>0</v>
+      </c>
+      <c r="O123" s="1">
+        <v>0</v>
+      </c>
+      <c r="P123" s="2">
+        <v>1</v>
+      </c>
+      <c r="S123" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="V123" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="13"/>
+      <c r="B124" s="13">
+        <v>7001</v>
+      </c>
+      <c r="C124" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E124" s="13">
+        <v>7</v>
+      </c>
+      <c r="F124" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="G124" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="H124" s="13">
+        <v>1</v>
+      </c>
+      <c r="I124" s="14"/>
+      <c r="J124" s="2">
+        <v>0</v>
+      </c>
+      <c r="K124" s="2">
+        <v>0</v>
+      </c>
+      <c r="L124" s="7">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N124" s="1">
+        <v>1</v>
+      </c>
+      <c r="O124" s="1">
+        <v>0</v>
+      </c>
+      <c r="P124" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q124" s="13"/>
+      <c r="R124" s="13"/>
+      <c r="S124" s="13"/>
+      <c r="T124" s="13"/>
+      <c r="U124" s="13"/>
+      <c r="V124" s="2">
+        <v>0</v>
+      </c>
+      <c r="W124" s="13"/>
+      <c r="X124" s="17"/>
+      <c r="Y124" s="17"/>
+      <c r="Z124" s="17"/>
+      <c r="AA124" s="17"/>
+      <c r="AB124" s="17"/>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A125" s="7"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="17"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="7"/>
-      <c r="H125" s="7"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
-      <c r="K125" s="7"/>
-      <c r="L125" s="7"/>
-      <c r="M125" s="7"/>
-      <c r="N125" s="7"/>
+      <c r="B125" s="7">
+        <v>7002</v>
+      </c>
+      <c r="C125" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E125" s="7">
+        <v>7</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G125" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="H125" s="7">
+        <v>1</v>
+      </c>
+      <c r="I125" s="12"/>
+      <c r="J125" s="2">
+        <v>0</v>
+      </c>
+      <c r="K125" s="2">
+        <v>0</v>
+      </c>
+      <c r="L125" s="7">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N125" s="1">
+        <v>1</v>
+      </c>
+      <c r="O125" s="1">
+        <v>0</v>
+      </c>
+      <c r="P125" s="2">
+        <v>1</v>
+      </c>
       <c r="Q125" s="7"/>
       <c r="R125" s="7"/>
       <c r="S125" s="7"/>
       <c r="T125" s="7"/>
       <c r="U125" s="7"/>
-      <c r="V125" s="7"/>
+      <c r="V125" s="2">
+        <v>0</v>
+      </c>
       <c r="W125" s="7"/>
     </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A126" s="7"/>
-      <c r="B126" s="7"/>
-      <c r="C126" s="17"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="7"/>
-      <c r="G126" s="7"/>
-      <c r="H126" s="7"/>
-      <c r="I126" s="7"/>
-      <c r="J126" s="7"/>
-      <c r="K126" s="7"/>
-      <c r="L126" s="7"/>
-      <c r="M126" s="7"/>
-      <c r="N126" s="7"/>
+      <c r="B126" s="7">
+        <v>7003</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E126" s="7">
+        <v>7</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G126" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="H126" s="7">
+        <v>1</v>
+      </c>
+      <c r="I126" s="12"/>
+      <c r="J126" s="2">
+        <v>0</v>
+      </c>
+      <c r="K126" s="2">
+        <v>0</v>
+      </c>
+      <c r="L126" s="7">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N126" s="1">
+        <v>1</v>
+      </c>
+      <c r="O126" s="1">
+        <v>0</v>
+      </c>
+      <c r="P126" s="2">
+        <v>1</v>
+      </c>
       <c r="Q126" s="7"/>
       <c r="R126" s="7"/>
       <c r="S126" s="7"/>
       <c r="T126" s="7"/>
       <c r="U126" s="7"/>
-      <c r="V126" s="7"/>
+      <c r="V126" s="2">
+        <v>0</v>
+      </c>
       <c r="W126" s="7"/>
     </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A127" s="7"/>
-      <c r="B127" s="7"/>
-      <c r="C127" s="17"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-      <c r="G127" s="7"/>
-      <c r="H127" s="7"/>
-      <c r="I127" s="7"/>
-      <c r="J127" s="7"/>
-      <c r="K127" s="7"/>
-      <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
-      <c r="N127" s="7"/>
+      <c r="B127" s="7">
+        <v>7004</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E127" s="7">
+        <v>7</v>
+      </c>
+      <c r="F127" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="G127" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="H127" s="7">
+        <v>1</v>
+      </c>
+      <c r="I127" s="12"/>
+      <c r="J127" s="2">
+        <v>0</v>
+      </c>
+      <c r="K127" s="2">
+        <v>0</v>
+      </c>
+      <c r="L127" s="7">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N127" s="1">
+        <v>1</v>
+      </c>
+      <c r="O127" s="1">
+        <v>0</v>
+      </c>
+      <c r="P127" s="2">
+        <v>0</v>
+      </c>
       <c r="Q127" s="7"/>
       <c r="R127" s="7"/>
       <c r="S127" s="7"/>
       <c r="T127" s="7"/>
       <c r="U127" s="7"/>
-      <c r="V127" s="7"/>
+      <c r="V127" s="2">
+        <v>0</v>
+      </c>
       <c r="W127" s="7"/>
     </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A128" s="7"/>
-      <c r="B128" s="7"/>
-      <c r="C128" s="17"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="7"/>
-      <c r="G128" s="7"/>
-      <c r="H128" s="7"/>
-      <c r="I128" s="7"/>
-      <c r="J128" s="7"/>
-      <c r="K128" s="7"/>
-      <c r="L128" s="7"/>
-      <c r="M128" s="7"/>
-      <c r="N128" s="7"/>
+      <c r="B128" s="7">
+        <v>7005</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E128" s="7">
+        <v>7</v>
+      </c>
+      <c r="F128" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="G128" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="H128" s="7">
+        <v>1</v>
+      </c>
+      <c r="I128" s="12"/>
+      <c r="J128" s="2">
+        <v>0</v>
+      </c>
+      <c r="K128" s="2">
+        <v>0</v>
+      </c>
+      <c r="L128" s="7">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N128" s="1">
+        <v>1</v>
+      </c>
+      <c r="O128" s="1">
+        <v>0</v>
+      </c>
+      <c r="P128" s="2">
+        <v>1</v>
+      </c>
       <c r="Q128" s="7"/>
       <c r="R128" s="7"/>
       <c r="S128" s="7"/>
       <c r="T128" s="7"/>
       <c r="U128" s="7"/>
-      <c r="V128" s="7"/>
+      <c r="V128" s="2">
+        <v>0</v>
+      </c>
       <c r="W128" s="7"/>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
-      <c r="C129" s="17"/>
+      <c r="C129" s="16"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7"/>
@@ -7460,10 +8155,10 @@
       <c r="V129" s="7"/>
       <c r="W129" s="7"/>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
-      <c r="C130" s="17"/>
+      <c r="C130" s="16"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
@@ -7483,10 +8178,10 @@
       <c r="V130" s="7"/>
       <c r="W130" s="7"/>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
-      <c r="C131" s="17"/>
+      <c r="C131" s="16"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7"/>
@@ -7506,10 +8201,10 @@
       <c r="V131" s="7"/>
       <c r="W131" s="7"/>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
-      <c r="C132" s="17"/>
+      <c r="C132" s="16"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
@@ -7529,10 +8224,10 @@
       <c r="V132" s="7"/>
       <c r="W132" s="7"/>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
-      <c r="C133" s="17"/>
+      <c r="C133" s="16"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
@@ -7552,10 +8247,10 @@
       <c r="V133" s="7"/>
       <c r="W133" s="7"/>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
-      <c r="C134" s="17"/>
+      <c r="C134" s="16"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
@@ -7575,10 +8270,10 @@
       <c r="V134" s="7"/>
       <c r="W134" s="7"/>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
-      <c r="C135" s="17"/>
+      <c r="C135" s="16"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
@@ -7598,10 +8293,10 @@
       <c r="V135" s="7"/>
       <c r="W135" s="7"/>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
-      <c r="C136" s="17"/>
+      <c r="C136" s="16"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
@@ -7621,10 +8316,10 @@
       <c r="V136" s="7"/>
       <c r="W136" s="7"/>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
-      <c r="C137" s="17"/>
+      <c r="C137" s="16"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
       <c r="F137" s="7"/>
@@ -7644,10 +8339,10 @@
       <c r="V137" s="7"/>
       <c r="W137" s="7"/>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
-      <c r="C138" s="17"/>
+      <c r="C138" s="16"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
@@ -7667,10 +8362,10 @@
       <c r="V138" s="7"/>
       <c r="W138" s="7"/>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
-      <c r="C139" s="17"/>
+      <c r="C139" s="16"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
       <c r="F139" s="7"/>
@@ -7690,10 +8385,10 @@
       <c r="V139" s="7"/>
       <c r="W139" s="7"/>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="17"/>
+      <c r="C140" s="16"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
@@ -7713,10 +8408,10 @@
       <c r="V140" s="7"/>
       <c r="W140" s="7"/>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
-      <c r="C141" s="17"/>
+      <c r="C141" s="16"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7"/>
@@ -7736,10 +8431,10 @@
       <c r="V141" s="7"/>
       <c r="W141" s="7"/>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
-      <c r="C142" s="17"/>
+      <c r="C142" s="16"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
       <c r="F142" s="7"/>
@@ -7759,10 +8454,10 @@
       <c r="V142" s="7"/>
       <c r="W142" s="7"/>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
-      <c r="C143" s="17"/>
+      <c r="C143" s="16"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
       <c r="F143" s="7"/>
@@ -7782,10 +8477,10 @@
       <c r="V143" s="7"/>
       <c r="W143" s="7"/>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
-      <c r="C144" s="17"/>
+      <c r="C144" s="16"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
       <c r="F144" s="7"/>
@@ -7805,10 +8500,10 @@
       <c r="V144" s="7"/>
       <c r="W144" s="7"/>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
-      <c r="C145" s="17"/>
+      <c r="C145" s="16"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
       <c r="F145" s="7"/>
@@ -7828,10 +8523,10 @@
       <c r="V145" s="7"/>
       <c r="W145" s="7"/>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="17"/>
+      <c r="C146" s="16"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7"/>
@@ -7851,10 +8546,10 @@
       <c r="V146" s="7"/>
       <c r="W146" s="7"/>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
-      <c r="C147" s="17"/>
+      <c r="C147" s="16"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7"/>
@@ -7874,10 +8569,10 @@
       <c r="V147" s="7"/>
       <c r="W147" s="7"/>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
-      <c r="C148" s="17"/>
+      <c r="C148" s="16"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7"/>
@@ -7897,10 +8592,10 @@
       <c r="V148" s="7"/>
       <c r="W148" s="7"/>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="17"/>
+      <c r="C149" s="16"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7"/>
@@ -7920,10 +8615,10 @@
       <c r="V149" s="7"/>
       <c r="W149" s="7"/>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
-      <c r="C150" s="17"/>
+      <c r="C150" s="16"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7"/>
@@ -7943,10 +8638,10 @@
       <c r="V150" s="7"/>
       <c r="W150" s="7"/>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
-      <c r="C151" s="17"/>
+      <c r="C151" s="16"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
       <c r="F151" s="7"/>
@@ -7966,10 +8661,10 @@
       <c r="V151" s="7"/>
       <c r="W151" s="7"/>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
-      <c r="C152" s="17"/>
+      <c r="C152" s="16"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
       <c r="F152" s="7"/>
@@ -7989,10 +8684,10 @@
       <c r="V152" s="7"/>
       <c r="W152" s="7"/>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
-      <c r="C153" s="17"/>
+      <c r="C153" s="16"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
       <c r="F153" s="7"/>
@@ -8012,10 +8707,10 @@
       <c r="V153" s="7"/>
       <c r="W153" s="7"/>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
-      <c r="C154" s="17"/>
+      <c r="C154" s="16"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
       <c r="F154" s="7"/>
@@ -8035,10 +8730,10 @@
       <c r="V154" s="7"/>
       <c r="W154" s="7"/>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
-      <c r="C155" s="17"/>
+      <c r="C155" s="16"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
       <c r="F155" s="7"/>
@@ -8058,10 +8753,10 @@
       <c r="V155" s="7"/>
       <c r="W155" s="7"/>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
-      <c r="C156" s="17"/>
+      <c r="C156" s="16"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7"/>
@@ -8081,10 +8776,10 @@
       <c r="V156" s="7"/>
       <c r="W156" s="7"/>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
-      <c r="C157" s="17"/>
+      <c r="C157" s="16"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="7"/>
@@ -8104,10 +8799,10 @@
       <c r="V157" s="7"/>
       <c r="W157" s="7"/>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
-      <c r="C158" s="17"/>
+      <c r="C158" s="16"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7"/>
@@ -8127,10 +8822,10 @@
       <c r="V158" s="7"/>
       <c r="W158" s="7"/>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
-      <c r="C159" s="17"/>
+      <c r="C159" s="16"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
       <c r="F159" s="7"/>
@@ -8150,10 +8845,10 @@
       <c r="V159" s="7"/>
       <c r="W159" s="7"/>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
-      <c r="C160" s="17"/>
+      <c r="C160" s="16"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
       <c r="F160" s="7"/>
@@ -8173,10 +8868,10 @@
       <c r="V160" s="7"/>
       <c r="W160" s="7"/>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
-      <c r="C161" s="17"/>
+      <c r="C161" s="16"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
       <c r="F161" s="7"/>
@@ -8196,10 +8891,10 @@
       <c r="V161" s="7"/>
       <c r="W161" s="7"/>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
-      <c r="C162" s="17"/>
+      <c r="C162" s="16"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7"/>
@@ -8219,10 +8914,10 @@
       <c r="V162" s="7"/>
       <c r="W162" s="7"/>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
-      <c r="C163" s="17"/>
+      <c r="C163" s="16"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
       <c r="F163" s="7"/>
@@ -8242,10 +8937,10 @@
       <c r="V163" s="7"/>
       <c r="W163" s="7"/>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
-      <c r="C164" s="17"/>
+      <c r="C164" s="16"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7"/>
@@ -8265,10 +8960,10 @@
       <c r="V164" s="7"/>
       <c r="W164" s="7"/>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
-      <c r="C165" s="17"/>
+      <c r="C165" s="16"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
       <c r="F165" s="7"/>
@@ -8288,10 +8983,10 @@
       <c r="V165" s="7"/>
       <c r="W165" s="7"/>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
-      <c r="C166" s="17"/>
+      <c r="C166" s="16"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
       <c r="F166" s="7"/>
@@ -8311,10 +9006,10 @@
       <c r="V166" s="7"/>
       <c r="W166" s="7"/>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
-      <c r="C167" s="17"/>
+      <c r="C167" s="16"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
       <c r="F167" s="7"/>
@@ -8334,10 +9029,10 @@
       <c r="V167" s="7"/>
       <c r="W167" s="7"/>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
-      <c r="C168" s="17"/>
+      <c r="C168" s="16"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
@@ -8357,10 +9052,10 @@
       <c r="V168" s="7"/>
       <c r="W168" s="7"/>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
-      <c r="C169" s="17"/>
+      <c r="C169" s="16"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
       <c r="F169" s="7"/>
@@ -8380,10 +9075,10 @@
       <c r="V169" s="7"/>
       <c r="W169" s="7"/>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
-      <c r="C170" s="17"/>
+      <c r="C170" s="16"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
@@ -8403,10 +9098,10 @@
       <c r="V170" s="7"/>
       <c r="W170" s="7"/>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
-      <c r="C171" s="17"/>
+      <c r="C171" s="16"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="7"/>
@@ -8426,10 +9121,10 @@
       <c r="V171" s="7"/>
       <c r="W171" s="7"/>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
-      <c r="C172" s="17"/>
+      <c r="C172" s="16"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
@@ -8449,10 +9144,10 @@
       <c r="V172" s="7"/>
       <c r="W172" s="7"/>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
-      <c r="C173" s="17"/>
+      <c r="C173" s="16"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -8472,10 +9167,10 @@
       <c r="V173" s="7"/>
       <c r="W173" s="7"/>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
-      <c r="C174" s="17"/>
+      <c r="C174" s="16"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
@@ -8495,10 +9190,10 @@
       <c r="V174" s="7"/>
       <c r="W174" s="7"/>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
-      <c r="C175" s="17"/>
+      <c r="C175" s="16"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
@@ -8518,10 +9213,10 @@
       <c r="V175" s="7"/>
       <c r="W175" s="7"/>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
-      <c r="C176" s="17"/>
+      <c r="C176" s="16"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
@@ -8541,10 +9236,10 @@
       <c r="V176" s="7"/>
       <c r="W176" s="7"/>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
-      <c r="C177" s="17"/>
+      <c r="C177" s="16"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
       <c r="F177" s="7"/>
@@ -8564,10 +9259,10 @@
       <c r="V177" s="7"/>
       <c r="W177" s="7"/>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
-      <c r="C178" s="17"/>
+      <c r="C178" s="16"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
@@ -8587,10 +9282,10 @@
       <c r="V178" s="7"/>
       <c r="W178" s="7"/>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
-      <c r="C179" s="17"/>
+      <c r="C179" s="16"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
       <c r="F179" s="7"/>
@@ -8610,10 +9305,10 @@
       <c r="V179" s="7"/>
       <c r="W179" s="7"/>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
-      <c r="C180" s="17"/>
+      <c r="C180" s="16"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
@@ -8633,10 +9328,10 @@
       <c r="V180" s="7"/>
       <c r="W180" s="7"/>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
-      <c r="C181" s="17"/>
+      <c r="C181" s="16"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
@@ -8656,10 +9351,10 @@
       <c r="V181" s="7"/>
       <c r="W181" s="7"/>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
-      <c r="C182" s="17"/>
+      <c r="C182" s="16"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -8679,10 +9374,10 @@
       <c r="V182" s="7"/>
       <c r="W182" s="7"/>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
-      <c r="C183" s="17"/>
+      <c r="C183" s="16"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
@@ -8702,10 +9397,10 @@
       <c r="V183" s="7"/>
       <c r="W183" s="7"/>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
-      <c r="C184" s="17"/>
+      <c r="C184" s="16"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -8725,10 +9420,10 @@
       <c r="V184" s="7"/>
       <c r="W184" s="7"/>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
-      <c r="C185" s="17"/>
+      <c r="C185" s="16"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
@@ -8748,10 +9443,10 @@
       <c r="V185" s="7"/>
       <c r="W185" s="7"/>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
-      <c r="C186" s="17"/>
+      <c r="C186" s="16"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -8771,62 +9466,545 @@
       <c r="V186" s="7"/>
       <c r="W186" s="7"/>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A187" s="19"/>
-      <c r="B187" s="19"/>
-      <c r="C187" s="19"/>
-      <c r="D187" s="19"/>
-      <c r="E187" s="19"/>
-      <c r="F187" s="19"/>
-      <c r="G187" s="19"/>
-      <c r="H187" s="19"/>
-      <c r="I187" s="19"/>
-      <c r="J187" s="19"/>
-      <c r="K187" s="19"/>
-      <c r="L187" s="12"/>
-      <c r="M187" s="12"/>
-      <c r="Q187" s="19"/>
-      <c r="R187" s="19"/>
-      <c r="S187" s="19"/>
-      <c r="T187" s="19"/>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A188" s="19"/>
-      <c r="B188" s="19"/>
-      <c r="C188" s="19"/>
-      <c r="D188" s="19"/>
-      <c r="E188" s="19"/>
-      <c r="F188" s="19"/>
-      <c r="G188" s="19"/>
-      <c r="H188" s="19"/>
-      <c r="I188" s="19"/>
-      <c r="J188" s="19"/>
-      <c r="K188" s="19"/>
-      <c r="L188" s="12"/>
-      <c r="M188" s="12"/>
-      <c r="Q188" s="19"/>
-      <c r="R188" s="19"/>
-      <c r="S188" s="19"/>
-      <c r="T188" s="19"/>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A189" s="19"/>
-      <c r="B189" s="19"/>
-      <c r="C189" s="19"/>
-      <c r="D189" s="19"/>
-      <c r="E189" s="19"/>
-      <c r="F189" s="19"/>
-      <c r="G189" s="19"/>
-      <c r="H189" s="19"/>
-      <c r="I189" s="19"/>
-      <c r="J189" s="19"/>
-      <c r="K189" s="19"/>
-      <c r="L189" s="12"/>
-      <c r="M189" s="12"/>
-      <c r="Q189" s="19"/>
-      <c r="R189" s="19"/>
-      <c r="S189" s="19"/>
-      <c r="T189" s="19"/>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A187" s="7"/>
+      <c r="B187" s="7"/>
+      <c r="C187" s="16"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="7"/>
+      <c r="I187" s="7"/>
+      <c r="J187" s="7"/>
+      <c r="K187" s="7"/>
+      <c r="L187" s="7"/>
+      <c r="M187" s="7"/>
+      <c r="N187" s="7"/>
+      <c r="Q187" s="7"/>
+      <c r="R187" s="7"/>
+      <c r="S187" s="7"/>
+      <c r="T187" s="7"/>
+      <c r="U187" s="7"/>
+      <c r="V187" s="7"/>
+      <c r="W187" s="7"/>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A188" s="7"/>
+      <c r="B188" s="7"/>
+      <c r="C188" s="16"/>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
+      <c r="G188" s="7"/>
+      <c r="H188" s="7"/>
+      <c r="I188" s="7"/>
+      <c r="J188" s="7"/>
+      <c r="K188" s="7"/>
+      <c r="L188" s="7"/>
+      <c r="M188" s="7"/>
+      <c r="N188" s="7"/>
+      <c r="Q188" s="7"/>
+      <c r="R188" s="7"/>
+      <c r="S188" s="7"/>
+      <c r="T188" s="7"/>
+      <c r="U188" s="7"/>
+      <c r="V188" s="7"/>
+      <c r="W188" s="7"/>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A189" s="7"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="16"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
+      <c r="G189" s="7"/>
+      <c r="H189" s="7"/>
+      <c r="I189" s="7"/>
+      <c r="J189" s="7"/>
+      <c r="K189" s="7"/>
+      <c r="L189" s="7"/>
+      <c r="M189" s="7"/>
+      <c r="N189" s="7"/>
+      <c r="Q189" s="7"/>
+      <c r="R189" s="7"/>
+      <c r="S189" s="7"/>
+      <c r="T189" s="7"/>
+      <c r="U189" s="7"/>
+      <c r="V189" s="7"/>
+      <c r="W189" s="7"/>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A190" s="7"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="16"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
+      <c r="G190" s="7"/>
+      <c r="H190" s="7"/>
+      <c r="I190" s="7"/>
+      <c r="J190" s="7"/>
+      <c r="K190" s="7"/>
+      <c r="L190" s="7"/>
+      <c r="M190" s="7"/>
+      <c r="N190" s="7"/>
+      <c r="Q190" s="7"/>
+      <c r="R190" s="7"/>
+      <c r="S190" s="7"/>
+      <c r="T190" s="7"/>
+      <c r="U190" s="7"/>
+      <c r="V190" s="7"/>
+      <c r="W190" s="7"/>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="16"/>
+      <c r="D191" s="7"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
+      <c r="G191" s="7"/>
+      <c r="H191" s="7"/>
+      <c r="I191" s="7"/>
+      <c r="J191" s="7"/>
+      <c r="K191" s="7"/>
+      <c r="L191" s="7"/>
+      <c r="M191" s="7"/>
+      <c r="N191" s="7"/>
+      <c r="Q191" s="7"/>
+      <c r="R191" s="7"/>
+      <c r="S191" s="7"/>
+      <c r="T191" s="7"/>
+      <c r="U191" s="7"/>
+      <c r="V191" s="7"/>
+      <c r="W191" s="7"/>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="16"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="7"/>
+      <c r="H192" s="7"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
+      <c r="K192" s="7"/>
+      <c r="L192" s="7"/>
+      <c r="M192" s="7"/>
+      <c r="N192" s="7"/>
+      <c r="Q192" s="7"/>
+      <c r="R192" s="7"/>
+      <c r="S192" s="7"/>
+      <c r="T192" s="7"/>
+      <c r="U192" s="7"/>
+      <c r="V192" s="7"/>
+      <c r="W192" s="7"/>
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="16"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
+      <c r="G193" s="7"/>
+      <c r="H193" s="7"/>
+      <c r="I193" s="7"/>
+      <c r="J193" s="7"/>
+      <c r="K193" s="7"/>
+      <c r="L193" s="7"/>
+      <c r="M193" s="7"/>
+      <c r="N193" s="7"/>
+      <c r="Q193" s="7"/>
+      <c r="R193" s="7"/>
+      <c r="S193" s="7"/>
+      <c r="T193" s="7"/>
+      <c r="U193" s="7"/>
+      <c r="V193" s="7"/>
+      <c r="W193" s="7"/>
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A194" s="7"/>
+      <c r="B194" s="7"/>
+      <c r="C194" s="16"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
+      <c r="G194" s="7"/>
+      <c r="H194" s="7"/>
+      <c r="I194" s="7"/>
+      <c r="J194" s="7"/>
+      <c r="K194" s="7"/>
+      <c r="L194" s="7"/>
+      <c r="M194" s="7"/>
+      <c r="N194" s="7"/>
+      <c r="Q194" s="7"/>
+      <c r="R194" s="7"/>
+      <c r="S194" s="7"/>
+      <c r="T194" s="7"/>
+      <c r="U194" s="7"/>
+      <c r="V194" s="7"/>
+      <c r="W194" s="7"/>
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="16"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="7"/>
+      <c r="K195" s="7"/>
+      <c r="L195" s="7"/>
+      <c r="M195" s="7"/>
+      <c r="N195" s="7"/>
+      <c r="Q195" s="7"/>
+      <c r="R195" s="7"/>
+      <c r="S195" s="7"/>
+      <c r="T195" s="7"/>
+      <c r="U195" s="7"/>
+      <c r="V195" s="7"/>
+      <c r="W195" s="7"/>
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="16"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
+      <c r="F196" s="7"/>
+      <c r="G196" s="7"/>
+      <c r="H196" s="7"/>
+      <c r="I196" s="7"/>
+      <c r="J196" s="7"/>
+      <c r="K196" s="7"/>
+      <c r="L196" s="7"/>
+      <c r="M196" s="7"/>
+      <c r="N196" s="7"/>
+      <c r="Q196" s="7"/>
+      <c r="R196" s="7"/>
+      <c r="S196" s="7"/>
+      <c r="T196" s="7"/>
+      <c r="U196" s="7"/>
+      <c r="V196" s="7"/>
+      <c r="W196" s="7"/>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="16"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="7"/>
+      <c r="F197" s="7"/>
+      <c r="G197" s="7"/>
+      <c r="H197" s="7"/>
+      <c r="I197" s="7"/>
+      <c r="J197" s="7"/>
+      <c r="K197" s="7"/>
+      <c r="L197" s="7"/>
+      <c r="M197" s="7"/>
+      <c r="N197" s="7"/>
+      <c r="Q197" s="7"/>
+      <c r="R197" s="7"/>
+      <c r="S197" s="7"/>
+      <c r="T197" s="7"/>
+      <c r="U197" s="7"/>
+      <c r="V197" s="7"/>
+      <c r="W197" s="7"/>
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A198" s="7"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="16"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7"/>
+      <c r="G198" s="7"/>
+      <c r="H198" s="7"/>
+      <c r="I198" s="7"/>
+      <c r="J198" s="7"/>
+      <c r="K198" s="7"/>
+      <c r="L198" s="7"/>
+      <c r="M198" s="7"/>
+      <c r="N198" s="7"/>
+      <c r="Q198" s="7"/>
+      <c r="R198" s="7"/>
+      <c r="S198" s="7"/>
+      <c r="T198" s="7"/>
+      <c r="U198" s="7"/>
+      <c r="V198" s="7"/>
+      <c r="W198" s="7"/>
+    </row>
+    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A199" s="7"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="16"/>
+      <c r="D199" s="7"/>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7"/>
+      <c r="G199" s="7"/>
+      <c r="H199" s="7"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="7"/>
+      <c r="K199" s="7"/>
+      <c r="L199" s="7"/>
+      <c r="M199" s="7"/>
+      <c r="N199" s="7"/>
+      <c r="Q199" s="7"/>
+      <c r="R199" s="7"/>
+      <c r="S199" s="7"/>
+      <c r="T199" s="7"/>
+      <c r="U199" s="7"/>
+      <c r="V199" s="7"/>
+      <c r="W199" s="7"/>
+    </row>
+    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A200" s="7"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="16"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="7"/>
+      <c r="H200" s="7"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="7"/>
+      <c r="K200" s="7"/>
+      <c r="L200" s="7"/>
+      <c r="M200" s="7"/>
+      <c r="N200" s="7"/>
+      <c r="Q200" s="7"/>
+      <c r="R200" s="7"/>
+      <c r="S200" s="7"/>
+      <c r="T200" s="7"/>
+      <c r="U200" s="7"/>
+      <c r="V200" s="7"/>
+      <c r="W200" s="7"/>
+    </row>
+    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A201" s="7"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="16"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
+      <c r="G201" s="7"/>
+      <c r="H201" s="7"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="7"/>
+      <c r="K201" s="7"/>
+      <c r="L201" s="7"/>
+      <c r="M201" s="7"/>
+      <c r="N201" s="7"/>
+      <c r="Q201" s="7"/>
+      <c r="R201" s="7"/>
+      <c r="S201" s="7"/>
+      <c r="T201" s="7"/>
+      <c r="U201" s="7"/>
+      <c r="V201" s="7"/>
+      <c r="W201" s="7"/>
+    </row>
+    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A202" s="7"/>
+      <c r="B202" s="7"/>
+      <c r="C202" s="16"/>
+      <c r="D202" s="7"/>
+      <c r="E202" s="7"/>
+      <c r="F202" s="7"/>
+      <c r="G202" s="7"/>
+      <c r="H202" s="7"/>
+      <c r="I202" s="7"/>
+      <c r="J202" s="7"/>
+      <c r="K202" s="7"/>
+      <c r="L202" s="7"/>
+      <c r="M202" s="7"/>
+      <c r="N202" s="7"/>
+      <c r="Q202" s="7"/>
+      <c r="R202" s="7"/>
+      <c r="S202" s="7"/>
+      <c r="T202" s="7"/>
+      <c r="U202" s="7"/>
+      <c r="V202" s="7"/>
+      <c r="W202" s="7"/>
+    </row>
+    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A203" s="7"/>
+      <c r="B203" s="7"/>
+      <c r="C203" s="16"/>
+      <c r="D203" s="7"/>
+      <c r="E203" s="7"/>
+      <c r="F203" s="7"/>
+      <c r="G203" s="7"/>
+      <c r="H203" s="7"/>
+      <c r="I203" s="7"/>
+      <c r="J203" s="7"/>
+      <c r="K203" s="7"/>
+      <c r="L203" s="7"/>
+      <c r="M203" s="7"/>
+      <c r="N203" s="7"/>
+      <c r="Q203" s="7"/>
+      <c r="R203" s="7"/>
+      <c r="S203" s="7"/>
+      <c r="T203" s="7"/>
+      <c r="U203" s="7"/>
+      <c r="V203" s="7"/>
+      <c r="W203" s="7"/>
+    </row>
+    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A204" s="7"/>
+      <c r="B204" s="7"/>
+      <c r="C204" s="16"/>
+      <c r="D204" s="7"/>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
+      <c r="G204" s="7"/>
+      <c r="H204" s="7"/>
+      <c r="I204" s="7"/>
+      <c r="J204" s="7"/>
+      <c r="K204" s="7"/>
+      <c r="L204" s="7"/>
+      <c r="M204" s="7"/>
+      <c r="N204" s="7"/>
+      <c r="Q204" s="7"/>
+      <c r="R204" s="7"/>
+      <c r="S204" s="7"/>
+      <c r="T204" s="7"/>
+      <c r="U204" s="7"/>
+      <c r="V204" s="7"/>
+      <c r="W204" s="7"/>
+    </row>
+    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A205" s="7"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="16"/>
+      <c r="D205" s="7"/>
+      <c r="E205" s="7"/>
+      <c r="F205" s="7"/>
+      <c r="G205" s="7"/>
+      <c r="H205" s="7"/>
+      <c r="I205" s="7"/>
+      <c r="J205" s="7"/>
+      <c r="K205" s="7"/>
+      <c r="L205" s="7"/>
+      <c r="M205" s="7"/>
+      <c r="N205" s="7"/>
+      <c r="Q205" s="7"/>
+      <c r="R205" s="7"/>
+      <c r="S205" s="7"/>
+      <c r="T205" s="7"/>
+      <c r="U205" s="7"/>
+      <c r="V205" s="7"/>
+      <c r="W205" s="7"/>
+    </row>
+    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A206" s="7"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="16"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="7"/>
+      <c r="F206" s="7"/>
+      <c r="G206" s="7"/>
+      <c r="H206" s="7"/>
+      <c r="I206" s="7"/>
+      <c r="J206" s="7"/>
+      <c r="K206" s="7"/>
+      <c r="L206" s="7"/>
+      <c r="M206" s="7"/>
+      <c r="N206" s="7"/>
+      <c r="Q206" s="7"/>
+      <c r="R206" s="7"/>
+      <c r="S206" s="7"/>
+      <c r="T206" s="7"/>
+      <c r="U206" s="7"/>
+      <c r="V206" s="7"/>
+      <c r="W206" s="7"/>
+    </row>
+    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A207" s="7"/>
+      <c r="B207" s="7"/>
+      <c r="C207" s="16"/>
+      <c r="D207" s="7"/>
+      <c r="E207" s="7"/>
+      <c r="F207" s="7"/>
+      <c r="G207" s="7"/>
+      <c r="H207" s="7"/>
+      <c r="I207" s="7"/>
+      <c r="J207" s="7"/>
+      <c r="K207" s="7"/>
+      <c r="L207" s="7"/>
+      <c r="M207" s="7"/>
+      <c r="N207" s="7"/>
+      <c r="Q207" s="7"/>
+      <c r="R207" s="7"/>
+      <c r="S207" s="7"/>
+      <c r="T207" s="7"/>
+      <c r="U207" s="7"/>
+      <c r="V207" s="7"/>
+      <c r="W207" s="7"/>
+    </row>
+    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A208" s="18"/>
+      <c r="B208" s="18"/>
+      <c r="C208" s="18"/>
+      <c r="D208" s="18"/>
+      <c r="E208" s="18"/>
+      <c r="F208" s="18"/>
+      <c r="G208" s="18"/>
+      <c r="H208" s="18"/>
+      <c r="I208" s="18"/>
+      <c r="J208" s="18"/>
+      <c r="K208" s="18"/>
+      <c r="L208" s="12"/>
+      <c r="M208" s="12"/>
+      <c r="Q208" s="18"/>
+      <c r="R208" s="18"/>
+      <c r="S208" s="18"/>
+      <c r="T208" s="18"/>
+    </row>
+    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A209" s="18"/>
+      <c r="B209" s="18"/>
+      <c r="C209" s="18"/>
+      <c r="D209" s="18"/>
+      <c r="E209" s="18"/>
+      <c r="F209" s="18"/>
+      <c r="G209" s="18"/>
+      <c r="H209" s="18"/>
+      <c r="I209" s="18"/>
+      <c r="J209" s="18"/>
+      <c r="K209" s="18"/>
+      <c r="L209" s="12"/>
+      <c r="M209" s="12"/>
+      <c r="Q209" s="18"/>
+      <c r="R209" s="18"/>
+      <c r="S209" s="18"/>
+      <c r="T209" s="18"/>
+    </row>
+    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A210" s="18"/>
+      <c r="B210" s="18"/>
+      <c r="C210" s="18"/>
+      <c r="D210" s="18"/>
+      <c r="E210" s="18"/>
+      <c r="F210" s="18"/>
+      <c r="G210" s="18"/>
+      <c r="H210" s="18"/>
+      <c r="I210" s="18"/>
+      <c r="J210" s="18"/>
+      <c r="K210" s="18"/>
+      <c r="L210" s="12"/>
+      <c r="M210" s="12"/>
+      <c r="Q210" s="18"/>
+      <c r="R210" s="18"/>
+      <c r="S210" s="18"/>
+      <c r="T210" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
@@ -8837,7 +10015,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="L19:R61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="12" max="12" width="5.1640625" customWidth="1"/>
     <col min="13" max="13" width="18.33203125" customWidth="1"/>
@@ -8845,24 +10023,24 @@
     <col min="16" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
+        <v>250</v>
+      </c>
+      <c r="M19" t="s">
         <v>251</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>252</v>
       </c>
-      <c r="N19" t="s">
+      <c r="P19" t="s">
         <v>253</v>
       </c>
-      <c r="P19" t="s">
+      <c r="R19" t="s">
         <v>254</v>
       </c>
-      <c r="R19" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="20" spans="12:18" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L20">
         <v>5001</v>
       </c>
@@ -8873,10 +10051,10 @@
         <v>5</v>
       </c>
       <c r="O20" t="s">
+        <v>255</v>
+      </c>
+      <c r="P20" t="s">
         <v>256</v>
-      </c>
-      <c r="P20" t="s">
-        <v>257</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -8886,7 +10064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L21">
         <v>5002</v>
       </c>
@@ -8897,10 +10075,10 @@
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -8910,7 +10088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L22">
         <v>5003</v>
       </c>
@@ -8921,10 +10099,10 @@
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P22" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -8934,7 +10112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>5004</v>
       </c>
@@ -8945,10 +10123,10 @@
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -8958,7 +10136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L24">
         <v>5005</v>
       </c>
@@ -8969,10 +10147,10 @@
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P24" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -8982,7 +10160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L25">
         <v>5006</v>
       </c>
@@ -8993,10 +10171,10 @@
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -9006,7 +10184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L26">
         <v>5007</v>
       </c>
@@ -9017,10 +10195,10 @@
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -9030,7 +10208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L27">
         <v>5008</v>
       </c>
@@ -9041,10 +10219,10 @@
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -9054,7 +10232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L28">
         <v>5009</v>
       </c>
@@ -9065,10 +10243,10 @@
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="P28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -9078,7 +10256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L29">
         <v>6001</v>
       </c>
@@ -9086,10 +10264,10 @@
         <v>207</v>
       </c>
       <c r="O29" t="s">
+        <v>265</v>
+      </c>
+      <c r="P29" t="s">
         <v>266</v>
-      </c>
-      <c r="P29" t="s">
-        <v>267</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -9099,7 +10277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L30">
         <v>6002</v>
       </c>
@@ -9107,10 +10285,10 @@
         <v>209</v>
       </c>
       <c r="O30" t="s">
+        <v>265</v>
+      </c>
+      <c r="P30" t="s">
         <v>266</v>
-      </c>
-      <c r="P30" t="s">
-        <v>267</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -9120,7 +10298,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L31">
         <v>6003</v>
       </c>
@@ -9128,10 +10306,10 @@
         <v>210</v>
       </c>
       <c r="O31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -9141,7 +10319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L32">
         <v>6004</v>
       </c>
@@ -9149,10 +10327,10 @@
         <v>212</v>
       </c>
       <c r="O32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -9162,7 +10340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L33">
         <v>6005</v>
       </c>
@@ -9170,10 +10348,10 @@
         <v>214</v>
       </c>
       <c r="O33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P33" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -9183,7 +10361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L34">
         <v>6006</v>
       </c>
@@ -9191,10 +10369,10 @@
         <v>216</v>
       </c>
       <c r="O34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P34" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -9204,7 +10382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L35">
         <v>6007</v>
       </c>
@@ -9212,10 +10390,10 @@
         <v>218</v>
       </c>
       <c r="O35" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P35" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -9225,7 +10403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L36">
         <v>6008</v>
       </c>
@@ -9233,10 +10411,10 @@
         <v>219</v>
       </c>
       <c r="O36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -9246,7 +10424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L37">
         <v>6009</v>
       </c>
@@ -9254,10 +10432,10 @@
         <v>221</v>
       </c>
       <c r="O37" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -9267,7 +10445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L38">
         <v>6010</v>
       </c>
@@ -9275,10 +10453,10 @@
         <v>223</v>
       </c>
       <c r="O38" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -9288,7 +10466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L39">
         <v>6011</v>
       </c>
@@ -9296,10 +10474,10 @@
         <v>224</v>
       </c>
       <c r="O39" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P39" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -9309,7 +10487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L40">
         <v>6012</v>
       </c>
@@ -9317,10 +10495,10 @@
         <v>225</v>
       </c>
       <c r="O40" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -9330,7 +10508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L41">
         <v>6013</v>
       </c>
@@ -9338,10 +10516,10 @@
         <v>226</v>
       </c>
       <c r="O41" t="s">
+        <v>265</v>
+      </c>
+      <c r="P41" t="s">
         <v>266</v>
-      </c>
-      <c r="P41" t="s">
-        <v>267</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -9351,7 +10529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L42">
         <v>6014</v>
       </c>
@@ -9359,10 +10537,10 @@
         <v>227</v>
       </c>
       <c r="O42" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -9372,7 +10550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L43">
         <v>6015</v>
       </c>
@@ -9380,10 +10558,10 @@
         <v>229</v>
       </c>
       <c r="O43" t="s">
+        <v>265</v>
+      </c>
+      <c r="P43" t="s">
         <v>266</v>
-      </c>
-      <c r="P43" t="s">
-        <v>267</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -9393,7 +10571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L44">
         <v>7001</v>
       </c>
@@ -9404,10 +10582,10 @@
         <v>7</v>
       </c>
       <c r="O44" t="s">
+        <v>274</v>
+      </c>
+      <c r="P44" t="s">
         <v>275</v>
-      </c>
-      <c r="P44" t="s">
-        <v>276</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -9417,7 +10595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L45">
         <v>7002</v>
       </c>
@@ -9428,10 +10606,10 @@
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P45" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -9441,7 +10619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L46">
         <v>7003</v>
       </c>
@@ -9452,10 +10630,10 @@
         <v>7</v>
       </c>
       <c r="O46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -9465,7 +10643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L47">
         <v>7004</v>
       </c>
@@ -9476,10 +10654,10 @@
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -9489,7 +10667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L48">
         <v>8001</v>
       </c>
@@ -9500,10 +10678,10 @@
         <v>8</v>
       </c>
       <c r="O48" t="s">
+        <v>279</v>
+      </c>
+      <c r="P48" t="s">
         <v>280</v>
-      </c>
-      <c r="P48" t="s">
-        <v>281</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -9513,21 +10691,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L49">
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" t="s">
+        <v>279</v>
+      </c>
+      <c r="P49" t="s">
         <v>280</v>
-      </c>
-      <c r="P49" t="s">
-        <v>281</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -9537,21 +10715,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L50">
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" t="s">
+        <v>279</v>
+      </c>
+      <c r="P50" t="s">
         <v>280</v>
-      </c>
-      <c r="P50" t="s">
-        <v>281</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -9561,21 +10739,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L51">
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" t="s">
+        <v>279</v>
+      </c>
+      <c r="P51" t="s">
         <v>280</v>
-      </c>
-      <c r="P51" t="s">
-        <v>281</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -9585,21 +10763,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L52">
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" t="s">
+        <v>279</v>
+      </c>
+      <c r="P52" t="s">
         <v>280</v>
-      </c>
-      <c r="P52" t="s">
-        <v>281</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -9609,21 +10787,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L53">
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" t="s">
+        <v>279</v>
+      </c>
+      <c r="P53" t="s">
         <v>280</v>
-      </c>
-      <c r="P53" t="s">
-        <v>281</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -9633,21 +10811,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L54">
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" t="s">
+        <v>279</v>
+      </c>
+      <c r="P54" t="s">
         <v>280</v>
-      </c>
-      <c r="P54" t="s">
-        <v>281</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -9657,21 +10835,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L55">
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" t="s">
+        <v>279</v>
+      </c>
+      <c r="P55" t="s">
         <v>280</v>
-      </c>
-      <c r="P55" t="s">
-        <v>281</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -9681,21 +10859,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L56">
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" t="s">
+        <v>279</v>
+      </c>
+      <c r="P56" t="s">
         <v>280</v>
-      </c>
-      <c r="P56" t="s">
-        <v>281</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -9705,21 +10883,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L57">
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" t="s">
+        <v>279</v>
+      </c>
+      <c r="P57" t="s">
         <v>280</v>
-      </c>
-      <c r="P57" t="s">
-        <v>281</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -9729,21 +10907,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L58">
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" t="s">
+        <v>279</v>
+      </c>
+      <c r="P58" t="s">
         <v>280</v>
-      </c>
-      <c r="P58" t="s">
-        <v>281</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -9753,21 +10931,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L59">
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" t="s">
+        <v>279</v>
+      </c>
+      <c r="P59" t="s">
         <v>280</v>
-      </c>
-      <c r="P59" t="s">
-        <v>281</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -9777,21 +10955,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L60">
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" t="s">
+        <v>279</v>
+      </c>
+      <c r="P60" t="s">
         <v>280</v>
-      </c>
-      <c r="P60" t="s">
-        <v>281</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -9801,21 +10979,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="12:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L61">
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" t="s">
+        <v>279</v>
+      </c>
+      <c r="P61" t="s">
         <v>280</v>
-      </c>
-      <c r="P61" t="s">
-        <v>281</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55A927ED-08EB-46E2-AC58-0C92C90A547C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30600" windowHeight="18360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="347">
   <si>
     <t>##var</t>
   </si>
@@ -48,12 +42,18 @@
     <t>name</t>
   </si>
   <si>
+    <t>itemTip</t>
+  </si>
+  <si>
     <t>itemType</t>
   </si>
   <si>
     <t>model</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>model_size</t>
   </si>
   <si>
@@ -111,6 +111,9 @@
     <t>if_lake</t>
   </si>
   <si>
+    <t>BuffType</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -123,6 +126,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -141,6 +147,9 @@
     <t>道具模型</t>
   </si>
   <si>
+    <t>道具图标</t>
+  </si>
+  <si>
     <t>道具模型大小</t>
   </si>
   <si>
@@ -195,6 +204,9 @@
     <t>是否会被湖神吃</t>
   </si>
   <si>
+    <t>buff效果</t>
+  </si>
+  <si>
     <t>唯一id</t>
   </si>
   <si>
@@ -249,76 +261,85 @@
     <t>0可以被湖神吃 1不可以被湖神吃</t>
   </si>
   <si>
+    <t>buffid，buffid 只有合成道具配置</t>
+  </si>
+  <si>
     <t>土豆-种子袋</t>
   </si>
   <si>
+    <t>Prefab/Plants/Potato</t>
+  </si>
+  <si>
     <t>蘑菇-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/seedbag</t>
+    <t>Prefab/plant/seedbag</t>
   </si>
   <si>
     <t>南瓜-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag Pumkin</t>
+    <t>Prefab/plant/SeedBag Pumkin</t>
   </si>
   <si>
     <t>胡萝卜-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag Carrot</t>
+    <t>Prefab/plant/SeedBag Carrot</t>
   </si>
   <si>
     <t>水甜菜-种子袋</t>
   </si>
   <si>
+    <t>Prefab/Plants/WaterBeet</t>
+  </si>
+  <si>
     <t>番茄-红-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag TomatoRed</t>
+    <t>Prefab/plant/SeedBag TomatoRed</t>
   </si>
   <si>
     <t>番茄-橙-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag TomatoOrange</t>
+    <t>Prefab/plant/SeedBag TomatoOrange</t>
   </si>
   <si>
     <t>番茄-黄-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag TomatoYellow</t>
+    <t>Prefab/plant/SeedBag TomatoYellow</t>
   </si>
   <si>
     <t>番茄-绿-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag TomatoGreen</t>
+    <t>Prefab/plant/SeedBag TomatoGreen</t>
   </si>
   <si>
     <t>番茄-青-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag TomatoCyan</t>
+    <t>Prefab/plant/SeedBag TomatoCyan</t>
   </si>
   <si>
     <t>番茄-蓝-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag TomatoBlue</t>
+    <t>Prefab/plant/SeedBag TomatoBlue</t>
   </si>
   <si>
     <t>番茄-紫-种子袋</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag TomatoPurple</t>
+    <t>Prefab/plant/SeedBag TomatoPurple</t>
   </si>
   <si>
     <t>花椰菜-种子袋(一次性)</t>
   </si>
   <si>
-    <t>prefab/plant/SeedBag CauliFlower</t>
+    <t>Prefab/plant/SeedBag CauliFlower</t>
   </si>
   <si>
     <t>花椰菜-种子袋(永久)</t>
@@ -327,7 +348,13 @@
     <t>土豆</t>
   </si>
   <si>
-    <t>prefab/plant/PotatoModel</t>
+    <t>阿巴，这里等文案策划配置</t>
+  </si>
+  <si>
+    <t>Prefab/Plant/Potato</t>
+  </si>
+  <si>
+    <t>Art/Images/Icons/Group 62@2x#10</t>
   </si>
   <si>
     <t>台球音效</t>
@@ -342,7 +369,7 @@
     <t>蘑菇</t>
   </si>
   <si>
-    <t>prefab/plant/mushroom_002</t>
+    <t>Prefab/Plant/Mushroom</t>
   </si>
   <si>
     <t>弹飞触碰到的道具，玩家</t>
@@ -354,7 +381,7 @@
     <t>南瓜</t>
   </si>
   <si>
-    <t>prefab/plant/Pumpkin</t>
+    <t>Prefab/Plant/Pumpkin</t>
   </si>
   <si>
     <t>吞入碰到的作物/玩家，吞下作物1s吐出（此时不会吞下其他作物/玩家，玩家也无法交互），吞下玩家，玩家模型消失，屏幕显示南瓜头（玩家此时只能按任意方向键从按下的方向键出来）</t>
@@ -369,7 +396,7 @@
     <t>胡萝卜</t>
   </si>
   <si>
-    <t>prefab/plant/Carrot</t>
+    <t>Prefab/Plant/Carrot</t>
   </si>
   <si>
     <t>瓶子音效</t>
@@ -387,7 +414,7 @@
     <t>水甜菜</t>
   </si>
   <si>
-    <t>prefab/plant/Beet</t>
+    <t>Prefab/Plant/WaterBeet</t>
   </si>
   <si>
     <t>无效果</t>
@@ -402,7 +429,7 @@
     <t>番茄-红</t>
   </si>
   <si>
-    <t>prefab/plant/Tomato_red</t>
+    <t>Prefab/Plant/Tomato_red</t>
   </si>
   <si>
     <t>染色</t>
@@ -417,31 +444,43 @@
     <t>番茄-橙</t>
   </si>
   <si>
+    <t>Prefab/Plant/Tomato_orange</t>
+  </si>
+  <si>
     <t>番茄-黄</t>
   </si>
   <si>
-    <t>prefab/plant/Tomato_yellow</t>
+    <t>Prefab/Plant/Tomato_yellow</t>
   </si>
   <si>
     <t>番茄-绿</t>
   </si>
   <si>
-    <t>prefab/plant/Tomato_green</t>
+    <t>Prefab/Plant/Tomato_green</t>
   </si>
   <si>
     <t>番茄-青</t>
   </si>
   <si>
+    <t>Prefab/Plant/Tomato_cyan</t>
+  </si>
+  <si>
     <t>番茄-蓝</t>
   </si>
   <si>
+    <t>Prefab/Plant/Tomato_blue</t>
+  </si>
+  <si>
     <t>番茄-紫</t>
   </si>
   <si>
+    <t>Prefab/Plant/Tomato_purple</t>
+  </si>
+  <si>
     <t>花椰菜</t>
   </si>
   <si>
-    <t>prefab/plant/Cauliflower</t>
+    <t>Prefab/Plant/Cauliflower</t>
   </si>
   <si>
     <t>碰到播放音效，“咩”</t>
@@ -456,7 +495,7 @@
     <t>猕猴桃</t>
   </si>
   <si>
-    <t>prefab/plant/mihoutao</t>
+    <t>Prefab/Plant/Kiwi</t>
   </si>
   <si>
     <t>保龄球音效</t>
@@ -471,42 +510,63 @@
     <t>野草</t>
   </si>
   <si>
+    <t>Prefab/Plant/Grass</t>
+  </si>
+  <si>
     <t>吃下后可以和羊npc对话</t>
   </si>
   <si>
     <t>土豆-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/PotatoModel</t>
+  </si>
+  <si>
     <t>土豆-存储</t>
   </si>
   <si>
     <t>蘑菇-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/mushroom_002</t>
+  </si>
+  <si>
     <t>蘑菇-存储</t>
   </si>
   <si>
     <t>南瓜-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/Pumpkin</t>
+  </si>
+  <si>
     <t>南瓜-存储</t>
   </si>
   <si>
     <t>胡萝卜-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/Carrot</t>
+  </si>
+  <si>
     <t>胡萝卜-存储</t>
   </si>
   <si>
     <t>水甜菜-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/Beet</t>
+  </si>
+  <si>
     <t>水甜菜-存储</t>
   </si>
   <si>
     <t>番茄-红-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/Tomato_red</t>
+  </si>
+  <si>
     <t>番茄-红-存储</t>
   </si>
   <si>
@@ -519,12 +579,18 @@
     <t>番茄-黄-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/Tomato_yellow</t>
+  </si>
+  <si>
     <t>番茄-黄-存储</t>
   </si>
   <si>
     <t>番茄-绿-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/Tomato_green</t>
+  </si>
+  <si>
     <t>番茄-绿-存储</t>
   </si>
   <si>
@@ -549,12 +615,18 @@
     <t>花椰菜-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/Cauliflower</t>
+  </si>
+  <si>
     <t>花椰菜-存储</t>
   </si>
   <si>
     <t>猕猴桃-巨大作物</t>
   </si>
   <si>
+    <t>Prefab/plant/mihoutao</t>
+  </si>
+  <si>
     <t>猕猴桃-存储</t>
   </si>
   <si>
@@ -612,144 +684,357 @@
     <t>洒水壶</t>
   </si>
   <si>
+    <t>Prefab/Plants/Kettle</t>
+  </si>
+  <si>
     <t>删除染色</t>
   </si>
   <si>
     <t>莲叶</t>
   </si>
   <si>
-    <t>prefab/Item/Lotus_Leaf</t>
+    <t>Prefab/Item/Lotus_Leaf</t>
   </si>
   <si>
     <t>猕猴桃树</t>
   </si>
   <si>
-    <t>prefab/Item/Kiwi_Tree</t>
+    <t>Prefab/Plants/Kiwi_Tree</t>
   </si>
   <si>
     <t>灌木丛根</t>
   </si>
   <si>
-    <t>prefab/Item/Bush_Root</t>
+    <t>Prefab/Plants/Bush_Root</t>
   </si>
   <si>
     <t>传送门</t>
   </si>
   <si>
-    <t>prefab/Item/Portal</t>
+    <t>Prefab/Item/Portal</t>
   </si>
   <si>
     <t>隐藏门</t>
   </si>
   <si>
-    <t>prefab/Item/Hidden_Door</t>
+    <t>Prefab/Item/Hidden_Door</t>
   </si>
   <si>
     <t>钥匙</t>
   </si>
   <si>
-    <t>prefab/Item/Key</t>
+    <t>Prefab/Item/Key</t>
   </si>
   <si>
     <t>爆米花机</t>
   </si>
   <si>
-    <t>prefab/Item/Popcorn_Machine</t>
+    <t>Prefab/Item/Popcorn_Machine</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;蘑菇味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;南瓜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-土豆&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;南瓜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-蘑菇&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;胡萝卜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-南瓜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;水甜菜味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-胡萝卜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;红番茄味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-水甜菜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;花椰菜味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-红番茄&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜&amp;猕猴桃味</t>
+  </si>
+  <si>
+    <t>爆米花-花椰菜&amp;野草味</t>
+  </si>
+  <si>
+    <t>爆米花-猕猴桃&amp;野草味</t>
+  </si>
+  <si>
+    <t>土豆-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/mushroom_002</t>
+  </si>
+  <si>
+    <t>蘑菇-房子</t>
+  </si>
+  <si>
+    <t>南瓜-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/Pumpkin</t>
+  </si>
+  <si>
+    <t>胡萝卜-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/Carrot</t>
+  </si>
+  <si>
+    <t>水甜菜-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/Beet</t>
+  </si>
+  <si>
+    <t>番茄-红-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/Tomato_red</t>
+  </si>
+  <si>
+    <t>番茄-橙-房子</t>
+  </si>
+  <si>
+    <t>番茄-黄-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/Tomato_yellow</t>
+  </si>
+  <si>
+    <t>番茄-绿-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/Tomato_green</t>
+  </si>
+  <si>
+    <t>番茄-青-房子</t>
+  </si>
+  <si>
+    <t>番茄-蓝-房子</t>
+  </si>
+  <si>
+    <t>番茄-紫-房子</t>
+  </si>
+  <si>
+    <t>花椰菜-房子</t>
+  </si>
+  <si>
+    <t>猕猴桃-房子</t>
+  </si>
+  <si>
+    <t>Prefab/Bulit/Kiwi</t>
+  </si>
+  <si>
+    <t>野草-房子</t>
+  </si>
+  <si>
+    <t>格蕾丝</t>
+  </si>
+  <si>
+    <t>Prefab/GameController/Player_V2</t>
+  </si>
+  <si>
+    <t>甜菜女士</t>
+  </si>
+  <si>
+    <t>Prefab/Npc/Sheep</t>
+  </si>
+  <si>
+    <t>花椰菜羊-白</t>
+  </si>
+  <si>
+    <t>花椰菜羊-绿</t>
+  </si>
+  <si>
+    <t>Prefab/Npc/sheep_Green</t>
+  </si>
+  <si>
+    <t>猴子先生</t>
+  </si>
+  <si>
+    <t>Prefab/Npc/Character_monkey</t>
+  </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>中文名称</t>
+  </si>
+  <si>
+    <t>分类标识</t>
+  </si>
+  <si>
+    <t>英文名称</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>Item/</t>
+  </si>
+  <si>
+    <t>Watering_Can</t>
+  </si>
+  <si>
+    <t>Lotus_Leaf</t>
+  </si>
+  <si>
+    <t>Kiwi_Tree</t>
+  </si>
+  <si>
+    <t>Bush_Root</t>
+  </si>
+  <si>
+    <t>Portal</t>
+  </si>
+  <si>
+    <t>Hidden_Door</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Popcorn_Machine</t>
   </si>
   <si>
     <t>爆米花-花椰菜汤味</t>
   </si>
   <si>
-    <t>土豆-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/mushroom_002</t>
-  </si>
-  <si>
-    <t>蘑菇-房子</t>
-  </si>
-  <si>
-    <t>南瓜-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/Pumpkin</t>
-  </si>
-  <si>
-    <t>胡萝卜-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/Carrot</t>
-  </si>
-  <si>
-    <t>水甜菜-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/Beet</t>
-  </si>
-  <si>
-    <t>番茄-红-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/Tomato_red</t>
-  </si>
-  <si>
-    <t>番茄-橙-房子</t>
-  </si>
-  <si>
-    <t>番茄-黄-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/Tomato_yellow</t>
-  </si>
-  <si>
-    <t>番茄-绿-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/Tomato_green</t>
-  </si>
-  <si>
-    <t>番茄-青-房子</t>
-  </si>
-  <si>
-    <t>番茄-蓝-房子</t>
-  </si>
-  <si>
-    <t>番茄-紫-房子</t>
-  </si>
-  <si>
-    <t>花椰菜-房子</t>
-  </si>
-  <si>
-    <t>猕猴桃-房子</t>
-  </si>
-  <si>
-    <t>prefab/Bulit/Kiwi</t>
-  </si>
-  <si>
-    <t>野草-房子</t>
-  </si>
-  <si>
-    <t>甜菜女士</t>
-  </si>
-  <si>
-    <t>花椰菜羊-白</t>
-  </si>
-  <si>
-    <t>花椰菜羊-绿</t>
-  </si>
-  <si>
-    <t>prefab/Npc/sheep_Green</t>
-  </si>
-  <si>
-    <t>猴子先生</t>
-  </si>
-  <si>
-    <t>prefab/Npc/Character_monkey</t>
+    <t>Popcorn_Cauliflower_Soup_Flavor</t>
+  </si>
+  <si>
+    <t>Bulit/</t>
+  </si>
+  <si>
+    <t>mushroom_002</t>
+  </si>
+  <si>
+    <t>Pumpkin</t>
+  </si>
+  <si>
+    <t>Carrot</t>
+  </si>
+  <si>
+    <t>Beet</t>
+  </si>
+  <si>
+    <t>Tomato_red</t>
+  </si>
+  <si>
+    <t>Tomato_yellow</t>
+  </si>
+  <si>
+    <t>Tomato_green</t>
+  </si>
+  <si>
+    <t>Kiwi</t>
+  </si>
+  <si>
+    <t>Npc/</t>
+  </si>
+  <si>
+    <t>Ms._Beet</t>
+  </si>
+  <si>
+    <t>Cauliflower_Sheep_White</t>
+  </si>
+  <si>
+    <t>Cauliflower_Sheep_Green</t>
+  </si>
+  <si>
+    <t>Mr._Monkey</t>
   </si>
   <si>
     <t>土豆-幼苗</t>
   </si>
   <si>
+    <t>Seedling/</t>
+  </si>
+  <si>
+    <t>seedling</t>
+  </si>
+  <si>
     <t>蘑菇-幼苗</t>
   </si>
   <si>
@@ -787,276 +1072,19 @@
   </si>
   <si>
     <t>花椰菜-幼苗(永久)</t>
-  </si>
-  <si>
-    <t>编号</t>
-  </si>
-  <si>
-    <t>中文名称</t>
-  </si>
-  <si>
-    <t>分类标识</t>
-  </si>
-  <si>
-    <t>英文名称</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>Item/</t>
-  </si>
-  <si>
-    <t>Watering_Can</t>
-  </si>
-  <si>
-    <t>Lotus_Leaf</t>
-  </si>
-  <si>
-    <t>Kiwi_Tree</t>
-  </si>
-  <si>
-    <t>Bush_Root</t>
-  </si>
-  <si>
-    <t>Portal</t>
-  </si>
-  <si>
-    <t>Hidden_Door</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Popcorn_Machine</t>
-  </si>
-  <si>
-    <t>Popcorn_Cauliflower_Soup_Flavor</t>
-  </si>
-  <si>
-    <t>Bulit/</t>
-  </si>
-  <si>
-    <t>mushroom_002</t>
-  </si>
-  <si>
-    <t>Pumpkin</t>
-  </si>
-  <si>
-    <t>Carrot</t>
-  </si>
-  <si>
-    <t>Beet</t>
-  </si>
-  <si>
-    <t>Tomato_red</t>
-  </si>
-  <si>
-    <t>Tomato_yellow</t>
-  </si>
-  <si>
-    <t>Tomato_green</t>
-  </si>
-  <si>
-    <t>Kiwi</t>
-  </si>
-  <si>
-    <t>Npc/</t>
-  </si>
-  <si>
-    <t>Ms._Beet</t>
-  </si>
-  <si>
-    <t>Cauliflower_Sheep_White</t>
-  </si>
-  <si>
-    <t>Cauliflower_Sheep_Green</t>
-  </si>
-  <si>
-    <t>Mr._Monkey</t>
-  </si>
-  <si>
-    <t>Seedling/</t>
-  </si>
-  <si>
-    <t>seedling</t>
-  </si>
-  <si>
-    <t>Prefab/Plants/Kettle</t>
-  </si>
-  <si>
-    <t>itemTip</t>
-  </si>
-  <si>
-    <t>阿巴，这里等文案策划配置</t>
-  </si>
-  <si>
-    <t>阿巴，这里等文案策划配置</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>格蕾丝</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>prefab/GameController/Player_V2</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>prefab/Npc/Sheep</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具图标</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Art/Images/Icons/Group 62@2x#10</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
-  <si>
-    <t>甜菜女士</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>BuffType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=,),int</t>
-  </si>
-  <si>
-    <t>buff效果</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>buffid，buffid 只有合成道具配置</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prefab/Plants/Potato</t>
-  </si>
-  <si>
-    <t>Prefab/Plants/WaterBeet</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;蘑菇味</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;南瓜味</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;胡萝卜味</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;水甜菜味</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;红番茄味</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;花椰菜味</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;猕猴桃味</t>
-  </si>
-  <si>
-    <t>爆米花-土豆&amp;野草味</t>
-  </si>
-  <si>
-    <t>爆米花-蘑菇&amp;南瓜味</t>
-  </si>
-  <si>
-    <t>爆米花-蘑菇&amp;胡萝卜味</t>
-  </si>
-  <si>
-    <t>爆米花-蘑菇&amp;水甜菜味</t>
-  </si>
-  <si>
-    <t>爆米花-蘑菇&amp;红番茄味</t>
-  </si>
-  <si>
-    <t>爆米花-蘑菇&amp;花椰菜味</t>
-  </si>
-  <si>
-    <t>爆米花-蘑菇&amp;猕猴桃味</t>
-  </si>
-  <si>
-    <t>爆米花-蘑菇&amp;野草味</t>
-  </si>
-  <si>
-    <t>爆米花-南瓜&amp;胡萝卜味</t>
-  </si>
-  <si>
-    <t>爆米花-南瓜&amp;水甜菜味</t>
-  </si>
-  <si>
-    <t>爆米花-南瓜&amp;红番茄味</t>
-  </si>
-  <si>
-    <t>爆米花-南瓜&amp;花椰菜味</t>
-  </si>
-  <si>
-    <t>爆米花-南瓜&amp;猕猴桃味</t>
-  </si>
-  <si>
-    <t>爆米花-南瓜&amp;野草味</t>
-  </si>
-  <si>
-    <t>爆米花-胡萝卜&amp;水甜菜味</t>
-  </si>
-  <si>
-    <t>爆米花-胡萝卜&amp;红番茄味</t>
-  </si>
-  <si>
-    <t>爆米花-胡萝卜&amp;花椰菜味</t>
-  </si>
-  <si>
-    <t>爆米花-胡萝卜&amp;猕猴桃味</t>
-  </si>
-  <si>
-    <t>爆米花-胡萝卜&amp;野草味</t>
-  </si>
-  <si>
-    <t>爆米花-水甜菜&amp;红番茄味</t>
-  </si>
-  <si>
-    <t>爆米花-水甜菜&amp;花椰菜味</t>
-  </si>
-  <si>
-    <t>爆米花-水甜菜&amp;猕猴桃味</t>
-  </si>
-  <si>
-    <t>爆米花-水甜菜&amp;野草味</t>
-  </si>
-  <si>
-    <t>爆米花-红番茄&amp;花椰菜味</t>
-  </si>
-  <si>
-    <t>爆米花-红番茄&amp;猕猴桃味</t>
-  </si>
-  <si>
-    <t>爆米花-红番茄&amp;野草味</t>
-  </si>
-  <si>
-    <t>爆米花-花椰菜&amp;猕猴桃味</t>
-  </si>
-  <si>
-    <t>爆米花-花椰菜&amp;野草味</t>
-  </si>
-  <si>
-    <t>爆米花-猕猴桃&amp;野草味</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1069,7 +1097,6 @@
       <sz val="11"/>
       <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1078,7 +1105,6 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1087,7 +1113,6 @@
       <sz val="10"/>
       <color rgb="FF1F2329"/>
       <name val="等线"/>
-      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1095,7 +1120,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1103,7 +1127,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1112,22 +1149,6 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1135,43 +1156,155 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1196,8 +1329,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1306,11 +1625,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1336,65 +1897,103 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1652,33 +2251,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AB210"/>
-  <sheetFormatPr defaultColWidth="12.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="12.1666666666667" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="12.1640625" style="2"/>
-    <col min="3" max="3" width="22.83203125" style="2" customWidth="1"/>
+    <col min="1" max="2" width="12.1666666666667" style="2"/>
+    <col min="3" max="3" width="22.8333333333333" style="2" customWidth="1"/>
     <col min="4" max="4" width="24.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="28.58203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.9140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.4140625" style="2" customWidth="1"/>
-    <col min="10" max="12" width="7.08203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" style="2" customWidth="1"/>
-    <col min="14" max="18" width="12.1640625" style="2"/>
-    <col min="19" max="20" width="17.83203125" style="2" customWidth="1"/>
-    <col min="21" max="22" width="26.33203125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="12.1640625" style="2"/>
-    <col min="29" max="16384" width="12.1640625" style="2"/>
+    <col min="6" max="6" width="28.5833333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.3333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.91666666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="8.41666666666667" style="2" customWidth="1"/>
+    <col min="10" max="12" width="7.08333333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="16.6666666666667" style="2" customWidth="1"/>
+    <col min="14" max="18" width="12.1666666666667" style="2"/>
+    <col min="19" max="20" width="17.8333333333333" style="2" customWidth="1"/>
+    <col min="21" max="22" width="26.3333333333333" style="2" customWidth="1"/>
+    <col min="23" max="23" width="12.1666666666667" style="2"/>
+    <col min="29" max="16384" width="12.1666666666667" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1689,340 +2288,340 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>282</v>
+        <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA2" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA1" s="22" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="23" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="U3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA3" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" s="4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA3" s="22" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="X4" s="8" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Z4" s="8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="AA4" s="8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="7"/>
       <c r="B5" s="2">
         <v>1001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E5" s="2">
         <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>296</v>
+        <v>78</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="2">
@@ -2056,19 +2655,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22">
       <c r="A6" s="7"/>
       <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="2">
@@ -2102,19 +2701,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22">
       <c r="A7" s="7"/>
       <c r="B7" s="2">
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="2">
@@ -2148,19 +2747,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22">
       <c r="A8" s="7"/>
       <c r="B8" s="2">
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="2">
@@ -2194,19 +2793,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22">
       <c r="A9" s="7"/>
       <c r="B9" s="2">
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>297</v>
+        <v>86</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="2">
@@ -2240,19 +2839,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22">
       <c r="A10" s="7"/>
       <c r="B10" s="2">
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G10" s="8"/>
       <c r="H10" s="2">
@@ -2286,19 +2885,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22">
       <c r="A11" s="7"/>
       <c r="B11" s="2">
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G11" s="8"/>
       <c r="H11" s="2">
@@ -2332,19 +2931,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22">
       <c r="A12" s="7"/>
       <c r="B12" s="2">
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G12" s="8"/>
       <c r="H12" s="2">
@@ -2378,19 +2977,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22">
       <c r="A13" s="7"/>
       <c r="B13" s="2">
         <v>1009</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="2">
@@ -2424,19 +3023,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22">
       <c r="A14" s="7"/>
       <c r="B14" s="2">
         <v>1010</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G14" s="8"/>
       <c r="H14" s="2">
@@ -2470,19 +3069,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22">
       <c r="A15" s="7"/>
       <c r="B15" s="2">
         <v>1011</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G15" s="8"/>
       <c r="H15" s="2">
@@ -2516,19 +3115,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22">
       <c r="A16" s="7"/>
       <c r="B16" s="2">
         <v>1012</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="2">
@@ -2562,19 +3161,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22">
       <c r="A17" s="7"/>
       <c r="B17" s="2">
         <v>1013</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G17" s="8"/>
       <c r="H17" s="2">
@@ -2608,18 +3207,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:22">
       <c r="B18" s="2">
         <v>1014</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="2">
@@ -2653,24 +3252,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" s="1" customFormat="1" spans="2:22">
       <c r="B19" s="1">
         <v>2001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>284</v>
+        <v>104</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>290</v>
+      <c r="F19" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H19" s="1">
         <v>1</v>
@@ -2700,39 +3299,39 @@
         <v>1</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="V19" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:23">
       <c r="B20" s="2">
         <v>2002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E20" s="2">
         <v>2</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="21" t="s">
-        <v>290</v>
+        <v>112</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -2762,36 +3361,36 @@
         <v>1</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="V20" s="2">
         <v>1</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23">
       <c r="B21" s="2">
         <v>2003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>290</v>
+        <v>116</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -2821,36 +3420,36 @@
         <v>1</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="V21" s="2">
         <v>1</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" ht="14.5" customHeight="1" spans="2:23">
       <c r="B22" s="2">
         <v>2004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2">
         <v>2</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>290</v>
+        <v>121</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -2880,42 +3479,42 @@
         <v>1</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="V22" s="2">
         <v>1</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23">
       <c r="B23" s="2">
         <v>2005</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2">
         <v>2</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G23" s="21" t="s">
-        <v>290</v>
+        <v>127</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -2945,36 +3544,36 @@
         <v>1</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="V23" s="2">
         <v>1</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23">
       <c r="B24" s="2">
         <v>2006</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2">
         <v>2</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>290</v>
+        <v>132</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -3004,36 +3603,36 @@
         <v>1</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="V24" s="2">
         <v>1</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23">
       <c r="B25" s="2">
         <v>2007</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E25" s="2">
         <v>2</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="21" t="s">
-        <v>290</v>
+        <v>137</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -3063,36 +3662,36 @@
         <v>1</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="V25" s="2">
         <v>1</v>
       </c>
       <c r="W25" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23">
       <c r="B26" s="2">
         <v>2008</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E26" s="2">
         <v>2</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>290</v>
+        <v>139</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -3122,36 +3721,36 @@
         <v>1</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="V26" s="2">
         <v>1</v>
       </c>
       <c r="W26" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23">
       <c r="B27" s="2">
         <v>2009</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E27" s="2">
         <v>2</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G27" s="21" t="s">
-        <v>290</v>
+        <v>141</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -3181,36 +3780,36 @@
         <v>1</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="V27" s="2">
         <v>1</v>
       </c>
       <c r="W27" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23">
       <c r="B28" s="2">
         <v>2010</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E28" s="2">
         <v>2</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>290</v>
+        <v>143</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -3240,36 +3839,36 @@
         <v>1</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="V28" s="2">
         <v>1</v>
       </c>
       <c r="W28" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23">
       <c r="B29" s="2">
         <v>2011</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E29" s="2">
         <v>2</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="21" t="s">
-        <v>290</v>
+        <v>145</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -3299,36 +3898,36 @@
         <v>1</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="V29" s="2">
         <v>1</v>
       </c>
       <c r="W29" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23">
       <c r="B30" s="2">
         <v>2012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E30" s="2">
         <v>2</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>290</v>
+        <v>147</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -3358,36 +3957,36 @@
         <v>1</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="V30" s="2">
         <v>1</v>
       </c>
       <c r="W30" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23">
       <c r="B31" s="2">
         <v>2013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E31" s="2">
         <v>2</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G31" s="21" t="s">
-        <v>290</v>
+        <v>149</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -3417,36 +4016,36 @@
         <v>1</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="V31" s="2">
         <v>1</v>
       </c>
       <c r="W31" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23">
       <c r="B32" s="2">
         <v>2014</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E32" s="2">
         <v>2</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>290</v>
+        <v>149</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -3476,36 +4075,36 @@
         <v>1</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="V32" s="2">
         <v>1</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23">
       <c r="B33" s="2">
         <v>2015</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E33" s="2">
         <v>2</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>290</v>
+        <v>154</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -3535,42 +4134,42 @@
         <v>1</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="V33" s="2">
         <v>1</v>
       </c>
       <c r="W33" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23">
       <c r="B34" s="2">
         <v>2016</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E34" s="2">
         <v>2</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>290</v>
+        <v>159</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -3600,32 +4199,32 @@
         <v>1</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="V34" s="2">
         <v>1</v>
       </c>
       <c r="W34" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="2:23" s="1" customFormat="1" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="2:22">
       <c r="B35" s="1">
         <v>3001</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G35" s="9"/>
+      <c r="F35" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G35" s="10"/>
       <c r="H35" s="1">
         <v>4</v>
       </c>
@@ -3651,24 +4250,24 @@
         <v>1</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="V35" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:22">
       <c r="B36" s="2">
         <v>3002</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E36" s="2">
         <v>3</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="2">
@@ -3696,24 +4295,24 @@
         <v>1</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="V36" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:22">
       <c r="B37" s="2">
         <v>3003</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E37" s="2">
         <v>3</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="H37" s="2">
         <v>4</v>
@@ -3740,24 +4339,24 @@
         <v>1</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="V37" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:22">
       <c r="B38" s="2">
         <v>3004</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="E38" s="2">
         <v>3</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="H38" s="2">
         <v>4</v>
@@ -3784,24 +4383,24 @@
         <v>1</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="V38" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:22">
       <c r="B39" s="2">
         <v>3005</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="E39" s="2">
         <v>3</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="H39" s="2">
         <v>4</v>
@@ -3828,24 +4427,24 @@
         <v>1</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="V39" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:22">
       <c r="B40" s="2">
         <v>3006</v>
       </c>
-      <c r="C40" s="24" t="s">
-        <v>155</v>
+      <c r="C40" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="E40" s="2">
         <v>3</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H40" s="2">
         <v>4</v>
@@ -3872,24 +4471,24 @@
         <v>1</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="V40" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:22">
       <c r="B41" s="2">
         <v>3007</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="E41" s="2">
         <v>3</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H41" s="2">
         <v>4</v>
@@ -3916,24 +4515,24 @@
         <v>1</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="V41" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:22">
       <c r="B42" s="2">
         <v>3008</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E42" s="2">
         <v>3</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="H42" s="2">
         <v>4</v>
@@ -3960,24 +4559,24 @@
         <v>1</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="V42" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:22">
       <c r="B43" s="2">
         <v>3009</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="E43" s="2">
         <v>3</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="H43" s="2">
         <v>4</v>
@@ -4004,24 +4603,24 @@
         <v>1</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="V43" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:22">
       <c r="B44" s="2">
         <v>3010</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="E44" s="2">
         <v>3</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H44" s="2">
         <v>4</v>
@@ -4048,24 +4647,24 @@
         <v>1</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="V44" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:22">
       <c r="B45" s="2">
         <v>3011</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="E45" s="2">
         <v>3</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H45" s="2">
         <v>4</v>
@@ -4092,24 +4691,24 @@
         <v>1</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="V45" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:22">
       <c r="B46" s="2">
         <v>3012</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="E46" s="2">
         <v>3</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H46" s="2">
         <v>4</v>
@@ -4136,24 +4735,24 @@
         <v>1</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="V46" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:22">
       <c r="B47" s="2">
         <v>3013</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="E47" s="2">
         <v>3</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="2">
@@ -4181,24 +4780,24 @@
         <v>1</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="V47" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:22">
       <c r="B48" s="2">
         <v>3014</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="E48" s="2">
         <v>3</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="G48" s="8"/>
       <c r="H48" s="2">
@@ -4226,24 +4825,24 @@
         <v>1</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="V48" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:22">
       <c r="B49" s="2">
         <v>3015</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="E49" s="2">
         <v>3</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="H49" s="2">
         <v>4</v>
@@ -4270,26 +4869,26 @@
         <v>1</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="V49" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" s="1" customFormat="1" spans="2:22">
       <c r="B50" s="1">
         <v>4001</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E50" s="1">
         <v>4</v>
       </c>
-      <c r="F50" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="G50" s="9"/>
+      <c r="F50" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="G50" s="10"/>
       <c r="H50" s="1">
         <v>0.5</v>
       </c>
@@ -4315,24 +4914,24 @@
         <v>1</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="V50" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:22">
       <c r="B51" s="2">
         <v>4002</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="E51" s="2">
         <v>4</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="2">
@@ -4360,24 +4959,24 @@
         <v>1</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="V51" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:22">
       <c r="B52" s="2">
         <v>4003</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="E52" s="2">
         <v>4</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="H52" s="2">
         <v>0.5</v>
@@ -4404,24 +5003,24 @@
         <v>1</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="V52" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:22">
       <c r="B53" s="2">
         <v>4004</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="E53" s="2">
         <v>4</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="H53" s="2">
         <v>0.5</v>
@@ -4448,24 +5047,24 @@
         <v>1</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="V53" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:22">
       <c r="B54" s="2">
         <v>4005</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="E54" s="2">
         <v>4</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="H54" s="2">
         <v>0.5</v>
@@ -4492,24 +5091,24 @@
         <v>1</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V54" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:22">
       <c r="B55" s="2">
         <v>4006</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="E55" s="2">
         <v>4</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H55" s="2">
         <v>0.5</v>
@@ -4536,24 +5135,24 @@
         <v>1</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="V55" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:22">
       <c r="B56" s="2">
         <v>4007</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="E56" s="2">
         <v>4</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H56" s="2">
         <v>0.5</v>
@@ -4580,24 +5179,24 @@
         <v>1</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="V56" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:22">
       <c r="B57" s="2">
         <v>4008</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="E57" s="2">
         <v>4</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="H57" s="2">
         <v>0.5</v>
@@ -4624,24 +5223,24 @@
         <v>1</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="V57" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:22">
       <c r="B58" s="2">
         <v>4009</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="E58" s="2">
         <v>4</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="H58" s="2">
         <v>0.5</v>
@@ -4668,24 +5267,24 @@
         <v>1</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="V58" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:22">
       <c r="B59" s="2">
         <v>4010</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="E59" s="2">
         <v>4</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H59" s="2">
         <v>0.5</v>
@@ -4712,24 +5311,24 @@
         <v>1</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="V59" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:22">
       <c r="B60" s="2">
         <v>4011</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="E60" s="2">
         <v>4</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H60" s="2">
         <v>0.5</v>
@@ -4756,24 +5355,24 @@
         <v>1</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="V60" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:22">
       <c r="B61" s="2">
         <v>4012</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="E61" s="2">
         <v>4</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="H61" s="2">
         <v>0.5</v>
@@ -4800,24 +5399,24 @@
         <v>1</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="V61" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:22">
       <c r="B62" s="2">
         <v>4013</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="E62" s="2">
         <v>4</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="G62" s="8"/>
       <c r="H62" s="2">
@@ -4845,24 +5444,24 @@
         <v>1</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V62" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:22">
       <c r="B63" s="2">
         <v>4014</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="E63" s="2">
         <v>4</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="2">
@@ -4890,24 +5489,24 @@
         <v>1</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="V63" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="2:22" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:22">
       <c r="B64" s="2">
         <v>4015</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="E64" s="2">
         <v>4</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="H64" s="2">
         <v>0.5</v>
@@ -4934,26 +5533,26 @@
         <v>1</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V64" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" s="1" customFormat="1" spans="2:23">
       <c r="B65" s="1">
         <v>5001</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="E65" s="1">
         <v>5</v>
       </c>
-      <c r="F65" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="G65" s="11"/>
+      <c r="F65" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G65" s="15"/>
       <c r="H65" s="1">
         <v>1</v>
       </c>
@@ -4979,30 +5578,30 @@
         <v>1</v>
       </c>
       <c r="S65" s="1" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="V65" s="2">
         <v>1</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28">
       <c r="B66" s="2">
         <v>5002</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="E66" s="2">
         <v>5</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="H66" s="2">
         <v>1</v>
@@ -5029,7 +5628,7 @@
         <v>0</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V66" s="2">
         <v>0</v>
@@ -5040,26 +5639,26 @@
       <c r="AA66" s="2"/>
       <c r="AB66" s="2"/>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:23">
       <c r="A67" s="7"/>
       <c r="B67" s="2">
         <v>5003</v>
       </c>
       <c r="C67" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="D67" s="7"/>
       <c r="E67" s="2">
         <v>5</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7">
         <v>1</v>
       </c>
-      <c r="I67" s="12"/>
+      <c r="I67" s="19"/>
       <c r="J67" s="2">
         <v>0</v>
       </c>
@@ -5091,26 +5690,26 @@
       </c>
       <c r="W67" s="7"/>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:23">
       <c r="A68" s="7"/>
       <c r="B68" s="2">
         <v>5004</v>
       </c>
       <c r="C68" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="2">
         <v>5</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7">
         <v>1</v>
       </c>
-      <c r="I68" s="12"/>
+      <c r="I68" s="19"/>
       <c r="J68" s="2">
         <v>0</v>
       </c>
@@ -5142,26 +5741,26 @@
       </c>
       <c r="W68" s="7"/>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:23">
       <c r="A69" s="7"/>
       <c r="B69" s="2">
         <v>5005</v>
       </c>
       <c r="C69" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="D69" s="7"/>
       <c r="E69" s="2">
         <v>5</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7">
         <v>1</v>
       </c>
-      <c r="I69" s="12"/>
+      <c r="I69" s="19"/>
       <c r="J69" s="2">
         <v>0</v>
       </c>
@@ -5193,26 +5792,26 @@
       </c>
       <c r="W69" s="7"/>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:23">
       <c r="A70" s="7"/>
       <c r="B70" s="2">
         <v>5006</v>
       </c>
       <c r="C70" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="D70" s="7"/>
       <c r="E70" s="2">
         <v>5</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7">
         <v>1</v>
       </c>
-      <c r="I70" s="12"/>
+      <c r="I70" s="19"/>
       <c r="J70" s="2">
         <v>0</v>
       </c>
@@ -5244,26 +5843,26 @@
       </c>
       <c r="W70" s="7"/>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:23">
       <c r="A71" s="7"/>
       <c r="B71" s="2">
         <v>5007</v>
       </c>
       <c r="C71" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="D71" s="7"/>
       <c r="E71" s="2">
         <v>5</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7">
         <v>1</v>
       </c>
-      <c r="I71" s="12"/>
+      <c r="I71" s="19"/>
       <c r="J71" s="2">
         <v>0</v>
       </c>
@@ -5295,26 +5894,26 @@
       </c>
       <c r="W71" s="7"/>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:23">
       <c r="A72" s="7"/>
       <c r="B72" s="2">
         <v>5008</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="D72" s="7"/>
       <c r="E72" s="2">
         <v>5</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7">
         <v>1</v>
       </c>
-      <c r="I72" s="12"/>
+      <c r="I72" s="19"/>
       <c r="J72" s="2">
         <v>0</v>
       </c>
@@ -5346,24 +5945,24 @@
       </c>
       <c r="W72" s="7"/>
     </row>
-    <row r="73" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="20">
+    <row r="73" s="1" customFormat="1" spans="2:22">
+      <c r="B73" s="9">
         <v>5009</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>298</v>
+        <v>233</v>
       </c>
       <c r="E73" s="1">
         <v>5</v>
       </c>
-      <c r="F73" s="25" t="s">
-        <v>281</v>
-      </c>
-      <c r="G73" s="25"/>
-      <c r="H73" s="13">
-        <v>1</v>
-      </c>
-      <c r="I73" s="14"/>
+      <c r="F73" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="G73" s="16"/>
+      <c r="H73" s="17">
+        <v>1</v>
+      </c>
+      <c r="I73" s="20"/>
       <c r="J73" s="1">
         <v>0</v>
       </c>
@@ -5386,30 +5985,30 @@
         <v>1</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V73" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B74" s="21">
+    <row r="74" spans="2:28">
+      <c r="B74" s="11">
         <v>5010</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>299</v>
+        <v>234</v>
       </c>
       <c r="E74" s="2">
         <v>5</v>
       </c>
-      <c r="F74" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G74" s="19"/>
+      <c r="F74" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G74" s="18"/>
       <c r="H74" s="7">
         <v>1</v>
       </c>
-      <c r="I74" s="12"/>
+      <c r="I74" s="19"/>
       <c r="J74" s="2">
         <v>0</v>
       </c>
@@ -5432,7 +6031,7 @@
         <v>1</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V74" s="2">
         <v>1</v>
@@ -5443,24 +6042,24 @@
       <c r="AA74" s="2"/>
       <c r="AB74" s="2"/>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B75" s="21">
+    <row r="75" spans="2:28">
+      <c r="B75" s="11">
         <v>5011</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="E75" s="2">
         <v>5</v>
       </c>
-      <c r="F75" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G75" s="19"/>
+      <c r="F75" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G75" s="18"/>
       <c r="H75" s="7">
         <v>1</v>
       </c>
-      <c r="I75" s="12"/>
+      <c r="I75" s="19"/>
       <c r="J75" s="2">
         <v>0</v>
       </c>
@@ -5483,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V75" s="2">
         <v>1</v>
@@ -5494,24 +6093,24 @@
       <c r="AA75" s="2"/>
       <c r="AB75" s="2"/>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B76" s="21">
+    <row r="76" spans="2:28">
+      <c r="B76" s="11">
         <v>5012</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>301</v>
+        <v>236</v>
       </c>
       <c r="E76" s="2">
         <v>5</v>
       </c>
-      <c r="F76" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G76" s="19"/>
+      <c r="F76" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G76" s="18"/>
       <c r="H76" s="7">
         <v>1</v>
       </c>
-      <c r="I76" s="12"/>
+      <c r="I76" s="19"/>
       <c r="J76" s="2">
         <v>0</v>
       </c>
@@ -5534,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V76" s="2">
         <v>1</v>
@@ -5545,24 +6144,24 @@
       <c r="AA76" s="2"/>
       <c r="AB76" s="2"/>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B77" s="21">
+    <row r="77" spans="2:28">
+      <c r="B77" s="11">
         <v>5013</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>302</v>
+        <v>237</v>
       </c>
       <c r="E77" s="2">
         <v>5</v>
       </c>
-      <c r="F77" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G77" s="19"/>
+      <c r="F77" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G77" s="18"/>
       <c r="H77" s="7">
         <v>1</v>
       </c>
-      <c r="I77" s="12"/>
+      <c r="I77" s="19"/>
       <c r="J77" s="2">
         <v>0</v>
       </c>
@@ -5585,7 +6184,7 @@
         <v>1</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V77" s="2">
         <v>1</v>
@@ -5596,24 +6195,24 @@
       <c r="AA77" s="2"/>
       <c r="AB77" s="2"/>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B78" s="21">
+    <row r="78" spans="2:28">
+      <c r="B78" s="11">
         <v>5014</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>303</v>
+        <v>238</v>
       </c>
       <c r="E78" s="2">
         <v>5</v>
       </c>
-      <c r="F78" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G78" s="19"/>
+      <c r="F78" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G78" s="18"/>
       <c r="H78" s="7">
         <v>1</v>
       </c>
-      <c r="I78" s="12"/>
+      <c r="I78" s="19"/>
       <c r="J78" s="2">
         <v>0</v>
       </c>
@@ -5636,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V78" s="2">
         <v>1</v>
@@ -5647,24 +6246,24 @@
       <c r="AA78" s="2"/>
       <c r="AB78" s="2"/>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B79" s="21">
+    <row r="79" spans="2:28">
+      <c r="B79" s="11">
         <v>5015</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>304</v>
+        <v>239</v>
       </c>
       <c r="E79" s="2">
         <v>5</v>
       </c>
-      <c r="F79" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G79" s="19"/>
+      <c r="F79" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G79" s="18"/>
       <c r="H79" s="7">
         <v>1</v>
       </c>
-      <c r="I79" s="12"/>
+      <c r="I79" s="19"/>
       <c r="J79" s="2">
         <v>0</v>
       </c>
@@ -5687,7 +6286,7 @@
         <v>1</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V79" s="2">
         <v>1</v>
@@ -5698,24 +6297,24 @@
       <c r="AA79" s="2"/>
       <c r="AB79" s="2"/>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B80" s="21">
+    <row r="80" spans="2:28">
+      <c r="B80" s="11">
         <v>5016</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>305</v>
+        <v>240</v>
       </c>
       <c r="E80" s="2">
         <v>5</v>
       </c>
-      <c r="F80" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G80" s="19"/>
+      <c r="F80" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G80" s="18"/>
       <c r="H80" s="7">
         <v>1</v>
       </c>
-      <c r="I80" s="12"/>
+      <c r="I80" s="19"/>
       <c r="J80" s="2">
         <v>0</v>
       </c>
@@ -5738,7 +6337,7 @@
         <v>1</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V80" s="2">
         <v>1</v>
@@ -5749,24 +6348,24 @@
       <c r="AA80" s="2"/>
       <c r="AB80" s="2"/>
     </row>
-    <row r="81" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B81" s="21">
+    <row r="81" spans="2:28">
+      <c r="B81" s="11">
         <v>5017</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="E81" s="2">
         <v>5</v>
       </c>
-      <c r="F81" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G81" s="19"/>
+      <c r="F81" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G81" s="18"/>
       <c r="H81" s="7">
         <v>1</v>
       </c>
-      <c r="I81" s="12"/>
+      <c r="I81" s="19"/>
       <c r="J81" s="2">
         <v>0</v>
       </c>
@@ -5789,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V81" s="2">
         <v>1</v>
@@ -5800,24 +6399,24 @@
       <c r="AA81" s="2"/>
       <c r="AB81" s="2"/>
     </row>
-    <row r="82" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B82" s="21">
+    <row r="82" spans="2:28">
+      <c r="B82" s="11">
         <v>5018</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="E82" s="2">
         <v>5</v>
       </c>
-      <c r="F82" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G82" s="19"/>
+      <c r="F82" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G82" s="18"/>
       <c r="H82" s="7">
         <v>1</v>
       </c>
-      <c r="I82" s="12"/>
+      <c r="I82" s="19"/>
       <c r="J82" s="2">
         <v>0</v>
       </c>
@@ -5840,7 +6439,7 @@
         <v>1</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V82" s="2">
         <v>1</v>
@@ -5851,24 +6450,24 @@
       <c r="AA82" s="2"/>
       <c r="AB82" s="2"/>
     </row>
-    <row r="83" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B83" s="21">
+    <row r="83" spans="2:28">
+      <c r="B83" s="11">
         <v>5019</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="E83" s="2">
         <v>5</v>
       </c>
-      <c r="F83" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G83" s="19"/>
+      <c r="F83" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G83" s="18"/>
       <c r="H83" s="7">
         <v>1</v>
       </c>
-      <c r="I83" s="12"/>
+      <c r="I83" s="19"/>
       <c r="J83" s="2">
         <v>0</v>
       </c>
@@ -5891,7 +6490,7 @@
         <v>1</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V83" s="2">
         <v>1</v>
@@ -5902,24 +6501,24 @@
       <c r="AA83" s="2"/>
       <c r="AB83" s="2"/>
     </row>
-    <row r="84" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B84" s="21">
+    <row r="84" spans="2:28">
+      <c r="B84" s="11">
         <v>5020</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="E84" s="2">
         <v>5</v>
       </c>
-      <c r="F84" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G84" s="19"/>
+      <c r="F84" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G84" s="18"/>
       <c r="H84" s="7">
         <v>1</v>
       </c>
-      <c r="I84" s="12"/>
+      <c r="I84" s="19"/>
       <c r="J84" s="2">
         <v>0</v>
       </c>
@@ -5942,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V84" s="2">
         <v>1</v>
@@ -5953,24 +6552,24 @@
       <c r="AA84" s="2"/>
       <c r="AB84" s="2"/>
     </row>
-    <row r="85" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B85" s="21">
+    <row r="85" spans="2:28">
+      <c r="B85" s="11">
         <v>5021</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="E85" s="2">
         <v>5</v>
       </c>
-      <c r="F85" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G85" s="19"/>
+      <c r="F85" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G85" s="18"/>
       <c r="H85" s="7">
         <v>1</v>
       </c>
-      <c r="I85" s="12"/>
+      <c r="I85" s="19"/>
       <c r="J85" s="2">
         <v>0</v>
       </c>
@@ -5993,7 +6592,7 @@
         <v>1</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V85" s="2">
         <v>1</v>
@@ -6004,24 +6603,24 @@
       <c r="AA85" s="2"/>
       <c r="AB85" s="2"/>
     </row>
-    <row r="86" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B86" s="21">
+    <row r="86" spans="2:28">
+      <c r="B86" s="11">
         <v>5022</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="E86" s="2">
         <v>5</v>
       </c>
-      <c r="F86" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G86" s="19"/>
+      <c r="F86" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G86" s="18"/>
       <c r="H86" s="7">
         <v>1</v>
       </c>
-      <c r="I86" s="12"/>
+      <c r="I86" s="19"/>
       <c r="J86" s="2">
         <v>0</v>
       </c>
@@ -6044,7 +6643,7 @@
         <v>1</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V86" s="2">
         <v>1</v>
@@ -6055,24 +6654,24 @@
       <c r="AA86" s="2"/>
       <c r="AB86" s="2"/>
     </row>
-    <row r="87" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B87" s="21">
+    <row r="87" spans="2:28">
+      <c r="B87" s="11">
         <v>5023</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="E87" s="2">
         <v>5</v>
       </c>
-      <c r="F87" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G87" s="19"/>
+      <c r="F87" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G87" s="18"/>
       <c r="H87" s="7">
         <v>1</v>
       </c>
-      <c r="I87" s="12"/>
+      <c r="I87" s="19"/>
       <c r="J87" s="2">
         <v>0</v>
       </c>
@@ -6095,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V87" s="2">
         <v>1</v>
@@ -6106,24 +6705,24 @@
       <c r="AA87" s="2"/>
       <c r="AB87" s="2"/>
     </row>
-    <row r="88" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B88" s="21">
+    <row r="88" spans="2:28">
+      <c r="B88" s="11">
         <v>5024</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>313</v>
+        <v>248</v>
       </c>
       <c r="E88" s="2">
         <v>5</v>
       </c>
-      <c r="F88" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G88" s="19"/>
+      <c r="F88" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G88" s="18"/>
       <c r="H88" s="7">
         <v>1</v>
       </c>
-      <c r="I88" s="12"/>
+      <c r="I88" s="19"/>
       <c r="J88" s="2">
         <v>0</v>
       </c>
@@ -6146,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V88" s="2">
         <v>1</v>
@@ -6157,24 +6756,24 @@
       <c r="AA88" s="2"/>
       <c r="AB88" s="2"/>
     </row>
-    <row r="89" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B89" s="21">
+    <row r="89" spans="2:28">
+      <c r="B89" s="11">
         <v>5025</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="E89" s="2">
         <v>5</v>
       </c>
-      <c r="F89" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G89" s="19"/>
+      <c r="F89" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G89" s="18"/>
       <c r="H89" s="7">
         <v>1</v>
       </c>
-      <c r="I89" s="12"/>
+      <c r="I89" s="19"/>
       <c r="J89" s="2">
         <v>0</v>
       </c>
@@ -6197,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V89" s="2">
         <v>1</v>
@@ -6208,24 +6807,24 @@
       <c r="AA89" s="2"/>
       <c r="AB89" s="2"/>
     </row>
-    <row r="90" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B90" s="21">
+    <row r="90" spans="2:28">
+      <c r="B90" s="11">
         <v>5026</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>315</v>
+        <v>250</v>
       </c>
       <c r="E90" s="2">
         <v>5</v>
       </c>
-      <c r="F90" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G90" s="19"/>
+      <c r="F90" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G90" s="18"/>
       <c r="H90" s="7">
         <v>1</v>
       </c>
-      <c r="I90" s="12"/>
+      <c r="I90" s="19"/>
       <c r="J90" s="2">
         <v>0</v>
       </c>
@@ -6248,7 +6847,7 @@
         <v>1</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V90" s="2">
         <v>1</v>
@@ -6259,24 +6858,24 @@
       <c r="AA90" s="2"/>
       <c r="AB90" s="2"/>
     </row>
-    <row r="91" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B91" s="21">
+    <row r="91" spans="2:28">
+      <c r="B91" s="11">
         <v>5027</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>316</v>
+        <v>251</v>
       </c>
       <c r="E91" s="2">
         <v>5</v>
       </c>
-      <c r="F91" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G91" s="19"/>
+      <c r="F91" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G91" s="18"/>
       <c r="H91" s="7">
         <v>1</v>
       </c>
-      <c r="I91" s="12"/>
+      <c r="I91" s="19"/>
       <c r="J91" s="2">
         <v>0</v>
       </c>
@@ -6299,7 +6898,7 @@
         <v>1</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V91" s="2">
         <v>1</v>
@@ -6310,24 +6909,24 @@
       <c r="AA91" s="2"/>
       <c r="AB91" s="2"/>
     </row>
-    <row r="92" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B92" s="21">
+    <row r="92" spans="2:28">
+      <c r="B92" s="11">
         <v>5028</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>317</v>
+        <v>252</v>
       </c>
       <c r="E92" s="2">
         <v>5</v>
       </c>
-      <c r="F92" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G92" s="19"/>
+      <c r="F92" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G92" s="18"/>
       <c r="H92" s="7">
         <v>1</v>
       </c>
-      <c r="I92" s="12"/>
+      <c r="I92" s="19"/>
       <c r="J92" s="2">
         <v>0</v>
       </c>
@@ -6350,7 +6949,7 @@
         <v>1</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V92" s="2">
         <v>1</v>
@@ -6361,24 +6960,24 @@
       <c r="AA92" s="2"/>
       <c r="AB92" s="2"/>
     </row>
-    <row r="93" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B93" s="21">
+    <row r="93" spans="2:28">
+      <c r="B93" s="11">
         <v>5029</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>318</v>
+        <v>253</v>
       </c>
       <c r="E93" s="2">
         <v>5</v>
       </c>
-      <c r="F93" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G93" s="19"/>
+      <c r="F93" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G93" s="18"/>
       <c r="H93" s="7">
         <v>1</v>
       </c>
-      <c r="I93" s="12"/>
+      <c r="I93" s="19"/>
       <c r="J93" s="2">
         <v>0</v>
       </c>
@@ -6401,7 +7000,7 @@
         <v>1</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V93" s="2">
         <v>1</v>
@@ -6412,24 +7011,24 @@
       <c r="AA93" s="2"/>
       <c r="AB93" s="2"/>
     </row>
-    <row r="94" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B94" s="21">
+    <row r="94" spans="2:28">
+      <c r="B94" s="11">
         <v>5030</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>319</v>
+        <v>254</v>
       </c>
       <c r="E94" s="2">
         <v>5</v>
       </c>
-      <c r="F94" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G94" s="19"/>
+      <c r="F94" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G94" s="18"/>
       <c r="H94" s="7">
         <v>1</v>
       </c>
-      <c r="I94" s="12"/>
+      <c r="I94" s="19"/>
       <c r="J94" s="2">
         <v>0</v>
       </c>
@@ -6452,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V94" s="2">
         <v>1</v>
@@ -6463,24 +7062,24 @@
       <c r="AA94" s="2"/>
       <c r="AB94" s="2"/>
     </row>
-    <row r="95" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B95" s="21">
+    <row r="95" spans="2:28">
+      <c r="B95" s="11">
         <v>5031</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>320</v>
+        <v>255</v>
       </c>
       <c r="E95" s="2">
         <v>5</v>
       </c>
-      <c r="F95" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G95" s="19"/>
+      <c r="F95" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G95" s="18"/>
       <c r="H95" s="7">
         <v>1</v>
       </c>
-      <c r="I95" s="12"/>
+      <c r="I95" s="19"/>
       <c r="J95" s="2">
         <v>0</v>
       </c>
@@ -6503,7 +7102,7 @@
         <v>1</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V95" s="2">
         <v>1</v>
@@ -6514,24 +7113,24 @@
       <c r="AA95" s="2"/>
       <c r="AB95" s="2"/>
     </row>
-    <row r="96" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B96" s="21">
+    <row r="96" spans="2:28">
+      <c r="B96" s="11">
         <v>5032</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="E96" s="2">
         <v>5</v>
       </c>
-      <c r="F96" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G96" s="19"/>
+      <c r="F96" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G96" s="18"/>
       <c r="H96" s="7">
         <v>1</v>
       </c>
-      <c r="I96" s="12"/>
+      <c r="I96" s="19"/>
       <c r="J96" s="2">
         <v>0</v>
       </c>
@@ -6554,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V96" s="2">
         <v>1</v>
@@ -6565,24 +7164,24 @@
       <c r="AA96" s="2"/>
       <c r="AB96" s="2"/>
     </row>
-    <row r="97" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B97" s="21">
+    <row r="97" spans="2:28">
+      <c r="B97" s="11">
         <v>5033</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>322</v>
+        <v>257</v>
       </c>
       <c r="E97" s="2">
         <v>5</v>
       </c>
-      <c r="F97" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G97" s="19"/>
+      <c r="F97" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G97" s="18"/>
       <c r="H97" s="7">
         <v>1</v>
       </c>
-      <c r="I97" s="12"/>
+      <c r="I97" s="19"/>
       <c r="J97" s="2">
         <v>0</v>
       </c>
@@ -6605,7 +7204,7 @@
         <v>1</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V97" s="2">
         <v>1</v>
@@ -6616,24 +7215,24 @@
       <c r="AA97" s="2"/>
       <c r="AB97" s="2"/>
     </row>
-    <row r="98" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B98" s="21">
+    <row r="98" spans="2:28">
+      <c r="B98" s="11">
         <v>5034</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>323</v>
+        <v>258</v>
       </c>
       <c r="E98" s="2">
         <v>5</v>
       </c>
-      <c r="F98" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G98" s="19"/>
+      <c r="F98" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G98" s="18"/>
       <c r="H98" s="7">
         <v>1</v>
       </c>
-      <c r="I98" s="12"/>
+      <c r="I98" s="19"/>
       <c r="J98" s="2">
         <v>0</v>
       </c>
@@ -6656,7 +7255,7 @@
         <v>1</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V98" s="2">
         <v>1</v>
@@ -6667,24 +7266,24 @@
       <c r="AA98" s="2"/>
       <c r="AB98" s="2"/>
     </row>
-    <row r="99" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B99" s="21">
+    <row r="99" spans="2:28">
+      <c r="B99" s="11">
         <v>5035</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="E99" s="2">
         <v>5</v>
       </c>
-      <c r="F99" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G99" s="19"/>
+      <c r="F99" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G99" s="18"/>
       <c r="H99" s="7">
         <v>1</v>
       </c>
-      <c r="I99" s="12"/>
+      <c r="I99" s="19"/>
       <c r="J99" s="2">
         <v>0</v>
       </c>
@@ -6707,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V99" s="2">
         <v>1</v>
@@ -6718,24 +7317,24 @@
       <c r="AA99" s="2"/>
       <c r="AB99" s="2"/>
     </row>
-    <row r="100" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B100" s="21">
+    <row r="100" spans="2:28">
+      <c r="B100" s="11">
         <v>5036</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>325</v>
+        <v>260</v>
       </c>
       <c r="E100" s="2">
         <v>5</v>
       </c>
-      <c r="F100" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G100" s="19"/>
+      <c r="F100" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G100" s="18"/>
       <c r="H100" s="7">
         <v>1</v>
       </c>
-      <c r="I100" s="12"/>
+      <c r="I100" s="19"/>
       <c r="J100" s="2">
         <v>0</v>
       </c>
@@ -6758,7 +7357,7 @@
         <v>1</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V100" s="2">
         <v>1</v>
@@ -6769,24 +7368,24 @@
       <c r="AA100" s="2"/>
       <c r="AB100" s="2"/>
     </row>
-    <row r="101" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B101" s="21">
+    <row r="101" spans="2:28">
+      <c r="B101" s="11">
         <v>5037</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>326</v>
+        <v>261</v>
       </c>
       <c r="E101" s="2">
         <v>5</v>
       </c>
-      <c r="F101" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G101" s="19"/>
+      <c r="F101" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G101" s="18"/>
       <c r="H101" s="7">
         <v>1</v>
       </c>
-      <c r="I101" s="12"/>
+      <c r="I101" s="19"/>
       <c r="J101" s="2">
         <v>0</v>
       </c>
@@ -6809,7 +7408,7 @@
         <v>1</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V101" s="2">
         <v>1</v>
@@ -6820,24 +7419,24 @@
       <c r="AA101" s="2"/>
       <c r="AB101" s="2"/>
     </row>
-    <row r="102" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B102" s="21">
+    <row r="102" spans="2:28">
+      <c r="B102" s="11">
         <v>5038</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>327</v>
+        <v>262</v>
       </c>
       <c r="E102" s="2">
         <v>5</v>
       </c>
-      <c r="F102" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G102" s="19"/>
+      <c r="F102" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G102" s="18"/>
       <c r="H102" s="7">
         <v>1</v>
       </c>
-      <c r="I102" s="12"/>
+      <c r="I102" s="19"/>
       <c r="J102" s="2">
         <v>0</v>
       </c>
@@ -6860,7 +7459,7 @@
         <v>1</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V102" s="2">
         <v>1</v>
@@ -6871,24 +7470,24 @@
       <c r="AA102" s="2"/>
       <c r="AB102" s="2"/>
     </row>
-    <row r="103" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B103" s="21">
+    <row r="103" spans="2:28">
+      <c r="B103" s="11">
         <v>5039</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>328</v>
+        <v>263</v>
       </c>
       <c r="E103" s="2">
         <v>5</v>
       </c>
-      <c r="F103" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G103" s="19"/>
+      <c r="F103" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G103" s="18"/>
       <c r="H103" s="7">
         <v>1</v>
       </c>
-      <c r="I103" s="12"/>
+      <c r="I103" s="19"/>
       <c r="J103" s="2">
         <v>0</v>
       </c>
@@ -6911,7 +7510,7 @@
         <v>1</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V103" s="2">
         <v>1</v>
@@ -6922,24 +7521,24 @@
       <c r="AA103" s="2"/>
       <c r="AB103" s="2"/>
     </row>
-    <row r="104" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B104" s="21">
+    <row r="104" spans="2:28">
+      <c r="B104" s="11">
         <v>5040</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>329</v>
+        <v>264</v>
       </c>
       <c r="E104" s="2">
         <v>5</v>
       </c>
-      <c r="F104" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G104" s="19"/>
+      <c r="F104" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G104" s="18"/>
       <c r="H104" s="7">
         <v>1</v>
       </c>
-      <c r="I104" s="12"/>
+      <c r="I104" s="19"/>
       <c r="J104" s="2">
         <v>0</v>
       </c>
@@ -6962,7 +7561,7 @@
         <v>1</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V104" s="2">
         <v>1</v>
@@ -6973,24 +7572,24 @@
       <c r="AA104" s="2"/>
       <c r="AB104" s="2"/>
     </row>
-    <row r="105" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B105" s="21">
+    <row r="105" spans="2:28">
+      <c r="B105" s="11">
         <v>5041</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>330</v>
+        <v>265</v>
       </c>
       <c r="E105" s="2">
         <v>5</v>
       </c>
-      <c r="F105" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G105" s="19"/>
+      <c r="F105" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G105" s="18"/>
       <c r="H105" s="7">
         <v>1</v>
       </c>
-      <c r="I105" s="12"/>
+      <c r="I105" s="19"/>
       <c r="J105" s="2">
         <v>0</v>
       </c>
@@ -7013,7 +7612,7 @@
         <v>1</v>
       </c>
       <c r="S105" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V105" s="2">
         <v>1</v>
@@ -7024,24 +7623,24 @@
       <c r="AA105" s="2"/>
       <c r="AB105" s="2"/>
     </row>
-    <row r="106" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B106" s="21">
+    <row r="106" spans="2:28">
+      <c r="B106" s="11">
         <v>5042</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>331</v>
+        <v>266</v>
       </c>
       <c r="E106" s="2">
         <v>5</v>
       </c>
-      <c r="F106" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G106" s="19"/>
+      <c r="F106" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G106" s="18"/>
       <c r="H106" s="7">
         <v>1</v>
       </c>
-      <c r="I106" s="12"/>
+      <c r="I106" s="19"/>
       <c r="J106" s="2">
         <v>0</v>
       </c>
@@ -7064,7 +7663,7 @@
         <v>1</v>
       </c>
       <c r="S106" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V106" s="2">
         <v>1</v>
@@ -7075,24 +7674,24 @@
       <c r="AA106" s="2"/>
       <c r="AB106" s="2"/>
     </row>
-    <row r="107" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B107" s="21">
+    <row r="107" spans="2:28">
+      <c r="B107" s="11">
         <v>5043</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>332</v>
+        <v>267</v>
       </c>
       <c r="E107" s="2">
         <v>5</v>
       </c>
-      <c r="F107" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G107" s="19"/>
+      <c r="F107" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G107" s="18"/>
       <c r="H107" s="7">
         <v>1</v>
       </c>
-      <c r="I107" s="12"/>
+      <c r="I107" s="19"/>
       <c r="J107" s="2">
         <v>0</v>
       </c>
@@ -7115,7 +7714,7 @@
         <v>1</v>
       </c>
       <c r="S107" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V107" s="2">
         <v>1</v>
@@ -7126,24 +7725,24 @@
       <c r="AA107" s="2"/>
       <c r="AB107" s="2"/>
     </row>
-    <row r="108" spans="2:28" x14ac:dyDescent="0.3">
-      <c r="B108" s="21">
+    <row r="108" spans="2:28">
+      <c r="B108" s="11">
         <v>5044</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>333</v>
+        <v>268</v>
       </c>
       <c r="E108" s="2">
         <v>5</v>
       </c>
-      <c r="F108" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="G108" s="19"/>
+      <c r="F108" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G108" s="18"/>
       <c r="H108" s="7">
         <v>1</v>
       </c>
-      <c r="I108" s="12"/>
+      <c r="I108" s="19"/>
       <c r="J108" s="2">
         <v>0</v>
       </c>
@@ -7166,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="V108" s="2">
         <v>1</v>
@@ -7177,23 +7776,23 @@
       <c r="AA108" s="2"/>
       <c r="AB108" s="2"/>
     </row>
-    <row r="109" spans="2:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" s="1" customFormat="1" spans="2:22">
       <c r="B109" s="1">
         <v>6001</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="E109" s="1">
         <v>6</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="H109" s="13">
-        <v>1</v>
-      </c>
-      <c r="I109" s="14"/>
+        <v>270</v>
+      </c>
+      <c r="H109" s="17">
+        <v>1</v>
+      </c>
+      <c r="I109" s="20"/>
       <c r="J109" s="1">
         <v>0</v>
       </c>
@@ -7216,29 +7815,29 @@
         <v>1</v>
       </c>
       <c r="S109" s="1" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="V109" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:28" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:22">
       <c r="B110" s="2">
         <v>6002</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="E110" s="2">
         <v>6</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="H110" s="7">
         <v>1</v>
       </c>
-      <c r="I110" s="12"/>
+      <c r="I110" s="19"/>
       <c r="J110" s="2">
         <v>0</v>
       </c>
@@ -7261,29 +7860,29 @@
         <v>1</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="V110" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:28" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:22">
       <c r="B111" s="2">
         <v>6003</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="E111" s="2">
         <v>6</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="H111" s="7">
         <v>1</v>
       </c>
-      <c r="I111" s="12"/>
+      <c r="I111" s="19"/>
       <c r="J111" s="2">
         <v>0</v>
       </c>
@@ -7306,29 +7905,29 @@
         <v>1</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="V111" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:28" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:22">
       <c r="B112" s="2">
         <v>6004</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>212</v>
+        <v>274</v>
       </c>
       <c r="E112" s="2">
         <v>6</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="H112" s="7">
         <v>1</v>
       </c>
-      <c r="I112" s="12"/>
+      <c r="I112" s="19"/>
       <c r="J112" s="2">
         <v>0</v>
       </c>
@@ -7351,29 +7950,29 @@
         <v>1</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="V112" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:22">
       <c r="B113" s="2">
         <v>6005</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="E113" s="2">
         <v>6</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
       <c r="H113" s="7">
         <v>1</v>
       </c>
-      <c r="I113" s="12"/>
+      <c r="I113" s="19"/>
       <c r="J113" s="2">
         <v>0</v>
       </c>
@@ -7396,29 +7995,29 @@
         <v>1</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="V113" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:22">
       <c r="B114" s="2">
         <v>6006</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="E114" s="2">
         <v>6</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="H114" s="7">
         <v>1</v>
       </c>
-      <c r="I114" s="12"/>
+      <c r="I114" s="19"/>
       <c r="J114" s="2">
         <v>0</v>
       </c>
@@ -7441,29 +8040,29 @@
         <v>1</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="V114" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:22">
       <c r="B115" s="2">
         <v>6007</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="E115" s="2">
         <v>6</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="H115" s="7">
         <v>1</v>
       </c>
-      <c r="I115" s="12"/>
+      <c r="I115" s="19"/>
       <c r="J115" s="2">
         <v>0</v>
       </c>
@@ -7486,29 +8085,29 @@
         <v>1</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="V115" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:22">
       <c r="B116" s="2">
         <v>6008</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="E116" s="2">
         <v>6</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="H116" s="7">
         <v>1</v>
       </c>
-      <c r="I116" s="12"/>
+      <c r="I116" s="19"/>
       <c r="J116" s="2">
         <v>0</v>
       </c>
@@ -7531,29 +8130,29 @@
         <v>1</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="V116" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:22">
       <c r="B117" s="2">
         <v>6009</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="E117" s="2">
         <v>6</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>222</v>
+        <v>284</v>
       </c>
       <c r="H117" s="7">
         <v>1</v>
       </c>
-      <c r="I117" s="12"/>
+      <c r="I117" s="19"/>
       <c r="J117" s="2">
         <v>0</v>
       </c>
@@ -7576,29 +8175,29 @@
         <v>1</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="V117" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:22">
       <c r="B118" s="2">
         <v>6010</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="E118" s="2">
         <v>6</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="H118" s="7">
         <v>1</v>
       </c>
-      <c r="I118" s="12"/>
+      <c r="I118" s="19"/>
       <c r="J118" s="2">
         <v>0</v>
       </c>
@@ -7621,29 +8220,29 @@
         <v>1</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="V118" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:22">
       <c r="B119" s="2">
         <v>6011</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="E119" s="2">
         <v>6</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="H119" s="7">
         <v>1</v>
       </c>
-      <c r="I119" s="12"/>
+      <c r="I119" s="19"/>
       <c r="J119" s="2">
         <v>0</v>
       </c>
@@ -7666,29 +8265,29 @@
         <v>1</v>
       </c>
       <c r="S119" s="2" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="V119" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:22">
       <c r="B120" s="2">
         <v>6012</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>225</v>
+        <v>287</v>
       </c>
       <c r="E120" s="2">
         <v>6</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="H120" s="7">
         <v>1</v>
       </c>
-      <c r="I120" s="12"/>
+      <c r="I120" s="19"/>
       <c r="J120" s="2">
         <v>0</v>
       </c>
@@ -7711,29 +8310,29 @@
         <v>1</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="V120" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:22">
       <c r="B121" s="2">
         <v>6013</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>226</v>
+        <v>288</v>
       </c>
       <c r="E121" s="2">
         <v>6</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="H121" s="7">
         <v>1</v>
       </c>
-      <c r="I121" s="12"/>
+      <c r="I121" s="19"/>
       <c r="J121" s="2">
         <v>0</v>
       </c>
@@ -7756,29 +8355,29 @@
         <v>1</v>
       </c>
       <c r="S121" s="2" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="V121" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:22">
       <c r="B122" s="2">
         <v>6014</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="E122" s="2">
         <v>6</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="H122" s="7">
         <v>1</v>
       </c>
-      <c r="I122" s="12"/>
+      <c r="I122" s="19"/>
       <c r="J122" s="2">
         <v>0</v>
       </c>
@@ -7801,29 +8400,29 @@
         <v>1</v>
       </c>
       <c r="S122" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="V122" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:22">
       <c r="B123" s="2">
         <v>6015</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="E123" s="2">
         <v>6</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="H123" s="7">
         <v>1</v>
       </c>
-      <c r="I123" s="12"/>
+      <c r="I123" s="19"/>
       <c r="J123" s="2">
         <v>0</v>
       </c>
@@ -7846,36 +8445,36 @@
         <v>1</v>
       </c>
       <c r="S123" s="2" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="V123" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="13"/>
-      <c r="B124" s="13">
+    <row r="124" s="1" customFormat="1" spans="1:28">
+      <c r="A124" s="17"/>
+      <c r="B124" s="17">
         <v>7001</v>
       </c>
-      <c r="C124" s="20" t="s">
-        <v>285</v>
+      <c r="C124" s="9" t="s">
+        <v>292</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E124" s="13">
+        <v>105</v>
+      </c>
+      <c r="E124" s="17">
         <v>7</v>
       </c>
-      <c r="F124" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="G124" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="H124" s="13">
-        <v>1</v>
-      </c>
-      <c r="I124" s="14"/>
+      <c r="F124" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="G124" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="H124" s="17">
+        <v>1</v>
+      </c>
+      <c r="I124" s="20"/>
       <c r="J124" s="2">
         <v>0</v>
       </c>
@@ -7897,45 +8496,45 @@
       <c r="P124" s="2">
         <v>1</v>
       </c>
-      <c r="Q124" s="13"/>
-      <c r="R124" s="13"/>
-      <c r="S124" s="13"/>
-      <c r="T124" s="13"/>
-      <c r="U124" s="13"/>
+      <c r="Q124" s="17"/>
+      <c r="R124" s="17"/>
+      <c r="S124" s="17"/>
+      <c r="T124" s="17"/>
+      <c r="U124" s="17"/>
       <c r="V124" s="2">
         <v>0</v>
       </c>
-      <c r="W124" s="13"/>
-      <c r="X124" s="17"/>
-      <c r="Y124" s="17"/>
-      <c r="Z124" s="17"/>
-      <c r="AA124" s="17"/>
-      <c r="AB124" s="17"/>
-    </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="W124" s="17"/>
+      <c r="X124" s="21"/>
+      <c r="Y124" s="21"/>
+      <c r="Z124" s="21"/>
+      <c r="AA124" s="21"/>
+      <c r="AB124" s="21"/>
+    </row>
+    <row r="125" spans="1:23">
       <c r="A125" s="7"/>
       <c r="B125" s="7">
         <v>7002</v>
       </c>
-      <c r="C125" s="21" t="s">
-        <v>291</v>
+      <c r="C125" s="11" t="s">
+        <v>294</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E125" s="7">
         <v>7</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G125" s="21" t="s">
-        <v>290</v>
+        <v>295</v>
+      </c>
+      <c r="G125" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H125" s="7">
         <v>1</v>
       </c>
-      <c r="I125" s="12"/>
+      <c r="I125" s="19"/>
       <c r="J125" s="2">
         <v>0</v>
       </c>
@@ -7967,30 +8566,30 @@
       </c>
       <c r="W125" s="7"/>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:23">
       <c r="A126" s="7"/>
       <c r="B126" s="7">
         <v>7003</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>231</v>
+        <v>296</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E126" s="7">
         <v>7</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="G126" s="21" t="s">
-        <v>290</v>
+        <v>295</v>
+      </c>
+      <c r="G126" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H126" s="7">
         <v>1</v>
       </c>
-      <c r="I126" s="12"/>
+      <c r="I126" s="19"/>
       <c r="J126" s="2">
         <v>0</v>
       </c>
@@ -8022,30 +8621,30 @@
       </c>
       <c r="W126" s="7"/>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:23">
       <c r="A127" s="7"/>
       <c r="B127" s="7">
         <v>7004</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E127" s="7">
         <v>7</v>
       </c>
-      <c r="F127" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="G127" s="21" t="s">
-        <v>290</v>
+      <c r="F127" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="G127" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H127" s="7">
         <v>1</v>
       </c>
-      <c r="I127" s="12"/>
+      <c r="I127" s="19"/>
       <c r="J127" s="2">
         <v>0</v>
       </c>
@@ -8077,30 +8676,30 @@
       </c>
       <c r="W127" s="7"/>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:23">
       <c r="A128" s="7"/>
       <c r="B128" s="7">
         <v>7005</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>283</v>
+        <v>105</v>
       </c>
       <c r="E128" s="7">
         <v>7</v>
       </c>
-      <c r="F128" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="G128" s="21" t="s">
-        <v>290</v>
+      <c r="F128" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="G128" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="H128" s="7">
         <v>1</v>
       </c>
-      <c r="I128" s="12"/>
+      <c r="I128" s="19"/>
       <c r="J128" s="2">
         <v>0</v>
       </c>
@@ -8132,10 +8731,10 @@
       </c>
       <c r="W128" s="7"/>
     </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:23">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
-      <c r="C129" s="16"/>
+      <c r="C129" s="22"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
       <c r="F129" s="7"/>
@@ -8155,10 +8754,10 @@
       <c r="V129" s="7"/>
       <c r="W129" s="7"/>
     </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:23">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
-      <c r="C130" s="16"/>
+      <c r="C130" s="22"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
       <c r="F130" s="7"/>
@@ -8178,10 +8777,10 @@
       <c r="V130" s="7"/>
       <c r="W130" s="7"/>
     </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:23">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
-      <c r="C131" s="16"/>
+      <c r="C131" s="22"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
       <c r="F131" s="7"/>
@@ -8201,10 +8800,10 @@
       <c r="V131" s="7"/>
       <c r="W131" s="7"/>
     </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:23">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
-      <c r="C132" s="16"/>
+      <c r="C132" s="22"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
       <c r="F132" s="7"/>
@@ -8224,10 +8823,10 @@
       <c r="V132" s="7"/>
       <c r="W132" s="7"/>
     </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:23">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
-      <c r="C133" s="16"/>
+      <c r="C133" s="22"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
       <c r="F133" s="7"/>
@@ -8247,10 +8846,10 @@
       <c r="V133" s="7"/>
       <c r="W133" s="7"/>
     </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:23">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
-      <c r="C134" s="16"/>
+      <c r="C134" s="22"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
       <c r="F134" s="7"/>
@@ -8270,10 +8869,10 @@
       <c r="V134" s="7"/>
       <c r="W134" s="7"/>
     </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:23">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
-      <c r="C135" s="16"/>
+      <c r="C135" s="22"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
@@ -8293,10 +8892,10 @@
       <c r="V135" s="7"/>
       <c r="W135" s="7"/>
     </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:23">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
-      <c r="C136" s="16"/>
+      <c r="C136" s="22"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
       <c r="F136" s="7"/>
@@ -8316,10 +8915,10 @@
       <c r="V136" s="7"/>
       <c r="W136" s="7"/>
     </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:23">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
-      <c r="C137" s="16"/>
+      <c r="C137" s="22"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
       <c r="F137" s="7"/>
@@ -8339,10 +8938,10 @@
       <c r="V137" s="7"/>
       <c r="W137" s="7"/>
     </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:23">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
-      <c r="C138" s="16"/>
+      <c r="C138" s="22"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
@@ -8362,10 +8961,10 @@
       <c r="V138" s="7"/>
       <c r="W138" s="7"/>
     </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:23">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
-      <c r="C139" s="16"/>
+      <c r="C139" s="22"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
       <c r="F139" s="7"/>
@@ -8385,10 +8984,10 @@
       <c r="V139" s="7"/>
       <c r="W139" s="7"/>
     </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:23">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
-      <c r="C140" s="16"/>
+      <c r="C140" s="22"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
       <c r="F140" s="7"/>
@@ -8408,10 +9007,10 @@
       <c r="V140" s="7"/>
       <c r="W140" s="7"/>
     </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:23">
       <c r="A141" s="7"/>
       <c r="B141" s="7"/>
-      <c r="C141" s="16"/>
+      <c r="C141" s="22"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7"/>
@@ -8431,10 +9030,10 @@
       <c r="V141" s="7"/>
       <c r="W141" s="7"/>
     </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:23">
       <c r="A142" s="7"/>
       <c r="B142" s="7"/>
-      <c r="C142" s="16"/>
+      <c r="C142" s="22"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
       <c r="F142" s="7"/>
@@ -8454,10 +9053,10 @@
       <c r="V142" s="7"/>
       <c r="W142" s="7"/>
     </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:23">
       <c r="A143" s="7"/>
       <c r="B143" s="7"/>
-      <c r="C143" s="16"/>
+      <c r="C143" s="22"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
       <c r="F143" s="7"/>
@@ -8477,10 +9076,10 @@
       <c r="V143" s="7"/>
       <c r="W143" s="7"/>
     </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:23">
       <c r="A144" s="7"/>
       <c r="B144" s="7"/>
-      <c r="C144" s="16"/>
+      <c r="C144" s="22"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
       <c r="F144" s="7"/>
@@ -8500,10 +9099,10 @@
       <c r="V144" s="7"/>
       <c r="W144" s="7"/>
     </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:23">
       <c r="A145" s="7"/>
       <c r="B145" s="7"/>
-      <c r="C145" s="16"/>
+      <c r="C145" s="22"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
       <c r="F145" s="7"/>
@@ -8523,10 +9122,10 @@
       <c r="V145" s="7"/>
       <c r="W145" s="7"/>
     </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:23">
       <c r="A146" s="7"/>
       <c r="B146" s="7"/>
-      <c r="C146" s="16"/>
+      <c r="C146" s="22"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
       <c r="F146" s="7"/>
@@ -8546,10 +9145,10 @@
       <c r="V146" s="7"/>
       <c r="W146" s="7"/>
     </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:23">
       <c r="A147" s="7"/>
       <c r="B147" s="7"/>
-      <c r="C147" s="16"/>
+      <c r="C147" s="22"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
       <c r="F147" s="7"/>
@@ -8569,10 +9168,10 @@
       <c r="V147" s="7"/>
       <c r="W147" s="7"/>
     </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:23">
       <c r="A148" s="7"/>
       <c r="B148" s="7"/>
-      <c r="C148" s="16"/>
+      <c r="C148" s="22"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
       <c r="F148" s="7"/>
@@ -8592,10 +9191,10 @@
       <c r="V148" s="7"/>
       <c r="W148" s="7"/>
     </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:23">
       <c r="A149" s="7"/>
       <c r="B149" s="7"/>
-      <c r="C149" s="16"/>
+      <c r="C149" s="22"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
       <c r="F149" s="7"/>
@@ -8615,10 +9214,10 @@
       <c r="V149" s="7"/>
       <c r="W149" s="7"/>
     </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:23">
       <c r="A150" s="7"/>
       <c r="B150" s="7"/>
-      <c r="C150" s="16"/>
+      <c r="C150" s="22"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
       <c r="F150" s="7"/>
@@ -8638,10 +9237,10 @@
       <c r="V150" s="7"/>
       <c r="W150" s="7"/>
     </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:23">
       <c r="A151" s="7"/>
       <c r="B151" s="7"/>
-      <c r="C151" s="16"/>
+      <c r="C151" s="22"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
       <c r="F151" s="7"/>
@@ -8661,10 +9260,10 @@
       <c r="V151" s="7"/>
       <c r="W151" s="7"/>
     </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:23">
       <c r="A152" s="7"/>
       <c r="B152" s="7"/>
-      <c r="C152" s="16"/>
+      <c r="C152" s="22"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
       <c r="F152" s="7"/>
@@ -8684,10 +9283,10 @@
       <c r="V152" s="7"/>
       <c r="W152" s="7"/>
     </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:23">
       <c r="A153" s="7"/>
       <c r="B153" s="7"/>
-      <c r="C153" s="16"/>
+      <c r="C153" s="22"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
       <c r="F153" s="7"/>
@@ -8707,10 +9306,10 @@
       <c r="V153" s="7"/>
       <c r="W153" s="7"/>
     </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:23">
       <c r="A154" s="7"/>
       <c r="B154" s="7"/>
-      <c r="C154" s="16"/>
+      <c r="C154" s="22"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
       <c r="F154" s="7"/>
@@ -8730,10 +9329,10 @@
       <c r="V154" s="7"/>
       <c r="W154" s="7"/>
     </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:23">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
-      <c r="C155" s="16"/>
+      <c r="C155" s="22"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
       <c r="F155" s="7"/>
@@ -8753,10 +9352,10 @@
       <c r="V155" s="7"/>
       <c r="W155" s="7"/>
     </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:23">
       <c r="A156" s="7"/>
       <c r="B156" s="7"/>
-      <c r="C156" s="16"/>
+      <c r="C156" s="22"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
       <c r="F156" s="7"/>
@@ -8776,10 +9375,10 @@
       <c r="V156" s="7"/>
       <c r="W156" s="7"/>
     </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:23">
       <c r="A157" s="7"/>
       <c r="B157" s="7"/>
-      <c r="C157" s="16"/>
+      <c r="C157" s="22"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
       <c r="F157" s="7"/>
@@ -8799,10 +9398,10 @@
       <c r="V157" s="7"/>
       <c r="W157" s="7"/>
     </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:23">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
-      <c r="C158" s="16"/>
+      <c r="C158" s="22"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
       <c r="F158" s="7"/>
@@ -8822,10 +9421,10 @@
       <c r="V158" s="7"/>
       <c r="W158" s="7"/>
     </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:23">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
-      <c r="C159" s="16"/>
+      <c r="C159" s="22"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
       <c r="F159" s="7"/>
@@ -8845,10 +9444,10 @@
       <c r="V159" s="7"/>
       <c r="W159" s="7"/>
     </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:23">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
-      <c r="C160" s="16"/>
+      <c r="C160" s="22"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
       <c r="F160" s="7"/>
@@ -8868,10 +9467,10 @@
       <c r="V160" s="7"/>
       <c r="W160" s="7"/>
     </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:23">
       <c r="A161" s="7"/>
       <c r="B161" s="7"/>
-      <c r="C161" s="16"/>
+      <c r="C161" s="22"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
       <c r="F161" s="7"/>
@@ -8891,10 +9490,10 @@
       <c r="V161" s="7"/>
       <c r="W161" s="7"/>
     </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23">
       <c r="A162" s="7"/>
       <c r="B162" s="7"/>
-      <c r="C162" s="16"/>
+      <c r="C162" s="22"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
       <c r="F162" s="7"/>
@@ -8914,10 +9513,10 @@
       <c r="V162" s="7"/>
       <c r="W162" s="7"/>
     </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23">
       <c r="A163" s="7"/>
       <c r="B163" s="7"/>
-      <c r="C163" s="16"/>
+      <c r="C163" s="22"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
       <c r="F163" s="7"/>
@@ -8937,10 +9536,10 @@
       <c r="V163" s="7"/>
       <c r="W163" s="7"/>
     </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:23">
       <c r="A164" s="7"/>
       <c r="B164" s="7"/>
-      <c r="C164" s="16"/>
+      <c r="C164" s="22"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
       <c r="F164" s="7"/>
@@ -8960,10 +9559,10 @@
       <c r="V164" s="7"/>
       <c r="W164" s="7"/>
     </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:23">
       <c r="A165" s="7"/>
       <c r="B165" s="7"/>
-      <c r="C165" s="16"/>
+      <c r="C165" s="22"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
       <c r="F165" s="7"/>
@@ -8983,10 +9582,10 @@
       <c r="V165" s="7"/>
       <c r="W165" s="7"/>
     </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:23">
       <c r="A166" s="7"/>
       <c r="B166" s="7"/>
-      <c r="C166" s="16"/>
+      <c r="C166" s="22"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
       <c r="F166" s="7"/>
@@ -9006,10 +9605,10 @@
       <c r="V166" s="7"/>
       <c r="W166" s="7"/>
     </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:23">
       <c r="A167" s="7"/>
       <c r="B167" s="7"/>
-      <c r="C167" s="16"/>
+      <c r="C167" s="22"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
       <c r="F167" s="7"/>
@@ -9029,10 +9628,10 @@
       <c r="V167" s="7"/>
       <c r="W167" s="7"/>
     </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:23">
       <c r="A168" s="7"/>
       <c r="B168" s="7"/>
-      <c r="C168" s="16"/>
+      <c r="C168" s="22"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
@@ -9052,10 +9651,10 @@
       <c r="V168" s="7"/>
       <c r="W168" s="7"/>
     </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:23">
       <c r="A169" s="7"/>
       <c r="B169" s="7"/>
-      <c r="C169" s="16"/>
+      <c r="C169" s="22"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
       <c r="F169" s="7"/>
@@ -9075,10 +9674,10 @@
       <c r="V169" s="7"/>
       <c r="W169" s="7"/>
     </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:23">
       <c r="A170" s="7"/>
       <c r="B170" s="7"/>
-      <c r="C170" s="16"/>
+      <c r="C170" s="22"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
       <c r="F170" s="7"/>
@@ -9098,10 +9697,10 @@
       <c r="V170" s="7"/>
       <c r="W170" s="7"/>
     </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:23">
       <c r="A171" s="7"/>
       <c r="B171" s="7"/>
-      <c r="C171" s="16"/>
+      <c r="C171" s="22"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
       <c r="F171" s="7"/>
@@ -9121,10 +9720,10 @@
       <c r="V171" s="7"/>
       <c r="W171" s="7"/>
     </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:23">
       <c r="A172" s="7"/>
       <c r="B172" s="7"/>
-      <c r="C172" s="16"/>
+      <c r="C172" s="22"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
       <c r="F172" s="7"/>
@@ -9144,10 +9743,10 @@
       <c r="V172" s="7"/>
       <c r="W172" s="7"/>
     </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:23">
       <c r="A173" s="7"/>
       <c r="B173" s="7"/>
-      <c r="C173" s="16"/>
+      <c r="C173" s="22"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
       <c r="F173" s="7"/>
@@ -9167,10 +9766,10 @@
       <c r="V173" s="7"/>
       <c r="W173" s="7"/>
     </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:23">
       <c r="A174" s="7"/>
       <c r="B174" s="7"/>
-      <c r="C174" s="16"/>
+      <c r="C174" s="22"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
       <c r="F174" s="7"/>
@@ -9190,10 +9789,10 @@
       <c r="V174" s="7"/>
       <c r="W174" s="7"/>
     </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:23">
       <c r="A175" s="7"/>
       <c r="B175" s="7"/>
-      <c r="C175" s="16"/>
+      <c r="C175" s="22"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
@@ -9213,10 +9812,10 @@
       <c r="V175" s="7"/>
       <c r="W175" s="7"/>
     </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:23">
       <c r="A176" s="7"/>
       <c r="B176" s="7"/>
-      <c r="C176" s="16"/>
+      <c r="C176" s="22"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
       <c r="F176" s="7"/>
@@ -9236,10 +9835,10 @@
       <c r="V176" s="7"/>
       <c r="W176" s="7"/>
     </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:23">
       <c r="A177" s="7"/>
       <c r="B177" s="7"/>
-      <c r="C177" s="16"/>
+      <c r="C177" s="22"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
       <c r="F177" s="7"/>
@@ -9259,10 +9858,10 @@
       <c r="V177" s="7"/>
       <c r="W177" s="7"/>
     </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:23">
       <c r="A178" s="7"/>
       <c r="B178" s="7"/>
-      <c r="C178" s="16"/>
+      <c r="C178" s="22"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
@@ -9282,10 +9881,10 @@
       <c r="V178" s="7"/>
       <c r="W178" s="7"/>
     </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:23">
       <c r="A179" s="7"/>
       <c r="B179" s="7"/>
-      <c r="C179" s="16"/>
+      <c r="C179" s="22"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
       <c r="F179" s="7"/>
@@ -9305,10 +9904,10 @@
       <c r="V179" s="7"/>
       <c r="W179" s="7"/>
     </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:23">
       <c r="A180" s="7"/>
       <c r="B180" s="7"/>
-      <c r="C180" s="16"/>
+      <c r="C180" s="22"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
       <c r="F180" s="7"/>
@@ -9328,10 +9927,10 @@
       <c r="V180" s="7"/>
       <c r="W180" s="7"/>
     </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:23">
       <c r="A181" s="7"/>
       <c r="B181" s="7"/>
-      <c r="C181" s="16"/>
+      <c r="C181" s="22"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
@@ -9351,10 +9950,10 @@
       <c r="V181" s="7"/>
       <c r="W181" s="7"/>
     </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:23">
       <c r="A182" s="7"/>
       <c r="B182" s="7"/>
-      <c r="C182" s="16"/>
+      <c r="C182" s="22"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
       <c r="F182" s="7"/>
@@ -9374,10 +9973,10 @@
       <c r="V182" s="7"/>
       <c r="W182" s="7"/>
     </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:23">
       <c r="A183" s="7"/>
       <c r="B183" s="7"/>
-      <c r="C183" s="16"/>
+      <c r="C183" s="22"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
       <c r="F183" s="7"/>
@@ -9397,10 +9996,10 @@
       <c r="V183" s="7"/>
       <c r="W183" s="7"/>
     </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:23">
       <c r="A184" s="7"/>
       <c r="B184" s="7"/>
-      <c r="C184" s="16"/>
+      <c r="C184" s="22"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
@@ -9420,10 +10019,10 @@
       <c r="V184" s="7"/>
       <c r="W184" s="7"/>
     </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:23">
       <c r="A185" s="7"/>
       <c r="B185" s="7"/>
-      <c r="C185" s="16"/>
+      <c r="C185" s="22"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7"/>
       <c r="F185" s="7"/>
@@ -9443,10 +10042,10 @@
       <c r="V185" s="7"/>
       <c r="W185" s="7"/>
     </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:23">
       <c r="A186" s="7"/>
       <c r="B186" s="7"/>
-      <c r="C186" s="16"/>
+      <c r="C186" s="22"/>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -9466,10 +10065,10 @@
       <c r="V186" s="7"/>
       <c r="W186" s="7"/>
     </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:23">
       <c r="A187" s="7"/>
       <c r="B187" s="7"/>
-      <c r="C187" s="16"/>
+      <c r="C187" s="22"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -9489,10 +10088,10 @@
       <c r="V187" s="7"/>
       <c r="W187" s="7"/>
     </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:23">
       <c r="A188" s="7"/>
       <c r="B188" s="7"/>
-      <c r="C188" s="16"/>
+      <c r="C188" s="22"/>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -9512,10 +10111,10 @@
       <c r="V188" s="7"/>
       <c r="W188" s="7"/>
     </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:23">
       <c r="A189" s="7"/>
       <c r="B189" s="7"/>
-      <c r="C189" s="16"/>
+      <c r="C189" s="22"/>
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
@@ -9535,10 +10134,10 @@
       <c r="V189" s="7"/>
       <c r="W189" s="7"/>
     </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:23">
       <c r="A190" s="7"/>
       <c r="B190" s="7"/>
-      <c r="C190" s="16"/>
+      <c r="C190" s="22"/>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
@@ -9558,10 +10157,10 @@
       <c r="V190" s="7"/>
       <c r="W190" s="7"/>
     </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:23">
       <c r="A191" s="7"/>
       <c r="B191" s="7"/>
-      <c r="C191" s="16"/>
+      <c r="C191" s="22"/>
       <c r="D191" s="7"/>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
@@ -9581,10 +10180,10 @@
       <c r="V191" s="7"/>
       <c r="W191" s="7"/>
     </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:23">
       <c r="A192" s="7"/>
       <c r="B192" s="7"/>
-      <c r="C192" s="16"/>
+      <c r="C192" s="22"/>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
@@ -9604,10 +10203,10 @@
       <c r="V192" s="7"/>
       <c r="W192" s="7"/>
     </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:23">
       <c r="A193" s="7"/>
       <c r="B193" s="7"/>
-      <c r="C193" s="16"/>
+      <c r="C193" s="22"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
@@ -9627,10 +10226,10 @@
       <c r="V193" s="7"/>
       <c r="W193" s="7"/>
     </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:23">
       <c r="A194" s="7"/>
       <c r="B194" s="7"/>
-      <c r="C194" s="16"/>
+      <c r="C194" s="22"/>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
       <c r="F194" s="7"/>
@@ -9650,10 +10249,10 @@
       <c r="V194" s="7"/>
       <c r="W194" s="7"/>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:23">
       <c r="A195" s="7"/>
       <c r="B195" s="7"/>
-      <c r="C195" s="16"/>
+      <c r="C195" s="22"/>
       <c r="D195" s="7"/>
       <c r="E195" s="7"/>
       <c r="F195" s="7"/>
@@ -9673,10 +10272,10 @@
       <c r="V195" s="7"/>
       <c r="W195" s="7"/>
     </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:23">
       <c r="A196" s="7"/>
       <c r="B196" s="7"/>
-      <c r="C196" s="16"/>
+      <c r="C196" s="22"/>
       <c r="D196" s="7"/>
       <c r="E196" s="7"/>
       <c r="F196" s="7"/>
@@ -9696,10 +10295,10 @@
       <c r="V196" s="7"/>
       <c r="W196" s="7"/>
     </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:23">
       <c r="A197" s="7"/>
       <c r="B197" s="7"/>
-      <c r="C197" s="16"/>
+      <c r="C197" s="22"/>
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
       <c r="F197" s="7"/>
@@ -9719,10 +10318,10 @@
       <c r="V197" s="7"/>
       <c r="W197" s="7"/>
     </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:23">
       <c r="A198" s="7"/>
       <c r="B198" s="7"/>
-      <c r="C198" s="16"/>
+      <c r="C198" s="22"/>
       <c r="D198" s="7"/>
       <c r="E198" s="7"/>
       <c r="F198" s="7"/>
@@ -9742,10 +10341,10 @@
       <c r="V198" s="7"/>
       <c r="W198" s="7"/>
     </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:23">
       <c r="A199" s="7"/>
       <c r="B199" s="7"/>
-      <c r="C199" s="16"/>
+      <c r="C199" s="22"/>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
       <c r="F199" s="7"/>
@@ -9765,10 +10364,10 @@
       <c r="V199" s="7"/>
       <c r="W199" s="7"/>
     </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:23">
       <c r="A200" s="7"/>
       <c r="B200" s="7"/>
-      <c r="C200" s="16"/>
+      <c r="C200" s="22"/>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
       <c r="F200" s="7"/>
@@ -9788,10 +10387,10 @@
       <c r="V200" s="7"/>
       <c r="W200" s="7"/>
     </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:23">
       <c r="A201" s="7"/>
       <c r="B201" s="7"/>
-      <c r="C201" s="16"/>
+      <c r="C201" s="22"/>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
       <c r="F201" s="7"/>
@@ -9811,10 +10410,10 @@
       <c r="V201" s="7"/>
       <c r="W201" s="7"/>
     </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:23">
       <c r="A202" s="7"/>
       <c r="B202" s="7"/>
-      <c r="C202" s="16"/>
+      <c r="C202" s="22"/>
       <c r="D202" s="7"/>
       <c r="E202" s="7"/>
       <c r="F202" s="7"/>
@@ -9834,10 +10433,10 @@
       <c r="V202" s="7"/>
       <c r="W202" s="7"/>
     </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:23">
       <c r="A203" s="7"/>
       <c r="B203" s="7"/>
-      <c r="C203" s="16"/>
+      <c r="C203" s="22"/>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
       <c r="F203" s="7"/>
@@ -9857,10 +10456,10 @@
       <c r="V203" s="7"/>
       <c r="W203" s="7"/>
     </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:23">
       <c r="A204" s="7"/>
       <c r="B204" s="7"/>
-      <c r="C204" s="16"/>
+      <c r="C204" s="22"/>
       <c r="D204" s="7"/>
       <c r="E204" s="7"/>
       <c r="F204" s="7"/>
@@ -9880,10 +10479,10 @@
       <c r="V204" s="7"/>
       <c r="W204" s="7"/>
     </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:23">
       <c r="A205" s="7"/>
       <c r="B205" s="7"/>
-      <c r="C205" s="16"/>
+      <c r="C205" s="22"/>
       <c r="D205" s="7"/>
       <c r="E205" s="7"/>
       <c r="F205" s="7"/>
@@ -9903,10 +10502,10 @@
       <c r="V205" s="7"/>
       <c r="W205" s="7"/>
     </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:23">
       <c r="A206" s="7"/>
       <c r="B206" s="7"/>
-      <c r="C206" s="16"/>
+      <c r="C206" s="22"/>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
       <c r="F206" s="7"/>
@@ -9926,10 +10525,10 @@
       <c r="V206" s="7"/>
       <c r="W206" s="7"/>
     </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="207" ht="15" spans="1:23">
       <c r="A207" s="7"/>
       <c r="B207" s="7"/>
-      <c r="C207" s="16"/>
+      <c r="C207" s="22"/>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
       <c r="F207" s="7"/>
@@ -9949,112 +10548,113 @@
       <c r="V207" s="7"/>
       <c r="W207" s="7"/>
     </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A208" s="18"/>
-      <c r="B208" s="18"/>
-      <c r="C208" s="18"/>
-      <c r="D208" s="18"/>
-      <c r="E208" s="18"/>
-      <c r="F208" s="18"/>
-      <c r="G208" s="18"/>
-      <c r="H208" s="18"/>
-      <c r="I208" s="18"/>
-      <c r="J208" s="18"/>
-      <c r="K208" s="18"/>
-      <c r="L208" s="12"/>
-      <c r="M208" s="12"/>
-      <c r="Q208" s="18"/>
-      <c r="R208" s="18"/>
-      <c r="S208" s="18"/>
-      <c r="T208" s="18"/>
-    </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A209" s="18"/>
-      <c r="B209" s="18"/>
-      <c r="C209" s="18"/>
-      <c r="D209" s="18"/>
-      <c r="E209" s="18"/>
-      <c r="F209" s="18"/>
-      <c r="G209" s="18"/>
-      <c r="H209" s="18"/>
-      <c r="I209" s="18"/>
-      <c r="J209" s="18"/>
-      <c r="K209" s="18"/>
-      <c r="L209" s="12"/>
-      <c r="M209" s="12"/>
-      <c r="Q209" s="18"/>
-      <c r="R209" s="18"/>
-      <c r="S209" s="18"/>
-      <c r="T209" s="18"/>
-    </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A210" s="18"/>
-      <c r="B210" s="18"/>
-      <c r="C210" s="18"/>
-      <c r="D210" s="18"/>
-      <c r="E210" s="18"/>
-      <c r="F210" s="18"/>
-      <c r="G210" s="18"/>
-      <c r="H210" s="18"/>
-      <c r="I210" s="18"/>
-      <c r="J210" s="18"/>
-      <c r="K210" s="18"/>
-      <c r="L210" s="12"/>
-      <c r="M210" s="12"/>
-      <c r="Q210" s="18"/>
-      <c r="R210" s="18"/>
-      <c r="S210" s="18"/>
-      <c r="T210" s="18"/>
+    <row r="208" ht="15" spans="1:20">
+      <c r="A208" s="23"/>
+      <c r="B208" s="23"/>
+      <c r="C208" s="23"/>
+      <c r="D208" s="23"/>
+      <c r="E208" s="23"/>
+      <c r="F208" s="23"/>
+      <c r="G208" s="23"/>
+      <c r="H208" s="23"/>
+      <c r="I208" s="23"/>
+      <c r="J208" s="23"/>
+      <c r="K208" s="23"/>
+      <c r="L208" s="19"/>
+      <c r="M208" s="19"/>
+      <c r="Q208" s="23"/>
+      <c r="R208" s="23"/>
+      <c r="S208" s="23"/>
+      <c r="T208" s="23"/>
+    </row>
+    <row r="209" ht="15" spans="1:20">
+      <c r="A209" s="23"/>
+      <c r="B209" s="23"/>
+      <c r="C209" s="23"/>
+      <c r="D209" s="23"/>
+      <c r="E209" s="23"/>
+      <c r="F209" s="23"/>
+      <c r="G209" s="23"/>
+      <c r="H209" s="23"/>
+      <c r="I209" s="23"/>
+      <c r="J209" s="23"/>
+      <c r="K209" s="23"/>
+      <c r="L209" s="19"/>
+      <c r="M209" s="19"/>
+      <c r="Q209" s="23"/>
+      <c r="R209" s="23"/>
+      <c r="S209" s="23"/>
+      <c r="T209" s="23"/>
+    </row>
+    <row r="210" ht="15" spans="1:20">
+      <c r="A210" s="23"/>
+      <c r="B210" s="23"/>
+      <c r="C210" s="23"/>
+      <c r="D210" s="23"/>
+      <c r="E210" s="23"/>
+      <c r="F210" s="23"/>
+      <c r="G210" s="23"/>
+      <c r="H210" s="23"/>
+      <c r="I210" s="23"/>
+      <c r="J210" s="23"/>
+      <c r="K210" s="23"/>
+      <c r="L210" s="19"/>
+      <c r="M210" s="19"/>
+      <c r="Q210" s="23"/>
+      <c r="R210" s="23"/>
+      <c r="S210" s="23"/>
+      <c r="T210" s="23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="L19:R61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="12" max="12" width="5.1640625" customWidth="1"/>
-    <col min="13" max="13" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="5.16666666666667" customWidth="1"/>
+    <col min="13" max="13" width="18.3333333333333" customWidth="1"/>
     <col min="14" max="15" width="20.5" customWidth="1"/>
     <col min="16" max="17" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="12:18">
       <c r="L19" t="s">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="M19" t="s">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="N19" t="s">
-        <v>252</v>
+        <v>303</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>304</v>
       </c>
       <c r="R19" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="20" spans="12:18" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="12:18">
       <c r="L20">
         <v>5001</v>
       </c>
       <c r="M20" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P20" t="s">
-        <v>256</v>
+        <v>307</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -10064,21 +10664,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="12:18">
       <c r="L21">
         <v>5002</v>
       </c>
       <c r="M21" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P21" t="s">
-        <v>257</v>
+        <v>308</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -10088,21 +10688,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="12:18">
       <c r="L22">
         <v>5003</v>
       </c>
       <c r="M22" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -10112,21 +10712,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="12:18">
       <c r="L23">
         <v>5004</v>
       </c>
       <c r="M23" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P23" t="s">
-        <v>259</v>
+        <v>310</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -10136,21 +10736,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="12:18">
       <c r="L24">
         <v>5005</v>
       </c>
       <c r="M24" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="N24">
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -10160,21 +10760,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="12:18">
       <c r="L25">
         <v>5006</v>
       </c>
       <c r="M25" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P25" t="s">
-        <v>261</v>
+        <v>312</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -10184,21 +10784,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="12:18">
       <c r="L26">
         <v>5007</v>
       </c>
       <c r="M26" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P26" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -10208,21 +10808,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="12:18">
       <c r="L27">
         <v>5008</v>
       </c>
       <c r="M27" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -10232,21 +10832,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="12:18">
       <c r="L28">
         <v>5009</v>
       </c>
       <c r="M28" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -10256,18 +10856,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="12:18">
       <c r="L29">
         <v>6001</v>
       </c>
       <c r="M29" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="O29" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -10277,18 +10877,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="12:18">
       <c r="L30">
         <v>6002</v>
       </c>
       <c r="M30" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="O30" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P30" t="s">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -10298,18 +10898,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="12:18">
       <c r="L31">
         <v>6003</v>
       </c>
       <c r="M31" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="O31" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P31" t="s">
-        <v>267</v>
+        <v>319</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -10319,18 +10919,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="12:18">
       <c r="L32">
         <v>6004</v>
       </c>
       <c r="M32" t="s">
-        <v>212</v>
+        <v>274</v>
       </c>
       <c r="O32" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P32" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -10340,18 +10940,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:18">
       <c r="L33">
         <v>6005</v>
       </c>
       <c r="M33" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="O33" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P33" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -10361,18 +10961,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:18">
       <c r="L34">
         <v>6006</v>
       </c>
       <c r="M34" t="s">
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="O34" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P34" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -10382,18 +10982,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:18">
       <c r="L35">
         <v>6007</v>
       </c>
       <c r="M35" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="O35" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P35" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -10403,18 +11003,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:18">
       <c r="L36">
         <v>6008</v>
       </c>
       <c r="M36" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="O36" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P36" t="s">
-        <v>271</v>
+        <v>323</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -10424,18 +11024,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:18">
       <c r="L37">
         <v>6009</v>
       </c>
       <c r="M37" t="s">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="O37" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P37" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -10445,18 +11045,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:18">
       <c r="L38">
         <v>6010</v>
       </c>
       <c r="M38" t="s">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="O38" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P38" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -10466,18 +11066,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:18">
       <c r="L39">
         <v>6011</v>
       </c>
       <c r="M39" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="O39" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P39" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -10487,18 +11087,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:18">
       <c r="L40">
         <v>6012</v>
       </c>
       <c r="M40" t="s">
-        <v>225</v>
+        <v>287</v>
       </c>
       <c r="O40" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P40" t="s">
-        <v>270</v>
+        <v>322</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -10508,18 +11108,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:18">
       <c r="L41">
         <v>6013</v>
       </c>
       <c r="M41" t="s">
-        <v>226</v>
+        <v>288</v>
       </c>
       <c r="O41" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P41" t="s">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -10529,18 +11129,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="12:18">
       <c r="L42">
         <v>6014</v>
       </c>
       <c r="M42" t="s">
-        <v>227</v>
+        <v>289</v>
       </c>
       <c r="O42" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P42" t="s">
-        <v>273</v>
+        <v>325</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -10550,18 +11150,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="12:18">
       <c r="L43">
         <v>6015</v>
       </c>
       <c r="M43" t="s">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="O43" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="P43" t="s">
-        <v>266</v>
+        <v>318</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -10571,21 +11171,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="12:18">
       <c r="L44">
         <v>7001</v>
       </c>
       <c r="M44" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="N44">
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="P44" t="s">
-        <v>275</v>
+        <v>327</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -10595,21 +11195,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="12:18">
       <c r="L45">
         <v>7002</v>
       </c>
       <c r="M45" t="s">
-        <v>231</v>
+        <v>296</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="P45" t="s">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -10619,21 +11219,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="12:18">
       <c r="L46">
         <v>7003</v>
       </c>
       <c r="M46" t="s">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="P46" t="s">
-        <v>277</v>
+        <v>329</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -10643,21 +11243,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="12:18">
       <c r="L47">
         <v>7004</v>
       </c>
       <c r="M47" t="s">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>274</v>
+        <v>326</v>
       </c>
       <c r="P47" t="s">
-        <v>278</v>
+        <v>330</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -10667,21 +11267,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="12:18">
       <c r="L48">
         <v>8001</v>
       </c>
       <c r="M48" t="s">
-        <v>236</v>
+        <v>331</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
       <c r="O48" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P48" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -10691,21 +11291,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:18">
       <c r="L49">
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>237</v>
+        <v>334</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -10715,21 +11315,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="12:18">
       <c r="L50">
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>238</v>
+        <v>335</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -10739,21 +11339,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="12:18">
       <c r="L51">
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>239</v>
+        <v>336</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P51" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -10763,21 +11363,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:18">
       <c r="L52">
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>240</v>
+        <v>337</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P52" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -10787,21 +11387,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:18">
       <c r="L53">
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>241</v>
+        <v>338</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P53" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -10811,21 +11411,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:18">
       <c r="L54">
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>242</v>
+        <v>339</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P54" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -10835,21 +11435,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="12:18">
       <c r="L55">
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P55" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -10859,21 +11459,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="12:18">
       <c r="L56">
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>244</v>
+        <v>341</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P56" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -10883,21 +11483,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="12:18">
       <c r="L57">
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>245</v>
+        <v>342</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P57" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -10907,21 +11507,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="12:18">
       <c r="L58">
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P58" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -10931,21 +11531,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:18">
       <c r="L59">
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>247</v>
+        <v>344</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P59" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -10955,21 +11555,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:18">
       <c r="L60">
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>248</v>
+        <v>345</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P60" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -10979,21 +11579,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="12:18">
       <c r="L61">
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>249</v>
+        <v>346</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>
@@ -11004,7 +11604,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC22CB9-6B3A-4696-8CAA-F1F03CB203FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34595592-06C4-4A06-9122-B9CEC09D9FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1447,7 +1447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1565,6 +1565,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5480,161 +5489,161 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="36">
+    <row r="66" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="1">
         <v>5002</v>
       </c>
-      <c r="C66" s="36" t="s">
+      <c r="C66" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="E66" s="36">
+      <c r="E66" s="1">
         <v>5</v>
       </c>
-      <c r="F66" s="36" t="s">
+      <c r="F66" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="H66" s="36">
-        <v>1</v>
-      </c>
-      <c r="J66" s="36">
-        <v>0</v>
-      </c>
-      <c r="K66" s="36">
-        <v>0</v>
-      </c>
-      <c r="L66" s="36">
-        <v>1</v>
-      </c>
-      <c r="M66" s="36">
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
         <v>0.3</v>
       </c>
-      <c r="N66" s="36">
-        <v>1</v>
-      </c>
-      <c r="O66" s="36">
-        <v>1</v>
-      </c>
-      <c r="P66" s="36">
-        <v>0</v>
-      </c>
-      <c r="S66" s="36" t="s">
+      <c r="N66" s="1">
+        <v>1</v>
+      </c>
+      <c r="O66" s="1">
+        <v>1</v>
+      </c>
+      <c r="P66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="V66" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
-      <c r="B67" s="36">
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="45"/>
+      <c r="B67" s="1">
         <v>5003</v>
       </c>
-      <c r="C67" s="38" t="s">
+      <c r="C67" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="D67" s="37"/>
-      <c r="E67" s="36">
+      <c r="D67" s="45"/>
+      <c r="E67" s="1">
         <v>5</v>
       </c>
-      <c r="F67" s="37" t="s">
+      <c r="F67" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="G67" s="39"/>
-      <c r="H67" s="37">
-        <v>1</v>
-      </c>
-      <c r="I67" s="40"/>
-      <c r="J67" s="36">
-        <v>0</v>
-      </c>
-      <c r="K67" s="36">
-        <v>0</v>
-      </c>
-      <c r="L67" s="37">
-        <v>0</v>
-      </c>
-      <c r="M67" s="36">
+      <c r="G67" s="46"/>
+      <c r="H67" s="45">
+        <v>1</v>
+      </c>
+      <c r="I67" s="47"/>
+      <c r="J67" s="1">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1">
+        <v>0</v>
+      </c>
+      <c r="L67" s="45">
+        <v>0</v>
+      </c>
+      <c r="M67" s="1">
         <v>0.3</v>
       </c>
-      <c r="N67" s="36">
-        <v>1</v>
-      </c>
-      <c r="O67" s="36">
-        <v>1</v>
-      </c>
-      <c r="P67" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="37"/>
-      <c r="R67" s="37"/>
-      <c r="S67" s="37"/>
-      <c r="T67" s="37"/>
-      <c r="U67" s="37"/>
-      <c r="V67" s="36">
-        <v>0</v>
-      </c>
-      <c r="W67" s="37"/>
-      <c r="X67" s="38"/>
-      <c r="Y67" s="38"/>
-      <c r="Z67" s="38"/>
-      <c r="AA67" s="38"/>
-      <c r="AB67" s="38"/>
-    </row>
-    <row r="68" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
-      <c r="B68" s="36">
+      <c r="N67" s="1">
+        <v>1</v>
+      </c>
+      <c r="O67" s="1">
+        <v>1</v>
+      </c>
+      <c r="P67" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="45"/>
+      <c r="R67" s="45"/>
+      <c r="S67" s="45"/>
+      <c r="T67" s="45"/>
+      <c r="U67" s="45"/>
+      <c r="V67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="45"/>
+      <c r="X67" s="12"/>
+      <c r="Y67" s="12"/>
+      <c r="Z67" s="12"/>
+      <c r="AA67" s="12"/>
+      <c r="AB67" s="12"/>
+    </row>
+    <row r="68" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="45"/>
+      <c r="B68" s="1">
         <v>5004</v>
       </c>
-      <c r="C68" s="38" t="s">
+      <c r="C68" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="D68" s="37"/>
-      <c r="E68" s="36">
+      <c r="D68" s="45"/>
+      <c r="E68" s="1">
         <v>5</v>
       </c>
-      <c r="F68" s="37" t="s">
+      <c r="F68" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="G68" s="39"/>
-      <c r="H68" s="37">
-        <v>1</v>
-      </c>
-      <c r="I68" s="40"/>
-      <c r="J68" s="36">
-        <v>0</v>
-      </c>
-      <c r="K68" s="36">
-        <v>1</v>
-      </c>
-      <c r="L68" s="37">
-        <v>0</v>
-      </c>
-      <c r="M68" s="36">
+      <c r="G68" s="46"/>
+      <c r="H68" s="45">
+        <v>1</v>
+      </c>
+      <c r="I68" s="47"/>
+      <c r="J68" s="1">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1">
+        <v>1</v>
+      </c>
+      <c r="L68" s="45">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
         <v>0.3</v>
       </c>
-      <c r="N68" s="36">
-        <v>1</v>
-      </c>
-      <c r="O68" s="36">
-        <v>1</v>
-      </c>
-      <c r="P68" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="37"/>
-      <c r="R68" s="37"/>
-      <c r="S68" s="37"/>
-      <c r="T68" s="37"/>
-      <c r="U68" s="37"/>
-      <c r="V68" s="36">
-        <v>0</v>
-      </c>
-      <c r="W68" s="37"/>
-      <c r="X68" s="38"/>
-      <c r="Y68" s="38"/>
-      <c r="Z68" s="38"/>
-      <c r="AA68" s="38"/>
-      <c r="AB68" s="38"/>
+      <c r="N68" s="1">
+        <v>1</v>
+      </c>
+      <c r="O68" s="1">
+        <v>1</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="45"/>
+      <c r="R68" s="45"/>
+      <c r="S68" s="45"/>
+      <c r="T68" s="45"/>
+      <c r="U68" s="45"/>
+      <c r="V68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="45"/>
+      <c r="X68" s="12"/>
+      <c r="Y68" s="12"/>
+      <c r="Z68" s="12"/>
+      <c r="AA68" s="12"/>
+      <c r="AB68" s="12"/>
     </row>
     <row r="69" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="37"/>
@@ -5692,173 +5701,173 @@
       <c r="AA69" s="38"/>
       <c r="AB69" s="38"/>
     </row>
-    <row r="70" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
-      <c r="B70" s="36">
+    <row r="70" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="45"/>
+      <c r="B70" s="1">
         <v>5006</v>
       </c>
-      <c r="C70" s="38" t="s">
+      <c r="C70" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D70" s="37"/>
-      <c r="E70" s="36">
+      <c r="D70" s="45"/>
+      <c r="E70" s="1">
         <v>5</v>
       </c>
-      <c r="F70" s="37" t="s">
+      <c r="F70" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="G70" s="39"/>
-      <c r="H70" s="37">
-        <v>1</v>
-      </c>
-      <c r="I70" s="40"/>
-      <c r="J70" s="36">
-        <v>0</v>
-      </c>
-      <c r="K70" s="36">
-        <v>0</v>
-      </c>
-      <c r="L70" s="37">
-        <v>1</v>
-      </c>
-      <c r="M70" s="36">
+      <c r="G70" s="46"/>
+      <c r="H70" s="45">
+        <v>1</v>
+      </c>
+      <c r="I70" s="47"/>
+      <c r="J70" s="1">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="45">
+        <v>1</v>
+      </c>
+      <c r="M70" s="1">
         <v>0.3</v>
       </c>
-      <c r="N70" s="36">
-        <v>1</v>
-      </c>
-      <c r="O70" s="36">
-        <v>1</v>
-      </c>
-      <c r="P70" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="37"/>
-      <c r="R70" s="37"/>
-      <c r="S70" s="37"/>
-      <c r="T70" s="37"/>
-      <c r="U70" s="37"/>
-      <c r="V70" s="36">
-        <v>0</v>
-      </c>
-      <c r="W70" s="37"/>
-      <c r="X70" s="38"/>
-      <c r="Y70" s="38"/>
-      <c r="Z70" s="38"/>
-      <c r="AA70" s="38"/>
-      <c r="AB70" s="38"/>
-    </row>
-    <row r="71" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
-      <c r="B71" s="36">
+      <c r="N70" s="1">
+        <v>1</v>
+      </c>
+      <c r="O70" s="1">
+        <v>1</v>
+      </c>
+      <c r="P70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="45"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="45"/>
+      <c r="T70" s="45"/>
+      <c r="U70" s="45"/>
+      <c r="V70" s="1">
+        <v>0</v>
+      </c>
+      <c r="W70" s="45"/>
+      <c r="X70" s="12"/>
+      <c r="Y70" s="12"/>
+      <c r="Z70" s="12"/>
+      <c r="AA70" s="12"/>
+      <c r="AB70" s="12"/>
+    </row>
+    <row r="71" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="45"/>
+      <c r="B71" s="1">
         <v>5007</v>
       </c>
-      <c r="C71" s="38" t="s">
+      <c r="C71" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="D71" s="37"/>
-      <c r="E71" s="36">
+      <c r="D71" s="45"/>
+      <c r="E71" s="1">
         <v>5</v>
       </c>
-      <c r="F71" s="37" t="s">
+      <c r="F71" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="G71" s="39"/>
-      <c r="H71" s="37">
-        <v>1</v>
-      </c>
-      <c r="I71" s="40"/>
-      <c r="J71" s="36">
-        <v>0</v>
-      </c>
-      <c r="K71" s="36">
-        <v>0</v>
-      </c>
-      <c r="L71" s="37">
-        <v>0</v>
-      </c>
-      <c r="M71" s="36">
+      <c r="G71" s="46"/>
+      <c r="H71" s="45">
+        <v>1</v>
+      </c>
+      <c r="I71" s="47"/>
+      <c r="J71" s="1">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1">
+        <v>0</v>
+      </c>
+      <c r="L71" s="45">
+        <v>0</v>
+      </c>
+      <c r="M71" s="1">
         <v>0.3</v>
       </c>
-      <c r="N71" s="36">
-        <v>1</v>
-      </c>
-      <c r="O71" s="36">
-        <v>1</v>
-      </c>
-      <c r="P71" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q71" s="37"/>
-      <c r="R71" s="37"/>
-      <c r="S71" s="37"/>
-      <c r="T71" s="37"/>
-      <c r="U71" s="37"/>
-      <c r="V71" s="36">
-        <v>0</v>
-      </c>
-      <c r="W71" s="37"/>
-      <c r="X71" s="38"/>
-      <c r="Y71" s="38"/>
-      <c r="Z71" s="38"/>
-      <c r="AA71" s="38"/>
-      <c r="AB71" s="38"/>
-    </row>
-    <row r="72" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
-      <c r="B72" s="36">
+      <c r="N71" s="1">
+        <v>1</v>
+      </c>
+      <c r="O71" s="1">
+        <v>1</v>
+      </c>
+      <c r="P71" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q71" s="45"/>
+      <c r="R71" s="45"/>
+      <c r="S71" s="45"/>
+      <c r="T71" s="45"/>
+      <c r="U71" s="45"/>
+      <c r="V71" s="1">
+        <v>0</v>
+      </c>
+      <c r="W71" s="45"/>
+      <c r="X71" s="12"/>
+      <c r="Y71" s="12"/>
+      <c r="Z71" s="12"/>
+      <c r="AA71" s="12"/>
+      <c r="AB71" s="12"/>
+    </row>
+    <row r="72" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="45"/>
+      <c r="B72" s="1">
         <v>5008</v>
       </c>
-      <c r="C72" s="38" t="s">
+      <c r="C72" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D72" s="37"/>
-      <c r="E72" s="36">
+      <c r="D72" s="45"/>
+      <c r="E72" s="1">
         <v>5</v>
       </c>
-      <c r="F72" s="37" t="s">
+      <c r="F72" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="G72" s="39"/>
-      <c r="H72" s="37">
-        <v>1</v>
-      </c>
-      <c r="I72" s="40"/>
-      <c r="J72" s="36">
-        <v>0</v>
-      </c>
-      <c r="K72" s="36">
-        <v>0</v>
-      </c>
-      <c r="L72" s="37">
-        <v>0</v>
-      </c>
-      <c r="M72" s="36">
+      <c r="G72" s="46"/>
+      <c r="H72" s="45">
+        <v>1</v>
+      </c>
+      <c r="I72" s="47"/>
+      <c r="J72" s="1">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>0</v>
+      </c>
+      <c r="L72" s="45">
+        <v>0</v>
+      </c>
+      <c r="M72" s="1">
         <v>0.3</v>
       </c>
-      <c r="N72" s="36">
-        <v>1</v>
-      </c>
-      <c r="O72" s="36">
-        <v>0</v>
-      </c>
-      <c r="P72" s="36">
-        <v>1</v>
-      </c>
-      <c r="Q72" s="37"/>
-      <c r="R72" s="37"/>
-      <c r="S72" s="37"/>
-      <c r="T72" s="37"/>
-      <c r="U72" s="37"/>
-      <c r="V72" s="36">
-        <v>0</v>
-      </c>
-      <c r="W72" s="37"/>
-      <c r="X72" s="38"/>
-      <c r="Y72" s="38"/>
-      <c r="Z72" s="38"/>
-      <c r="AA72" s="38"/>
-      <c r="AB72" s="38"/>
+      <c r="N72" s="1">
+        <v>1</v>
+      </c>
+      <c r="O72" s="1">
+        <v>0</v>
+      </c>
+      <c r="P72" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q72" s="45"/>
+      <c r="R72" s="45"/>
+      <c r="S72" s="45"/>
+      <c r="T72" s="45"/>
+      <c r="U72" s="45"/>
+      <c r="V72" s="1">
+        <v>0</v>
+      </c>
+      <c r="W72" s="45"/>
+      <c r="X72" s="12"/>
+      <c r="Y72" s="12"/>
+      <c r="Z72" s="12"/>
+      <c r="AA72" s="12"/>
+      <c r="AB72" s="12"/>
     </row>
     <row r="73" spans="1:28" s="36" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B73" s="41">

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="402">
   <si>
     <t>##var</t>
   </si>
@@ -777,115 +777,223 @@
     <t>爆米花-土豆&amp;蘑菇味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_Mushroom</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;南瓜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_Pumpkin</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;胡萝卜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_Carrot</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;水甜菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_WaterBeet</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;红番茄味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_RedTomato</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;花椰菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_Broccoli</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;猕猴桃味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_Kiwi</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Potato_Weed</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;南瓜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Mushroom_Pumpkin</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;胡萝卜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Mushroom_Carrot</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;水甜菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Mushroom_WaterBeet</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;红番茄味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Mushroom_RedTomato</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;花椰菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Mushroom_Broccoli</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;猕猴桃味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Mushroom_Kiwi</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Mushroom_Weed</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;胡萝卜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Pumpkin_Carrot</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;水甜菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Pumpkin_WaterBeet</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;红番茄味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Pumpkin_RedTomato</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;花椰菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Pumpkin_Broccoli</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;猕猴桃味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Pumpkin_Kiwi</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Pumpkin_Weed</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;水甜菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Carrot_WaterBeet</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;红番茄味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Carrot_RedTomato</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;花椰菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Carrot_Broccoli</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;猕猴桃味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Carrot_Kiwi</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Carrot_Weed</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;红番茄味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/WaterBeet_RedTomato</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;花椰菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/WaterBeet_Broccoli</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;猕猴桃味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/WaterBeet_Kiwi</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/WaterBeet_Weed</t>
+  </si>
+  <si>
     <t>爆米花-红番茄&amp;花椰菜味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/RedTomato_Broccoli</t>
+  </si>
+  <si>
     <t>爆米花-红番茄&amp;猕猴桃味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/RedTomato_Kiwi</t>
+  </si>
+  <si>
     <t>爆米花-红番茄&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/RedTomato_Weed</t>
+  </si>
+  <si>
     <t>爆米花-花椰菜&amp;猕猴桃味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Broccoli_Kiwi</t>
+  </si>
+  <si>
     <t>爆米花-花椰菜&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Broccoli_Weed</t>
+  </si>
+  <si>
     <t>爆米花-猕猴桃&amp;野草味</t>
   </si>
   <si>
+    <t>Prefab/Item/Popcorn/Kiwi_Weed</t>
+  </si>
+  <si>
     <t>土豆-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/mushroom_002</t>
+    <t>Prefab/Buildings/mushroom_002</t>
   </si>
   <si>
     <t>蘑菇-房子</t>
@@ -894,25 +1002,25 @@
     <t>南瓜-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/Pumpkin</t>
+    <t>Prefab/Buildings/Pumpkin</t>
   </si>
   <si>
     <t>胡萝卜-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/Carrot</t>
+    <t>Prefab/Buildings/Carrot</t>
   </si>
   <si>
     <t>水甜菜-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/Beet</t>
+    <t>Prefab/Buildings/Beet</t>
   </si>
   <si>
     <t>番茄-红-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/Tomato_red</t>
+    <t>Prefab/Buildings/Tomato_red</t>
   </si>
   <si>
     <t>番茄-橙-房子</t>
@@ -921,13 +1029,13 @@
     <t>番茄-黄-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/Tomato_yellow</t>
+    <t>Prefab/Buildings/Tomato_yellow</t>
   </si>
   <si>
     <t>番茄-绿-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/Tomato_green</t>
+    <t>Prefab/Buildings/Tomato_green</t>
   </si>
   <si>
     <t>番茄-青-房子</t>
@@ -945,7 +1053,7 @@
     <t>猕猴桃-房子</t>
   </si>
   <si>
-    <t>Prefab/Bulit/Kiwi</t>
+    <t>Prefab/Buildings/Kiwi</t>
   </si>
   <si>
     <t>野草-房子</t>
@@ -1141,7 +1249,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1153,14 +1261,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2329"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1190,35 +1290,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1823,137 +1895,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1980,94 +2052,63 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2396,7 +2437,7 @@
     <col min="3" max="3" width="22.8333333333333" style="6" customWidth="1"/>
     <col min="4" max="4" width="24.25" style="6" customWidth="1"/>
     <col min="5" max="5" width="8.75" style="6" customWidth="1"/>
-    <col min="6" max="6" width="28.5833333333333" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.75" style="6" customWidth="1"/>
     <col min="7" max="7" width="20.0833333333333" style="6" customWidth="1"/>
     <col min="8" max="8" width="8.91666666666667" style="6" customWidth="1"/>
     <col min="9" max="9" width="8.41666666666667" style="6" customWidth="1"/>
@@ -2429,7 +2470,7 @@
       <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="9" t="s">
@@ -2447,7 +2488,7 @@
       <c r="L1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="9" t="s">
@@ -2480,22 +2521,22 @@
       <c r="W1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="21" t="s">
+      <c r="X1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="21" t="s">
+      <c r="Y1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="21" t="s">
+      <c r="Z1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="21" t="s">
+      <c r="AA1" s="17" t="s">
         <v>26</v>
       </c>
       <c r="AB1"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:28">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2513,7 +2554,7 @@
       <c r="F2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>29</v>
       </c>
       <c r="H2" s="9" t="s">
@@ -2531,7 +2572,7 @@
       <c r="L2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="9" t="s">
         <v>30</v>
       </c>
       <c r="N2" s="9" t="s">
@@ -2579,7 +2620,7 @@
       <c r="AB2"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:28">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>32</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -2597,7 +2638,7 @@
       <c r="F3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>38</v>
       </c>
       <c r="H3" s="9" t="s">
@@ -2615,7 +2656,7 @@
       <c r="L3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>44</v>
       </c>
       <c r="N3" s="9" t="s">
@@ -2657,13 +2698,13 @@
       <c r="Z3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" s="21" t="s">
+      <c r="AA3" s="17" t="s">
         <v>57</v>
       </c>
       <c r="AB3"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:28">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2732,22 +2773,22 @@
       <c r="W4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="X4" s="22" t="s">
+      <c r="X4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="Y4" s="22" t="s">
+      <c r="Y4" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="Z4" s="22" t="s">
+      <c r="Z4" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="AA4" s="22" t="s">
+      <c r="AA4" s="18" t="s">
         <v>76</v>
       </c>
       <c r="AB4"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:28">
-      <c r="A5" s="13"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -2757,10 +2798,10 @@
       <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="15"/>
+      <c r="G5" s="13"/>
       <c r="H5" s="2">
         <v>1</v>
       </c>
@@ -2791,14 +2832,14 @@
       <c r="V5" s="2">
         <v>0</v>
       </c>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="23"/>
-      <c r="AB5" s="23"/>
+      <c r="X5" s="19"/>
+      <c r="Y5" s="19"/>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="19"/>
+      <c r="AB5" s="19"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:28">
-      <c r="A6" s="13"/>
+      <c r="A6" s="12"/>
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -2808,10 +2849,10 @@
       <c r="E6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="13"/>
       <c r="H6" s="2">
         <v>1</v>
       </c>
@@ -2842,14 +2883,14 @@
       <c r="V6" s="2">
         <v>0</v>
       </c>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:28">
-      <c r="A7" s="13"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="2">
         <v>1003</v>
       </c>
@@ -2859,10 +2900,10 @@
       <c r="E7" s="2">
         <v>1</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="13"/>
       <c r="H7" s="2">
         <v>1</v>
       </c>
@@ -2893,14 +2934,14 @@
       <c r="V7" s="2">
         <v>0</v>
       </c>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:28">
-      <c r="A8" s="13"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="2">
         <v>1004</v>
       </c>
@@ -2910,10 +2951,10 @@
       <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="15"/>
+      <c r="G8" s="13"/>
       <c r="H8" s="2">
         <v>1</v>
       </c>
@@ -2944,14 +2985,14 @@
       <c r="V8" s="2">
         <v>0</v>
       </c>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:28">
-      <c r="A9" s="13"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="2">
         <v>1005</v>
       </c>
@@ -2961,10 +3002,10 @@
       <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="13"/>
       <c r="H9" s="2">
         <v>1</v>
       </c>
@@ -2995,14 +3036,14 @@
       <c r="V9" s="2">
         <v>0</v>
       </c>
-      <c r="X9" s="23"/>
-      <c r="Y9" s="23"/>
-      <c r="Z9" s="23"/>
-      <c r="AA9" s="23"/>
-      <c r="AB9" s="23"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:28">
-      <c r="A10" s="13"/>
+      <c r="A10" s="12"/>
       <c r="B10" s="2">
         <v>1006</v>
       </c>
@@ -3012,10 +3053,10 @@
       <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="15"/>
+      <c r="G10" s="13"/>
       <c r="H10" s="2">
         <v>1</v>
       </c>
@@ -3046,14 +3087,14 @@
       <c r="V10" s="2">
         <v>0</v>
       </c>
-      <c r="X10" s="23"/>
-      <c r="Y10" s="23"/>
-      <c r="Z10" s="23"/>
-      <c r="AA10" s="23"/>
-      <c r="AB10" s="23"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:28">
-      <c r="A11" s="13"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="2">
         <v>1007</v>
       </c>
@@ -3063,10 +3104,10 @@
       <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="13"/>
       <c r="H11" s="2">
         <v>1</v>
       </c>
@@ -3097,14 +3138,14 @@
       <c r="V11" s="2">
         <v>0</v>
       </c>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="23"/>
-      <c r="AA11" s="23"/>
-      <c r="AB11" s="23"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:28">
-      <c r="A12" s="13"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="2">
         <v>1008</v>
       </c>
@@ -3114,10 +3155,10 @@
       <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="15"/>
+      <c r="G12" s="13"/>
       <c r="H12" s="2">
         <v>1</v>
       </c>
@@ -3148,14 +3189,14 @@
       <c r="V12" s="2">
         <v>0</v>
       </c>
-      <c r="X12" s="23"/>
-      <c r="Y12" s="23"/>
-      <c r="Z12" s="23"/>
-      <c r="AA12" s="23"/>
-      <c r="AB12" s="23"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:28">
-      <c r="A13" s="13"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="2">
         <v>1009</v>
       </c>
@@ -3165,10 +3206,10 @@
       <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="15"/>
+      <c r="G13" s="13"/>
       <c r="H13" s="2">
         <v>1</v>
       </c>
@@ -3199,14 +3240,14 @@
       <c r="V13" s="2">
         <v>0</v>
       </c>
-      <c r="X13" s="23"/>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
+      <c r="AA13" s="19"/>
+      <c r="AB13" s="19"/>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:28">
-      <c r="A14" s="13"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="2">
         <v>1010</v>
       </c>
@@ -3216,10 +3257,10 @@
       <c r="E14" s="2">
         <v>1</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="13"/>
       <c r="H14" s="2">
         <v>1</v>
       </c>
@@ -3250,14 +3291,14 @@
       <c r="V14" s="2">
         <v>0</v>
       </c>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
+      <c r="X14" s="19"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="19"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="19"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:28">
-      <c r="A15" s="13"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="2">
         <v>1011</v>
       </c>
@@ -3267,10 +3308,10 @@
       <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="13"/>
       <c r="H15" s="2">
         <v>1</v>
       </c>
@@ -3301,14 +3342,14 @@
       <c r="V15" s="2">
         <v>0</v>
       </c>
-      <c r="X15" s="23"/>
-      <c r="Y15" s="23"/>
-      <c r="Z15" s="23"/>
-      <c r="AA15" s="23"/>
-      <c r="AB15" s="23"/>
+      <c r="X15" s="19"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="19"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="19"/>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:28">
-      <c r="A16" s="13"/>
+      <c r="A16" s="12"/>
       <c r="B16" s="2">
         <v>1012</v>
       </c>
@@ -3318,10 +3359,10 @@
       <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="15"/>
+      <c r="G16" s="13"/>
       <c r="H16" s="2">
         <v>1</v>
       </c>
@@ -3352,14 +3393,14 @@
       <c r="V16" s="2">
         <v>0</v>
       </c>
-      <c r="X16" s="23"/>
-      <c r="Y16" s="23"/>
-      <c r="Z16" s="23"/>
-      <c r="AA16" s="23"/>
-      <c r="AB16" s="23"/>
+      <c r="X16" s="19"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="19"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="19"/>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:28">
-      <c r="A17" s="13"/>
+      <c r="A17" s="12"/>
       <c r="B17" s="2">
         <v>1013</v>
       </c>
@@ -3369,10 +3410,10 @@
       <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="G17" s="13"/>
       <c r="H17" s="2">
         <v>1</v>
       </c>
@@ -3403,11 +3444,11 @@
       <c r="V17" s="2">
         <v>0</v>
       </c>
-      <c r="X17" s="23"/>
-      <c r="Y17" s="23"/>
-      <c r="Z17" s="23"/>
-      <c r="AA17" s="23"/>
-      <c r="AB17" s="23"/>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="19"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="19"/>
     </row>
     <row r="18" s="2" customFormat="1" spans="2:28">
       <c r="B18" s="2">
@@ -3419,10 +3460,10 @@
       <c r="E18" s="2">
         <v>1</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="15"/>
+      <c r="G18" s="13"/>
       <c r="H18" s="2">
         <v>1</v>
       </c>
@@ -3453,11 +3494,11 @@
       <c r="V18" s="2">
         <v>0</v>
       </c>
-      <c r="X18" s="23"/>
-      <c r="Y18" s="23"/>
-      <c r="Z18" s="23"/>
-      <c r="AA18" s="23"/>
-      <c r="AB18" s="23"/>
+      <c r="X18" s="19"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="19"/>
+      <c r="AA18" s="19"/>
+      <c r="AB18" s="19"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="2:22">
       <c r="B19" s="3">
@@ -3466,16 +3507,16 @@
       <c r="C19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="14" t="s">
         <v>105</v>
       </c>
       <c r="E19" s="3">
         <v>2</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="14" t="s">
         <v>107</v>
       </c>
       <c r="H19" s="3">
@@ -3534,10 +3575,10 @@
       <c r="E20" s="3">
         <v>2</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="14" t="s">
         <v>113</v>
       </c>
       <c r="H20" s="3">
@@ -3579,11 +3620,11 @@
       <c r="W20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="20"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="2:28">
       <c r="B21" s="3">
@@ -3601,7 +3642,7 @@
       <c r="F21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="14" t="s">
         <v>118</v>
       </c>
       <c r="H21" s="3">
@@ -3643,11 +3684,11 @@
       <c r="W21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="14.5" customHeight="1" spans="2:28">
       <c r="B22" s="3">
@@ -3665,7 +3706,7 @@
       <c r="F22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="14" t="s">
         <v>124</v>
       </c>
       <c r="H22" s="3">
@@ -3713,11 +3754,11 @@
       <c r="W22" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="24"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="2:28">
       <c r="B23" s="3">
@@ -3735,7 +3776,7 @@
       <c r="F23" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="14" t="s">
         <v>131</v>
       </c>
       <c r="H23" s="3">
@@ -3777,11 +3818,11 @@
       <c r="W23" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="24"/>
-      <c r="AA23" s="24"/>
-      <c r="AB23" s="24"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="2:28">
       <c r="B24" s="3">
@@ -3799,7 +3840,7 @@
       <c r="F24" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="14" t="s">
         <v>137</v>
       </c>
       <c r="H24" s="3">
@@ -3841,11 +3882,11 @@
       <c r="W24" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X24" s="24"/>
-      <c r="Y24" s="24"/>
-      <c r="Z24" s="24"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="24"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="2:28">
       <c r="B25" s="3">
@@ -3863,7 +3904,7 @@
       <c r="F25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="14" t="s">
         <v>143</v>
       </c>
       <c r="H25" s="3">
@@ -3905,11 +3946,11 @@
       <c r="W25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="2:28">
       <c r="B26" s="3">
@@ -3927,7 +3968,7 @@
       <c r="F26" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="14" t="s">
         <v>146</v>
       </c>
       <c r="H26" s="3">
@@ -3969,11 +4010,11 @@
       <c r="W26" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X26" s="24"/>
-      <c r="Y26" s="24"/>
-      <c r="Z26" s="24"/>
-      <c r="AA26" s="24"/>
-      <c r="AB26" s="24"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
     </row>
     <row r="27" s="3" customFormat="1" spans="2:28">
       <c r="B27" s="3">
@@ -3991,7 +4032,7 @@
       <c r="F27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="14" t="s">
         <v>149</v>
       </c>
       <c r="H27" s="3">
@@ -4033,11 +4074,11 @@
       <c r="W27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X27" s="24"/>
-      <c r="Y27" s="24"/>
-      <c r="Z27" s="24"/>
-      <c r="AA27" s="24"/>
-      <c r="AB27" s="24"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
     </row>
     <row r="28" s="3" customFormat="1" spans="2:28">
       <c r="B28" s="3">
@@ -4055,7 +4096,7 @@
       <c r="F28" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="14" t="s">
         <v>152</v>
       </c>
       <c r="H28" s="3">
@@ -4097,11 +4138,11 @@
       <c r="W28" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X28" s="24"/>
-      <c r="Y28" s="24"/>
-      <c r="Z28" s="24"/>
-      <c r="AA28" s="24"/>
-      <c r="AB28" s="24"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
     </row>
     <row r="29" s="3" customFormat="1" spans="2:28">
       <c r="B29" s="3">
@@ -4119,7 +4160,7 @@
       <c r="F29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G29" s="16" t="s">
+      <c r="G29" s="14" t="s">
         <v>155</v>
       </c>
       <c r="H29" s="3">
@@ -4161,11 +4202,11 @@
       <c r="W29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X29" s="24"/>
-      <c r="Y29" s="24"/>
-      <c r="Z29" s="24"/>
-      <c r="AA29" s="24"/>
-      <c r="AB29" s="24"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="20"/>
+      <c r="Z29" s="20"/>
+      <c r="AA29" s="20"/>
+      <c r="AB29" s="20"/>
     </row>
     <row r="30" s="3" customFormat="1" spans="2:28">
       <c r="B30" s="3">
@@ -4183,7 +4224,7 @@
       <c r="F30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="16" t="s">
+      <c r="G30" s="14" t="s">
         <v>158</v>
       </c>
       <c r="H30" s="3">
@@ -4225,11 +4266,11 @@
       <c r="W30" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X30" s="24"/>
-      <c r="Y30" s="24"/>
-      <c r="Z30" s="24"/>
-      <c r="AA30" s="24"/>
-      <c r="AB30" s="24"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
     </row>
     <row r="31" s="3" customFormat="1" spans="2:28">
       <c r="B31" s="3">
@@ -4244,10 +4285,10 @@
       <c r="E31" s="3">
         <v>2</v>
       </c>
-      <c r="F31" s="16" t="s">
+      <c r="F31" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="14" t="s">
         <v>161</v>
       </c>
       <c r="H31" s="3">
@@ -4289,11 +4330,11 @@
       <c r="W31" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="X31" s="24"/>
-      <c r="Y31" s="24"/>
-      <c r="Z31" s="24"/>
-      <c r="AA31" s="24"/>
-      <c r="AB31" s="24"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
     </row>
     <row r="32" s="3" customFormat="1" spans="2:28">
       <c r="B32" s="3">
@@ -4308,10 +4349,10 @@
       <c r="E32" s="3">
         <v>2</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="14" t="s">
         <v>161</v>
       </c>
       <c r="H32" s="3">
@@ -4353,11 +4394,11 @@
       <c r="W32" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="X32" s="24"/>
-      <c r="Y32" s="24"/>
-      <c r="Z32" s="24"/>
-      <c r="AA32" s="24"/>
-      <c r="AB32" s="24"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
     </row>
     <row r="33" s="3" customFormat="1" spans="2:28">
       <c r="B33" s="3">
@@ -4372,10 +4413,10 @@
       <c r="E33" s="3">
         <v>2</v>
       </c>
-      <c r="F33" s="16" t="s">
+      <c r="F33" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="14" t="s">
         <v>167</v>
       </c>
       <c r="H33" s="3">
@@ -4423,11 +4464,11 @@
       <c r="W33" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="X33" s="24"/>
-      <c r="Y33" s="24"/>
-      <c r="Z33" s="24"/>
-      <c r="AA33" s="24"/>
-      <c r="AB33" s="24"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
     </row>
     <row r="34" s="3" customFormat="1" spans="2:28">
       <c r="B34" s="3">
@@ -4445,7 +4486,7 @@
       <c r="F34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="14" t="s">
         <v>173</v>
       </c>
       <c r="H34" s="3">
@@ -4487,11 +4528,11 @@
       <c r="W34" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="X34" s="24"/>
-      <c r="Y34" s="24"/>
-      <c r="Z34" s="24"/>
-      <c r="AA34" s="24"/>
-      <c r="AB34" s="24"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="20"/>
+      <c r="AB34" s="20"/>
     </row>
     <row r="35" s="3" customFormat="1" spans="2:22">
       <c r="B35" s="3">
@@ -4503,10 +4544,10 @@
       <c r="E35" s="3">
         <v>3</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G35" s="17"/>
+      <c r="G35" s="14"/>
       <c r="H35" s="3">
         <v>4</v>
       </c>
@@ -4549,10 +4590,10 @@
       <c r="E36" s="3">
         <v>3</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="F36" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="G36" s="17"/>
+      <c r="G36" s="14"/>
       <c r="H36" s="3">
         <v>4</v>
       </c>
@@ -4584,11 +4625,11 @@
       <c r="V36" s="3">
         <v>1</v>
       </c>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="24"/>
-      <c r="Z36" s="24"/>
-      <c r="AA36" s="24"/>
-      <c r="AB36" s="24"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
     </row>
     <row r="37" s="3" customFormat="1" spans="2:28">
       <c r="B37" s="3">
@@ -4634,11 +4675,11 @@
       <c r="V37" s="3">
         <v>1</v>
       </c>
-      <c r="X37" s="24"/>
-      <c r="Y37" s="24"/>
-      <c r="Z37" s="24"/>
-      <c r="AA37" s="24"/>
-      <c r="AB37" s="24"/>
+      <c r="X37" s="20"/>
+      <c r="Y37" s="20"/>
+      <c r="Z37" s="20"/>
+      <c r="AA37" s="20"/>
+      <c r="AB37" s="20"/>
     </row>
     <row r="38" s="3" customFormat="1" spans="2:28">
       <c r="B38" s="3">
@@ -4684,11 +4725,11 @@
       <c r="V38" s="3">
         <v>1</v>
       </c>
-      <c r="X38" s="24"/>
-      <c r="Y38" s="24"/>
-      <c r="Z38" s="24"/>
-      <c r="AA38" s="24"/>
-      <c r="AB38" s="24"/>
+      <c r="X38" s="20"/>
+      <c r="Y38" s="20"/>
+      <c r="Z38" s="20"/>
+      <c r="AA38" s="20"/>
+      <c r="AB38" s="20"/>
     </row>
     <row r="39" s="3" customFormat="1" spans="2:28">
       <c r="B39" s="3">
@@ -4734,17 +4775,17 @@
       <c r="V39" s="3">
         <v>1</v>
       </c>
-      <c r="X39" s="24"/>
-      <c r="Y39" s="24"/>
-      <c r="Z39" s="24"/>
-      <c r="AA39" s="24"/>
-      <c r="AB39" s="24"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
     </row>
     <row r="40" s="3" customFormat="1" spans="2:28">
       <c r="B40" s="3">
         <v>3006</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="15" t="s">
         <v>190</v>
       </c>
       <c r="E40" s="3">
@@ -4784,11 +4825,11 @@
       <c r="V40" s="3">
         <v>1</v>
       </c>
-      <c r="X40" s="24"/>
-      <c r="Y40" s="24"/>
-      <c r="Z40" s="24"/>
-      <c r="AA40" s="24"/>
-      <c r="AB40" s="24"/>
+      <c r="X40" s="20"/>
+      <c r="Y40" s="20"/>
+      <c r="Z40" s="20"/>
+      <c r="AA40" s="20"/>
+      <c r="AB40" s="20"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="2:28">
       <c r="B41" s="3">
@@ -4834,11 +4875,11 @@
       <c r="V41" s="3">
         <v>1</v>
       </c>
-      <c r="X41" s="24"/>
-      <c r="Y41" s="24"/>
-      <c r="Z41" s="24"/>
-      <c r="AA41" s="24"/>
-      <c r="AB41" s="24"/>
+      <c r="X41" s="20"/>
+      <c r="Y41" s="20"/>
+      <c r="Z41" s="20"/>
+      <c r="AA41" s="20"/>
+      <c r="AB41" s="20"/>
     </row>
     <row r="42" s="3" customFormat="1" spans="2:28">
       <c r="B42" s="3">
@@ -4884,11 +4925,11 @@
       <c r="V42" s="3">
         <v>1</v>
       </c>
-      <c r="X42" s="24"/>
-      <c r="Y42" s="24"/>
-      <c r="Z42" s="24"/>
-      <c r="AA42" s="24"/>
-      <c r="AB42" s="24"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="20"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
     </row>
     <row r="43" s="3" customFormat="1" spans="2:28">
       <c r="B43" s="3">
@@ -4934,11 +4975,11 @@
       <c r="V43" s="3">
         <v>1</v>
       </c>
-      <c r="X43" s="24"/>
-      <c r="Y43" s="24"/>
-      <c r="Z43" s="24"/>
-      <c r="AA43" s="24"/>
-      <c r="AB43" s="24"/>
+      <c r="X43" s="20"/>
+      <c r="Y43" s="20"/>
+      <c r="Z43" s="20"/>
+      <c r="AA43" s="20"/>
+      <c r="AB43" s="20"/>
     </row>
     <row r="44" s="3" customFormat="1" spans="2:28">
       <c r="B44" s="3">
@@ -4984,11 +5025,11 @@
       <c r="V44" s="3">
         <v>1</v>
       </c>
-      <c r="X44" s="24"/>
-      <c r="Y44" s="24"/>
-      <c r="Z44" s="24"/>
-      <c r="AA44" s="24"/>
-      <c r="AB44" s="24"/>
+      <c r="X44" s="20"/>
+      <c r="Y44" s="20"/>
+      <c r="Z44" s="20"/>
+      <c r="AA44" s="20"/>
+      <c r="AB44" s="20"/>
     </row>
     <row r="45" s="3" customFormat="1" spans="2:28">
       <c r="B45" s="3">
@@ -5034,11 +5075,11 @@
       <c r="V45" s="3">
         <v>1</v>
       </c>
-      <c r="X45" s="24"/>
-      <c r="Y45" s="24"/>
-      <c r="Z45" s="24"/>
-      <c r="AA45" s="24"/>
-      <c r="AB45" s="24"/>
+      <c r="X45" s="20"/>
+      <c r="Y45" s="20"/>
+      <c r="Z45" s="20"/>
+      <c r="AA45" s="20"/>
+      <c r="AB45" s="20"/>
     </row>
     <row r="46" s="3" customFormat="1" spans="2:28">
       <c r="B46" s="3">
@@ -5084,11 +5125,11 @@
       <c r="V46" s="3">
         <v>1</v>
       </c>
-      <c r="X46" s="24"/>
-      <c r="Y46" s="24"/>
-      <c r="Z46" s="24"/>
-      <c r="AA46" s="24"/>
-      <c r="AB46" s="24"/>
+      <c r="X46" s="20"/>
+      <c r="Y46" s="20"/>
+      <c r="Z46" s="20"/>
+      <c r="AA46" s="20"/>
+      <c r="AB46" s="20"/>
     </row>
     <row r="47" s="3" customFormat="1" spans="2:28">
       <c r="B47" s="3">
@@ -5100,10 +5141,10 @@
       <c r="E47" s="3">
         <v>3</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="G47" s="17"/>
+      <c r="G47" s="14"/>
       <c r="H47" s="3">
         <v>4</v>
       </c>
@@ -5135,11 +5176,11 @@
       <c r="V47" s="3">
         <v>1</v>
       </c>
-      <c r="X47" s="24"/>
-      <c r="Y47" s="24"/>
-      <c r="Z47" s="24"/>
-      <c r="AA47" s="24"/>
-      <c r="AB47" s="24"/>
+      <c r="X47" s="20"/>
+      <c r="Y47" s="20"/>
+      <c r="Z47" s="20"/>
+      <c r="AA47" s="20"/>
+      <c r="AB47" s="20"/>
     </row>
     <row r="48" s="3" customFormat="1" spans="2:28">
       <c r="B48" s="3">
@@ -5151,10 +5192,10 @@
       <c r="E48" s="3">
         <v>3</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F48" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="G48" s="17"/>
+      <c r="G48" s="14"/>
       <c r="H48" s="3">
         <v>4</v>
       </c>
@@ -5186,11 +5227,11 @@
       <c r="V48" s="3">
         <v>1</v>
       </c>
-      <c r="X48" s="24"/>
-      <c r="Y48" s="24"/>
-      <c r="Z48" s="24"/>
-      <c r="AA48" s="24"/>
-      <c r="AB48" s="24"/>
+      <c r="X48" s="20"/>
+      <c r="Y48" s="20"/>
+      <c r="Z48" s="20"/>
+      <c r="AA48" s="20"/>
+      <c r="AB48" s="20"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="2:28">
       <c r="B49" s="3">
@@ -5236,11 +5277,11 @@
       <c r="V49" s="3">
         <v>1</v>
       </c>
-      <c r="X49" s="24"/>
-      <c r="Y49" s="24"/>
-      <c r="Z49" s="24"/>
-      <c r="AA49" s="24"/>
-      <c r="AB49" s="24"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
     </row>
     <row r="50" s="4" customFormat="1" spans="2:22">
       <c r="B50" s="4">
@@ -5252,10 +5293,10 @@
       <c r="E50" s="4">
         <v>4</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="F50" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="G50" s="20"/>
+      <c r="G50" s="16"/>
       <c r="H50" s="4">
         <v>0.5</v>
       </c>
@@ -5297,10 +5338,10 @@
       <c r="E51" s="4">
         <v>4</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="F51" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="G51" s="20"/>
+      <c r="G51" s="16"/>
       <c r="H51" s="4">
         <v>0.5</v>
       </c>
@@ -5331,11 +5372,11 @@
       <c r="V51" s="4">
         <v>1</v>
       </c>
-      <c r="X51" s="25"/>
-      <c r="Y51" s="25"/>
-      <c r="Z51" s="25"/>
-      <c r="AA51" s="25"/>
-      <c r="AB51" s="25"/>
+      <c r="X51" s="21"/>
+      <c r="Y51" s="21"/>
+      <c r="Z51" s="21"/>
+      <c r="AA51" s="21"/>
+      <c r="AB51" s="21"/>
     </row>
     <row r="52" s="4" customFormat="1" spans="2:28">
       <c r="B52" s="4">
@@ -5380,11 +5421,11 @@
       <c r="V52" s="4">
         <v>1</v>
       </c>
-      <c r="X52" s="25"/>
-      <c r="Y52" s="25"/>
-      <c r="Z52" s="25"/>
-      <c r="AA52" s="25"/>
-      <c r="AB52" s="25"/>
+      <c r="X52" s="21"/>
+      <c r="Y52" s="21"/>
+      <c r="Z52" s="21"/>
+      <c r="AA52" s="21"/>
+      <c r="AB52" s="21"/>
     </row>
     <row r="53" s="4" customFormat="1" spans="2:28">
       <c r="B53" s="4">
@@ -5429,11 +5470,11 @@
       <c r="V53" s="4">
         <v>1</v>
       </c>
-      <c r="X53" s="25"/>
-      <c r="Y53" s="25"/>
-      <c r="Z53" s="25"/>
-      <c r="AA53" s="25"/>
-      <c r="AB53" s="25"/>
+      <c r="X53" s="21"/>
+      <c r="Y53" s="21"/>
+      <c r="Z53" s="21"/>
+      <c r="AA53" s="21"/>
+      <c r="AB53" s="21"/>
     </row>
     <row r="54" s="4" customFormat="1" spans="2:28">
       <c r="B54" s="4">
@@ -5478,11 +5519,11 @@
       <c r="V54" s="4">
         <v>1</v>
       </c>
-      <c r="X54" s="25"/>
-      <c r="Y54" s="25"/>
-      <c r="Z54" s="25"/>
-      <c r="AA54" s="25"/>
-      <c r="AB54" s="25"/>
+      <c r="X54" s="21"/>
+      <c r="Y54" s="21"/>
+      <c r="Z54" s="21"/>
+      <c r="AA54" s="21"/>
+      <c r="AB54" s="21"/>
     </row>
     <row r="55" s="4" customFormat="1" spans="2:28">
       <c r="B55" s="4">
@@ -5527,11 +5568,11 @@
       <c r="V55" s="4">
         <v>1</v>
       </c>
-      <c r="X55" s="25"/>
-      <c r="Y55" s="25"/>
-      <c r="Z55" s="25"/>
-      <c r="AA55" s="25"/>
-      <c r="AB55" s="25"/>
+      <c r="X55" s="21"/>
+      <c r="Y55" s="21"/>
+      <c r="Z55" s="21"/>
+      <c r="AA55" s="21"/>
+      <c r="AB55" s="21"/>
     </row>
     <row r="56" s="4" customFormat="1" spans="2:28">
       <c r="B56" s="4">
@@ -5576,11 +5617,11 @@
       <c r="V56" s="4">
         <v>1</v>
       </c>
-      <c r="X56" s="25"/>
-      <c r="Y56" s="25"/>
-      <c r="Z56" s="25"/>
-      <c r="AA56" s="25"/>
-      <c r="AB56" s="25"/>
+      <c r="X56" s="21"/>
+      <c r="Y56" s="21"/>
+      <c r="Z56" s="21"/>
+      <c r="AA56" s="21"/>
+      <c r="AB56" s="21"/>
     </row>
     <row r="57" s="4" customFormat="1" spans="2:28">
       <c r="B57" s="4">
@@ -5625,11 +5666,11 @@
       <c r="V57" s="4">
         <v>1</v>
       </c>
-      <c r="X57" s="25"/>
-      <c r="Y57" s="25"/>
-      <c r="Z57" s="25"/>
-      <c r="AA57" s="25"/>
-      <c r="AB57" s="25"/>
+      <c r="X57" s="21"/>
+      <c r="Y57" s="21"/>
+      <c r="Z57" s="21"/>
+      <c r="AA57" s="21"/>
+      <c r="AB57" s="21"/>
     </row>
     <row r="58" s="4" customFormat="1" spans="2:28">
       <c r="B58" s="4">
@@ -5674,11 +5715,11 @@
       <c r="V58" s="4">
         <v>1</v>
       </c>
-      <c r="X58" s="25"/>
-      <c r="Y58" s="25"/>
-      <c r="Z58" s="25"/>
-      <c r="AA58" s="25"/>
-      <c r="AB58" s="25"/>
+      <c r="X58" s="21"/>
+      <c r="Y58" s="21"/>
+      <c r="Z58" s="21"/>
+      <c r="AA58" s="21"/>
+      <c r="AB58" s="21"/>
     </row>
     <row r="59" s="4" customFormat="1" spans="2:28">
       <c r="B59" s="4">
@@ -5723,11 +5764,11 @@
       <c r="V59" s="4">
         <v>1</v>
       </c>
-      <c r="X59" s="25"/>
-      <c r="Y59" s="25"/>
-      <c r="Z59" s="25"/>
-      <c r="AA59" s="25"/>
-      <c r="AB59" s="25"/>
+      <c r="X59" s="21"/>
+      <c r="Y59" s="21"/>
+      <c r="Z59" s="21"/>
+      <c r="AA59" s="21"/>
+      <c r="AB59" s="21"/>
     </row>
     <row r="60" s="4" customFormat="1" spans="2:28">
       <c r="B60" s="4">
@@ -5772,11 +5813,11 @@
       <c r="V60" s="4">
         <v>1</v>
       </c>
-      <c r="X60" s="25"/>
-      <c r="Y60" s="25"/>
-      <c r="Z60" s="25"/>
-      <c r="AA60" s="25"/>
-      <c r="AB60" s="25"/>
+      <c r="X60" s="21"/>
+      <c r="Y60" s="21"/>
+      <c r="Z60" s="21"/>
+      <c r="AA60" s="21"/>
+      <c r="AB60" s="21"/>
     </row>
     <row r="61" s="4" customFormat="1" spans="2:28">
       <c r="B61" s="4">
@@ -5821,11 +5862,11 @@
       <c r="V61" s="4">
         <v>1</v>
       </c>
-      <c r="X61" s="25"/>
-      <c r="Y61" s="25"/>
-      <c r="Z61" s="25"/>
-      <c r="AA61" s="25"/>
-      <c r="AB61" s="25"/>
+      <c r="X61" s="21"/>
+      <c r="Y61" s="21"/>
+      <c r="Z61" s="21"/>
+      <c r="AA61" s="21"/>
+      <c r="AB61" s="21"/>
     </row>
     <row r="62" s="4" customFormat="1" spans="2:28">
       <c r="B62" s="4">
@@ -5837,10 +5878,10 @@
       <c r="E62" s="4">
         <v>4</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F62" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="G62" s="20"/>
+      <c r="G62" s="16"/>
       <c r="H62" s="4">
         <v>0.5</v>
       </c>
@@ -5871,11 +5912,11 @@
       <c r="V62" s="4">
         <v>1</v>
       </c>
-      <c r="X62" s="25"/>
-      <c r="Y62" s="25"/>
-      <c r="Z62" s="25"/>
-      <c r="AA62" s="25"/>
-      <c r="AB62" s="25"/>
+      <c r="X62" s="21"/>
+      <c r="Y62" s="21"/>
+      <c r="Z62" s="21"/>
+      <c r="AA62" s="21"/>
+      <c r="AB62" s="21"/>
     </row>
     <row r="63" s="4" customFormat="1" spans="2:28">
       <c r="B63" s="4">
@@ -5887,10 +5928,10 @@
       <c r="E63" s="4">
         <v>4</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="F63" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="G63" s="20"/>
+      <c r="G63" s="16"/>
       <c r="H63" s="4">
         <v>0.5</v>
       </c>
@@ -5921,11 +5962,11 @@
       <c r="V63" s="4">
         <v>1</v>
       </c>
-      <c r="X63" s="25"/>
-      <c r="Y63" s="25"/>
-      <c r="Z63" s="25"/>
-      <c r="AA63" s="25"/>
-      <c r="AB63" s="25"/>
+      <c r="X63" s="21"/>
+      <c r="Y63" s="21"/>
+      <c r="Z63" s="21"/>
+      <c r="AA63" s="21"/>
+      <c r="AB63" s="21"/>
     </row>
     <row r="64" s="4" customFormat="1" spans="2:28">
       <c r="B64" s="4">
@@ -5970,11 +6011,11 @@
       <c r="V64" s="4">
         <v>1</v>
       </c>
-      <c r="X64" s="25"/>
-      <c r="Y64" s="25"/>
-      <c r="Z64" s="25"/>
-      <c r="AA64" s="25"/>
-      <c r="AB64" s="25"/>
+      <c r="X64" s="21"/>
+      <c r="Y64" s="21"/>
+      <c r="Z64" s="21"/>
+      <c r="AA64" s="21"/>
+      <c r="AB64" s="21"/>
     </row>
     <row r="65" s="3" customFormat="1" spans="2:23">
       <c r="B65" s="3">
@@ -5986,10 +6027,10 @@
       <c r="E65" s="3">
         <v>5</v>
       </c>
-      <c r="F65" s="26" t="s">
+      <c r="F65" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="G65" s="27"/>
+      <c r="G65" s="22"/>
       <c r="H65" s="3">
         <v>1</v>
       </c>
@@ -6072,32 +6113,32 @@
       </c>
     </row>
     <row r="67" s="3" customFormat="1" spans="1:28">
-      <c r="A67" s="28"/>
+      <c r="A67" s="23"/>
       <c r="B67" s="3">
         <v>5003</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="D67" s="28"/>
+      <c r="D67" s="23"/>
       <c r="E67" s="3">
         <v>5</v>
       </c>
-      <c r="F67" s="28" t="s">
+      <c r="F67" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="G67" s="29"/>
-      <c r="H67" s="28">
-        <v>1</v>
-      </c>
-      <c r="I67" s="35"/>
+      <c r="G67" s="23"/>
+      <c r="H67" s="23">
+        <v>1</v>
+      </c>
+      <c r="I67" s="27"/>
       <c r="J67" s="3">
         <v>0</v>
       </c>
       <c r="K67" s="3">
         <v>0</v>
       </c>
-      <c r="L67" s="28">
+      <c r="L67" s="23">
         <v>0</v>
       </c>
       <c r="M67" s="3">
@@ -6112,48 +6153,48 @@
       <c r="P67" s="3">
         <v>1</v>
       </c>
-      <c r="Q67" s="28"/>
-      <c r="R67" s="28"/>
-      <c r="S67" s="28"/>
-      <c r="T67" s="28"/>
-      <c r="U67" s="28"/>
+      <c r="Q67" s="23"/>
+      <c r="R67" s="23"/>
+      <c r="S67" s="23"/>
+      <c r="T67" s="23"/>
+      <c r="U67" s="23"/>
       <c r="V67" s="3">
         <v>0</v>
       </c>
-      <c r="W67" s="28"/>
-      <c r="X67" s="24"/>
-      <c r="Y67" s="24"/>
-      <c r="Z67" s="24"/>
-      <c r="AA67" s="24"/>
-      <c r="AB67" s="24"/>
+      <c r="W67" s="23"/>
+      <c r="X67" s="20"/>
+      <c r="Y67" s="20"/>
+      <c r="Z67" s="20"/>
+      <c r="AA67" s="20"/>
+      <c r="AB67" s="20"/>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:28">
-      <c r="A68" s="28"/>
+      <c r="A68" s="23"/>
       <c r="B68" s="3">
         <v>5004</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D68" s="28"/>
+      <c r="D68" s="23"/>
       <c r="E68" s="3">
         <v>5</v>
       </c>
-      <c r="F68" s="28" t="s">
+      <c r="F68" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="G68" s="29"/>
-      <c r="H68" s="28">
-        <v>1</v>
-      </c>
-      <c r="I68" s="35"/>
+      <c r="G68" s="23"/>
+      <c r="H68" s="23">
+        <v>1</v>
+      </c>
+      <c r="I68" s="27"/>
       <c r="J68" s="3">
         <v>0</v>
       </c>
       <c r="K68" s="3">
         <v>1</v>
       </c>
-      <c r="L68" s="28">
+      <c r="L68" s="23">
         <v>0</v>
       </c>
       <c r="M68" s="3">
@@ -6168,48 +6209,48 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="28"/>
-      <c r="R68" s="28"/>
-      <c r="S68" s="28"/>
-      <c r="T68" s="28"/>
-      <c r="U68" s="28"/>
+      <c r="Q68" s="23"/>
+      <c r="R68" s="23"/>
+      <c r="S68" s="23"/>
+      <c r="T68" s="23"/>
+      <c r="U68" s="23"/>
       <c r="V68" s="3">
         <v>0</v>
       </c>
-      <c r="W68" s="28"/>
-      <c r="X68" s="24"/>
-      <c r="Y68" s="24"/>
-      <c r="Z68" s="24"/>
-      <c r="AA68" s="24"/>
-      <c r="AB68" s="24"/>
+      <c r="W68" s="23"/>
+      <c r="X68" s="20"/>
+      <c r="Y68" s="20"/>
+      <c r="Z68" s="20"/>
+      <c r="AA68" s="20"/>
+      <c r="AB68" s="20"/>
     </row>
     <row r="69" s="5" customFormat="1" spans="1:28">
-      <c r="A69" s="30"/>
+      <c r="A69" s="24"/>
       <c r="B69" s="5">
         <v>5005</v>
       </c>
-      <c r="C69" s="31" t="s">
+      <c r="C69" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="D69" s="30"/>
+      <c r="D69" s="24"/>
       <c r="E69" s="5">
         <v>5</v>
       </c>
-      <c r="F69" s="30" t="s">
+      <c r="F69" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="G69" s="32"/>
-      <c r="H69" s="30">
-        <v>1</v>
-      </c>
-      <c r="I69" s="36"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24">
+        <v>1</v>
+      </c>
+      <c r="I69" s="28"/>
       <c r="J69" s="5">
         <v>0</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
       </c>
-      <c r="L69" s="30">
+      <c r="L69" s="24">
         <v>1</v>
       </c>
       <c r="M69" s="5">
@@ -6224,48 +6265,48 @@
       <c r="P69" s="5">
         <v>1</v>
       </c>
-      <c r="Q69" s="30"/>
-      <c r="R69" s="30"/>
-      <c r="S69" s="30"/>
-      <c r="T69" s="30"/>
-      <c r="U69" s="30"/>
+      <c r="Q69" s="24"/>
+      <c r="R69" s="24"/>
+      <c r="S69" s="24"/>
+      <c r="T69" s="24"/>
+      <c r="U69" s="24"/>
       <c r="V69" s="5">
         <v>0</v>
       </c>
-      <c r="W69" s="30"/>
-      <c r="X69" s="31"/>
-      <c r="Y69" s="31"/>
-      <c r="Z69" s="31"/>
-      <c r="AA69" s="31"/>
-      <c r="AB69" s="31"/>
+      <c r="W69" s="24"/>
+      <c r="X69" s="25"/>
+      <c r="Y69" s="25"/>
+      <c r="Z69" s="25"/>
+      <c r="AA69" s="25"/>
+      <c r="AB69" s="25"/>
     </row>
     <row r="70" s="3" customFormat="1" spans="1:28">
-      <c r="A70" s="28"/>
+      <c r="A70" s="23"/>
       <c r="B70" s="3">
         <v>5006</v>
       </c>
-      <c r="C70" s="24" t="s">
+      <c r="C70" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="D70" s="28"/>
+      <c r="D70" s="23"/>
       <c r="E70" s="3">
         <v>5</v>
       </c>
-      <c r="F70" s="28" t="s">
+      <c r="F70" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="G70" s="29"/>
-      <c r="H70" s="28">
-        <v>1</v>
-      </c>
-      <c r="I70" s="35"/>
+      <c r="G70" s="23"/>
+      <c r="H70" s="23">
+        <v>1</v>
+      </c>
+      <c r="I70" s="27"/>
       <c r="J70" s="3">
         <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="28">
+      <c r="L70" s="23">
         <v>1</v>
       </c>
       <c r="M70" s="3">
@@ -6280,48 +6321,48 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="28"/>
-      <c r="R70" s="28"/>
-      <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
-      <c r="U70" s="28"/>
+      <c r="Q70" s="23"/>
+      <c r="R70" s="23"/>
+      <c r="S70" s="23"/>
+      <c r="T70" s="23"/>
+      <c r="U70" s="23"/>
       <c r="V70" s="3">
         <v>0</v>
       </c>
-      <c r="W70" s="28"/>
-      <c r="X70" s="24"/>
-      <c r="Y70" s="24"/>
-      <c r="Z70" s="24"/>
-      <c r="AA70" s="24"/>
-      <c r="AB70" s="24"/>
+      <c r="W70" s="23"/>
+      <c r="X70" s="20"/>
+      <c r="Y70" s="20"/>
+      <c r="Z70" s="20"/>
+      <c r="AA70" s="20"/>
+      <c r="AB70" s="20"/>
     </row>
     <row r="71" s="3" customFormat="1" spans="1:28">
-      <c r="A71" s="28"/>
+      <c r="A71" s="23"/>
       <c r="B71" s="3">
         <v>5007</v>
       </c>
-      <c r="C71" s="24" t="s">
+      <c r="C71" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="D71" s="28"/>
+      <c r="D71" s="23"/>
       <c r="E71" s="3">
         <v>5</v>
       </c>
-      <c r="F71" s="28" t="s">
+      <c r="F71" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="G71" s="29"/>
-      <c r="H71" s="28">
-        <v>1</v>
-      </c>
-      <c r="I71" s="35"/>
+      <c r="G71" s="23"/>
+      <c r="H71" s="23">
+        <v>1</v>
+      </c>
+      <c r="I71" s="27"/>
       <c r="J71" s="3">
         <v>0</v>
       </c>
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="28">
+      <c r="L71" s="23">
         <v>0</v>
       </c>
       <c r="M71" s="3">
@@ -6336,48 +6377,48 @@
       <c r="P71" s="3">
         <v>1</v>
       </c>
-      <c r="Q71" s="28"/>
-      <c r="R71" s="28"/>
-      <c r="S71" s="28"/>
-      <c r="T71" s="28"/>
-      <c r="U71" s="28"/>
+      <c r="Q71" s="23"/>
+      <c r="R71" s="23"/>
+      <c r="S71" s="23"/>
+      <c r="T71" s="23"/>
+      <c r="U71" s="23"/>
       <c r="V71" s="3">
         <v>0</v>
       </c>
-      <c r="W71" s="28"/>
-      <c r="X71" s="24"/>
-      <c r="Y71" s="24"/>
-      <c r="Z71" s="24"/>
-      <c r="AA71" s="24"/>
-      <c r="AB71" s="24"/>
+      <c r="W71" s="23"/>
+      <c r="X71" s="20"/>
+      <c r="Y71" s="20"/>
+      <c r="Z71" s="20"/>
+      <c r="AA71" s="20"/>
+      <c r="AB71" s="20"/>
     </row>
     <row r="72" s="3" customFormat="1" spans="1:28">
-      <c r="A72" s="28"/>
+      <c r="A72" s="23"/>
       <c r="B72" s="3">
         <v>5008</v>
       </c>
-      <c r="C72" s="24" t="s">
+      <c r="C72" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="D72" s="28"/>
+      <c r="D72" s="23"/>
       <c r="E72" s="3">
         <v>5</v>
       </c>
-      <c r="F72" s="28" t="s">
+      <c r="F72" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="G72" s="29"/>
-      <c r="H72" s="28">
-        <v>1</v>
-      </c>
-      <c r="I72" s="35"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="23">
+        <v>1</v>
+      </c>
+      <c r="I72" s="27"/>
       <c r="J72" s="3">
         <v>0</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
       </c>
-      <c r="L72" s="28">
+      <c r="L72" s="23">
         <v>0</v>
       </c>
       <c r="M72" s="3">
@@ -6392,23 +6433,23 @@
       <c r="P72" s="3">
         <v>1</v>
       </c>
-      <c r="Q72" s="28"/>
-      <c r="R72" s="28"/>
-      <c r="S72" s="28"/>
-      <c r="T72" s="28"/>
-      <c r="U72" s="28"/>
+      <c r="Q72" s="23"/>
+      <c r="R72" s="23"/>
+      <c r="S72" s="23"/>
+      <c r="T72" s="23"/>
+      <c r="U72" s="23"/>
       <c r="V72" s="3">
         <v>0</v>
       </c>
-      <c r="W72" s="28"/>
-      <c r="X72" s="24"/>
-      <c r="Y72" s="24"/>
-      <c r="Z72" s="24"/>
-      <c r="AA72" s="24"/>
-      <c r="AB72" s="24"/>
+      <c r="W72" s="23"/>
+      <c r="X72" s="20"/>
+      <c r="Y72" s="20"/>
+      <c r="Z72" s="20"/>
+      <c r="AA72" s="20"/>
+      <c r="AB72" s="20"/>
     </row>
     <row r="73" s="5" customFormat="1" spans="2:22">
-      <c r="B73" s="33">
+      <c r="B73" s="26">
         <v>5009</v>
       </c>
       <c r="C73" s="5" t="s">
@@ -6417,14 +6458,14 @@
       <c r="E73" s="5">
         <v>5</v>
       </c>
-      <c r="F73" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G73" s="34"/>
-      <c r="H73" s="30">
-        <v>1</v>
-      </c>
-      <c r="I73" s="36"/>
+      <c r="F73" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="G73" s="26"/>
+      <c r="H73" s="24">
+        <v>1</v>
+      </c>
+      <c r="I73" s="28"/>
       <c r="J73" s="5">
         <v>0</v>
       </c>
@@ -6454,23 +6495,23 @@
       </c>
     </row>
     <row r="74" s="5" customFormat="1" spans="2:22">
-      <c r="B74" s="33">
+      <c r="B74" s="26">
         <v>5010</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E74" s="5">
         <v>5</v>
       </c>
-      <c r="F74" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G74" s="34"/>
-      <c r="H74" s="30">
-        <v>1</v>
-      </c>
-      <c r="I74" s="36"/>
+      <c r="F74" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="G74" s="26"/>
+      <c r="H74" s="24">
+        <v>1</v>
+      </c>
+      <c r="I74" s="28"/>
       <c r="J74" s="5">
         <v>0</v>
       </c>
@@ -6500,23 +6541,23 @@
       </c>
     </row>
     <row r="75" s="5" customFormat="1" spans="2:22">
-      <c r="B75" s="33">
+      <c r="B75" s="26">
         <v>5011</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E75" s="5">
         <v>5</v>
       </c>
-      <c r="F75" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G75" s="34"/>
-      <c r="H75" s="30">
-        <v>1</v>
-      </c>
-      <c r="I75" s="36"/>
+      <c r="F75" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="G75" s="26"/>
+      <c r="H75" s="24">
+        <v>1</v>
+      </c>
+      <c r="I75" s="28"/>
       <c r="J75" s="5">
         <v>0</v>
       </c>
@@ -6546,23 +6587,23 @@
       </c>
     </row>
     <row r="76" s="5" customFormat="1" spans="2:22">
-      <c r="B76" s="33">
+      <c r="B76" s="26">
         <v>5012</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E76" s="5">
         <v>5</v>
       </c>
-      <c r="F76" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G76" s="34"/>
-      <c r="H76" s="30">
-        <v>1</v>
-      </c>
-      <c r="I76" s="36"/>
+      <c r="F76" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="G76" s="26"/>
+      <c r="H76" s="24">
+        <v>1</v>
+      </c>
+      <c r="I76" s="28"/>
       <c r="J76" s="5">
         <v>0</v>
       </c>
@@ -6592,23 +6633,23 @@
       </c>
     </row>
     <row r="77" s="5" customFormat="1" spans="2:22">
-      <c r="B77" s="33">
+      <c r="B77" s="26">
         <v>5013</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E77" s="5">
         <v>5</v>
       </c>
-      <c r="F77" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G77" s="34"/>
-      <c r="H77" s="30">
-        <v>1</v>
-      </c>
-      <c r="I77" s="36"/>
+      <c r="F77" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="G77" s="26"/>
+      <c r="H77" s="24">
+        <v>1</v>
+      </c>
+      <c r="I77" s="28"/>
       <c r="J77" s="5">
         <v>0</v>
       </c>
@@ -6638,23 +6679,23 @@
       </c>
     </row>
     <row r="78" s="5" customFormat="1" spans="2:22">
-      <c r="B78" s="33">
+      <c r="B78" s="26">
         <v>5014</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E78" s="5">
         <v>5</v>
       </c>
-      <c r="F78" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G78" s="34"/>
-      <c r="H78" s="30">
-        <v>1</v>
-      </c>
-      <c r="I78" s="36"/>
+      <c r="F78" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="G78" s="26"/>
+      <c r="H78" s="24">
+        <v>1</v>
+      </c>
+      <c r="I78" s="28"/>
       <c r="J78" s="5">
         <v>0</v>
       </c>
@@ -6684,23 +6725,23 @@
       </c>
     </row>
     <row r="79" s="5" customFormat="1" spans="2:22">
-      <c r="B79" s="33">
+      <c r="B79" s="26">
         <v>5015</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E79" s="5">
         <v>5</v>
       </c>
-      <c r="F79" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G79" s="34"/>
-      <c r="H79" s="30">
-        <v>1</v>
-      </c>
-      <c r="I79" s="36"/>
+      <c r="F79" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="G79" s="26"/>
+      <c r="H79" s="24">
+        <v>1</v>
+      </c>
+      <c r="I79" s="28"/>
       <c r="J79" s="5">
         <v>0</v>
       </c>
@@ -6730,23 +6771,23 @@
       </c>
     </row>
     <row r="80" s="5" customFormat="1" spans="2:22">
-      <c r="B80" s="33">
+      <c r="B80" s="26">
         <v>5016</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E80" s="5">
         <v>5</v>
       </c>
-      <c r="F80" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G80" s="34"/>
-      <c r="H80" s="30">
-        <v>1</v>
-      </c>
-      <c r="I80" s="36"/>
+      <c r="F80" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="G80" s="26"/>
+      <c r="H80" s="24">
+        <v>1</v>
+      </c>
+      <c r="I80" s="28"/>
       <c r="J80" s="5">
         <v>0</v>
       </c>
@@ -6776,23 +6817,23 @@
       </c>
     </row>
     <row r="81" s="5" customFormat="1" spans="2:22">
-      <c r="B81" s="33">
+      <c r="B81" s="26">
         <v>5017</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E81" s="5">
         <v>5</v>
       </c>
-      <c r="F81" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G81" s="34"/>
-      <c r="H81" s="30">
-        <v>1</v>
-      </c>
-      <c r="I81" s="36"/>
+      <c r="F81" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="G81" s="26"/>
+      <c r="H81" s="24">
+        <v>1</v>
+      </c>
+      <c r="I81" s="28"/>
       <c r="J81" s="5">
         <v>0</v>
       </c>
@@ -6822,23 +6863,23 @@
       </c>
     </row>
     <row r="82" s="5" customFormat="1" spans="2:22">
-      <c r="B82" s="33">
+      <c r="B82" s="26">
         <v>5018</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E82" s="5">
         <v>5</v>
       </c>
-      <c r="F82" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G82" s="34"/>
-      <c r="H82" s="30">
-        <v>1</v>
-      </c>
-      <c r="I82" s="36"/>
+      <c r="F82" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="G82" s="26"/>
+      <c r="H82" s="24">
+        <v>1</v>
+      </c>
+      <c r="I82" s="28"/>
       <c r="J82" s="5">
         <v>0</v>
       </c>
@@ -6868,23 +6909,23 @@
       </c>
     </row>
     <row r="83" s="5" customFormat="1" spans="2:22">
-      <c r="B83" s="33">
+      <c r="B83" s="26">
         <v>5019</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E83" s="5">
         <v>5</v>
       </c>
-      <c r="F83" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G83" s="34"/>
-      <c r="H83" s="30">
-        <v>1</v>
-      </c>
-      <c r="I83" s="36"/>
+      <c r="F83" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G83" s="26"/>
+      <c r="H83" s="24">
+        <v>1</v>
+      </c>
+      <c r="I83" s="28"/>
       <c r="J83" s="5">
         <v>0</v>
       </c>
@@ -6914,23 +6955,23 @@
       </c>
     </row>
     <row r="84" s="5" customFormat="1" spans="2:22">
-      <c r="B84" s="33">
+      <c r="B84" s="26">
         <v>5020</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E84" s="5">
         <v>5</v>
       </c>
-      <c r="F84" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G84" s="34"/>
-      <c r="H84" s="30">
-        <v>1</v>
-      </c>
-      <c r="I84" s="36"/>
+      <c r="F84" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="G84" s="26"/>
+      <c r="H84" s="24">
+        <v>1</v>
+      </c>
+      <c r="I84" s="28"/>
       <c r="J84" s="5">
         <v>0</v>
       </c>
@@ -6960,23 +7001,23 @@
       </c>
     </row>
     <row r="85" s="5" customFormat="1" spans="2:22">
-      <c r="B85" s="33">
+      <c r="B85" s="26">
         <v>5021</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="E85" s="5">
         <v>5</v>
       </c>
-      <c r="F85" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G85" s="34"/>
-      <c r="H85" s="30">
-        <v>1</v>
-      </c>
-      <c r="I85" s="36"/>
+      <c r="F85" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="G85" s="26"/>
+      <c r="H85" s="24">
+        <v>1</v>
+      </c>
+      <c r="I85" s="28"/>
       <c r="J85" s="5">
         <v>0</v>
       </c>
@@ -7006,23 +7047,23 @@
       </c>
     </row>
     <row r="86" s="5" customFormat="1" spans="2:22">
-      <c r="B86" s="33">
+      <c r="B86" s="26">
         <v>5022</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="E86" s="5">
         <v>5</v>
       </c>
-      <c r="F86" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G86" s="34"/>
-      <c r="H86" s="30">
-        <v>1</v>
-      </c>
-      <c r="I86" s="36"/>
+      <c r="F86" s="26" t="s">
+        <v>274</v>
+      </c>
+      <c r="G86" s="26"/>
+      <c r="H86" s="24">
+        <v>1</v>
+      </c>
+      <c r="I86" s="28"/>
       <c r="J86" s="5">
         <v>0</v>
       </c>
@@ -7052,23 +7093,23 @@
       </c>
     </row>
     <row r="87" s="5" customFormat="1" spans="2:22">
-      <c r="B87" s="33">
+      <c r="B87" s="26">
         <v>5023</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="E87" s="5">
         <v>5</v>
       </c>
-      <c r="F87" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G87" s="34"/>
-      <c r="H87" s="30">
-        <v>1</v>
-      </c>
-      <c r="I87" s="36"/>
+      <c r="F87" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="G87" s="26"/>
+      <c r="H87" s="24">
+        <v>1</v>
+      </c>
+      <c r="I87" s="28"/>
       <c r="J87" s="5">
         <v>0</v>
       </c>
@@ -7098,23 +7139,23 @@
       </c>
     </row>
     <row r="88" s="5" customFormat="1" spans="2:22">
-      <c r="B88" s="33">
+      <c r="B88" s="26">
         <v>5024</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="E88" s="5">
         <v>5</v>
       </c>
-      <c r="F88" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G88" s="34"/>
-      <c r="H88" s="30">
-        <v>1</v>
-      </c>
-      <c r="I88" s="36"/>
+      <c r="F88" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="G88" s="26"/>
+      <c r="H88" s="24">
+        <v>1</v>
+      </c>
+      <c r="I88" s="28"/>
       <c r="J88" s="5">
         <v>0</v>
       </c>
@@ -7144,23 +7185,23 @@
       </c>
     </row>
     <row r="89" s="5" customFormat="1" spans="2:22">
-      <c r="B89" s="33">
+      <c r="B89" s="26">
         <v>5025</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E89" s="5">
         <v>5</v>
       </c>
-      <c r="F89" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G89" s="34"/>
-      <c r="H89" s="30">
-        <v>1</v>
-      </c>
-      <c r="I89" s="36"/>
+      <c r="F89" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="G89" s="26"/>
+      <c r="H89" s="24">
+        <v>1</v>
+      </c>
+      <c r="I89" s="28"/>
       <c r="J89" s="5">
         <v>0</v>
       </c>
@@ -7190,23 +7231,23 @@
       </c>
     </row>
     <row r="90" s="5" customFormat="1" spans="2:22">
-      <c r="B90" s="33">
+      <c r="B90" s="26">
         <v>5026</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="E90" s="5">
         <v>5</v>
       </c>
-      <c r="F90" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G90" s="34"/>
-      <c r="H90" s="30">
-        <v>1</v>
-      </c>
-      <c r="I90" s="36"/>
+      <c r="F90" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="G90" s="26"/>
+      <c r="H90" s="24">
+        <v>1</v>
+      </c>
+      <c r="I90" s="28"/>
       <c r="J90" s="5">
         <v>0</v>
       </c>
@@ -7236,23 +7277,23 @@
       </c>
     </row>
     <row r="91" s="5" customFormat="1" spans="2:22">
-      <c r="B91" s="33">
+      <c r="B91" s="26">
         <v>5027</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="E91" s="5">
         <v>5</v>
       </c>
-      <c r="F91" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G91" s="34"/>
-      <c r="H91" s="30">
-        <v>1</v>
-      </c>
-      <c r="I91" s="36"/>
+      <c r="F91" s="26" t="s">
+        <v>284</v>
+      </c>
+      <c r="G91" s="26"/>
+      <c r="H91" s="24">
+        <v>1</v>
+      </c>
+      <c r="I91" s="28"/>
       <c r="J91" s="5">
         <v>0</v>
       </c>
@@ -7282,23 +7323,23 @@
       </c>
     </row>
     <row r="92" s="5" customFormat="1" spans="2:22">
-      <c r="B92" s="33">
+      <c r="B92" s="26">
         <v>5028</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="E92" s="5">
         <v>5</v>
       </c>
-      <c r="F92" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G92" s="34"/>
-      <c r="H92" s="30">
-        <v>1</v>
-      </c>
-      <c r="I92" s="36"/>
+      <c r="F92" s="26" t="s">
+        <v>286</v>
+      </c>
+      <c r="G92" s="26"/>
+      <c r="H92" s="24">
+        <v>1</v>
+      </c>
+      <c r="I92" s="28"/>
       <c r="J92" s="5">
         <v>0</v>
       </c>
@@ -7328,23 +7369,23 @@
       </c>
     </row>
     <row r="93" s="5" customFormat="1" spans="2:22">
-      <c r="B93" s="33">
+      <c r="B93" s="26">
         <v>5029</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="E93" s="5">
         <v>5</v>
       </c>
-      <c r="F93" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G93" s="34"/>
-      <c r="H93" s="30">
-        <v>1</v>
-      </c>
-      <c r="I93" s="36"/>
+      <c r="F93" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="G93" s="26"/>
+      <c r="H93" s="24">
+        <v>1</v>
+      </c>
+      <c r="I93" s="28"/>
       <c r="J93" s="5">
         <v>0</v>
       </c>
@@ -7374,23 +7415,23 @@
       </c>
     </row>
     <row r="94" s="5" customFormat="1" spans="2:22">
-      <c r="B94" s="33">
+      <c r="B94" s="26">
         <v>5030</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="E94" s="5">
         <v>5</v>
       </c>
-      <c r="F94" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G94" s="34"/>
-      <c r="H94" s="30">
-        <v>1</v>
-      </c>
-      <c r="I94" s="36"/>
+      <c r="F94" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="G94" s="26"/>
+      <c r="H94" s="24">
+        <v>1</v>
+      </c>
+      <c r="I94" s="28"/>
       <c r="J94" s="5">
         <v>0</v>
       </c>
@@ -7420,23 +7461,23 @@
       </c>
     </row>
     <row r="95" s="5" customFormat="1" spans="2:22">
-      <c r="B95" s="33">
+      <c r="B95" s="26">
         <v>5031</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="E95" s="5">
         <v>5</v>
       </c>
-      <c r="F95" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G95" s="34"/>
-      <c r="H95" s="30">
-        <v>1</v>
-      </c>
-      <c r="I95" s="36"/>
+      <c r="F95" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="G95" s="26"/>
+      <c r="H95" s="24">
+        <v>1</v>
+      </c>
+      <c r="I95" s="28"/>
       <c r="J95" s="5">
         <v>0</v>
       </c>
@@ -7466,23 +7507,23 @@
       </c>
     </row>
     <row r="96" s="5" customFormat="1" spans="2:22">
-      <c r="B96" s="33">
+      <c r="B96" s="26">
         <v>5032</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="E96" s="5">
         <v>5</v>
       </c>
-      <c r="F96" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G96" s="34"/>
-      <c r="H96" s="30">
-        <v>1</v>
-      </c>
-      <c r="I96" s="36"/>
+      <c r="F96" s="26" t="s">
+        <v>294</v>
+      </c>
+      <c r="G96" s="26"/>
+      <c r="H96" s="24">
+        <v>1</v>
+      </c>
+      <c r="I96" s="28"/>
       <c r="J96" s="5">
         <v>0</v>
       </c>
@@ -7512,23 +7553,23 @@
       </c>
     </row>
     <row r="97" s="5" customFormat="1" spans="2:22">
-      <c r="B97" s="33">
+      <c r="B97" s="26">
         <v>5033</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="E97" s="5">
         <v>5</v>
       </c>
-      <c r="F97" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G97" s="34"/>
-      <c r="H97" s="30">
-        <v>1</v>
-      </c>
-      <c r="I97" s="36"/>
+      <c r="F97" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="G97" s="26"/>
+      <c r="H97" s="24">
+        <v>1</v>
+      </c>
+      <c r="I97" s="28"/>
       <c r="J97" s="5">
         <v>0</v>
       </c>
@@ -7558,23 +7599,23 @@
       </c>
     </row>
     <row r="98" s="5" customFormat="1" spans="2:22">
-      <c r="B98" s="33">
+      <c r="B98" s="26">
         <v>5034</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="E98" s="5">
         <v>5</v>
       </c>
-      <c r="F98" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G98" s="34"/>
-      <c r="H98" s="30">
-        <v>1</v>
-      </c>
-      <c r="I98" s="36"/>
+      <c r="F98" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="G98" s="26"/>
+      <c r="H98" s="24">
+        <v>1</v>
+      </c>
+      <c r="I98" s="28"/>
       <c r="J98" s="5">
         <v>0</v>
       </c>
@@ -7604,23 +7645,23 @@
       </c>
     </row>
     <row r="99" s="5" customFormat="1" spans="2:22">
-      <c r="B99" s="33">
+      <c r="B99" s="26">
         <v>5035</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="E99" s="5">
         <v>5</v>
       </c>
-      <c r="F99" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G99" s="34"/>
-      <c r="H99" s="30">
-        <v>1</v>
-      </c>
-      <c r="I99" s="36"/>
+      <c r="F99" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="G99" s="26"/>
+      <c r="H99" s="24">
+        <v>1</v>
+      </c>
+      <c r="I99" s="28"/>
       <c r="J99" s="5">
         <v>0</v>
       </c>
@@ -7650,23 +7691,23 @@
       </c>
     </row>
     <row r="100" s="5" customFormat="1" spans="2:22">
-      <c r="B100" s="33">
+      <c r="B100" s="26">
         <v>5036</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="E100" s="5">
         <v>5</v>
       </c>
-      <c r="F100" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G100" s="34"/>
-      <c r="H100" s="30">
-        <v>1</v>
-      </c>
-      <c r="I100" s="36"/>
+      <c r="F100" s="26" t="s">
+        <v>302</v>
+      </c>
+      <c r="G100" s="26"/>
+      <c r="H100" s="24">
+        <v>1</v>
+      </c>
+      <c r="I100" s="28"/>
       <c r="J100" s="5">
         <v>0</v>
       </c>
@@ -7696,23 +7737,23 @@
       </c>
     </row>
     <row r="101" s="5" customFormat="1" spans="2:22">
-      <c r="B101" s="33">
+      <c r="B101" s="26">
         <v>5037</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="E101" s="5">
         <v>5</v>
       </c>
-      <c r="F101" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G101" s="34"/>
-      <c r="H101" s="30">
-        <v>1</v>
-      </c>
-      <c r="I101" s="36"/>
+      <c r="F101" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="G101" s="26"/>
+      <c r="H101" s="24">
+        <v>1</v>
+      </c>
+      <c r="I101" s="28"/>
       <c r="J101" s="5">
         <v>0</v>
       </c>
@@ -7742,23 +7783,23 @@
       </c>
     </row>
     <row r="102" s="5" customFormat="1" spans="2:22">
-      <c r="B102" s="33">
+      <c r="B102" s="26">
         <v>5038</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>276</v>
+        <v>305</v>
       </c>
       <c r="E102" s="5">
         <v>5</v>
       </c>
-      <c r="F102" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G102" s="34"/>
-      <c r="H102" s="30">
-        <v>1</v>
-      </c>
-      <c r="I102" s="36"/>
+      <c r="F102" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="G102" s="26"/>
+      <c r="H102" s="24">
+        <v>1</v>
+      </c>
+      <c r="I102" s="28"/>
       <c r="J102" s="5">
         <v>0</v>
       </c>
@@ -7788,23 +7829,23 @@
       </c>
     </row>
     <row r="103" s="5" customFormat="1" spans="2:22">
-      <c r="B103" s="33">
+      <c r="B103" s="26">
         <v>5039</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="E103" s="5">
         <v>5</v>
       </c>
-      <c r="F103" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G103" s="34"/>
-      <c r="H103" s="30">
-        <v>1</v>
-      </c>
-      <c r="I103" s="36"/>
+      <c r="F103" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="G103" s="26"/>
+      <c r="H103" s="24">
+        <v>1</v>
+      </c>
+      <c r="I103" s="28"/>
       <c r="J103" s="5">
         <v>0</v>
       </c>
@@ -7834,23 +7875,23 @@
       </c>
     </row>
     <row r="104" s="5" customFormat="1" spans="2:22">
-      <c r="B104" s="33">
+      <c r="B104" s="26">
         <v>5040</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
       <c r="E104" s="5">
         <v>5</v>
       </c>
-      <c r="F104" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G104" s="34"/>
-      <c r="H104" s="30">
-        <v>1</v>
-      </c>
-      <c r="I104" s="36"/>
+      <c r="F104" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="G104" s="26"/>
+      <c r="H104" s="24">
+        <v>1</v>
+      </c>
+      <c r="I104" s="28"/>
       <c r="J104" s="5">
         <v>0</v>
       </c>
@@ -7880,23 +7921,23 @@
       </c>
     </row>
     <row r="105" s="5" customFormat="1" spans="2:22">
-      <c r="B105" s="33">
+      <c r="B105" s="26">
         <v>5041</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="E105" s="5">
         <v>5</v>
       </c>
-      <c r="F105" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G105" s="34"/>
-      <c r="H105" s="30">
-        <v>1</v>
-      </c>
-      <c r="I105" s="36"/>
+      <c r="F105" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="G105" s="26"/>
+      <c r="H105" s="24">
+        <v>1</v>
+      </c>
+      <c r="I105" s="28"/>
       <c r="J105" s="5">
         <v>0</v>
       </c>
@@ -7926,23 +7967,23 @@
       </c>
     </row>
     <row r="106" s="5" customFormat="1" spans="2:22">
-      <c r="B106" s="33">
+      <c r="B106" s="26">
         <v>5042</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="E106" s="5">
         <v>5</v>
       </c>
-      <c r="F106" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G106" s="34"/>
-      <c r="H106" s="30">
-        <v>1</v>
-      </c>
-      <c r="I106" s="36"/>
+      <c r="F106" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="G106" s="26"/>
+      <c r="H106" s="24">
+        <v>1</v>
+      </c>
+      <c r="I106" s="28"/>
       <c r="J106" s="5">
         <v>0</v>
       </c>
@@ -7972,23 +8013,23 @@
       </c>
     </row>
     <row r="107" s="5" customFormat="1" spans="2:22">
-      <c r="B107" s="33">
+      <c r="B107" s="26">
         <v>5043</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="E107" s="5">
         <v>5</v>
       </c>
-      <c r="F107" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G107" s="34"/>
-      <c r="H107" s="30">
-        <v>1</v>
-      </c>
-      <c r="I107" s="36"/>
+      <c r="F107" s="26" t="s">
+        <v>316</v>
+      </c>
+      <c r="G107" s="26"/>
+      <c r="H107" s="24">
+        <v>1</v>
+      </c>
+      <c r="I107" s="28"/>
       <c r="J107" s="5">
         <v>0</v>
       </c>
@@ -8018,23 +8059,23 @@
       </c>
     </row>
     <row r="108" s="5" customFormat="1" spans="2:22">
-      <c r="B108" s="33">
+      <c r="B108" s="26">
         <v>5044</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="E108" s="5">
         <v>5</v>
       </c>
-      <c r="F108" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="G108" s="34"/>
-      <c r="H108" s="30">
-        <v>1</v>
-      </c>
-      <c r="I108" s="36"/>
+      <c r="F108" s="26" t="s">
+        <v>318</v>
+      </c>
+      <c r="G108" s="26"/>
+      <c r="H108" s="24">
+        <v>1</v>
+      </c>
+      <c r="I108" s="28"/>
       <c r="J108" s="5">
         <v>0</v>
       </c>
@@ -8068,18 +8109,18 @@
         <v>6001</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="E109" s="5">
         <v>6</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="H109" s="30">
-        <v>1</v>
-      </c>
-      <c r="I109" s="36"/>
+        <v>320</v>
+      </c>
+      <c r="H109" s="24">
+        <v>1</v>
+      </c>
+      <c r="I109" s="28"/>
       <c r="J109" s="5">
         <v>0</v>
       </c>
@@ -8113,18 +8154,18 @@
         <v>6002</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="E110" s="5">
         <v>6</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="H110" s="30">
-        <v>1</v>
-      </c>
-      <c r="I110" s="36"/>
+        <v>320</v>
+      </c>
+      <c r="H110" s="24">
+        <v>1</v>
+      </c>
+      <c r="I110" s="28"/>
       <c r="J110" s="5">
         <v>0</v>
       </c>
@@ -8152,29 +8193,29 @@
       <c r="V110" s="5">
         <v>0</v>
       </c>
-      <c r="X110" s="31"/>
-      <c r="Y110" s="31"/>
-      <c r="Z110" s="31"/>
-      <c r="AA110" s="31"/>
-      <c r="AB110" s="31"/>
+      <c r="X110" s="25"/>
+      <c r="Y110" s="25"/>
+      <c r="Z110" s="25"/>
+      <c r="AA110" s="25"/>
+      <c r="AB110" s="25"/>
     </row>
     <row r="111" s="5" customFormat="1" spans="2:28">
       <c r="B111" s="5">
         <v>6003</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="E111" s="5">
         <v>6</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="H111" s="30">
-        <v>1</v>
-      </c>
-      <c r="I111" s="36"/>
+        <v>323</v>
+      </c>
+      <c r="H111" s="24">
+        <v>1</v>
+      </c>
+      <c r="I111" s="28"/>
       <c r="J111" s="5">
         <v>0</v>
       </c>
@@ -8202,29 +8243,29 @@
       <c r="V111" s="5">
         <v>0</v>
       </c>
-      <c r="X111" s="31"/>
-      <c r="Y111" s="31"/>
-      <c r="Z111" s="31"/>
-      <c r="AA111" s="31"/>
-      <c r="AB111" s="31"/>
+      <c r="X111" s="25"/>
+      <c r="Y111" s="25"/>
+      <c r="Z111" s="25"/>
+      <c r="AA111" s="25"/>
+      <c r="AB111" s="25"/>
     </row>
     <row r="112" s="5" customFormat="1" spans="2:28">
       <c r="B112" s="5">
         <v>6004</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="E112" s="5">
         <v>6</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H112" s="30">
-        <v>1</v>
-      </c>
-      <c r="I112" s="36"/>
+        <v>325</v>
+      </c>
+      <c r="H112" s="24">
+        <v>1</v>
+      </c>
+      <c r="I112" s="28"/>
       <c r="J112" s="5">
         <v>0</v>
       </c>
@@ -8252,29 +8293,29 @@
       <c r="V112" s="5">
         <v>0</v>
       </c>
-      <c r="X112" s="31"/>
-      <c r="Y112" s="31"/>
-      <c r="Z112" s="31"/>
-      <c r="AA112" s="31"/>
-      <c r="AB112" s="31"/>
+      <c r="X112" s="25"/>
+      <c r="Y112" s="25"/>
+      <c r="Z112" s="25"/>
+      <c r="AA112" s="25"/>
+      <c r="AB112" s="25"/>
     </row>
     <row r="113" s="5" customFormat="1" spans="2:28">
       <c r="B113" s="5">
         <v>6005</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="E113" s="5">
         <v>6</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="H113" s="30">
-        <v>1</v>
-      </c>
-      <c r="I113" s="36"/>
+        <v>327</v>
+      </c>
+      <c r="H113" s="24">
+        <v>1</v>
+      </c>
+      <c r="I113" s="28"/>
       <c r="J113" s="5">
         <v>0</v>
       </c>
@@ -8302,29 +8343,29 @@
       <c r="V113" s="5">
         <v>0</v>
       </c>
-      <c r="X113" s="31"/>
-      <c r="Y113" s="31"/>
-      <c r="Z113" s="31"/>
-      <c r="AA113" s="31"/>
-      <c r="AB113" s="31"/>
+      <c r="X113" s="25"/>
+      <c r="Y113" s="25"/>
+      <c r="Z113" s="25"/>
+      <c r="AA113" s="25"/>
+      <c r="AB113" s="25"/>
     </row>
     <row r="114" s="5" customFormat="1" spans="2:28">
       <c r="B114" s="5">
         <v>6006</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="E114" s="5">
         <v>6</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="H114" s="30">
-        <v>1</v>
-      </c>
-      <c r="I114" s="36"/>
+        <v>329</v>
+      </c>
+      <c r="H114" s="24">
+        <v>1</v>
+      </c>
+      <c r="I114" s="28"/>
       <c r="J114" s="5">
         <v>0</v>
       </c>
@@ -8352,29 +8393,29 @@
       <c r="V114" s="5">
         <v>0</v>
       </c>
-      <c r="X114" s="31"/>
-      <c r="Y114" s="31"/>
-      <c r="Z114" s="31"/>
-      <c r="AA114" s="31"/>
-      <c r="AB114" s="31"/>
+      <c r="X114" s="25"/>
+      <c r="Y114" s="25"/>
+      <c r="Z114" s="25"/>
+      <c r="AA114" s="25"/>
+      <c r="AB114" s="25"/>
     </row>
     <row r="115" s="5" customFormat="1" spans="2:28">
       <c r="B115" s="5">
         <v>6007</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="E115" s="5">
         <v>6</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="H115" s="30">
-        <v>1</v>
-      </c>
-      <c r="I115" s="36"/>
+        <v>329</v>
+      </c>
+      <c r="H115" s="24">
+        <v>1</v>
+      </c>
+      <c r="I115" s="28"/>
       <c r="J115" s="5">
         <v>0</v>
       </c>
@@ -8402,29 +8443,29 @@
       <c r="V115" s="5">
         <v>0</v>
       </c>
-      <c r="X115" s="31"/>
-      <c r="Y115" s="31"/>
-      <c r="Z115" s="31"/>
-      <c r="AA115" s="31"/>
-      <c r="AB115" s="31"/>
+      <c r="X115" s="25"/>
+      <c r="Y115" s="25"/>
+      <c r="Z115" s="25"/>
+      <c r="AA115" s="25"/>
+      <c r="AB115" s="25"/>
     </row>
     <row r="116" s="5" customFormat="1" spans="2:28">
       <c r="B116" s="5">
         <v>6008</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="E116" s="5">
         <v>6</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="H116" s="30">
-        <v>1</v>
-      </c>
-      <c r="I116" s="36"/>
+        <v>332</v>
+      </c>
+      <c r="H116" s="24">
+        <v>1</v>
+      </c>
+      <c r="I116" s="28"/>
       <c r="J116" s="5">
         <v>0</v>
       </c>
@@ -8452,29 +8493,29 @@
       <c r="V116" s="5">
         <v>0</v>
       </c>
-      <c r="X116" s="31"/>
-      <c r="Y116" s="31"/>
-      <c r="Z116" s="31"/>
-      <c r="AA116" s="31"/>
-      <c r="AB116" s="31"/>
+      <c r="X116" s="25"/>
+      <c r="Y116" s="25"/>
+      <c r="Z116" s="25"/>
+      <c r="AA116" s="25"/>
+      <c r="AB116" s="25"/>
     </row>
     <row r="117" s="5" customFormat="1" spans="2:28">
       <c r="B117" s="5">
         <v>6009</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="E117" s="5">
         <v>6</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="H117" s="30">
-        <v>1</v>
-      </c>
-      <c r="I117" s="36"/>
+        <v>334</v>
+      </c>
+      <c r="H117" s="24">
+        <v>1</v>
+      </c>
+      <c r="I117" s="28"/>
       <c r="J117" s="5">
         <v>0</v>
       </c>
@@ -8502,29 +8543,29 @@
       <c r="V117" s="5">
         <v>0</v>
       </c>
-      <c r="X117" s="31"/>
-      <c r="Y117" s="31"/>
-      <c r="Z117" s="31"/>
-      <c r="AA117" s="31"/>
-      <c r="AB117" s="31"/>
+      <c r="X117" s="25"/>
+      <c r="Y117" s="25"/>
+      <c r="Z117" s="25"/>
+      <c r="AA117" s="25"/>
+      <c r="AB117" s="25"/>
     </row>
     <row r="118" s="5" customFormat="1" spans="2:28">
       <c r="B118" s="5">
         <v>6010</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="E118" s="5">
         <v>6</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="H118" s="30">
-        <v>1</v>
-      </c>
-      <c r="I118" s="36"/>
+        <v>329</v>
+      </c>
+      <c r="H118" s="24">
+        <v>1</v>
+      </c>
+      <c r="I118" s="28"/>
       <c r="J118" s="5">
         <v>0</v>
       </c>
@@ -8552,29 +8593,29 @@
       <c r="V118" s="5">
         <v>0</v>
       </c>
-      <c r="X118" s="31"/>
-      <c r="Y118" s="31"/>
-      <c r="Z118" s="31"/>
-      <c r="AA118" s="31"/>
-      <c r="AB118" s="31"/>
+      <c r="X118" s="25"/>
+      <c r="Y118" s="25"/>
+      <c r="Z118" s="25"/>
+      <c r="AA118" s="25"/>
+      <c r="AB118" s="25"/>
     </row>
     <row r="119" s="5" customFormat="1" spans="2:28">
       <c r="B119" s="5">
         <v>6011</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="E119" s="5">
         <v>6</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="H119" s="30">
-        <v>1</v>
-      </c>
-      <c r="I119" s="36"/>
+        <v>329</v>
+      </c>
+      <c r="H119" s="24">
+        <v>1</v>
+      </c>
+      <c r="I119" s="28"/>
       <c r="J119" s="5">
         <v>0</v>
       </c>
@@ -8602,29 +8643,29 @@
       <c r="V119" s="5">
         <v>0</v>
       </c>
-      <c r="X119" s="31"/>
-      <c r="Y119" s="31"/>
-      <c r="Z119" s="31"/>
-      <c r="AA119" s="31"/>
-      <c r="AB119" s="31"/>
+      <c r="X119" s="25"/>
+      <c r="Y119" s="25"/>
+      <c r="Z119" s="25"/>
+      <c r="AA119" s="25"/>
+      <c r="AB119" s="25"/>
     </row>
     <row r="120" s="5" customFormat="1" spans="2:28">
       <c r="B120" s="5">
         <v>6012</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="E120" s="5">
         <v>6</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="H120" s="30">
-        <v>1</v>
-      </c>
-      <c r="I120" s="36"/>
+        <v>329</v>
+      </c>
+      <c r="H120" s="24">
+        <v>1</v>
+      </c>
+      <c r="I120" s="28"/>
       <c r="J120" s="5">
         <v>0</v>
       </c>
@@ -8652,29 +8693,29 @@
       <c r="V120" s="5">
         <v>0</v>
       </c>
-      <c r="X120" s="31"/>
-      <c r="Y120" s="31"/>
-      <c r="Z120" s="31"/>
-      <c r="AA120" s="31"/>
-      <c r="AB120" s="31"/>
+      <c r="X120" s="25"/>
+      <c r="Y120" s="25"/>
+      <c r="Z120" s="25"/>
+      <c r="AA120" s="25"/>
+      <c r="AB120" s="25"/>
     </row>
     <row r="121" s="5" customFormat="1" spans="2:28">
       <c r="B121" s="5">
         <v>6013</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E121" s="5">
         <v>6</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="H121" s="30">
-        <v>1</v>
-      </c>
-      <c r="I121" s="36"/>
+        <v>320</v>
+      </c>
+      <c r="H121" s="24">
+        <v>1</v>
+      </c>
+      <c r="I121" s="28"/>
       <c r="J121" s="5">
         <v>0</v>
       </c>
@@ -8702,29 +8743,29 @@
       <c r="V121" s="5">
         <v>0</v>
       </c>
-      <c r="X121" s="31"/>
-      <c r="Y121" s="31"/>
-      <c r="Z121" s="31"/>
-      <c r="AA121" s="31"/>
-      <c r="AB121" s="31"/>
+      <c r="X121" s="25"/>
+      <c r="Y121" s="25"/>
+      <c r="Z121" s="25"/>
+      <c r="AA121" s="25"/>
+      <c r="AB121" s="25"/>
     </row>
     <row r="122" s="5" customFormat="1" spans="2:28">
       <c r="B122" s="5">
         <v>6014</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="E122" s="5">
         <v>6</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="H122" s="30">
-        <v>1</v>
-      </c>
-      <c r="I122" s="36"/>
+        <v>340</v>
+      </c>
+      <c r="H122" s="24">
+        <v>1</v>
+      </c>
+      <c r="I122" s="28"/>
       <c r="J122" s="5">
         <v>0</v>
       </c>
@@ -8752,29 +8793,29 @@
       <c r="V122" s="5">
         <v>0</v>
       </c>
-      <c r="X122" s="31"/>
-      <c r="Y122" s="31"/>
-      <c r="Z122" s="31"/>
-      <c r="AA122" s="31"/>
-      <c r="AB122" s="31"/>
+      <c r="X122" s="25"/>
+      <c r="Y122" s="25"/>
+      <c r="Z122" s="25"/>
+      <c r="AA122" s="25"/>
+      <c r="AB122" s="25"/>
     </row>
     <row r="123" s="5" customFormat="1" spans="2:28">
       <c r="B123" s="5">
         <v>6015</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="E123" s="5">
         <v>6</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="H123" s="30">
-        <v>1</v>
-      </c>
-      <c r="I123" s="36"/>
+        <v>320</v>
+      </c>
+      <c r="H123" s="24">
+        <v>1</v>
+      </c>
+      <c r="I123" s="28"/>
       <c r="J123" s="5">
         <v>0</v>
       </c>
@@ -8802,43 +8843,43 @@
       <c r="V123" s="5">
         <v>0</v>
       </c>
-      <c r="X123" s="31"/>
-      <c r="Y123" s="31"/>
-      <c r="Z123" s="31"/>
-      <c r="AA123" s="31"/>
-      <c r="AB123" s="31"/>
+      <c r="X123" s="25"/>
+      <c r="Y123" s="25"/>
+      <c r="Z123" s="25"/>
+      <c r="AA123" s="25"/>
+      <c r="AB123" s="25"/>
     </row>
     <row r="124" s="5" customFormat="1" spans="1:28">
-      <c r="A124" s="30"/>
-      <c r="B124" s="30">
+      <c r="A124" s="24"/>
+      <c r="B124" s="24">
         <v>7001</v>
       </c>
-      <c r="C124" s="33" t="s">
-        <v>306</v>
+      <c r="C124" s="26" t="s">
+        <v>342</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E124" s="30">
+      <c r="E124" s="24">
         <v>7</v>
       </c>
-      <c r="F124" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="G124" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="H124" s="30">
-        <v>1</v>
-      </c>
-      <c r="I124" s="36"/>
+      <c r="F124" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="G124" s="26" t="s">
+        <v>344</v>
+      </c>
+      <c r="H124" s="24">
+        <v>1</v>
+      </c>
+      <c r="I124" s="28"/>
       <c r="J124" s="5">
         <v>0</v>
       </c>
       <c r="K124" s="5">
         <v>0</v>
       </c>
-      <c r="L124" s="30">
+      <c r="L124" s="24">
         <v>0</v>
       </c>
       <c r="M124" s="5">
@@ -8853,52 +8894,52 @@
       <c r="P124" s="5">
         <v>1</v>
       </c>
-      <c r="Q124" s="30"/>
-      <c r="R124" s="30"/>
-      <c r="S124" s="30"/>
-      <c r="T124" s="30"/>
-      <c r="U124" s="30"/>
+      <c r="Q124" s="24"/>
+      <c r="R124" s="24"/>
+      <c r="S124" s="24"/>
+      <c r="T124" s="24"/>
+      <c r="U124" s="24"/>
       <c r="V124" s="5">
         <v>0</v>
       </c>
-      <c r="W124" s="30"/>
-      <c r="X124" s="31"/>
-      <c r="Y124" s="31"/>
-      <c r="Z124" s="31"/>
-      <c r="AA124" s="31"/>
-      <c r="AB124" s="31"/>
+      <c r="W124" s="24"/>
+      <c r="X124" s="25"/>
+      <c r="Y124" s="25"/>
+      <c r="Z124" s="25"/>
+      <c r="AA124" s="25"/>
+      <c r="AB124" s="25"/>
     </row>
     <row r="125" s="5" customFormat="1" spans="1:28">
-      <c r="A125" s="30"/>
-      <c r="B125" s="30">
+      <c r="A125" s="24"/>
+      <c r="B125" s="24">
         <v>7002</v>
       </c>
-      <c r="C125" s="33" t="s">
-        <v>309</v>
+      <c r="C125" s="26" t="s">
+        <v>345</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E125" s="30">
+      <c r="E125" s="24">
         <v>7</v>
       </c>
-      <c r="F125" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="G125" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="H125" s="30">
-        <v>1</v>
-      </c>
-      <c r="I125" s="36"/>
+      <c r="F125" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="G125" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="H125" s="24">
+        <v>1</v>
+      </c>
+      <c r="I125" s="28"/>
       <c r="J125" s="5">
         <v>0</v>
       </c>
       <c r="K125" s="5">
         <v>0</v>
       </c>
-      <c r="L125" s="30">
+      <c r="L125" s="24">
         <v>0</v>
       </c>
       <c r="M125" s="5">
@@ -8913,52 +8954,52 @@
       <c r="P125" s="5">
         <v>1</v>
       </c>
-      <c r="Q125" s="30"/>
-      <c r="R125" s="30"/>
-      <c r="S125" s="30"/>
-      <c r="T125" s="30"/>
-      <c r="U125" s="30"/>
+      <c r="Q125" s="24"/>
+      <c r="R125" s="24"/>
+      <c r="S125" s="24"/>
+      <c r="T125" s="24"/>
+      <c r="U125" s="24"/>
       <c r="V125" s="5">
         <v>0</v>
       </c>
-      <c r="W125" s="30"/>
-      <c r="X125" s="31"/>
-      <c r="Y125" s="31"/>
-      <c r="Z125" s="31"/>
-      <c r="AA125" s="31"/>
-      <c r="AB125" s="31"/>
+      <c r="W125" s="24"/>
+      <c r="X125" s="25"/>
+      <c r="Y125" s="25"/>
+      <c r="Z125" s="25"/>
+      <c r="AA125" s="25"/>
+      <c r="AB125" s="25"/>
     </row>
     <row r="126" s="5" customFormat="1" spans="1:28">
-      <c r="A126" s="30"/>
-      <c r="B126" s="30">
+      <c r="A126" s="24"/>
+      <c r="B126" s="24">
         <v>7003</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E126" s="30">
+      <c r="E126" s="24">
         <v>7</v>
       </c>
-      <c r="F126" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="G126" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="H126" s="30">
-        <v>1</v>
-      </c>
-      <c r="I126" s="36"/>
+      <c r="F126" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="G126" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="H126" s="24">
+        <v>1</v>
+      </c>
+      <c r="I126" s="28"/>
       <c r="J126" s="5">
         <v>0</v>
       </c>
       <c r="K126" s="5">
         <v>0</v>
       </c>
-      <c r="L126" s="30">
+      <c r="L126" s="24">
         <v>0</v>
       </c>
       <c r="M126" s="5">
@@ -8973,52 +9014,52 @@
       <c r="P126" s="5">
         <v>1</v>
       </c>
-      <c r="Q126" s="30"/>
-      <c r="R126" s="30"/>
-      <c r="S126" s="30"/>
-      <c r="T126" s="30"/>
-      <c r="U126" s="30"/>
+      <c r="Q126" s="24"/>
+      <c r="R126" s="24"/>
+      <c r="S126" s="24"/>
+      <c r="T126" s="24"/>
+      <c r="U126" s="24"/>
       <c r="V126" s="5">
         <v>0</v>
       </c>
-      <c r="W126" s="30"/>
-      <c r="X126" s="31"/>
-      <c r="Y126" s="31"/>
-      <c r="Z126" s="31"/>
-      <c r="AA126" s="31"/>
-      <c r="AB126" s="31"/>
+      <c r="W126" s="24"/>
+      <c r="X126" s="25"/>
+      <c r="Y126" s="25"/>
+      <c r="Z126" s="25"/>
+      <c r="AA126" s="25"/>
+      <c r="AB126" s="25"/>
     </row>
     <row r="127" s="5" customFormat="1" spans="1:28">
-      <c r="A127" s="30"/>
-      <c r="B127" s="30">
+      <c r="A127" s="24"/>
+      <c r="B127" s="24">
         <v>7004</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E127" s="30">
+      <c r="E127" s="24">
         <v>7</v>
       </c>
-      <c r="F127" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="G127" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="H127" s="30">
-        <v>1</v>
-      </c>
-      <c r="I127" s="36"/>
+      <c r="F127" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="G127" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="H127" s="24">
+        <v>1</v>
+      </c>
+      <c r="I127" s="28"/>
       <c r="J127" s="5">
         <v>0</v>
       </c>
       <c r="K127" s="5">
         <v>0</v>
       </c>
-      <c r="L127" s="30">
+      <c r="L127" s="24">
         <v>0</v>
       </c>
       <c r="M127" s="5">
@@ -9033,52 +9074,52 @@
       <c r="P127" s="5">
         <v>0</v>
       </c>
-      <c r="Q127" s="30"/>
-      <c r="R127" s="30"/>
-      <c r="S127" s="30"/>
-      <c r="T127" s="30"/>
-      <c r="U127" s="30"/>
+      <c r="Q127" s="24"/>
+      <c r="R127" s="24"/>
+      <c r="S127" s="24"/>
+      <c r="T127" s="24"/>
+      <c r="U127" s="24"/>
       <c r="V127" s="5">
         <v>0</v>
       </c>
-      <c r="W127" s="30"/>
-      <c r="X127" s="31"/>
-      <c r="Y127" s="31"/>
-      <c r="Z127" s="31"/>
-      <c r="AA127" s="31"/>
-      <c r="AB127" s="31"/>
+      <c r="W127" s="24"/>
+      <c r="X127" s="25"/>
+      <c r="Y127" s="25"/>
+      <c r="Z127" s="25"/>
+      <c r="AA127" s="25"/>
+      <c r="AB127" s="25"/>
     </row>
     <row r="128" s="5" customFormat="1" spans="1:28">
-      <c r="A128" s="30"/>
-      <c r="B128" s="30">
+      <c r="A128" s="24"/>
+      <c r="B128" s="24">
         <v>7005</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E128" s="30">
+      <c r="E128" s="24">
         <v>7</v>
       </c>
-      <c r="F128" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="G128" s="33" t="s">
-        <v>319</v>
-      </c>
-      <c r="H128" s="30">
-        <v>1</v>
-      </c>
-      <c r="I128" s="36"/>
+      <c r="F128" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="G128" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="H128" s="24">
+        <v>1</v>
+      </c>
+      <c r="I128" s="28"/>
       <c r="J128" s="5">
         <v>0</v>
       </c>
       <c r="K128" s="5">
         <v>0</v>
       </c>
-      <c r="L128" s="30">
+      <c r="L128" s="24">
         <v>0</v>
       </c>
       <c r="M128" s="5">
@@ -9093,1894 +9134,1894 @@
       <c r="P128" s="5">
         <v>1</v>
       </c>
-      <c r="Q128" s="30"/>
-      <c r="R128" s="30"/>
-      <c r="S128" s="30"/>
-      <c r="T128" s="30"/>
-      <c r="U128" s="30"/>
+      <c r="Q128" s="24"/>
+      <c r="R128" s="24"/>
+      <c r="S128" s="24"/>
+      <c r="T128" s="24"/>
+      <c r="U128" s="24"/>
       <c r="V128" s="5">
         <v>0</v>
       </c>
-      <c r="W128" s="30"/>
-      <c r="X128" s="31"/>
-      <c r="Y128" s="31"/>
-      <c r="Z128" s="31"/>
-      <c r="AA128" s="31"/>
-      <c r="AB128" s="31"/>
+      <c r="W128" s="24"/>
+      <c r="X128" s="25"/>
+      <c r="Y128" s="25"/>
+      <c r="Z128" s="25"/>
+      <c r="AA128" s="25"/>
+      <c r="AB128" s="25"/>
     </row>
     <row r="129" spans="1:23">
-      <c r="A129" s="37"/>
-      <c r="B129" s="37"/>
-      <c r="C129" s="38"/>
-      <c r="D129" s="37"/>
-      <c r="E129" s="37"/>
-      <c r="F129" s="37"/>
-      <c r="G129" s="39"/>
-      <c r="H129" s="37"/>
-      <c r="I129" s="37"/>
-      <c r="J129" s="37"/>
-      <c r="K129" s="37"/>
-      <c r="L129" s="37"/>
-      <c r="M129" s="39"/>
-      <c r="N129" s="37"/>
-      <c r="Q129" s="37"/>
-      <c r="R129" s="37"/>
-      <c r="S129" s="37"/>
-      <c r="T129" s="37"/>
-      <c r="U129" s="37"/>
-      <c r="V129" s="37"/>
-      <c r="W129" s="37"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="30"/>
+      <c r="D129" s="29"/>
+      <c r="E129" s="29"/>
+      <c r="F129" s="29"/>
+      <c r="G129" s="29"/>
+      <c r="H129" s="29"/>
+      <c r="I129" s="29"/>
+      <c r="J129" s="29"/>
+      <c r="K129" s="29"/>
+      <c r="L129" s="29"/>
+      <c r="M129" s="29"/>
+      <c r="N129" s="29"/>
+      <c r="Q129" s="29"/>
+      <c r="R129" s="29"/>
+      <c r="S129" s="29"/>
+      <c r="T129" s="29"/>
+      <c r="U129" s="29"/>
+      <c r="V129" s="29"/>
+      <c r="W129" s="29"/>
     </row>
     <row r="130" spans="1:23">
-      <c r="A130" s="37"/>
-      <c r="B130" s="37"/>
-      <c r="C130" s="38"/>
-      <c r="D130" s="37"/>
-      <c r="E130" s="37"/>
-      <c r="F130" s="37"/>
-      <c r="G130" s="39"/>
-      <c r="H130" s="37"/>
-      <c r="I130" s="37"/>
-      <c r="J130" s="37"/>
-      <c r="K130" s="37"/>
-      <c r="L130" s="37"/>
-      <c r="M130" s="39"/>
-      <c r="N130" s="37"/>
-      <c r="Q130" s="37"/>
-      <c r="R130" s="37"/>
-      <c r="S130" s="37"/>
-      <c r="T130" s="37"/>
-      <c r="U130" s="37"/>
-      <c r="V130" s="37"/>
-      <c r="W130" s="37"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="29"/>
+      <c r="E130" s="29"/>
+      <c r="F130" s="29"/>
+      <c r="G130" s="29"/>
+      <c r="H130" s="29"/>
+      <c r="I130" s="29"/>
+      <c r="J130" s="29"/>
+      <c r="K130" s="29"/>
+      <c r="L130" s="29"/>
+      <c r="M130" s="29"/>
+      <c r="N130" s="29"/>
+      <c r="Q130" s="29"/>
+      <c r="R130" s="29"/>
+      <c r="S130" s="29"/>
+      <c r="T130" s="29"/>
+      <c r="U130" s="29"/>
+      <c r="V130" s="29"/>
+      <c r="W130" s="29"/>
     </row>
     <row r="131" spans="1:23">
-      <c r="A131" s="37"/>
-      <c r="B131" s="37"/>
-      <c r="C131" s="38"/>
-      <c r="D131" s="37"/>
-      <c r="E131" s="37"/>
-      <c r="F131" s="37"/>
-      <c r="G131" s="39"/>
-      <c r="H131" s="37"/>
-      <c r="I131" s="37"/>
-      <c r="J131" s="37"/>
-      <c r="K131" s="37"/>
-      <c r="L131" s="37"/>
-      <c r="M131" s="39"/>
-      <c r="N131" s="37"/>
-      <c r="Q131" s="37"/>
-      <c r="R131" s="37"/>
-      <c r="S131" s="37"/>
-      <c r="T131" s="37"/>
-      <c r="U131" s="37"/>
-      <c r="V131" s="37"/>
-      <c r="W131" s="37"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="30"/>
+      <c r="D131" s="29"/>
+      <c r="E131" s="29"/>
+      <c r="F131" s="29"/>
+      <c r="G131" s="29"/>
+      <c r="H131" s="29"/>
+      <c r="I131" s="29"/>
+      <c r="J131" s="29"/>
+      <c r="K131" s="29"/>
+      <c r="L131" s="29"/>
+      <c r="M131" s="29"/>
+      <c r="N131" s="29"/>
+      <c r="Q131" s="29"/>
+      <c r="R131" s="29"/>
+      <c r="S131" s="29"/>
+      <c r="T131" s="29"/>
+      <c r="U131" s="29"/>
+      <c r="V131" s="29"/>
+      <c r="W131" s="29"/>
     </row>
     <row r="132" spans="1:23">
-      <c r="A132" s="37"/>
-      <c r="B132" s="37"/>
-      <c r="C132" s="38"/>
-      <c r="D132" s="37"/>
-      <c r="E132" s="37"/>
-      <c r="F132" s="37"/>
-      <c r="G132" s="39"/>
-      <c r="H132" s="37"/>
-      <c r="I132" s="37"/>
-      <c r="J132" s="37"/>
-      <c r="K132" s="37"/>
-      <c r="L132" s="37"/>
-      <c r="M132" s="39"/>
-      <c r="N132" s="37"/>
-      <c r="Q132" s="37"/>
-      <c r="R132" s="37"/>
-      <c r="S132" s="37"/>
-      <c r="T132" s="37"/>
-      <c r="U132" s="37"/>
-      <c r="V132" s="37"/>
-      <c r="W132" s="37"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="30"/>
+      <c r="D132" s="29"/>
+      <c r="E132" s="29"/>
+      <c r="F132" s="29"/>
+      <c r="G132" s="29"/>
+      <c r="H132" s="29"/>
+      <c r="I132" s="29"/>
+      <c r="J132" s="29"/>
+      <c r="K132" s="29"/>
+      <c r="L132" s="29"/>
+      <c r="M132" s="29"/>
+      <c r="N132" s="29"/>
+      <c r="Q132" s="29"/>
+      <c r="R132" s="29"/>
+      <c r="S132" s="29"/>
+      <c r="T132" s="29"/>
+      <c r="U132" s="29"/>
+      <c r="V132" s="29"/>
+      <c r="W132" s="29"/>
     </row>
     <row r="133" spans="1:23">
-      <c r="A133" s="37"/>
-      <c r="B133" s="37"/>
-      <c r="C133" s="38"/>
-      <c r="D133" s="37"/>
-      <c r="E133" s="37"/>
-      <c r="F133" s="37"/>
-      <c r="G133" s="39"/>
-      <c r="H133" s="37"/>
-      <c r="I133" s="37"/>
-      <c r="J133" s="37"/>
-      <c r="K133" s="37"/>
-      <c r="L133" s="37"/>
-      <c r="M133" s="39"/>
-      <c r="N133" s="37"/>
-      <c r="Q133" s="37"/>
-      <c r="R133" s="37"/>
-      <c r="S133" s="37"/>
-      <c r="T133" s="37"/>
-      <c r="U133" s="37"/>
-      <c r="V133" s="37"/>
-      <c r="W133" s="37"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="29"/>
+      <c r="E133" s="29"/>
+      <c r="F133" s="29"/>
+      <c r="G133" s="29"/>
+      <c r="H133" s="29"/>
+      <c r="I133" s="29"/>
+      <c r="J133" s="29"/>
+      <c r="K133" s="29"/>
+      <c r="L133" s="29"/>
+      <c r="M133" s="29"/>
+      <c r="N133" s="29"/>
+      <c r="Q133" s="29"/>
+      <c r="R133" s="29"/>
+      <c r="S133" s="29"/>
+      <c r="T133" s="29"/>
+      <c r="U133" s="29"/>
+      <c r="V133" s="29"/>
+      <c r="W133" s="29"/>
     </row>
     <row r="134" spans="1:23">
-      <c r="A134" s="37"/>
-      <c r="B134" s="37"/>
-      <c r="C134" s="38"/>
-      <c r="D134" s="37"/>
-      <c r="E134" s="37"/>
-      <c r="F134" s="37"/>
-      <c r="G134" s="39"/>
-      <c r="H134" s="37"/>
-      <c r="I134" s="37"/>
-      <c r="J134" s="37"/>
-      <c r="K134" s="37"/>
-      <c r="L134" s="37"/>
-      <c r="M134" s="39"/>
-      <c r="N134" s="37"/>
-      <c r="Q134" s="37"/>
-      <c r="R134" s="37"/>
-      <c r="S134" s="37"/>
-      <c r="T134" s="37"/>
-      <c r="U134" s="37"/>
-      <c r="V134" s="37"/>
-      <c r="W134" s="37"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="30"/>
+      <c r="D134" s="29"/>
+      <c r="E134" s="29"/>
+      <c r="F134" s="29"/>
+      <c r="G134" s="29"/>
+      <c r="H134" s="29"/>
+      <c r="I134" s="29"/>
+      <c r="J134" s="29"/>
+      <c r="K134" s="29"/>
+      <c r="L134" s="29"/>
+      <c r="M134" s="29"/>
+      <c r="N134" s="29"/>
+      <c r="Q134" s="29"/>
+      <c r="R134" s="29"/>
+      <c r="S134" s="29"/>
+      <c r="T134" s="29"/>
+      <c r="U134" s="29"/>
+      <c r="V134" s="29"/>
+      <c r="W134" s="29"/>
     </row>
     <row r="135" spans="1:23">
-      <c r="A135" s="37"/>
-      <c r="B135" s="37"/>
-      <c r="C135" s="38"/>
-      <c r="D135" s="37"/>
-      <c r="E135" s="37"/>
-      <c r="F135" s="37"/>
-      <c r="G135" s="39"/>
-      <c r="H135" s="37"/>
-      <c r="I135" s="37"/>
-      <c r="J135" s="37"/>
-      <c r="K135" s="37"/>
-      <c r="L135" s="37"/>
-      <c r="M135" s="39"/>
-      <c r="N135" s="37"/>
-      <c r="Q135" s="37"/>
-      <c r="R135" s="37"/>
-      <c r="S135" s="37"/>
-      <c r="T135" s="37"/>
-      <c r="U135" s="37"/>
-      <c r="V135" s="37"/>
-      <c r="W135" s="37"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="30"/>
+      <c r="D135" s="29"/>
+      <c r="E135" s="29"/>
+      <c r="F135" s="29"/>
+      <c r="G135" s="29"/>
+      <c r="H135" s="29"/>
+      <c r="I135" s="29"/>
+      <c r="J135" s="29"/>
+      <c r="K135" s="29"/>
+      <c r="L135" s="29"/>
+      <c r="M135" s="29"/>
+      <c r="N135" s="29"/>
+      <c r="Q135" s="29"/>
+      <c r="R135" s="29"/>
+      <c r="S135" s="29"/>
+      <c r="T135" s="29"/>
+      <c r="U135" s="29"/>
+      <c r="V135" s="29"/>
+      <c r="W135" s="29"/>
     </row>
     <row r="136" spans="1:23">
-      <c r="A136" s="37"/>
-      <c r="B136" s="37"/>
-      <c r="C136" s="38"/>
-      <c r="D136" s="37"/>
-      <c r="E136" s="37"/>
-      <c r="F136" s="37"/>
-      <c r="G136" s="39"/>
-      <c r="H136" s="37"/>
-      <c r="I136" s="37"/>
-      <c r="J136" s="37"/>
-      <c r="K136" s="37"/>
-      <c r="L136" s="37"/>
-      <c r="M136" s="39"/>
-      <c r="N136" s="37"/>
-      <c r="Q136" s="37"/>
-      <c r="R136" s="37"/>
-      <c r="S136" s="37"/>
-      <c r="T136" s="37"/>
-      <c r="U136" s="37"/>
-      <c r="V136" s="37"/>
-      <c r="W136" s="37"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="29"/>
+      <c r="E136" s="29"/>
+      <c r="F136" s="29"/>
+      <c r="G136" s="29"/>
+      <c r="H136" s="29"/>
+      <c r="I136" s="29"/>
+      <c r="J136" s="29"/>
+      <c r="K136" s="29"/>
+      <c r="L136" s="29"/>
+      <c r="M136" s="29"/>
+      <c r="N136" s="29"/>
+      <c r="Q136" s="29"/>
+      <c r="R136" s="29"/>
+      <c r="S136" s="29"/>
+      <c r="T136" s="29"/>
+      <c r="U136" s="29"/>
+      <c r="V136" s="29"/>
+      <c r="W136" s="29"/>
     </row>
     <row r="137" spans="1:23">
-      <c r="A137" s="37"/>
-      <c r="B137" s="37"/>
-      <c r="C137" s="38"/>
-      <c r="D137" s="37"/>
-      <c r="E137" s="37"/>
-      <c r="F137" s="37"/>
-      <c r="G137" s="39"/>
-      <c r="H137" s="37"/>
-      <c r="I137" s="37"/>
-      <c r="J137" s="37"/>
-      <c r="K137" s="37"/>
-      <c r="L137" s="37"/>
-      <c r="M137" s="39"/>
-      <c r="N137" s="37"/>
-      <c r="Q137" s="37"/>
-      <c r="R137" s="37"/>
-      <c r="S137" s="37"/>
-      <c r="T137" s="37"/>
-      <c r="U137" s="37"/>
-      <c r="V137" s="37"/>
-      <c r="W137" s="37"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="30"/>
+      <c r="D137" s="29"/>
+      <c r="E137" s="29"/>
+      <c r="F137" s="29"/>
+      <c r="G137" s="29"/>
+      <c r="H137" s="29"/>
+      <c r="I137" s="29"/>
+      <c r="J137" s="29"/>
+      <c r="K137" s="29"/>
+      <c r="L137" s="29"/>
+      <c r="M137" s="29"/>
+      <c r="N137" s="29"/>
+      <c r="Q137" s="29"/>
+      <c r="R137" s="29"/>
+      <c r="S137" s="29"/>
+      <c r="T137" s="29"/>
+      <c r="U137" s="29"/>
+      <c r="V137" s="29"/>
+      <c r="W137" s="29"/>
     </row>
     <row r="138" spans="1:23">
-      <c r="A138" s="37"/>
-      <c r="B138" s="37"/>
-      <c r="C138" s="38"/>
-      <c r="D138" s="37"/>
-      <c r="E138" s="37"/>
-      <c r="F138" s="37"/>
-      <c r="G138" s="39"/>
-      <c r="H138" s="37"/>
-      <c r="I138" s="37"/>
-      <c r="J138" s="37"/>
-      <c r="K138" s="37"/>
-      <c r="L138" s="37"/>
-      <c r="M138" s="39"/>
-      <c r="N138" s="37"/>
-      <c r="Q138" s="37"/>
-      <c r="R138" s="37"/>
-      <c r="S138" s="37"/>
-      <c r="T138" s="37"/>
-      <c r="U138" s="37"/>
-      <c r="V138" s="37"/>
-      <c r="W138" s="37"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="30"/>
+      <c r="D138" s="29"/>
+      <c r="E138" s="29"/>
+      <c r="F138" s="29"/>
+      <c r="G138" s="29"/>
+      <c r="H138" s="29"/>
+      <c r="I138" s="29"/>
+      <c r="J138" s="29"/>
+      <c r="K138" s="29"/>
+      <c r="L138" s="29"/>
+      <c r="M138" s="29"/>
+      <c r="N138" s="29"/>
+      <c r="Q138" s="29"/>
+      <c r="R138" s="29"/>
+      <c r="S138" s="29"/>
+      <c r="T138" s="29"/>
+      <c r="U138" s="29"/>
+      <c r="V138" s="29"/>
+      <c r="W138" s="29"/>
     </row>
     <row r="139" spans="1:23">
-      <c r="A139" s="37"/>
-      <c r="B139" s="37"/>
-      <c r="C139" s="38"/>
-      <c r="D139" s="37"/>
-      <c r="E139" s="37"/>
-      <c r="F139" s="37"/>
-      <c r="G139" s="39"/>
-      <c r="H139" s="37"/>
-      <c r="I139" s="37"/>
-      <c r="J139" s="37"/>
-      <c r="K139" s="37"/>
-      <c r="L139" s="37"/>
-      <c r="M139" s="39"/>
-      <c r="N139" s="37"/>
-      <c r="Q139" s="37"/>
-      <c r="R139" s="37"/>
-      <c r="S139" s="37"/>
-      <c r="T139" s="37"/>
-      <c r="U139" s="37"/>
-      <c r="V139" s="37"/>
-      <c r="W139" s="37"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="30"/>
+      <c r="D139" s="29"/>
+      <c r="E139" s="29"/>
+      <c r="F139" s="29"/>
+      <c r="G139" s="29"/>
+      <c r="H139" s="29"/>
+      <c r="I139" s="29"/>
+      <c r="J139" s="29"/>
+      <c r="K139" s="29"/>
+      <c r="L139" s="29"/>
+      <c r="M139" s="29"/>
+      <c r="N139" s="29"/>
+      <c r="Q139" s="29"/>
+      <c r="R139" s="29"/>
+      <c r="S139" s="29"/>
+      <c r="T139" s="29"/>
+      <c r="U139" s="29"/>
+      <c r="V139" s="29"/>
+      <c r="W139" s="29"/>
     </row>
     <row r="140" spans="1:23">
-      <c r="A140" s="37"/>
-      <c r="B140" s="37"/>
-      <c r="C140" s="38"/>
-      <c r="D140" s="37"/>
-      <c r="E140" s="37"/>
-      <c r="F140" s="37"/>
-      <c r="G140" s="39"/>
-      <c r="H140" s="37"/>
-      <c r="I140" s="37"/>
-      <c r="J140" s="37"/>
-      <c r="K140" s="37"/>
-      <c r="L140" s="37"/>
-      <c r="M140" s="39"/>
-      <c r="N140" s="37"/>
-      <c r="Q140" s="37"/>
-      <c r="R140" s="37"/>
-      <c r="S140" s="37"/>
-      <c r="T140" s="37"/>
-      <c r="U140" s="37"/>
-      <c r="V140" s="37"/>
-      <c r="W140" s="37"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="29"/>
+      <c r="E140" s="29"/>
+      <c r="F140" s="29"/>
+      <c r="G140" s="29"/>
+      <c r="H140" s="29"/>
+      <c r="I140" s="29"/>
+      <c r="J140" s="29"/>
+      <c r="K140" s="29"/>
+      <c r="L140" s="29"/>
+      <c r="M140" s="29"/>
+      <c r="N140" s="29"/>
+      <c r="Q140" s="29"/>
+      <c r="R140" s="29"/>
+      <c r="S140" s="29"/>
+      <c r="T140" s="29"/>
+      <c r="U140" s="29"/>
+      <c r="V140" s="29"/>
+      <c r="W140" s="29"/>
     </row>
     <row r="141" spans="1:23">
-      <c r="A141" s="37"/>
-      <c r="B141" s="37"/>
-      <c r="C141" s="38"/>
-      <c r="D141" s="37"/>
-      <c r="E141" s="37"/>
-      <c r="F141" s="37"/>
-      <c r="G141" s="39"/>
-      <c r="H141" s="37"/>
-      <c r="I141" s="37"/>
-      <c r="J141" s="37"/>
-      <c r="K141" s="37"/>
-      <c r="L141" s="37"/>
-      <c r="M141" s="39"/>
-      <c r="N141" s="37"/>
-      <c r="Q141" s="37"/>
-      <c r="R141" s="37"/>
-      <c r="S141" s="37"/>
-      <c r="T141" s="37"/>
-      <c r="U141" s="37"/>
-      <c r="V141" s="37"/>
-      <c r="W141" s="37"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="30"/>
+      <c r="D141" s="29"/>
+      <c r="E141" s="29"/>
+      <c r="F141" s="29"/>
+      <c r="G141" s="29"/>
+      <c r="H141" s="29"/>
+      <c r="I141" s="29"/>
+      <c r="J141" s="29"/>
+      <c r="K141" s="29"/>
+      <c r="L141" s="29"/>
+      <c r="M141" s="29"/>
+      <c r="N141" s="29"/>
+      <c r="Q141" s="29"/>
+      <c r="R141" s="29"/>
+      <c r="S141" s="29"/>
+      <c r="T141" s="29"/>
+      <c r="U141" s="29"/>
+      <c r="V141" s="29"/>
+      <c r="W141" s="29"/>
     </row>
     <row r="142" spans="1:23">
-      <c r="A142" s="37"/>
-      <c r="B142" s="37"/>
-      <c r="C142" s="38"/>
-      <c r="D142" s="37"/>
-      <c r="E142" s="37"/>
-      <c r="F142" s="37"/>
-      <c r="G142" s="39"/>
-      <c r="H142" s="37"/>
-      <c r="I142" s="37"/>
-      <c r="J142" s="37"/>
-      <c r="K142" s="37"/>
-      <c r="L142" s="37"/>
-      <c r="M142" s="39"/>
-      <c r="N142" s="37"/>
-      <c r="Q142" s="37"/>
-      <c r="R142" s="37"/>
-      <c r="S142" s="37"/>
-      <c r="T142" s="37"/>
-      <c r="U142" s="37"/>
-      <c r="V142" s="37"/>
-      <c r="W142" s="37"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="30"/>
+      <c r="D142" s="29"/>
+      <c r="E142" s="29"/>
+      <c r="F142" s="29"/>
+      <c r="G142" s="29"/>
+      <c r="H142" s="29"/>
+      <c r="I142" s="29"/>
+      <c r="J142" s="29"/>
+      <c r="K142" s="29"/>
+      <c r="L142" s="29"/>
+      <c r="M142" s="29"/>
+      <c r="N142" s="29"/>
+      <c r="Q142" s="29"/>
+      <c r="R142" s="29"/>
+      <c r="S142" s="29"/>
+      <c r="T142" s="29"/>
+      <c r="U142" s="29"/>
+      <c r="V142" s="29"/>
+      <c r="W142" s="29"/>
     </row>
     <row r="143" spans="1:23">
-      <c r="A143" s="37"/>
-      <c r="B143" s="37"/>
-      <c r="C143" s="38"/>
-      <c r="D143" s="37"/>
-      <c r="E143" s="37"/>
-      <c r="F143" s="37"/>
-      <c r="G143" s="39"/>
-      <c r="H143" s="37"/>
-      <c r="I143" s="37"/>
-      <c r="J143" s="37"/>
-      <c r="K143" s="37"/>
-      <c r="L143" s="37"/>
-      <c r="M143" s="39"/>
-      <c r="N143" s="37"/>
-      <c r="Q143" s="37"/>
-      <c r="R143" s="37"/>
-      <c r="S143" s="37"/>
-      <c r="T143" s="37"/>
-      <c r="U143" s="37"/>
-      <c r="V143" s="37"/>
-      <c r="W143" s="37"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="30"/>
+      <c r="D143" s="29"/>
+      <c r="E143" s="29"/>
+      <c r="F143" s="29"/>
+      <c r="G143" s="29"/>
+      <c r="H143" s="29"/>
+      <c r="I143" s="29"/>
+      <c r="J143" s="29"/>
+      <c r="K143" s="29"/>
+      <c r="L143" s="29"/>
+      <c r="M143" s="29"/>
+      <c r="N143" s="29"/>
+      <c r="Q143" s="29"/>
+      <c r="R143" s="29"/>
+      <c r="S143" s="29"/>
+      <c r="T143" s="29"/>
+      <c r="U143" s="29"/>
+      <c r="V143" s="29"/>
+      <c r="W143" s="29"/>
     </row>
     <row r="144" spans="1:23">
-      <c r="A144" s="37"/>
-      <c r="B144" s="37"/>
-      <c r="C144" s="38"/>
-      <c r="D144" s="37"/>
-      <c r="E144" s="37"/>
-      <c r="F144" s="37"/>
-      <c r="G144" s="39"/>
-      <c r="H144" s="37"/>
-      <c r="I144" s="37"/>
-      <c r="J144" s="37"/>
-      <c r="K144" s="37"/>
-      <c r="L144" s="37"/>
-      <c r="M144" s="39"/>
-      <c r="N144" s="37"/>
-      <c r="Q144" s="37"/>
-      <c r="R144" s="37"/>
-      <c r="S144" s="37"/>
-      <c r="T144" s="37"/>
-      <c r="U144" s="37"/>
-      <c r="V144" s="37"/>
-      <c r="W144" s="37"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="29"/>
+      <c r="E144" s="29"/>
+      <c r="F144" s="29"/>
+      <c r="G144" s="29"/>
+      <c r="H144" s="29"/>
+      <c r="I144" s="29"/>
+      <c r="J144" s="29"/>
+      <c r="K144" s="29"/>
+      <c r="L144" s="29"/>
+      <c r="M144" s="29"/>
+      <c r="N144" s="29"/>
+      <c r="Q144" s="29"/>
+      <c r="R144" s="29"/>
+      <c r="S144" s="29"/>
+      <c r="T144" s="29"/>
+      <c r="U144" s="29"/>
+      <c r="V144" s="29"/>
+      <c r="W144" s="29"/>
     </row>
     <row r="145" spans="1:23">
-      <c r="A145" s="37"/>
-      <c r="B145" s="37"/>
-      <c r="C145" s="38"/>
-      <c r="D145" s="37"/>
-      <c r="E145" s="37"/>
-      <c r="F145" s="37"/>
-      <c r="G145" s="39"/>
-      <c r="H145" s="37"/>
-      <c r="I145" s="37"/>
-      <c r="J145" s="37"/>
-      <c r="K145" s="37"/>
-      <c r="L145" s="37"/>
-      <c r="M145" s="39"/>
-      <c r="N145" s="37"/>
-      <c r="Q145" s="37"/>
-      <c r="R145" s="37"/>
-      <c r="S145" s="37"/>
-      <c r="T145" s="37"/>
-      <c r="U145" s="37"/>
-      <c r="V145" s="37"/>
-      <c r="W145" s="37"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="30"/>
+      <c r="D145" s="29"/>
+      <c r="E145" s="29"/>
+      <c r="F145" s="29"/>
+      <c r="G145" s="29"/>
+      <c r="H145" s="29"/>
+      <c r="I145" s="29"/>
+      <c r="J145" s="29"/>
+      <c r="K145" s="29"/>
+      <c r="L145" s="29"/>
+      <c r="M145" s="29"/>
+      <c r="N145" s="29"/>
+      <c r="Q145" s="29"/>
+      <c r="R145" s="29"/>
+      <c r="S145" s="29"/>
+      <c r="T145" s="29"/>
+      <c r="U145" s="29"/>
+      <c r="V145" s="29"/>
+      <c r="W145" s="29"/>
     </row>
     <row r="146" spans="1:23">
-      <c r="A146" s="37"/>
-      <c r="B146" s="37"/>
-      <c r="C146" s="38"/>
-      <c r="D146" s="37"/>
-      <c r="E146" s="37"/>
-      <c r="F146" s="37"/>
-      <c r="G146" s="39"/>
-      <c r="H146" s="37"/>
-      <c r="I146" s="37"/>
-      <c r="J146" s="37"/>
-      <c r="K146" s="37"/>
-      <c r="L146" s="37"/>
-      <c r="M146" s="39"/>
-      <c r="N146" s="37"/>
-      <c r="Q146" s="37"/>
-      <c r="R146" s="37"/>
-      <c r="S146" s="37"/>
-      <c r="T146" s="37"/>
-      <c r="U146" s="37"/>
-      <c r="V146" s="37"/>
-      <c r="W146" s="37"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="30"/>
+      <c r="D146" s="29"/>
+      <c r="E146" s="29"/>
+      <c r="F146" s="29"/>
+      <c r="G146" s="29"/>
+      <c r="H146" s="29"/>
+      <c r="I146" s="29"/>
+      <c r="J146" s="29"/>
+      <c r="K146" s="29"/>
+      <c r="L146" s="29"/>
+      <c r="M146" s="29"/>
+      <c r="N146" s="29"/>
+      <c r="Q146" s="29"/>
+      <c r="R146" s="29"/>
+      <c r="S146" s="29"/>
+      <c r="T146" s="29"/>
+      <c r="U146" s="29"/>
+      <c r="V146" s="29"/>
+      <c r="W146" s="29"/>
     </row>
     <row r="147" spans="1:23">
-      <c r="A147" s="37"/>
-      <c r="B147" s="37"/>
-      <c r="C147" s="38"/>
-      <c r="D147" s="37"/>
-      <c r="E147" s="37"/>
-      <c r="F147" s="37"/>
-      <c r="G147" s="39"/>
-      <c r="H147" s="37"/>
-      <c r="I147" s="37"/>
-      <c r="J147" s="37"/>
-      <c r="K147" s="37"/>
-      <c r="L147" s="37"/>
-      <c r="M147" s="39"/>
-      <c r="N147" s="37"/>
-      <c r="Q147" s="37"/>
-      <c r="R147" s="37"/>
-      <c r="S147" s="37"/>
-      <c r="T147" s="37"/>
-      <c r="U147" s="37"/>
-      <c r="V147" s="37"/>
-      <c r="W147" s="37"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="30"/>
+      <c r="D147" s="29"/>
+      <c r="E147" s="29"/>
+      <c r="F147" s="29"/>
+      <c r="G147" s="29"/>
+      <c r="H147" s="29"/>
+      <c r="I147" s="29"/>
+      <c r="J147" s="29"/>
+      <c r="K147" s="29"/>
+      <c r="L147" s="29"/>
+      <c r="M147" s="29"/>
+      <c r="N147" s="29"/>
+      <c r="Q147" s="29"/>
+      <c r="R147" s="29"/>
+      <c r="S147" s="29"/>
+      <c r="T147" s="29"/>
+      <c r="U147" s="29"/>
+      <c r="V147" s="29"/>
+      <c r="W147" s="29"/>
     </row>
     <row r="148" spans="1:23">
-      <c r="A148" s="37"/>
-      <c r="B148" s="37"/>
-      <c r="C148" s="38"/>
-      <c r="D148" s="37"/>
-      <c r="E148" s="37"/>
-      <c r="F148" s="37"/>
-      <c r="G148" s="39"/>
-      <c r="H148" s="37"/>
-      <c r="I148" s="37"/>
-      <c r="J148" s="37"/>
-      <c r="K148" s="37"/>
-      <c r="L148" s="37"/>
-      <c r="M148" s="39"/>
-      <c r="N148" s="37"/>
-      <c r="Q148" s="37"/>
-      <c r="R148" s="37"/>
-      <c r="S148" s="37"/>
-      <c r="T148" s="37"/>
-      <c r="U148" s="37"/>
-      <c r="V148" s="37"/>
-      <c r="W148" s="37"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="30"/>
+      <c r="D148" s="29"/>
+      <c r="E148" s="29"/>
+      <c r="F148" s="29"/>
+      <c r="G148" s="29"/>
+      <c r="H148" s="29"/>
+      <c r="I148" s="29"/>
+      <c r="J148" s="29"/>
+      <c r="K148" s="29"/>
+      <c r="L148" s="29"/>
+      <c r="M148" s="29"/>
+      <c r="N148" s="29"/>
+      <c r="Q148" s="29"/>
+      <c r="R148" s="29"/>
+      <c r="S148" s="29"/>
+      <c r="T148" s="29"/>
+      <c r="U148" s="29"/>
+      <c r="V148" s="29"/>
+      <c r="W148" s="29"/>
     </row>
     <row r="149" spans="1:23">
-      <c r="A149" s="37"/>
-      <c r="B149" s="37"/>
-      <c r="C149" s="38"/>
-      <c r="D149" s="37"/>
-      <c r="E149" s="37"/>
-      <c r="F149" s="37"/>
-      <c r="G149" s="39"/>
-      <c r="H149" s="37"/>
-      <c r="I149" s="37"/>
-      <c r="J149" s="37"/>
-      <c r="K149" s="37"/>
-      <c r="L149" s="37"/>
-      <c r="M149" s="39"/>
-      <c r="N149" s="37"/>
-      <c r="Q149" s="37"/>
-      <c r="R149" s="37"/>
-      <c r="S149" s="37"/>
-      <c r="T149" s="37"/>
-      <c r="U149" s="37"/>
-      <c r="V149" s="37"/>
-      <c r="W149" s="37"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="30"/>
+      <c r="D149" s="29"/>
+      <c r="E149" s="29"/>
+      <c r="F149" s="29"/>
+      <c r="G149" s="29"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="29"/>
+      <c r="J149" s="29"/>
+      <c r="K149" s="29"/>
+      <c r="L149" s="29"/>
+      <c r="M149" s="29"/>
+      <c r="N149" s="29"/>
+      <c r="Q149" s="29"/>
+      <c r="R149" s="29"/>
+      <c r="S149" s="29"/>
+      <c r="T149" s="29"/>
+      <c r="U149" s="29"/>
+      <c r="V149" s="29"/>
+      <c r="W149" s="29"/>
     </row>
     <row r="150" spans="1:23">
-      <c r="A150" s="37"/>
-      <c r="B150" s="37"/>
-      <c r="C150" s="38"/>
-      <c r="D150" s="37"/>
-      <c r="E150" s="37"/>
-      <c r="F150" s="37"/>
-      <c r="G150" s="39"/>
-      <c r="H150" s="37"/>
-      <c r="I150" s="37"/>
-      <c r="J150" s="37"/>
-      <c r="K150" s="37"/>
-      <c r="L150" s="37"/>
-      <c r="M150" s="39"/>
-      <c r="N150" s="37"/>
-      <c r="Q150" s="37"/>
-      <c r="R150" s="37"/>
-      <c r="S150" s="37"/>
-      <c r="T150" s="37"/>
-      <c r="U150" s="37"/>
-      <c r="V150" s="37"/>
-      <c r="W150" s="37"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="30"/>
+      <c r="D150" s="29"/>
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="29"/>
+      <c r="J150" s="29"/>
+      <c r="K150" s="29"/>
+      <c r="L150" s="29"/>
+      <c r="M150" s="29"/>
+      <c r="N150" s="29"/>
+      <c r="Q150" s="29"/>
+      <c r="R150" s="29"/>
+      <c r="S150" s="29"/>
+      <c r="T150" s="29"/>
+      <c r="U150" s="29"/>
+      <c r="V150" s="29"/>
+      <c r="W150" s="29"/>
     </row>
     <row r="151" spans="1:23">
-      <c r="A151" s="37"/>
-      <c r="B151" s="37"/>
-      <c r="C151" s="38"/>
-      <c r="D151" s="37"/>
-      <c r="E151" s="37"/>
-      <c r="F151" s="37"/>
-      <c r="G151" s="39"/>
-      <c r="H151" s="37"/>
-      <c r="I151" s="37"/>
-      <c r="J151" s="37"/>
-      <c r="K151" s="37"/>
-      <c r="L151" s="37"/>
-      <c r="M151" s="39"/>
-      <c r="N151" s="37"/>
-      <c r="Q151" s="37"/>
-      <c r="R151" s="37"/>
-      <c r="S151" s="37"/>
-      <c r="T151" s="37"/>
-      <c r="U151" s="37"/>
-      <c r="V151" s="37"/>
-      <c r="W151" s="37"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="30"/>
+      <c r="D151" s="29"/>
+      <c r="E151" s="29"/>
+      <c r="F151" s="29"/>
+      <c r="G151" s="29"/>
+      <c r="H151" s="29"/>
+      <c r="I151" s="29"/>
+      <c r="J151" s="29"/>
+      <c r="K151" s="29"/>
+      <c r="L151" s="29"/>
+      <c r="M151" s="29"/>
+      <c r="N151" s="29"/>
+      <c r="Q151" s="29"/>
+      <c r="R151" s="29"/>
+      <c r="S151" s="29"/>
+      <c r="T151" s="29"/>
+      <c r="U151" s="29"/>
+      <c r="V151" s="29"/>
+      <c r="W151" s="29"/>
     </row>
     <row r="152" spans="1:23">
-      <c r="A152" s="37"/>
-      <c r="B152" s="37"/>
-      <c r="C152" s="38"/>
-      <c r="D152" s="37"/>
-      <c r="E152" s="37"/>
-      <c r="F152" s="37"/>
-      <c r="G152" s="39"/>
-      <c r="H152" s="37"/>
-      <c r="I152" s="37"/>
-      <c r="J152" s="37"/>
-      <c r="K152" s="37"/>
-      <c r="L152" s="37"/>
-      <c r="M152" s="39"/>
-      <c r="N152" s="37"/>
-      <c r="Q152" s="37"/>
-      <c r="R152" s="37"/>
-      <c r="S152" s="37"/>
-      <c r="T152" s="37"/>
-      <c r="U152" s="37"/>
-      <c r="V152" s="37"/>
-      <c r="W152" s="37"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="30"/>
+      <c r="D152" s="29"/>
+      <c r="E152" s="29"/>
+      <c r="F152" s="29"/>
+      <c r="G152" s="29"/>
+      <c r="H152" s="29"/>
+      <c r="I152" s="29"/>
+      <c r="J152" s="29"/>
+      <c r="K152" s="29"/>
+      <c r="L152" s="29"/>
+      <c r="M152" s="29"/>
+      <c r="N152" s="29"/>
+      <c r="Q152" s="29"/>
+      <c r="R152" s="29"/>
+      <c r="S152" s="29"/>
+      <c r="T152" s="29"/>
+      <c r="U152" s="29"/>
+      <c r="V152" s="29"/>
+      <c r="W152" s="29"/>
     </row>
     <row r="153" spans="1:23">
-      <c r="A153" s="37"/>
-      <c r="B153" s="37"/>
-      <c r="C153" s="38"/>
-      <c r="D153" s="37"/>
-      <c r="E153" s="37"/>
-      <c r="F153" s="37"/>
-      <c r="G153" s="39"/>
-      <c r="H153" s="37"/>
-      <c r="I153" s="37"/>
-      <c r="J153" s="37"/>
-      <c r="K153" s="37"/>
-      <c r="L153" s="37"/>
-      <c r="M153" s="39"/>
-      <c r="N153" s="37"/>
-      <c r="Q153" s="37"/>
-      <c r="R153" s="37"/>
-      <c r="S153" s="37"/>
-      <c r="T153" s="37"/>
-      <c r="U153" s="37"/>
-      <c r="V153" s="37"/>
-      <c r="W153" s="37"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="30"/>
+      <c r="D153" s="29"/>
+      <c r="E153" s="29"/>
+      <c r="F153" s="29"/>
+      <c r="G153" s="29"/>
+      <c r="H153" s="29"/>
+      <c r="I153" s="29"/>
+      <c r="J153" s="29"/>
+      <c r="K153" s="29"/>
+      <c r="L153" s="29"/>
+      <c r="M153" s="29"/>
+      <c r="N153" s="29"/>
+      <c r="Q153" s="29"/>
+      <c r="R153" s="29"/>
+      <c r="S153" s="29"/>
+      <c r="T153" s="29"/>
+      <c r="U153" s="29"/>
+      <c r="V153" s="29"/>
+      <c r="W153" s="29"/>
     </row>
     <row r="154" spans="1:23">
-      <c r="A154" s="37"/>
-      <c r="B154" s="37"/>
-      <c r="C154" s="38"/>
-      <c r="D154" s="37"/>
-      <c r="E154" s="37"/>
-      <c r="F154" s="37"/>
-      <c r="G154" s="39"/>
-      <c r="H154" s="37"/>
-      <c r="I154" s="37"/>
-      <c r="J154" s="37"/>
-      <c r="K154" s="37"/>
-      <c r="L154" s="37"/>
-      <c r="M154" s="39"/>
-      <c r="N154" s="37"/>
-      <c r="Q154" s="37"/>
-      <c r="R154" s="37"/>
-      <c r="S154" s="37"/>
-      <c r="T154" s="37"/>
-      <c r="U154" s="37"/>
-      <c r="V154" s="37"/>
-      <c r="W154" s="37"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="30"/>
+      <c r="D154" s="29"/>
+      <c r="E154" s="29"/>
+      <c r="F154" s="29"/>
+      <c r="G154" s="29"/>
+      <c r="H154" s="29"/>
+      <c r="I154" s="29"/>
+      <c r="J154" s="29"/>
+      <c r="K154" s="29"/>
+      <c r="L154" s="29"/>
+      <c r="M154" s="29"/>
+      <c r="N154" s="29"/>
+      <c r="Q154" s="29"/>
+      <c r="R154" s="29"/>
+      <c r="S154" s="29"/>
+      <c r="T154" s="29"/>
+      <c r="U154" s="29"/>
+      <c r="V154" s="29"/>
+      <c r="W154" s="29"/>
     </row>
     <row r="155" spans="1:23">
-      <c r="A155" s="37"/>
-      <c r="B155" s="37"/>
-      <c r="C155" s="38"/>
-      <c r="D155" s="37"/>
-      <c r="E155" s="37"/>
-      <c r="F155" s="37"/>
-      <c r="G155" s="39"/>
-      <c r="H155" s="37"/>
-      <c r="I155" s="37"/>
-      <c r="J155" s="37"/>
-      <c r="K155" s="37"/>
-      <c r="L155" s="37"/>
-      <c r="M155" s="39"/>
-      <c r="N155" s="37"/>
-      <c r="Q155" s="37"/>
-      <c r="R155" s="37"/>
-      <c r="S155" s="37"/>
-      <c r="T155" s="37"/>
-      <c r="U155" s="37"/>
-      <c r="V155" s="37"/>
-      <c r="W155" s="37"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="30"/>
+      <c r="D155" s="29"/>
+      <c r="E155" s="29"/>
+      <c r="F155" s="29"/>
+      <c r="G155" s="29"/>
+      <c r="H155" s="29"/>
+      <c r="I155" s="29"/>
+      <c r="J155" s="29"/>
+      <c r="K155" s="29"/>
+      <c r="L155" s="29"/>
+      <c r="M155" s="29"/>
+      <c r="N155" s="29"/>
+      <c r="Q155" s="29"/>
+      <c r="R155" s="29"/>
+      <c r="S155" s="29"/>
+      <c r="T155" s="29"/>
+      <c r="U155" s="29"/>
+      <c r="V155" s="29"/>
+      <c r="W155" s="29"/>
     </row>
     <row r="156" spans="1:23">
-      <c r="A156" s="37"/>
-      <c r="B156" s="37"/>
-      <c r="C156" s="38"/>
-      <c r="D156" s="37"/>
-      <c r="E156" s="37"/>
-      <c r="F156" s="37"/>
-      <c r="G156" s="39"/>
-      <c r="H156" s="37"/>
-      <c r="I156" s="37"/>
-      <c r="J156" s="37"/>
-      <c r="K156" s="37"/>
-      <c r="L156" s="37"/>
-      <c r="M156" s="39"/>
-      <c r="N156" s="37"/>
-      <c r="Q156" s="37"/>
-      <c r="R156" s="37"/>
-      <c r="S156" s="37"/>
-      <c r="T156" s="37"/>
-      <c r="U156" s="37"/>
-      <c r="V156" s="37"/>
-      <c r="W156" s="37"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="30"/>
+      <c r="D156" s="29"/>
+      <c r="E156" s="29"/>
+      <c r="F156" s="29"/>
+      <c r="G156" s="29"/>
+      <c r="H156" s="29"/>
+      <c r="I156" s="29"/>
+      <c r="J156" s="29"/>
+      <c r="K156" s="29"/>
+      <c r="L156" s="29"/>
+      <c r="M156" s="29"/>
+      <c r="N156" s="29"/>
+      <c r="Q156" s="29"/>
+      <c r="R156" s="29"/>
+      <c r="S156" s="29"/>
+      <c r="T156" s="29"/>
+      <c r="U156" s="29"/>
+      <c r="V156" s="29"/>
+      <c r="W156" s="29"/>
     </row>
     <row r="157" spans="1:23">
-      <c r="A157" s="37"/>
-      <c r="B157" s="37"/>
-      <c r="C157" s="38"/>
-      <c r="D157" s="37"/>
-      <c r="E157" s="37"/>
-      <c r="F157" s="37"/>
-      <c r="G157" s="39"/>
-      <c r="H157" s="37"/>
-      <c r="I157" s="37"/>
-      <c r="J157" s="37"/>
-      <c r="K157" s="37"/>
-      <c r="L157" s="37"/>
-      <c r="M157" s="39"/>
-      <c r="N157" s="37"/>
-      <c r="Q157" s="37"/>
-      <c r="R157" s="37"/>
-      <c r="S157" s="37"/>
-      <c r="T157" s="37"/>
-      <c r="U157" s="37"/>
-      <c r="V157" s="37"/>
-      <c r="W157" s="37"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="30"/>
+      <c r="D157" s="29"/>
+      <c r="E157" s="29"/>
+      <c r="F157" s="29"/>
+      <c r="G157" s="29"/>
+      <c r="H157" s="29"/>
+      <c r="I157" s="29"/>
+      <c r="J157" s="29"/>
+      <c r="K157" s="29"/>
+      <c r="L157" s="29"/>
+      <c r="M157" s="29"/>
+      <c r="N157" s="29"/>
+      <c r="Q157" s="29"/>
+      <c r="R157" s="29"/>
+      <c r="S157" s="29"/>
+      <c r="T157" s="29"/>
+      <c r="U157" s="29"/>
+      <c r="V157" s="29"/>
+      <c r="W157" s="29"/>
     </row>
     <row r="158" spans="1:23">
-      <c r="A158" s="37"/>
-      <c r="B158" s="37"/>
-      <c r="C158" s="38"/>
-      <c r="D158" s="37"/>
-      <c r="E158" s="37"/>
-      <c r="F158" s="37"/>
-      <c r="G158" s="39"/>
-      <c r="H158" s="37"/>
-      <c r="I158" s="37"/>
-      <c r="J158" s="37"/>
-      <c r="K158" s="37"/>
-      <c r="L158" s="37"/>
-      <c r="M158" s="39"/>
-      <c r="N158" s="37"/>
-      <c r="Q158" s="37"/>
-      <c r="R158" s="37"/>
-      <c r="S158" s="37"/>
-      <c r="T158" s="37"/>
-      <c r="U158" s="37"/>
-      <c r="V158" s="37"/>
-      <c r="W158" s="37"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="30"/>
+      <c r="D158" s="29"/>
+      <c r="E158" s="29"/>
+      <c r="F158" s="29"/>
+      <c r="G158" s="29"/>
+      <c r="H158" s="29"/>
+      <c r="I158" s="29"/>
+      <c r="J158" s="29"/>
+      <c r="K158" s="29"/>
+      <c r="L158" s="29"/>
+      <c r="M158" s="29"/>
+      <c r="N158" s="29"/>
+      <c r="Q158" s="29"/>
+      <c r="R158" s="29"/>
+      <c r="S158" s="29"/>
+      <c r="T158" s="29"/>
+      <c r="U158" s="29"/>
+      <c r="V158" s="29"/>
+      <c r="W158" s="29"/>
     </row>
     <row r="159" spans="1:23">
-      <c r="A159" s="37"/>
-      <c r="B159" s="37"/>
-      <c r="C159" s="38"/>
-      <c r="D159" s="37"/>
-      <c r="E159" s="37"/>
-      <c r="F159" s="37"/>
-      <c r="G159" s="39"/>
-      <c r="H159" s="37"/>
-      <c r="I159" s="37"/>
-      <c r="J159" s="37"/>
-      <c r="K159" s="37"/>
-      <c r="L159" s="37"/>
-      <c r="M159" s="39"/>
-      <c r="N159" s="37"/>
-      <c r="Q159" s="37"/>
-      <c r="R159" s="37"/>
-      <c r="S159" s="37"/>
-      <c r="T159" s="37"/>
-      <c r="U159" s="37"/>
-      <c r="V159" s="37"/>
-      <c r="W159" s="37"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
+      <c r="C159" s="30"/>
+      <c r="D159" s="29"/>
+      <c r="E159" s="29"/>
+      <c r="F159" s="29"/>
+      <c r="G159" s="29"/>
+      <c r="H159" s="29"/>
+      <c r="I159" s="29"/>
+      <c r="J159" s="29"/>
+      <c r="K159" s="29"/>
+      <c r="L159" s="29"/>
+      <c r="M159" s="29"/>
+      <c r="N159" s="29"/>
+      <c r="Q159" s="29"/>
+      <c r="R159" s="29"/>
+      <c r="S159" s="29"/>
+      <c r="T159" s="29"/>
+      <c r="U159" s="29"/>
+      <c r="V159" s="29"/>
+      <c r="W159" s="29"/>
     </row>
     <row r="160" spans="1:23">
-      <c r="A160" s="37"/>
-      <c r="B160" s="37"/>
-      <c r="C160" s="38"/>
-      <c r="D160" s="37"/>
-      <c r="E160" s="37"/>
-      <c r="F160" s="37"/>
-      <c r="G160" s="39"/>
-      <c r="H160" s="37"/>
-      <c r="I160" s="37"/>
-      <c r="J160" s="37"/>
-      <c r="K160" s="37"/>
-      <c r="L160" s="37"/>
-      <c r="M160" s="39"/>
-      <c r="N160" s="37"/>
-      <c r="Q160" s="37"/>
-      <c r="R160" s="37"/>
-      <c r="S160" s="37"/>
-      <c r="T160" s="37"/>
-      <c r="U160" s="37"/>
-      <c r="V160" s="37"/>
-      <c r="W160" s="37"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="30"/>
+      <c r="D160" s="29"/>
+      <c r="E160" s="29"/>
+      <c r="F160" s="29"/>
+      <c r="G160" s="29"/>
+      <c r="H160" s="29"/>
+      <c r="I160" s="29"/>
+      <c r="J160" s="29"/>
+      <c r="K160" s="29"/>
+      <c r="L160" s="29"/>
+      <c r="M160" s="29"/>
+      <c r="N160" s="29"/>
+      <c r="Q160" s="29"/>
+      <c r="R160" s="29"/>
+      <c r="S160" s="29"/>
+      <c r="T160" s="29"/>
+      <c r="U160" s="29"/>
+      <c r="V160" s="29"/>
+      <c r="W160" s="29"/>
     </row>
     <row r="161" spans="1:23">
-      <c r="A161" s="37"/>
-      <c r="B161" s="37"/>
-      <c r="C161" s="38"/>
-      <c r="D161" s="37"/>
-      <c r="E161" s="37"/>
-      <c r="F161" s="37"/>
-      <c r="G161" s="39"/>
-      <c r="H161" s="37"/>
-      <c r="I161" s="37"/>
-      <c r="J161" s="37"/>
-      <c r="K161" s="37"/>
-      <c r="L161" s="37"/>
-      <c r="M161" s="39"/>
-      <c r="N161" s="37"/>
-      <c r="Q161" s="37"/>
-      <c r="R161" s="37"/>
-      <c r="S161" s="37"/>
-      <c r="T161" s="37"/>
-      <c r="U161" s="37"/>
-      <c r="V161" s="37"/>
-      <c r="W161" s="37"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
+      <c r="C161" s="30"/>
+      <c r="D161" s="29"/>
+      <c r="E161" s="29"/>
+      <c r="F161" s="29"/>
+      <c r="G161" s="29"/>
+      <c r="H161" s="29"/>
+      <c r="I161" s="29"/>
+      <c r="J161" s="29"/>
+      <c r="K161" s="29"/>
+      <c r="L161" s="29"/>
+      <c r="M161" s="29"/>
+      <c r="N161" s="29"/>
+      <c r="Q161" s="29"/>
+      <c r="R161" s="29"/>
+      <c r="S161" s="29"/>
+      <c r="T161" s="29"/>
+      <c r="U161" s="29"/>
+      <c r="V161" s="29"/>
+      <c r="W161" s="29"/>
     </row>
     <row r="162" spans="1:23">
-      <c r="A162" s="37"/>
-      <c r="B162" s="37"/>
-      <c r="C162" s="38"/>
-      <c r="D162" s="37"/>
-      <c r="E162" s="37"/>
-      <c r="F162" s="37"/>
-      <c r="G162" s="39"/>
-      <c r="H162" s="37"/>
-      <c r="I162" s="37"/>
-      <c r="J162" s="37"/>
-      <c r="K162" s="37"/>
-      <c r="L162" s="37"/>
-      <c r="M162" s="39"/>
-      <c r="N162" s="37"/>
-      <c r="Q162" s="37"/>
-      <c r="R162" s="37"/>
-      <c r="S162" s="37"/>
-      <c r="T162" s="37"/>
-      <c r="U162" s="37"/>
-      <c r="V162" s="37"/>
-      <c r="W162" s="37"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
+      <c r="C162" s="30"/>
+      <c r="D162" s="29"/>
+      <c r="E162" s="29"/>
+      <c r="F162" s="29"/>
+      <c r="G162" s="29"/>
+      <c r="H162" s="29"/>
+      <c r="I162" s="29"/>
+      <c r="J162" s="29"/>
+      <c r="K162" s="29"/>
+      <c r="L162" s="29"/>
+      <c r="M162" s="29"/>
+      <c r="N162" s="29"/>
+      <c r="Q162" s="29"/>
+      <c r="R162" s="29"/>
+      <c r="S162" s="29"/>
+      <c r="T162" s="29"/>
+      <c r="U162" s="29"/>
+      <c r="V162" s="29"/>
+      <c r="W162" s="29"/>
     </row>
     <row r="163" spans="1:23">
-      <c r="A163" s="37"/>
-      <c r="B163" s="37"/>
-      <c r="C163" s="38"/>
-      <c r="D163" s="37"/>
-      <c r="E163" s="37"/>
-      <c r="F163" s="37"/>
-      <c r="G163" s="39"/>
-      <c r="H163" s="37"/>
-      <c r="I163" s="37"/>
-      <c r="J163" s="37"/>
-      <c r="K163" s="37"/>
-      <c r="L163" s="37"/>
-      <c r="M163" s="39"/>
-      <c r="N163" s="37"/>
-      <c r="Q163" s="37"/>
-      <c r="R163" s="37"/>
-      <c r="S163" s="37"/>
-      <c r="T163" s="37"/>
-      <c r="U163" s="37"/>
-      <c r="V163" s="37"/>
-      <c r="W163" s="37"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
+      <c r="C163" s="30"/>
+      <c r="D163" s="29"/>
+      <c r="E163" s="29"/>
+      <c r="F163" s="29"/>
+      <c r="G163" s="29"/>
+      <c r="H163" s="29"/>
+      <c r="I163" s="29"/>
+      <c r="J163" s="29"/>
+      <c r="K163" s="29"/>
+      <c r="L163" s="29"/>
+      <c r="M163" s="29"/>
+      <c r="N163" s="29"/>
+      <c r="Q163" s="29"/>
+      <c r="R163" s="29"/>
+      <c r="S163" s="29"/>
+      <c r="T163" s="29"/>
+      <c r="U163" s="29"/>
+      <c r="V163" s="29"/>
+      <c r="W163" s="29"/>
     </row>
     <row r="164" spans="1:23">
-      <c r="A164" s="37"/>
-      <c r="B164" s="37"/>
-      <c r="C164" s="38"/>
-      <c r="D164" s="37"/>
-      <c r="E164" s="37"/>
-      <c r="F164" s="37"/>
-      <c r="G164" s="39"/>
-      <c r="H164" s="37"/>
-      <c r="I164" s="37"/>
-      <c r="J164" s="37"/>
-      <c r="K164" s="37"/>
-      <c r="L164" s="37"/>
-      <c r="M164" s="39"/>
-      <c r="N164" s="37"/>
-      <c r="Q164" s="37"/>
-      <c r="R164" s="37"/>
-      <c r="S164" s="37"/>
-      <c r="T164" s="37"/>
-      <c r="U164" s="37"/>
-      <c r="V164" s="37"/>
-      <c r="W164" s="37"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
+      <c r="C164" s="30"/>
+      <c r="D164" s="29"/>
+      <c r="E164" s="29"/>
+      <c r="F164" s="29"/>
+      <c r="G164" s="29"/>
+      <c r="H164" s="29"/>
+      <c r="I164" s="29"/>
+      <c r="J164" s="29"/>
+      <c r="K164" s="29"/>
+      <c r="L164" s="29"/>
+      <c r="M164" s="29"/>
+      <c r="N164" s="29"/>
+      <c r="Q164" s="29"/>
+      <c r="R164" s="29"/>
+      <c r="S164" s="29"/>
+      <c r="T164" s="29"/>
+      <c r="U164" s="29"/>
+      <c r="V164" s="29"/>
+      <c r="W164" s="29"/>
     </row>
     <row r="165" spans="1:23">
-      <c r="A165" s="37"/>
-      <c r="B165" s="37"/>
-      <c r="C165" s="38"/>
-      <c r="D165" s="37"/>
-      <c r="E165" s="37"/>
-      <c r="F165" s="37"/>
-      <c r="G165" s="39"/>
-      <c r="H165" s="37"/>
-      <c r="I165" s="37"/>
-      <c r="J165" s="37"/>
-      <c r="K165" s="37"/>
-      <c r="L165" s="37"/>
-      <c r="M165" s="39"/>
-      <c r="N165" s="37"/>
-      <c r="Q165" s="37"/>
-      <c r="R165" s="37"/>
-      <c r="S165" s="37"/>
-      <c r="T165" s="37"/>
-      <c r="U165" s="37"/>
-      <c r="V165" s="37"/>
-      <c r="W165" s="37"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
+      <c r="C165" s="30"/>
+      <c r="D165" s="29"/>
+      <c r="E165" s="29"/>
+      <c r="F165" s="29"/>
+      <c r="G165" s="29"/>
+      <c r="H165" s="29"/>
+      <c r="I165" s="29"/>
+      <c r="J165" s="29"/>
+      <c r="K165" s="29"/>
+      <c r="L165" s="29"/>
+      <c r="M165" s="29"/>
+      <c r="N165" s="29"/>
+      <c r="Q165" s="29"/>
+      <c r="R165" s="29"/>
+      <c r="S165" s="29"/>
+      <c r="T165" s="29"/>
+      <c r="U165" s="29"/>
+      <c r="V165" s="29"/>
+      <c r="W165" s="29"/>
     </row>
     <row r="166" spans="1:23">
-      <c r="A166" s="37"/>
-      <c r="B166" s="37"/>
-      <c r="C166" s="38"/>
-      <c r="D166" s="37"/>
-      <c r="E166" s="37"/>
-      <c r="F166" s="37"/>
-      <c r="G166" s="39"/>
-      <c r="H166" s="37"/>
-      <c r="I166" s="37"/>
-      <c r="J166" s="37"/>
-      <c r="K166" s="37"/>
-      <c r="L166" s="37"/>
-      <c r="M166" s="39"/>
-      <c r="N166" s="37"/>
-      <c r="Q166" s="37"/>
-      <c r="R166" s="37"/>
-      <c r="S166" s="37"/>
-      <c r="T166" s="37"/>
-      <c r="U166" s="37"/>
-      <c r="V166" s="37"/>
-      <c r="W166" s="37"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="30"/>
+      <c r="D166" s="29"/>
+      <c r="E166" s="29"/>
+      <c r="F166" s="29"/>
+      <c r="G166" s="29"/>
+      <c r="H166" s="29"/>
+      <c r="I166" s="29"/>
+      <c r="J166" s="29"/>
+      <c r="K166" s="29"/>
+      <c r="L166" s="29"/>
+      <c r="M166" s="29"/>
+      <c r="N166" s="29"/>
+      <c r="Q166" s="29"/>
+      <c r="R166" s="29"/>
+      <c r="S166" s="29"/>
+      <c r="T166" s="29"/>
+      <c r="U166" s="29"/>
+      <c r="V166" s="29"/>
+      <c r="W166" s="29"/>
     </row>
     <row r="167" spans="1:23">
-      <c r="A167" s="37"/>
-      <c r="B167" s="37"/>
-      <c r="C167" s="38"/>
-      <c r="D167" s="37"/>
-      <c r="E167" s="37"/>
-      <c r="F167" s="37"/>
-      <c r="G167" s="39"/>
-      <c r="H167" s="37"/>
-      <c r="I167" s="37"/>
-      <c r="J167" s="37"/>
-      <c r="K167" s="37"/>
-      <c r="L167" s="37"/>
-      <c r="M167" s="39"/>
-      <c r="N167" s="37"/>
-      <c r="Q167" s="37"/>
-      <c r="R167" s="37"/>
-      <c r="S167" s="37"/>
-      <c r="T167" s="37"/>
-      <c r="U167" s="37"/>
-      <c r="V167" s="37"/>
-      <c r="W167" s="37"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
+      <c r="C167" s="30"/>
+      <c r="D167" s="29"/>
+      <c r="E167" s="29"/>
+      <c r="F167" s="29"/>
+      <c r="G167" s="29"/>
+      <c r="H167" s="29"/>
+      <c r="I167" s="29"/>
+      <c r="J167" s="29"/>
+      <c r="K167" s="29"/>
+      <c r="L167" s="29"/>
+      <c r="M167" s="29"/>
+      <c r="N167" s="29"/>
+      <c r="Q167" s="29"/>
+      <c r="R167" s="29"/>
+      <c r="S167" s="29"/>
+      <c r="T167" s="29"/>
+      <c r="U167" s="29"/>
+      <c r="V167" s="29"/>
+      <c r="W167" s="29"/>
     </row>
     <row r="168" spans="1:23">
-      <c r="A168" s="37"/>
-      <c r="B168" s="37"/>
-      <c r="C168" s="38"/>
-      <c r="D168" s="37"/>
-      <c r="E168" s="37"/>
-      <c r="F168" s="37"/>
-      <c r="G168" s="39"/>
-      <c r="H168" s="37"/>
-      <c r="I168" s="37"/>
-      <c r="J168" s="37"/>
-      <c r="K168" s="37"/>
-      <c r="L168" s="37"/>
-      <c r="M168" s="39"/>
-      <c r="N168" s="37"/>
-      <c r="Q168" s="37"/>
-      <c r="R168" s="37"/>
-      <c r="S168" s="37"/>
-      <c r="T168" s="37"/>
-      <c r="U168" s="37"/>
-      <c r="V168" s="37"/>
-      <c r="W168" s="37"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
+      <c r="C168" s="30"/>
+      <c r="D168" s="29"/>
+      <c r="E168" s="29"/>
+      <c r="F168" s="29"/>
+      <c r="G168" s="29"/>
+      <c r="H168" s="29"/>
+      <c r="I168" s="29"/>
+      <c r="J168" s="29"/>
+      <c r="K168" s="29"/>
+      <c r="L168" s="29"/>
+      <c r="M168" s="29"/>
+      <c r="N168" s="29"/>
+      <c r="Q168" s="29"/>
+      <c r="R168" s="29"/>
+      <c r="S168" s="29"/>
+      <c r="T168" s="29"/>
+      <c r="U168" s="29"/>
+      <c r="V168" s="29"/>
+      <c r="W168" s="29"/>
     </row>
     <row r="169" spans="1:23">
-      <c r="A169" s="37"/>
-      <c r="B169" s="37"/>
-      <c r="C169" s="38"/>
-      <c r="D169" s="37"/>
-      <c r="E169" s="37"/>
-      <c r="F169" s="37"/>
-      <c r="G169" s="39"/>
-      <c r="H169" s="37"/>
-      <c r="I169" s="37"/>
-      <c r="J169" s="37"/>
-      <c r="K169" s="37"/>
-      <c r="L169" s="37"/>
-      <c r="M169" s="39"/>
-      <c r="N169" s="37"/>
-      <c r="Q169" s="37"/>
-      <c r="R169" s="37"/>
-      <c r="S169" s="37"/>
-      <c r="T169" s="37"/>
-      <c r="U169" s="37"/>
-      <c r="V169" s="37"/>
-      <c r="W169" s="37"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
+      <c r="C169" s="30"/>
+      <c r="D169" s="29"/>
+      <c r="E169" s="29"/>
+      <c r="F169" s="29"/>
+      <c r="G169" s="29"/>
+      <c r="H169" s="29"/>
+      <c r="I169" s="29"/>
+      <c r="J169" s="29"/>
+      <c r="K169" s="29"/>
+      <c r="L169" s="29"/>
+      <c r="M169" s="29"/>
+      <c r="N169" s="29"/>
+      <c r="Q169" s="29"/>
+      <c r="R169" s="29"/>
+      <c r="S169" s="29"/>
+      <c r="T169" s="29"/>
+      <c r="U169" s="29"/>
+      <c r="V169" s="29"/>
+      <c r="W169" s="29"/>
     </row>
     <row r="170" spans="1:23">
-      <c r="A170" s="37"/>
-      <c r="B170" s="37"/>
-      <c r="C170" s="38"/>
-      <c r="D170" s="37"/>
-      <c r="E170" s="37"/>
-      <c r="F170" s="37"/>
-      <c r="G170" s="39"/>
-      <c r="H170" s="37"/>
-      <c r="I170" s="37"/>
-      <c r="J170" s="37"/>
-      <c r="K170" s="37"/>
-      <c r="L170" s="37"/>
-      <c r="M170" s="39"/>
-      <c r="N170" s="37"/>
-      <c r="Q170" s="37"/>
-      <c r="R170" s="37"/>
-      <c r="S170" s="37"/>
-      <c r="T170" s="37"/>
-      <c r="U170" s="37"/>
-      <c r="V170" s="37"/>
-      <c r="W170" s="37"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
+      <c r="C170" s="30"/>
+      <c r="D170" s="29"/>
+      <c r="E170" s="29"/>
+      <c r="F170" s="29"/>
+      <c r="G170" s="29"/>
+      <c r="H170" s="29"/>
+      <c r="I170" s="29"/>
+      <c r="J170" s="29"/>
+      <c r="K170" s="29"/>
+      <c r="L170" s="29"/>
+      <c r="M170" s="29"/>
+      <c r="N170" s="29"/>
+      <c r="Q170" s="29"/>
+      <c r="R170" s="29"/>
+      <c r="S170" s="29"/>
+      <c r="T170" s="29"/>
+      <c r="U170" s="29"/>
+      <c r="V170" s="29"/>
+      <c r="W170" s="29"/>
     </row>
     <row r="171" spans="1:23">
-      <c r="A171" s="37"/>
-      <c r="B171" s="37"/>
-      <c r="C171" s="38"/>
-      <c r="D171" s="37"/>
-      <c r="E171" s="37"/>
-      <c r="F171" s="37"/>
-      <c r="G171" s="39"/>
-      <c r="H171" s="37"/>
-      <c r="I171" s="37"/>
-      <c r="J171" s="37"/>
-      <c r="K171" s="37"/>
-      <c r="L171" s="37"/>
-      <c r="M171" s="39"/>
-      <c r="N171" s="37"/>
-      <c r="Q171" s="37"/>
-      <c r="R171" s="37"/>
-      <c r="S171" s="37"/>
-      <c r="T171" s="37"/>
-      <c r="U171" s="37"/>
-      <c r="V171" s="37"/>
-      <c r="W171" s="37"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
+      <c r="C171" s="30"/>
+      <c r="D171" s="29"/>
+      <c r="E171" s="29"/>
+      <c r="F171" s="29"/>
+      <c r="G171" s="29"/>
+      <c r="H171" s="29"/>
+      <c r="I171" s="29"/>
+      <c r="J171" s="29"/>
+      <c r="K171" s="29"/>
+      <c r="L171" s="29"/>
+      <c r="M171" s="29"/>
+      <c r="N171" s="29"/>
+      <c r="Q171" s="29"/>
+      <c r="R171" s="29"/>
+      <c r="S171" s="29"/>
+      <c r="T171" s="29"/>
+      <c r="U171" s="29"/>
+      <c r="V171" s="29"/>
+      <c r="W171" s="29"/>
     </row>
     <row r="172" spans="1:23">
-      <c r="A172" s="37"/>
-      <c r="B172" s="37"/>
-      <c r="C172" s="38"/>
-      <c r="D172" s="37"/>
-      <c r="E172" s="37"/>
-      <c r="F172" s="37"/>
-      <c r="G172" s="39"/>
-      <c r="H172" s="37"/>
-      <c r="I172" s="37"/>
-      <c r="J172" s="37"/>
-      <c r="K172" s="37"/>
-      <c r="L172" s="37"/>
-      <c r="M172" s="39"/>
-      <c r="N172" s="37"/>
-      <c r="Q172" s="37"/>
-      <c r="R172" s="37"/>
-      <c r="S172" s="37"/>
-      <c r="T172" s="37"/>
-      <c r="U172" s="37"/>
-      <c r="V172" s="37"/>
-      <c r="W172" s="37"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="30"/>
+      <c r="D172" s="29"/>
+      <c r="E172" s="29"/>
+      <c r="F172" s="29"/>
+      <c r="G172" s="29"/>
+      <c r="H172" s="29"/>
+      <c r="I172" s="29"/>
+      <c r="J172" s="29"/>
+      <c r="K172" s="29"/>
+      <c r="L172" s="29"/>
+      <c r="M172" s="29"/>
+      <c r="N172" s="29"/>
+      <c r="Q172" s="29"/>
+      <c r="R172" s="29"/>
+      <c r="S172" s="29"/>
+      <c r="T172" s="29"/>
+      <c r="U172" s="29"/>
+      <c r="V172" s="29"/>
+      <c r="W172" s="29"/>
     </row>
     <row r="173" spans="1:23">
-      <c r="A173" s="37"/>
-      <c r="B173" s="37"/>
-      <c r="C173" s="38"/>
-      <c r="D173" s="37"/>
-      <c r="E173" s="37"/>
-      <c r="F173" s="37"/>
-      <c r="G173" s="39"/>
-      <c r="H173" s="37"/>
-      <c r="I173" s="37"/>
-      <c r="J173" s="37"/>
-      <c r="K173" s="37"/>
-      <c r="L173" s="37"/>
-      <c r="M173" s="39"/>
-      <c r="N173" s="37"/>
-      <c r="Q173" s="37"/>
-      <c r="R173" s="37"/>
-      <c r="S173" s="37"/>
-      <c r="T173" s="37"/>
-      <c r="U173" s="37"/>
-      <c r="V173" s="37"/>
-      <c r="W173" s="37"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
+      <c r="C173" s="30"/>
+      <c r="D173" s="29"/>
+      <c r="E173" s="29"/>
+      <c r="F173" s="29"/>
+      <c r="G173" s="29"/>
+      <c r="H173" s="29"/>
+      <c r="I173" s="29"/>
+      <c r="J173" s="29"/>
+      <c r="K173" s="29"/>
+      <c r="L173" s="29"/>
+      <c r="M173" s="29"/>
+      <c r="N173" s="29"/>
+      <c r="Q173" s="29"/>
+      <c r="R173" s="29"/>
+      <c r="S173" s="29"/>
+      <c r="T173" s="29"/>
+      <c r="U173" s="29"/>
+      <c r="V173" s="29"/>
+      <c r="W173" s="29"/>
     </row>
     <row r="174" spans="1:23">
-      <c r="A174" s="37"/>
-      <c r="B174" s="37"/>
-      <c r="C174" s="38"/>
-      <c r="D174" s="37"/>
-      <c r="E174" s="37"/>
-      <c r="F174" s="37"/>
-      <c r="G174" s="39"/>
-      <c r="H174" s="37"/>
-      <c r="I174" s="37"/>
-      <c r="J174" s="37"/>
-      <c r="K174" s="37"/>
-      <c r="L174" s="37"/>
-      <c r="M174" s="39"/>
-      <c r="N174" s="37"/>
-      <c r="Q174" s="37"/>
-      <c r="R174" s="37"/>
-      <c r="S174" s="37"/>
-      <c r="T174" s="37"/>
-      <c r="U174" s="37"/>
-      <c r="V174" s="37"/>
-      <c r="W174" s="37"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
+      <c r="C174" s="30"/>
+      <c r="D174" s="29"/>
+      <c r="E174" s="29"/>
+      <c r="F174" s="29"/>
+      <c r="G174" s="29"/>
+      <c r="H174" s="29"/>
+      <c r="I174" s="29"/>
+      <c r="J174" s="29"/>
+      <c r="K174" s="29"/>
+      <c r="L174" s="29"/>
+      <c r="M174" s="29"/>
+      <c r="N174" s="29"/>
+      <c r="Q174" s="29"/>
+      <c r="R174" s="29"/>
+      <c r="S174" s="29"/>
+      <c r="T174" s="29"/>
+      <c r="U174" s="29"/>
+      <c r="V174" s="29"/>
+      <c r="W174" s="29"/>
     </row>
     <row r="175" spans="1:23">
-      <c r="A175" s="37"/>
-      <c r="B175" s="37"/>
-      <c r="C175" s="38"/>
-      <c r="D175" s="37"/>
-      <c r="E175" s="37"/>
-      <c r="F175" s="37"/>
-      <c r="G175" s="39"/>
-      <c r="H175" s="37"/>
-      <c r="I175" s="37"/>
-      <c r="J175" s="37"/>
-      <c r="K175" s="37"/>
-      <c r="L175" s="37"/>
-      <c r="M175" s="39"/>
-      <c r="N175" s="37"/>
-      <c r="Q175" s="37"/>
-      <c r="R175" s="37"/>
-      <c r="S175" s="37"/>
-      <c r="T175" s="37"/>
-      <c r="U175" s="37"/>
-      <c r="V175" s="37"/>
-      <c r="W175" s="37"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
+      <c r="C175" s="30"/>
+      <c r="D175" s="29"/>
+      <c r="E175" s="29"/>
+      <c r="F175" s="29"/>
+      <c r="G175" s="29"/>
+      <c r="H175" s="29"/>
+      <c r="I175" s="29"/>
+      <c r="J175" s="29"/>
+      <c r="K175" s="29"/>
+      <c r="L175" s="29"/>
+      <c r="M175" s="29"/>
+      <c r="N175" s="29"/>
+      <c r="Q175" s="29"/>
+      <c r="R175" s="29"/>
+      <c r="S175" s="29"/>
+      <c r="T175" s="29"/>
+      <c r="U175" s="29"/>
+      <c r="V175" s="29"/>
+      <c r="W175" s="29"/>
     </row>
     <row r="176" spans="1:23">
-      <c r="A176" s="37"/>
-      <c r="B176" s="37"/>
-      <c r="C176" s="38"/>
-      <c r="D176" s="37"/>
-      <c r="E176" s="37"/>
-      <c r="F176" s="37"/>
-      <c r="G176" s="39"/>
-      <c r="H176" s="37"/>
-      <c r="I176" s="37"/>
-      <c r="J176" s="37"/>
-      <c r="K176" s="37"/>
-      <c r="L176" s="37"/>
-      <c r="M176" s="39"/>
-      <c r="N176" s="37"/>
-      <c r="Q176" s="37"/>
-      <c r="R176" s="37"/>
-      <c r="S176" s="37"/>
-      <c r="T176" s="37"/>
-      <c r="U176" s="37"/>
-      <c r="V176" s="37"/>
-      <c r="W176" s="37"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
+      <c r="C176" s="30"/>
+      <c r="D176" s="29"/>
+      <c r="E176" s="29"/>
+      <c r="F176" s="29"/>
+      <c r="G176" s="29"/>
+      <c r="H176" s="29"/>
+      <c r="I176" s="29"/>
+      <c r="J176" s="29"/>
+      <c r="K176" s="29"/>
+      <c r="L176" s="29"/>
+      <c r="M176" s="29"/>
+      <c r="N176" s="29"/>
+      <c r="Q176" s="29"/>
+      <c r="R176" s="29"/>
+      <c r="S176" s="29"/>
+      <c r="T176" s="29"/>
+      <c r="U176" s="29"/>
+      <c r="V176" s="29"/>
+      <c r="W176" s="29"/>
     </row>
     <row r="177" spans="1:23">
-      <c r="A177" s="37"/>
-      <c r="B177" s="37"/>
-      <c r="C177" s="38"/>
-      <c r="D177" s="37"/>
-      <c r="E177" s="37"/>
-      <c r="F177" s="37"/>
-      <c r="G177" s="39"/>
-      <c r="H177" s="37"/>
-      <c r="I177" s="37"/>
-      <c r="J177" s="37"/>
-      <c r="K177" s="37"/>
-      <c r="L177" s="37"/>
-      <c r="M177" s="39"/>
-      <c r="N177" s="37"/>
-      <c r="Q177" s="37"/>
-      <c r="R177" s="37"/>
-      <c r="S177" s="37"/>
-      <c r="T177" s="37"/>
-      <c r="U177" s="37"/>
-      <c r="V177" s="37"/>
-      <c r="W177" s="37"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
+      <c r="C177" s="30"/>
+      <c r="D177" s="29"/>
+      <c r="E177" s="29"/>
+      <c r="F177" s="29"/>
+      <c r="G177" s="29"/>
+      <c r="H177" s="29"/>
+      <c r="I177" s="29"/>
+      <c r="J177" s="29"/>
+      <c r="K177" s="29"/>
+      <c r="L177" s="29"/>
+      <c r="M177" s="29"/>
+      <c r="N177" s="29"/>
+      <c r="Q177" s="29"/>
+      <c r="R177" s="29"/>
+      <c r="S177" s="29"/>
+      <c r="T177" s="29"/>
+      <c r="U177" s="29"/>
+      <c r="V177" s="29"/>
+      <c r="W177" s="29"/>
     </row>
     <row r="178" spans="1:23">
-      <c r="A178" s="37"/>
-      <c r="B178" s="37"/>
-      <c r="C178" s="38"/>
-      <c r="D178" s="37"/>
-      <c r="E178" s="37"/>
-      <c r="F178" s="37"/>
-      <c r="G178" s="39"/>
-      <c r="H178" s="37"/>
-      <c r="I178" s="37"/>
-      <c r="J178" s="37"/>
-      <c r="K178" s="37"/>
-      <c r="L178" s="37"/>
-      <c r="M178" s="39"/>
-      <c r="N178" s="37"/>
-      <c r="Q178" s="37"/>
-      <c r="R178" s="37"/>
-      <c r="S178" s="37"/>
-      <c r="T178" s="37"/>
-      <c r="U178" s="37"/>
-      <c r="V178" s="37"/>
-      <c r="W178" s="37"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="30"/>
+      <c r="D178" s="29"/>
+      <c r="E178" s="29"/>
+      <c r="F178" s="29"/>
+      <c r="G178" s="29"/>
+      <c r="H178" s="29"/>
+      <c r="I178" s="29"/>
+      <c r="J178" s="29"/>
+      <c r="K178" s="29"/>
+      <c r="L178" s="29"/>
+      <c r="M178" s="29"/>
+      <c r="N178" s="29"/>
+      <c r="Q178" s="29"/>
+      <c r="R178" s="29"/>
+      <c r="S178" s="29"/>
+      <c r="T178" s="29"/>
+      <c r="U178" s="29"/>
+      <c r="V178" s="29"/>
+      <c r="W178" s="29"/>
     </row>
     <row r="179" spans="1:23">
-      <c r="A179" s="37"/>
-      <c r="B179" s="37"/>
-      <c r="C179" s="38"/>
-      <c r="D179" s="37"/>
-      <c r="E179" s="37"/>
-      <c r="F179" s="37"/>
-      <c r="G179" s="39"/>
-      <c r="H179" s="37"/>
-      <c r="I179" s="37"/>
-      <c r="J179" s="37"/>
-      <c r="K179" s="37"/>
-      <c r="L179" s="37"/>
-      <c r="M179" s="39"/>
-      <c r="N179" s="37"/>
-      <c r="Q179" s="37"/>
-      <c r="R179" s="37"/>
-      <c r="S179" s="37"/>
-      <c r="T179" s="37"/>
-      <c r="U179" s="37"/>
-      <c r="V179" s="37"/>
-      <c r="W179" s="37"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
+      <c r="C179" s="30"/>
+      <c r="D179" s="29"/>
+      <c r="E179" s="29"/>
+      <c r="F179" s="29"/>
+      <c r="G179" s="29"/>
+      <c r="H179" s="29"/>
+      <c r="I179" s="29"/>
+      <c r="J179" s="29"/>
+      <c r="K179" s="29"/>
+      <c r="L179" s="29"/>
+      <c r="M179" s="29"/>
+      <c r="N179" s="29"/>
+      <c r="Q179" s="29"/>
+      <c r="R179" s="29"/>
+      <c r="S179" s="29"/>
+      <c r="T179" s="29"/>
+      <c r="U179" s="29"/>
+      <c r="V179" s="29"/>
+      <c r="W179" s="29"/>
     </row>
     <row r="180" spans="1:23">
-      <c r="A180" s="37"/>
-      <c r="B180" s="37"/>
-      <c r="C180" s="38"/>
-      <c r="D180" s="37"/>
-      <c r="E180" s="37"/>
-      <c r="F180" s="37"/>
-      <c r="G180" s="39"/>
-      <c r="H180" s="37"/>
-      <c r="I180" s="37"/>
-      <c r="J180" s="37"/>
-      <c r="K180" s="37"/>
-      <c r="L180" s="37"/>
-      <c r="M180" s="39"/>
-      <c r="N180" s="37"/>
-      <c r="Q180" s="37"/>
-      <c r="R180" s="37"/>
-      <c r="S180" s="37"/>
-      <c r="T180" s="37"/>
-      <c r="U180" s="37"/>
-      <c r="V180" s="37"/>
-      <c r="W180" s="37"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
+      <c r="C180" s="30"/>
+      <c r="D180" s="29"/>
+      <c r="E180" s="29"/>
+      <c r="F180" s="29"/>
+      <c r="G180" s="29"/>
+      <c r="H180" s="29"/>
+      <c r="I180" s="29"/>
+      <c r="J180" s="29"/>
+      <c r="K180" s="29"/>
+      <c r="L180" s="29"/>
+      <c r="M180" s="29"/>
+      <c r="N180" s="29"/>
+      <c r="Q180" s="29"/>
+      <c r="R180" s="29"/>
+      <c r="S180" s="29"/>
+      <c r="T180" s="29"/>
+      <c r="U180" s="29"/>
+      <c r="V180" s="29"/>
+      <c r="W180" s="29"/>
     </row>
     <row r="181" spans="1:23">
-      <c r="A181" s="37"/>
-      <c r="B181" s="37"/>
-      <c r="C181" s="38"/>
-      <c r="D181" s="37"/>
-      <c r="E181" s="37"/>
-      <c r="F181" s="37"/>
-      <c r="G181" s="39"/>
-      <c r="H181" s="37"/>
-      <c r="I181" s="37"/>
-      <c r="J181" s="37"/>
-      <c r="K181" s="37"/>
-      <c r="L181" s="37"/>
-      <c r="M181" s="39"/>
-      <c r="N181" s="37"/>
-      <c r="Q181" s="37"/>
-      <c r="R181" s="37"/>
-      <c r="S181" s="37"/>
-      <c r="T181" s="37"/>
-      <c r="U181" s="37"/>
-      <c r="V181" s="37"/>
-      <c r="W181" s="37"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
+      <c r="C181" s="30"/>
+      <c r="D181" s="29"/>
+      <c r="E181" s="29"/>
+      <c r="F181" s="29"/>
+      <c r="G181" s="29"/>
+      <c r="H181" s="29"/>
+      <c r="I181" s="29"/>
+      <c r="J181" s="29"/>
+      <c r="K181" s="29"/>
+      <c r="L181" s="29"/>
+      <c r="M181" s="29"/>
+      <c r="N181" s="29"/>
+      <c r="Q181" s="29"/>
+      <c r="R181" s="29"/>
+      <c r="S181" s="29"/>
+      <c r="T181" s="29"/>
+      <c r="U181" s="29"/>
+      <c r="V181" s="29"/>
+      <c r="W181" s="29"/>
     </row>
     <row r="182" spans="1:23">
-      <c r="A182" s="37"/>
-      <c r="B182" s="37"/>
-      <c r="C182" s="38"/>
-      <c r="D182" s="37"/>
-      <c r="E182" s="37"/>
-      <c r="F182" s="37"/>
-      <c r="G182" s="39"/>
-      <c r="H182" s="37"/>
-      <c r="I182" s="37"/>
-      <c r="J182" s="37"/>
-      <c r="K182" s="37"/>
-      <c r="L182" s="37"/>
-      <c r="M182" s="39"/>
-      <c r="N182" s="37"/>
-      <c r="Q182" s="37"/>
-      <c r="R182" s="37"/>
-      <c r="S182" s="37"/>
-      <c r="T182" s="37"/>
-      <c r="U182" s="37"/>
-      <c r="V182" s="37"/>
-      <c r="W182" s="37"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
+      <c r="C182" s="30"/>
+      <c r="D182" s="29"/>
+      <c r="E182" s="29"/>
+      <c r="F182" s="29"/>
+      <c r="G182" s="29"/>
+      <c r="H182" s="29"/>
+      <c r="I182" s="29"/>
+      <c r="J182" s="29"/>
+      <c r="K182" s="29"/>
+      <c r="L182" s="29"/>
+      <c r="M182" s="29"/>
+      <c r="N182" s="29"/>
+      <c r="Q182" s="29"/>
+      <c r="R182" s="29"/>
+      <c r="S182" s="29"/>
+      <c r="T182" s="29"/>
+      <c r="U182" s="29"/>
+      <c r="V182" s="29"/>
+      <c r="W182" s="29"/>
     </row>
     <row r="183" spans="1:23">
-      <c r="A183" s="37"/>
-      <c r="B183" s="37"/>
-      <c r="C183" s="38"/>
-      <c r="D183" s="37"/>
-      <c r="E183" s="37"/>
-      <c r="F183" s="37"/>
-      <c r="G183" s="39"/>
-      <c r="H183" s="37"/>
-      <c r="I183" s="37"/>
-      <c r="J183" s="37"/>
-      <c r="K183" s="37"/>
-      <c r="L183" s="37"/>
-      <c r="M183" s="39"/>
-      <c r="N183" s="37"/>
-      <c r="Q183" s="37"/>
-      <c r="R183" s="37"/>
-      <c r="S183" s="37"/>
-      <c r="T183" s="37"/>
-      <c r="U183" s="37"/>
-      <c r="V183" s="37"/>
-      <c r="W183" s="37"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
+      <c r="C183" s="30"/>
+      <c r="D183" s="29"/>
+      <c r="E183" s="29"/>
+      <c r="F183" s="29"/>
+      <c r="G183" s="29"/>
+      <c r="H183" s="29"/>
+      <c r="I183" s="29"/>
+      <c r="J183" s="29"/>
+      <c r="K183" s="29"/>
+      <c r="L183" s="29"/>
+      <c r="M183" s="29"/>
+      <c r="N183" s="29"/>
+      <c r="Q183" s="29"/>
+      <c r="R183" s="29"/>
+      <c r="S183" s="29"/>
+      <c r="T183" s="29"/>
+      <c r="U183" s="29"/>
+      <c r="V183" s="29"/>
+      <c r="W183" s="29"/>
     </row>
     <row r="184" spans="1:23">
-      <c r="A184" s="37"/>
-      <c r="B184" s="37"/>
-      <c r="C184" s="38"/>
-      <c r="D184" s="37"/>
-      <c r="E184" s="37"/>
-      <c r="F184" s="37"/>
-      <c r="G184" s="39"/>
-      <c r="H184" s="37"/>
-      <c r="I184" s="37"/>
-      <c r="J184" s="37"/>
-      <c r="K184" s="37"/>
-      <c r="L184" s="37"/>
-      <c r="M184" s="39"/>
-      <c r="N184" s="37"/>
-      <c r="Q184" s="37"/>
-      <c r="R184" s="37"/>
-      <c r="S184" s="37"/>
-      <c r="T184" s="37"/>
-      <c r="U184" s="37"/>
-      <c r="V184" s="37"/>
-      <c r="W184" s="37"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="30"/>
+      <c r="D184" s="29"/>
+      <c r="E184" s="29"/>
+      <c r="F184" s="29"/>
+      <c r="G184" s="29"/>
+      <c r="H184" s="29"/>
+      <c r="I184" s="29"/>
+      <c r="J184" s="29"/>
+      <c r="K184" s="29"/>
+      <c r="L184" s="29"/>
+      <c r="M184" s="29"/>
+      <c r="N184" s="29"/>
+      <c r="Q184" s="29"/>
+      <c r="R184" s="29"/>
+      <c r="S184" s="29"/>
+      <c r="T184" s="29"/>
+      <c r="U184" s="29"/>
+      <c r="V184" s="29"/>
+      <c r="W184" s="29"/>
     </row>
     <row r="185" spans="1:23">
-      <c r="A185" s="37"/>
-      <c r="B185" s="37"/>
-      <c r="C185" s="38"/>
-      <c r="D185" s="37"/>
-      <c r="E185" s="37"/>
-      <c r="F185" s="37"/>
-      <c r="G185" s="39"/>
-      <c r="H185" s="37"/>
-      <c r="I185" s="37"/>
-      <c r="J185" s="37"/>
-      <c r="K185" s="37"/>
-      <c r="L185" s="37"/>
-      <c r="M185" s="39"/>
-      <c r="N185" s="37"/>
-      <c r="Q185" s="37"/>
-      <c r="R185" s="37"/>
-      <c r="S185" s="37"/>
-      <c r="T185" s="37"/>
-      <c r="U185" s="37"/>
-      <c r="V185" s="37"/>
-      <c r="W185" s="37"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
+      <c r="C185" s="30"/>
+      <c r="D185" s="29"/>
+      <c r="E185" s="29"/>
+      <c r="F185" s="29"/>
+      <c r="G185" s="29"/>
+      <c r="H185" s="29"/>
+      <c r="I185" s="29"/>
+      <c r="J185" s="29"/>
+      <c r="K185" s="29"/>
+      <c r="L185" s="29"/>
+      <c r="M185" s="29"/>
+      <c r="N185" s="29"/>
+      <c r="Q185" s="29"/>
+      <c r="R185" s="29"/>
+      <c r="S185" s="29"/>
+      <c r="T185" s="29"/>
+      <c r="U185" s="29"/>
+      <c r="V185" s="29"/>
+      <c r="W185" s="29"/>
     </row>
     <row r="186" spans="1:23">
-      <c r="A186" s="37"/>
-      <c r="B186" s="37"/>
-      <c r="C186" s="38"/>
-      <c r="D186" s="37"/>
-      <c r="E186" s="37"/>
-      <c r="F186" s="37"/>
-      <c r="G186" s="39"/>
-      <c r="H186" s="37"/>
-      <c r="I186" s="37"/>
-      <c r="J186" s="37"/>
-      <c r="K186" s="37"/>
-      <c r="L186" s="37"/>
-      <c r="M186" s="39"/>
-      <c r="N186" s="37"/>
-      <c r="Q186" s="37"/>
-      <c r="R186" s="37"/>
-      <c r="S186" s="37"/>
-      <c r="T186" s="37"/>
-      <c r="U186" s="37"/>
-      <c r="V186" s="37"/>
-      <c r="W186" s="37"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
+      <c r="C186" s="30"/>
+      <c r="D186" s="29"/>
+      <c r="E186" s="29"/>
+      <c r="F186" s="29"/>
+      <c r="G186" s="29"/>
+      <c r="H186" s="29"/>
+      <c r="I186" s="29"/>
+      <c r="J186" s="29"/>
+      <c r="K186" s="29"/>
+      <c r="L186" s="29"/>
+      <c r="M186" s="29"/>
+      <c r="N186" s="29"/>
+      <c r="Q186" s="29"/>
+      <c r="R186" s="29"/>
+      <c r="S186" s="29"/>
+      <c r="T186" s="29"/>
+      <c r="U186" s="29"/>
+      <c r="V186" s="29"/>
+      <c r="W186" s="29"/>
     </row>
     <row r="187" spans="1:23">
-      <c r="A187" s="37"/>
-      <c r="B187" s="37"/>
-      <c r="C187" s="38"/>
-      <c r="D187" s="37"/>
-      <c r="E187" s="37"/>
-      <c r="F187" s="37"/>
-      <c r="G187" s="39"/>
-      <c r="H187" s="37"/>
-      <c r="I187" s="37"/>
-      <c r="J187" s="37"/>
-      <c r="K187" s="37"/>
-      <c r="L187" s="37"/>
-      <c r="M187" s="39"/>
-      <c r="N187" s="37"/>
-      <c r="Q187" s="37"/>
-      <c r="R187" s="37"/>
-      <c r="S187" s="37"/>
-      <c r="T187" s="37"/>
-      <c r="U187" s="37"/>
-      <c r="V187" s="37"/>
-      <c r="W187" s="37"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
+      <c r="C187" s="30"/>
+      <c r="D187" s="29"/>
+      <c r="E187" s="29"/>
+      <c r="F187" s="29"/>
+      <c r="G187" s="29"/>
+      <c r="H187" s="29"/>
+      <c r="I187" s="29"/>
+      <c r="J187" s="29"/>
+      <c r="K187" s="29"/>
+      <c r="L187" s="29"/>
+      <c r="M187" s="29"/>
+      <c r="N187" s="29"/>
+      <c r="Q187" s="29"/>
+      <c r="R187" s="29"/>
+      <c r="S187" s="29"/>
+      <c r="T187" s="29"/>
+      <c r="U187" s="29"/>
+      <c r="V187" s="29"/>
+      <c r="W187" s="29"/>
     </row>
     <row r="188" spans="1:23">
-      <c r="A188" s="37"/>
-      <c r="B188" s="37"/>
-      <c r="C188" s="38"/>
-      <c r="D188" s="37"/>
-      <c r="E188" s="37"/>
-      <c r="F188" s="37"/>
-      <c r="G188" s="39"/>
-      <c r="H188" s="37"/>
-      <c r="I188" s="37"/>
-      <c r="J188" s="37"/>
-      <c r="K188" s="37"/>
-      <c r="L188" s="37"/>
-      <c r="M188" s="39"/>
-      <c r="N188" s="37"/>
-      <c r="Q188" s="37"/>
-      <c r="R188" s="37"/>
-      <c r="S188" s="37"/>
-      <c r="T188" s="37"/>
-      <c r="U188" s="37"/>
-      <c r="V188" s="37"/>
-      <c r="W188" s="37"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
+      <c r="C188" s="30"/>
+      <c r="D188" s="29"/>
+      <c r="E188" s="29"/>
+      <c r="F188" s="29"/>
+      <c r="G188" s="29"/>
+      <c r="H188" s="29"/>
+      <c r="I188" s="29"/>
+      <c r="J188" s="29"/>
+      <c r="K188" s="29"/>
+      <c r="L188" s="29"/>
+      <c r="M188" s="29"/>
+      <c r="N188" s="29"/>
+      <c r="Q188" s="29"/>
+      <c r="R188" s="29"/>
+      <c r="S188" s="29"/>
+      <c r="T188" s="29"/>
+      <c r="U188" s="29"/>
+      <c r="V188" s="29"/>
+      <c r="W188" s="29"/>
     </row>
     <row r="189" spans="1:23">
-      <c r="A189" s="37"/>
-      <c r="B189" s="37"/>
-      <c r="C189" s="38"/>
-      <c r="D189" s="37"/>
-      <c r="E189" s="37"/>
-      <c r="F189" s="37"/>
-      <c r="G189" s="39"/>
-      <c r="H189" s="37"/>
-      <c r="I189" s="37"/>
-      <c r="J189" s="37"/>
-      <c r="K189" s="37"/>
-      <c r="L189" s="37"/>
-      <c r="M189" s="39"/>
-      <c r="N189" s="37"/>
-      <c r="Q189" s="37"/>
-      <c r="R189" s="37"/>
-      <c r="S189" s="37"/>
-      <c r="T189" s="37"/>
-      <c r="U189" s="37"/>
-      <c r="V189" s="37"/>
-      <c r="W189" s="37"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
+      <c r="C189" s="30"/>
+      <c r="D189" s="29"/>
+      <c r="E189" s="29"/>
+      <c r="F189" s="29"/>
+      <c r="G189" s="29"/>
+      <c r="H189" s="29"/>
+      <c r="I189" s="29"/>
+      <c r="J189" s="29"/>
+      <c r="K189" s="29"/>
+      <c r="L189" s="29"/>
+      <c r="M189" s="29"/>
+      <c r="N189" s="29"/>
+      <c r="Q189" s="29"/>
+      <c r="R189" s="29"/>
+      <c r="S189" s="29"/>
+      <c r="T189" s="29"/>
+      <c r="U189" s="29"/>
+      <c r="V189" s="29"/>
+      <c r="W189" s="29"/>
     </row>
     <row r="190" spans="1:23">
-      <c r="A190" s="37"/>
-      <c r="B190" s="37"/>
-      <c r="C190" s="38"/>
-      <c r="D190" s="37"/>
-      <c r="E190" s="37"/>
-      <c r="F190" s="37"/>
-      <c r="G190" s="39"/>
-      <c r="H190" s="37"/>
-      <c r="I190" s="37"/>
-      <c r="J190" s="37"/>
-      <c r="K190" s="37"/>
-      <c r="L190" s="37"/>
-      <c r="M190" s="39"/>
-      <c r="N190" s="37"/>
-      <c r="Q190" s="37"/>
-      <c r="R190" s="37"/>
-      <c r="S190" s="37"/>
-      <c r="T190" s="37"/>
-      <c r="U190" s="37"/>
-      <c r="V190" s="37"/>
-      <c r="W190" s="37"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="30"/>
+      <c r="D190" s="29"/>
+      <c r="E190" s="29"/>
+      <c r="F190" s="29"/>
+      <c r="G190" s="29"/>
+      <c r="H190" s="29"/>
+      <c r="I190" s="29"/>
+      <c r="J190" s="29"/>
+      <c r="K190" s="29"/>
+      <c r="L190" s="29"/>
+      <c r="M190" s="29"/>
+      <c r="N190" s="29"/>
+      <c r="Q190" s="29"/>
+      <c r="R190" s="29"/>
+      <c r="S190" s="29"/>
+      <c r="T190" s="29"/>
+      <c r="U190" s="29"/>
+      <c r="V190" s="29"/>
+      <c r="W190" s="29"/>
     </row>
     <row r="191" spans="1:23">
-      <c r="A191" s="37"/>
-      <c r="B191" s="37"/>
-      <c r="C191" s="38"/>
-      <c r="D191" s="37"/>
-      <c r="E191" s="37"/>
-      <c r="F191" s="37"/>
-      <c r="G191" s="39"/>
-      <c r="H191" s="37"/>
-      <c r="I191" s="37"/>
-      <c r="J191" s="37"/>
-      <c r="K191" s="37"/>
-      <c r="L191" s="37"/>
-      <c r="M191" s="39"/>
-      <c r="N191" s="37"/>
-      <c r="Q191" s="37"/>
-      <c r="R191" s="37"/>
-      <c r="S191" s="37"/>
-      <c r="T191" s="37"/>
-      <c r="U191" s="37"/>
-      <c r="V191" s="37"/>
-      <c r="W191" s="37"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
+      <c r="C191" s="30"/>
+      <c r="D191" s="29"/>
+      <c r="E191" s="29"/>
+      <c r="F191" s="29"/>
+      <c r="G191" s="29"/>
+      <c r="H191" s="29"/>
+      <c r="I191" s="29"/>
+      <c r="J191" s="29"/>
+      <c r="K191" s="29"/>
+      <c r="L191" s="29"/>
+      <c r="M191" s="29"/>
+      <c r="N191" s="29"/>
+      <c r="Q191" s="29"/>
+      <c r="R191" s="29"/>
+      <c r="S191" s="29"/>
+      <c r="T191" s="29"/>
+      <c r="U191" s="29"/>
+      <c r="V191" s="29"/>
+      <c r="W191" s="29"/>
     </row>
     <row r="192" spans="1:23">
-      <c r="A192" s="37"/>
-      <c r="B192" s="37"/>
-      <c r="C192" s="38"/>
-      <c r="D192" s="37"/>
-      <c r="E192" s="37"/>
-      <c r="F192" s="37"/>
-      <c r="G192" s="39"/>
-      <c r="H192" s="37"/>
-      <c r="I192" s="37"/>
-      <c r="J192" s="37"/>
-      <c r="K192" s="37"/>
-      <c r="L192" s="37"/>
-      <c r="M192" s="39"/>
-      <c r="N192" s="37"/>
-      <c r="Q192" s="37"/>
-      <c r="R192" s="37"/>
-      <c r="S192" s="37"/>
-      <c r="T192" s="37"/>
-      <c r="U192" s="37"/>
-      <c r="V192" s="37"/>
-      <c r="W192" s="37"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
+      <c r="C192" s="30"/>
+      <c r="D192" s="29"/>
+      <c r="E192" s="29"/>
+      <c r="F192" s="29"/>
+      <c r="G192" s="29"/>
+      <c r="H192" s="29"/>
+      <c r="I192" s="29"/>
+      <c r="J192" s="29"/>
+      <c r="K192" s="29"/>
+      <c r="L192" s="29"/>
+      <c r="M192" s="29"/>
+      <c r="N192" s="29"/>
+      <c r="Q192" s="29"/>
+      <c r="R192" s="29"/>
+      <c r="S192" s="29"/>
+      <c r="T192" s="29"/>
+      <c r="U192" s="29"/>
+      <c r="V192" s="29"/>
+      <c r="W192" s="29"/>
     </row>
     <row r="193" spans="1:23">
-      <c r="A193" s="37"/>
-      <c r="B193" s="37"/>
-      <c r="C193" s="38"/>
-      <c r="D193" s="37"/>
-      <c r="E193" s="37"/>
-      <c r="F193" s="37"/>
-      <c r="G193" s="39"/>
-      <c r="H193" s="37"/>
-      <c r="I193" s="37"/>
-      <c r="J193" s="37"/>
-      <c r="K193" s="37"/>
-      <c r="L193" s="37"/>
-      <c r="M193" s="39"/>
-      <c r="N193" s="37"/>
-      <c r="Q193" s="37"/>
-      <c r="R193" s="37"/>
-      <c r="S193" s="37"/>
-      <c r="T193" s="37"/>
-      <c r="U193" s="37"/>
-      <c r="V193" s="37"/>
-      <c r="W193" s="37"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
+      <c r="C193" s="30"/>
+      <c r="D193" s="29"/>
+      <c r="E193" s="29"/>
+      <c r="F193" s="29"/>
+      <c r="G193" s="29"/>
+      <c r="H193" s="29"/>
+      <c r="I193" s="29"/>
+      <c r="J193" s="29"/>
+      <c r="K193" s="29"/>
+      <c r="L193" s="29"/>
+      <c r="M193" s="29"/>
+      <c r="N193" s="29"/>
+      <c r="Q193" s="29"/>
+      <c r="R193" s="29"/>
+      <c r="S193" s="29"/>
+      <c r="T193" s="29"/>
+      <c r="U193" s="29"/>
+      <c r="V193" s="29"/>
+      <c r="W193" s="29"/>
     </row>
     <row r="194" spans="1:23">
-      <c r="A194" s="37"/>
-      <c r="B194" s="37"/>
-      <c r="C194" s="38"/>
-      <c r="D194" s="37"/>
-      <c r="E194" s="37"/>
-      <c r="F194" s="37"/>
-      <c r="G194" s="39"/>
-      <c r="H194" s="37"/>
-      <c r="I194" s="37"/>
-      <c r="J194" s="37"/>
-      <c r="K194" s="37"/>
-      <c r="L194" s="37"/>
-      <c r="M194" s="39"/>
-      <c r="N194" s="37"/>
-      <c r="Q194" s="37"/>
-      <c r="R194" s="37"/>
-      <c r="S194" s="37"/>
-      <c r="T194" s="37"/>
-      <c r="U194" s="37"/>
-      <c r="V194" s="37"/>
-      <c r="W194" s="37"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
+      <c r="C194" s="30"/>
+      <c r="D194" s="29"/>
+      <c r="E194" s="29"/>
+      <c r="F194" s="29"/>
+      <c r="G194" s="29"/>
+      <c r="H194" s="29"/>
+      <c r="I194" s="29"/>
+      <c r="J194" s="29"/>
+      <c r="K194" s="29"/>
+      <c r="L194" s="29"/>
+      <c r="M194" s="29"/>
+      <c r="N194" s="29"/>
+      <c r="Q194" s="29"/>
+      <c r="R194" s="29"/>
+      <c r="S194" s="29"/>
+      <c r="T194" s="29"/>
+      <c r="U194" s="29"/>
+      <c r="V194" s="29"/>
+      <c r="W194" s="29"/>
     </row>
     <row r="195" spans="1:23">
-      <c r="A195" s="37"/>
-      <c r="B195" s="37"/>
-      <c r="C195" s="38"/>
-      <c r="D195" s="37"/>
-      <c r="E195" s="37"/>
-      <c r="F195" s="37"/>
-      <c r="G195" s="39"/>
-      <c r="H195" s="37"/>
-      <c r="I195" s="37"/>
-      <c r="J195" s="37"/>
-      <c r="K195" s="37"/>
-      <c r="L195" s="37"/>
-      <c r="M195" s="39"/>
-      <c r="N195" s="37"/>
-      <c r="Q195" s="37"/>
-      <c r="R195" s="37"/>
-      <c r="S195" s="37"/>
-      <c r="T195" s="37"/>
-      <c r="U195" s="37"/>
-      <c r="V195" s="37"/>
-      <c r="W195" s="37"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
+      <c r="C195" s="30"/>
+      <c r="D195" s="29"/>
+      <c r="E195" s="29"/>
+      <c r="F195" s="29"/>
+      <c r="G195" s="29"/>
+      <c r="H195" s="29"/>
+      <c r="I195" s="29"/>
+      <c r="J195" s="29"/>
+      <c r="K195" s="29"/>
+      <c r="L195" s="29"/>
+      <c r="M195" s="29"/>
+      <c r="N195" s="29"/>
+      <c r="Q195" s="29"/>
+      <c r="R195" s="29"/>
+      <c r="S195" s="29"/>
+      <c r="T195" s="29"/>
+      <c r="U195" s="29"/>
+      <c r="V195" s="29"/>
+      <c r="W195" s="29"/>
     </row>
     <row r="196" spans="1:23">
-      <c r="A196" s="37"/>
-      <c r="B196" s="37"/>
-      <c r="C196" s="38"/>
-      <c r="D196" s="37"/>
-      <c r="E196" s="37"/>
-      <c r="F196" s="37"/>
-      <c r="G196" s="39"/>
-      <c r="H196" s="37"/>
-      <c r="I196" s="37"/>
-      <c r="J196" s="37"/>
-      <c r="K196" s="37"/>
-      <c r="L196" s="37"/>
-      <c r="M196" s="39"/>
-      <c r="N196" s="37"/>
-      <c r="Q196" s="37"/>
-      <c r="R196" s="37"/>
-      <c r="S196" s="37"/>
-      <c r="T196" s="37"/>
-      <c r="U196" s="37"/>
-      <c r="V196" s="37"/>
-      <c r="W196" s="37"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="30"/>
+      <c r="D196" s="29"/>
+      <c r="E196" s="29"/>
+      <c r="F196" s="29"/>
+      <c r="G196" s="29"/>
+      <c r="H196" s="29"/>
+      <c r="I196" s="29"/>
+      <c r="J196" s="29"/>
+      <c r="K196" s="29"/>
+      <c r="L196" s="29"/>
+      <c r="M196" s="29"/>
+      <c r="N196" s="29"/>
+      <c r="Q196" s="29"/>
+      <c r="R196" s="29"/>
+      <c r="S196" s="29"/>
+      <c r="T196" s="29"/>
+      <c r="U196" s="29"/>
+      <c r="V196" s="29"/>
+      <c r="W196" s="29"/>
     </row>
     <row r="197" spans="1:23">
-      <c r="A197" s="37"/>
-      <c r="B197" s="37"/>
-      <c r="C197" s="38"/>
-      <c r="D197" s="37"/>
-      <c r="E197" s="37"/>
-      <c r="F197" s="37"/>
-      <c r="G197" s="39"/>
-      <c r="H197" s="37"/>
-      <c r="I197" s="37"/>
-      <c r="J197" s="37"/>
-      <c r="K197" s="37"/>
-      <c r="L197" s="37"/>
-      <c r="M197" s="39"/>
-      <c r="N197" s="37"/>
-      <c r="Q197" s="37"/>
-      <c r="R197" s="37"/>
-      <c r="S197" s="37"/>
-      <c r="T197" s="37"/>
-      <c r="U197" s="37"/>
-      <c r="V197" s="37"/>
-      <c r="W197" s="37"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
+      <c r="C197" s="30"/>
+      <c r="D197" s="29"/>
+      <c r="E197" s="29"/>
+      <c r="F197" s="29"/>
+      <c r="G197" s="29"/>
+      <c r="H197" s="29"/>
+      <c r="I197" s="29"/>
+      <c r="J197" s="29"/>
+      <c r="K197" s="29"/>
+      <c r="L197" s="29"/>
+      <c r="M197" s="29"/>
+      <c r="N197" s="29"/>
+      <c r="Q197" s="29"/>
+      <c r="R197" s="29"/>
+      <c r="S197" s="29"/>
+      <c r="T197" s="29"/>
+      <c r="U197" s="29"/>
+      <c r="V197" s="29"/>
+      <c r="W197" s="29"/>
     </row>
     <row r="198" spans="1:23">
-      <c r="A198" s="37"/>
-      <c r="B198" s="37"/>
-      <c r="C198" s="38"/>
-      <c r="D198" s="37"/>
-      <c r="E198" s="37"/>
-      <c r="F198" s="37"/>
-      <c r="G198" s="39"/>
-      <c r="H198" s="37"/>
-      <c r="I198" s="37"/>
-      <c r="J198" s="37"/>
-      <c r="K198" s="37"/>
-      <c r="L198" s="37"/>
-      <c r="M198" s="39"/>
-      <c r="N198" s="37"/>
-      <c r="Q198" s="37"/>
-      <c r="R198" s="37"/>
-      <c r="S198" s="37"/>
-      <c r="T198" s="37"/>
-      <c r="U198" s="37"/>
-      <c r="V198" s="37"/>
-      <c r="W198" s="37"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
+      <c r="C198" s="30"/>
+      <c r="D198" s="29"/>
+      <c r="E198" s="29"/>
+      <c r="F198" s="29"/>
+      <c r="G198" s="29"/>
+      <c r="H198" s="29"/>
+      <c r="I198" s="29"/>
+      <c r="J198" s="29"/>
+      <c r="K198" s="29"/>
+      <c r="L198" s="29"/>
+      <c r="M198" s="29"/>
+      <c r="N198" s="29"/>
+      <c r="Q198" s="29"/>
+      <c r="R198" s="29"/>
+      <c r="S198" s="29"/>
+      <c r="T198" s="29"/>
+      <c r="U198" s="29"/>
+      <c r="V198" s="29"/>
+      <c r="W198" s="29"/>
     </row>
     <row r="199" spans="1:23">
-      <c r="A199" s="37"/>
-      <c r="B199" s="37"/>
-      <c r="C199" s="38"/>
-      <c r="D199" s="37"/>
-      <c r="E199" s="37"/>
-      <c r="F199" s="37"/>
-      <c r="G199" s="39"/>
-      <c r="H199" s="37"/>
-      <c r="I199" s="37"/>
-      <c r="J199" s="37"/>
-      <c r="K199" s="37"/>
-      <c r="L199" s="37"/>
-      <c r="M199" s="39"/>
-      <c r="N199" s="37"/>
-      <c r="Q199" s="37"/>
-      <c r="R199" s="37"/>
-      <c r="S199" s="37"/>
-      <c r="T199" s="37"/>
-      <c r="U199" s="37"/>
-      <c r="V199" s="37"/>
-      <c r="W199" s="37"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
+      <c r="C199" s="30"/>
+      <c r="D199" s="29"/>
+      <c r="E199" s="29"/>
+      <c r="F199" s="29"/>
+      <c r="G199" s="29"/>
+      <c r="H199" s="29"/>
+      <c r="I199" s="29"/>
+      <c r="J199" s="29"/>
+      <c r="K199" s="29"/>
+      <c r="L199" s="29"/>
+      <c r="M199" s="29"/>
+      <c r="N199" s="29"/>
+      <c r="Q199" s="29"/>
+      <c r="R199" s="29"/>
+      <c r="S199" s="29"/>
+      <c r="T199" s="29"/>
+      <c r="U199" s="29"/>
+      <c r="V199" s="29"/>
+      <c r="W199" s="29"/>
     </row>
     <row r="200" spans="1:23">
-      <c r="A200" s="37"/>
-      <c r="B200" s="37"/>
-      <c r="C200" s="38"/>
-      <c r="D200" s="37"/>
-      <c r="E200" s="37"/>
-      <c r="F200" s="37"/>
-      <c r="G200" s="39"/>
-      <c r="H200" s="37"/>
-      <c r="I200" s="37"/>
-      <c r="J200" s="37"/>
-      <c r="K200" s="37"/>
-      <c r="L200" s="37"/>
-      <c r="M200" s="39"/>
-      <c r="N200" s="37"/>
-      <c r="Q200" s="37"/>
-      <c r="R200" s="37"/>
-      <c r="S200" s="37"/>
-      <c r="T200" s="37"/>
-      <c r="U200" s="37"/>
-      <c r="V200" s="37"/>
-      <c r="W200" s="37"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
+      <c r="C200" s="30"/>
+      <c r="D200" s="29"/>
+      <c r="E200" s="29"/>
+      <c r="F200" s="29"/>
+      <c r="G200" s="29"/>
+      <c r="H200" s="29"/>
+      <c r="I200" s="29"/>
+      <c r="J200" s="29"/>
+      <c r="K200" s="29"/>
+      <c r="L200" s="29"/>
+      <c r="M200" s="29"/>
+      <c r="N200" s="29"/>
+      <c r="Q200" s="29"/>
+      <c r="R200" s="29"/>
+      <c r="S200" s="29"/>
+      <c r="T200" s="29"/>
+      <c r="U200" s="29"/>
+      <c r="V200" s="29"/>
+      <c r="W200" s="29"/>
     </row>
     <row r="201" spans="1:23">
-      <c r="A201" s="37"/>
-      <c r="B201" s="37"/>
-      <c r="C201" s="38"/>
-      <c r="D201" s="37"/>
-      <c r="E201" s="37"/>
-      <c r="F201" s="37"/>
-      <c r="G201" s="39"/>
-      <c r="H201" s="37"/>
-      <c r="I201" s="37"/>
-      <c r="J201" s="37"/>
-      <c r="K201" s="37"/>
-      <c r="L201" s="37"/>
-      <c r="M201" s="39"/>
-      <c r="N201" s="37"/>
-      <c r="Q201" s="37"/>
-      <c r="R201" s="37"/>
-      <c r="S201" s="37"/>
-      <c r="T201" s="37"/>
-      <c r="U201" s="37"/>
-      <c r="V201" s="37"/>
-      <c r="W201" s="37"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
+      <c r="C201" s="30"/>
+      <c r="D201" s="29"/>
+      <c r="E201" s="29"/>
+      <c r="F201" s="29"/>
+      <c r="G201" s="29"/>
+      <c r="H201" s="29"/>
+      <c r="I201" s="29"/>
+      <c r="J201" s="29"/>
+      <c r="K201" s="29"/>
+      <c r="L201" s="29"/>
+      <c r="M201" s="29"/>
+      <c r="N201" s="29"/>
+      <c r="Q201" s="29"/>
+      <c r="R201" s="29"/>
+      <c r="S201" s="29"/>
+      <c r="T201" s="29"/>
+      <c r="U201" s="29"/>
+      <c r="V201" s="29"/>
+      <c r="W201" s="29"/>
     </row>
     <row r="202" spans="1:23">
-      <c r="A202" s="37"/>
-      <c r="B202" s="37"/>
-      <c r="C202" s="38"/>
-      <c r="D202" s="37"/>
-      <c r="E202" s="37"/>
-      <c r="F202" s="37"/>
-      <c r="G202" s="39"/>
-      <c r="H202" s="37"/>
-      <c r="I202" s="37"/>
-      <c r="J202" s="37"/>
-      <c r="K202" s="37"/>
-      <c r="L202" s="37"/>
-      <c r="M202" s="39"/>
-      <c r="N202" s="37"/>
-      <c r="Q202" s="37"/>
-      <c r="R202" s="37"/>
-      <c r="S202" s="37"/>
-      <c r="T202" s="37"/>
-      <c r="U202" s="37"/>
-      <c r="V202" s="37"/>
-      <c r="W202" s="37"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="30"/>
+      <c r="D202" s="29"/>
+      <c r="E202" s="29"/>
+      <c r="F202" s="29"/>
+      <c r="G202" s="29"/>
+      <c r="H202" s="29"/>
+      <c r="I202" s="29"/>
+      <c r="J202" s="29"/>
+      <c r="K202" s="29"/>
+      <c r="L202" s="29"/>
+      <c r="M202" s="29"/>
+      <c r="N202" s="29"/>
+      <c r="Q202" s="29"/>
+      <c r="R202" s="29"/>
+      <c r="S202" s="29"/>
+      <c r="T202" s="29"/>
+      <c r="U202" s="29"/>
+      <c r="V202" s="29"/>
+      <c r="W202" s="29"/>
     </row>
     <row r="203" spans="1:23">
-      <c r="A203" s="37"/>
-      <c r="B203" s="37"/>
-      <c r="C203" s="38"/>
-      <c r="D203" s="37"/>
-      <c r="E203" s="37"/>
-      <c r="F203" s="37"/>
-      <c r="G203" s="39"/>
-      <c r="H203" s="37"/>
-      <c r="I203" s="37"/>
-      <c r="J203" s="37"/>
-      <c r="K203" s="37"/>
-      <c r="L203" s="37"/>
-      <c r="M203" s="39"/>
-      <c r="N203" s="37"/>
-      <c r="Q203" s="37"/>
-      <c r="R203" s="37"/>
-      <c r="S203" s="37"/>
-      <c r="T203" s="37"/>
-      <c r="U203" s="37"/>
-      <c r="V203" s="37"/>
-      <c r="W203" s="37"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
+      <c r="C203" s="30"/>
+      <c r="D203" s="29"/>
+      <c r="E203" s="29"/>
+      <c r="F203" s="29"/>
+      <c r="G203" s="29"/>
+      <c r="H203" s="29"/>
+      <c r="I203" s="29"/>
+      <c r="J203" s="29"/>
+      <c r="K203" s="29"/>
+      <c r="L203" s="29"/>
+      <c r="M203" s="29"/>
+      <c r="N203" s="29"/>
+      <c r="Q203" s="29"/>
+      <c r="R203" s="29"/>
+      <c r="S203" s="29"/>
+      <c r="T203" s="29"/>
+      <c r="U203" s="29"/>
+      <c r="V203" s="29"/>
+      <c r="W203" s="29"/>
     </row>
     <row r="204" spans="1:23">
-      <c r="A204" s="37"/>
-      <c r="B204" s="37"/>
-      <c r="C204" s="38"/>
-      <c r="D204" s="37"/>
-      <c r="E204" s="37"/>
-      <c r="F204" s="37"/>
-      <c r="G204" s="39"/>
-      <c r="H204" s="37"/>
-      <c r="I204" s="37"/>
-      <c r="J204" s="37"/>
-      <c r="K204" s="37"/>
-      <c r="L204" s="37"/>
-      <c r="M204" s="39"/>
-      <c r="N204" s="37"/>
-      <c r="Q204" s="37"/>
-      <c r="R204" s="37"/>
-      <c r="S204" s="37"/>
-      <c r="T204" s="37"/>
-      <c r="U204" s="37"/>
-      <c r="V204" s="37"/>
-      <c r="W204" s="37"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
+      <c r="C204" s="30"/>
+      <c r="D204" s="29"/>
+      <c r="E204" s="29"/>
+      <c r="F204" s="29"/>
+      <c r="G204" s="29"/>
+      <c r="H204" s="29"/>
+      <c r="I204" s="29"/>
+      <c r="J204" s="29"/>
+      <c r="K204" s="29"/>
+      <c r="L204" s="29"/>
+      <c r="M204" s="29"/>
+      <c r="N204" s="29"/>
+      <c r="Q204" s="29"/>
+      <c r="R204" s="29"/>
+      <c r="S204" s="29"/>
+      <c r="T204" s="29"/>
+      <c r="U204" s="29"/>
+      <c r="V204" s="29"/>
+      <c r="W204" s="29"/>
     </row>
     <row r="205" spans="1:23">
-      <c r="A205" s="37"/>
-      <c r="B205" s="37"/>
-      <c r="C205" s="38"/>
-      <c r="D205" s="37"/>
-      <c r="E205" s="37"/>
-      <c r="F205" s="37"/>
-      <c r="G205" s="39"/>
-      <c r="H205" s="37"/>
-      <c r="I205" s="37"/>
-      <c r="J205" s="37"/>
-      <c r="K205" s="37"/>
-      <c r="L205" s="37"/>
-      <c r="M205" s="39"/>
-      <c r="N205" s="37"/>
-      <c r="Q205" s="37"/>
-      <c r="R205" s="37"/>
-      <c r="S205" s="37"/>
-      <c r="T205" s="37"/>
-      <c r="U205" s="37"/>
-      <c r="V205" s="37"/>
-      <c r="W205" s="37"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
+      <c r="C205" s="30"/>
+      <c r="D205" s="29"/>
+      <c r="E205" s="29"/>
+      <c r="F205" s="29"/>
+      <c r="G205" s="29"/>
+      <c r="H205" s="29"/>
+      <c r="I205" s="29"/>
+      <c r="J205" s="29"/>
+      <c r="K205" s="29"/>
+      <c r="L205" s="29"/>
+      <c r="M205" s="29"/>
+      <c r="N205" s="29"/>
+      <c r="Q205" s="29"/>
+      <c r="R205" s="29"/>
+      <c r="S205" s="29"/>
+      <c r="T205" s="29"/>
+      <c r="U205" s="29"/>
+      <c r="V205" s="29"/>
+      <c r="W205" s="29"/>
     </row>
     <row r="206" spans="1:23">
-      <c r="A206" s="37"/>
-      <c r="B206" s="37"/>
-      <c r="C206" s="38"/>
-      <c r="D206" s="37"/>
-      <c r="E206" s="37"/>
-      <c r="F206" s="37"/>
-      <c r="G206" s="39"/>
-      <c r="H206" s="37"/>
-      <c r="I206" s="37"/>
-      <c r="J206" s="37"/>
-      <c r="K206" s="37"/>
-      <c r="L206" s="37"/>
-      <c r="M206" s="39"/>
-      <c r="N206" s="37"/>
-      <c r="Q206" s="37"/>
-      <c r="R206" s="37"/>
-      <c r="S206" s="37"/>
-      <c r="T206" s="37"/>
-      <c r="U206" s="37"/>
-      <c r="V206" s="37"/>
-      <c r="W206" s="37"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
+      <c r="C206" s="30"/>
+      <c r="D206" s="29"/>
+      <c r="E206" s="29"/>
+      <c r="F206" s="29"/>
+      <c r="G206" s="29"/>
+      <c r="H206" s="29"/>
+      <c r="I206" s="29"/>
+      <c r="J206" s="29"/>
+      <c r="K206" s="29"/>
+      <c r="L206" s="29"/>
+      <c r="M206" s="29"/>
+      <c r="N206" s="29"/>
+      <c r="Q206" s="29"/>
+      <c r="R206" s="29"/>
+      <c r="S206" s="29"/>
+      <c r="T206" s="29"/>
+      <c r="U206" s="29"/>
+      <c r="V206" s="29"/>
+      <c r="W206" s="29"/>
     </row>
     <row r="207" ht="15" spans="1:23">
-      <c r="A207" s="37"/>
-      <c r="B207" s="37"/>
-      <c r="C207" s="38"/>
-      <c r="D207" s="37"/>
-      <c r="E207" s="37"/>
-      <c r="F207" s="37"/>
-      <c r="G207" s="39"/>
-      <c r="H207" s="37"/>
-      <c r="I207" s="37"/>
-      <c r="J207" s="37"/>
-      <c r="K207" s="37"/>
-      <c r="L207" s="37"/>
-      <c r="M207" s="39"/>
-      <c r="N207" s="37"/>
-      <c r="Q207" s="37"/>
-      <c r="R207" s="37"/>
-      <c r="S207" s="37"/>
-      <c r="T207" s="37"/>
-      <c r="U207" s="37"/>
-      <c r="V207" s="37"/>
-      <c r="W207" s="37"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
+      <c r="C207" s="30"/>
+      <c r="D207" s="29"/>
+      <c r="E207" s="29"/>
+      <c r="F207" s="29"/>
+      <c r="G207" s="29"/>
+      <c r="H207" s="29"/>
+      <c r="I207" s="29"/>
+      <c r="J207" s="29"/>
+      <c r="K207" s="29"/>
+      <c r="L207" s="29"/>
+      <c r="M207" s="29"/>
+      <c r="N207" s="29"/>
+      <c r="Q207" s="29"/>
+      <c r="R207" s="29"/>
+      <c r="S207" s="29"/>
+      <c r="T207" s="29"/>
+      <c r="U207" s="29"/>
+      <c r="V207" s="29"/>
+      <c r="W207" s="29"/>
     </row>
     <row r="208" ht="15" spans="1:20">
-      <c r="A208" s="40"/>
-      <c r="B208" s="40"/>
-      <c r="C208" s="40"/>
-      <c r="D208" s="40"/>
-      <c r="E208" s="40"/>
-      <c r="F208" s="40"/>
-      <c r="G208" s="41"/>
-      <c r="H208" s="40"/>
-      <c r="I208" s="40"/>
-      <c r="J208" s="40"/>
-      <c r="K208" s="40"/>
-      <c r="L208" s="42"/>
-      <c r="M208" s="43"/>
-      <c r="Q208" s="40"/>
-      <c r="R208" s="40"/>
-      <c r="S208" s="40"/>
-      <c r="T208" s="40"/>
+      <c r="A208" s="31"/>
+      <c r="B208" s="31"/>
+      <c r="C208" s="31"/>
+      <c r="D208" s="31"/>
+      <c r="E208" s="31"/>
+      <c r="F208" s="31"/>
+      <c r="G208" s="31"/>
+      <c r="H208" s="31"/>
+      <c r="I208" s="31"/>
+      <c r="J208" s="31"/>
+      <c r="K208" s="31"/>
+      <c r="L208" s="32"/>
+      <c r="M208" s="32"/>
+      <c r="Q208" s="31"/>
+      <c r="R208" s="31"/>
+      <c r="S208" s="31"/>
+      <c r="T208" s="31"/>
     </row>
     <row r="209" ht="15" spans="1:20">
-      <c r="A209" s="40"/>
-      <c r="B209" s="40"/>
-      <c r="C209" s="40"/>
-      <c r="D209" s="40"/>
-      <c r="E209" s="40"/>
-      <c r="F209" s="40"/>
-      <c r="G209" s="41"/>
-      <c r="H209" s="40"/>
-      <c r="I209" s="40"/>
-      <c r="J209" s="40"/>
-      <c r="K209" s="40"/>
-      <c r="L209" s="42"/>
-      <c r="M209" s="43"/>
-      <c r="Q209" s="40"/>
-      <c r="R209" s="40"/>
-      <c r="S209" s="40"/>
-      <c r="T209" s="40"/>
+      <c r="A209" s="31"/>
+      <c r="B209" s="31"/>
+      <c r="C209" s="31"/>
+      <c r="D209" s="31"/>
+      <c r="E209" s="31"/>
+      <c r="F209" s="31"/>
+      <c r="G209" s="31"/>
+      <c r="H209" s="31"/>
+      <c r="I209" s="31"/>
+      <c r="J209" s="31"/>
+      <c r="K209" s="31"/>
+      <c r="L209" s="32"/>
+      <c r="M209" s="32"/>
+      <c r="Q209" s="31"/>
+      <c r="R209" s="31"/>
+      <c r="S209" s="31"/>
+      <c r="T209" s="31"/>
     </row>
     <row r="210" ht="15" spans="1:20">
-      <c r="A210" s="40"/>
-      <c r="B210" s="40"/>
-      <c r="C210" s="40"/>
-      <c r="D210" s="40"/>
-      <c r="E210" s="40"/>
-      <c r="F210" s="40"/>
-      <c r="G210" s="41"/>
-      <c r="H210" s="40"/>
-      <c r="I210" s="40"/>
-      <c r="J210" s="40"/>
-      <c r="K210" s="40"/>
-      <c r="L210" s="42"/>
-      <c r="M210" s="43"/>
-      <c r="Q210" s="40"/>
-      <c r="R210" s="40"/>
-      <c r="S210" s="40"/>
-      <c r="T210" s="40"/>
+      <c r="A210" s="31"/>
+      <c r="B210" s="31"/>
+      <c r="C210" s="31"/>
+      <c r="D210" s="31"/>
+      <c r="E210" s="31"/>
+      <c r="F210" s="31"/>
+      <c r="G210" s="31"/>
+      <c r="H210" s="31"/>
+      <c r="I210" s="31"/>
+      <c r="J210" s="31"/>
+      <c r="K210" s="31"/>
+      <c r="L210" s="32"/>
+      <c r="M210" s="32"/>
+      <c r="Q210" s="31"/>
+      <c r="R210" s="31"/>
+      <c r="S210" s="31"/>
+      <c r="T210" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11002,19 +11043,19 @@
   <sheetData>
     <row r="19" spans="12:18">
       <c r="L19" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="M19" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="N19" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="P19" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
       <c r="R19" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="12:18">
@@ -11028,10 +11069,10 @@
         <v>5</v>
       </c>
       <c r="O20" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P20" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="Q20" t="str">
         <f>O20&amp;P20</f>
@@ -11052,10 +11093,10 @@
         <v>5</v>
       </c>
       <c r="O21" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P21" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="Q21" t="str">
         <f t="shared" ref="Q21:Q61" si="0">O21&amp;P21</f>
@@ -11076,10 +11117,10 @@
         <v>5</v>
       </c>
       <c r="O22" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P22" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="Q22" t="str">
         <f t="shared" si="0"/>
@@ -11100,10 +11141,10 @@
         <v>5</v>
       </c>
       <c r="O23" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P23" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
       <c r="Q23" t="str">
         <f t="shared" si="0"/>
@@ -11124,10 +11165,10 @@
         <v>5</v>
       </c>
       <c r="O24" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P24" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
@@ -11148,10 +11189,10 @@
         <v>5</v>
       </c>
       <c r="O25" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P25" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
@@ -11172,10 +11213,10 @@
         <v>5</v>
       </c>
       <c r="O26" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P26" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
@@ -11196,10 +11237,10 @@
         <v>5</v>
       </c>
       <c r="O27" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P27" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
@@ -11214,16 +11255,16 @@
         <v>5009</v>
       </c>
       <c r="M28" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
       <c r="P28" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
@@ -11238,13 +11279,13 @@
         <v>6001</v>
       </c>
       <c r="M29" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="O29" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P29" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="Q29" t="str">
         <f t="shared" si="0"/>
@@ -11259,13 +11300,13 @@
         <v>6002</v>
       </c>
       <c r="M30" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="O30" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P30" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="Q30" t="str">
         <f t="shared" si="0"/>
@@ -11280,13 +11321,13 @@
         <v>6003</v>
       </c>
       <c r="M31" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="O31" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P31" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="Q31" t="str">
         <f t="shared" si="0"/>
@@ -11301,13 +11342,13 @@
         <v>6004</v>
       </c>
       <c r="M32" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="O32" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P32" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
       <c r="Q32" t="str">
         <f t="shared" si="0"/>
@@ -11322,13 +11363,13 @@
         <v>6005</v>
       </c>
       <c r="M33" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="O33" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P33" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="Q33" t="str">
         <f t="shared" si="0"/>
@@ -11343,13 +11384,13 @@
         <v>6006</v>
       </c>
       <c r="M34" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="O34" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P34" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="Q34" t="str">
         <f t="shared" si="0"/>
@@ -11364,13 +11405,13 @@
         <v>6007</v>
       </c>
       <c r="M35" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="O35" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P35" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="Q35" t="str">
         <f t="shared" si="0"/>
@@ -11385,13 +11426,13 @@
         <v>6008</v>
       </c>
       <c r="M36" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
       <c r="O36" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P36" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="Q36" t="str">
         <f t="shared" si="0"/>
@@ -11406,13 +11447,13 @@
         <v>6009</v>
       </c>
       <c r="M37" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
       <c r="O37" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P37" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="Q37" t="str">
         <f t="shared" si="0"/>
@@ -11427,13 +11468,13 @@
         <v>6010</v>
       </c>
       <c r="M38" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
       <c r="O38" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P38" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="Q38" t="str">
         <f t="shared" si="0"/>
@@ -11448,13 +11489,13 @@
         <v>6011</v>
       </c>
       <c r="M39" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="O39" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P39" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="Q39" t="str">
         <f t="shared" si="0"/>
@@ -11469,13 +11510,13 @@
         <v>6012</v>
       </c>
       <c r="M40" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="O40" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P40" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="Q40" t="str">
         <f t="shared" si="0"/>
@@ -11490,13 +11531,13 @@
         <v>6013</v>
       </c>
       <c r="M41" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="O41" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P41" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="Q41" t="str">
         <f t="shared" si="0"/>
@@ -11511,13 +11552,13 @@
         <v>6014</v>
       </c>
       <c r="M42" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
       <c r="O42" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P42" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="Q42" t="str">
         <f t="shared" si="0"/>
@@ -11532,13 +11573,13 @@
         <v>6015</v>
       </c>
       <c r="M43" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="O43" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="P43" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="Q43" t="str">
         <f t="shared" si="0"/>
@@ -11553,16 +11594,16 @@
         <v>7001</v>
       </c>
       <c r="M44" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
       <c r="N44">
         <v>7</v>
       </c>
       <c r="O44" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="P44" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="Q44" t="str">
         <f t="shared" si="0"/>
@@ -11577,16 +11618,16 @@
         <v>7002</v>
       </c>
       <c r="M45" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="N45">
         <v>7</v>
       </c>
       <c r="O45" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="P45" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
       <c r="Q45" t="str">
         <f t="shared" si="0"/>
@@ -11601,16 +11642,16 @@
         <v>7003</v>
       </c>
       <c r="M46" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
       <c r="N46">
         <v>7</v>
       </c>
       <c r="O46" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="P46" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="Q46" t="str">
         <f t="shared" si="0"/>
@@ -11625,16 +11666,16 @@
         <v>7004</v>
       </c>
       <c r="M47" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="N47">
         <v>7</v>
       </c>
       <c r="O47" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
       <c r="P47" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
       <c r="Q47" t="str">
         <f t="shared" si="0"/>
@@ -11649,16 +11690,16 @@
         <v>8001</v>
       </c>
       <c r="M48" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="N48">
         <v>8</v>
       </c>
       <c r="O48" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P48" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q48" t="str">
         <f t="shared" si="0"/>
@@ -11673,16 +11714,16 @@
         <v>8002</v>
       </c>
       <c r="M49" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="N49">
         <v>8</v>
       </c>
       <c r="O49" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P49" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q49" t="str">
         <f t="shared" si="0"/>
@@ -11697,16 +11738,16 @@
         <v>8003</v>
       </c>
       <c r="M50" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="N50">
         <v>8</v>
       </c>
       <c r="O50" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P50" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q50" t="str">
         <f t="shared" si="0"/>
@@ -11721,16 +11762,16 @@
         <v>8004</v>
       </c>
       <c r="M51" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="N51">
         <v>8</v>
       </c>
       <c r="O51" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P51" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q51" t="str">
         <f t="shared" si="0"/>
@@ -11745,16 +11786,16 @@
         <v>8005</v>
       </c>
       <c r="M52" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="N52">
         <v>8</v>
       </c>
       <c r="O52" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P52" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q52" t="str">
         <f t="shared" si="0"/>
@@ -11769,16 +11810,16 @@
         <v>8006</v>
       </c>
       <c r="M53" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
       <c r="N53">
         <v>8</v>
       </c>
       <c r="O53" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P53" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q53" t="str">
         <f t="shared" si="0"/>
@@ -11793,16 +11834,16 @@
         <v>8007</v>
       </c>
       <c r="M54" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="N54">
         <v>8</v>
       </c>
       <c r="O54" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P54" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q54" t="str">
         <f t="shared" si="0"/>
@@ -11817,16 +11858,16 @@
         <v>8008</v>
       </c>
       <c r="M55" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="N55">
         <v>8</v>
       </c>
       <c r="O55" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P55" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q55" t="str">
         <f t="shared" si="0"/>
@@ -11841,16 +11882,16 @@
         <v>8009</v>
       </c>
       <c r="M56" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="N56">
         <v>8</v>
       </c>
       <c r="O56" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P56" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q56" t="str">
         <f t="shared" si="0"/>
@@ -11865,16 +11906,16 @@
         <v>8010</v>
       </c>
       <c r="M57" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="N57">
         <v>8</v>
       </c>
       <c r="O57" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P57" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q57" t="str">
         <f t="shared" si="0"/>
@@ -11889,16 +11930,16 @@
         <v>8011</v>
       </c>
       <c r="M58" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="N58">
         <v>8</v>
       </c>
       <c r="O58" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P58" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q58" t="str">
         <f t="shared" si="0"/>
@@ -11913,16 +11954,16 @@
         <v>8012</v>
       </c>
       <c r="M59" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
       <c r="N59">
         <v>8</v>
       </c>
       <c r="O59" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P59" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q59" t="str">
         <f t="shared" si="0"/>
@@ -11937,16 +11978,16 @@
         <v>8013</v>
       </c>
       <c r="M60" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="N60">
         <v>8</v>
       </c>
       <c r="O60" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P60" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q60" t="str">
         <f t="shared" si="0"/>
@@ -11961,16 +12002,16 @@
         <v>8014</v>
       </c>
       <c r="M61" t="s">
-        <v>365</v>
+        <v>401</v>
       </c>
       <c r="N61">
         <v>8</v>
       </c>
       <c r="O61" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
       <c r="P61" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="Q61" t="str">
         <f t="shared" si="0"/>

--- a/Tools/Luban/DataTables/Datas/D_道具.xlsx
+++ b/Tools/Luban/DataTables/Datas/D_道具.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30360" windowHeight="17775"/>
+    <workbookView windowHeight="14970"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="427">
   <si>
     <t>##var</t>
   </si>
@@ -780,18 +780,27 @@
     <t>Prefab/Item/Popcorn/Potato_Mushroom</t>
   </si>
   <si>
+    <t>1002#1011</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;南瓜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Potato_Pumpkin</t>
   </si>
   <si>
+    <t>1010#1017</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;胡萝卜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Potato_Carrot</t>
   </si>
   <si>
+    <t>1008#1016</t>
+  </si>
+  <si>
     <t>爆米花-土豆&amp;水甜菜味</t>
   </si>
   <si>
@@ -828,18 +837,27 @@
     <t>Prefab/Item/Popcorn/Mushroom_Pumpkin</t>
   </si>
   <si>
+    <t>1002#1011#1010#1017</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;胡萝卜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Mushroom_Carrot</t>
   </si>
   <si>
+    <t>1002#1011#1008#1016</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;水甜菜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Mushroom_WaterBeet</t>
   </si>
   <si>
+    <t>1002#1011#1013</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;红番茄味</t>
   </si>
   <si>
@@ -852,30 +870,45 @@
     <t>Prefab/Item/Popcorn/Mushroom_Broccoli</t>
   </si>
   <si>
+    <t>1002#1011#1014</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;猕猴桃味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Mushroom_Kiwi</t>
   </si>
   <si>
+    <t>1002#1011#1009</t>
+  </si>
+  <si>
     <t>爆米花-蘑菇&amp;野草味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Mushroom_Weed</t>
   </si>
   <si>
+    <t>1002#1011#1015</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;胡萝卜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Pumpkin_Carrot</t>
   </si>
   <si>
+    <t>1010#1017#1008#1016</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;水甜菜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Pumpkin_WaterBeet</t>
   </si>
   <si>
+    <t>1010#1017#1013</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;红番茄味</t>
   </si>
   <si>
@@ -888,24 +921,36 @@
     <t>Prefab/Item/Popcorn/Pumpkin_Broccoli</t>
   </si>
   <si>
+    <t>1010#1017#1014</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;猕猴桃味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Pumpkin_Kiwi</t>
   </si>
   <si>
+    <t>1010#1017#1009</t>
+  </si>
+  <si>
     <t>爆米花-南瓜&amp;野草味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Pumpkin_Weed</t>
   </si>
   <si>
+    <t>1010#1017#1015</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;水甜菜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Carrot_WaterBeet</t>
   </si>
   <si>
+    <t>1008#1016#1013</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;红番茄味</t>
   </si>
   <si>
@@ -918,42 +963,63 @@
     <t>Prefab/Item/Popcorn/Carrot_Broccoli</t>
   </si>
   <si>
+    <t>1008#1016#1014</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;猕猴桃味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Carrot_Kiwi</t>
   </si>
   <si>
+    <t>1008#1016#1009</t>
+  </si>
+  <si>
     <t>爆米花-胡萝卜&amp;野草味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Carrot_Weed</t>
   </si>
   <si>
+    <t>1008#1016#1015</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;红番茄味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/WaterBeet_RedTomato</t>
   </si>
   <si>
+    <t>1013#1013</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;花椰菜味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/WaterBeet_Broccoli</t>
   </si>
   <si>
+    <t>1013#1014</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;猕猴桃味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/WaterBeet_Kiwi</t>
   </si>
   <si>
+    <t>1013#1009</t>
+  </si>
+  <si>
     <t>爆米花-水甜菜&amp;野草味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/WaterBeet_Weed</t>
   </si>
   <si>
+    <t>1013#1015</t>
+  </si>
+  <si>
     <t>爆米花-红番茄&amp;花椰菜味</t>
   </si>
   <si>
@@ -978,16 +1044,25 @@
     <t>Prefab/Item/Popcorn/Broccoli_Kiwi</t>
   </si>
   <si>
+    <t>1014#1009</t>
+  </si>
+  <si>
     <t>爆米花-花椰菜&amp;野草味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Broccoli_Weed</t>
   </si>
   <si>
+    <t>1014#1015</t>
+  </si>
+  <si>
     <t>爆米花-猕猴桃&amp;野草味</t>
   </si>
   <si>
     <t>Prefab/Item/Popcorn/Kiwi_Weed</t>
+  </si>
+  <si>
+    <t>1009#1015</t>
   </si>
   <si>
     <t>土豆-房子</t>
@@ -2025,7 +2100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2043,6 +2118,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -2073,14 +2151,29 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2099,16 +2192,31 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2444,267 +2552,268 @@
     <col min="10" max="12" width="7.08333333333333" style="6" customWidth="1"/>
     <col min="13" max="13" width="16.6666666666667" style="6" customWidth="1"/>
     <col min="14" max="18" width="12.1666666666667" style="6"/>
-    <col min="19" max="20" width="17.8333333333333" style="6" customWidth="1"/>
+    <col min="19" max="19" width="17.8333333333333" style="6" customWidth="1"/>
+    <col min="20" max="20" width="17.8333333333333" style="7" customWidth="1"/>
     <col min="21" max="22" width="26.3333333333333" style="6" customWidth="1"/>
     <col min="23" max="23" width="12.1666666666667" style="6"/>
-    <col min="24" max="28" width="12.1666666666667" style="7"/>
+    <col min="24" max="28" width="12.1666666666667" style="8"/>
     <col min="29" max="16384" width="12.1666666666667" style="6"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:28">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="W1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="17" t="s">
+      <c r="X1" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="17" t="s">
+      <c r="Y1" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="17" t="s">
+      <c r="Z1" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="17" t="s">
+      <c r="AA1" s="19" t="s">
         <v>26</v>
       </c>
       <c r="AB1"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:28">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="9" t="s">
+      <c r="R2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="S2" s="9" t="s">
+      <c r="S2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="T2" s="9" t="s">
+      <c r="T2" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="U2" s="9" t="s">
+      <c r="U2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="V2" s="9" t="s">
+      <c r="V2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="W2" s="9" t="s">
+      <c r="W2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="9" t="s">
+      <c r="X2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Y2" s="9" t="s">
+      <c r="Y2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="9" t="s">
+      <c r="Z2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AA2" s="9" t="s">
+      <c r="AA2" s="10" t="s">
         <v>31</v>
       </c>
       <c r="AB2"/>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:28">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="9" t="s">
+      <c r="M3" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="P3" s="9" t="s">
+      <c r="P3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="Q3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="R3" s="9" t="s">
+      <c r="R3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="T3" s="9" t="s">
+      <c r="T3" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="U3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="V3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="9" t="s">
+      <c r="W3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="X3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="9" t="s">
+      <c r="Y3" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="9" t="s">
+      <c r="Z3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AA3" s="17" t="s">
+      <c r="AA3" s="19" t="s">
         <v>57</v>
       </c>
       <c r="AB3"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:28">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2761,7 +2870,7 @@
       <c r="S4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="T4" s="20" t="s">
         <v>71</v>
       </c>
       <c r="U4" s="1" t="s">
@@ -2773,22 +2882,22 @@
       <c r="W4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="X4" s="18" t="s">
+      <c r="X4" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="Y4" s="18" t="s">
+      <c r="Y4" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="Z4" s="18" t="s">
+      <c r="Z4" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="AA4" s="18" t="s">
+      <c r="AA4" s="21" t="s">
         <v>76</v>
       </c>
       <c r="AB4"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:28">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="2">
         <v>1001</v>
       </c>
@@ -2798,10 +2907,10 @@
       <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G5" s="13"/>
+      <c r="G5" s="14"/>
       <c r="H5" s="2">
         <v>1</v>
       </c>
@@ -2829,17 +2938,18 @@
       <c r="P5" s="2">
         <v>1</v>
       </c>
+      <c r="T5" s="22"/>
       <c r="V5" s="2">
         <v>0</v>
       </c>
-      <c r="X5" s="19"/>
-      <c r="Y5" s="19"/>
-      <c r="Z5" s="19"/>
-      <c r="AA5" s="19"/>
-      <c r="AB5" s="19"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:28">
-      <c r="A6" s="12"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="2">
         <v>1002</v>
       </c>
@@ -2849,10 +2959,10 @@
       <c r="E6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="14"/>
       <c r="H6" s="2">
         <v>1</v>
       </c>
@@ -2880,17 +2990,18 @@
       <c r="P6" s="2">
         <v>1</v>
       </c>
+      <c r="T6" s="22"/>
       <c r="V6" s="2">
         <v>0</v>
       </c>
-      <c r="X6" s="19"/>
-      <c r="Y6" s="19"/>
-      <c r="Z6" s="19"/>
-      <c r="AA6" s="19"/>
-      <c r="AB6" s="19"/>
+      <c r="X6" s="23"/>
+      <c r="Y6" s="23"/>
+      <c r="Z6" s="23"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:28">
-      <c r="A7" s="12"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="2">
         <v>1003</v>
       </c>
@@ -2900,10 +3011,10 @@
       <c r="E7" s="2">
         <v>1</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="14"/>
       <c r="H7" s="2">
         <v>1</v>
       </c>
@@ -2931,17 +3042,18 @@
       <c r="P7" s="2">
         <v>1</v>
       </c>
+      <c r="T7" s="22"/>
       <c r="V7" s="2">
         <v>0</v>
       </c>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="19"/>
-      <c r="AB7" s="19"/>
+      <c r="X7" s="23"/>
+      <c r="Y7" s="23"/>
+      <c r="Z7" s="23"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:28">
-      <c r="A8" s="12"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="2">
         <v>1004</v>
       </c>
@@ -2951,10 +3063,10 @@
       <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="13"/>
+      <c r="G8" s="14"/>
       <c r="H8" s="2">
         <v>1</v>
       </c>
@@ -2982,17 +3094,18 @@
       <c r="P8" s="2">
         <v>1</v>
       </c>
+      <c r="T8" s="22"/>
       <c r="V8" s="2">
         <v>0</v>
       </c>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
+      <c r="X8" s="23"/>
+      <c r="Y8" s="23"/>
+      <c r="Z8" s="23"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:28">
-      <c r="A9" s="12"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="2">
         <v>1005</v>
       </c>
@@ -3002,10 +3115,10 @@
       <c r="E9" s="2">
         <v>1</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="14"/>
       <c r="H9" s="2">
         <v>1</v>
       </c>
@@ -3033,17 +3146,18 @@
       <c r="P9" s="2">
         <v>1</v>
       </c>
+      <c r="T9" s="22"/>
       <c r="V9" s="2">
         <v>0</v>
       </c>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
+      <c r="X9" s="23"/>
+      <c r="Y9" s="23"/>
+      <c r="Z9" s="23"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
     </row>
     <row r="10" s="2" customFormat="1" spans="1:28">
-      <c r="A10" s="12"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="2">
         <v>1006</v>
       </c>
@@ -3053,10 +3167,10 @@
       <c r="E10" s="2">
         <v>1</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="13"/>
+      <c r="G10" s="14"/>
       <c r="H10" s="2">
         <v>1</v>
       </c>
@@ -3084,17 +3198,18 @@
       <c r="P10" s="2">
         <v>1</v>
       </c>
+      <c r="T10" s="22"/>
       <c r="V10" s="2">
         <v>0</v>
       </c>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="19"/>
-      <c r="AB10" s="19"/>
+      <c r="X10" s="23"/>
+      <c r="Y10" s="23"/>
+      <c r="Z10" s="23"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
     </row>
     <row r="11" s="2" customFormat="1" spans="1:28">
-      <c r="A11" s="12"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="2">
         <v>1007</v>
       </c>
@@ -3104,10 +3219,10 @@
       <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="13"/>
+      <c r="G11" s="14"/>
       <c r="H11" s="2">
         <v>1</v>
       </c>
@@ -3135,17 +3250,18 @@
       <c r="P11" s="2">
         <v>1</v>
       </c>
+      <c r="T11" s="22"/>
       <c r="V11" s="2">
         <v>0</v>
       </c>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="19"/>
-      <c r="AB11" s="19"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="23"/>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="23"/>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:28">
-      <c r="A12" s="12"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="2">
         <v>1008</v>
       </c>
@@ -3155,10 +3271,10 @@
       <c r="E12" s="2">
         <v>1</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="13"/>
+      <c r="G12" s="14"/>
       <c r="H12" s="2">
         <v>1</v>
       </c>
@@ -3186,17 +3302,18 @@
       <c r="P12" s="2">
         <v>1</v>
       </c>
+      <c r="T12" s="22"/>
       <c r="V12" s="2">
         <v>0</v>
       </c>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="19"/>
-      <c r="AB12" s="19"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="23"/>
+      <c r="Z12" s="23"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
     </row>
     <row r="13" s="2" customFormat="1" spans="1:28">
-      <c r="A13" s="12"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="2">
         <v>1009</v>
       </c>
@@ -3206,10 +3323,10 @@
       <c r="E13" s="2">
         <v>1</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="13"/>
+      <c r="G13" s="14"/>
       <c r="H13" s="2">
         <v>1</v>
       </c>
@@ -3237,17 +3354,18 @@
       <c r="P13" s="2">
         <v>1</v>
       </c>
+      <c r="T13" s="22"/>
       <c r="V13" s="2">
         <v>0</v>
       </c>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
+      <c r="X13" s="23"/>
+      <c r="Y13" s="23"/>
+      <c r="Z13" s="23"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
     </row>
     <row r="14" s="2" customFormat="1" spans="1:28">
-      <c r="A14" s="12"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="2">
         <v>1010</v>
       </c>
@@ -3257,10 +3375,10 @@
       <c r="E14" s="2">
         <v>1</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="13"/>
+      <c r="G14" s="14"/>
       <c r="H14" s="2">
         <v>1</v>
       </c>
@@ -3288,17 +3406,18 @@
       <c r="P14" s="2">
         <v>1</v>
       </c>
+      <c r="T14" s="22"/>
       <c r="V14" s="2">
         <v>0</v>
       </c>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="19"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="19"/>
-      <c r="AB14" s="19"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
     </row>
     <row r="15" s="2" customFormat="1" spans="1:28">
-      <c r="A15" s="12"/>
+      <c r="A15" s="13"/>
       <c r="B15" s="2">
         <v>1011</v>
       </c>
@@ -3308,10 +3427,10 @@
       <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="13"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="2">
         <v>1</v>
       </c>
@@ -3339,17 +3458,18 @@
       <c r="P15" s="2">
         <v>0</v>
       </c>
+      <c r="T15" s="22"/>
       <c r="V15" s="2">
         <v>0</v>
       </c>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="19"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="19"/>
-      <c r="AB15" s="19"/>
+      <c r="X15" s="23"/>
+      <c r="Y15" s="23"/>
+      <c r="Z15" s="23"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
     </row>
     <row r="16" s="2" customFormat="1" spans="1:28">
-      <c r="A16" s="12"/>
+      <c r="A16" s="13"/>
       <c r="B16" s="2">
         <v>1012</v>
       </c>
@@ -3359,10 +3479,10 @@
       <c r="E16" s="2">
         <v>1</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G16" s="13"/>
+      <c r="G16" s="14"/>
       <c r="H16" s="2">
         <v>1</v>
       </c>
@@ -3390,17 +3510,18 @@
       <c r="P16" s="2">
         <v>1</v>
       </c>
+      <c r="T16" s="22"/>
       <c r="V16" s="2">
         <v>0</v>
       </c>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="19"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="19"/>
-      <c r="AB16" s="19"/>
+      <c r="X16" s="23"/>
+      <c r="Y16" s="23"/>
+      <c r="Z16" s="23"/>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="23"/>
     </row>
     <row r="17" s="2" customFormat="1" spans="1:28">
-      <c r="A17" s="12"/>
+      <c r="A17" s="13"/>
       <c r="B17" s="2">
         <v>1013</v>
       </c>
@@ -3410,10 +3531,10 @@
       <c r="E17" s="2">
         <v>1</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="13"/>
+      <c r="G17" s="14"/>
       <c r="H17" s="2">
         <v>1</v>
       </c>
@@ -3441,14 +3562,15 @@
       <c r="P17" s="2">
         <v>1</v>
       </c>
+      <c r="T17" s="22"/>
       <c r="V17" s="2">
         <v>0</v>
       </c>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-      <c r="AB17" s="19"/>
+      <c r="X17" s="23"/>
+      <c r="Y17" s="23"/>
+      <c r="Z17" s="23"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="23"/>
     </row>
     <row r="18" s="2" customFormat="1" spans="2:28">
       <c r="B18" s="2">
@@ -3460,10 +3582,10 @@
       <c r="E18" s="2">
         <v>1</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="13"/>
+      <c r="G18" s="14"/>
       <c r="H18" s="2">
         <v>1</v>
       </c>
@@ -3491,14 +3613,15 @@
       <c r="P18" s="2">
         <v>1</v>
       </c>
+      <c r="T18" s="22"/>
       <c r="V18" s="2">
         <v>0</v>
       </c>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-      <c r="AB18" s="19"/>
+      <c r="X18" s="23"/>
+      <c r="Y18" s="23"/>
+      <c r="Z18" s="23"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="2:22">
       <c r="B19" s="3">
@@ -3507,16 +3630,16 @@
       <c r="C19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="15" t="s">
         <v>105</v>
       </c>
       <c r="E19" s="3">
         <v>2</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="15" t="s">
         <v>107</v>
       </c>
       <c r="H19" s="3">
@@ -3555,6 +3678,7 @@
       <c r="S19" s="3" t="s">
         <v>109</v>
       </c>
+      <c r="T19" s="24"/>
       <c r="U19" s="3" t="s">
         <v>110</v>
       </c>
@@ -3575,10 +3699,10 @@
       <c r="E20" s="3">
         <v>2</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="15" t="s">
         <v>113</v>
       </c>
       <c r="H20" s="3">
@@ -3611,6 +3735,7 @@
       <c r="S20" s="3" t="s">
         <v>114</v>
       </c>
+      <c r="T20" s="24"/>
       <c r="U20" s="3" t="s">
         <v>114</v>
       </c>
@@ -3620,11 +3745,11 @@
       <c r="W20" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="X20" s="20"/>
-      <c r="Y20" s="20"/>
-      <c r="Z20" s="20"/>
-      <c r="AA20" s="20"/>
-      <c r="AB20" s="20"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="2:28">
       <c r="B21" s="3">
@@ -3642,7 +3767,7 @@
       <c r="F21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="15" t="s">
         <v>118</v>
       </c>
       <c r="H21" s="3">
@@ -3675,6 +3800,7 @@
       <c r="S21" s="3" t="s">
         <v>119</v>
       </c>
+      <c r="T21" s="24"/>
       <c r="U21" s="3" t="s">
         <v>120</v>
       </c>
@@ -3684,11 +3810,11 @@
       <c r="W21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
     </row>
     <row r="22" s="3" customFormat="1" ht="14.5" customHeight="1" spans="2:28">
       <c r="B22" s="3">
@@ -3706,7 +3832,7 @@
       <c r="F22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="15" t="s">
         <v>124</v>
       </c>
       <c r="H22" s="3">
@@ -3745,6 +3871,7 @@
       <c r="S22" s="3" t="s">
         <v>126</v>
       </c>
+      <c r="T22" s="24"/>
       <c r="U22" s="3" t="s">
         <v>127</v>
       </c>
@@ -3754,11 +3881,11 @@
       <c r="W22" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="2:28">
       <c r="B23" s="3">
@@ -3776,7 +3903,7 @@
       <c r="F23" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="15" t="s">
         <v>131</v>
       </c>
       <c r="H23" s="3">
@@ -3809,6 +3936,7 @@
       <c r="S23" s="3" t="s">
         <v>132</v>
       </c>
+      <c r="T23" s="24"/>
       <c r="U23" s="3" t="s">
         <v>133</v>
       </c>
@@ -3818,11 +3946,11 @@
       <c r="W23" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="2:28">
       <c r="B24" s="3">
@@ -3840,7 +3968,7 @@
       <c r="F24" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="15" t="s">
         <v>137</v>
       </c>
       <c r="H24" s="3">
@@ -3873,6 +4001,7 @@
       <c r="S24" s="3" t="s">
         <v>138</v>
       </c>
+      <c r="T24" s="24"/>
       <c r="U24" s="3" t="s">
         <v>139</v>
       </c>
@@ -3882,11 +4011,11 @@
       <c r="W24" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
     </row>
     <row r="25" s="3" customFormat="1" spans="2:28">
       <c r="B25" s="3">
@@ -3904,7 +4033,7 @@
       <c r="F25" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="15" t="s">
         <v>143</v>
       </c>
       <c r="H25" s="3">
@@ -3937,6 +4066,7 @@
       <c r="S25" s="3" t="s">
         <v>138</v>
       </c>
+      <c r="T25" s="24"/>
       <c r="U25" s="3" t="s">
         <v>139</v>
       </c>
@@ -3946,11 +4076,11 @@
       <c r="W25" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
     </row>
     <row r="26" s="3" customFormat="1" spans="2:28">
       <c r="B26" s="3">
@@ -3968,7 +4098,7 @@
       <c r="F26" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="15" t="s">
         <v>146</v>
       </c>
       <c r="H26" s="3">
@@ -4001,6 +4131,7 @@
       <c r="S26" s="3" t="s">
         <v>138</v>
       </c>
+      <c r="T26" s="24"/>
       <c r="U26" s="3" t="s">
         <v>139</v>
       </c>
@@ -4010,11 +4141,11 @@
       <c r="W26" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
     </row>
     <row r="27" s="3" customFormat="1" spans="2:28">
       <c r="B27" s="3">
@@ -4032,7 +4163,7 @@
       <c r="F27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="15" t="s">
         <v>149</v>
       </c>
       <c r="H27" s="3">
@@ -4065,6 +4196,7 @@
       <c r="S27" s="3" t="s">
         <v>138</v>
       </c>
+      <c r="T27" s="24"/>
       <c r="U27" s="3" t="s">
         <v>139</v>
       </c>
@@ -4074,11 +4206,11 @@
       <c r="W27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
     </row>
     <row r="28" s="3" customFormat="1" spans="2:28">
       <c r="B28" s="3">
@@ -4096,7 +4228,7 @@
       <c r="F28" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="15" t="s">
         <v>152</v>
       </c>
       <c r="H28" s="3">
@@ -4129,6 +4261,7 @@
       <c r="S28" s="3" t="s">
         <v>138</v>
       </c>
+      <c r="T28" s="24"/>
       <c r="U28" s="3" t="s">
         <v>139</v>
       </c>
@@ -4138,11 +4271,11 @@
       <c r="W28" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
     </row>
     <row r="29" s="3" customFormat="1" spans="2:28">
       <c r="B29" s="3">
@@ -4160,7 +4293,7 @@
       <c r="F29" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="15" t="s">
         <v>155</v>
       </c>
       <c r="H29" s="3">
@@ -4193,6 +4326,7 @@
       <c r="S29" s="3" t="s">
         <v>138</v>
       </c>
+      <c r="T29" s="24"/>
       <c r="U29" s="3" t="s">
         <v>139</v>
       </c>
@@ -4202,11 +4336,11 @@
       <c r="W29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X29" s="20"/>
-      <c r="Y29" s="20"/>
-      <c r="Z29" s="20"/>
-      <c r="AA29" s="20"/>
-      <c r="AB29" s="20"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
     </row>
     <row r="30" s="3" customFormat="1" spans="2:28">
       <c r="B30" s="3">
@@ -4224,7 +4358,7 @@
       <c r="F30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="15" t="s">
         <v>158</v>
       </c>
       <c r="H30" s="3">
@@ -4257,6 +4391,7 @@
       <c r="S30" s="3" t="s">
         <v>138</v>
       </c>
+      <c r="T30" s="24"/>
       <c r="U30" s="3" t="s">
         <v>139</v>
       </c>
@@ -4266,11 +4401,11 @@
       <c r="W30" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="X30" s="20"/>
-      <c r="Y30" s="20"/>
-      <c r="Z30" s="20"/>
-      <c r="AA30" s="20"/>
-      <c r="AB30" s="20"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
     </row>
     <row r="31" s="3" customFormat="1" spans="2:28">
       <c r="B31" s="3">
@@ -4285,10 +4420,10 @@
       <c r="E31" s="3">
         <v>2</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="15" t="s">
         <v>161</v>
       </c>
       <c r="H31" s="3">
@@ -4321,6 +4456,7 @@
       <c r="S31" s="3" t="s">
         <v>132</v>
       </c>
+      <c r="T31" s="24"/>
       <c r="U31" s="3" t="s">
         <v>162</v>
       </c>
@@ -4330,11 +4466,11 @@
       <c r="W31" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="X31" s="20"/>
-      <c r="Y31" s="20"/>
-      <c r="Z31" s="20"/>
-      <c r="AA31" s="20"/>
-      <c r="AB31" s="20"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
     </row>
     <row r="32" s="3" customFormat="1" spans="2:28">
       <c r="B32" s="3">
@@ -4349,10 +4485,10 @@
       <c r="E32" s="3">
         <v>2</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="15" t="s">
         <v>161</v>
       </c>
       <c r="H32" s="3">
@@ -4385,6 +4521,7 @@
       <c r="S32" s="3" t="s">
         <v>132</v>
       </c>
+      <c r="T32" s="24"/>
       <c r="U32" s="3" t="s">
         <v>164</v>
       </c>
@@ -4394,11 +4531,11 @@
       <c r="W32" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="X32" s="20"/>
-      <c r="Y32" s="20"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="20"/>
-      <c r="AB32" s="20"/>
+      <c r="X32" s="25"/>
+      <c r="Y32" s="25"/>
+      <c r="Z32" s="25"/>
+      <c r="AA32" s="25"/>
+      <c r="AB32" s="25"/>
     </row>
     <row r="33" s="3" customFormat="1" spans="2:28">
       <c r="B33" s="3">
@@ -4413,10 +4550,10 @@
       <c r="E33" s="3">
         <v>2</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="G33" s="15" t="s">
         <v>167</v>
       </c>
       <c r="H33" s="3">
@@ -4455,6 +4592,7 @@
       <c r="S33" s="3" t="s">
         <v>169</v>
       </c>
+      <c r="T33" s="24"/>
       <c r="U33" s="3" t="s">
         <v>134</v>
       </c>
@@ -4464,11 +4602,11 @@
       <c r="W33" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="X33" s="20"/>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="20"/>
-      <c r="AB33" s="20"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="25"/>
+      <c r="AA33" s="25"/>
+      <c r="AB33" s="25"/>
     </row>
     <row r="34" s="3" customFormat="1" spans="2:28">
       <c r="B34" s="3">
@@ -4486,7 +4624,7 @@
       <c r="F34" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="15" t="s">
         <v>173</v>
       </c>
       <c r="H34" s="3">
@@ -4519,6 +4657,7 @@
       <c r="S34" s="3" t="s">
         <v>132</v>
       </c>
+      <c r="T34" s="24"/>
       <c r="U34" s="3" t="s">
         <v>134</v>
       </c>
@@ -4528,11 +4667,11 @@
       <c r="W34" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="X34" s="20"/>
-      <c r="Y34" s="20"/>
-      <c r="Z34" s="20"/>
-      <c r="AA34" s="20"/>
-      <c r="AB34" s="20"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
     </row>
     <row r="35" s="3" customFormat="1" spans="2:22">
       <c r="B35" s="3">
@@ -4544,10 +4683,10 @@
       <c r="E35" s="3">
         <v>3</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="G35" s="14"/>
+      <c r="G35" s="15"/>
       <c r="H35" s="3">
         <v>4</v>
       </c>
@@ -4576,6 +4715,7 @@
       <c r="S35" s="3" t="s">
         <v>177</v>
       </c>
+      <c r="T35" s="24"/>
       <c r="V35" s="3">
         <v>1</v>
       </c>
@@ -4590,10 +4730,10 @@
       <c r="E36" s="3">
         <v>3</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="G36" s="14"/>
+      <c r="G36" s="15"/>
       <c r="H36" s="3">
         <v>4</v>
       </c>
@@ -4622,14 +4762,15 @@
       <c r="S36" s="3" t="s">
         <v>180</v>
       </c>
+      <c r="T36" s="24"/>
       <c r="V36" s="3">
         <v>1</v>
       </c>
-      <c r="X36" s="20"/>
-      <c r="Y36" s="20"/>
-      <c r="Z36" s="20"/>
-      <c r="AA36" s="20"/>
-      <c r="AB36" s="20"/>
+      <c r="X36" s="25"/>
+      <c r="Y36" s="25"/>
+      <c r="Z36" s="25"/>
+      <c r="AA36" s="25"/>
+      <c r="AB36" s="25"/>
     </row>
     <row r="37" s="3" customFormat="1" spans="2:28">
       <c r="B37" s="3">
@@ -4672,14 +4813,15 @@
       <c r="S37" s="3" t="s">
         <v>183</v>
       </c>
+      <c r="T37" s="24"/>
       <c r="V37" s="3">
         <v>1</v>
       </c>
-      <c r="X37" s="20"/>
-      <c r="Y37" s="20"/>
-      <c r="Z37" s="20"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="20"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="25"/>
+      <c r="Z37" s="25"/>
+      <c r="AA37" s="25"/>
+      <c r="AB37" s="25"/>
     </row>
     <row r="38" s="3" customFormat="1" spans="2:28">
       <c r="B38" s="3">
@@ -4722,14 +4864,15 @@
       <c r="S38" s="3" t="s">
         <v>186</v>
       </c>
+      <c r="T38" s="24"/>
       <c r="V38" s="3">
         <v>1</v>
       </c>
-      <c r="X38" s="20"/>
-      <c r="Y38" s="20"/>
-      <c r="Z38" s="20"/>
-      <c r="AA38" s="20"/>
-      <c r="AB38" s="20"/>
+      <c r="X38" s="25"/>
+      <c r="Y38" s="25"/>
+      <c r="Z38" s="25"/>
+      <c r="AA38" s="25"/>
+      <c r="AB38" s="25"/>
     </row>
     <row r="39" s="3" customFormat="1" spans="2:28">
       <c r="B39" s="3">
@@ -4772,20 +4915,21 @@
       <c r="S39" s="3" t="s">
         <v>189</v>
       </c>
+      <c r="T39" s="24"/>
       <c r="V39" s="3">
         <v>1</v>
       </c>
-      <c r="X39" s="20"/>
-      <c r="Y39" s="20"/>
-      <c r="Z39" s="20"/>
-      <c r="AA39" s="20"/>
-      <c r="AB39" s="20"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="25"/>
+      <c r="Z39" s="25"/>
+      <c r="AA39" s="25"/>
+      <c r="AB39" s="25"/>
     </row>
     <row r="40" s="3" customFormat="1" spans="2:28">
       <c r="B40" s="3">
         <v>3006</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="16" t="s">
         <v>190</v>
       </c>
       <c r="E40" s="3">
@@ -4822,14 +4966,15 @@
       <c r="S40" s="3" t="s">
         <v>192</v>
       </c>
+      <c r="T40" s="24"/>
       <c r="V40" s="3">
         <v>1</v>
       </c>
-      <c r="X40" s="20"/>
-      <c r="Y40" s="20"/>
-      <c r="Z40" s="20"/>
-      <c r="AA40" s="20"/>
-      <c r="AB40" s="20"/>
+      <c r="X40" s="25"/>
+      <c r="Y40" s="25"/>
+      <c r="Z40" s="25"/>
+      <c r="AA40" s="25"/>
+      <c r="AB40" s="25"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="2:28">
       <c r="B41" s="3">
@@ -4872,14 +5017,15 @@
       <c r="S41" s="3" t="s">
         <v>194</v>
       </c>
+      <c r="T41" s="24"/>
       <c r="V41" s="3">
         <v>1</v>
       </c>
-      <c r="X41" s="20"/>
-      <c r="Y41" s="20"/>
-      <c r="Z41" s="20"/>
-      <c r="AA41" s="20"/>
-      <c r="AB41" s="20"/>
+      <c r="X41" s="25"/>
+      <c r="Y41" s="25"/>
+      <c r="Z41" s="25"/>
+      <c r="AA41" s="25"/>
+      <c r="AB41" s="25"/>
     </row>
     <row r="42" s="3" customFormat="1" spans="2:28">
       <c r="B42" s="3">
@@ -4922,14 +5068,15 @@
       <c r="S42" s="3" t="s">
         <v>197</v>
       </c>
+      <c r="T42" s="24"/>
       <c r="V42" s="3">
         <v>1</v>
       </c>
-      <c r="X42" s="20"/>
-      <c r="Y42" s="20"/>
-      <c r="Z42" s="20"/>
-      <c r="AA42" s="20"/>
-      <c r="AB42" s="20"/>
+      <c r="X42" s="25"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="25"/>
+      <c r="AA42" s="25"/>
+      <c r="AB42" s="25"/>
     </row>
     <row r="43" s="3" customFormat="1" spans="2:28">
       <c r="B43" s="3">
@@ -4972,14 +5119,15 @@
       <c r="S43" s="3" t="s">
         <v>200</v>
       </c>
+      <c r="T43" s="24"/>
       <c r="V43" s="3">
         <v>1</v>
       </c>
-      <c r="X43" s="20"/>
-      <c r="Y43" s="20"/>
-      <c r="Z43" s="20"/>
-      <c r="AA43" s="20"/>
-      <c r="AB43" s="20"/>
+      <c r="X43" s="25"/>
+      <c r="Y43" s="25"/>
+      <c r="Z43" s="25"/>
+      <c r="AA43" s="25"/>
+      <c r="AB43" s="25"/>
     </row>
     <row r="44" s="3" customFormat="1" spans="2:28">
       <c r="B44" s="3">
@@ -5022,14 +5170,15 @@
       <c r="S44" s="3" t="s">
         <v>202</v>
       </c>
+      <c r="T44" s="24"/>
       <c r="V44" s="3">
         <v>1</v>
       </c>
-      <c r="X44" s="20"/>
-      <c r="Y44" s="20"/>
-      <c r="Z44" s="20"/>
-      <c r="AA44" s="20"/>
-      <c r="AB44" s="20"/>
+      <c r="X44" s="25"/>
+      <c r="Y44" s="25"/>
+      <c r="Z44" s="25"/>
+      <c r="AA44" s="25"/>
+      <c r="AB44" s="25"/>
     </row>
     <row r="45" s="3" customFormat="1" spans="2:28">
       <c r="B45" s="3">
@@ -5072,14 +5221,15 @@
       <c r="S45" s="3" t="s">
         <v>204</v>
       </c>
+      <c r="T45" s="24"/>
       <c r="V45" s="3">
         <v>1</v>
       </c>
-      <c r="X45" s="20"/>
-      <c r="Y45" s="20"/>
-      <c r="Z45" s="20"/>
-      <c r="AA45" s="20"/>
-      <c r="AB45" s="20"/>
+      <c r="X45" s="25"/>
+      <c r="Y45" s="25"/>
+      <c r="Z45" s="25"/>
+      <c r="AA45" s="25"/>
+      <c r="AB45" s="25"/>
     </row>
     <row r="46" s="3" customFormat="1" spans="2:28">
       <c r="B46" s="3">
@@ -5122,14 +5272,15 @@
       <c r="S46" s="3" t="s">
         <v>206</v>
       </c>
+      <c r="T46" s="24"/>
       <c r="V46" s="3">
         <v>1</v>
       </c>
-      <c r="X46" s="20"/>
-      <c r="Y46" s="20"/>
-      <c r="Z46" s="20"/>
-      <c r="AA46" s="20"/>
-      <c r="AB46" s="20"/>
+      <c r="X46" s="25"/>
+      <c r="Y46" s="25"/>
+      <c r="Z46" s="25"/>
+      <c r="AA46" s="25"/>
+      <c r="AB46" s="25"/>
     </row>
     <row r="47" s="3" customFormat="1" spans="2:28">
       <c r="B47" s="3">
@@ -5141,10 +5292,10 @@
       <c r="E47" s="3">
         <v>3</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="G47" s="14"/>
+      <c r="G47" s="15"/>
       <c r="H47" s="3">
         <v>4</v>
       </c>
@@ -5173,14 +5324,15 @@
       <c r="S47" s="3" t="s">
         <v>209</v>
       </c>
+      <c r="T47" s="24"/>
       <c r="V47" s="3">
         <v>1</v>
       </c>
-      <c r="X47" s="20"/>
-      <c r="Y47" s="20"/>
-      <c r="Z47" s="20"/>
-      <c r="AA47" s="20"/>
-      <c r="AB47" s="20"/>
+      <c r="X47" s="25"/>
+      <c r="Y47" s="25"/>
+      <c r="Z47" s="25"/>
+      <c r="AA47" s="25"/>
+      <c r="AB47" s="25"/>
     </row>
     <row r="48" s="3" customFormat="1" spans="2:28">
       <c r="B48" s="3">
@@ -5192,10 +5344,10 @@
       <c r="E48" s="3">
         <v>3</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="G48" s="14"/>
+      <c r="G48" s="15"/>
       <c r="H48" s="3">
         <v>4</v>
       </c>
@@ -5224,14 +5376,15 @@
       <c r="S48" s="3" t="s">
         <v>212</v>
       </c>
+      <c r="T48" s="24"/>
       <c r="V48" s="3">
         <v>1</v>
       </c>
-      <c r="X48" s="20"/>
-      <c r="Y48" s="20"/>
-      <c r="Z48" s="20"/>
-      <c r="AA48" s="20"/>
-      <c r="AB48" s="20"/>
+      <c r="X48" s="25"/>
+      <c r="Y48" s="25"/>
+      <c r="Z48" s="25"/>
+      <c r="AA48" s="25"/>
+      <c r="AB48" s="25"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="2:28">
       <c r="B49" s="3">
@@ -5274,14 +5427,15 @@
       <c r="S49" s="3" t="s">
         <v>214</v>
       </c>
+      <c r="T49" s="24"/>
       <c r="V49" s="3">
         <v>1</v>
       </c>
-      <c r="X49" s="20"/>
-      <c r="Y49" s="20"/>
-      <c r="Z49" s="20"/>
-      <c r="AA49" s="20"/>
-      <c r="AB49" s="20"/>
+      <c r="X49" s="25"/>
+      <c r="Y49" s="25"/>
+      <c r="Z49" s="25"/>
+      <c r="AA49" s="25"/>
+      <c r="AB49" s="25"/>
     </row>
     <row r="50" s="4" customFormat="1" spans="2:22">
       <c r="B50" s="4">
@@ -5293,10 +5447,10 @@
       <c r="E50" s="4">
         <v>4</v>
       </c>
-      <c r="F50" s="16" t="s">
+      <c r="F50" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="G50" s="16"/>
+      <c r="G50" s="17"/>
       <c r="H50" s="4">
         <v>0.5</v>
       </c>
@@ -5324,6 +5478,7 @@
       <c r="S50" s="4" t="s">
         <v>109</v>
       </c>
+      <c r="T50" s="26"/>
       <c r="V50" s="4">
         <v>1</v>
       </c>
@@ -5338,10 +5493,10 @@
       <c r="E51" s="4">
         <v>4</v>
       </c>
-      <c r="F51" s="16" t="s">
+      <c r="F51" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="G51" s="16"/>
+      <c r="G51" s="17"/>
       <c r="H51" s="4">
         <v>0.5</v>
       </c>
@@ -5369,14 +5524,15 @@
       <c r="S51" s="4" t="s">
         <v>114</v>
       </c>
+      <c r="T51" s="26"/>
       <c r="V51" s="4">
         <v>1</v>
       </c>
-      <c r="X51" s="21"/>
-      <c r="Y51" s="21"/>
-      <c r="Z51" s="21"/>
-      <c r="AA51" s="21"/>
-      <c r="AB51" s="21"/>
+      <c r="X51" s="27"/>
+      <c r="Y51" s="27"/>
+      <c r="Z51" s="27"/>
+      <c r="AA51" s="27"/>
+      <c r="AB51" s="27"/>
     </row>
     <row r="52" s="4" customFormat="1" spans="2:28">
       <c r="B52" s="4">
@@ -5418,14 +5574,15 @@
       <c r="S52" s="4" t="s">
         <v>119</v>
       </c>
+      <c r="T52" s="26"/>
       <c r="V52" s="4">
         <v>1</v>
       </c>
-      <c r="X52" s="21"/>
-      <c r="Y52" s="21"/>
-      <c r="Z52" s="21"/>
-      <c r="AA52" s="21"/>
-      <c r="AB52" s="21"/>
+      <c r="X52" s="27"/>
+      <c r="Y52" s="27"/>
+      <c r="Z52" s="27"/>
+      <c r="AA52" s="27"/>
+      <c r="AB52" s="27"/>
     </row>
     <row r="53" s="4" customFormat="1" spans="2:28">
       <c r="B53" s="4">
@@ -5467,14 +5624,15 @@
       <c r="S53" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="T53" s="26"/>
       <c r="V53" s="4">
         <v>1</v>
       </c>
-      <c r="X53" s="21"/>
-      <c r="Y53" s="21"/>
-      <c r="Z53" s="21"/>
-      <c r="AA53" s="21"/>
-      <c r="AB53" s="21"/>
+      <c r="X53" s="27"/>
+      <c r="Y53" s="27"/>
+      <c r="Z53" s="27"/>
+      <c r="AA53" s="27"/>
+      <c r="AB53" s="27"/>
     </row>
     <row r="54" s="4" customFormat="1" spans="2:28">
       <c r="B54" s="4">
@@ -5516,14 +5674,15 @@
       <c r="S54" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="T54" s="26"/>
       <c r="V54" s="4">
         <v>1</v>
       </c>
-      <c r="X54" s="21"/>
-      <c r="Y54" s="21"/>
-      <c r="Z54" s="21"/>
-      <c r="AA54" s="21"/>
-      <c r="AB54" s="21"/>
+      <c r="X54" s="27"/>
+      <c r="Y54" s="27"/>
+      <c r="Z54" s="27"/>
+      <c r="AA54" s="27"/>
+      <c r="AB54" s="27"/>
     </row>
     <row r="55" s="4" customFormat="1" spans="2:28">
       <c r="B55" s="4">
@@ -5565,14 +5724,15 @@
       <c r="S55" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="T55" s="26"/>
       <c r="V55" s="4">
         <v>1</v>
       </c>
-      <c r="X55" s="21"/>
-      <c r="Y55" s="21"/>
-      <c r="Z55" s="21"/>
-      <c r="AA55" s="21"/>
-      <c r="AB55" s="21"/>
+      <c r="X55" s="27"/>
+      <c r="Y55" s="27"/>
+      <c r="Z55" s="27"/>
+      <c r="AA55" s="27"/>
+      <c r="AB55" s="27"/>
     </row>
     <row r="56" s="4" customFormat="1" spans="2:28">
       <c r="B56" s="4">
@@ -5614,14 +5774,15 @@
       <c r="S56" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="T56" s="26"/>
       <c r="V56" s="4">
         <v>1</v>
       </c>
-      <c r="X56" s="21"/>
-      <c r="Y56" s="21"/>
-      <c r="Z56" s="21"/>
-      <c r="AA56" s="21"/>
-      <c r="AB56" s="21"/>
+      <c r="X56" s="27"/>
+      <c r="Y56" s="27"/>
+      <c r="Z56" s="27"/>
+      <c r="AA56" s="27"/>
+      <c r="AB56" s="27"/>
     </row>
     <row r="57" s="4" customFormat="1" spans="2:28">
       <c r="B57" s="4">
@@ -5663,14 +5824,15 @@
       <c r="S57" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="T57" s="26"/>
       <c r="V57" s="4">
         <v>1</v>
       </c>
-      <c r="X57" s="21"/>
-      <c r="Y57" s="21"/>
-      <c r="Z57" s="21"/>
-      <c r="AA57" s="21"/>
-      <c r="AB57" s="21"/>
+      <c r="X57" s="27"/>
+      <c r="Y57" s="27"/>
+      <c r="Z57" s="27"/>
+      <c r="AA57" s="27"/>
+      <c r="AB57" s="27"/>
     </row>
     <row r="58" s="4" customFormat="1" spans="2:28">
       <c r="B58" s="4">
@@ -5712,14 +5874,15 @@
       <c r="S58" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="T58" s="26"/>
       <c r="V58" s="4">
         <v>1</v>
       </c>
-      <c r="X58" s="21"/>
-      <c r="Y58" s="21"/>
-      <c r="Z58" s="21"/>
-      <c r="AA58" s="21"/>
-      <c r="AB58" s="21"/>
+      <c r="X58" s="27"/>
+      <c r="Y58" s="27"/>
+      <c r="Z58" s="27"/>
+      <c r="AA58" s="27"/>
+      <c r="AB58" s="27"/>
     </row>
     <row r="59" s="4" customFormat="1" spans="2:28">
       <c r="B59" s="4">
@@ -5761,14 +5924,15 @@
       <c r="S59" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="T59" s="26"/>
       <c r="V59" s="4">
         <v>1</v>
       </c>
-      <c r="X59" s="21"/>
-      <c r="Y59" s="21"/>
-      <c r="Z59" s="21"/>
-      <c r="AA59" s="21"/>
-      <c r="AB59" s="21"/>
+      <c r="X59" s="27"/>
+      <c r="Y59" s="27"/>
+      <c r="Z59" s="27"/>
+      <c r="AA59" s="27"/>
+      <c r="AB59" s="27"/>
     </row>
     <row r="60" s="4" customFormat="1" spans="2:28">
       <c r="B60" s="4">
@@ -5810,14 +5974,15 @@
       <c r="S60" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="T60" s="26"/>
       <c r="V60" s="4">
         <v>1</v>
       </c>
-      <c r="X60" s="21"/>
-      <c r="Y60" s="21"/>
-      <c r="Z60" s="21"/>
-      <c r="AA60" s="21"/>
-      <c r="AB60" s="21"/>
+      <c r="X60" s="27"/>
+      <c r="Y60" s="27"/>
+      <c r="Z60" s="27"/>
+      <c r="AA60" s="27"/>
+      <c r="AB60" s="27"/>
     </row>
     <row r="61" s="4" customFormat="1" spans="2:28">
       <c r="B61" s="4">
@@ -5859,14 +6024,15 @@
       <c r="S61" s="4" t="s">
         <v>138</v>
       </c>
+      <c r="T61" s="26"/>
       <c r="V61" s="4">
         <v>1</v>
       </c>
-      <c r="X61" s="21"/>
-      <c r="Y61" s="21"/>
-      <c r="Z61" s="21"/>
-      <c r="AA61" s="21"/>
-      <c r="AB61" s="21"/>
+      <c r="X61" s="27"/>
+      <c r="Y61" s="27"/>
+      <c r="Z61" s="27"/>
+      <c r="AA61" s="27"/>
+      <c r="AB61" s="27"/>
     </row>
     <row r="62" s="4" customFormat="1" spans="2:28">
       <c r="B62" s="4">
@@ -5878,10 +6044,10 @@
       <c r="E62" s="4">
         <v>4</v>
       </c>
-      <c r="F62" s="16" t="s">
+      <c r="F62" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="G62" s="16"/>
+      <c r="G62" s="17"/>
       <c r="H62" s="4">
         <v>0.5</v>
       </c>
@@ -5909,14 +6075,15 @@
       <c r="S62" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="T62" s="26"/>
       <c r="V62" s="4">
         <v>1</v>
       </c>
-      <c r="X62" s="21"/>
-      <c r="Y62" s="21"/>
-      <c r="Z62" s="21"/>
-      <c r="AA62" s="21"/>
-      <c r="AB62" s="21"/>
+      <c r="X62" s="27"/>
+      <c r="Y62" s="27"/>
+      <c r="Z62" s="27"/>
+      <c r="AA62" s="27"/>
+      <c r="AB62" s="27"/>
     </row>
     <row r="63" s="4" customFormat="1" spans="2:28">
       <c r="B63" s="4">
@@ -5928,10 +6095,10 @@
       <c r="E63" s="4">
         <v>4</v>
       </c>
-      <c r="F63" s="16" t="s">
+      <c r="F63" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="G63" s="16"/>
+      <c r="G63" s="17"/>
       <c r="H63" s="4">
         <v>0.5</v>
       </c>
@@ -5959,14 +6126,15 @@
       <c r="S63" s="4" t="s">
         <v>169</v>
       </c>
+      <c r="T63" s="26"/>
       <c r="V63" s="4">
         <v>1</v>
       </c>
-      <c r="X63" s="21"/>
-      <c r="Y63" s="21"/>
-      <c r="Z63" s="21"/>
-      <c r="AA63" s="21"/>
-      <c r="AB63" s="21"/>
+      <c r="X63" s="27"/>
+      <c r="Y63" s="27"/>
+      <c r="Z63" s="27"/>
+      <c r="AA63" s="27"/>
+      <c r="AB63" s="27"/>
     </row>
     <row r="64" s="4" customFormat="1" spans="2:28">
       <c r="B64" s="4">
@@ -6008,14 +6176,15 @@
       <c r="S64" s="4" t="s">
         <v>132</v>
       </c>
+      <c r="T64" s="26"/>
       <c r="V64" s="4">
         <v>1</v>
       </c>
-      <c r="X64" s="21"/>
-      <c r="Y64" s="21"/>
-      <c r="Z64" s="21"/>
-      <c r="AA64" s="21"/>
-      <c r="AB64" s="21"/>
+      <c r="X64" s="27"/>
+      <c r="Y64" s="27"/>
+      <c r="Z64" s="27"/>
+      <c r="AA64" s="27"/>
+      <c r="AB64" s="27"/>
     </row>
     <row r="65" s="3" customFormat="1" spans="2:23">
       <c r="B65" s="3">
@@ -6027,10 +6196,10 @@
       <c r="E65" s="3">
         <v>5</v>
       </c>
-      <c r="F65" s="22" t="s">
+      <c r="F65" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="G65" s="22"/>
+      <c r="G65" s="28"/>
       <c r="H65" s="3">
         <v>1</v>
       </c>
@@ -6058,6 +6227,7 @@
       <c r="S65" s="3" t="s">
         <v>232</v>
       </c>
+      <c r="T65" s="24"/>
       <c r="U65" s="3" t="s">
         <v>134</v>
       </c>
@@ -6108,37 +6278,38 @@
       <c r="S66" s="3" t="s">
         <v>132</v>
       </c>
+      <c r="T66" s="24"/>
       <c r="V66" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="67" s="3" customFormat="1" spans="1:28">
-      <c r="A67" s="23"/>
+      <c r="A67" s="29"/>
       <c r="B67" s="3">
         <v>5003</v>
       </c>
-      <c r="C67" s="20" t="s">
+      <c r="C67" s="25" t="s">
         <v>235</v>
       </c>
-      <c r="D67" s="23"/>
+      <c r="D67" s="29"/>
       <c r="E67" s="3">
         <v>5</v>
       </c>
-      <c r="F67" s="23" t="s">
+      <c r="F67" s="29" t="s">
         <v>236</v>
       </c>
-      <c r="G67" s="23"/>
-      <c r="H67" s="23">
-        <v>1</v>
-      </c>
-      <c r="I67" s="27"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29">
+        <v>1</v>
+      </c>
+      <c r="I67" s="33"/>
       <c r="J67" s="3">
         <v>0</v>
       </c>
       <c r="K67" s="3">
         <v>0</v>
       </c>
-      <c r="L67" s="23">
+      <c r="L67" s="29">
         <v>0</v>
       </c>
       <c r="M67" s="3">
@@ -6153,48 +6324,48 @@
       <c r="P67" s="3">
         <v>1</v>
       </c>
-      <c r="Q67" s="23"/>
-      <c r="R67" s="23"/>
-      <c r="S67" s="23"/>
-      <c r="T67" s="23"/>
-      <c r="U67" s="23"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="29"/>
+      <c r="S67" s="29"/>
+      <c r="T67" s="35"/>
+      <c r="U67" s="29"/>
       <c r="V67" s="3">
         <v>0</v>
       </c>
-      <c r="W67" s="23"/>
-      <c r="X67" s="20"/>
-      <c r="Y67" s="20"/>
-      <c r="Z67" s="20"/>
-      <c r="AA67" s="20"/>
-      <c r="AB67" s="20"/>
+      <c r="W67" s="29"/>
+      <c r="X67" s="25"/>
+      <c r="Y67" s="25"/>
+      <c r="Z67" s="25"/>
+      <c r="AA67" s="25"/>
+      <c r="AB67" s="25"/>
     </row>
     <row r="68" s="3" customFormat="1" spans="1:28">
-      <c r="A68" s="23"/>
+      <c r="A68" s="29"/>
       <c r="B68" s="3">
         <v>5004</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="D68" s="23"/>
+      <c r="D68" s="29"/>
       <c r="E68" s="3">
         <v>5</v>
       </c>
-      <c r="F68" s="23" t="s">
+      <c r="F68" s="29" t="s">
         <v>238</v>
       </c>
-      <c r="G68" s="23"/>
-      <c r="H68" s="23">
-        <v>1</v>
-      </c>
-      <c r="I68" s="27"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29">
+        <v>1</v>
+      </c>
+      <c r="I68" s="33"/>
       <c r="J68" s="3">
         <v>0</v>
       </c>
       <c r="K68" s="3">
         <v>1</v>
       </c>
-      <c r="L68" s="23">
+      <c r="L68" s="29">
         <v>0</v>
       </c>
       <c r="M68" s="3">
@@ -6209,48 +6380,48 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="23"/>
-      <c r="R68" s="23"/>
-      <c r="S68" s="23"/>
-      <c r="T68" s="23"/>
-      <c r="U68" s="23"/>
+      <c r="Q68" s="29"/>
+      <c r="R68" s="29"/>
+      <c r="S68" s="29"/>
+      <c r="T68" s="35"/>
+      <c r="U68" s="29"/>
       <c r="V68" s="3">
         <v>0</v>
       </c>
-      <c r="W68" s="23"/>
-      <c r="X68" s="20"/>
-      <c r="Y68" s="20"/>
-      <c r="Z68" s="20"/>
-      <c r="AA68" s="20"/>
-      <c r="AB68" s="20"/>
+      <c r="W68" s="29"/>
+      <c r="X68" s="25"/>
+      <c r="Y68" s="25"/>
+      <c r="Z68" s="25"/>
+      <c r="AA68" s="25"/>
+      <c r="AB68" s="25"/>
     </row>
     <row r="69" s="5" customFormat="1" spans="1:28">
-      <c r="A69" s="24"/>
+      <c r="A69" s="30"/>
       <c r="B69" s="5">
         <v>5005</v>
       </c>
-      <c r="C69" s="25" t="s">
+      <c r="C69" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="D69" s="24"/>
+      <c r="D69" s="30"/>
       <c r="E69" s="5">
         <v>5</v>
       </c>
-      <c r="F69" s="24" t="s">
+      <c r="F69" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24">
-        <v>1</v>
-      </c>
-      <c r="I69" s="28"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30">
+        <v>1</v>
+      </c>
+      <c r="I69" s="34"/>
       <c r="J69" s="5">
         <v>0</v>
       </c>
       <c r="K69" s="5">
         <v>0</v>
       </c>
-      <c r="L69" s="24">
+      <c r="L69" s="30">
         <v>1</v>
       </c>
       <c r="M69" s="5">
@@ -6265,48 +6436,48 @@
       <c r="P69" s="5">
         <v>1</v>
       </c>
-      <c r="Q69" s="24"/>
-      <c r="R69" s="24"/>
-      <c r="S69" s="24"/>
-      <c r="T69" s="24"/>
-      <c r="U69" s="24"/>
+      <c r="Q69" s="30"/>
+      <c r="R69" s="30"/>
+      <c r="S69" s="30"/>
+      <c r="T69" s="36"/>
+      <c r="U69" s="30"/>
       <c r="V69" s="5">
         <v>0</v>
       </c>
-      <c r="W69" s="24"/>
-      <c r="X69" s="25"/>
-      <c r="Y69" s="25"/>
-      <c r="Z69" s="25"/>
-      <c r="AA69" s="25"/>
-      <c r="AB69" s="25"/>
+      <c r="W69" s="30"/>
+      <c r="X69" s="31"/>
+      <c r="Y69" s="31"/>
+      <c r="Z69" s="31"/>
+      <c r="AA69" s="31"/>
+      <c r="AB69" s="31"/>
     </row>
     <row r="70" s="3" customFormat="1" spans="1:28">
-      <c r="A70" s="23"/>
+      <c r="A70" s="29"/>
       <c r="B70" s="3">
         <v>5006</v>
       </c>
-      <c r="C70" s="20" t="s">
+      <c r="C70" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="D70" s="23"/>
+      <c r="D70" s="29"/>
       <c r="E70" s="3">
         <v>5</v>
       </c>
-      <c r="F70" s="23" t="s">
+      <c r="F70" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="G70" s="23"/>
-      <c r="H70" s="23">
-        <v>1</v>
-      </c>
-      <c r="I70" s="27"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29">
+        <v>1</v>
+      </c>
+      <c r="I70" s="33"/>
       <c r="J70" s="3">
         <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="23">
+      <c r="L70" s="29">
         <v>1</v>
       </c>
       <c r="M70" s="3">
@@ -6321,48 +6492,48 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="23"/>
-      <c r="R70" s="23"/>
-      <c r="S70" s="23"/>
-      <c r="T70" s="23"/>
-      <c r="U70" s="23"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="29"/>
+      <c r="S70" s="29"/>
+      <c r="T70" s="35"/>
+      <c r="U70" s="29"/>
       <c r="V70" s="3">
         <v>0</v>
       </c>
-      <c r="W70" s="23"/>
-      <c r="X70" s="20"/>
-      <c r="Y70" s="20"/>
-      <c r="Z70" s="20"/>
-      <c r="AA70" s="20"/>
-      <c r="AB70" s="20"/>
+      <c r="W70" s="29"/>
+      <c r="X70" s="25"/>
+      <c r="Y70" s="25"/>
+      <c r="Z70" s="25"/>
+      <c r="AA70" s="25"/>
+      <c r="AB70" s="25"/>
     </row>
     <row r="71" s="3" customFormat="1" spans="1:28">
-      <c r="A71" s="23"/>
+      <c r="A71" s="29"/>
       <c r="B71" s="3">
         <v>5007</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C71" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="D71" s="23"/>
+      <c r="D71" s="29"/>
       <c r="E71" s="3">
         <v>5</v>
       </c>
-      <c r="F71" s="23" t="s">
+      <c r="F71" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="G71" s="23"/>
-      <c r="H71" s="23">
-        <v>1</v>
-      </c>
-      <c r="I71" s="27"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29">
+        <v>1</v>
+      </c>
+      <c r="I71" s="33"/>
       <c r="J71" s="3">
         <v>0</v>
       </c>
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="23">
+      <c r="L71" s="29">
         <v>0</v>
       </c>
       <c r="M71" s="3">
@@ -6377,48 +6548,48 @@
       <c r="P71" s="3">
         <v>1</v>
       </c>
-      <c r="Q71" s="23"/>
-      <c r="R71" s="23"/>
-      <c r="S71" s="23"/>
-      <c r="T71" s="23"/>
-      <c r="U71" s="23"/>
+      <c r="Q71" s="29"/>
+      <c r="R71" s="29"/>
+      <c r="S71" s="29"/>
+      <c r="T71" s="35"/>
+      <c r="U71" s="29"/>
       <c r="V71" s="3">
         <v>0</v>
       </c>
-      <c r="W71" s="23"/>
-      <c r="X71" s="20"/>
-      <c r="Y71" s="20"/>
-      <c r="Z71" s="20"/>
-      <c r="AA71" s="20"/>
-      <c r="AB71" s="20"/>
+      <c r="W71" s="29"/>
+      <c r="X71" s="25"/>
+      <c r="Y71" s="25"/>
+      <c r="Z71" s="25"/>
+      <c r="AA71" s="25"/>
+      <c r="AB71" s="25"/>
     </row>
     <row r="72" s="3" customFormat="1" spans="1:28">
-      <c r="A72" s="23"/>
+      <c r="A72" s="29"/>
       <c r="B72" s="3">
         <v>5008</v>
       </c>
-      <c r="C72" s="20" t="s">
+      <c r="C72" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="D72" s="23"/>
+      <c r="D72" s="29"/>
       <c r="E72" s="3">
         <v>5</v>
       </c>
-      <c r="F72" s="23" t="s">
+      <c r="F72" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23">
-        <v>1</v>
-      </c>
-      <c r="I72" s="27"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29">
+        <v>1</v>
+      </c>
+      <c r="I72" s="33"/>
       <c r="J72" s="3">
         <v>0</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
       </c>
-      <c r="L72" s="23">
+      <c r="L72" s="29">
         <v>0</v>
       </c>
       <c r="M72" s="3">
@@ -6433,23 +6604,23 @@
       <c r="P72" s="3">
         <v>1</v>
       </c>
-      <c r="Q72" s="23"/>
-      <c r="R72" s="23"/>
-      <c r="S72" s="23"/>
-      <c r="T72" s="23"/>
-      <c r="U72" s="23"/>
+      <c r="Q72" s="29"/>
+      <c r="R72" s="29"/>
+      <c r="S72" s="29"/>
+      <c r="T72" s="35"/>
+      <c r="U72" s="29"/>
       <c r="V72" s="3">
         <v>0</v>
       </c>
-      <c r="W72" s="23"/>
-      <c r="X72" s="20"/>
-      <c r="Y72" s="20"/>
-      <c r="Z72" s="20"/>
-      <c r="AA72" s="20"/>
-      <c r="AB72" s="20"/>
+      <c r="W72" s="29"/>
+      <c r="X72" s="25"/>
+      <c r="Y72" s="25"/>
+      <c r="Z72" s="25"/>
+      <c r="AA72" s="25"/>
+      <c r="AB72" s="25"/>
     </row>
     <row r="73" s="5" customFormat="1" spans="2:22">
-      <c r="B73" s="26">
+      <c r="B73" s="32">
         <v>5009</v>
       </c>
       <c r="C73" s="5" t="s">
@@ -6458,14 +6629,14 @@
       <c r="E73" s="5">
         <v>5</v>
       </c>
-      <c r="F73" s="26" t="s">
+      <c r="F73" s="32" t="s">
         <v>248</v>
       </c>
-      <c r="G73" s="26"/>
-      <c r="H73" s="24">
-        <v>1</v>
-      </c>
-      <c r="I73" s="28"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="30">
+        <v>1</v>
+      </c>
+      <c r="I73" s="34"/>
       <c r="J73" s="5">
         <v>0</v>
       </c>
@@ -6490,28 +6661,31 @@
       <c r="S73" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T73" s="37" t="s">
+        <v>249</v>
+      </c>
       <c r="V73" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="74" s="5" customFormat="1" spans="2:22">
-      <c r="B74" s="26">
+      <c r="B74" s="32">
         <v>5010</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E74" s="5">
         <v>5</v>
       </c>
-      <c r="F74" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="G74" s="26"/>
-      <c r="H74" s="24">
-        <v>1</v>
-      </c>
-      <c r="I74" s="28"/>
+      <c r="F74" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="G74" s="32"/>
+      <c r="H74" s="30">
+        <v>1</v>
+      </c>
+      <c r="I74" s="34"/>
       <c r="J74" s="5">
         <v>0</v>
       </c>
@@ -6536,28 +6710,31 @@
       <c r="S74" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T74" s="37" t="s">
+        <v>252</v>
+      </c>
       <c r="V74" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="75" s="5" customFormat="1" spans="2:22">
-      <c r="B75" s="26">
+      <c r="B75" s="32">
         <v>5011</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E75" s="5">
         <v>5</v>
       </c>
-      <c r="F75" s="26" t="s">
-        <v>252</v>
-      </c>
-      <c r="G75" s="26"/>
-      <c r="H75" s="24">
-        <v>1</v>
-      </c>
-      <c r="I75" s="28"/>
+      <c r="F75" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="G75" s="32"/>
+      <c r="H75" s="30">
+        <v>1</v>
+      </c>
+      <c r="I75" s="34"/>
       <c r="J75" s="5">
         <v>0</v>
       </c>
@@ -6582,28 +6759,31 @@
       <c r="S75" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T75" s="37" t="s">
+        <v>255</v>
+      </c>
       <c r="V75" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="76" s="5" customFormat="1" spans="2:22">
-      <c r="B76" s="26">
+      <c r="B76" s="32">
         <v>5012</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E76" s="5">
         <v>5</v>
       </c>
-      <c r="F76" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="G76" s="26"/>
-      <c r="H76" s="24">
-        <v>1</v>
-      </c>
-      <c r="I76" s="28"/>
+      <c r="F76" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="G76" s="32"/>
+      <c r="H76" s="30">
+        <v>1</v>
+      </c>
+      <c r="I76" s="34"/>
       <c r="J76" s="5">
         <v>0</v>
       </c>
@@ -6628,28 +6808,31 @@
       <c r="S76" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T76" s="37">
+        <v>1013</v>
+      </c>
       <c r="V76" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="77" s="5" customFormat="1" spans="2:22">
-      <c r="B77" s="26">
+      <c r="B77" s="32">
         <v>5013</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E77" s="5">
         <v>5</v>
       </c>
-      <c r="F77" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="G77" s="26"/>
-      <c r="H77" s="24">
-        <v>1</v>
-      </c>
-      <c r="I77" s="28"/>
+      <c r="F77" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="G77" s="32"/>
+      <c r="H77" s="30">
+        <v>1</v>
+      </c>
+      <c r="I77" s="34"/>
       <c r="J77" s="5">
         <v>0</v>
       </c>
@@ -6674,28 +6857,31 @@
       <c r="S77" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T77" s="37">
+        <v>1013</v>
+      </c>
       <c r="V77" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="78" s="5" customFormat="1" spans="2:22">
-      <c r="B78" s="26">
+      <c r="B78" s="32">
         <v>5014</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E78" s="5">
         <v>5</v>
       </c>
-      <c r="F78" s="26" t="s">
-        <v>258</v>
-      </c>
-      <c r="G78" s="26"/>
-      <c r="H78" s="24">
-        <v>1</v>
-      </c>
-      <c r="I78" s="28"/>
+      <c r="F78" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="G78" s="32"/>
+      <c r="H78" s="30">
+        <v>1</v>
+      </c>
+      <c r="I78" s="34"/>
       <c r="J78" s="5">
         <v>0</v>
       </c>
@@ -6720,28 +6906,31 @@
       <c r="S78" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T78" s="37">
+        <v>1014</v>
+      </c>
       <c r="V78" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="79" s="5" customFormat="1" spans="2:22">
-      <c r="B79" s="26">
+      <c r="B79" s="32">
         <v>5015</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E79" s="5">
         <v>5</v>
       </c>
-      <c r="F79" s="26" t="s">
-        <v>260</v>
-      </c>
-      <c r="G79" s="26"/>
-      <c r="H79" s="24">
-        <v>1</v>
-      </c>
-      <c r="I79" s="28"/>
+      <c r="F79" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="G79" s="32"/>
+      <c r="H79" s="30">
+        <v>1</v>
+      </c>
+      <c r="I79" s="34"/>
       <c r="J79" s="5">
         <v>0</v>
       </c>
@@ -6766,28 +6955,31 @@
       <c r="S79" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T79" s="37">
+        <v>1009</v>
+      </c>
       <c r="V79" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="80" s="5" customFormat="1" spans="2:22">
-      <c r="B80" s="26">
+      <c r="B80" s="32">
         <v>5016</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E80" s="5">
         <v>5</v>
       </c>
-      <c r="F80" s="26" t="s">
-        <v>262</v>
-      </c>
-      <c r="G80" s="26"/>
-      <c r="H80" s="24">
-        <v>1</v>
-      </c>
-      <c r="I80" s="28"/>
+      <c r="F80" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="G80" s="32"/>
+      <c r="H80" s="30">
+        <v>1</v>
+      </c>
+      <c r="I80" s="34"/>
       <c r="J80" s="5">
         <v>0</v>
       </c>
@@ -6812,28 +7004,31 @@
       <c r="S80" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T80" s="37">
+        <v>1015</v>
+      </c>
       <c r="V80" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="81" s="5" customFormat="1" spans="2:22">
-      <c r="B81" s="26">
+      <c r="B81" s="32">
         <v>5017</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E81" s="5">
         <v>5</v>
       </c>
-      <c r="F81" s="26" t="s">
-        <v>264</v>
-      </c>
-      <c r="G81" s="26"/>
-      <c r="H81" s="24">
-        <v>1</v>
-      </c>
-      <c r="I81" s="28"/>
+      <c r="F81" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="G81" s="32"/>
+      <c r="H81" s="30">
+        <v>1</v>
+      </c>
+      <c r="I81" s="34"/>
       <c r="J81" s="5">
         <v>0</v>
       </c>
@@ -6858,28 +7053,31 @@
       <c r="S81" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T81" s="37" t="s">
+        <v>268</v>
+      </c>
       <c r="V81" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="82" s="5" customFormat="1" spans="2:22">
-      <c r="B82" s="26">
+      <c r="B82" s="32">
         <v>5018</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E82" s="5">
         <v>5</v>
       </c>
-      <c r="F82" s="26" t="s">
-        <v>266</v>
-      </c>
-      <c r="G82" s="26"/>
-      <c r="H82" s="24">
-        <v>1</v>
-      </c>
-      <c r="I82" s="28"/>
+      <c r="F82" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="G82" s="32"/>
+      <c r="H82" s="30">
+        <v>1</v>
+      </c>
+      <c r="I82" s="34"/>
       <c r="J82" s="5">
         <v>0</v>
       </c>
@@ -6904,28 +7102,31 @@
       <c r="S82" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T82" s="37" t="s">
+        <v>271</v>
+      </c>
       <c r="V82" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="83" s="5" customFormat="1" spans="2:22">
-      <c r="B83" s="26">
+      <c r="B83" s="32">
         <v>5019</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E83" s="5">
         <v>5</v>
       </c>
-      <c r="F83" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="G83" s="26"/>
-      <c r="H83" s="24">
-        <v>1</v>
-      </c>
-      <c r="I83" s="28"/>
+      <c r="F83" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="G83" s="32"/>
+      <c r="H83" s="30">
+        <v>1</v>
+      </c>
+      <c r="I83" s="34"/>
       <c r="J83" s="5">
         <v>0</v>
       </c>
@@ -6950,28 +7151,31 @@
       <c r="S83" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T83" s="37" t="s">
+        <v>274</v>
+      </c>
       <c r="V83" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="84" s="5" customFormat="1" spans="2:22">
-      <c r="B84" s="26">
+      <c r="B84" s="32">
         <v>5020</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E84" s="5">
         <v>5</v>
       </c>
-      <c r="F84" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="G84" s="26"/>
-      <c r="H84" s="24">
-        <v>1</v>
-      </c>
-      <c r="I84" s="28"/>
+      <c r="F84" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="G84" s="32"/>
+      <c r="H84" s="30">
+        <v>1</v>
+      </c>
+      <c r="I84" s="34"/>
       <c r="J84" s="5">
         <v>0</v>
       </c>
@@ -6996,28 +7200,31 @@
       <c r="S84" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T84" s="37" t="s">
+        <v>274</v>
+      </c>
       <c r="V84" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="85" s="5" customFormat="1" spans="2:22">
-      <c r="B85" s="26">
+      <c r="B85" s="32">
         <v>5021</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E85" s="5">
         <v>5</v>
       </c>
-      <c r="F85" s="26" t="s">
-        <v>272</v>
-      </c>
-      <c r="G85" s="26"/>
-      <c r="H85" s="24">
-        <v>1</v>
-      </c>
-      <c r="I85" s="28"/>
+      <c r="F85" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="G85" s="32"/>
+      <c r="H85" s="30">
+        <v>1</v>
+      </c>
+      <c r="I85" s="34"/>
       <c r="J85" s="5">
         <v>0</v>
       </c>
@@ -7042,28 +7249,31 @@
       <c r="S85" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T85" s="37" t="s">
+        <v>279</v>
+      </c>
       <c r="V85" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="86" s="5" customFormat="1" spans="2:22">
-      <c r="B86" s="26">
+      <c r="B86" s="32">
         <v>5022</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="E86" s="5">
         <v>5</v>
       </c>
-      <c r="F86" s="26" t="s">
-        <v>274</v>
-      </c>
-      <c r="G86" s="26"/>
-      <c r="H86" s="24">
-        <v>1</v>
-      </c>
-      <c r="I86" s="28"/>
+      <c r="F86" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="G86" s="32"/>
+      <c r="H86" s="30">
+        <v>1</v>
+      </c>
+      <c r="I86" s="34"/>
       <c r="J86" s="5">
         <v>0</v>
       </c>
@@ -7088,28 +7298,31 @@
       <c r="S86" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T86" s="37" t="s">
+        <v>282</v>
+      </c>
       <c r="V86" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="87" s="5" customFormat="1" spans="2:22">
-      <c r="B87" s="26">
+      <c r="B87" s="32">
         <v>5023</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="E87" s="5">
         <v>5</v>
       </c>
-      <c r="F87" s="26" t="s">
-        <v>276</v>
-      </c>
-      <c r="G87" s="26"/>
-      <c r="H87" s="24">
-        <v>1</v>
-      </c>
-      <c r="I87" s="28"/>
+      <c r="F87" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="G87" s="32"/>
+      <c r="H87" s="30">
+        <v>1</v>
+      </c>
+      <c r="I87" s="34"/>
       <c r="J87" s="5">
         <v>0</v>
       </c>
@@ -7134,28 +7347,31 @@
       <c r="S87" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T87" s="37" t="s">
+        <v>285</v>
+      </c>
       <c r="V87" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="88" s="5" customFormat="1" spans="2:22">
-      <c r="B88" s="26">
+      <c r="B88" s="32">
         <v>5024</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="E88" s="5">
         <v>5</v>
       </c>
-      <c r="F88" s="26" t="s">
-        <v>278</v>
-      </c>
-      <c r="G88" s="26"/>
-      <c r="H88" s="24">
-        <v>1</v>
-      </c>
-      <c r="I88" s="28"/>
+      <c r="F88" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="G88" s="32"/>
+      <c r="H88" s="30">
+        <v>1</v>
+      </c>
+      <c r="I88" s="34"/>
       <c r="J88" s="5">
         <v>0</v>
       </c>
@@ -7180,28 +7396,31 @@
       <c r="S88" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T88" s="37" t="s">
+        <v>288</v>
+      </c>
       <c r="V88" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="89" s="5" customFormat="1" spans="2:22">
-      <c r="B89" s="26">
+      <c r="B89" s="32">
         <v>5025</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="E89" s="5">
         <v>5</v>
       </c>
-      <c r="F89" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="G89" s="26"/>
-      <c r="H89" s="24">
-        <v>1</v>
-      </c>
-      <c r="I89" s="28"/>
+      <c r="F89" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="G89" s="32"/>
+      <c r="H89" s="30">
+        <v>1</v>
+      </c>
+      <c r="I89" s="34"/>
       <c r="J89" s="5">
         <v>0</v>
       </c>
@@ -7226,28 +7445,31 @@
       <c r="S89" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T89" s="37" t="s">
+        <v>291</v>
+      </c>
       <c r="V89" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="90" s="5" customFormat="1" spans="2:22">
-      <c r="B90" s="26">
+      <c r="B90" s="32">
         <v>5026</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="E90" s="5">
         <v>5</v>
       </c>
-      <c r="F90" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="G90" s="26"/>
-      <c r="H90" s="24">
-        <v>1</v>
-      </c>
-      <c r="I90" s="28"/>
+      <c r="F90" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="G90" s="32"/>
+      <c r="H90" s="30">
+        <v>1</v>
+      </c>
+      <c r="I90" s="34"/>
       <c r="J90" s="5">
         <v>0</v>
       </c>
@@ -7272,28 +7494,31 @@
       <c r="S90" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T90" s="37" t="s">
+        <v>291</v>
+      </c>
       <c r="V90" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="91" s="5" customFormat="1" spans="2:22">
-      <c r="B91" s="26">
+      <c r="B91" s="32">
         <v>5027</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="E91" s="5">
         <v>5</v>
       </c>
-      <c r="F91" s="26" t="s">
-        <v>284</v>
-      </c>
-      <c r="G91" s="26"/>
-      <c r="H91" s="24">
-        <v>1</v>
-      </c>
-      <c r="I91" s="28"/>
+      <c r="F91" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="G91" s="32"/>
+      <c r="H91" s="30">
+        <v>1</v>
+      </c>
+      <c r="I91" s="34"/>
       <c r="J91" s="5">
         <v>0</v>
       </c>
@@ -7318,28 +7543,31 @@
       <c r="S91" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T91" s="37" t="s">
+        <v>296</v>
+      </c>
       <c r="V91" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="92" s="5" customFormat="1" spans="2:22">
-      <c r="B92" s="26">
+      <c r="B92" s="32">
         <v>5028</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="E92" s="5">
         <v>5</v>
       </c>
-      <c r="F92" s="26" t="s">
-        <v>286</v>
-      </c>
-      <c r="G92" s="26"/>
-      <c r="H92" s="24">
-        <v>1</v>
-      </c>
-      <c r="I92" s="28"/>
+      <c r="F92" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="G92" s="32"/>
+      <c r="H92" s="30">
+        <v>1</v>
+      </c>
+      <c r="I92" s="34"/>
       <c r="J92" s="5">
         <v>0</v>
       </c>
@@ -7364,28 +7592,31 @@
       <c r="S92" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T92" s="37" t="s">
+        <v>299</v>
+      </c>
       <c r="V92" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="93" s="5" customFormat="1" spans="2:22">
-      <c r="B93" s="26">
+      <c r="B93" s="32">
         <v>5029</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="E93" s="5">
         <v>5</v>
       </c>
-      <c r="F93" s="26" t="s">
-        <v>288</v>
-      </c>
-      <c r="G93" s="26"/>
-      <c r="H93" s="24">
-        <v>1</v>
-      </c>
-      <c r="I93" s="28"/>
+      <c r="F93" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="G93" s="32"/>
+      <c r="H93" s="30">
+        <v>1</v>
+      </c>
+      <c r="I93" s="34"/>
       <c r="J93" s="5">
         <v>0</v>
       </c>
@@ -7410,28 +7641,31 @@
       <c r="S93" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T93" s="37" t="s">
+        <v>302</v>
+      </c>
       <c r="V93" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="94" s="5" customFormat="1" spans="2:22">
-      <c r="B94" s="26">
+      <c r="B94" s="32">
         <v>5030</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="E94" s="5">
         <v>5</v>
       </c>
-      <c r="F94" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="G94" s="26"/>
-      <c r="H94" s="24">
-        <v>1</v>
-      </c>
-      <c r="I94" s="28"/>
+      <c r="F94" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="G94" s="32"/>
+      <c r="H94" s="30">
+        <v>1</v>
+      </c>
+      <c r="I94" s="34"/>
       <c r="J94" s="5">
         <v>0</v>
       </c>
@@ -7456,28 +7690,31 @@
       <c r="S94" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T94" s="37" t="s">
+        <v>305</v>
+      </c>
       <c r="V94" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="95" s="5" customFormat="1" spans="2:22">
-      <c r="B95" s="26">
+      <c r="B95" s="32">
         <v>5031</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="E95" s="5">
         <v>5</v>
       </c>
-      <c r="F95" s="26" t="s">
-        <v>292</v>
-      </c>
-      <c r="G95" s="26"/>
-      <c r="H95" s="24">
-        <v>1</v>
-      </c>
-      <c r="I95" s="28"/>
+      <c r="F95" s="32" t="s">
+        <v>307</v>
+      </c>
+      <c r="G95" s="32"/>
+      <c r="H95" s="30">
+        <v>1</v>
+      </c>
+      <c r="I95" s="34"/>
       <c r="J95" s="5">
         <v>0</v>
       </c>
@@ -7502,28 +7739,31 @@
       <c r="S95" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T95" s="37" t="s">
+        <v>305</v>
+      </c>
       <c r="V95" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="96" s="5" customFormat="1" spans="2:22">
-      <c r="B96" s="26">
+      <c r="B96" s="32">
         <v>5032</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="E96" s="5">
         <v>5</v>
       </c>
-      <c r="F96" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="G96" s="26"/>
-      <c r="H96" s="24">
-        <v>1</v>
-      </c>
-      <c r="I96" s="28"/>
+      <c r="F96" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="G96" s="32"/>
+      <c r="H96" s="30">
+        <v>1</v>
+      </c>
+      <c r="I96" s="34"/>
       <c r="J96" s="5">
         <v>0</v>
       </c>
@@ -7548,28 +7788,31 @@
       <c r="S96" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T96" s="37" t="s">
+        <v>310</v>
+      </c>
       <c r="V96" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="97" s="5" customFormat="1" spans="2:22">
-      <c r="B97" s="26">
+      <c r="B97" s="32">
         <v>5033</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="E97" s="5">
         <v>5</v>
       </c>
-      <c r="F97" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="G97" s="26"/>
-      <c r="H97" s="24">
-        <v>1</v>
-      </c>
-      <c r="I97" s="28"/>
+      <c r="F97" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="G97" s="32"/>
+      <c r="H97" s="30">
+        <v>1</v>
+      </c>
+      <c r="I97" s="34"/>
       <c r="J97" s="5">
         <v>0</v>
       </c>
@@ -7594,28 +7837,31 @@
       <c r="S97" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T97" s="37" t="s">
+        <v>313</v>
+      </c>
       <c r="V97" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="98" s="5" customFormat="1" spans="2:22">
-      <c r="B98" s="26">
+      <c r="B98" s="32">
         <v>5034</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="E98" s="5">
         <v>5</v>
       </c>
-      <c r="F98" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G98" s="26"/>
-      <c r="H98" s="24">
-        <v>1</v>
-      </c>
-      <c r="I98" s="28"/>
+      <c r="F98" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="G98" s="32"/>
+      <c r="H98" s="30">
+        <v>1</v>
+      </c>
+      <c r="I98" s="34"/>
       <c r="J98" s="5">
         <v>0</v>
       </c>
@@ -7640,28 +7886,31 @@
       <c r="S98" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T98" s="37" t="s">
+        <v>316</v>
+      </c>
       <c r="V98" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="99" s="5" customFormat="1" spans="2:22">
-      <c r="B99" s="26">
+      <c r="B99" s="32">
         <v>5035</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E99" s="5">
         <v>5</v>
       </c>
-      <c r="F99" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="G99" s="26"/>
-      <c r="H99" s="24">
-        <v>1</v>
-      </c>
-      <c r="I99" s="28"/>
+      <c r="F99" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="G99" s="32"/>
+      <c r="H99" s="30">
+        <v>1</v>
+      </c>
+      <c r="I99" s="34"/>
       <c r="J99" s="5">
         <v>0</v>
       </c>
@@ -7686,28 +7935,31 @@
       <c r="S99" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T99" s="37" t="s">
+        <v>319</v>
+      </c>
       <c r="V99" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="100" s="5" customFormat="1" spans="2:22">
-      <c r="B100" s="26">
+      <c r="B100" s="32">
         <v>5036</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="E100" s="5">
         <v>5</v>
       </c>
-      <c r="F100" s="26" t="s">
-        <v>302</v>
-      </c>
-      <c r="G100" s="26"/>
-      <c r="H100" s="24">
-        <v>1</v>
-      </c>
-      <c r="I100" s="28"/>
+      <c r="F100" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="G100" s="32"/>
+      <c r="H100" s="30">
+        <v>1</v>
+      </c>
+      <c r="I100" s="34"/>
       <c r="J100" s="5">
         <v>0</v>
       </c>
@@ -7732,28 +7984,31 @@
       <c r="S100" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T100" s="37" t="s">
+        <v>322</v>
+      </c>
       <c r="V100" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="101" s="5" customFormat="1" spans="2:22">
-      <c r="B101" s="26">
+      <c r="B101" s="32">
         <v>5037</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="E101" s="5">
         <v>5</v>
       </c>
-      <c r="F101" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="G101" s="26"/>
-      <c r="H101" s="24">
-        <v>1</v>
-      </c>
-      <c r="I101" s="28"/>
+      <c r="F101" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="G101" s="32"/>
+      <c r="H101" s="30">
+        <v>1</v>
+      </c>
+      <c r="I101" s="34"/>
       <c r="J101" s="5">
         <v>0</v>
       </c>
@@ -7778,28 +8033,31 @@
       <c r="S101" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T101" s="37" t="s">
+        <v>325</v>
+      </c>
       <c r="V101" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="102" s="5" customFormat="1" spans="2:22">
-      <c r="B102" s="26">
+      <c r="B102" s="32">
         <v>5038</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="E102" s="5">
         <v>5</v>
       </c>
-      <c r="F102" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="G102" s="26"/>
-      <c r="H102" s="24">
-        <v>1</v>
-      </c>
-      <c r="I102" s="28"/>
+      <c r="F102" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="G102" s="32"/>
+      <c r="H102" s="30">
+        <v>1</v>
+      </c>
+      <c r="I102" s="34"/>
       <c r="J102" s="5">
         <v>0</v>
       </c>
@@ -7824,28 +8082,31 @@
       <c r="S102" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T102" s="37" t="s">
+        <v>328</v>
+      </c>
       <c r="V102" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="103" s="5" customFormat="1" spans="2:22">
-      <c r="B103" s="26">
+      <c r="B103" s="32">
         <v>5039</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="E103" s="5">
         <v>5</v>
       </c>
-      <c r="F103" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="G103" s="26"/>
-      <c r="H103" s="24">
-        <v>1</v>
-      </c>
-      <c r="I103" s="28"/>
+      <c r="F103" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="G103" s="32"/>
+      <c r="H103" s="30">
+        <v>1</v>
+      </c>
+      <c r="I103" s="34"/>
       <c r="J103" s="5">
         <v>0</v>
       </c>
@@ -7870,28 +8131,31 @@
       <c r="S103" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T103" s="37" t="s">
+        <v>322</v>
+      </c>
       <c r="V103" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="104" s="5" customFormat="1" spans="2:22">
-      <c r="B104" s="26">
+      <c r="B104" s="32">
         <v>5040</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="E104" s="5">
         <v>5</v>
       </c>
-      <c r="F104" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="G104" s="26"/>
-      <c r="H104" s="24">
-        <v>1</v>
-      </c>
-      <c r="I104" s="28"/>
+      <c r="F104" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="G104" s="32"/>
+      <c r="H104" s="30">
+        <v>1</v>
+      </c>
+      <c r="I104" s="34"/>
       <c r="J104" s="5">
         <v>0</v>
       </c>
@@ -7916,28 +8180,31 @@
       <c r="S104" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T104" s="37" t="s">
+        <v>325</v>
+      </c>
       <c r="V104" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="105" s="5" customFormat="1" spans="2:22">
-      <c r="B105" s="26">
+      <c r="B105" s="32">
         <v>5041</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="E105" s="5">
         <v>5</v>
       </c>
-      <c r="F105" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="G105" s="26"/>
-      <c r="H105" s="24">
-        <v>1</v>
-      </c>
-      <c r="I105" s="28"/>
+      <c r="F105" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="G105" s="32"/>
+      <c r="H105" s="30">
+        <v>1</v>
+      </c>
+      <c r="I105" s="34"/>
       <c r="J105" s="5">
         <v>0</v>
       </c>
@@ -7962,28 +8229,31 @@
       <c r="S105" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T105" s="37" t="s">
+        <v>328</v>
+      </c>
       <c r="V105" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="106" s="5" customFormat="1" spans="2:22">
-      <c r="B106" s="26">
+      <c r="B106" s="32">
         <v>5042</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="E106" s="5">
         <v>5</v>
       </c>
-      <c r="F106" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="G106" s="26"/>
-      <c r="H106" s="24">
-        <v>1</v>
-      </c>
-      <c r="I106" s="28"/>
+      <c r="F106" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="G106" s="32"/>
+      <c r="H106" s="30">
+        <v>1</v>
+      </c>
+      <c r="I106" s="34"/>
       <c r="J106" s="5">
         <v>0</v>
       </c>
@@ -8008,28 +8278,31 @@
       <c r="S106" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T106" s="37" t="s">
+        <v>337</v>
+      </c>
       <c r="V106" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="107" s="5" customFormat="1" spans="2:22">
-      <c r="B107" s="26">
+      <c r="B107" s="32">
         <v>5043</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="E107" s="5">
         <v>5</v>
       </c>
-      <c r="F107" s="26" t="s">
-        <v>316</v>
-      </c>
-      <c r="G107" s="26"/>
-      <c r="H107" s="24">
-        <v>1</v>
-      </c>
-      <c r="I107" s="28"/>
+      <c r="F107" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="G107" s="32"/>
+      <c r="H107" s="30">
+        <v>1</v>
+      </c>
+      <c r="I107" s="34"/>
       <c r="J107" s="5">
         <v>0</v>
       </c>
@@ -8054,28 +8327,31 @@
       <c r="S107" s="5" t="s">
         <v>132</v>
       </c>
+      <c r="T107" s="37" t="s">
+        <v>340</v>
+      </c>
       <c r="V107" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="108" s="5" customFormat="1" spans="2:22">
-      <c r="B108" s="26">
+      <c r="B108" s="32">
         <v>5044</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="E108" s="5">
         <v>5</v>
       </c>
-      <c r="F108" s="26" t="s">
-        <v>318</v>
-      </c>
-      <c r="G108" s="26"/>
-      <c r="H108" s="24">
-        <v>1</v>
-      </c>
-      <c r="I108" s="28"/>
+      <c r="F108" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="G108" s="32"/>
+      <c r="H108" s="30">
+        <v>1</v>
+      </c>
+      <c r="I108" s="34"/>
       <c r="J108" s="5">
         <v>0</v>
       </c>
@@ -8099,6 +8375,9 @@
       </c>
       <c r="S108" s="5" t="s">
         <v>132</v>
+      </c>
+      <c r="T108" s="37" t="s">
+        <v>343</v>
       </c>
       <c r="V108" s="5">
         <v>1</v>
@@ -8109,18 +8388,18 @@
         <v>6001</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="E109" s="5">
         <v>6</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H109" s="24">
-        <v>1</v>
-      </c>
-      <c r="I109" s="28"/>
+        <v>345</v>
+      </c>
+      <c r="H109" s="30">
+        <v>1</v>
+      </c>
+      <c r="I109" s="34"/>
       <c r="J109" s="5">
         <v>0</v>
       </c>
@@ -8145,6 +8424,7 @@
       <c r="S109" s="5" t="s">
         <v>177</v>
       </c>
+      <c r="T109" s="37"/>
       <c r="V109" s="5">
         <v>0</v>
       </c>
@@ -8154,18 +8434,18 @@
         <v>6002</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="E110" s="5">
         <v>6</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H110" s="24">
-        <v>1</v>
-      </c>
-      <c r="I110" s="28"/>
+        <v>345</v>
+      </c>
+      <c r="H110" s="30">
+        <v>1</v>
+      </c>
+      <c r="I110" s="34"/>
       <c r="J110" s="5">
         <v>0</v>
       </c>
@@ -8190,32 +8470,33 @@
       <c r="S110" s="5" t="s">
         <v>180</v>
       </c>
+      <c r="T110" s="37"/>
       <c r="V110" s="5">
         <v>0</v>
       </c>
-      <c r="X110" s="25"/>
-      <c r="Y110" s="25"/>
-      <c r="Z110" s="25"/>
-      <c r="AA110" s="25"/>
-      <c r="AB110" s="25"/>
+      <c r="X110" s="31"/>
+      <c r="Y110" s="31"/>
+      <c r="Z110" s="31"/>
+      <c r="AA110" s="31"/>
+      <c r="AB110" s="31"/>
     </row>
     <row r="111" s="5" customFormat="1" spans="2:28">
       <c r="B111" s="5">
         <v>6003</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="E111" s="5">
         <v>6</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H111" s="24">
-        <v>1</v>
-      </c>
-      <c r="I111" s="28"/>
+        <v>348</v>
+      </c>
+      <c r="H111" s="30">
+        <v>1</v>
+      </c>
+      <c r="I111" s="34"/>
       <c r="J111" s="5">
         <v>0</v>
       </c>
@@ -8240,32 +8521,33 @@
       <c r="S111" s="5" t="s">
         <v>183</v>
       </c>
+      <c r="T111" s="37"/>
       <c r="V111" s="5">
         <v>0</v>
       </c>
-      <c r="X111" s="25"/>
-      <c r="Y111" s="25"/>
-      <c r="Z111" s="25"/>
-      <c r="AA111" s="25"/>
-      <c r="AB111" s="25"/>
+      <c r="X111" s="31"/>
+      <c r="Y111" s="31"/>
+      <c r="Z111" s="31"/>
+      <c r="AA111" s="31"/>
+      <c r="AB111" s="31"/>
     </row>
     <row r="112" s="5" customFormat="1" spans="2:28">
       <c r="B112" s="5">
         <v>6004</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="E112" s="5">
         <v>6</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="H112" s="24">
-        <v>1</v>
-      </c>
-      <c r="I112" s="28"/>
+        <v>350</v>
+      </c>
+      <c r="H112" s="30">
+        <v>1</v>
+      </c>
+      <c r="I112" s="34"/>
       <c r="J112" s="5">
         <v>0</v>
       </c>
@@ -8290,32 +8572,33 @@
       <c r="S112" s="5" t="s">
         <v>186</v>
       </c>
+      <c r="T112" s="37"/>
       <c r="V112" s="5">
         <v>0</v>
       </c>
-      <c r="X112" s="25"/>
-      <c r="Y112" s="25"/>
-      <c r="Z112" s="25"/>
-      <c r="AA112" s="25"/>
-      <c r="AB112" s="25"/>
+      <c r="X112" s="31"/>
+      <c r="Y112" s="31"/>
+      <c r="Z112" s="31"/>
+      <c r="AA112" s="31"/>
+      <c r="AB112" s="31"/>
     </row>
     <row r="113" s="5" customFormat="1" spans="2:28">
       <c r="B113" s="5">
         <v>6005</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="E113" s="5">
         <v>6</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="H113" s="24">
-        <v>1</v>
-      </c>
-      <c r="I113" s="28"/>
+        <v>352</v>
+      </c>
+      <c r="H113" s="30">
+        <v>1</v>
+      </c>
+      <c r="I113" s="34"/>
       <c r="J113" s="5">
         <v>0</v>
       </c>
@@ -8340,32 +8623,33 @@
       <c r="S113" s="5" t="s">
         <v>189</v>
       </c>
+      <c r="T113" s="37"/>
       <c r="V113" s="5">
         <v>0</v>
       </c>
-      <c r="X113" s="25"/>
-      <c r="Y113" s="25"/>
-      <c r="Z113" s="25"/>
-      <c r="AA113" s="25"/>
-      <c r="AB113" s="25"/>
+      <c r="X113" s="31"/>
+      <c r="Y113" s="31"/>
+      <c r="Z113" s="31"/>
+      <c r="AA113" s="31"/>
+      <c r="AB113" s="31"/>
     </row>
     <row r="114" s="5" customFormat="1" spans="2:28">
       <c r="B114" s="5">
         <v>6006</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="E114" s="5">
         <v>6</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="H114" s="24">
-        <v>1</v>
-      </c>
-      <c r="I114" s="28"/>
+        <v>354</v>
+      </c>
+      <c r="H114" s="30">
+        <v>1</v>
+      </c>
+      <c r="I114" s="34"/>
       <c r="J114" s="5">
         <v>0</v>
       </c>
@@ -8390,32 +8674,33 @@
       <c r="S114" s="5" t="s">
         <v>192</v>
       </c>
+      <c r="T114" s="37"/>
       <c r="V114" s="5">
         <v>0</v>
       </c>
-      <c r="X114" s="25"/>
-      <c r="Y114" s="25"/>
-      <c r="Z114" s="25"/>
-      <c r="AA114" s="25"/>
-      <c r="AB114" s="25"/>
+      <c r="X114" s="31"/>
+      <c r="Y114" s="31"/>
+      <c r="Z114" s="31"/>
+      <c r="AA114" s="31"/>
+      <c r="AB114" s="31"/>
     </row>
     <row r="115" s="5" customFormat="1" spans="2:28">
       <c r="B115" s="5">
         <v>6007</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="E115" s="5">
         <v>6</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="H115" s="24">
-        <v>1</v>
-      </c>
-      <c r="I115" s="28"/>
+        <v>354</v>
+      </c>
+      <c r="H115" s="30">
+        <v>1</v>
+      </c>
+      <c r="I115" s="34"/>
       <c r="J115" s="5">
         <v>0</v>
       </c>
@@ -8440,32 +8725,33 @@
       <c r="S115" s="5" t="s">
         <v>194</v>
       </c>
+      <c r="T115" s="37"/>
       <c r="V115" s="5">
         <v>0</v>
       </c>
-      <c r="X115" s="25"/>
-      <c r="Y115" s="25"/>
-      <c r="Z115" s="25"/>
-      <c r="AA115" s="25"/>
-      <c r="AB115" s="25"/>
+      <c r="X115" s="31"/>
+      <c r="Y115" s="31"/>
+      <c r="Z115" s="31"/>
+      <c r="AA115" s="31"/>
+      <c r="AB115" s="31"/>
     </row>
     <row r="116" s="5" customFormat="1" spans="2:28">
       <c r="B116" s="5">
         <v>6008</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="E116" s="5">
         <v>6</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="H116" s="24">
-        <v>1</v>
-      </c>
-      <c r="I116" s="28"/>
+        <v>357</v>
+      </c>
+      <c r="H116" s="30">
+        <v>1</v>
+      </c>
+      <c r="I116" s="34"/>
       <c r="J116" s="5">
         <v>0</v>
       </c>
@@ -8490,32 +8776,33 @@
       <c r="S116" s="5" t="s">
         <v>197</v>
       </c>
+      <c r="T116" s="37"/>
       <c r="V116" s="5">
         <v>0</v>
       </c>
-      <c r="X116" s="25"/>
-      <c r="Y116" s="25"/>
-      <c r="Z116" s="25"/>
-      <c r="AA116" s="25"/>
-      <c r="AB116" s="25"/>
+      <c r="X116" s="31"/>
+      <c r="Y116" s="31"/>
+      <c r="Z116" s="31"/>
+      <c r="AA116" s="31"/>
+      <c r="AB116" s="31"/>
     </row>
     <row r="117" s="5" customFormat="1" spans="2:28">
       <c r="B117" s="5">
         <v>6009</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="E117" s="5">
         <v>6</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H117" s="24">
-        <v>1</v>
-      </c>
-      <c r="I117" s="28"/>
+        <v>359</v>
+      </c>
+      <c r="H117" s="30">
+        <v>1</v>
+      </c>
+      <c r="I117" s="34"/>
       <c r="J117" s="5">
         <v>0</v>
       </c>
@@ -8540,32 +8827,33 @@
       <c r="S117" s="5" t="s">
         <v>200</v>
       </c>
+      <c r="T117" s="37"/>
       <c r="V117" s="5">
         <v>0</v>
       </c>
-      <c r="X117" s="25"/>
-      <c r="Y117" s="25"/>
-      <c r="Z117" s="25"/>
-      <c r="AA117" s="25"/>
-      <c r="AB117" s="25"/>
+      <c r="X117" s="31"/>
+      <c r="Y117" s="31"/>
+      <c r="Z117" s="31"/>
+      <c r="AA117" s="31"/>
+      <c r="AB117" s="31"/>
     </row>
     <row r="118" s="5" customFormat="1" spans="2:28">
       <c r="B118" s="5">
         <v>6010</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="E118" s="5">
         <v>6</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="H118" s="24">
-        <v>1</v>
-      </c>
-      <c r="I118" s="28"/>
+        <v>354</v>
+      </c>
+      <c r="H118" s="30">
+        <v>1</v>
+      </c>
+      <c r="I118" s="34"/>
       <c r="J118" s="5">
         <v>0</v>
       </c>
@@ -8590,32 +8878,33 @@
       <c r="S118" s="5" t="s">
         <v>202</v>
       </c>
+      <c r="T118" s="37"/>
       <c r="V118" s="5">
         <v>0</v>
       </c>
-      <c r="X118" s="25"/>
-      <c r="Y118" s="25"/>
-      <c r="Z118" s="25"/>
-      <c r="AA118" s="25"/>
-      <c r="AB118" s="25"/>
+      <c r="X118" s="31"/>
+      <c r="Y118" s="31"/>
+      <c r="Z118" s="31"/>
+      <c r="AA118" s="31"/>
+      <c r="AB118" s="31"/>
     </row>
     <row r="119" s="5" customFormat="1" spans="2:28">
       <c r="B119" s="5">
         <v>6011</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="E119" s="5">
         <v>6</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="H119" s="24">
-        <v>1</v>
-      </c>
-      <c r="I119" s="28"/>
+        <v>354</v>
+      </c>
+      <c r="H119" s="30">
+        <v>1</v>
+      </c>
+      <c r="I119" s="34"/>
       <c r="J119" s="5">
         <v>0</v>
       </c>
@@ -8640,32 +8929,33 @@
       <c r="S119" s="5" t="s">
         <v>204</v>
       </c>
+      <c r="T119" s="37"/>
       <c r="V119" s="5">
         <v>0</v>
       </c>
-      <c r="X119" s="25"/>
-      <c r="Y119" s="25"/>
-      <c r="Z119" s="25"/>
-      <c r="AA119" s="25"/>
-      <c r="AB119" s="25"/>
+      <c r="X119" s="31"/>
+      <c r="Y119" s="31"/>
+      <c r="Z119" s="31"/>
+      <c r="AA119" s="31"/>
+      <c r="AB119" s="31"/>
     </row>
     <row r="120" s="5" customFormat="1" spans="2:28">
       <c r="B120" s="5">
         <v>6012</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="E120" s="5">
         <v>6</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="H120" s="24">
-        <v>1</v>
-      </c>
-      <c r="I120" s="28"/>
+        <v>354</v>
+      </c>
+      <c r="H120" s="30">
+        <v>1</v>
+      </c>
+      <c r="I120" s="34"/>
       <c r="J120" s="5">
         <v>0</v>
       </c>
@@ -8690,32 +8980,33 @@
       <c r="S120" s="5" t="s">
         <v>206</v>
       </c>
+      <c r="T120" s="37"/>
       <c r="V120" s="5">
         <v>0</v>
       </c>
-      <c r="X120" s="25"/>
-      <c r="Y120" s="25"/>
-      <c r="Z120" s="25"/>
-      <c r="AA120" s="25"/>
-      <c r="AB120" s="25"/>
+      <c r="X120" s="31"/>
+      <c r="Y120" s="31"/>
+      <c r="Z120" s="31"/>
+      <c r="AA120" s="31"/>
+      <c r="AB120" s="31"/>
     </row>
     <row r="121" s="5" customFormat="1" spans="2:28">
       <c r="B121" s="5">
         <v>6013</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="E121" s="5">
         <v>6</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H121" s="24">
-        <v>1</v>
-      </c>
-      <c r="I121" s="28"/>
+        <v>345</v>
+      </c>
+      <c r="H121" s="30">
+        <v>1</v>
+      </c>
+      <c r="I121" s="34"/>
       <c r="J121" s="5">
         <v>0</v>
       </c>
@@ -8740,32 +9031,33 @@
       <c r="S121" s="5" t="s">
         <v>209</v>
       </c>
+      <c r="T121" s="37"/>
       <c r="V121" s="5">
         <v>0</v>
       </c>
-      <c r="X121" s="25"/>
-      <c r="Y121" s="25"/>
-      <c r="Z121" s="25"/>
-      <c r="AA121" s="25"/>
-      <c r="AB121" s="25"/>
+      <c r="X121" s="31"/>
+      <c r="Y121" s="31"/>
+      <c r="Z121" s="31"/>
+      <c r="AA121" s="31"/>
+      <c r="AB121" s="31"/>
     </row>
     <row r="122" s="5" customFormat="1" spans="2:28">
       <c r="B122" s="5">
         <v>6014</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="E122" s="5">
         <v>6</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H122" s="24">
-        <v>1</v>
-      </c>
-      <c r="I122" s="28"/>
+        <v>365</v>
+      </c>
+      <c r="H122" s="30">
+        <v>1</v>
+      </c>
+      <c r="I122" s="34"/>
       <c r="J122" s="5">
         <v>0</v>
       </c>
@@ -8790,32 +9082,33 @@
       <c r="S122" s="5" t="s">
         <v>212</v>
       </c>
+      <c r="T122" s="37"/>
       <c r="V122" s="5">
         <v>0</v>
       </c>
-      <c r="X122" s="25"/>
-      <c r="Y122" s="25"/>
-      <c r="Z122" s="25"/>
-      <c r="AA122" s="25"/>
-      <c r="AB122" s="25"/>
+      <c r="X122" s="31"/>
+      <c r="Y122" s="31"/>
+      <c r="Z122" s="31"/>
+      <c r="AA122" s="31"/>
+      <c r="AB122" s="31"/>
     </row>
     <row r="123" s="5" customFormat="1" spans="2:28">
       <c r="B123" s="5">
         <v>6015</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="E123" s="5">
         <v>6</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H123" s="24">
-        <v>1</v>
-      </c>
-      <c r="I123" s="28"/>
+        <v>345</v>
+      </c>
+      <c r="H123" s="30">
+        <v>1</v>
+      </c>
+      <c r="I123" s="34"/>
       <c r="J123" s="5">
         <v>0</v>
       </c>
@@ -8840,46 +9133,47 @@
       <c r="S123" s="5" t="s">
         <v>214</v>
       </c>
+      <c r="T123" s="37"/>
       <c r="V123" s="5">
         <v>0</v>
       </c>
-      <c r="X123" s="25"/>
-      <c r="Y123" s="25"/>
-      <c r="Z123" s="25"/>
-      <c r="AA123" s="25"/>
-      <c r="AB123" s="25"/>
+      <c r="X123" s="31"/>
+      <c r="Y123" s="31"/>
+      <c r="Z123" s="31"/>
+      <c r="AA123" s="31"/>
+      <c r="AB123" s="31"/>
     </row>
     <row r="124" s="5" customFormat="1" spans="1:28">
-      <c r="A124" s="24"/>
-      <c r="B124" s="24">
+      <c r="A124" s="30"/>
+      <c r="B124" s="30">
         <v>7001</v>
       </c>
-      <c r="C124" s="26" t="s">
-        <v>342</v>
+      <c r="C124" s="32" t="s">
+        <v>367</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E124" s="24">
+      <c r="E124" s="30">
         <v>7</v>
       </c>
-      <c r="F124" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="G124" s="26" t="s">
-        <v>344</v>
-      </c>
-      <c r="H124" s="24">
-        <v>1</v>
-      </c>
-      <c r="I124" s="28"/>
+      <c r="F124" s="30" t="s">
+        <v>368</v>
+      </c>
+      <c r="G124" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="H124" s="30">
+        <v>1</v>
+      </c>
+      <c r="I124" s="34"/>
       <c r="J124" s="5">
         <v>0</v>
       </c>
       <c r="K124" s="5">
         <v>0</v>
       </c>
-      <c r="L124" s="24">
+      <c r="L124" s="30">
         <v>0</v>
       </c>
       <c r="M124" s="5">
@@ -8894,52 +9188,52 @@
       <c r="P124" s="5">
         <v>1</v>
       </c>
-      <c r="Q124" s="24"/>
-      <c r="R124" s="24"/>
-      <c r="S124" s="24"/>
-      <c r="T124" s="24"/>
-      <c r="U124" s="24"/>
+      <c r="Q124" s="30"/>
+      <c r="R124" s="30"/>
+      <c r="S124" s="30"/>
+      <c r="T124" s="36"/>
+      <c r="U124" s="30"/>
       <c r="V124" s="5">
         <v>0</v>
       </c>
-      <c r="W124" s="24"/>
-      <c r="X124" s="25"/>
-      <c r="Y124" s="25"/>
-      <c r="Z124" s="25"/>
-      <c r="AA124" s="25"/>
-      <c r="AB124" s="25"/>
+      <c r="W124" s="30"/>
+      <c r="X124" s="31"/>
+      <c r="Y124" s="31"/>
+      <c r="Z124" s="31"/>
+      <c r="AA124" s="31"/>
+      <c r="AB124" s="31"/>
     </row>
     <row r="125" s="5" customFormat="1" spans="1:28">
-      <c r="A125" s="24"/>
-      <c r="B125" s="24">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30">
         <v>7002</v>
       </c>
-      <c r="C125" s="26" t="s">
-        <v>345</v>
+      <c r="C125" s="32" t="s">
+        <v>370</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E125" s="24">
+      <c r="E125" s="30">
         <v>7</v>
       </c>
-      <c r="F125" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="G125" s="26" t="s">
-        <v>347</v>
-      </c>
-      <c r="H125" s="24">
-        <v>1</v>
-      </c>
-      <c r="I125" s="28"/>
+      <c r="F125" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="G125" s="32" t="s">
+        <v>372</v>
+      </c>
+      <c r="H125" s="30">
+        <v>1</v>
+      </c>
+      <c r="I125" s="34"/>
       <c r="J125" s="5">
         <v>0</v>
       </c>
       <c r="K125" s="5">
         <v>0</v>
       </c>
-      <c r="L125" s="24">
+      <c r="L125" s="30">
         <v>0</v>
       </c>
       <c r="M125" s="5">
@@ -8954,52 +9248,52 @@
       <c r="P125" s="5">
         <v>1</v>
       </c>
-      <c r="Q125" s="24"/>
-      <c r="R125" s="24"/>
-      <c r="S125" s="24"/>
-      <c r="T125" s="24"/>
-      <c r="U125" s="24"/>
+      <c r="Q125" s="30"/>
+      <c r="R125" s="30"/>
+      <c r="S125" s="30"/>
+      <c r="T125" s="36"/>
+      <c r="U125" s="30"/>
       <c r="V125" s="5">
         <v>0</v>
       </c>
-      <c r="W125" s="24"/>
-      <c r="X125" s="25"/>
-      <c r="Y125" s="25"/>
-      <c r="Z125" s="25"/>
-      <c r="AA125" s="25"/>
-      <c r="AB125" s="25"/>
+      <c r="W125" s="30"/>
+      <c r="X125" s="31"/>
+      <c r="Y125" s="31"/>
+      <c r="Z125" s="31"/>
+      <c r="AA125" s="31"/>
+      <c r="AB125" s="31"/>
     </row>
     <row r="126" s="5" customFormat="1" spans="1:28">
-      <c r="A126" s="24"/>
-      <c r="B126" s="24">
+      <c r="A126" s="30"/>
+      <c r="B126" s="30">
         <v>7003</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E126" s="24">
+      <c r="E126" s="30">
       